--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4793" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91AC18CE-5373-4274-8C86-DE9552FD1390}"/>
+  <xr:revisionPtr revIDLastSave="4885" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B68FE8E-29DA-429B-AF65-C9F46B050110}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -23,73 +23,73 @@
     <sheet name="Dashboard Maratonas" sheetId="27" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ações InCompany'!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ações InCompany'!$A$1:$A$748</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Ações InCompany'!$A$1:$T$676</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6494" uniqueCount="2944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6527" uniqueCount="2956">
   <si>
     <t>ID</t>
   </si>
@@ -8413,28 +8413,37 @@
     <t>21 e 22/05/2026</t>
   </si>
   <si>
+    <t>Em andamento</t>
+  </si>
+  <si>
+    <t>4141/2026</t>
+  </si>
+  <si>
+    <t>Fiscalizações Baseadas em Risco</t>
+  </si>
+  <si>
+    <t>08 a 12/06/2026</t>
+  </si>
+  <si>
+    <t>Reinaldo Alencar; Rogério Ribeiro</t>
+  </si>
+  <si>
+    <t>3685/2026</t>
+  </si>
+  <si>
+    <t>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T2</t>
+  </si>
+  <si>
+    <t>09 a 11/06/2026</t>
+  </si>
+  <si>
     <t>A realizar</t>
   </si>
   <si>
-    <t>4141/2026</t>
-  </si>
-  <si>
-    <t>Fiscalizações Baseadas em Risco</t>
-  </si>
-  <si>
-    <t>08 a 12/06/2026</t>
-  </si>
-  <si>
-    <t>Reinaldo Alencar; Rogério Ribeiro</t>
-  </si>
-  <si>
-    <t>3685/2026</t>
-  </si>
-  <si>
-    <t>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T2</t>
-  </si>
-  <si>
-    <t>09 a 11/06/2026</t>
+    <t>Escola de Instrutores - Design Instrucional</t>
+  </si>
+  <si>
+    <t>16 a 18/06/2026</t>
   </si>
   <si>
     <t>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T3</t>
@@ -8611,6 +8620,33 @@
     <t>André Pachioni Baeta</t>
   </si>
   <si>
+    <t>6371/2026</t>
+  </si>
+  <si>
+    <t>Painel MROSC</t>
+  </si>
+  <si>
+    <t>20/07/2026</t>
+  </si>
+  <si>
+    <t>6414/2026</t>
+  </si>
+  <si>
+    <t>31º SEMAT</t>
+  </si>
+  <si>
+    <t>3 e 4/08/2026</t>
+  </si>
+  <si>
+    <t>6503/2026</t>
+  </si>
+  <si>
+    <t>Curso “Sisaudit na Prática”</t>
+  </si>
+  <si>
+    <t>Davi Assunção Salvador Nery de Castro; David da Silva de Araújo; Hamilton de Jesus Lopes Neto</t>
+  </si>
+  <si>
     <t>ID Ação</t>
   </si>
   <si>
@@ -8755,6 +8791,9 @@
     <t>2026-042</t>
   </si>
   <si>
+    <t>2026-044</t>
+  </si>
+  <si>
     <t>DASHBOARD DE CURSOS — 2026</t>
   </si>
   <si>
@@ -8909,9 +8948,6 @@
   </si>
   <si>
     <t>Solicitado</t>
-  </si>
-  <si>
-    <t>Em andamento</t>
   </si>
   <si>
     <t>2026/2027</t>
@@ -8996,10 +9032,10 @@
     <t>Participantes</t>
   </si>
   <si>
-    <t>Escola de Instrutores - Design Instrucional</t>
-  </si>
-  <si>
-    <t>16 a 18/06/2026</t>
+    <t>teste</t>
+  </si>
+  <si>
+    <t>03/06/2026</t>
   </si>
 </sst>
 </file>
@@ -12229,10 +12265,10 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>13</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -12458,10 +12494,10 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>400</c:v>
+                  <c:v>417</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>371</c:v>
+                  <c:v>403</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>370</c:v>
@@ -12810,13 +12846,13 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -12911,7 +12947,7 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -12935,7 +12971,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -14914,7 +14950,27 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}" name="Tabela2" displayName="Tabela2" ref="B1:T684" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48" totalsRowBorderDxfId="47">
-  <autoFilter ref="B1:T684" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}"/>
+  <autoFilter ref="B1:T684" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+    <filterColumn colId="16" hiddenButton="1"/>
+    <filterColumn colId="17" hiddenButton="1"/>
+    <filterColumn colId="18" hiddenButton="1"/>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:T684">
     <sortCondition ref="I1:I684"/>
   </sortState>
@@ -33822,7 +33878,7 @@
       <c r="S312" s="22">
         <v>75</v>
       </c>
-      <c r="T312" s="20" t="s">
+      <c r="T312" s="54" t="s">
         <v>1326</v>
       </c>
     </row>
@@ -38445,7 +38501,7 @@
         <v>0</v>
       </c>
       <c r="R386" s="23">
-        <f t="shared" ref="R386:R392" si="6">SUM(O386:Q386)</f>
+        <f t="shared" ref="R386:R449" si="6">SUM(O386:Q386)</f>
         <v>49</v>
       </c>
       <c r="S386" s="22">
@@ -50914,7 +50970,7 @@
         <v>30</v>
       </c>
       <c r="R586" s="23">
-        <f t="shared" ref="R586:R640" si="10">SUM(O586:Q586)</f>
+        <f t="shared" ref="R586:R649" si="10">SUM(O586:Q586)</f>
         <v>30</v>
       </c>
       <c r="S586" s="22">
@@ -56544,7 +56600,7 @@
         <v>2026</v>
       </c>
       <c r="C678" s="274" t="s">
-        <v>2748</v>
+        <v>21</v>
       </c>
       <c r="D678" s="64" t="s">
         <v>2749</v>
@@ -56573,16 +56629,24 @@
       <c r="L678" s="199">
         <v>16717.689999999999</v>
       </c>
-      <c r="M678" s="198"/>
+      <c r="M678" s="198">
+        <v>4.93</v>
+      </c>
       <c r="N678" s="62">
         <v>20</v>
       </c>
-      <c r="O678" s="63"/>
-      <c r="P678" s="63"/>
-      <c r="Q678" s="63"/>
+      <c r="O678" s="63">
+        <v>17</v>
+      </c>
+      <c r="P678" s="63">
+        <v>0</v>
+      </c>
+      <c r="Q678" s="63">
+        <v>0</v>
+      </c>
       <c r="R678" s="63">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S678" s="64">
         <v>20</v>
@@ -56600,7 +56664,7 @@
         <v>2026</v>
       </c>
       <c r="C679" s="70" t="s">
-        <v>2748</v>
+        <v>21</v>
       </c>
       <c r="D679" s="180" t="s">
         <v>2753</v>
@@ -56629,14 +56693,24 @@
       <c r="L679" s="71">
         <v>9211.69</v>
       </c>
-      <c r="M679" s="197"/>
-      <c r="N679" s="184"/>
-      <c r="O679" s="185"/>
-      <c r="P679" s="185"/>
-      <c r="Q679" s="185"/>
+      <c r="M679" s="197">
+        <v>4.82</v>
+      </c>
+      <c r="N679" s="184">
+        <v>30</v>
+      </c>
+      <c r="O679" s="185">
+        <v>0</v>
+      </c>
+      <c r="P679" s="185">
+        <v>32</v>
+      </c>
+      <c r="Q679" s="185">
+        <v>0</v>
+      </c>
       <c r="R679" s="185">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="S679" s="180">
         <v>12</v>
@@ -56654,13 +56728,13 @@
         <v>2026</v>
       </c>
       <c r="C680" s="228" t="s">
-        <v>2748</v>
+        <v>2756</v>
       </c>
       <c r="D680" s="70" t="s">
         <v>2742</v>
       </c>
       <c r="E680" s="65" t="s">
-        <v>2942</v>
+        <v>2757</v>
       </c>
       <c r="F680" s="29" t="s">
         <v>23</v>
@@ -56669,7 +56743,7 @@
         <v>2693</v>
       </c>
       <c r="H680" s="68" t="s">
-        <v>2943</v>
+        <v>2758</v>
       </c>
       <c r="I680" s="69">
         <v>46189</v>
@@ -56714,7 +56788,7 @@
         <v>2753</v>
       </c>
       <c r="E681" s="273" t="s">
-        <v>2756</v>
+        <v>2759</v>
       </c>
       <c r="F681" s="31" t="s">
         <v>61</v>
@@ -56723,7 +56797,7 @@
         <v>2688</v>
       </c>
       <c r="H681" s="189" t="s">
-        <v>2757</v>
+        <v>2760</v>
       </c>
       <c r="I681" s="190">
         <v>46189</v>
@@ -56762,13 +56836,13 @@
         <v>2026</v>
       </c>
       <c r="C682" s="70" t="s">
-        <v>2748</v>
+        <v>2756</v>
       </c>
       <c r="D682" s="180" t="s">
-        <v>2758</v>
+        <v>2761</v>
       </c>
       <c r="E682" s="164" t="s">
-        <v>2759</v>
+        <v>2762</v>
       </c>
       <c r="F682" s="29" t="s">
         <v>61</v>
@@ -56777,7 +56851,7 @@
         <v>2688</v>
       </c>
       <c r="H682" s="182" t="s">
-        <v>2760</v>
+        <v>2763</v>
       </c>
       <c r="I682" s="183">
         <v>46195</v>
@@ -56816,13 +56890,13 @@
         <v>2026</v>
       </c>
       <c r="C683" s="70" t="s">
-        <v>2748</v>
+        <v>2756</v>
       </c>
       <c r="D683" s="186" t="s">
-        <v>2761</v>
+        <v>2764</v>
       </c>
       <c r="E683" s="187" t="s">
-        <v>2762</v>
+        <v>2765</v>
       </c>
       <c r="F683" s="31" t="s">
         <v>61</v>
@@ -56831,7 +56905,7 @@
         <v>71</v>
       </c>
       <c r="H683" s="189" t="s">
-        <v>2763</v>
+        <v>2766</v>
       </c>
       <c r="I683" s="190">
         <v>46335</v>
@@ -56870,13 +56944,13 @@
         <v>2026</v>
       </c>
       <c r="C684" s="228" t="s">
-        <v>2764</v>
+        <v>2767</v>
       </c>
       <c r="D684" s="70" t="s">
-        <v>2765</v>
+        <v>2768</v>
       </c>
       <c r="E684" s="164" t="s">
-        <v>2766</v>
+        <v>2769</v>
       </c>
       <c r="F684" s="66" t="s">
         <v>80</v>
@@ -56908,7 +56982,7 @@
         <v>32</v>
       </c>
       <c r="T684" s="67" t="s">
-        <v>2767</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="685" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -56920,13 +56994,13 @@
         <v>2026</v>
       </c>
       <c r="C685" s="219" t="s">
-        <v>2748</v>
+        <v>2756</v>
       </c>
       <c r="D685" s="210" t="s">
-        <v>2768</v>
+        <v>2771</v>
       </c>
       <c r="E685" s="211" t="s">
-        <v>2769</v>
+        <v>2772</v>
       </c>
       <c r="F685" s="212" t="s">
         <v>61</v>
@@ -56935,7 +57009,7 @@
         <v>71</v>
       </c>
       <c r="H685" s="213" t="s">
-        <v>2770</v>
+        <v>2773</v>
       </c>
       <c r="I685" s="214">
         <v>46286</v>
@@ -56975,13 +57049,13 @@
         <v>2026</v>
       </c>
       <c r="C686" s="219" t="s">
-        <v>2764</v>
+        <v>2767</v>
       </c>
       <c r="D686" s="219" t="s">
-        <v>2771</v>
+        <v>2774</v>
       </c>
       <c r="E686" s="240" t="s">
-        <v>2772</v>
+        <v>2775</v>
       </c>
       <c r="F686" s="221" t="s">
         <v>23</v>
@@ -56990,7 +57064,7 @@
         <v>67</v>
       </c>
       <c r="H686" s="222" t="s">
-        <v>2773</v>
+        <v>2776</v>
       </c>
       <c r="I686" s="223">
         <v>46167</v>
@@ -57035,10 +57109,10 @@
         <v>2741</v>
       </c>
       <c r="D687" s="210" t="s">
-        <v>2774</v>
+        <v>2777</v>
       </c>
       <c r="E687" s="211" t="s">
-        <v>2775</v>
+        <v>2778</v>
       </c>
       <c r="F687" s="212" t="s">
         <v>23</v>
@@ -57047,7 +57121,7 @@
         <v>67</v>
       </c>
       <c r="H687" s="213" t="s">
-        <v>2776</v>
+        <v>2779</v>
       </c>
       <c r="I687" s="214">
         <v>46174</v>
@@ -57074,7 +57148,7 @@
         <v>25</v>
       </c>
       <c r="T687" t="s">
-        <v>2777</v>
+        <v>2780</v>
       </c>
       <c r="U687" s="203"/>
     </row>
@@ -57087,13 +57161,13 @@
         <v>2026</v>
       </c>
       <c r="C688" s="219" t="s">
-        <v>2748</v>
+        <v>2756</v>
       </c>
       <c r="D688" s="219" t="s">
-        <v>2778</v>
+        <v>2781</v>
       </c>
       <c r="E688" s="240" t="s">
-        <v>2779</v>
+        <v>2782</v>
       </c>
       <c r="F688" s="221" t="s">
         <v>80</v>
@@ -57102,7 +57176,7 @@
         <v>2725</v>
       </c>
       <c r="H688" s="222" t="s">
-        <v>2780</v>
+        <v>2783</v>
       </c>
       <c r="I688" s="223">
         <v>46204</v>
@@ -57147,10 +57221,10 @@
         <v>21</v>
       </c>
       <c r="D689" s="210" t="s">
-        <v>2781</v>
+        <v>2784</v>
       </c>
       <c r="E689" s="245" t="s">
-        <v>2782</v>
+        <v>2785</v>
       </c>
       <c r="F689" s="212" t="s">
         <v>23</v>
@@ -57159,7 +57233,7 @@
         <v>2709</v>
       </c>
       <c r="H689" s="247" t="s">
-        <v>2783</v>
+        <v>2786</v>
       </c>
       <c r="I689" s="214">
         <v>46154</v>
@@ -57171,7 +57245,7 @@
         <v>34</v>
       </c>
       <c r="L689" s="26">
-        <v>9067.76</v>
+        <v>6497.28</v>
       </c>
       <c r="M689" s="215">
         <v>4.88</v>
@@ -57209,13 +57283,13 @@
         <v>2026</v>
       </c>
       <c r="C690" s="219" t="s">
-        <v>2748</v>
+        <v>2756</v>
       </c>
       <c r="D690" s="219" t="s">
-        <v>2781</v>
+        <v>2784</v>
       </c>
       <c r="E690" s="246" t="s">
-        <v>2784</v>
+        <v>2787</v>
       </c>
       <c r="F690" s="221" t="s">
         <v>23</v>
@@ -57224,7 +57298,7 @@
         <v>2709</v>
       </c>
       <c r="H690" s="248" t="s">
-        <v>2785</v>
+        <v>2788</v>
       </c>
       <c r="I690" s="223">
         <v>46196</v>
@@ -57236,7 +57310,7 @@
         <v>34</v>
       </c>
       <c r="L690" s="26">
-        <v>9067.76</v>
+        <v>6497.28</v>
       </c>
       <c r="M690" s="215"/>
       <c r="N690" s="226">
@@ -57269,7 +57343,7 @@
         <v>21</v>
       </c>
       <c r="D691" s="210" t="s">
-        <v>2786</v>
+        <v>2789</v>
       </c>
       <c r="E691" s="245" t="s">
         <v>2667</v>
@@ -57281,7 +57355,7 @@
         <v>37</v>
       </c>
       <c r="H691" s="213" t="s">
-        <v>2787</v>
+        <v>2790</v>
       </c>
       <c r="I691" s="214">
         <v>46160</v>
@@ -57334,10 +57408,10 @@
         <v>21</v>
       </c>
       <c r="D692" s="219" t="s">
-        <v>2788</v>
+        <v>2791</v>
       </c>
       <c r="E692" s="246" t="s">
-        <v>2789</v>
+        <v>2792</v>
       </c>
       <c r="F692" s="221" t="s">
         <v>23</v>
@@ -57346,7 +57420,7 @@
         <v>363</v>
       </c>
       <c r="H692" s="222" t="s">
-        <v>2790</v>
+        <v>2793</v>
       </c>
       <c r="I692" s="223">
         <v>46140</v>
@@ -57399,10 +57473,10 @@
         <v>21</v>
       </c>
       <c r="D693" s="210" t="s">
-        <v>2791</v>
+        <v>2794</v>
       </c>
       <c r="E693" s="245" t="s">
-        <v>2792</v>
+        <v>2795</v>
       </c>
       <c r="F693" s="212" t="s">
         <v>23</v>
@@ -57411,7 +57485,7 @@
         <v>24</v>
       </c>
       <c r="H693" s="213" t="s">
-        <v>2793</v>
+        <v>2796</v>
       </c>
       <c r="I693" s="214">
         <v>46148</v>
@@ -57448,7 +57522,7 @@
         <v>12</v>
       </c>
       <c r="T693" s="209" t="s">
-        <v>2794</v>
+        <v>2797</v>
       </c>
       <c r="U693" s="203"/>
     </row>
@@ -57461,13 +57535,13 @@
         <v>2026</v>
       </c>
       <c r="C694" s="219" t="s">
-        <v>2748</v>
+        <v>2756</v>
       </c>
       <c r="D694" s="219" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="E694" s="220" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="F694" s="221" t="s">
         <v>61</v>
@@ -57476,7 +57550,7 @@
         <v>2688</v>
       </c>
       <c r="H694" s="222" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="I694" s="223">
         <v>46157</v>
@@ -57514,13 +57588,13 @@
         <v>2026</v>
       </c>
       <c r="C695" s="219" t="s">
-        <v>2748</v>
+        <v>2756</v>
       </c>
       <c r="D695" s="210" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E695" s="211" t="s">
-        <v>2799</v>
+        <v>2802</v>
       </c>
       <c r="F695" s="212" t="s">
         <v>80</v>
@@ -57529,7 +57603,7 @@
         <v>2725</v>
       </c>
       <c r="H695" s="213" t="s">
-        <v>2800</v>
+        <v>2803</v>
       </c>
       <c r="I695" s="214">
         <v>46223</v>
@@ -57570,10 +57644,10 @@
         <v>21</v>
       </c>
       <c r="D696" s="219" t="s">
-        <v>2801</v>
+        <v>2804</v>
       </c>
       <c r="E696" s="220" t="s">
-        <v>2802</v>
+        <v>2805</v>
       </c>
       <c r="F696" s="221" t="s">
         <v>80</v>
@@ -57582,7 +57656,7 @@
         <v>2725</v>
       </c>
       <c r="H696" s="222" t="s">
-        <v>2803</v>
+        <v>2806</v>
       </c>
       <c r="I696" s="223">
         <v>46167</v>
@@ -57627,10 +57701,10 @@
         <v>21</v>
       </c>
       <c r="D697" s="210" t="s">
-        <v>2804</v>
+        <v>2807</v>
       </c>
       <c r="E697" s="211" t="s">
-        <v>2805</v>
+        <v>2808</v>
       </c>
       <c r="F697" s="212" t="s">
         <v>80</v>
@@ -57639,7 +57713,7 @@
         <v>2725</v>
       </c>
       <c r="H697" s="213" t="s">
-        <v>2806</v>
+        <v>2809</v>
       </c>
       <c r="I697" s="214">
         <v>46148</v>
@@ -57672,7 +57746,7 @@
         <v>3</v>
       </c>
       <c r="T697" s="209" t="s">
-        <v>2807</v>
+        <v>2810</v>
       </c>
       <c r="U697" s="203"/>
     </row>
@@ -57685,13 +57759,13 @@
         <v>2026</v>
       </c>
       <c r="C698" s="219" t="s">
-        <v>2748</v>
+        <v>2756</v>
       </c>
       <c r="D698" s="219" t="s">
-        <v>2808</v>
+        <v>2811</v>
       </c>
       <c r="E698" s="220" t="s">
-        <v>2809</v>
+        <v>2812</v>
       </c>
       <c r="F698" s="221" t="s">
         <v>23</v>
@@ -57700,7 +57774,7 @@
         <v>24</v>
       </c>
       <c r="H698" s="222" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="I698" s="223">
         <v>46204</v>
@@ -57738,13 +57812,13 @@
         <v>2026</v>
       </c>
       <c r="C699" s="219" t="s">
-        <v>2748</v>
+        <v>2756</v>
       </c>
       <c r="D699" s="210" t="s">
-        <v>2810</v>
+        <v>2813</v>
       </c>
       <c r="E699" s="211" t="s">
-        <v>2811</v>
+        <v>2814</v>
       </c>
       <c r="F699" s="212" t="s">
         <v>23</v>
@@ -57753,7 +57827,7 @@
         <v>67</v>
       </c>
       <c r="H699" s="213" t="s">
-        <v>2812</v>
+        <v>2815</v>
       </c>
       <c r="I699" s="214">
         <v>46244</v>
@@ -57780,121 +57854,215 @@
         <v>10</v>
       </c>
       <c r="T699" s="209" t="s">
-        <v>2813</v>
+        <v>2816</v>
       </c>
       <c r="U699" s="203"/>
     </row>
     <row r="700" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="218" t="str">
         <f>IF(B700="","",B700&amp;"-"&amp;TEXT(COUNTIF(B$2:B700,B700),"000"))</f>
-        <v/>
-      </c>
-      <c r="B700" s="219"/>
-      <c r="C700" s="219"/>
-      <c r="D700" s="219"/>
-      <c r="E700" s="220"/>
-      <c r="F700" s="221"/>
-      <c r="G700" s="218"/>
-      <c r="H700" s="222"/>
-      <c r="I700" s="223"/>
-      <c r="J700" s="223"/>
-      <c r="K700" s="219"/>
-      <c r="L700" s="224"/>
+        <v>2026-044</v>
+      </c>
+      <c r="B700" s="219">
+        <v>2026</v>
+      </c>
+      <c r="C700" s="219" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D700" s="219" t="s">
+        <v>2817</v>
+      </c>
+      <c r="E700" s="220" t="s">
+        <v>2818</v>
+      </c>
+      <c r="F700" s="221" t="s">
+        <v>61</v>
+      </c>
+      <c r="G700" s="218" t="s">
+        <v>71</v>
+      </c>
+      <c r="H700" s="222" t="s">
+        <v>2819</v>
+      </c>
+      <c r="I700" s="223">
+        <v>46223</v>
+      </c>
+      <c r="J700" s="223">
+        <v>46223</v>
+      </c>
+      <c r="K700" s="219" t="s">
+        <v>34</v>
+      </c>
+      <c r="L700" s="224">
+        <v>0</v>
+      </c>
       <c r="M700" s="215"/>
       <c r="N700" s="226"/>
       <c r="O700" s="225"/>
       <c r="P700" s="225"/>
       <c r="Q700" s="225"/>
-      <c r="R700" s="225" t="str">
+      <c r="R700" s="225">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="S700" s="219"/>
-      <c r="T700" s="218"/>
+        <v>0</v>
+      </c>
+      <c r="S700" s="219">
+        <v>4</v>
+      </c>
+      <c r="T700" s="218" t="s">
+        <v>471</v>
+      </c>
       <c r="U700" s="203"/>
     </row>
     <row r="701" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="209" t="str">
         <f>IF(B701="","",B701&amp;"-"&amp;TEXT(COUNTIF(B$2:B701,B701),"000"))</f>
-        <v/>
-      </c>
-      <c r="B701" s="210"/>
-      <c r="C701" s="219"/>
-      <c r="D701" s="210"/>
-      <c r="E701" s="211"/>
-      <c r="F701" s="212"/>
-      <c r="G701" s="209"/>
-      <c r="H701" s="213"/>
-      <c r="I701" s="214"/>
-      <c r="J701" s="214"/>
-      <c r="K701" s="210"/>
+        <v>2026-045</v>
+      </c>
+      <c r="B701" s="210">
+        <v>2026</v>
+      </c>
+      <c r="C701" s="219" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D701" s="210" t="s">
+        <v>2820</v>
+      </c>
+      <c r="E701" s="211" t="s">
+        <v>2821</v>
+      </c>
+      <c r="F701" s="212" t="s">
+        <v>61</v>
+      </c>
+      <c r="G701" s="209" t="s">
+        <v>71</v>
+      </c>
+      <c r="H701" s="213" t="s">
+        <v>2822</v>
+      </c>
+      <c r="I701" s="214">
+        <v>46237</v>
+      </c>
+      <c r="J701" s="214">
+        <v>46238</v>
+      </c>
+      <c r="K701" s="210" t="s">
+        <v>34</v>
+      </c>
       <c r="L701" s="224"/>
       <c r="M701" s="215"/>
-      <c r="N701" s="216"/>
+      <c r="N701" s="216">
+        <v>400</v>
+      </c>
       <c r="O701" s="217"/>
       <c r="P701" s="217"/>
       <c r="Q701" s="217"/>
-      <c r="R701" s="217" t="str">
+      <c r="R701" s="217">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="S701" s="210"/>
+        <v>0</v>
+      </c>
+      <c r="S701" s="210">
+        <v>8</v>
+      </c>
       <c r="T701" s="209"/>
       <c r="U701" s="203"/>
     </row>
     <row r="702" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="218" t="str">
         <f>IF(B702="","",B702&amp;"-"&amp;TEXT(COUNTIF(B$2:B702,B702),"000"))</f>
-        <v/>
-      </c>
-      <c r="B702" s="219"/>
-      <c r="C702" s="219"/>
-      <c r="D702" s="219"/>
-      <c r="E702" s="220"/>
-      <c r="F702" s="221"/>
-      <c r="G702" s="218"/>
-      <c r="H702" s="222"/>
-      <c r="I702" s="223"/>
-      <c r="J702" s="223"/>
-      <c r="K702" s="219"/>
+        <v>2026-046</v>
+      </c>
+      <c r="B702" s="219">
+        <v>2026</v>
+      </c>
+      <c r="C702" s="219" t="s">
+        <v>2748</v>
+      </c>
+      <c r="D702" s="219" t="s">
+        <v>2823</v>
+      </c>
+      <c r="E702" s="220" t="s">
+        <v>2824</v>
+      </c>
+      <c r="F702" s="221" t="s">
+        <v>23</v>
+      </c>
+      <c r="G702" s="218" t="s">
+        <v>24</v>
+      </c>
+      <c r="H702" s="222" t="s">
+        <v>2758</v>
+      </c>
+      <c r="I702" s="223">
+        <v>46189</v>
+      </c>
+      <c r="J702" s="223">
+        <v>46191</v>
+      </c>
+      <c r="K702" s="219" t="s">
+        <v>34</v>
+      </c>
       <c r="L702" s="224"/>
       <c r="M702" s="215"/>
       <c r="N702" s="226"/>
       <c r="O702" s="225"/>
       <c r="P702" s="225"/>
       <c r="Q702" s="225"/>
-      <c r="R702" s="225" t="str">
+      <c r="R702" s="225">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="S702" s="219"/>
-      <c r="T702" s="218"/>
+        <v>0</v>
+      </c>
+      <c r="S702" s="219">
+        <v>12</v>
+      </c>
+      <c r="T702" s="218" t="s">
+        <v>2825</v>
+      </c>
       <c r="U702" s="203"/>
     </row>
     <row r="703" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="209" t="str">
         <f>IF(B703="","",B703&amp;"-"&amp;TEXT(COUNTIF(B$2:B703,B703),"000"))</f>
-        <v/>
-      </c>
-      <c r="B703" s="210"/>
-      <c r="C703" s="219"/>
+        <v>2026-047</v>
+      </c>
+      <c r="B703" s="210">
+        <v>2026</v>
+      </c>
+      <c r="C703" s="219" t="s">
+        <v>2756</v>
+      </c>
       <c r="D703" s="210"/>
-      <c r="E703" s="211"/>
-      <c r="F703" s="212"/>
-      <c r="G703" s="209"/>
-      <c r="H703" s="213"/>
-      <c r="I703" s="214"/>
-      <c r="J703" s="214"/>
-      <c r="K703" s="210"/>
-      <c r="L703" s="224"/>
+      <c r="E703" s="211" t="s">
+        <v>2954</v>
+      </c>
+      <c r="F703" s="212" t="s">
+        <v>23</v>
+      </c>
+      <c r="G703" s="209" t="s">
+        <v>24</v>
+      </c>
+      <c r="H703" s="213" t="s">
+        <v>2955</v>
+      </c>
+      <c r="I703" s="213" t="s">
+        <v>2955</v>
+      </c>
+      <c r="J703" s="213" t="s">
+        <v>2955</v>
+      </c>
+      <c r="K703" s="210" t="s">
+        <v>34</v>
+      </c>
+      <c r="L703" s="224">
+        <v>1000</v>
+      </c>
       <c r="M703" s="215"/>
       <c r="N703" s="216"/>
       <c r="O703" s="217"/>
       <c r="P703" s="217"/>
       <c r="Q703" s="217"/>
-      <c r="R703" s="217" t="str">
+      <c r="R703" s="217">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S703" s="210"/>
       <c r="T703" s="209"/>
@@ -59229,6 +59397,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:A748" xr:uid="{9A950031-0FEE-4C02-A480-D14B9CA90666}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:T676">
     <sortCondition ref="B2:B676"/>
   </sortState>
@@ -59289,7 +59458,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Clique e insira um valor de a lista de itens" sqref="F518" xr:uid="{04F4F39B-F406-4ECC-A64A-F7A18A81A48D}">
       <formula1>"Interno,Externo,Híbrido"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Erro" error="Insira uma data válida. Formato: DD/MM/AAAA" sqref="I594:J594 I647:J648 I658:J658 I662:J662 I664:I673 I644:J645 I596:J640 I573:J590 I463:J571 I2:J460 I676:J676 J664:J674 I681:J1048576" xr:uid="{A71E4390-A059-418C-8F5C-AD2AF445253E}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Erro" error="Insira uma data válida. Formato: DD/MM/AAAA" sqref="I594:J594 I647:J648 I658:J658 I662:J662 I664:I673 I644:J645 I596:J640 I573:J590 I463:J571 I2:J460 I676:J676 J664:J674 I681:J702 I704:J1048576" xr:uid="{A71E4390-A059-418C-8F5C-AD2AF445253E}">
       <formula1>41640</formula1>
       <formula2>47848</formula2>
     </dataValidation>
@@ -59378,55 +59547,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="96" t="s">
-        <v>2814</v>
+        <v>2826</v>
       </c>
       <c r="C1" s="96" t="s">
-        <v>2815</v>
+        <v>2827</v>
       </c>
       <c r="D1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>2816</v>
+        <v>2828</v>
       </c>
       <c r="F1" s="96" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="96" t="s">
-        <v>2817</v>
+        <v>2829</v>
       </c>
       <c r="H1" s="96" t="s">
-        <v>2818</v>
+        <v>2830</v>
       </c>
       <c r="I1" s="96" t="s">
-        <v>2819</v>
+        <v>2831</v>
       </c>
       <c r="J1" s="96" t="s">
-        <v>2820</v>
+        <v>2832</v>
       </c>
       <c r="L1" s="129" t="s">
-        <v>2821</v>
+        <v>2833</v>
       </c>
       <c r="M1" s="100">
         <v>2026</v>
       </c>
       <c r="U1" s="162" t="s">
-        <v>2822</v>
+        <v>2834</v>
       </c>
       <c r="V1" s="161"/>
       <c r="X1" s="159" t="s">
-        <v>2823</v>
+        <v>2835</v>
       </c>
       <c r="Y1" s="107"/>
       <c r="Z1" s="107"/>
       <c r="AA1" s="107"/>
       <c r="AC1" s="254" t="s">
-        <v>2824</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="98" cm="1">
-        <f t="array" ref="A2:J64">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
+        <f t="array" ref="A2:J70">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
         <v>2026</v>
       </c>
       <c r="B2" s="98" t="str">
@@ -59457,25 +59626,25 @@
         <v>10.4</v>
       </c>
       <c r="X2" s="160" t="s">
-        <v>2814</v>
+        <v>2826</v>
       </c>
       <c r="Y2" s="160" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="160" t="s">
-        <v>2825</v>
+        <v>2837</v>
       </c>
       <c r="AA2" s="160" t="s">
-        <v>2826</v>
+        <v>2838</v>
       </c>
       <c r="AC2" s="255" t="s">
         <v>1</v>
       </c>
       <c r="AD2" s="255" t="s">
-        <v>2827</v>
+        <v>2839</v>
       </c>
       <c r="AE2" s="255" t="s">
-        <v>2828</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -59510,34 +59679,34 @@
         <v>5.2</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>2829</v>
+        <v>2841</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>2830</v>
+        <v>2842</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>2831</v>
+        <v>2843</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>2832</v>
+        <v>2844</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>2833</v>
+        <v>2845</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>2834</v>
+        <v>2846</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>2835</v>
+        <v>2847</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>2836</v>
+        <v>2848</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>2837</v>
+        <v>2849</v>
       </c>
       <c r="X3" t="s">
-        <v>2838</v>
+        <v>2850</v>
       </c>
       <c r="Y3" t="s">
         <v>2695</v>
@@ -59590,7 +59759,7 @@
         <v>5.2</v>
       </c>
       <c r="L4" cm="1">
-        <f t="array" ref="L4:Q35">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
+        <f t="array" ref="L4:Q39">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
         <v>2026</v>
       </c>
       <c r="M4" t="str">
@@ -59617,11 +59786,11 @@
         <v>1</v>
       </c>
       <c r="T4" cm="1">
-        <f t="array" ref="T4:T36">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
+        <f t="array" ref="T4:T40">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>2839</v>
+        <v>2851</v>
       </c>
       <c r="Y4" t="s">
         <v>2695</v>
@@ -59701,7 +59870,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>2840</v>
+        <v>2852</v>
       </c>
       <c r="Y5" t="s">
         <v>2711</v>
@@ -59716,7 +59885,7 @@
         <v>2026</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>2841</v>
+        <v>2853</v>
       </c>
       <c r="AE5" s="250">
         <v>16</v>
@@ -59781,10 +59950,10 @@
         <v>6</v>
       </c>
       <c r="X6" t="s">
-        <v>2840</v>
+        <v>2852</v>
       </c>
       <c r="Y6" t="s">
-        <v>2842</v>
+        <v>2854</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -59796,7 +59965,7 @@
         <v>2026</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>2843</v>
+        <v>2855</v>
       </c>
       <c r="AE6" s="250">
         <v>16</v>
@@ -59861,7 +60030,7 @@
         <v>8</v>
       </c>
       <c r="X7" s="98" t="s">
-        <v>2844</v>
+        <v>2856</v>
       </c>
       <c r="Y7" t="s">
         <v>2695</v>
@@ -59941,7 +60110,7 @@
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>2845</v>
+        <v>2857</v>
       </c>
       <c r="Y8" s="95" t="s">
         <v>1342</v>
@@ -60014,7 +60183,7 @@
         <v>11</v>
       </c>
       <c r="X9" t="s">
-        <v>2845</v>
+        <v>2857</v>
       </c>
       <c r="Y9" s="95" t="s">
         <v>1022</v>
@@ -60087,7 +60256,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="s">
-        <v>2845</v>
+        <v>2857</v>
       </c>
       <c r="Y10" s="95" t="s">
         <v>1366</v>
@@ -60160,10 +60329,10 @@
         <v>14</v>
       </c>
       <c r="X11" t="s">
-        <v>2845</v>
+        <v>2857</v>
       </c>
       <c r="Y11" s="95" t="s">
-        <v>2846</v>
+        <v>2858</v>
       </c>
       <c r="AA11">
         <v>1.2</v>
@@ -60233,10 +60402,10 @@
         <v>15</v>
       </c>
       <c r="X12" t="s">
-        <v>2845</v>
+        <v>2857</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>2847</v>
+        <v>2859</v>
       </c>
       <c r="AA12">
         <v>1.2</v>
@@ -60306,7 +60475,7 @@
         <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>2848</v>
+        <v>2860</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>1342</v>
@@ -60379,7 +60548,7 @@
         <v>18</v>
       </c>
       <c r="X14" t="s">
-        <v>2848</v>
+        <v>2860</v>
       </c>
       <c r="Y14" s="95" t="s">
         <v>1022</v>
@@ -60452,7 +60621,7 @@
         <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>2848</v>
+        <v>2860</v>
       </c>
       <c r="Y15" s="95" t="s">
         <v>1366</v>
@@ -60525,10 +60694,10 @@
         <v>22</v>
       </c>
       <c r="X16" t="s">
-        <v>2848</v>
+        <v>2860</v>
       </c>
       <c r="Y16" s="95" t="s">
-        <v>2846</v>
+        <v>2858</v>
       </c>
       <c r="AA16">
         <v>1.2</v>
@@ -60598,10 +60767,10 @@
         <v>23</v>
       </c>
       <c r="X17" t="s">
-        <v>2848</v>
+        <v>2860</v>
       </c>
       <c r="Y17" s="95" t="s">
-        <v>2847</v>
+        <v>2859</v>
       </c>
       <c r="AA17">
         <v>1.2</v>
@@ -60671,7 +60840,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>2849</v>
+        <v>2861</v>
       </c>
       <c r="Y18" s="95" t="s">
         <v>1342</v>
@@ -60744,7 +60913,7 @@
         <v>33</v>
       </c>
       <c r="X19" t="s">
-        <v>2849</v>
+        <v>2861</v>
       </c>
       <c r="Y19" s="95" t="s">
         <v>1022</v>
@@ -60796,7 +60965,7 @@
         <v>2026-022</v>
       </c>
       <c r="N20" t="str">
-        <v>A realizar</v>
+        <v>Realizado</v>
       </c>
       <c r="O20" t="str">
         <v>Fiscalizações Baseadas em Risco</v>
@@ -60817,7 +60986,7 @@
         <v>34</v>
       </c>
       <c r="X20" t="s">
-        <v>2849</v>
+        <v>2861</v>
       </c>
       <c r="Y20" s="95" t="s">
         <v>1366</v>
@@ -60869,7 +61038,7 @@
         <v>2026-023</v>
       </c>
       <c r="N21" t="str">
-        <v>A realizar</v>
+        <v>Realizado</v>
       </c>
       <c r="O21" t="str">
         <v>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T2</v>
@@ -60890,10 +61059,10 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>2849</v>
+        <v>2861</v>
       </c>
       <c r="Y21" s="95" t="s">
-        <v>2846</v>
+        <v>2858</v>
       </c>
       <c r="AA21">
         <v>1.2</v>
@@ -60963,10 +61132,10 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>2849</v>
+        <v>2861</v>
       </c>
       <c r="Y22" s="95" t="s">
-        <v>2847</v>
+        <v>2859</v>
       </c>
       <c r="AA22">
         <v>1.2</v>
@@ -61015,7 +61184,7 @@
         <v>2026-025</v>
       </c>
       <c r="N23" t="str">
-        <v>A realizar</v>
+        <v>Em andamento</v>
       </c>
       <c r="O23" t="str">
         <v>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T3</v>
@@ -61036,7 +61205,7 @@
         <v>39</v>
       </c>
       <c r="X23" s="98" t="s">
-        <v>2850</v>
+        <v>2862</v>
       </c>
       <c r="Y23" s="95" t="s">
         <v>2711</v>
@@ -61109,10 +61278,10 @@
         <v>41</v>
       </c>
       <c r="X24" s="98" t="s">
-        <v>2850</v>
+        <v>2862</v>
       </c>
       <c r="Y24" s="95" t="s">
-        <v>2842</v>
+        <v>2854</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -61182,7 +61351,7 @@
         <v>43</v>
       </c>
       <c r="X25" t="s">
-        <v>2851</v>
+        <v>2863</v>
       </c>
       <c r="Y25" s="95" t="s">
         <v>854</v>
@@ -61255,10 +61424,10 @@
         <v>45</v>
       </c>
       <c r="X26" t="s">
-        <v>2851</v>
+        <v>2863</v>
       </c>
       <c r="Y26" s="95" t="s">
-        <v>2852</v>
+        <v>2864</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -61331,7 +61500,7 @@
         <v>47</v>
       </c>
       <c r="X27" s="257" t="s">
-        <v>2853</v>
+        <v>2865</v>
       </c>
       <c r="Y27" s="95" t="s">
         <v>2711</v>
@@ -61404,10 +61573,10 @@
         <v>49</v>
       </c>
       <c r="X28" s="257" t="s">
-        <v>2853</v>
+        <v>2865</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>2842</v>
+        <v>2854</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -61477,7 +61646,7 @@
         <v>50</v>
       </c>
       <c r="X29" s="257" t="s">
-        <v>2854</v>
+        <v>2866</v>
       </c>
       <c r="Y29" s="95" t="s">
         <v>2711</v>
@@ -61550,10 +61719,10 @@
         <v>51</v>
       </c>
       <c r="X30" s="257" t="s">
+        <v>2866</v>
+      </c>
+      <c r="Y30" s="95" t="s">
         <v>2854</v>
-      </c>
-      <c r="Y30" s="95" t="s">
-        <v>2842</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -61623,7 +61792,7 @@
         <v>56</v>
       </c>
       <c r="X31" s="257" t="s">
-        <v>2855</v>
+        <v>2867</v>
       </c>
       <c r="Y31" s="95" t="s">
         <v>471</v>
@@ -61699,7 +61868,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="257" t="s">
-        <v>2856</v>
+        <v>2868</v>
       </c>
       <c r="Y32" t="s">
         <v>1342</v>
@@ -61775,10 +61944,10 @@
         <v>59</v>
       </c>
       <c r="X33" s="257" t="s">
-        <v>2856</v>
+        <v>2868</v>
       </c>
       <c r="Y33" t="s">
-        <v>2857</v>
+        <v>2869</v>
       </c>
       <c r="Z33">
         <v>4</v>
@@ -61788,7 +61957,7 @@
       </c>
       <c r="AC33" s="251"/>
       <c r="AD33" s="252" t="s">
-        <v>2858</v>
+        <v>2870</v>
       </c>
       <c r="AE33" s="253">
         <f>SUM(AE3:AE32)</f>
@@ -61854,10 +62023,10 @@
         <v>60</v>
       </c>
       <c r="X34" s="257" t="s">
-        <v>2856</v>
+        <v>2868</v>
       </c>
       <c r="Y34" t="s">
-        <v>2859</v>
+        <v>2871</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -61925,7 +62094,7 @@
         <v>62</v>
       </c>
       <c r="X35" s="257" t="s">
-        <v>2856</v>
+        <v>2868</v>
       </c>
       <c r="Y35" t="s">
         <v>107</v>
@@ -61945,7 +62114,7 @@
         <v>2026-022</v>
       </c>
       <c r="C36" s="98" t="str">
-        <v>A realizar</v>
+        <v>Realizado</v>
       </c>
       <c r="D36" s="95" t="str">
         <v>Fiscalizações Baseadas em Risco</v>
@@ -61968,17 +62137,35 @@
       <c r="J36" s="99">
         <v>23</v>
       </c>
-      <c r="R36" t="str">
-        <v/>
-      </c>
-      <c r="S36" t="str">
-        <v/>
+      <c r="L36">
+        <v>2026</v>
+      </c>
+      <c r="M36" t="str">
+        <v>2026-044</v>
+      </c>
+      <c r="N36" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="O36" t="str">
+        <v>Painel MROSC</v>
+      </c>
+      <c r="P36">
+        <v>4</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>Diversos</v>
+      </c>
+      <c r="R36">
+        <v>1</v>
+      </c>
+      <c r="S36">
+        <v>64</v>
       </c>
       <c r="T36">
         <v>63</v>
       </c>
       <c r="X36" s="257" t="s">
-        <v>2856</v>
+        <v>2868</v>
       </c>
       <c r="Y36" t="s">
         <v>548</v>
@@ -61998,7 +62185,7 @@
         <v>2026-022</v>
       </c>
       <c r="C37" s="163" t="str">
-        <v>A realizar</v>
+        <v>Realizado</v>
       </c>
       <c r="D37" t="str">
         <v>Fiscalizações Baseadas em Risco</v>
@@ -62021,14 +62208,35 @@
       <c r="J37" s="163">
         <v>23</v>
       </c>
-      <c r="R37" t="str">
-        <v/>
-      </c>
-      <c r="S37" t="str">
-        <v/>
+      <c r="L37">
+        <v>2026</v>
+      </c>
+      <c r="M37" t="str">
+        <v>2026-045</v>
+      </c>
+      <c r="N37" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="O37" t="str">
+        <v>31º SEMAT</v>
+      </c>
+      <c r="P37">
+        <v>8</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <v>65</v>
+      </c>
+      <c r="T37">
+        <v>64</v>
       </c>
       <c r="X37" t="s">
-        <v>2860</v>
+        <v>2872</v>
       </c>
       <c r="Y37" t="s">
         <v>417</v>
@@ -62048,7 +62256,7 @@
         <v>2026-023</v>
       </c>
       <c r="C38" s="163" t="str">
-        <v>A realizar</v>
+        <v>Realizado</v>
       </c>
       <c r="D38" t="str">
         <v>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T2</v>
@@ -62071,14 +62279,35 @@
       <c r="J38" s="163">
         <v>13.8</v>
       </c>
-      <c r="R38" t="str">
-        <v/>
-      </c>
-      <c r="S38" t="str">
-        <v/>
+      <c r="L38">
+        <v>2026</v>
+      </c>
+      <c r="M38" t="str">
+        <v>2026-046</v>
+      </c>
+      <c r="N38" t="str">
+        <v>Em andamento</v>
+      </c>
+      <c r="O38" t="str">
+        <v>Curso “Sisaudit na Prática”</v>
+      </c>
+      <c r="P38">
+        <v>12</v>
+      </c>
+      <c r="Q38" t="str">
+        <v>Davi Assunção Salvador Nery de Castro; David da Silva de Araújo; Hamilton de Jesus Lopes Neto</v>
+      </c>
+      <c r="R38">
+        <v>3</v>
+      </c>
+      <c r="S38">
+        <v>68</v>
+      </c>
+      <c r="T38">
+        <v>65</v>
       </c>
       <c r="X38" t="s">
-        <v>2860</v>
+        <v>2872</v>
       </c>
       <c r="Y38" s="260" t="s">
         <v>1095</v>
@@ -62098,7 +62327,7 @@
         <v>2026-023</v>
       </c>
       <c r="C39" s="163" t="str">
-        <v>A realizar</v>
+        <v>Realizado</v>
       </c>
       <c r="D39" t="str">
         <v>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T2</v>
@@ -62121,14 +62350,35 @@
       <c r="J39" s="163">
         <v>13.8</v>
       </c>
-      <c r="R39" t="str">
-        <v/>
-      </c>
-      <c r="S39" t="str">
-        <v/>
+      <c r="L39">
+        <v>2026</v>
+      </c>
+      <c r="M39" t="str">
+        <v>2026-047</v>
+      </c>
+      <c r="N39" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="O39" t="str">
+        <v>teste</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>1</v>
+      </c>
+      <c r="S39">
+        <v>69</v>
+      </c>
+      <c r="T39">
+        <v>68</v>
       </c>
       <c r="X39" t="s">
-        <v>2861</v>
+        <v>2873</v>
       </c>
       <c r="Y39" t="s">
         <v>548</v>
@@ -62177,6 +62427,21 @@
       <c r="S40" t="str">
         <v/>
       </c>
+      <c r="T40">
+        <v>69</v>
+      </c>
+      <c r="X40" t="s">
+        <v>2874</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>471</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41">
@@ -62186,7 +62451,7 @@
         <v>2026-025</v>
       </c>
       <c r="C41" s="163" t="str">
-        <v>A realizar</v>
+        <v>Em andamento</v>
       </c>
       <c r="D41" t="str">
         <v>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T3</v>
@@ -62224,7 +62489,7 @@
         <v>2026-025</v>
       </c>
       <c r="C42" s="163" t="str">
-        <v>A realizar</v>
+        <v>Em andamento</v>
       </c>
       <c r="D42" t="str">
         <v>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T3</v>
@@ -63090,7 +63355,37 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>2026</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2026-044</v>
+      </c>
+      <c r="C65" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Painel MROSC</v>
+      </c>
+      <c r="E65">
+        <v>4</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Diversos</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
       <c r="R65" t="str">
         <v/>
       </c>
@@ -63098,7 +63393,37 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2026</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2026-045</v>
+      </c>
+      <c r="C66" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D66" t="str">
+        <v>31º SEMAT</v>
+      </c>
+      <c r="E66">
+        <v>8</v>
+      </c>
+      <c r="F66" t="str">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>8</v>
+      </c>
+      <c r="I66">
+        <v>2.4</v>
+      </c>
+      <c r="J66">
+        <v>10.4</v>
+      </c>
       <c r="R66" t="str">
         <v/>
       </c>
@@ -63106,7 +63431,37 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>2026</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2026-046</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Em andamento</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Curso “Sisaudit na Prática”</v>
+      </c>
+      <c r="E67">
+        <v>12</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Davi Assunção Salvador Nery de Castro</v>
+      </c>
+      <c r="G67">
+        <v>3</v>
+      </c>
+      <c r="H67">
+        <v>12</v>
+      </c>
+      <c r="I67">
+        <v>1.2</v>
+      </c>
+      <c r="J67">
+        <v>13.2</v>
+      </c>
       <c r="R67" t="str">
         <v/>
       </c>
@@ -63114,7 +63469,37 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2026</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2026-046</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Em andamento</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Curso “Sisaudit na Prática”</v>
+      </c>
+      <c r="E68">
+        <v>12</v>
+      </c>
+      <c r="F68" t="str">
+        <v>David da Silva de Araújo</v>
+      </c>
+      <c r="G68">
+        <v>3</v>
+      </c>
+      <c r="H68">
+        <v>12</v>
+      </c>
+      <c r="I68">
+        <v>1.2</v>
+      </c>
+      <c r="J68">
+        <v>13.2</v>
+      </c>
       <c r="R68" t="str">
         <v/>
       </c>
@@ -63122,7 +63507,37 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>2026</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2026-046</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Em andamento</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Curso “Sisaudit na Prática”</v>
+      </c>
+      <c r="E69">
+        <v>12</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Hamilton de Jesus Lopes Neto</v>
+      </c>
+      <c r="G69">
+        <v>3</v>
+      </c>
+      <c r="H69">
+        <v>12</v>
+      </c>
+      <c r="I69">
+        <v>1.2</v>
+      </c>
+      <c r="J69">
+        <v>13.2</v>
+      </c>
       <c r="R69" t="str">
         <v/>
       </c>
@@ -63130,7 +63545,37 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2026</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2026-047</v>
+      </c>
+      <c r="C70" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D70" t="str">
+        <v>teste</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70" t="str">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
       <c r="R70" t="str">
         <v/>
       </c>
@@ -63138,7 +63583,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R71" t="str">
         <v/>
       </c>
@@ -63146,7 +63591,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R72" t="str">
         <v/>
       </c>
@@ -63154,7 +63599,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R73" t="str">
         <v/>
       </c>
@@ -63162,7 +63607,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R74" t="str">
         <v/>
       </c>
@@ -63170,7 +63615,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R75" t="str">
         <v/>
       </c>
@@ -63178,7 +63623,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R76" t="str">
         <v/>
       </c>
@@ -63186,7 +63631,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R77" t="str">
         <v/>
       </c>
@@ -63194,7 +63639,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R78" t="str">
         <v/>
       </c>
@@ -63202,7 +63647,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R79" t="str">
         <v/>
       </c>
@@ -63210,7 +63655,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R80" t="str">
         <v/>
       </c>
@@ -64201,7 +64646,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="280" t="s">
-        <v>2862</v>
+        <v>2875</v>
       </c>
       <c r="B1" s="280"/>
       <c r="C1" s="280"/>
@@ -64222,31 +64667,31 @@
     <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="281" t="s">
-        <v>2863</v>
+        <v>2876</v>
       </c>
       <c r="B4" s="282"/>
       <c r="D4" s="283" t="s">
-        <v>2864</v>
+        <v>2877</v>
       </c>
       <c r="E4" s="284"/>
       <c r="G4" s="125" t="s">
-        <v>2865</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A5" s="115">
         <f>COUNTIF('Ações InCompany'!B:B,2026)</f>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>2866</v>
+        <v>2879</v>
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>2866</v>
+        <v>2879</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
@@ -64264,11 +64709,11 @@
     </row>
     <row r="8" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A8" s="278" t="s">
-        <v>2867</v>
+        <v>2880</v>
       </c>
       <c r="B8" s="278"/>
       <c r="D8" s="278" t="s">
-        <v>2868</v>
+        <v>2881</v>
       </c>
       <c r="E8" s="278"/>
     </row>
@@ -64283,13 +64728,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="108" t="s">
-        <v>2869</v>
+        <v>2882</v>
       </c>
       <c r="D10" s="108" t="s">
-        <v>2870</v>
+        <v>2883</v>
       </c>
       <c r="E10" s="108" t="s">
-        <v>2871</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -64298,14 +64743,14 @@
       </c>
       <c r="B11" s="110">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!F:F,"Servidores do TCDF")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" s="109" t="s">
-        <v>2872</v>
+        <v>2885</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>400</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -64314,14 +64759,14 @@
       </c>
       <c r="B12" s="112">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!F:F,"Jurisdicionados")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>2873</v>
+        <v>2886</v>
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>371</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -64333,7 +64778,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="109" t="s">
-        <v>2874</v>
+        <v>2887</v>
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -64342,23 +64787,23 @@
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="113" t="s">
-        <v>2875</v>
+        <v>2888</v>
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>2876</v>
+        <v>2889</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
-        <v>1141</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A30" s="278" t="s">
-        <v>2877</v>
+        <v>2890</v>
       </c>
       <c r="B30" s="278"/>
       <c r="C30" s="278"/>
@@ -64377,16 +64822,16 @@
         <v>6</v>
       </c>
       <c r="B32" s="108" t="s">
-        <v>2878</v>
+        <v>2891</v>
       </c>
       <c r="C32" s="108" t="s">
-        <v>2879</v>
+        <v>2892</v>
       </c>
       <c r="D32" s="108" t="s">
-        <v>2880</v>
+        <v>2893</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>2881</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64399,15 +64844,15 @@
       </c>
       <c r="C33" s="127">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A33)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" s="117">
         <f t="shared" ref="D33:D44" si="0">B33+C33</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.17948717948717949</v>
+        <v>0.21951219512195122</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64428,7 +64873,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>7.6923076923076927E-2</v>
+        <v>7.3170731707317069E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64449,7 +64894,7 @@
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>0.12820512820512819</v>
+        <v>0.12195121951219512</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64470,7 +64915,7 @@
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>5.128205128205128E-2</v>
+        <v>4.878048780487805E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64491,7 +64936,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>5.128205128205128E-2</v>
+        <v>4.878048780487805E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64512,7 +64957,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.17948717948717949</v>
+        <v>0.17073170731707318</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64521,7 +64966,7 @@
       </c>
       <c r="B39" s="145">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A39)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="146">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A39)</f>
@@ -64529,11 +64974,11 @@
       </c>
       <c r="D39" s="145">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>7.6923076923076927E-2</v>
+        <v>9.7560975609756101E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64554,7 +64999,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>2.564102564102564E-2</v>
+        <v>2.4390243902439025E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64563,24 +65008,24 @@
       </c>
       <c r="B41" s="151">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A41)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C41" s="152">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A41)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" s="151">
         <f>B41+C41</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.17948717948717949</v>
+        <v>0.14634146341463414</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="156" t="s">
-        <v>2882</v>
+        <v>2895</v>
       </c>
       <c r="B42" s="153">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A42)</f>
@@ -64617,12 +65062,12 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>5.128205128205128E-2</v>
+        <v>4.878048780487805E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="148" t="s">
-        <v>2883</v>
+        <v>2896</v>
       </c>
       <c r="B44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,"")</f>
@@ -64643,11 +65088,11 @@
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="113" t="s">
-        <v>2875</v>
+        <v>2888</v>
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
@@ -64655,7 +65100,7 @@
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>
@@ -64694,163 +65139,163 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>2884</v>
+        <v>2897</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2885</v>
+        <v>2898</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2886</v>
+        <v>2899</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2887</v>
+        <v>2900</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2888</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>2889</v>
+        <v>2902</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2890</v>
+        <v>2903</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1728</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2891</v>
+        <v>2904</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>2892</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>2889</v>
+        <v>2902</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2890</v>
+        <v>2903</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2893</v>
+        <v>2906</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2894</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>2889</v>
+        <v>2902</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2890</v>
+        <v>2903</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>67</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2891</v>
+        <v>2904</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2895</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>2889</v>
+        <v>2902</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2890</v>
+        <v>2903</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>71</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>2896</v>
+        <v>2909</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2897</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>2889</v>
+        <v>2902</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2890</v>
+        <v>2903</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2725</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2898</v>
+        <v>2911</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2899</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>2889</v>
+        <v>2902</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2900</v>
+        <v>2913</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2901</v>
+        <v>2914</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2902</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>2889</v>
+        <v>2902</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2900</v>
+        <v>2913</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2903</v>
+        <v>2916</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2904</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>2889</v>
+        <v>2902</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2905</v>
+        <v>2918</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>456</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2906</v>
+        <v>2919</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2907</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>2889</v>
+        <v>2902</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2905</v>
+        <v>2918</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>198</v>
@@ -64859,15 +65304,15 @@
         <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2908</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>2889</v>
+        <v>2902</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2905</v>
+        <v>2918</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>363</v>
@@ -64876,7 +65321,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2909</v>
+        <v>2922</v>
       </c>
     </row>
   </sheetData>
@@ -64898,16 +65343,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>2910</v>
+        <v>2923</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>2911</v>
+        <v>2924</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>2815</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -64918,10 +65363,10 @@
         <v>34</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2912</v>
+        <v>2925</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2748</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -64932,10 +65377,10 @@
         <v>26</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2913</v>
+        <v>2926</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2914</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -64959,7 +65404,7 @@
     </row>
     <row r="6" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="12" t="s">
-        <v>2764</v>
+        <v>2767</v>
       </c>
     </row>
   </sheetData>
@@ -64983,180 +65428,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>2884</v>
+        <v>2897</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2885</v>
+        <v>2898</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2886</v>
+        <v>2899</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2887</v>
+        <v>2900</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2888</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>2915</v>
+        <v>2927</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2890</v>
+        <v>2903</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2891</v>
+        <v>2904</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2916</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>2915</v>
+        <v>2927</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2890</v>
+        <v>2903</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>67</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2893</v>
+        <v>2906</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2917</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>2915</v>
+        <v>2927</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2890</v>
+        <v>2903</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>71</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2896</v>
+        <v>2909</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2918</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>2915</v>
+        <v>2927</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2890</v>
+        <v>2903</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>2688</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2919</v>
+        <v>2931</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2920</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>2915</v>
+        <v>2927</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2890</v>
+        <v>2903</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2725</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2898</v>
+        <v>2911</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2899</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>2915</v>
+        <v>2927</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2900</v>
+        <v>2913</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>2709</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2921</v>
+        <v>2933</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2922</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>2915</v>
+        <v>2927</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2900</v>
+        <v>2913</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2903</v>
+        <v>2916</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2904</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>2915</v>
+        <v>2927</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2900</v>
+        <v>2913</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>2693</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2923</v>
+        <v>2935</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>2924</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>2915</v>
+        <v>2927</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2925</v>
+        <v>2937</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2882</v>
+        <v>2895</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>2926</v>
+        <v>2938</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>2927</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>2915</v>
+        <v>2927</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2925</v>
+        <v>2937</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>198</v>
@@ -65165,15 +65610,15 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2908</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>2915</v>
+        <v>2927</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2925</v>
+        <v>2937</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>363</v>
@@ -65182,7 +65627,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2909</v>
+        <v>2922</v>
       </c>
     </row>
   </sheetData>
@@ -65201,7 +65646,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="285" t="s">
-        <v>2928</v>
+        <v>2940</v>
       </c>
       <c r="B1" s="285"/>
       <c r="C1" s="285"/>
@@ -65211,7 +65656,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="286" t="s">
-        <v>2929</v>
+        <v>2941</v>
       </c>
       <c r="B2" s="286"/>
       <c r="C2" s="286"/>
@@ -65224,33 +65669,33 @@
         <v>19</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>2818</v>
+        <v>2830</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>2819</v>
+        <v>2831</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>2930</v>
+        <v>2942</v>
       </c>
       <c r="E4" s="102" t="s">
-        <v>2820</v>
+        <v>2832</v>
       </c>
       <c r="F4" s="102" t="s">
-        <v>2931</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="str" cm="1">
-        <f t="array" ref="A5:A30">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32),_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32)&lt;&gt;""))),"")</f>
-        <v>Adriana Cuoco Portugal</v>
+        <f t="array" ref="A5:A34">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32),_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32)&lt;&gt;""))),"")</f>
+        <v>0</v>
       </c>
       <c r="B5" s="103">
         <f>IF($A5="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A5))</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C5" s="103">
         <f>IF($A5="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A5))</f>
-        <v>3.84</v>
+        <v>2.4</v>
       </c>
       <c r="D5" s="256">
         <f>IF($A5="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A5))</f>
@@ -65258,11 +65703,11 @@
       </c>
       <c r="E5" s="241">
         <f>IF($A5="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A5)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A5))</f>
-        <v>19.84</v>
+        <v>10.4</v>
       </c>
       <c r="F5" s="101">
         <f>IF($A5="","",COUNTIFS('GECC 2026'!F$2:F$200,$A5))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" s="101">
         <f>IF($A5="","",COUNTIFS('GECC 2026'!G$2:G$200,$A5))</f>
@@ -65271,15 +65716,15 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <v>Adriana Magalhães</v>
+        <v>Adriana Cuoco Portugal</v>
       </c>
       <c r="B6" s="103">
         <f>IF($A6="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A6))</f>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C6" s="103">
         <f>IF($A6="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A6))</f>
-        <v>3.5999999999999996</v>
+        <v>3.84</v>
       </c>
       <c r="D6" s="256">
         <f>IF($A6="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A6))</f>
@@ -65287,24 +65732,24 @@
       </c>
       <c r="E6" s="241">
         <f>IF($A6="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A6)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A6))</f>
-        <v>27.6</v>
+        <v>19.84</v>
       </c>
       <c r="F6" s="101">
         <f>IF($A6="","",COUNTIFS('GECC 2026'!F$2:F$200,$A6))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <v>Arthur Wú</v>
+        <v>Adriana Magalhães</v>
       </c>
       <c r="B7" s="103">
         <f>IF($A7="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A7))</f>
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C7" s="103">
         <f>IF($A7="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A7))</f>
-        <v>10.199999999999999</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="D7" s="256">
         <f>IF($A7="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A7))</f>
@@ -65312,74 +65757,74 @@
       </c>
       <c r="E7" s="241">
         <f>IF($A7="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A7)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A7))</f>
-        <v>43.2</v>
+        <v>27.6</v>
       </c>
       <c r="F7" s="101">
         <f>IF($A7="","",COUNTIFS('GECC 2026'!F$2:F$200,$A7))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <v>Cássio Murilo Alves Costa Filho</v>
+        <v>Arthur Wú</v>
       </c>
       <c r="B8" s="103">
         <f>IF($A8="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A8))</f>
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C8" s="103">
         <f>IF($A8="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A8))</f>
-        <v>4.8</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D8" s="256">
         <f>IF($A8="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A8))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E8" s="241">
         <f>IF($A8="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A8)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A8))</f>
-        <v>36.799999999999997</v>
+        <v>43.2</v>
       </c>
       <c r="F8" s="101">
         <f>IF($A8="","",COUNTIFS('GECC 2026'!F$2:F$200,$A8))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
-        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
+        <v>Cássio Murilo Alves Costa Filho</v>
       </c>
       <c r="B9" s="103">
         <f>IF($A9="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A9))</f>
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C9" s="103">
         <f>IF($A9="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A9))</f>
-        <v>6.24</v>
+        <v>4.8</v>
       </c>
       <c r="D9" s="256">
         <f>IF($A9="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A9))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E9" s="241">
         <f>IF($A9="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A9)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A9))</f>
-        <v>42.24</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="F9" s="101">
         <f>IF($A9="","",COUNTIFS('GECC 2026'!F$2:F$200,$A9))</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
-        <v>Denise Duarte Guirra Kuhlmann</v>
+        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
       </c>
       <c r="B10" s="103">
         <f>IF($A10="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A10))</f>
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C10" s="103">
         <f>IF($A10="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A10))</f>
-        <v>2.6399999999999997</v>
+        <v>6.24</v>
       </c>
       <c r="D10" s="256">
         <f>IF($A10="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A10))</f>
@@ -65387,24 +65832,24 @@
       </c>
       <c r="E10" s="241">
         <f>IF($A10="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A10)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A10))</f>
-        <v>14.64</v>
+        <v>42.24</v>
       </c>
       <c r="F10" s="101">
         <f>IF($A10="","",COUNTIFS('GECC 2026'!F$2:F$200,$A10))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
-        <v>Diversos</v>
+        <v>Davi Assunção Salvador Nery de Castro</v>
       </c>
       <c r="B11" s="103">
         <f>IF($A11="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A11))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C11" s="103">
         <f>IF($A11="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A11))</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D11" s="256">
         <f>IF($A11="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A11))</f>
@@ -65412,7 +65857,7 @@
       </c>
       <c r="E11" s="241">
         <f>IF($A11="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A11)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A11))</f>
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="F11" s="101">
         <f>IF($A11="","",COUNTIFS('GECC 2026'!F$2:F$200,$A11))</f>
@@ -65421,15 +65866,15 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
-        <v>Fernanda Viana de Souza</v>
+        <v>David da Silva de Araújo</v>
       </c>
       <c r="B12" s="103">
         <f>IF($A12="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A12))</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12" s="103">
         <f>IF($A12="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A12))</f>
-        <v>3.09</v>
+        <v>1.2</v>
       </c>
       <c r="D12" s="256">
         <f>IF($A12="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A12))</f>
@@ -65437,24 +65882,24 @@
       </c>
       <c r="E12" s="241">
         <f>IF($A12="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A12)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A12))</f>
-        <v>18.09</v>
+        <v>13.2</v>
       </c>
       <c r="F12" s="101">
         <f>IF($A12="","",COUNTIFS('GECC 2026'!F$2:F$200,$A12))</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
-        <v>Flávio José Fonseca de Souza</v>
+        <v>Denise Duarte Guirra Kuhlmann</v>
       </c>
       <c r="B13" s="103">
         <f>IF($A13="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A13))</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C13" s="103">
         <f>IF($A13="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A13))</f>
-        <v>2.4</v>
+        <v>2.6399999999999997</v>
       </c>
       <c r="D13" s="256">
         <f>IF($A13="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A13))</f>
@@ -65462,24 +65907,24 @@
       </c>
       <c r="E13" s="241">
         <f>IF($A13="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A13)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A13))</f>
-        <v>10.4</v>
+        <v>14.64</v>
       </c>
       <c r="F13" s="101">
         <f>IF($A13="","",COUNTIFS('GECC 2026'!F$2:F$200,$A13))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
-        <v>Gabriel Heller</v>
+        <v>Diversos</v>
       </c>
       <c r="B14" s="103">
         <f>IF($A14="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A14))</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C14" s="103">
         <f>IF($A14="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A14))</f>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="256">
         <f>IF($A14="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A14))</f>
@@ -65487,7 +65932,7 @@
       </c>
       <c r="E14" s="241">
         <f>IF($A14="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A14)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A14))</f>
-        <v>37.200000000000003</v>
+        <v>0</v>
       </c>
       <c r="F14" s="101">
         <f>IF($A14="","",COUNTIFS('GECC 2026'!F$2:F$200,$A14))</f>
@@ -65496,15 +65941,15 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
-        <v>Gustavo Takahashi</v>
+        <v>Fernanda Viana de Souza</v>
       </c>
       <c r="B15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="D15" s="256">
         <f>IF($A15="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
@@ -65512,7 +65957,7 @@
       </c>
       <c r="E15" s="241">
         <f>IF($A15="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A15)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
-        <v>25</v>
+        <v>18.09</v>
       </c>
       <c r="F15" s="101">
         <f>IF($A15="","",COUNTIFS('GECC 2026'!F$2:F$200,$A15))</f>
@@ -65521,15 +65966,15 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
-        <v>Indio Artiaga do Brasil Rabelo</v>
+        <v>Flávio José Fonseca de Souza</v>
       </c>
       <c r="B16" s="103">
         <f>IF($A16="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A16))</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C16" s="103">
         <f>IF($A16="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A16))</f>
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="256">
         <f>IF($A16="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A16))</f>
@@ -65537,7 +65982,7 @@
       </c>
       <c r="E16" s="241">
         <f>IF($A16="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A16)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A16))</f>
-        <v>15.6</v>
+        <v>10.4</v>
       </c>
       <c r="F16" s="101">
         <f>IF($A16="","",COUNTIFS('GECC 2026'!F$2:F$200,$A16))</f>
@@ -65546,15 +65991,15 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
-        <v>Leonardo de Melo</v>
+        <v>Gabriel Heller</v>
       </c>
       <c r="B17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D17" s="256">
         <f>IF($A17="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
@@ -65562,24 +66007,24 @@
       </c>
       <c r="E17" s="241">
         <f>IF($A17="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A17)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
-        <v>0</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="F17" s="101">
         <f>IF($A17="","",COUNTIFS('GECC 2026'!F$2:F$200,$A17))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
-        <v>Leonardo José Alves Leal Neri</v>
+        <v>Gustavo Takahashi</v>
       </c>
       <c r="B18" s="103">
         <f>IF($A18="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A18))</f>
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C18" s="103">
         <f>IF($A18="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A18))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D18" s="256">
         <f>IF($A18="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A18))</f>
@@ -65587,24 +66032,24 @@
       </c>
       <c r="E18" s="241">
         <f>IF($A18="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A18)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A18))</f>
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="F18" s="101">
         <f>IF($A18="","",COUNTIFS('GECC 2026'!F$2:F$200,$A18))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
-        <v>Luciana Alvim</v>
+        <v>Hamilton de Jesus Lopes Neto</v>
       </c>
       <c r="B19" s="103">
         <f>IF($A19="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A19))</f>
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="C19" s="103">
         <f>IF($A19="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A19))</f>
-        <v>94</v>
+        <v>1.2</v>
       </c>
       <c r="D19" s="256">
         <f>IF($A19="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A19))</f>
@@ -65612,41 +66057,41 @@
       </c>
       <c r="E19" s="241">
         <f>IF($A19="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A19)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A19))</f>
-        <v>154</v>
+        <v>13.2</v>
       </c>
       <c r="F19" s="101">
         <f>IF($A19="","",COUNTIFS('GECC 2026'!F$2:F$200,$A19))</f>
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
-        <v>Marcelo Bálbio Moraes</v>
+        <v>Indio Artiaga do Brasil Rabelo</v>
       </c>
       <c r="B20" s="103">
         <f>IF($A20="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A20))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C20" s="103">
         <f>IF($A20="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A20))</f>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="D20" s="256">
         <f>IF($A20="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A20))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E20" s="241">
         <f>IF($A20="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A20)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A20))</f>
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="F20" s="101">
         <f>IF($A20="","",COUNTIFS('GECC 2026'!F$2:F$200,$A20))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
-        <v>Mauri Siqueira Montessi</v>
+        <v>Leonardo de Melo</v>
       </c>
       <c r="B21" s="103">
         <f>IF($A21="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A21))</f>
@@ -65658,53 +66103,53 @@
       </c>
       <c r="D21" s="256">
         <f>IF($A21="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A21))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E21" s="241">
         <f>IF($A21="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A21)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A21))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F21" s="101">
         <f>IF($A21="","",COUNTIFS('GECC 2026'!F$2:F$200,$A21))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
-        <v>Michel Martins de Morais</v>
+        <v>Leonardo José Alves Leal Neri</v>
       </c>
       <c r="B22" s="103">
         <f>IF($A22="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A22))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C22" s="103">
         <f>IF($A22="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A22))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D22" s="256">
         <f>IF($A22="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A22))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E22" s="241">
         <f>IF($A22="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A22)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A22))</f>
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="F22" s="101">
         <f>IF($A22="","",COUNTIFS('GECC 2026'!F$2:F$200,$A22))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
-        <v>Paulo José Góes Daltro</v>
+        <v>Luciana Alvim</v>
       </c>
       <c r="B23" s="103">
         <f>IF($A23="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A23))</f>
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C23" s="103">
         <f>IF($A23="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A23))</f>
-        <v>4.8</v>
+        <v>94</v>
       </c>
       <c r="D23" s="256">
         <f>IF($A23="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A23))</f>
@@ -65712,124 +66157,124 @@
       </c>
       <c r="E23" s="241">
         <f>IF($A23="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A23)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A23))</f>
-        <v>20.8</v>
+        <v>154</v>
       </c>
       <c r="F23" s="101">
         <f>IF($A23="","",COUNTIFS('GECC 2026'!F$2:F$200,$A23))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
-        <v>Priscila Nolasco</v>
+        <v>Marcelo Bálbio Moraes</v>
       </c>
       <c r="B24" s="103">
         <f>IF($A24="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A24))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C24" s="103">
         <f>IF($A24="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A24))</f>
-        <v>2.6399999999999997</v>
+        <v>0</v>
       </c>
       <c r="D24" s="256">
         <f>IF($A24="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A24))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E24" s="241">
         <f>IF($A24="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A24)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A24))</f>
-        <v>14.64</v>
+        <v>16</v>
       </c>
       <c r="F24" s="101">
         <f>IF($A24="","",COUNTIFS('GECC 2026'!F$2:F$200,$A24))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
-        <v>Reinaldo Alencar</v>
+        <v>Mauri Siqueira Montessi</v>
       </c>
       <c r="B25" s="103">
         <f>IF($A25="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A25))</f>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C25" s="103">
         <f>IF($A25="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A25))</f>
-        <v>7.1999999999999993</v>
+        <v>0</v>
       </c>
       <c r="D25" s="256">
         <f>IF($A25="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A25))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E25" s="241">
         <f>IF($A25="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A25)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A25))</f>
-        <v>55.2</v>
+        <v>16</v>
       </c>
       <c r="F25" s="101">
         <f>IF($A25="","",COUNTIFS('GECC 2026'!F$2:F$200,$A25))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
-        <v>Rogério Ribeiro</v>
+        <v>Michel Martins de Morais</v>
       </c>
       <c r="B26" s="103">
         <f>IF($A26="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A26))</f>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C26" s="103">
         <f>IF($A26="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A26))</f>
-        <v>7.1999999999999993</v>
+        <v>0</v>
       </c>
       <c r="D26" s="256">
         <f>IF($A26="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A26))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E26" s="241">
         <f>IF($A26="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A26)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A26))</f>
-        <v>55.2</v>
+        <v>16</v>
       </c>
       <c r="F26" s="101">
         <f>IF($A26="","",COUNTIFS('GECC 2026'!F$2:F$200,$A26))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
-        <v>Rômulo Miranda Alvim</v>
+        <v>Paulo José Góes Daltro</v>
       </c>
       <c r="B27" s="103">
         <f>IF($A27="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A27))</f>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C27" s="103">
         <f>IF($A27="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A27))</f>
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="D27" s="256">
         <f>IF($A27="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A27))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E27" s="241">
         <f>IF($A27="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A27)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A27))</f>
-        <v>43.6</v>
+        <v>20.8</v>
       </c>
       <c r="F27" s="101">
         <f>IF($A27="","",COUNTIFS('GECC 2026'!F$2:F$200,$A27))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>Servidores, colaboradores e estagiários do TCDF</v>
+        <v>Priscila Nolasco</v>
       </c>
       <c r="B28" s="103">
         <f>IF($A28="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A28))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C28" s="103">
         <f>IF($A28="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A28))</f>
-        <v>0</v>
+        <v>2.6399999999999997</v>
       </c>
       <c r="D28" s="256">
         <f>IF($A28="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A28))</f>
@@ -65837,24 +66282,24 @@
       </c>
       <c r="E28" s="241">
         <f>IF($A28="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A28)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A28))</f>
-        <v>0</v>
+        <v>14.64</v>
       </c>
       <c r="F28" s="101">
         <f>IF($A28="","",COUNTIFS('GECC 2026'!F$2:F$200,$A28))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>Tarsila Firmino Ely</v>
+        <v>Reinaldo Alencar</v>
       </c>
       <c r="B29" s="103">
         <f>IF($A29="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A29))</f>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C29" s="103">
         <f>IF($A29="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A29))</f>
-        <v>96.4</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="D29" s="256">
         <f>IF($A29="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A29))</f>
@@ -65862,24 +66307,24 @@
       </c>
       <c r="E29" s="241">
         <f>IF($A29="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A29)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A29))</f>
-        <v>152.4</v>
+        <v>55.2</v>
       </c>
       <c r="F29" s="101">
         <f>IF($A29="","",COUNTIFS('GECC 2026'!F$2:F$200,$A29))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>Túllio Herbeth Teixeira Moraes</v>
+        <v>Rogério Ribeiro</v>
       </c>
       <c r="B30" s="103">
         <f>IF($A30="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A30))</f>
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C30" s="103">
         <f>IF($A30="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A30))</f>
-        <v>0.44999999999999996</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="D30" s="256">
         <f>IF($A30="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A30))</f>
@@ -65887,102 +66332,114 @@
       </c>
       <c r="E30" s="241">
         <f>IF($A30="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A30)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A30))</f>
-        <v>3.45</v>
+        <v>55.2</v>
       </c>
       <c r="F30" s="101">
         <f>IF($A30="","",COUNTIFS('GECC 2026'!F$2:F$200,$A30))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="str">
+        <v>Rômulo Miranda Alvim</v>
+      </c>
+      <c r="B31" s="103">
+        <f>IF($A31="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A31))</f>
+        <v>24</v>
+      </c>
+      <c r="C31" s="103">
+        <f>IF($A31="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A31))</f>
+        <v>3.6</v>
+      </c>
+      <c r="D31" s="256">
+        <f>IF($A31="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
+        <v>16</v>
+      </c>
+      <c r="E31" s="241">
+        <f>IF($A31="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A31)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
+        <v>43.6</v>
+      </c>
+      <c r="F31" s="101">
+        <f>IF($A31="","",COUNTIFS('GECC 2026'!F$2:F$200,$A31))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="str">
+        <v>Servidores, colaboradores e estagiários do TCDF</v>
+      </c>
+      <c r="B32" s="103">
+        <f>IF($A32="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A32))</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="103">
+        <f>IF($A32="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A32))</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="256">
+        <f>IF($A32="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="241">
+        <f>IF($A32="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A32)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="101">
+        <f>IF($A32="","",COUNTIFS('GECC 2026'!F$2:F$200,$A32))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="103" t="str">
-        <f>IF($A31="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A31))</f>
-        <v/>
-      </c>
-      <c r="C31" s="103" t="str">
-        <f>IF($A31="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A31))</f>
-        <v/>
-      </c>
-      <c r="D31" s="256" t="str">
-        <f>IF($A31="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
-        <v/>
-      </c>
-      <c r="E31" s="241" t="str">
-        <f>IF($A31="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A31)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
-        <v/>
-      </c>
-      <c r="F31" s="101" t="str">
-        <f>IF($A31="","",COUNTIFS('GECC 2026'!F$2:F$200,$A31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="103" t="str">
-        <f>IF($A32="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v/>
-      </c>
-      <c r="C32" s="103" t="str">
-        <f>IF($A32="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v/>
-      </c>
-      <c r="D32" s="256" t="str">
-        <f>IF($A32="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
-        <v/>
-      </c>
-      <c r="E32" s="241" t="str">
-        <f>IF($A32="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A32)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
-        <v/>
-      </c>
-      <c r="F32" s="101" t="str">
-        <f>IF($A32="","",COUNTIFS('GECC 2026'!F$2:F$200,$A32))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="103" t="str">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="str">
+        <v>Tarsila Firmino Ely</v>
+      </c>
+      <c r="B33" s="103">
         <f>IF($A33="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A33))</f>
-        <v/>
-      </c>
-      <c r="C33" s="103" t="str">
+        <v>56</v>
+      </c>
+      <c r="C33" s="103">
         <f>IF($A33="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A33))</f>
-        <v/>
-      </c>
-      <c r="D33" s="256" t="str">
+        <v>96.4</v>
+      </c>
+      <c r="D33" s="256">
         <f>IF($A33="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A33))</f>
-        <v/>
-      </c>
-      <c r="E33" s="241" t="str">
+        <v>0</v>
+      </c>
+      <c r="E33" s="241">
         <f>IF($A33="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A33)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A33))</f>
-        <v/>
-      </c>
-      <c r="F33" s="101" t="str">
+        <v>152.4</v>
+      </c>
+      <c r="F33" s="101">
         <f>IF($A33="","",COUNTIFS('GECC 2026'!F$2:F$200,$A33))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="103" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="str">
+        <v>Túllio Herbeth Teixeira Moraes</v>
+      </c>
+      <c r="B34" s="103">
         <f>IF($A34="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A34))</f>
-        <v/>
-      </c>
-      <c r="C34" s="103" t="str">
+        <v>3</v>
+      </c>
+      <c r="C34" s="103">
         <f>IF($A34="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A34))</f>
-        <v/>
-      </c>
-      <c r="D34" s="256" t="str">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="D34" s="256">
         <f>IF($A34="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A34))</f>
-        <v/>
-      </c>
-      <c r="E34" s="241" t="str">
+        <v>0</v>
+      </c>
+      <c r="E34" s="241">
         <f>IF($A34="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A34)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A34))</f>
-        <v/>
-      </c>
-      <c r="F34" s="101" t="str">
+        <v>3.45</v>
+      </c>
+      <c r="F34" s="101">
         <f>IF($A34="","",COUNTIFS('GECC 2026'!F$2:F$200,$A34))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="103" t="str">
         <f>IF($A35="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A35))</f>
         <v/>
@@ -66004,7 +66461,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="103" t="str">
         <f>IF($A36="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A36))</f>
         <v/>
@@ -66026,7 +66483,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B37" s="103" t="str">
         <f>IF($A37="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A37))</f>
         <v/>
@@ -66048,7 +66505,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B38" s="103" t="str">
         <f>IF($A38="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A38))</f>
         <v/>
@@ -66070,7 +66527,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="103" t="str">
         <f>IF($A39="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A39))</f>
         <v/>
@@ -66092,7 +66549,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B40" s="103" t="str">
         <f>IF($A40="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A40))</f>
         <v/>
@@ -66114,7 +66571,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="103" t="str">
         <f>IF($A41="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A41))</f>
         <v/>
@@ -66136,7 +66593,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B42" s="103" t="str">
         <f>IF($A42="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A42))</f>
         <v/>
@@ -66158,7 +66615,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="103" t="str">
         <f>IF($A43="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A43))</f>
         <v/>
@@ -66180,7 +66637,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B44" s="103" t="str">
         <f>IF($A44="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A44))</f>
         <v/>
@@ -66202,7 +66659,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B45" s="103" t="str">
         <f>IF($A45="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A45))</f>
         <v/>
@@ -66224,7 +66681,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B46" s="103" t="str">
         <f>IF($A46="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A46))</f>
         <v/>
@@ -66246,7 +66703,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B47" s="103" t="str">
         <f>IF($A47="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A47))</f>
         <v/>
@@ -66268,7 +66725,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="103" t="str">
         <f>IF($A48="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A48))</f>
         <v/>
@@ -67476,15 +67933,15 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="242" t="s">
-        <v>2876</v>
+        <v>2889</v>
       </c>
       <c r="B105" s="243">
         <f>SUM(B5:B100)</f>
-        <v>540</v>
+        <v>584</v>
       </c>
       <c r="C105" s="243">
         <f>SUM(C5:C100)</f>
-        <v>269.89999999999998</v>
+        <v>275.89999999999998</v>
       </c>
       <c r="D105" s="256">
         <f>IF($A105="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A105))</f>
@@ -67496,7 +67953,7 @@
       </c>
       <c r="F105" s="244">
         <f>SUM(F5:F100)</f>
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -67527,7 +67984,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="287" t="s">
-        <v>2932</v>
+        <v>2944</v>
       </c>
       <c r="B1" s="287"/>
       <c r="C1" s="287"/>
@@ -67539,20 +67996,20 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="130" t="s">
-        <v>2933</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="288" t="s">
-        <v>2934</v>
+        <v>2946</v>
       </c>
       <c r="B4" s="289"/>
       <c r="D4" s="288" t="s">
-        <v>2935</v>
+        <v>2947</v>
       </c>
       <c r="E4" s="289"/>
       <c r="G4" s="288" t="s">
-        <v>2936</v>
+        <v>2948</v>
       </c>
       <c r="H4" s="289"/>
     </row>
@@ -67576,28 +68033,28 @@
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="143" t="s">
-        <v>2937</v>
+        <v>2949</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>2938</v>
+        <v>2950</v>
       </c>
       <c r="C7" s="143" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="143" t="s">
-        <v>2939</v>
+        <v>2951</v>
       </c>
       <c r="E7" s="143" t="s">
-        <v>2940</v>
+        <v>2952</v>
       </c>
       <c r="F7" s="143" t="s">
-        <v>2815</v>
+        <v>2827</v>
       </c>
       <c r="G7" s="143" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="143" t="s">
-        <v>2941</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4885" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B68FE8E-29DA-429B-AF65-C9F46B050110}"/>
+  <xr:revisionPtr revIDLastSave="4895" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9F6E309-8A30-460A-884A-5DD9F86E89A5}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6527" uniqueCount="2956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6519" uniqueCount="2954">
   <si>
     <t>ID</t>
   </si>
@@ -9030,12 +9030,6 @@
   </si>
   <si>
     <t>Participantes</t>
-  </si>
-  <si>
-    <t>teste</t>
-  </si>
-  <si>
-    <t>03/06/2026</t>
   </si>
 </sst>
 </file>
@@ -12965,7 +12959,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1</c:v>
@@ -58022,47 +58016,27 @@
     <row r="703" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="209" t="str">
         <f>IF(B703="","",B703&amp;"-"&amp;TEXT(COUNTIF(B$2:B703,B703),"000"))</f>
-        <v>2026-047</v>
-      </c>
-      <c r="B703" s="210">
-        <v>2026</v>
-      </c>
-      <c r="C703" s="219" t="s">
-        <v>2756</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B703" s="210"/>
+      <c r="C703" s="219"/>
       <c r="D703" s="210"/>
-      <c r="E703" s="211" t="s">
-        <v>2954</v>
-      </c>
-      <c r="F703" s="212" t="s">
-        <v>23</v>
-      </c>
-      <c r="G703" s="209" t="s">
-        <v>24</v>
-      </c>
-      <c r="H703" s="213" t="s">
-        <v>2955</v>
-      </c>
-      <c r="I703" s="213" t="s">
-        <v>2955</v>
-      </c>
-      <c r="J703" s="213" t="s">
-        <v>2955</v>
-      </c>
-      <c r="K703" s="210" t="s">
-        <v>34</v>
-      </c>
-      <c r="L703" s="224">
-        <v>1000</v>
-      </c>
+      <c r="E703" s="211"/>
+      <c r="F703" s="212"/>
+      <c r="G703" s="209"/>
+      <c r="H703" s="213"/>
+      <c r="I703" s="213"/>
+      <c r="J703" s="213"/>
+      <c r="K703" s="210"/>
+      <c r="L703" s="224"/>
       <c r="M703" s="215"/>
       <c r="N703" s="216"/>
       <c r="O703" s="217"/>
       <c r="P703" s="217"/>
       <c r="Q703" s="217"/>
-      <c r="R703" s="217">
+      <c r="R703" s="217" t="str">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="S703" s="210"/>
       <c r="T703" s="209"/>
@@ -59595,7 +59569,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="98" cm="1">
-        <f t="array" ref="A2:J70">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
+        <f t="array" ref="A2:J69">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
         <v>2026</v>
       </c>
       <c r="B2" s="98" t="str">
@@ -59759,7 +59733,7 @@
         <v>5.2</v>
       </c>
       <c r="L4" cm="1">
-        <f t="array" ref="L4:Q39">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
+        <f t="array" ref="L4:Q38">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
         <v>2026</v>
       </c>
       <c r="M4" t="str">
@@ -59786,7 +59760,7 @@
         <v>1</v>
       </c>
       <c r="T4" cm="1">
-        <f t="array" ref="T4:T40">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
+        <f t="array" ref="T4:T39">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
         <v>0</v>
       </c>
       <c r="X4" t="s">
@@ -62350,29 +62324,11 @@
       <c r="J39" s="163">
         <v>13.8</v>
       </c>
-      <c r="L39">
-        <v>2026</v>
-      </c>
-      <c r="M39" t="str">
-        <v>2026-047</v>
-      </c>
-      <c r="N39" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="O39" t="str">
-        <v>teste</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>0</v>
-      </c>
-      <c r="R39">
-        <v>1</v>
-      </c>
-      <c r="S39">
-        <v>69</v>
+      <c r="R39" t="str">
+        <v/>
+      </c>
+      <c r="S39" t="str">
+        <v/>
       </c>
       <c r="T39">
         <v>68</v>
@@ -62427,9 +62383,6 @@
       <c r="S40" t="str">
         <v/>
       </c>
-      <c r="T40">
-        <v>69</v>
-      </c>
       <c r="X40" t="s">
         <v>2874</v>
       </c>
@@ -63546,36 +63499,6 @@
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>2026</v>
-      </c>
-      <c r="B70" t="str">
-        <v>2026-047</v>
-      </c>
-      <c r="C70" t="str">
-        <v>A realizar</v>
-      </c>
-      <c r="D70" t="str">
-        <v>teste</v>
-      </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
-      <c r="F70" t="str">
-        <v>0</v>
-      </c>
-      <c r="G70">
-        <v>1</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
       <c r="R70" t="str">
         <v/>
       </c>
@@ -64681,7 +64604,7 @@
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A5" s="115">
         <f>COUNTIF('Ações InCompany'!B:B,2026)</f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="116" t="s">
         <v>2879</v>
@@ -64695,7 +64618,7 @@
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
@@ -64852,7 +64775,7 @@
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.21951219512195122</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64873,7 +64796,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>7.3170731707317069E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64894,7 +64817,7 @@
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>0.12195121951219512</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64915,7 +64838,7 @@
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>4.878048780487805E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64936,7 +64859,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>4.878048780487805E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64957,7 +64880,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.17073170731707318</v>
+        <v>0.17499999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64970,15 +64893,15 @@
       </c>
       <c r="C39" s="146">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A39)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" s="145">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>9.7560975609756101E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64999,7 +64922,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>2.4390243902439025E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65020,7 +64943,7 @@
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.14634146341463414</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65062,7 +64985,7 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>4.878048780487805E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65096,11 +65019,11 @@
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>
@@ -65707,7 +65630,7 @@
       </c>
       <c r="F5" s="101">
         <f>IF($A5="","",COUNTIFS('GECC 2026'!F$2:F$200,$A5))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="101">
         <f>IF($A5="","",COUNTIFS('GECC 2026'!G$2:G$200,$A5))</f>
@@ -67953,7 +67876,7 @@
       </c>
       <c r="F105" s="244">
         <f>SUM(F5:F100)</f>
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4895" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9F6E309-8A30-460A-884A-5DD9F86E89A5}"/>
+  <xr:revisionPtr revIDLastSave="4897" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E4F425A-E175-49FE-B536-057BED796534}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -8635,9 +8635,6 @@
     <t>31º SEMAT</t>
   </si>
   <si>
-    <t>3 e 4/08/2026</t>
-  </si>
-  <si>
     <t>6503/2026</t>
   </si>
   <si>
@@ -9030,6 +9027,9 @@
   </si>
   <si>
     <t>Participantes</t>
+  </si>
+  <si>
+    <t>6 e 7/08/2026</t>
   </si>
 </sst>
 </file>
@@ -14942,6 +14942,14 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}" name="Tabela2" displayName="Tabela2" ref="B1:T684" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="B1:T684" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}">
@@ -15353,7 +15361,7 @@
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
       <c r="R2" s="23">
-        <f t="shared" ref="R2:R65" si="0">SUM(O2:Q2)</f>
+        <f>SUM(O2:Q2)</f>
         <v>20</v>
       </c>
       <c r="S2" s="22">
@@ -15404,7 +15412,7 @@
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O3:Q3)</f>
         <v>16</v>
       </c>
       <c r="S3" s="24">
@@ -15455,7 +15463,7 @@
       <c r="P4" s="23"/>
       <c r="Q4" s="23"/>
       <c r="R4" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O4:Q4)</f>
         <v>24</v>
       </c>
       <c r="S4" s="22">
@@ -15506,7 +15514,7 @@
       <c r="P5" s="25"/>
       <c r="Q5" s="25"/>
       <c r="R5" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O5:Q5)</f>
         <v>16</v>
       </c>
       <c r="S5" s="24">
@@ -15557,7 +15565,7 @@
       <c r="P6" s="23"/>
       <c r="Q6" s="23"/>
       <c r="R6" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O6:Q6)</f>
         <v>40</v>
       </c>
       <c r="S6" s="22">
@@ -15608,7 +15616,7 @@
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
       <c r="R7" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O7:Q7)</f>
         <v>30</v>
       </c>
       <c r="S7" s="24">
@@ -15657,7 +15665,7 @@
       <c r="P8" s="23"/>
       <c r="Q8" s="23"/>
       <c r="R8" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O8:Q8)</f>
         <v>24</v>
       </c>
       <c r="S8" s="22">
@@ -15708,7 +15716,7 @@
       </c>
       <c r="Q9" s="25"/>
       <c r="R9" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O9:Q9)</f>
         <v>37</v>
       </c>
       <c r="S9" s="24">
@@ -15759,7 +15767,7 @@
       </c>
       <c r="Q10" s="23"/>
       <c r="R10" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O10:Q10)</f>
         <v>58</v>
       </c>
       <c r="S10" s="22">
@@ -15812,7 +15820,7 @@
       <c r="P11" s="25"/>
       <c r="Q11" s="25"/>
       <c r="R11" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O11:Q11)</f>
         <v>25</v>
       </c>
       <c r="S11" s="24">
@@ -15867,7 +15875,7 @@
       </c>
       <c r="Q12" s="23"/>
       <c r="R12" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O12:Q12)</f>
         <v>85</v>
       </c>
       <c r="S12" s="22">
@@ -15922,7 +15930,7 @@
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
       <c r="R13" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O13:Q13)</f>
         <v>19</v>
       </c>
       <c r="S13" s="24">
@@ -15977,7 +15985,7 @@
       </c>
       <c r="Q14" s="23"/>
       <c r="R14" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O14:Q14)</f>
         <v>89</v>
       </c>
       <c r="S14" s="22">
@@ -16032,7 +16040,7 @@
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
       <c r="R15" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O15:Q15)</f>
         <v>37</v>
       </c>
       <c r="S15" s="24">
@@ -16089,7 +16097,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O16:Q16)</f>
         <v>0</v>
       </c>
       <c r="S16" s="22">
@@ -16142,7 +16150,7 @@
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
       <c r="R17" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O17:Q17)</f>
         <v>30</v>
       </c>
       <c r="S17" s="24">
@@ -16197,7 +16205,7 @@
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
       <c r="R18" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O18:Q18)</f>
         <v>30</v>
       </c>
       <c r="S18" s="22">
@@ -16252,7 +16260,7 @@
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
       <c r="R19" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O19:Q19)</f>
         <v>15</v>
       </c>
       <c r="S19" s="24">
@@ -16307,7 +16315,7 @@
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
       <c r="R20" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O20:Q20)</f>
         <v>14</v>
       </c>
       <c r="S20" s="22">
@@ -16362,7 +16370,7 @@
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
       <c r="R21" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O21:Q21)</f>
         <v>14</v>
       </c>
       <c r="S21" s="24">
@@ -16417,7 +16425,7 @@
       </c>
       <c r="Q22" s="23"/>
       <c r="R22" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O22:Q22)</f>
         <v>49</v>
       </c>
       <c r="S22" s="22">
@@ -16472,7 +16480,7 @@
       <c r="P23" s="25"/>
       <c r="Q23" s="25"/>
       <c r="R23" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O23:Q23)</f>
         <v>43</v>
       </c>
       <c r="S23" s="24">
@@ -16527,7 +16535,7 @@
       <c r="P24" s="23"/>
       <c r="Q24" s="23"/>
       <c r="R24" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O24:Q24)</f>
         <v>25</v>
       </c>
       <c r="S24" s="22">
@@ -16582,7 +16590,7 @@
       <c r="P25" s="25"/>
       <c r="Q25" s="25"/>
       <c r="R25" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O25:Q25)</f>
         <v>35</v>
       </c>
       <c r="S25" s="24">
@@ -16637,7 +16645,7 @@
       <c r="P26" s="23"/>
       <c r="Q26" s="23"/>
       <c r="R26" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O26:Q26)</f>
         <v>35</v>
       </c>
       <c r="S26" s="22">
@@ -16690,7 +16698,7 @@
       <c r="P27" s="25"/>
       <c r="Q27" s="25"/>
       <c r="R27" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O27:Q27)</f>
         <v>87</v>
       </c>
       <c r="S27" s="24"/>
@@ -16741,7 +16749,7 @@
         <v>46</v>
       </c>
       <c r="R28" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O28:Q28)</f>
         <v>46</v>
       </c>
       <c r="S28" s="22">
@@ -16796,7 +16804,7 @@
       <c r="P29" s="25"/>
       <c r="Q29" s="25"/>
       <c r="R29" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O29:Q29)</f>
         <v>15</v>
       </c>
       <c r="S29" s="24">
@@ -16851,7 +16859,7 @@
       </c>
       <c r="Q30" s="23"/>
       <c r="R30" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O30:Q30)</f>
         <v>54</v>
       </c>
       <c r="S30" s="22">
@@ -16904,7 +16912,7 @@
       <c r="P31" s="25"/>
       <c r="Q31" s="25"/>
       <c r="R31" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O31:Q31)</f>
         <v>52</v>
       </c>
       <c r="S31" s="24">
@@ -16957,7 +16965,7 @@
         <v>46</v>
       </c>
       <c r="R32" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O32:Q32)</f>
         <v>46</v>
       </c>
       <c r="S32" s="22">
@@ -17010,7 +17018,7 @@
       <c r="P33" s="25"/>
       <c r="Q33" s="25"/>
       <c r="R33" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O33:Q33)</f>
         <v>14</v>
       </c>
       <c r="S33" s="24">
@@ -17061,7 +17069,7 @@
       <c r="P34" s="23"/>
       <c r="Q34" s="23"/>
       <c r="R34" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O34:Q34)</f>
         <v>25</v>
       </c>
       <c r="S34" s="22">
@@ -17112,7 +17120,7 @@
       <c r="P35" s="25"/>
       <c r="Q35" s="25"/>
       <c r="R35" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O35:Q35)</f>
         <v>17</v>
       </c>
       <c r="S35" s="24">
@@ -17167,7 +17175,7 @@
       </c>
       <c r="Q36" s="23"/>
       <c r="R36" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O36:Q36)</f>
         <v>75</v>
       </c>
       <c r="S36" s="22">
@@ -17222,7 +17230,7 @@
       </c>
       <c r="Q37" s="25"/>
       <c r="R37" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O37:Q37)</f>
         <v>18</v>
       </c>
       <c r="S37" s="24">
@@ -17277,7 +17285,7 @@
       <c r="P38" s="23"/>
       <c r="Q38" s="23"/>
       <c r="R38" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O38:Q38)</f>
         <v>33</v>
       </c>
       <c r="S38" s="22">
@@ -17332,7 +17340,7 @@
       </c>
       <c r="Q39" s="25"/>
       <c r="R39" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O39:Q39)</f>
         <v>55</v>
       </c>
       <c r="S39" s="24">
@@ -17387,7 +17395,7 @@
         <v>45</v>
       </c>
       <c r="R40" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O40:Q40)</f>
         <v>45</v>
       </c>
       <c r="S40" s="22">
@@ -17442,7 +17450,7 @@
       <c r="P41" s="25"/>
       <c r="Q41" s="25"/>
       <c r="R41" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O41:Q41)</f>
         <v>15</v>
       </c>
       <c r="S41" s="24">
@@ -17497,7 +17505,7 @@
         <v>21</v>
       </c>
       <c r="R42" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O42:Q42)</f>
         <v>21</v>
       </c>
       <c r="S42" s="22">
@@ -17552,7 +17560,7 @@
       <c r="P43" s="25"/>
       <c r="Q43" s="25"/>
       <c r="R43" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O43:Q43)</f>
         <v>40</v>
       </c>
       <c r="S43" s="24">
@@ -17607,7 +17615,7 @@
       </c>
       <c r="Q44" s="23"/>
       <c r="R44" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O44:Q44)</f>
         <v>45</v>
       </c>
       <c r="S44" s="22">
@@ -17662,7 +17670,7 @@
       <c r="P45" s="25"/>
       <c r="Q45" s="25"/>
       <c r="R45" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O45:Q45)</f>
         <v>13</v>
       </c>
       <c r="S45" s="24">
@@ -17717,7 +17725,7 @@
       <c r="P46" s="23"/>
       <c r="Q46" s="23"/>
       <c r="R46" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O46:Q46)</f>
         <v>35</v>
       </c>
       <c r="S46" s="22">
@@ -17774,7 +17782,7 @@
       </c>
       <c r="Q47" s="25"/>
       <c r="R47" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O47:Q47)</f>
         <v>71</v>
       </c>
       <c r="S47" s="24">
@@ -17833,7 +17841,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O48:Q48)</f>
         <v>329</v>
       </c>
       <c r="S48" s="22">
@@ -17888,7 +17896,7 @@
       <c r="P49" s="25"/>
       <c r="Q49" s="25"/>
       <c r="R49" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O49:Q49)</f>
         <v>26</v>
       </c>
       <c r="S49" s="24">
@@ -17943,7 +17951,7 @@
       <c r="P50" s="23"/>
       <c r="Q50" s="23"/>
       <c r="R50" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O50:Q50)</f>
         <v>35</v>
       </c>
       <c r="S50" s="22">
@@ -17998,7 +18006,7 @@
       </c>
       <c r="Q51" s="25"/>
       <c r="R51" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O51:Q51)</f>
         <v>46</v>
       </c>
       <c r="S51" s="24">
@@ -18053,7 +18061,7 @@
       </c>
       <c r="Q52" s="23"/>
       <c r="R52" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O52:Q52)</f>
         <v>52</v>
       </c>
       <c r="S52" s="22">
@@ -18108,7 +18116,7 @@
       <c r="P53" s="25"/>
       <c r="Q53" s="25"/>
       <c r="R53" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O53:Q53)</f>
         <v>34</v>
       </c>
       <c r="S53" s="24">
@@ -18163,7 +18171,7 @@
       <c r="P54" s="23"/>
       <c r="Q54" s="23"/>
       <c r="R54" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O54:Q54)</f>
         <v>27</v>
       </c>
       <c r="S54" s="22">
@@ -18218,7 +18226,7 @@
       <c r="P55" s="25"/>
       <c r="Q55" s="25"/>
       <c r="R55" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O55:Q55)</f>
         <v>16</v>
       </c>
       <c r="S55" s="24">
@@ -18273,7 +18281,7 @@
       </c>
       <c r="Q56" s="23"/>
       <c r="R56" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O56:Q56)</f>
         <v>55</v>
       </c>
       <c r="S56" s="22">
@@ -18328,7 +18336,7 @@
       <c r="P57" s="25"/>
       <c r="Q57" s="25"/>
       <c r="R57" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O57:Q57)</f>
         <v>14</v>
       </c>
       <c r="S57" s="24">
@@ -18383,7 +18391,7 @@
       </c>
       <c r="Q58" s="23"/>
       <c r="R58" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O58:Q58)</f>
         <v>47</v>
       </c>
       <c r="S58" s="22">
@@ -18438,7 +18446,7 @@
       <c r="P59" s="25"/>
       <c r="Q59" s="25"/>
       <c r="R59" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O59:Q59)</f>
         <v>31</v>
       </c>
       <c r="S59" s="24">
@@ -18493,7 +18501,7 @@
       </c>
       <c r="Q60" s="23"/>
       <c r="R60" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O60:Q60)</f>
         <v>28</v>
       </c>
       <c r="S60" s="22">
@@ -18548,7 +18556,7 @@
       </c>
       <c r="Q61" s="25"/>
       <c r="R61" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O61:Q61)</f>
         <v>34</v>
       </c>
       <c r="S61" s="24">
@@ -18603,7 +18611,7 @@
       </c>
       <c r="Q62" s="23"/>
       <c r="R62" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O62:Q62)</f>
         <v>60</v>
       </c>
       <c r="S62" s="22">
@@ -18658,7 +18666,7 @@
       <c r="P63" s="25"/>
       <c r="Q63" s="25"/>
       <c r="R63" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O63:Q63)</f>
         <v>29</v>
       </c>
       <c r="S63" s="24">
@@ -18713,7 +18721,7 @@
       <c r="P64" s="23"/>
       <c r="Q64" s="23"/>
       <c r="R64" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O64:Q64)</f>
         <v>26</v>
       </c>
       <c r="S64" s="22">
@@ -18768,7 +18776,7 @@
       </c>
       <c r="Q65" s="25"/>
       <c r="R65" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O65:Q65)</f>
         <v>47</v>
       </c>
       <c r="S65" s="24">
@@ -18823,7 +18831,7 @@
       <c r="P66" s="23"/>
       <c r="Q66" s="23"/>
       <c r="R66" s="23">
-        <f t="shared" ref="R66:R129" si="1">SUM(O66:Q66)</f>
+        <f>SUM(O66:Q66)</f>
         <v>20</v>
       </c>
       <c r="S66" s="22">
@@ -18878,7 +18886,7 @@
       </c>
       <c r="Q67" s="25"/>
       <c r="R67" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O67:Q67)</f>
         <v>43</v>
       </c>
       <c r="S67" s="24">
@@ -18933,7 +18941,7 @@
       <c r="P68" s="23"/>
       <c r="Q68" s="23"/>
       <c r="R68" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O68:Q68)</f>
         <v>15</v>
       </c>
       <c r="S68" s="22">
@@ -18988,7 +18996,7 @@
       <c r="P69" s="25"/>
       <c r="Q69" s="25"/>
       <c r="R69" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O69:Q69)</f>
         <v>29</v>
       </c>
       <c r="S69" s="24">
@@ -19043,7 +19051,7 @@
       </c>
       <c r="Q70" s="23"/>
       <c r="R70" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O70:Q70)</f>
         <v>46</v>
       </c>
       <c r="S70" s="22">
@@ -19098,7 +19106,7 @@
       <c r="P71" s="25"/>
       <c r="Q71" s="25"/>
       <c r="R71" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O71:Q71)</f>
         <v>14</v>
       </c>
       <c r="S71" s="24">
@@ -19153,7 +19161,7 @@
       <c r="P72" s="23"/>
       <c r="Q72" s="23"/>
       <c r="R72" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O72:Q72)</f>
         <v>12</v>
       </c>
       <c r="S72" s="22">
@@ -19208,7 +19216,7 @@
       <c r="P73" s="25"/>
       <c r="Q73" s="25"/>
       <c r="R73" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O73:Q73)</f>
         <v>18</v>
       </c>
       <c r="S73" s="24">
@@ -19263,7 +19271,7 @@
       <c r="P74" s="23"/>
       <c r="Q74" s="23"/>
       <c r="R74" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O74:Q74)</f>
         <v>30</v>
       </c>
       <c r="S74" s="22">
@@ -19318,7 +19326,7 @@
         <v>37</v>
       </c>
       <c r="R75" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O75:Q75)</f>
         <v>37</v>
       </c>
       <c r="S75" s="24">
@@ -19373,7 +19381,7 @@
       </c>
       <c r="Q76" s="23"/>
       <c r="R76" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O76:Q76)</f>
         <v>47</v>
       </c>
       <c r="S76" s="22">
@@ -19428,7 +19436,7 @@
       <c r="P77" s="25"/>
       <c r="Q77" s="25"/>
       <c r="R77" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O77:Q77)</f>
         <v>30</v>
       </c>
       <c r="S77" s="24">
@@ -19483,7 +19491,7 @@
       <c r="P78" s="23"/>
       <c r="Q78" s="23"/>
       <c r="R78" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O78:Q78)</f>
         <v>19</v>
       </c>
       <c r="S78" s="22">
@@ -19538,7 +19546,7 @@
       </c>
       <c r="Q79" s="25"/>
       <c r="R79" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O79:Q79)</f>
         <v>37</v>
       </c>
       <c r="S79" s="24">
@@ -19593,7 +19601,7 @@
       <c r="P80" s="23"/>
       <c r="Q80" s="23"/>
       <c r="R80" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O80:Q80)</f>
         <v>19</v>
       </c>
       <c r="S80" s="22">
@@ -19648,7 +19656,7 @@
       <c r="P81" s="25"/>
       <c r="Q81" s="25"/>
       <c r="R81" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O81:Q81)</f>
         <v>20</v>
       </c>
       <c r="S81" s="24">
@@ -19703,7 +19711,7 @@
       <c r="P82" s="23"/>
       <c r="Q82" s="23"/>
       <c r="R82" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O82:Q82)</f>
         <v>50</v>
       </c>
       <c r="S82" s="22">
@@ -19758,7 +19766,7 @@
       <c r="P83" s="25"/>
       <c r="Q83" s="25"/>
       <c r="R83" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O83:Q83)</f>
         <v>17</v>
       </c>
       <c r="S83" s="24">
@@ -19813,7 +19821,7 @@
       </c>
       <c r="Q84" s="23"/>
       <c r="R84" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O84:Q84)</f>
         <v>25</v>
       </c>
       <c r="S84" s="22">
@@ -19868,7 +19876,7 @@
         <v>49</v>
       </c>
       <c r="R85" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O85:Q85)</f>
         <v>49</v>
       </c>
       <c r="S85" s="24">
@@ -19923,7 +19931,7 @@
       </c>
       <c r="Q86" s="23"/>
       <c r="R86" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O86:Q86)</f>
         <v>34</v>
       </c>
       <c r="S86" s="22">
@@ -19978,7 +19986,7 @@
       <c r="P87" s="25"/>
       <c r="Q87" s="25"/>
       <c r="R87" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O87:Q87)</f>
         <v>19</v>
       </c>
       <c r="S87" s="24">
@@ -20037,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="R88" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O88:Q88)</f>
         <v>312</v>
       </c>
       <c r="S88" s="22">
@@ -20092,7 +20100,7 @@
       </c>
       <c r="Q89" s="25"/>
       <c r="R89" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O89:Q89)</f>
         <v>57</v>
       </c>
       <c r="S89" s="24">
@@ -20147,7 +20155,7 @@
       </c>
       <c r="Q90" s="23"/>
       <c r="R90" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O90:Q90)</f>
         <v>50</v>
       </c>
       <c r="S90" s="22">
@@ -20202,7 +20210,7 @@
       <c r="P91" s="25"/>
       <c r="Q91" s="25"/>
       <c r="R91" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O91:Q91)</f>
         <v>18</v>
       </c>
       <c r="S91" s="24">
@@ -20257,7 +20265,7 @@
       <c r="P92" s="23"/>
       <c r="Q92" s="23"/>
       <c r="R92" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O92:Q92)</f>
         <v>18</v>
       </c>
       <c r="S92" s="22">
@@ -20312,7 +20320,7 @@
       </c>
       <c r="Q93" s="25"/>
       <c r="R93" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O93:Q93)</f>
         <v>40</v>
       </c>
       <c r="S93" s="24">
@@ -20367,7 +20375,7 @@
       </c>
       <c r="Q94" s="23"/>
       <c r="R94" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O94:Q94)</f>
         <v>37</v>
       </c>
       <c r="S94" s="22">
@@ -20422,7 +20430,7 @@
         <v>96</v>
       </c>
       <c r="R95" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O95:Q95)</f>
         <v>96</v>
       </c>
       <c r="S95" s="24">
@@ -20477,7 +20485,7 @@
       <c r="P96" s="23"/>
       <c r="Q96" s="23"/>
       <c r="R96" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O96:Q96)</f>
         <v>19</v>
       </c>
       <c r="S96" s="22">
@@ -20532,7 +20540,7 @@
       </c>
       <c r="Q97" s="25"/>
       <c r="R97" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O97:Q97)</f>
         <v>65</v>
       </c>
       <c r="S97" s="24">
@@ -20587,7 +20595,7 @@
       <c r="P98" s="23"/>
       <c r="Q98" s="23"/>
       <c r="R98" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O98:Q98)</f>
         <v>19</v>
       </c>
       <c r="S98" s="22">
@@ -20642,7 +20650,7 @@
       <c r="P99" s="25"/>
       <c r="Q99" s="25"/>
       <c r="R99" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O99:Q99)</f>
         <v>19</v>
       </c>
       <c r="S99" s="24">
@@ -20697,7 +20705,7 @@
       <c r="P100" s="23"/>
       <c r="Q100" s="23"/>
       <c r="R100" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O100:Q100)</f>
         <v>20</v>
       </c>
       <c r="S100" s="22">
@@ -20752,7 +20760,7 @@
       </c>
       <c r="Q101" s="25"/>
       <c r="R101" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O101:Q101)</f>
         <v>63</v>
       </c>
       <c r="S101" s="24">
@@ -20807,7 +20815,7 @@
       <c r="P102" s="23"/>
       <c r="Q102" s="23"/>
       <c r="R102" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O102:Q102)</f>
         <v>18</v>
       </c>
       <c r="S102" s="22">
@@ -20862,7 +20870,7 @@
       <c r="P103" s="25"/>
       <c r="Q103" s="25"/>
       <c r="R103" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O103:Q103)</f>
         <v>31</v>
       </c>
       <c r="S103" s="24">
@@ -20917,7 +20925,7 @@
       </c>
       <c r="Q104" s="23"/>
       <c r="R104" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O104:Q104)</f>
         <v>59</v>
       </c>
       <c r="S104" s="22">
@@ -20972,7 +20980,7 @@
       <c r="P105" s="25"/>
       <c r="Q105" s="25"/>
       <c r="R105" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O105:Q105)</f>
         <v>25</v>
       </c>
       <c r="S105" s="24">
@@ -21027,7 +21035,7 @@
       </c>
       <c r="Q106" s="23"/>
       <c r="R106" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O106:Q106)</f>
         <v>34</v>
       </c>
       <c r="S106" s="22">
@@ -21082,7 +21090,7 @@
       <c r="P107" s="25"/>
       <c r="Q107" s="25"/>
       <c r="R107" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O107:Q107)</f>
         <v>19</v>
       </c>
       <c r="S107" s="24">
@@ -21141,7 +21149,7 @@
         <v>0</v>
       </c>
       <c r="R108" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O108:Q108)</f>
         <v>353</v>
       </c>
       <c r="S108" s="22">
@@ -21196,7 +21204,7 @@
       <c r="P109" s="25"/>
       <c r="Q109" s="25"/>
       <c r="R109" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O109:Q109)</f>
         <v>28</v>
       </c>
       <c r="S109" s="24">
@@ -21251,7 +21259,7 @@
       <c r="P110" s="23"/>
       <c r="Q110" s="23"/>
       <c r="R110" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O110:Q110)</f>
         <v>215</v>
       </c>
       <c r="S110" s="22">
@@ -21306,7 +21314,7 @@
       <c r="P111" s="25"/>
       <c r="Q111" s="25"/>
       <c r="R111" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O111:Q111)</f>
         <v>55</v>
       </c>
       <c r="S111" s="24">
@@ -21361,7 +21369,7 @@
       <c r="P112" s="23"/>
       <c r="Q112" s="23"/>
       <c r="R112" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O112:Q112)</f>
         <v>11</v>
       </c>
       <c r="S112" s="22">
@@ -21416,7 +21424,7 @@
       <c r="P113" s="25"/>
       <c r="Q113" s="25"/>
       <c r="R113" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O113:Q113)</f>
         <v>26</v>
       </c>
       <c r="S113" s="24">
@@ -21471,7 +21479,7 @@
       <c r="P114" s="23"/>
       <c r="Q114" s="23"/>
       <c r="R114" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O114:Q114)</f>
         <v>8</v>
       </c>
       <c r="S114" s="22">
@@ -21530,7 +21538,7 @@
         <v>0</v>
       </c>
       <c r="R115" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O115:Q115)</f>
         <v>38</v>
       </c>
       <c r="S115" s="24">
@@ -21591,7 +21599,7 @@
       </c>
       <c r="Q116" s="23"/>
       <c r="R116" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O116:Q116)</f>
         <v>18</v>
       </c>
       <c r="S116" s="22">
@@ -21652,7 +21660,7 @@
       </c>
       <c r="Q117" s="25"/>
       <c r="R117" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O117:Q117)</f>
         <v>45</v>
       </c>
       <c r="S117" s="24">
@@ -21713,7 +21721,7 @@
       </c>
       <c r="Q118" s="23"/>
       <c r="R118" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O118:Q118)</f>
         <v>45</v>
       </c>
       <c r="S118" s="22">
@@ -21774,7 +21782,7 @@
       </c>
       <c r="Q119" s="25"/>
       <c r="R119" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O119:Q119)</f>
         <v>44</v>
       </c>
       <c r="S119" s="24">
@@ -21835,7 +21843,7 @@
       </c>
       <c r="Q120" s="23"/>
       <c r="R120" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O120:Q120)</f>
         <v>50</v>
       </c>
       <c r="S120" s="22">
@@ -21896,7 +21904,7 @@
       </c>
       <c r="Q121" s="25"/>
       <c r="R121" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O121:Q121)</f>
         <v>41</v>
       </c>
       <c r="S121" s="24">
@@ -21957,7 +21965,7 @@
       </c>
       <c r="Q122" s="23"/>
       <c r="R122" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O122:Q122)</f>
         <v>44</v>
       </c>
       <c r="S122" s="22">
@@ -22018,7 +22026,7 @@
       </c>
       <c r="Q123" s="25"/>
       <c r="R123" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O123:Q123)</f>
         <v>40</v>
       </c>
       <c r="S123" s="24">
@@ -22079,7 +22087,7 @@
       </c>
       <c r="Q124" s="23"/>
       <c r="R124" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O124:Q124)</f>
         <v>12</v>
       </c>
       <c r="S124" s="22">
@@ -22140,7 +22148,7 @@
       </c>
       <c r="Q125" s="25"/>
       <c r="R125" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O125:Q125)</f>
         <v>19</v>
       </c>
       <c r="S125" s="24">
@@ -22201,7 +22209,7 @@
       </c>
       <c r="Q126" s="23"/>
       <c r="R126" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O126:Q126)</f>
         <v>14</v>
       </c>
       <c r="S126" s="22">
@@ -22262,7 +22270,7 @@
       </c>
       <c r="Q127" s="25"/>
       <c r="R127" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O127:Q127)</f>
         <v>19</v>
       </c>
       <c r="S127" s="24">
@@ -22323,7 +22331,7 @@
       </c>
       <c r="Q128" s="23"/>
       <c r="R128" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O128:Q128)</f>
         <v>9</v>
       </c>
       <c r="S128" s="22">
@@ -22384,7 +22392,7 @@
       </c>
       <c r="Q129" s="25"/>
       <c r="R129" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O129:Q129)</f>
         <v>45</v>
       </c>
       <c r="S129" s="24">
@@ -22445,7 +22453,7 @@
       </c>
       <c r="Q130" s="23"/>
       <c r="R130" s="23">
-        <f t="shared" ref="R130:R193" si="2">SUM(O130:Q130)</f>
+        <f>SUM(O130:Q130)</f>
         <v>25</v>
       </c>
       <c r="S130" s="22">
@@ -22506,7 +22514,7 @@
       </c>
       <c r="Q131" s="25"/>
       <c r="R131" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O131:Q131)</f>
         <v>15</v>
       </c>
       <c r="S131" s="24">
@@ -22567,7 +22575,7 @@
       </c>
       <c r="Q132" s="23"/>
       <c r="R132" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O132:Q132)</f>
         <v>26</v>
       </c>
       <c r="S132" s="22">
@@ -22628,7 +22636,7 @@
       </c>
       <c r="Q133" s="25"/>
       <c r="R133" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O133:Q133)</f>
         <v>16</v>
       </c>
       <c r="S133" s="24">
@@ -22689,7 +22697,7 @@
       </c>
       <c r="Q134" s="23"/>
       <c r="R134" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O134:Q134)</f>
         <v>15</v>
       </c>
       <c r="S134" s="22">
@@ -22750,7 +22758,7 @@
       </c>
       <c r="Q135" s="25"/>
       <c r="R135" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O135:Q135)</f>
         <v>14</v>
       </c>
       <c r="S135" s="24">
@@ -22811,7 +22819,7 @@
       </c>
       <c r="Q136" s="23"/>
       <c r="R136" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O136:Q136)</f>
         <v>182</v>
       </c>
       <c r="S136" s="22">
@@ -22872,7 +22880,7 @@
       </c>
       <c r="Q137" s="25"/>
       <c r="R137" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O137:Q137)</f>
         <v>34</v>
       </c>
       <c r="S137" s="24">
@@ -22935,7 +22943,7 @@
         <v>0</v>
       </c>
       <c r="R138" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O138:Q138)</f>
         <v>17</v>
       </c>
       <c r="S138" s="22">
@@ -22996,7 +23004,7 @@
       </c>
       <c r="Q139" s="25"/>
       <c r="R139" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O139:Q139)</f>
         <v>20</v>
       </c>
       <c r="S139" s="24">
@@ -23057,7 +23065,7 @@
       </c>
       <c r="Q140" s="23"/>
       <c r="R140" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O140:Q140)</f>
         <v>40</v>
       </c>
       <c r="S140" s="22">
@@ -23120,7 +23128,7 @@
         <v>0</v>
       </c>
       <c r="R141" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O141:Q141)</f>
         <v>12</v>
       </c>
       <c r="S141" s="24">
@@ -23181,7 +23189,7 @@
       </c>
       <c r="Q142" s="23"/>
       <c r="R142" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O142:Q142)</f>
         <v>12</v>
       </c>
       <c r="S142" s="22">
@@ -23242,7 +23250,7 @@
       </c>
       <c r="Q143" s="25"/>
       <c r="R143" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O143:Q143)</f>
         <v>19</v>
       </c>
       <c r="S143" s="24">
@@ -23303,7 +23311,7 @@
       </c>
       <c r="Q144" s="23"/>
       <c r="R144" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O144:Q144)</f>
         <v>12</v>
       </c>
       <c r="S144" s="22">
@@ -23366,7 +23374,7 @@
         <v>0</v>
       </c>
       <c r="R145" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O145:Q145)</f>
         <v>31</v>
       </c>
       <c r="S145" s="24">
@@ -23427,7 +23435,7 @@
       </c>
       <c r="Q146" s="23"/>
       <c r="R146" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O146:Q146)</f>
         <v>27</v>
       </c>
       <c r="S146" s="22">
@@ -23488,7 +23496,7 @@
         <v>0</v>
       </c>
       <c r="R147" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O147:Q147)</f>
         <v>54</v>
       </c>
       <c r="S147" s="24">
@@ -23549,7 +23557,7 @@
       </c>
       <c r="Q148" s="23"/>
       <c r="R148" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O148:Q148)</f>
         <v>9</v>
       </c>
       <c r="S148" s="22">
@@ -23610,7 +23618,7 @@
       </c>
       <c r="Q149" s="25"/>
       <c r="R149" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O149:Q149)</f>
         <v>38</v>
       </c>
       <c r="S149" s="24">
@@ -23671,7 +23679,7 @@
       </c>
       <c r="Q150" s="23"/>
       <c r="R150" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O150:Q150)</f>
         <v>62</v>
       </c>
       <c r="S150" s="22">
@@ -23732,7 +23740,7 @@
       </c>
       <c r="Q151" s="25"/>
       <c r="R151" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O151:Q151)</f>
         <v>13</v>
       </c>
       <c r="S151" s="24">
@@ -23793,7 +23801,7 @@
       </c>
       <c r="Q152" s="23"/>
       <c r="R152" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O152:Q152)</f>
         <v>8</v>
       </c>
       <c r="S152" s="22">
@@ -23854,7 +23862,7 @@
       </c>
       <c r="Q153" s="25"/>
       <c r="R153" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O153:Q153)</f>
         <v>20</v>
       </c>
       <c r="S153" s="24">
@@ -23917,7 +23925,7 @@
         <v>0</v>
       </c>
       <c r="R154" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O154:Q154)</f>
         <v>74</v>
       </c>
       <c r="S154" s="22">
@@ -23978,7 +23986,7 @@
       </c>
       <c r="Q155" s="25"/>
       <c r="R155" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O155:Q155)</f>
         <v>24</v>
       </c>
       <c r="S155" s="24">
@@ -24041,7 +24049,7 @@
         <v>0</v>
       </c>
       <c r="R156" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O156:Q156)</f>
         <v>21</v>
       </c>
       <c r="S156" s="22">
@@ -24104,7 +24112,7 @@
         <v>0</v>
       </c>
       <c r="R157" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O157:Q157)</f>
         <v>21</v>
       </c>
       <c r="S157" s="24">
@@ -24167,7 +24175,7 @@
         <v>0</v>
       </c>
       <c r="R158" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O158:Q158)</f>
         <v>13</v>
       </c>
       <c r="S158" s="22">
@@ -24230,7 +24238,7 @@
         <v>78</v>
       </c>
       <c r="R159" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O159:Q159)</f>
         <v>117</v>
       </c>
       <c r="S159" s="24">
@@ -24293,7 +24301,7 @@
         <v>0</v>
       </c>
       <c r="R160" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O160:Q160)</f>
         <v>20</v>
       </c>
       <c r="S160" s="22">
@@ -24357,7 +24365,7 @@
         <v>0</v>
       </c>
       <c r="R161" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O161:Q161)</f>
         <v>22</v>
       </c>
       <c r="S161" s="24">
@@ -24420,7 +24428,7 @@
         <v>0</v>
       </c>
       <c r="R162" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O162:Q162)</f>
         <v>21</v>
       </c>
       <c r="S162" s="22">
@@ -24483,7 +24491,7 @@
         <v>0</v>
       </c>
       <c r="R163" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O163:Q163)</f>
         <v>59</v>
       </c>
       <c r="S163" s="24">
@@ -24546,7 +24554,7 @@
         <v>0</v>
       </c>
       <c r="R164" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O164:Q164)</f>
         <v>24</v>
       </c>
       <c r="S164" s="22">
@@ -24609,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="R165" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O165:Q165)</f>
         <v>41</v>
       </c>
       <c r="S165" s="24">
@@ -24672,7 +24680,7 @@
         <v>0</v>
       </c>
       <c r="R166" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O166:Q166)</f>
         <v>35</v>
       </c>
       <c r="S166" s="22">
@@ -24735,7 +24743,7 @@
         <v>0</v>
       </c>
       <c r="R167" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O167:Q167)</f>
         <v>15</v>
       </c>
       <c r="S167" s="24">
@@ -24798,7 +24806,7 @@
         <v>0</v>
       </c>
       <c r="R168" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O168:Q168)</f>
         <v>23</v>
       </c>
       <c r="S168" s="22">
@@ -24861,7 +24869,7 @@
         <v>0</v>
       </c>
       <c r="R169" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O169:Q169)</f>
         <v>36</v>
       </c>
       <c r="S169" s="24">
@@ -24924,7 +24932,7 @@
         <v>0</v>
       </c>
       <c r="R170" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O170:Q170)</f>
         <v>84</v>
       </c>
       <c r="S170" s="22">
@@ -24987,7 +24995,7 @@
         <v>0</v>
       </c>
       <c r="R171" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O171:Q171)</f>
         <v>40</v>
       </c>
       <c r="S171" s="24">
@@ -25050,7 +25058,7 @@
         <v>0</v>
       </c>
       <c r="R172" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O172:Q172)</f>
         <v>40</v>
       </c>
       <c r="S172" s="22">
@@ -25113,7 +25121,7 @@
         <v>0</v>
       </c>
       <c r="R173" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O173:Q173)</f>
         <v>44</v>
       </c>
       <c r="S173" s="24">
@@ -25176,7 +25184,7 @@
         <v>0</v>
       </c>
       <c r="R174" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O174:Q174)</f>
         <v>31</v>
       </c>
       <c r="S174" s="22">
@@ -25239,7 +25247,7 @@
         <v>0</v>
       </c>
       <c r="R175" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O175:Q175)</f>
         <v>29</v>
       </c>
       <c r="S175" s="24">
@@ -25302,7 +25310,7 @@
         <v>97</v>
       </c>
       <c r="R176" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O176:Q176)</f>
         <v>119</v>
       </c>
       <c r="S176" s="22">
@@ -25366,7 +25374,7 @@
         <v>0</v>
       </c>
       <c r="R177" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O177:Q177)</f>
         <v>122</v>
       </c>
       <c r="S177" s="24">
@@ -25430,7 +25438,7 @@
         <v>0</v>
       </c>
       <c r="R178" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O178:Q178)</f>
         <v>116</v>
       </c>
       <c r="S178" s="22">
@@ -25494,7 +25502,7 @@
         <v>0</v>
       </c>
       <c r="R179" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O179:Q179)</f>
         <v>83</v>
       </c>
       <c r="S179" s="24">
@@ -25557,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="R180" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O180:Q180)</f>
         <v>69</v>
       </c>
       <c r="S180" s="22">
@@ -25620,7 +25628,7 @@
         <v>0</v>
       </c>
       <c r="R181" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O181:Q181)</f>
         <v>48</v>
       </c>
       <c r="S181" s="24">
@@ -25683,7 +25691,7 @@
         <v>0</v>
       </c>
       <c r="R182" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O182:Q182)</f>
         <v>19</v>
       </c>
       <c r="S182" s="22">
@@ -25746,7 +25754,7 @@
         <v>73</v>
       </c>
       <c r="R183" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O183:Q183)</f>
         <v>73</v>
       </c>
       <c r="S183" s="24">
@@ -25809,7 +25817,7 @@
         <v>0</v>
       </c>
       <c r="R184" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O184:Q184)</f>
         <v>94</v>
       </c>
       <c r="S184" s="22">
@@ -25872,7 +25880,7 @@
         <v>0</v>
       </c>
       <c r="R185" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O185:Q185)</f>
         <v>42</v>
       </c>
       <c r="S185" s="24">
@@ -25935,7 +25943,7 @@
         <v>0</v>
       </c>
       <c r="R186" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O186:Q186)</f>
         <v>32</v>
       </c>
       <c r="S186" s="22">
@@ -25998,7 +26006,7 @@
         <v>0</v>
       </c>
       <c r="R187" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O187:Q187)</f>
         <v>22</v>
       </c>
       <c r="S187" s="24">
@@ -26062,7 +26070,7 @@
         <v>0</v>
       </c>
       <c r="R188" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O188:Q188)</f>
         <v>590</v>
       </c>
       <c r="S188" s="22">
@@ -26126,7 +26134,7 @@
         <v>0</v>
       </c>
       <c r="R189" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O189:Q189)</f>
         <v>41</v>
       </c>
       <c r="S189" s="24">
@@ -26189,7 +26197,7 @@
         <v>0</v>
       </c>
       <c r="R190" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O190:Q190)</f>
         <v>80</v>
       </c>
       <c r="S190" s="22">
@@ -26253,7 +26261,7 @@
         <v>36</v>
       </c>
       <c r="R191" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O191:Q191)</f>
         <v>36</v>
       </c>
       <c r="S191" s="24">
@@ -26316,7 +26324,7 @@
         <v>0</v>
       </c>
       <c r="R192" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O192:Q192)</f>
         <v>70</v>
       </c>
       <c r="S192" s="22">
@@ -26379,7 +26387,7 @@
         <v>0</v>
       </c>
       <c r="R193" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O193:Q193)</f>
         <v>21</v>
       </c>
       <c r="S193" s="24">
@@ -26442,7 +26450,7 @@
         <v>0</v>
       </c>
       <c r="R194" s="23">
-        <f t="shared" ref="R194:R257" si="3">SUM(O194:Q194)</f>
+        <f>SUM(O194:Q194)</f>
         <v>20</v>
       </c>
       <c r="S194" s="22">
@@ -26505,7 +26513,7 @@
         <v>0</v>
       </c>
       <c r="R195" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O195:Q195)</f>
         <v>28</v>
       </c>
       <c r="S195" s="24">
@@ -26568,7 +26576,7 @@
         <v>0</v>
       </c>
       <c r="R196" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O196:Q196)</f>
         <v>25</v>
       </c>
       <c r="S196" s="22">
@@ -26631,7 +26639,7 @@
         <v>0</v>
       </c>
       <c r="R197" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O197:Q197)</f>
         <v>14</v>
       </c>
       <c r="S197" s="24">
@@ -26694,7 +26702,7 @@
         <v>0</v>
       </c>
       <c r="R198" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O198:Q198)</f>
         <v>46</v>
       </c>
       <c r="S198" s="22">
@@ -26757,7 +26765,7 @@
         <v>0</v>
       </c>
       <c r="R199" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O199:Q199)</f>
         <v>98</v>
       </c>
       <c r="S199" s="24">
@@ -26820,7 +26828,7 @@
         <v>44</v>
       </c>
       <c r="R200" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O200:Q200)</f>
         <v>50</v>
       </c>
       <c r="S200" s="22">
@@ -26883,7 +26891,7 @@
         <v>0</v>
       </c>
       <c r="R201" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O201:Q201)</f>
         <v>17</v>
       </c>
       <c r="S201" s="24">
@@ -26946,7 +26954,7 @@
         <v>0</v>
       </c>
       <c r="R202" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O202:Q202)</f>
         <v>53</v>
       </c>
       <c r="S202" s="22">
@@ -27009,7 +27017,7 @@
         <v>0</v>
       </c>
       <c r="R203" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O203:Q203)</f>
         <v>16</v>
       </c>
       <c r="S203" s="24">
@@ -27072,7 +27080,7 @@
         <v>59</v>
       </c>
       <c r="R204" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O204:Q204)</f>
         <v>59</v>
       </c>
       <c r="S204" s="22">
@@ -27135,7 +27143,7 @@
         <v>0</v>
       </c>
       <c r="R205" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O205:Q205)</f>
         <v>76</v>
       </c>
       <c r="S205" s="24">
@@ -27198,7 +27206,7 @@
         <v>0</v>
       </c>
       <c r="R206" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O206:Q206)</f>
         <v>33</v>
       </c>
       <c r="S206" s="22">
@@ -27261,7 +27269,7 @@
         <v>0</v>
       </c>
       <c r="R207" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O207:Q207)</f>
         <v>58</v>
       </c>
       <c r="S207" s="24">
@@ -27324,7 +27332,7 @@
         <v>37</v>
       </c>
       <c r="R208" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O208:Q208)</f>
         <v>60</v>
       </c>
       <c r="S208" s="22">
@@ -27387,7 +27395,7 @@
         <v>0</v>
       </c>
       <c r="R209" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O209:Q209)</f>
         <v>13</v>
       </c>
       <c r="S209" s="24">
@@ -27450,7 +27458,7 @@
         <v>0</v>
       </c>
       <c r="R210" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O210:Q210)</f>
         <v>14</v>
       </c>
       <c r="S210" s="22">
@@ -27513,7 +27521,7 @@
         <v>0</v>
       </c>
       <c r="R211" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O211:Q211)</f>
         <v>53</v>
       </c>
       <c r="S211" s="24">
@@ -27576,7 +27584,7 @@
         <v>0</v>
       </c>
       <c r="R212" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O212:Q212)</f>
         <v>105</v>
       </c>
       <c r="S212" s="22">
@@ -27639,7 +27647,7 @@
         <v>147</v>
       </c>
       <c r="R213" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O213:Q213)</f>
         <v>635</v>
       </c>
       <c r="S213" s="24">
@@ -27702,7 +27710,7 @@
         <v>0</v>
       </c>
       <c r="R214" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O214:Q214)</f>
         <v>34</v>
       </c>
       <c r="S214" s="22">
@@ -27765,7 +27773,7 @@
         <v>0</v>
       </c>
       <c r="R215" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O215:Q215)</f>
         <v>32</v>
       </c>
       <c r="S215" s="24">
@@ -27828,7 +27836,7 @@
         <v>0</v>
       </c>
       <c r="R216" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O216:Q216)</f>
         <v>10</v>
       </c>
       <c r="S216" s="22">
@@ -27891,7 +27899,7 @@
         <v>0</v>
       </c>
       <c r="R217" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O217:Q217)</f>
         <v>16</v>
       </c>
       <c r="S217" s="24">
@@ -27954,7 +27962,7 @@
         <v>0</v>
       </c>
       <c r="R218" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O218:Q218)</f>
         <v>20</v>
       </c>
       <c r="S218" s="22">
@@ -28018,7 +28026,7 @@
         <v>59</v>
       </c>
       <c r="R219" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O219:Q219)</f>
         <v>59</v>
       </c>
       <c r="S219" s="24">
@@ -28081,7 +28089,7 @@
         <v>0</v>
       </c>
       <c r="R220" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O220:Q220)</f>
         <v>70</v>
       </c>
       <c r="S220" s="22">
@@ -28144,7 +28152,7 @@
         <v>30</v>
       </c>
       <c r="R221" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O221:Q221)</f>
         <v>30</v>
       </c>
       <c r="S221" s="24">
@@ -28207,7 +28215,7 @@
         <v>0</v>
       </c>
       <c r="R222" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O222:Q222)</f>
         <v>14</v>
       </c>
       <c r="S222" s="22">
@@ -28270,7 +28278,7 @@
         <v>1</v>
       </c>
       <c r="R223" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O223:Q223)</f>
         <v>29</v>
       </c>
       <c r="S223" s="24">
@@ -28333,7 +28341,7 @@
         <v>0</v>
       </c>
       <c r="R224" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O224:Q224)</f>
         <v>37</v>
       </c>
       <c r="S224" s="22">
@@ -28396,7 +28404,7 @@
         <v>0</v>
       </c>
       <c r="R225" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O225:Q225)</f>
         <v>24</v>
       </c>
       <c r="S225" s="24">
@@ -28459,7 +28467,7 @@
         <v>0</v>
       </c>
       <c r="R226" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O226:Q226)</f>
         <v>32</v>
       </c>
       <c r="S226" s="22">
@@ -28522,7 +28530,7 @@
         <v>0</v>
       </c>
       <c r="R227" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O227:Q227)</f>
         <v>14</v>
       </c>
       <c r="S227" s="24">
@@ -28585,7 +28593,7 @@
         <v>0</v>
       </c>
       <c r="R228" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O228:Q228)</f>
         <v>31</v>
       </c>
       <c r="S228" s="22">
@@ -28648,7 +28656,7 @@
         <v>0</v>
       </c>
       <c r="R229" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O229:Q229)</f>
         <v>30</v>
       </c>
       <c r="S229" s="24">
@@ -28711,7 +28719,7 @@
         <v>5</v>
       </c>
       <c r="R230" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O230:Q230)</f>
         <v>52</v>
       </c>
       <c r="S230" s="22">
@@ -28774,7 +28782,7 @@
         <v>0</v>
       </c>
       <c r="R231" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O231:Q231)</f>
         <v>89</v>
       </c>
       <c r="S231" s="24">
@@ -28837,7 +28845,7 @@
         <v>0</v>
       </c>
       <c r="R232" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O232:Q232)</f>
         <v>13</v>
       </c>
       <c r="S232" s="22">
@@ -28900,7 +28908,7 @@
         <v>0</v>
       </c>
       <c r="R233" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O233:Q233)</f>
         <v>38</v>
       </c>
       <c r="S233" s="24">
@@ -28963,7 +28971,7 @@
         <v>0</v>
       </c>
       <c r="R234" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O234:Q234)</f>
         <v>44</v>
       </c>
       <c r="S234" s="22">
@@ -29026,7 +29034,7 @@
         <v>0</v>
       </c>
       <c r="R235" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O235:Q235)</f>
         <v>21</v>
       </c>
       <c r="S235" s="24">
@@ -29089,7 +29097,7 @@
         <v>0</v>
       </c>
       <c r="R236" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O236:Q236)</f>
         <v>45</v>
       </c>
       <c r="S236" s="22">
@@ -29152,7 +29160,7 @@
         <v>0</v>
       </c>
       <c r="R237" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O237:Q237)</f>
         <v>70</v>
       </c>
       <c r="S237" s="24">
@@ -29215,7 +29223,7 @@
         <v>0</v>
       </c>
       <c r="R238" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O238:Q238)</f>
         <v>15</v>
       </c>
       <c r="S238" s="22">
@@ -29278,7 +29286,7 @@
         <v>51</v>
       </c>
       <c r="R239" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O239:Q239)</f>
         <v>51</v>
       </c>
       <c r="S239" s="24">
@@ -29342,7 +29350,7 @@
         <v>31</v>
       </c>
       <c r="R240" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O240:Q240)</f>
         <v>31</v>
       </c>
       <c r="S240" s="22">
@@ -29405,7 +29413,7 @@
         <v>0</v>
       </c>
       <c r="R241" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O241:Q241)</f>
         <v>140</v>
       </c>
       <c r="S241" s="24">
@@ -29468,7 +29476,7 @@
         <v>0</v>
       </c>
       <c r="R242" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O242:Q242)</f>
         <v>15</v>
       </c>
       <c r="S242" s="22">
@@ -29531,7 +29539,7 @@
         <v>0</v>
       </c>
       <c r="R243" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O243:Q243)</f>
         <v>18</v>
       </c>
       <c r="S243" s="24">
@@ -29594,7 +29602,7 @@
         <v>0</v>
       </c>
       <c r="R244" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O244:Q244)</f>
         <v>55</v>
       </c>
       <c r="S244" s="22">
@@ -29657,7 +29665,7 @@
         <v>120</v>
       </c>
       <c r="R245" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O245:Q245)</f>
         <v>120</v>
       </c>
       <c r="S245" s="24">
@@ -29720,7 +29728,7 @@
         <v>22</v>
       </c>
       <c r="R246" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O246:Q246)</f>
         <v>34</v>
       </c>
       <c r="S246" s="22">
@@ -29783,7 +29791,7 @@
         <v>0</v>
       </c>
       <c r="R247" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O247:Q247)</f>
         <v>37</v>
       </c>
       <c r="S247" s="24">
@@ -29846,7 +29854,7 @@
         <v>0</v>
       </c>
       <c r="R248" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O248:Q248)</f>
         <v>6</v>
       </c>
       <c r="S248" s="22">
@@ -29909,7 +29917,7 @@
         <v>0</v>
       </c>
       <c r="R249" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O249:Q249)</f>
         <v>25</v>
       </c>
       <c r="S249" s="24">
@@ -29972,7 +29980,7 @@
         <v>0</v>
       </c>
       <c r="R250" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O250:Q250)</f>
         <v>26</v>
       </c>
       <c r="S250" s="22">
@@ -30035,7 +30043,7 @@
         <v>56</v>
       </c>
       <c r="R251" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O251:Q251)</f>
         <v>56</v>
       </c>
       <c r="S251" s="24">
@@ -30099,7 +30107,7 @@
         <v>0</v>
       </c>
       <c r="R252" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O252:Q252)</f>
         <v>26</v>
       </c>
       <c r="S252" s="22">
@@ -30162,7 +30170,7 @@
         <v>0</v>
       </c>
       <c r="R253" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O253:Q253)</f>
         <v>26</v>
       </c>
       <c r="S253" s="24">
@@ -30225,7 +30233,7 @@
         <v>0</v>
       </c>
       <c r="R254" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O254:Q254)</f>
         <v>11</v>
       </c>
       <c r="S254" s="22">
@@ -30286,7 +30294,7 @@
         <v>0</v>
       </c>
       <c r="R255" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O255:Q255)</f>
         <v>14</v>
       </c>
       <c r="S255" s="24">
@@ -30349,7 +30357,7 @@
         <v>49</v>
       </c>
       <c r="R256" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O256:Q256)</f>
         <v>49</v>
       </c>
       <c r="S256" s="22">
@@ -30412,7 +30420,7 @@
         <v>0</v>
       </c>
       <c r="R257" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O257:Q257)</f>
         <v>27</v>
       </c>
       <c r="S257" s="24">
@@ -30475,7 +30483,7 @@
         <v>7</v>
       </c>
       <c r="R258" s="23">
-        <f t="shared" ref="R258:R321" si="4">SUM(O258:Q258)</f>
+        <f>SUM(O258:Q258)</f>
         <v>22</v>
       </c>
       <c r="S258" s="22">
@@ -30538,7 +30546,7 @@
         <v>0</v>
       </c>
       <c r="R259" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O259:Q259)</f>
         <v>18</v>
       </c>
       <c r="S259" s="24">
@@ -30601,7 +30609,7 @@
         <v>31</v>
       </c>
       <c r="R260" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O260:Q260)</f>
         <v>31</v>
       </c>
       <c r="S260" s="22">
@@ -30664,7 +30672,7 @@
         <v>0</v>
       </c>
       <c r="R261" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O261:Q261)</f>
         <v>25</v>
       </c>
       <c r="S261" s="24">
@@ -30727,7 +30735,7 @@
         <v>0</v>
       </c>
       <c r="R262" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O262:Q262)</f>
         <v>9</v>
       </c>
       <c r="S262" s="22">
@@ -30790,7 +30798,7 @@
         <v>0</v>
       </c>
       <c r="R263" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O263:Q263)</f>
         <v>8</v>
       </c>
       <c r="S263" s="24">
@@ -30853,7 +30861,7 @@
         <v>29</v>
       </c>
       <c r="R264" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O264:Q264)</f>
         <v>29</v>
       </c>
       <c r="S264" s="22">
@@ -30916,7 +30924,7 @@
         <v>21</v>
       </c>
       <c r="R265" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O265:Q265)</f>
         <v>24</v>
       </c>
       <c r="S265" s="24">
@@ -30979,7 +30987,7 @@
         <v>0</v>
       </c>
       <c r="R266" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O266:Q266)</f>
         <v>66</v>
       </c>
       <c r="S266" s="22">
@@ -31042,7 +31050,7 @@
         <v>20</v>
       </c>
       <c r="R267" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O267:Q267)</f>
         <v>20</v>
       </c>
       <c r="S267" s="24">
@@ -31105,7 +31113,7 @@
         <v>0</v>
       </c>
       <c r="R268" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O268:Q268)</f>
         <v>13</v>
       </c>
       <c r="S268" s="22">
@@ -31168,7 +31176,7 @@
         <v>0</v>
       </c>
       <c r="R269" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O269:Q269)</f>
         <v>15</v>
       </c>
       <c r="S269" s="24">
@@ -31231,7 +31239,7 @@
         <v>0</v>
       </c>
       <c r="R270" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O270:Q270)</f>
         <v>5</v>
       </c>
       <c r="S270" s="22">
@@ -31294,7 +31302,7 @@
         <v>0</v>
       </c>
       <c r="R271" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O271:Q271)</f>
         <v>18</v>
       </c>
       <c r="S271" s="24">
@@ -31357,7 +31365,7 @@
         <v>0</v>
       </c>
       <c r="R272" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O272:Q272)</f>
         <v>8</v>
       </c>
       <c r="S272" s="22">
@@ -31420,7 +31428,7 @@
         <v>0</v>
       </c>
       <c r="R273" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O273:Q273)</f>
         <v>83</v>
       </c>
       <c r="S273" s="24">
@@ -31483,7 +31491,7 @@
         <v>0</v>
       </c>
       <c r="R274" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O274:Q274)</f>
         <v>24</v>
       </c>
       <c r="S274" s="22">
@@ -31546,7 +31554,7 @@
         <v>0</v>
       </c>
       <c r="R275" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O275:Q275)</f>
         <v>20</v>
       </c>
       <c r="S275" s="24">
@@ -31609,7 +31617,7 @@
         <v>39</v>
       </c>
       <c r="R276" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O276:Q276)</f>
         <v>39</v>
       </c>
       <c r="S276" s="22">
@@ -31672,7 +31680,7 @@
         <v>0</v>
       </c>
       <c r="R277" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O277:Q277)</f>
         <v>39</v>
       </c>
       <c r="S277" s="24">
@@ -31735,7 +31743,7 @@
         <v>0</v>
       </c>
       <c r="R278" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O278:Q278)</f>
         <v>277</v>
       </c>
       <c r="S278" s="22">
@@ -31798,7 +31806,7 @@
         <v>0</v>
       </c>
       <c r="R279" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O279:Q279)</f>
         <v>43</v>
       </c>
       <c r="S279" s="24">
@@ -31861,7 +31869,7 @@
         <v>0</v>
       </c>
       <c r="R280" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O280:Q280)</f>
         <v>21</v>
       </c>
       <c r="S280" s="22">
@@ -31924,7 +31932,7 @@
         <v>84</v>
       </c>
       <c r="R281" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O281:Q281)</f>
         <v>144</v>
       </c>
       <c r="S281" s="24">
@@ -31987,7 +31995,7 @@
         <v>0</v>
       </c>
       <c r="R282" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O282:Q282)</f>
         <v>19</v>
       </c>
       <c r="S282" s="22">
@@ -32050,7 +32058,7 @@
         <v>64</v>
       </c>
       <c r="R283" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O283:Q283)</f>
         <v>65</v>
       </c>
       <c r="S283" s="24">
@@ -32113,7 +32121,7 @@
         <v>0</v>
       </c>
       <c r="R284" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O284:Q284)</f>
         <v>72</v>
       </c>
       <c r="S284" s="22">
@@ -32176,7 +32184,7 @@
         <v>193</v>
       </c>
       <c r="R285" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O285:Q285)</f>
         <v>193</v>
       </c>
       <c r="S285" s="24">
@@ -32239,7 +32247,7 @@
         <v>0</v>
       </c>
       <c r="R286" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O286:Q286)</f>
         <v>46</v>
       </c>
       <c r="S286" s="22">
@@ -32302,7 +32310,7 @@
         <v>20</v>
       </c>
       <c r="R287" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O287:Q287)</f>
         <v>20</v>
       </c>
       <c r="S287" s="24">
@@ -32363,7 +32371,7 @@
         <v>0</v>
       </c>
       <c r="R288" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O288:Q288)</f>
         <v>23</v>
       </c>
       <c r="S288" s="22">
@@ -32424,7 +32432,7 @@
         <v>0</v>
       </c>
       <c r="R289" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O289:Q289)</f>
         <v>80</v>
       </c>
       <c r="S289" s="24">
@@ -32487,7 +32495,7 @@
         <v>0</v>
       </c>
       <c r="R290" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O290:Q290)</f>
         <v>21</v>
       </c>
       <c r="S290" s="22">
@@ -32550,7 +32558,7 @@
         <v>0</v>
       </c>
       <c r="R291" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O291:Q291)</f>
         <v>28</v>
       </c>
       <c r="S291" s="24">
@@ -32613,7 +32621,7 @@
         <v>35</v>
       </c>
       <c r="R292" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O292:Q292)</f>
         <v>35</v>
       </c>
       <c r="S292" s="22">
@@ -32676,7 +32684,7 @@
         <v>0</v>
       </c>
       <c r="R293" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O293:Q293)</f>
         <v>20</v>
       </c>
       <c r="S293" s="24">
@@ -32739,7 +32747,7 @@
         <v>0</v>
       </c>
       <c r="R294" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O294:Q294)</f>
         <v>188</v>
       </c>
       <c r="S294" s="22">
@@ -32802,7 +32810,7 @@
         <v>0</v>
       </c>
       <c r="R295" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O295:Q295)</f>
         <v>42</v>
       </c>
       <c r="S295" s="24">
@@ -32865,7 +32873,7 @@
         <v>0</v>
       </c>
       <c r="R296" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O296:Q296)</f>
         <v>31</v>
       </c>
       <c r="S296" s="22">
@@ -32929,7 +32937,7 @@
         <v>0</v>
       </c>
       <c r="R297" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O297:Q297)</f>
         <v>20</v>
       </c>
       <c r="S297" s="24">
@@ -32990,7 +32998,7 @@
         <v>0</v>
       </c>
       <c r="R298" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O298:Q298)</f>
         <v>70</v>
       </c>
       <c r="S298" s="22">
@@ -33053,7 +33061,7 @@
         <v>52</v>
       </c>
       <c r="R299" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O299:Q299)</f>
         <v>85</v>
       </c>
       <c r="S299" s="24">
@@ -33116,7 +33124,7 @@
         <v>54</v>
       </c>
       <c r="R300" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O300:Q300)</f>
         <v>54</v>
       </c>
       <c r="S300" s="22">
@@ -33179,7 +33187,7 @@
         <v>130</v>
       </c>
       <c r="R301" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O301:Q301)</f>
         <v>153</v>
       </c>
       <c r="S301" s="24">
@@ -33242,7 +33250,7 @@
         <v>0</v>
       </c>
       <c r="R302" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O302:Q302)</f>
         <v>19</v>
       </c>
       <c r="S302" s="22">
@@ -33305,7 +33313,7 @@
         <v>0</v>
       </c>
       <c r="R303" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O303:Q303)</f>
         <v>20</v>
       </c>
       <c r="S303" s="24">
@@ -33362,7 +33370,7 @@
       <c r="P304" s="23"/>
       <c r="Q304" s="23"/>
       <c r="R304" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O304:Q304)</f>
         <v>25</v>
       </c>
       <c r="S304" s="22">
@@ -33425,7 +33433,7 @@
         <v>0</v>
       </c>
       <c r="R305" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O305:Q305)</f>
         <v>70</v>
       </c>
       <c r="S305" s="24">
@@ -33488,7 +33496,7 @@
         <v>0</v>
       </c>
       <c r="R306" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O306:Q306)</f>
         <v>17</v>
       </c>
       <c r="S306" s="22">
@@ -33549,7 +33557,7 @@
         <v>1</v>
       </c>
       <c r="R307" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O307:Q307)</f>
         <v>24</v>
       </c>
       <c r="S307" s="24">
@@ -33613,7 +33621,7 @@
         <v>0</v>
       </c>
       <c r="R308" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O308:Q308)</f>
         <v>17</v>
       </c>
       <c r="S308" s="22">
@@ -33676,7 +33684,7 @@
         <v>0</v>
       </c>
       <c r="R309" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O309:Q309)</f>
         <v>17</v>
       </c>
       <c r="S309" s="24">
@@ -33739,7 +33747,7 @@
         <v>1</v>
       </c>
       <c r="R310" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O310:Q310)</f>
         <v>45</v>
       </c>
       <c r="S310" s="22">
@@ -33802,7 +33810,7 @@
         <v>0</v>
       </c>
       <c r="R311" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O311:Q311)</f>
         <v>26</v>
       </c>
       <c r="S311" s="24">
@@ -33866,7 +33874,7 @@
         <v>0</v>
       </c>
       <c r="R312" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O312:Q312)</f>
         <v>17</v>
       </c>
       <c r="S312" s="22">
@@ -33929,7 +33937,7 @@
         <v>0</v>
       </c>
       <c r="R313" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O313:Q313)</f>
         <v>30</v>
       </c>
       <c r="S313" s="24">
@@ -33993,7 +34001,7 @@
         <v>0</v>
       </c>
       <c r="R314" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O314:Q314)</f>
         <v>20</v>
       </c>
       <c r="S314" s="22">
@@ -34056,7 +34064,7 @@
         <v>33</v>
       </c>
       <c r="R315" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O315:Q315)</f>
         <v>33</v>
       </c>
       <c r="S315" s="24">
@@ -34119,7 +34127,7 @@
         <v>0</v>
       </c>
       <c r="R316" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O316:Q316)</f>
         <v>17</v>
       </c>
       <c r="S316" s="22">
@@ -34182,7 +34190,7 @@
         <v>0</v>
       </c>
       <c r="R317" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O317:Q317)</f>
         <v>15</v>
       </c>
       <c r="S317" s="24">
@@ -34245,7 +34253,7 @@
         <v>19</v>
       </c>
       <c r="R318" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O318:Q318)</f>
         <v>19</v>
       </c>
       <c r="S318" s="22">
@@ -34309,7 +34317,7 @@
         <v>0</v>
       </c>
       <c r="R319" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O319:Q319)</f>
         <v>16</v>
       </c>
       <c r="S319" s="24">
@@ -34373,7 +34381,7 @@
         <v>0</v>
       </c>
       <c r="R320" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O320:Q320)</f>
         <v>49</v>
       </c>
       <c r="S320" s="22">
@@ -34437,7 +34445,7 @@
         <v>0</v>
       </c>
       <c r="R321" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O321:Q321)</f>
         <v>126</v>
       </c>
       <c r="S321" s="24">
@@ -34500,7 +34508,7 @@
         <v>40</v>
       </c>
       <c r="R322" s="23">
-        <f t="shared" ref="R322:R385" si="5">SUM(O322:Q322)</f>
+        <f>SUM(O322:Q322)</f>
         <v>40</v>
       </c>
       <c r="S322" s="22">
@@ -34563,7 +34571,7 @@
         <v>40</v>
       </c>
       <c r="R323" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O323:Q323)</f>
         <v>40</v>
       </c>
       <c r="S323" s="24">
@@ -34626,7 +34634,7 @@
         <v>60</v>
       </c>
       <c r="R324" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O324:Q324)</f>
         <v>60</v>
       </c>
       <c r="S324" s="22">
@@ -34689,7 +34697,7 @@
         <v>30</v>
       </c>
       <c r="R325" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O325:Q325)</f>
         <v>30</v>
       </c>
       <c r="S325" s="24">
@@ -34752,7 +34760,7 @@
         <v>0</v>
       </c>
       <c r="R326" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O326:Q326)</f>
         <v>21</v>
       </c>
       <c r="S326" s="22">
@@ -34815,7 +34823,7 @@
         <v>0</v>
       </c>
       <c r="R327" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O327:Q327)</f>
         <v>20</v>
       </c>
       <c r="S327" s="24">
@@ -34878,7 +34886,7 @@
         <v>39</v>
       </c>
       <c r="R328" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O328:Q328)</f>
         <v>40</v>
       </c>
       <c r="S328" s="22">
@@ -34941,7 +34949,7 @@
         <v>0</v>
       </c>
       <c r="R329" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O329:Q329)</f>
         <v>80</v>
       </c>
       <c r="S329" s="24">
@@ -35004,7 +35012,7 @@
         <v>0</v>
       </c>
       <c r="R330" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O330:Q330)</f>
         <v>26</v>
       </c>
       <c r="S330" s="22">
@@ -35067,7 +35075,7 @@
         <v>0</v>
       </c>
       <c r="R331" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O331:Q331)</f>
         <v>15</v>
       </c>
       <c r="S331" s="24">
@@ -35130,7 +35138,7 @@
         <v>0</v>
       </c>
       <c r="R332" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O332:Q332)</f>
         <v>23</v>
       </c>
       <c r="S332" s="22">
@@ -35193,7 +35201,7 @@
         <v>0</v>
       </c>
       <c r="R333" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O333:Q333)</f>
         <v>207</v>
       </c>
       <c r="S333" s="24">
@@ -35256,7 +35264,7 @@
         <v>0</v>
       </c>
       <c r="R334" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O334:Q334)</f>
         <v>13</v>
       </c>
       <c r="S334" s="22">
@@ -35319,7 +35327,7 @@
         <v>0</v>
       </c>
       <c r="R335" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O335:Q335)</f>
         <v>184</v>
       </c>
       <c r="S335" s="24">
@@ -35382,7 +35390,7 @@
         <v>0</v>
       </c>
       <c r="R336" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O336:Q336)</f>
         <v>46</v>
       </c>
       <c r="S336" s="22">
@@ -35445,7 +35453,7 @@
         <v>16</v>
       </c>
       <c r="R337" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O337:Q337)</f>
         <v>60</v>
       </c>
       <c r="S337" s="24">
@@ -35508,7 +35516,7 @@
         <v>45</v>
       </c>
       <c r="R338" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O338:Q338)</f>
         <v>48</v>
       </c>
       <c r="S338" s="22">
@@ -35563,7 +35571,7 @@
         <v>40</v>
       </c>
       <c r="R339" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O339:Q339)</f>
         <v>40</v>
       </c>
       <c r="S339" s="24">
@@ -35622,7 +35630,7 @@
         <v>0</v>
       </c>
       <c r="R340" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O340:Q340)</f>
         <v>150</v>
       </c>
       <c r="S340" s="22">
@@ -35685,7 +35693,7 @@
         <v>0</v>
       </c>
       <c r="R341" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O341:Q341)</f>
         <v>20</v>
       </c>
       <c r="S341" s="24">
@@ -35740,7 +35748,7 @@
         <v>30</v>
       </c>
       <c r="R342" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O342:Q342)</f>
         <v>30</v>
       </c>
       <c r="S342" s="22">
@@ -35804,7 +35812,7 @@
         <v>0</v>
       </c>
       <c r="R343" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O343:Q343)</f>
         <v>67</v>
       </c>
       <c r="S343" s="24">
@@ -35867,7 +35875,7 @@
         <v>0</v>
       </c>
       <c r="R344" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O344:Q344)</f>
         <v>67</v>
       </c>
       <c r="S344" s="22">
@@ -35930,7 +35938,7 @@
         <v>0</v>
       </c>
       <c r="R345" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O345:Q345)</f>
         <v>57</v>
       </c>
       <c r="S345" s="24">
@@ -35993,7 +36001,7 @@
         <v>0</v>
       </c>
       <c r="R346" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O346:Q346)</f>
         <v>20</v>
       </c>
       <c r="S346" s="22">
@@ -36056,7 +36064,7 @@
         <v>0</v>
       </c>
       <c r="R347" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O347:Q347)</f>
         <v>315</v>
       </c>
       <c r="S347" s="24">
@@ -36119,7 +36127,7 @@
         <v>0</v>
       </c>
       <c r="R348" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O348:Q348)</f>
         <v>35</v>
       </c>
       <c r="S348" s="22">
@@ -36182,7 +36190,7 @@
         <v>0</v>
       </c>
       <c r="R349" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O349:Q349)</f>
         <v>17</v>
       </c>
       <c r="S349" s="24">
@@ -36246,7 +36254,7 @@
         <v>0</v>
       </c>
       <c r="R350" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O350:Q350)</f>
         <v>27</v>
       </c>
       <c r="S350" s="22">
@@ -36309,7 +36317,7 @@
         <v>0</v>
       </c>
       <c r="R351" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O351:Q351)</f>
         <v>45</v>
       </c>
       <c r="S351" s="24">
@@ -36372,7 +36380,7 @@
         <v>0</v>
       </c>
       <c r="R352" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O352:Q352)</f>
         <v>51</v>
       </c>
       <c r="S352" s="22">
@@ -36435,7 +36443,7 @@
         <v>0</v>
       </c>
       <c r="R353" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O353:Q353)</f>
         <v>5</v>
       </c>
       <c r="S353" s="24">
@@ -36498,7 +36506,7 @@
         <v>0</v>
       </c>
       <c r="R354" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O354:Q354)</f>
         <v>16</v>
       </c>
       <c r="S354" s="22">
@@ -36561,7 +36569,7 @@
         <v>0</v>
       </c>
       <c r="R355" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O355:Q355)</f>
         <v>30</v>
       </c>
       <c r="S355" s="24">
@@ -36624,7 +36632,7 @@
         <v>0</v>
       </c>
       <c r="R356" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O356:Q356)</f>
         <v>64</v>
       </c>
       <c r="S356" s="22">
@@ -36686,7 +36694,7 @@
         <v>0</v>
       </c>
       <c r="R357" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O357:Q357)</f>
         <v>57</v>
       </c>
       <c r="S357" s="24">
@@ -36749,7 +36757,7 @@
         <v>0</v>
       </c>
       <c r="R358" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O358:Q358)</f>
         <v>39</v>
       </c>
       <c r="S358" s="22">
@@ -36812,7 +36820,7 @@
         <v>0</v>
       </c>
       <c r="R359" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O359:Q359)</f>
         <v>16</v>
       </c>
       <c r="S359" s="24">
@@ -36875,7 +36883,7 @@
         <v>0</v>
       </c>
       <c r="R360" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O360:Q360)</f>
         <v>47</v>
       </c>
       <c r="S360" s="22">
@@ -36938,7 +36946,7 @@
         <v>2</v>
       </c>
       <c r="R361" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O361:Q361)</f>
         <v>13</v>
       </c>
       <c r="S361" s="24">
@@ -37001,7 +37009,7 @@
         <v>0</v>
       </c>
       <c r="R362" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O362:Q362)</f>
         <v>26</v>
       </c>
       <c r="S362" s="22">
@@ -37064,7 +37072,7 @@
         <v>43</v>
       </c>
       <c r="R363" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O363:Q363)</f>
         <v>43</v>
       </c>
       <c r="S363" s="24">
@@ -37127,7 +37135,7 @@
         <v>0</v>
       </c>
       <c r="R364" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O364:Q364)</f>
         <v>11</v>
       </c>
       <c r="S364" s="22">
@@ -37190,7 +37198,7 @@
         <v>0</v>
       </c>
       <c r="R365" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O365:Q365)</f>
         <v>11</v>
       </c>
       <c r="S365" s="24">
@@ -37254,7 +37262,7 @@
         <v>57</v>
       </c>
       <c r="R366" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O366:Q366)</f>
         <v>57</v>
       </c>
       <c r="S366" s="22">
@@ -37318,7 +37326,7 @@
         <v>0</v>
       </c>
       <c r="R367" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O367:Q367)</f>
         <v>22</v>
       </c>
       <c r="S367" s="24">
@@ -37381,7 +37389,7 @@
         <v>0</v>
       </c>
       <c r="R368" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O368:Q368)</f>
         <v>176</v>
       </c>
       <c r="S368" s="22">
@@ -37442,7 +37450,7 @@
         <v>0</v>
       </c>
       <c r="R369" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O369:Q369)</f>
         <v>56</v>
       </c>
       <c r="S369" s="24">
@@ -37506,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="R370" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O370:Q370)</f>
         <v>23</v>
       </c>
       <c r="S370" s="22">
@@ -37569,7 +37577,7 @@
         <v>39</v>
       </c>
       <c r="R371" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O371:Q371)</f>
         <v>39</v>
       </c>
       <c r="S371" s="24">
@@ -37632,7 +37640,7 @@
         <v>0</v>
       </c>
       <c r="R372" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O372:Q372)</f>
         <v>47</v>
       </c>
       <c r="S372" s="22">
@@ -37694,7 +37702,7 @@
         <v>53</v>
       </c>
       <c r="R373" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O373:Q373)</f>
         <v>53</v>
       </c>
       <c r="S373" s="24">
@@ -37757,7 +37765,7 @@
         <v>0</v>
       </c>
       <c r="R374" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O374:Q374)</f>
         <v>28</v>
       </c>
       <c r="S374" s="22">
@@ -37821,7 +37829,7 @@
         <v>0</v>
       </c>
       <c r="R375" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O375:Q375)</f>
         <v>18</v>
       </c>
       <c r="S375" s="24">
@@ -37885,7 +37893,7 @@
         <v>53</v>
       </c>
       <c r="R376" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O376:Q376)</f>
         <v>53</v>
       </c>
       <c r="S376" s="22">
@@ -37949,7 +37957,7 @@
         <v>0</v>
       </c>
       <c r="R377" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O377:Q377)</f>
         <v>10</v>
       </c>
       <c r="S377" s="24">
@@ -38013,7 +38021,7 @@
         <v>0</v>
       </c>
       <c r="R378" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O378:Q378)</f>
         <v>34</v>
       </c>
       <c r="S378" s="22">
@@ -38068,7 +38076,7 @@
         <v>0</v>
       </c>
       <c r="R379" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O379:Q379)</f>
         <v>0</v>
       </c>
       <c r="S379" s="24"/>
@@ -38127,7 +38135,7 @@
         <v>0</v>
       </c>
       <c r="R380" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O380:Q380)</f>
         <v>15</v>
       </c>
       <c r="S380" s="22">
@@ -38182,7 +38190,7 @@
       <c r="P381" s="25"/>
       <c r="Q381" s="25"/>
       <c r="R381" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O381:Q381)</f>
         <v>21</v>
       </c>
       <c r="S381" s="24">
@@ -38244,7 +38252,7 @@
         <v>17</v>
       </c>
       <c r="R382" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O382:Q382)</f>
         <v>17</v>
       </c>
       <c r="S382" s="22">
@@ -38308,7 +38316,7 @@
         <v>0</v>
       </c>
       <c r="R383" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O383:Q383)</f>
         <v>13</v>
       </c>
       <c r="S383" s="24">
@@ -38371,7 +38379,7 @@
         <v>0</v>
       </c>
       <c r="R384" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O384:Q384)</f>
         <v>114</v>
       </c>
       <c r="S384" s="22">
@@ -38432,7 +38440,7 @@
         <v>0</v>
       </c>
       <c r="R385" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O385:Q385)</f>
         <v>5</v>
       </c>
       <c r="S385" s="24">
@@ -38495,7 +38503,7 @@
         <v>0</v>
       </c>
       <c r="R386" s="23">
-        <f t="shared" ref="R386:R449" si="6">SUM(O386:Q386)</f>
+        <f>SUM(O386:Q386)</f>
         <v>49</v>
       </c>
       <c r="S386" s="22">
@@ -38558,7 +38566,7 @@
         <v>0</v>
       </c>
       <c r="R387" s="25">
-        <f t="shared" si="6"/>
+        <f>SUM(O387:Q387)</f>
         <v>22</v>
       </c>
       <c r="S387" s="24">
@@ -38621,7 +38629,7 @@
         <v>26</v>
       </c>
       <c r="R388" s="23">
-        <f t="shared" si="6"/>
+        <f>SUM(O388:Q388)</f>
         <v>91</v>
       </c>
       <c r="S388" s="22">
@@ -38685,7 +38693,7 @@
         <v>5</v>
       </c>
       <c r="R389" s="25">
-        <f t="shared" si="6"/>
+        <f>SUM(O389:Q389)</f>
         <v>5</v>
       </c>
       <c r="S389" s="24">
@@ -38748,7 +38756,7 @@
         <v>0</v>
       </c>
       <c r="R390" s="23">
-        <f t="shared" si="6"/>
+        <f>SUM(O390:Q390)</f>
         <v>181</v>
       </c>
       <c r="S390" s="22">
@@ -38812,7 +38820,7 @@
         <v>7</v>
       </c>
       <c r="R391" s="25">
-        <f t="shared" si="6"/>
+        <f>SUM(O391:Q391)</f>
         <v>7</v>
       </c>
       <c r="S391" s="24">
@@ -38875,7 +38883,7 @@
         <v>0</v>
       </c>
       <c r="R392" s="23">
-        <f t="shared" si="6"/>
+        <f>SUM(O392:Q392)</f>
         <v>9</v>
       </c>
       <c r="S392" s="22">
@@ -39001,7 +39009,7 @@
         <v>31</v>
       </c>
       <c r="R394" s="23">
-        <f t="shared" ref="R394:R457" si="7">SUM(O394:Q394)</f>
+        <f>SUM(O394:Q394)</f>
         <v>31</v>
       </c>
       <c r="S394" s="22">
@@ -39064,7 +39072,7 @@
         <v>0</v>
       </c>
       <c r="R395" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O395:Q395)</f>
         <v>19</v>
       </c>
       <c r="S395" s="24">
@@ -39127,7 +39135,7 @@
         <v>0</v>
       </c>
       <c r="R396" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O396:Q396)</f>
         <v>45</v>
       </c>
       <c r="S396" s="22">
@@ -39190,7 +39198,7 @@
         <v>0</v>
       </c>
       <c r="R397" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O397:Q397)</f>
         <v>0</v>
       </c>
       <c r="S397" s="24">
@@ -39253,7 +39261,7 @@
         <v>17</v>
       </c>
       <c r="R398" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O398:Q398)</f>
         <v>85</v>
       </c>
       <c r="S398" s="22">
@@ -39316,7 +39324,7 @@
         <v>0</v>
       </c>
       <c r="R399" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O399:Q399)</f>
         <v>7</v>
       </c>
       <c r="S399" s="24">
@@ -39373,7 +39381,7 @@
       <c r="P400" s="23"/>
       <c r="Q400" s="23"/>
       <c r="R400" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O400:Q400)</f>
         <v>30</v>
       </c>
       <c r="S400" s="22">
@@ -39434,7 +39442,7 @@
         <v>0</v>
       </c>
       <c r="R401" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O401:Q401)</f>
         <v>62</v>
       </c>
       <c r="S401" s="24">
@@ -39497,7 +39505,7 @@
         <v>68</v>
       </c>
       <c r="R402" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O402:Q402)</f>
         <v>68</v>
       </c>
       <c r="S402" s="22">
@@ -39556,7 +39564,7 @@
         <v>0</v>
       </c>
       <c r="R403" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O403:Q403)</f>
         <v>2</v>
       </c>
       <c r="S403" s="24">
@@ -39619,7 +39627,7 @@
         <v>0</v>
       </c>
       <c r="R404" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O404:Q404)</f>
         <v>36</v>
       </c>
       <c r="S404" s="22">
@@ -39682,7 +39690,7 @@
         <v>0</v>
       </c>
       <c r="R405" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O405:Q405)</f>
         <v>14</v>
       </c>
       <c r="S405" s="24">
@@ -39743,7 +39751,7 @@
         <v>44</v>
       </c>
       <c r="R406" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O406:Q406)</f>
         <v>44</v>
       </c>
       <c r="S406" s="22">
@@ -39806,7 +39814,7 @@
         <v>0</v>
       </c>
       <c r="R407" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O407:Q407)</f>
         <v>26</v>
       </c>
       <c r="S407" s="24">
@@ -39869,7 +39877,7 @@
         <v>0</v>
       </c>
       <c r="R408" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O408:Q408)</f>
         <v>23</v>
       </c>
       <c r="S408" s="22">
@@ -39924,7 +39932,7 @@
         <v>20</v>
       </c>
       <c r="R409" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O409:Q409)</f>
         <v>20</v>
       </c>
       <c r="S409" s="24">
@@ -39979,7 +39987,7 @@
         <v>0</v>
       </c>
       <c r="R410" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O410:Q410)</f>
         <v>0</v>
       </c>
       <c r="S410" s="22"/>
@@ -40038,7 +40046,7 @@
         <v>0</v>
       </c>
       <c r="R411" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O411:Q411)</f>
         <v>16</v>
       </c>
       <c r="S411" s="24">
@@ -40101,7 +40109,7 @@
         <v>44</v>
       </c>
       <c r="R412" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O412:Q412)</f>
         <v>44</v>
       </c>
       <c r="S412" s="22">
@@ -40164,7 +40172,7 @@
         <v>0</v>
       </c>
       <c r="R413" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O413:Q413)</f>
         <v>105</v>
       </c>
       <c r="S413" s="24">
@@ -40227,7 +40235,7 @@
         <v>0</v>
       </c>
       <c r="R414" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O414:Q414)</f>
         <v>50</v>
       </c>
       <c r="S414" s="22">
@@ -40290,7 +40298,7 @@
         <v>0</v>
       </c>
       <c r="R415" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O415:Q415)</f>
         <v>25</v>
       </c>
       <c r="S415" s="24">
@@ -40353,7 +40361,7 @@
         <v>0</v>
       </c>
       <c r="R416" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O416:Q416)</f>
         <v>9</v>
       </c>
       <c r="S416" s="22">
@@ -40416,7 +40424,7 @@
         <v>24</v>
       </c>
       <c r="R417" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O417:Q417)</f>
         <v>25</v>
       </c>
       <c r="S417" s="24">
@@ -40479,7 +40487,7 @@
         <v>0</v>
       </c>
       <c r="R418" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O418:Q418)</f>
         <v>13</v>
       </c>
       <c r="S418" s="22">
@@ -40543,7 +40551,7 @@
         <v>0</v>
       </c>
       <c r="R419" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O419:Q419)</f>
         <v>49</v>
       </c>
       <c r="S419" s="24">
@@ -40606,7 +40614,7 @@
         <v>128</v>
       </c>
       <c r="R420" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O420:Q420)</f>
         <v>128</v>
       </c>
       <c r="S420" s="22">
@@ -40669,7 +40677,7 @@
         <v>0</v>
       </c>
       <c r="R421" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O421:Q421)</f>
         <v>21</v>
       </c>
       <c r="S421" s="24">
@@ -40732,7 +40740,7 @@
         <v>0</v>
       </c>
       <c r="R422" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O422:Q422)</f>
         <v>8</v>
       </c>
       <c r="S422" s="22">
@@ -40795,7 +40803,7 @@
         <v>0</v>
       </c>
       <c r="R423" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O423:Q423)</f>
         <v>93</v>
       </c>
       <c r="S423" s="24">
@@ -40858,7 +40866,7 @@
         <v>0</v>
       </c>
       <c r="R424" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O424:Q424)</f>
         <v>6</v>
       </c>
       <c r="S424" s="22">
@@ -40919,7 +40927,7 @@
         <v>0</v>
       </c>
       <c r="R425" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O425:Q425)</f>
         <v>80</v>
       </c>
       <c r="S425" s="24">
@@ -40983,7 +40991,7 @@
         <v>0</v>
       </c>
       <c r="R426" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O426:Q426)</f>
         <v>8</v>
       </c>
       <c r="S426" s="22">
@@ -41046,7 +41054,7 @@
         <v>0</v>
       </c>
       <c r="R427" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O427:Q427)</f>
         <v>10</v>
       </c>
       <c r="S427" s="24">
@@ -41107,7 +41115,7 @@
         <v>80</v>
       </c>
       <c r="R428" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O428:Q428)</f>
         <v>80</v>
       </c>
       <c r="S428" s="22">
@@ -41168,7 +41176,7 @@
         <v>80</v>
       </c>
       <c r="R429" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O429:Q429)</f>
         <v>80</v>
       </c>
       <c r="S429" s="24">
@@ -41229,7 +41237,7 @@
         <v>80</v>
       </c>
       <c r="R430" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O430:Q430)</f>
         <v>80</v>
       </c>
       <c r="S430" s="22">
@@ -41290,7 +41298,7 @@
         <v>80</v>
       </c>
       <c r="R431" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O431:Q431)</f>
         <v>80</v>
       </c>
       <c r="S431" s="24">
@@ -41351,7 +41359,7 @@
         <v>80</v>
       </c>
       <c r="R432" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O432:Q432)</f>
         <v>80</v>
       </c>
       <c r="S432" s="22">
@@ -41415,7 +41423,7 @@
         <v>0</v>
       </c>
       <c r="R433" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O433:Q433)</f>
         <v>33</v>
       </c>
       <c r="S433" s="24">
@@ -41470,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="R434" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O434:Q434)</f>
         <v>0</v>
       </c>
       <c r="S434" s="22"/>
@@ -41529,7 +41537,7 @@
         <v>62</v>
       </c>
       <c r="R435" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O435:Q435)</f>
         <v>62</v>
       </c>
       <c r="S435" s="24">
@@ -41592,7 +41600,7 @@
         <v>0</v>
       </c>
       <c r="R436" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O436:Q436)</f>
         <v>42</v>
       </c>
       <c r="S436" s="22">
@@ -41655,7 +41663,7 @@
         <v>0</v>
       </c>
       <c r="R437" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O437:Q437)</f>
         <v>6</v>
       </c>
       <c r="S437" s="24">
@@ -41718,7 +41726,7 @@
         <v>0</v>
       </c>
       <c r="R438" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O438:Q438)</f>
         <v>49</v>
       </c>
       <c r="S438" s="22">
@@ -41781,7 +41789,7 @@
         <v>0</v>
       </c>
       <c r="R439" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O439:Q439)</f>
         <v>20</v>
       </c>
       <c r="S439" s="24">
@@ -41844,7 +41852,7 @@
         <v>28</v>
       </c>
       <c r="R440" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O440:Q440)</f>
         <v>28</v>
       </c>
       <c r="S440" s="22">
@@ -41907,7 +41915,7 @@
         <v>0</v>
       </c>
       <c r="R441" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O441:Q441)</f>
         <v>17</v>
       </c>
       <c r="S441" s="24">
@@ -41971,7 +41979,7 @@
         <v>0</v>
       </c>
       <c r="R442" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O442:Q442)</f>
         <v>17</v>
       </c>
       <c r="S442" s="22">
@@ -42035,7 +42043,7 @@
         <v>0</v>
       </c>
       <c r="R443" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O443:Q443)</f>
         <v>24</v>
       </c>
       <c r="S443" s="24">
@@ -42098,7 +42106,7 @@
         <v>0</v>
       </c>
       <c r="R444" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O444:Q444)</f>
         <v>16</v>
       </c>
       <c r="S444" s="22">
@@ -42161,7 +42169,7 @@
         <v>7</v>
       </c>
       <c r="R445" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O445:Q445)</f>
         <v>155</v>
       </c>
       <c r="S445" s="24">
@@ -42225,7 +42233,7 @@
         <v>0</v>
       </c>
       <c r="R446" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O446:Q446)</f>
         <v>8</v>
       </c>
       <c r="S446" s="22">
@@ -42288,7 +42296,7 @@
         <v>0</v>
       </c>
       <c r="R447" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O447:Q447)</f>
         <v>10</v>
       </c>
       <c r="S447" s="24">
@@ -42351,7 +42359,7 @@
         <v>0</v>
       </c>
       <c r="R448" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O448:Q448)</f>
         <v>15</v>
       </c>
       <c r="S448" s="22">
@@ -42414,7 +42422,7 @@
         <v>0</v>
       </c>
       <c r="R449" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O449:Q449)</f>
         <v>51</v>
       </c>
       <c r="S449" s="24">
@@ -42477,7 +42485,7 @@
         <v>0</v>
       </c>
       <c r="R450" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O450:Q450)</f>
         <v>52</v>
       </c>
       <c r="S450" s="22">
@@ -42541,7 +42549,7 @@
         <v>0</v>
       </c>
       <c r="R451" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O451:Q451)</f>
         <v>13</v>
       </c>
       <c r="S451" s="24">
@@ -42604,7 +42612,7 @@
         <v>0</v>
       </c>
       <c r="R452" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O452:Q452)</f>
         <v>90</v>
       </c>
       <c r="S452" s="22">
@@ -42667,7 +42675,7 @@
         <v>0</v>
       </c>
       <c r="R453" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O453:Q453)</f>
         <v>11</v>
       </c>
       <c r="S453" s="24">
@@ -42730,7 +42738,7 @@
         <v>0</v>
       </c>
       <c r="R454" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O454:Q454)</f>
         <v>50</v>
       </c>
       <c r="S454" s="22">
@@ -42794,7 +42802,7 @@
         <v>0</v>
       </c>
       <c r="R455" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O455:Q455)</f>
         <v>8</v>
       </c>
       <c r="S455" s="24">
@@ -42847,7 +42855,7 @@
         <v>0</v>
       </c>
       <c r="R456" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O456:Q456)</f>
         <v>0</v>
       </c>
       <c r="S456" s="22"/>
@@ -42906,7 +42914,7 @@
         <v>0</v>
       </c>
       <c r="R457" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O457:Q457)</f>
         <v>23</v>
       </c>
       <c r="S457" s="24">
@@ -42969,7 +42977,7 @@
         <v>0</v>
       </c>
       <c r="R458" s="23">
-        <f t="shared" ref="R458:R521" si="8">SUM(O458:Q458)</f>
+        <f>SUM(O458:Q458)</f>
         <v>23</v>
       </c>
       <c r="S458" s="22">
@@ -43032,7 +43040,7 @@
         <v>0</v>
       </c>
       <c r="R459" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O459:Q459)</f>
         <v>89</v>
       </c>
       <c r="S459" s="24">
@@ -43095,7 +43103,7 @@
         <v>0</v>
       </c>
       <c r="R460" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O460:Q460)</f>
         <v>22</v>
       </c>
       <c r="S460" s="22">
@@ -43159,7 +43167,7 @@
         <v>0</v>
       </c>
       <c r="R461" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O461:Q461)</f>
         <v>11</v>
       </c>
       <c r="S461" s="24">
@@ -43222,7 +43230,7 @@
         <v>0</v>
       </c>
       <c r="R462" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O462:Q462)</f>
         <v>21</v>
       </c>
       <c r="S462" s="22">
@@ -43285,7 +43293,7 @@
         <v>0</v>
       </c>
       <c r="R463" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O463:Q463)</f>
         <v>51</v>
       </c>
       <c r="S463" s="24">
@@ -43349,7 +43357,7 @@
         <v>0</v>
       </c>
       <c r="R464" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O464:Q464)</f>
         <v>7</v>
       </c>
       <c r="S464" s="22">
@@ -43412,7 +43420,7 @@
         <v>0</v>
       </c>
       <c r="R465" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O465:Q465)</f>
         <v>22</v>
       </c>
       <c r="S465" s="24">
@@ -43475,7 +43483,7 @@
         <v>156</v>
       </c>
       <c r="R466" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O466:Q466)</f>
         <v>213</v>
       </c>
       <c r="S466" s="22">
@@ -43538,7 +43546,7 @@
         <v>70</v>
       </c>
       <c r="R467" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O467:Q467)</f>
         <v>92</v>
       </c>
       <c r="S467" s="24">
@@ -43601,7 +43609,7 @@
         <v>0</v>
       </c>
       <c r="R468" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O468:Q468)</f>
         <v>18</v>
       </c>
       <c r="S468" s="22">
@@ -43665,7 +43673,7 @@
         <v>0</v>
       </c>
       <c r="R469" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O469:Q469)</f>
         <v>8</v>
       </c>
       <c r="S469" s="24">
@@ -43729,7 +43737,7 @@
         <v>0</v>
       </c>
       <c r="R470" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O470:Q470)</f>
         <v>8</v>
       </c>
       <c r="S470" s="22">
@@ -43793,7 +43801,7 @@
         <v>0</v>
       </c>
       <c r="R471" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O471:Q471)</f>
         <v>384</v>
       </c>
       <c r="S471" s="24">
@@ -43856,7 +43864,7 @@
         <v>0</v>
       </c>
       <c r="R472" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O472:Q472)</f>
         <v>24</v>
       </c>
       <c r="S472" s="22">
@@ -43919,7 +43927,7 @@
         <v>0</v>
       </c>
       <c r="R473" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O473:Q473)</f>
         <v>35</v>
       </c>
       <c r="S473" s="24">
@@ -43982,7 +43990,7 @@
         <v>0</v>
       </c>
       <c r="R474" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O474:Q474)</f>
         <v>53</v>
       </c>
       <c r="S474" s="22">
@@ -44045,7 +44053,7 @@
         <v>0</v>
       </c>
       <c r="R475" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O475:Q475)</f>
         <v>12</v>
       </c>
       <c r="S475" s="24">
@@ -44108,7 +44116,7 @@
         <v>0</v>
       </c>
       <c r="R476" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O476:Q476)</f>
         <v>60</v>
       </c>
       <c r="S476" s="22">
@@ -44171,7 +44179,7 @@
         <v>0</v>
       </c>
       <c r="R477" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O477:Q477)</f>
         <v>14</v>
       </c>
       <c r="S477" s="24">
@@ -44234,7 +44242,7 @@
         <v>0</v>
       </c>
       <c r="R478" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O478:Q478)</f>
         <v>20</v>
       </c>
       <c r="S478" s="22">
@@ -44297,7 +44305,7 @@
         <v>56</v>
       </c>
       <c r="R479" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O479:Q479)</f>
         <v>56</v>
       </c>
       <c r="S479" s="24">
@@ -44360,7 +44368,7 @@
         <v>0</v>
       </c>
       <c r="R480" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O480:Q480)</f>
         <v>38</v>
       </c>
       <c r="S480" s="22">
@@ -44423,7 +44431,7 @@
         <v>0</v>
       </c>
       <c r="R481" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O481:Q481)</f>
         <v>13</v>
       </c>
       <c r="S481" s="24">
@@ -44486,7 +44494,7 @@
         <v>0</v>
       </c>
       <c r="R482" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O482:Q482)</f>
         <v>24</v>
       </c>
       <c r="S482" s="22">
@@ -44549,7 +44557,7 @@
         <v>0</v>
       </c>
       <c r="R483" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O483:Q483)</f>
         <v>19</v>
       </c>
       <c r="S483" s="24">
@@ -44612,7 +44620,7 @@
         <v>0</v>
       </c>
       <c r="R484" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O484:Q484)</f>
         <v>10</v>
       </c>
       <c r="S484" s="22">
@@ -44676,7 +44684,7 @@
         <v>0</v>
       </c>
       <c r="R485" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O485:Q485)</f>
         <v>5</v>
       </c>
       <c r="S485" s="24">
@@ -44739,7 +44747,7 @@
         <v>0</v>
       </c>
       <c r="R486" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O486:Q486)</f>
         <v>21</v>
       </c>
       <c r="S486" s="22">
@@ -44802,7 +44810,7 @@
         <v>0</v>
       </c>
       <c r="R487" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O487:Q487)</f>
         <v>19</v>
       </c>
       <c r="S487" s="24">
@@ -44866,7 +44874,7 @@
         <v>0</v>
       </c>
       <c r="R488" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O488:Q488)</f>
         <v>7</v>
       </c>
       <c r="S488" s="22">
@@ -44929,7 +44937,7 @@
         <v>0</v>
       </c>
       <c r="R489" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O489:Q489)</f>
         <v>19</v>
       </c>
       <c r="S489" s="64">
@@ -44993,7 +45001,7 @@
         <v>61</v>
       </c>
       <c r="R490" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O490:Q490)</f>
         <v>61</v>
       </c>
       <c r="S490" s="70">
@@ -45056,7 +45064,7 @@
         <v>0</v>
       </c>
       <c r="R491" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O491:Q491)</f>
         <v>32</v>
       </c>
       <c r="S491" s="64">
@@ -45119,7 +45127,7 @@
         <v>0</v>
       </c>
       <c r="R492" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O492:Q492)</f>
         <v>43</v>
       </c>
       <c r="S492" s="70">
@@ -45182,7 +45190,7 @@
         <v>0</v>
       </c>
       <c r="R493" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O493:Q493)</f>
         <v>8</v>
       </c>
       <c r="S493" s="64">
@@ -45243,7 +45251,7 @@
         <v>0</v>
       </c>
       <c r="R494" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O494:Q494)</f>
         <v>80</v>
       </c>
       <c r="S494" s="70">
@@ -45298,7 +45306,7 @@
         <v>0</v>
       </c>
       <c r="R495" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O495:Q495)</f>
         <v>0</v>
       </c>
       <c r="S495" s="24"/>
@@ -45355,7 +45363,7 @@
         <v>0</v>
       </c>
       <c r="R496" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O496:Q496)</f>
         <v>170</v>
       </c>
       <c r="S496" s="70">
@@ -45418,7 +45426,7 @@
         <v>0</v>
       </c>
       <c r="R497" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O497:Q497)</f>
         <v>31</v>
       </c>
       <c r="S497" s="64">
@@ -45481,7 +45489,7 @@
         <v>0</v>
       </c>
       <c r="R498" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O498:Q498)</f>
         <v>11</v>
       </c>
       <c r="S498" s="70">
@@ -45544,7 +45552,7 @@
         <v>45</v>
       </c>
       <c r="R499" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O499:Q499)</f>
         <v>45</v>
       </c>
       <c r="S499" s="64">
@@ -45605,7 +45613,7 @@
         <v>0</v>
       </c>
       <c r="R500" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O500:Q500)</f>
         <v>40</v>
       </c>
       <c r="S500" s="70">
@@ -45669,7 +45677,7 @@
         <v>0</v>
       </c>
       <c r="R501" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O501:Q501)</f>
         <v>0</v>
       </c>
       <c r="S501" s="64">
@@ -45732,7 +45740,7 @@
         <v>0</v>
       </c>
       <c r="R502" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O502:Q502)</f>
         <v>34</v>
       </c>
       <c r="S502" s="70">
@@ -45795,7 +45803,7 @@
         <v>0</v>
       </c>
       <c r="R503" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O503:Q503)</f>
         <v>21</v>
       </c>
       <c r="S503" s="64">
@@ -45858,7 +45866,7 @@
         <v>0</v>
       </c>
       <c r="R504" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O504:Q504)</f>
         <v>16</v>
       </c>
       <c r="S504" s="70">
@@ -45919,7 +45927,7 @@
         <v>0</v>
       </c>
       <c r="R505" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O505:Q505)</f>
         <v>20</v>
       </c>
       <c r="S505" s="24">
@@ -45983,7 +45991,7 @@
         <v>0</v>
       </c>
       <c r="R506" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O506:Q506)</f>
         <v>8</v>
       </c>
       <c r="S506" s="22">
@@ -46046,7 +46054,7 @@
         <v>0</v>
       </c>
       <c r="R507" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O507:Q507)</f>
         <v>0</v>
       </c>
       <c r="S507" s="24">
@@ -46109,7 +46117,7 @@
         <v>0</v>
       </c>
       <c r="R508" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O508:Q508)</f>
         <v>13</v>
       </c>
       <c r="S508" s="22">
@@ -46170,7 +46178,7 @@
         <v>0</v>
       </c>
       <c r="R509" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O509:Q509)</f>
         <v>170</v>
       </c>
       <c r="S509" s="24">
@@ -46234,7 +46242,7 @@
         <v>66</v>
       </c>
       <c r="R510" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O510:Q510)</f>
         <v>66</v>
       </c>
       <c r="S510" s="22">
@@ -46295,7 +46303,7 @@
         <v>0</v>
       </c>
       <c r="R511" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O511:Q511)</f>
         <v>140</v>
       </c>
       <c r="S511" s="24">
@@ -46358,7 +46366,7 @@
         <v>0</v>
       </c>
       <c r="R512" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O512:Q512)</f>
         <v>45</v>
       </c>
       <c r="S512" s="22">
@@ -46421,7 +46429,7 @@
         <v>0</v>
       </c>
       <c r="R513" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O513:Q513)</f>
         <v>19</v>
       </c>
       <c r="S513" s="24">
@@ -46484,7 +46492,7 @@
         <v>0</v>
       </c>
       <c r="R514" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O514:Q514)</f>
         <v>15</v>
       </c>
       <c r="S514" s="22">
@@ -46547,7 +46555,7 @@
         <v>41</v>
       </c>
       <c r="R515" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O515:Q515)</f>
         <v>41</v>
       </c>
       <c r="S515" s="24">
@@ -46610,7 +46618,7 @@
         <v>0</v>
       </c>
       <c r="R516" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O516:Q516)</f>
         <v>96</v>
       </c>
       <c r="S516" s="22">
@@ -46674,7 +46682,7 @@
         <v>0</v>
       </c>
       <c r="R517" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O517:Q517)</f>
         <v>6</v>
       </c>
       <c r="S517" s="24">
@@ -46737,7 +46745,7 @@
         <v>0</v>
       </c>
       <c r="R518" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O518:Q518)</f>
         <v>47</v>
       </c>
       <c r="S518" s="22">
@@ -46800,7 +46808,7 @@
         <v>0</v>
       </c>
       <c r="R519" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O519:Q519)</f>
         <v>37</v>
       </c>
       <c r="S519" s="24">
@@ -46863,7 +46871,7 @@
         <v>0</v>
       </c>
       <c r="R520" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O520:Q520)</f>
         <v>20</v>
       </c>
       <c r="S520" s="22">
@@ -46926,7 +46934,7 @@
         <v>0</v>
       </c>
       <c r="R521" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O521:Q521)</f>
         <v>19</v>
       </c>
       <c r="S521" s="24">
@@ -46989,7 +46997,7 @@
         <v>0</v>
       </c>
       <c r="R522" s="23">
-        <f t="shared" ref="R522:R585" si="9">SUM(O522:Q522)</f>
+        <f>SUM(O522:Q522)</f>
         <v>0</v>
       </c>
       <c r="S522" s="22">
@@ -47052,7 +47060,7 @@
         <v>0</v>
       </c>
       <c r="R523" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O523:Q523)</f>
         <v>0</v>
       </c>
       <c r="S523" s="24">
@@ -47116,7 +47124,7 @@
         <v>0</v>
       </c>
       <c r="R524" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O524:Q524)</f>
         <v>6</v>
       </c>
       <c r="S524" s="22"/>
@@ -47175,7 +47183,7 @@
         <v>0</v>
       </c>
       <c r="R525" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O525:Q525)</f>
         <v>46</v>
       </c>
       <c r="S525" s="24">
@@ -47238,7 +47246,7 @@
         <v>0</v>
       </c>
       <c r="R526" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O526:Q526)</f>
         <v>20</v>
       </c>
       <c r="S526" s="22">
@@ -47293,7 +47301,7 @@
         <v>0</v>
       </c>
       <c r="R527" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O527:Q527)</f>
         <v>0</v>
       </c>
       <c r="S527" s="24"/>
@@ -47354,7 +47362,7 @@
         <v>0</v>
       </c>
       <c r="R528" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O528:Q528)</f>
         <v>20</v>
       </c>
       <c r="S528" s="22">
@@ -47417,7 +47425,7 @@
         <v>1</v>
       </c>
       <c r="R529" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O529:Q529)</f>
         <v>28</v>
       </c>
       <c r="S529" s="24">
@@ -47478,7 +47486,7 @@
         <v>23</v>
       </c>
       <c r="R530" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O530:Q530)</f>
         <v>138</v>
       </c>
       <c r="S530" s="22">
@@ -47541,7 +47549,7 @@
         <v>0</v>
       </c>
       <c r="R531" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O531:Q531)</f>
         <v>19</v>
       </c>
       <c r="S531" s="24">
@@ -47604,7 +47612,7 @@
         <v>0</v>
       </c>
       <c r="R532" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O532:Q532)</f>
         <v>118</v>
       </c>
       <c r="S532" s="22">
@@ -47668,7 +47676,7 @@
         <v>0</v>
       </c>
       <c r="R533" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O533:Q533)</f>
         <v>4</v>
       </c>
       <c r="S533" s="24">
@@ -47731,7 +47739,7 @@
         <v>49</v>
       </c>
       <c r="R534" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O534:Q534)</f>
         <v>49</v>
       </c>
       <c r="S534" s="22">
@@ -47795,7 +47803,7 @@
         <v>94</v>
       </c>
       <c r="R535" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O535:Q535)</f>
         <v>94</v>
       </c>
       <c r="S535" s="24">
@@ -47850,7 +47858,7 @@
         <v>0</v>
       </c>
       <c r="R536" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O536:Q536)</f>
         <v>0</v>
       </c>
       <c r="S536" s="22"/>
@@ -47909,7 +47917,7 @@
         <v>0</v>
       </c>
       <c r="R537" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O537:Q537)</f>
         <v>21</v>
       </c>
       <c r="S537" s="24">
@@ -47966,7 +47974,7 @@
         <v>0</v>
       </c>
       <c r="R538" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O538:Q538)</f>
         <v>49</v>
       </c>
       <c r="S538" s="22"/>
@@ -48025,7 +48033,7 @@
         <v>0</v>
       </c>
       <c r="R539" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O539:Q539)</f>
         <v>26</v>
       </c>
       <c r="S539" s="24">
@@ -48088,7 +48096,7 @@
         <v>0</v>
       </c>
       <c r="R540" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O540:Q540)</f>
         <v>8</v>
       </c>
       <c r="S540" s="22">
@@ -48151,7 +48159,7 @@
         <v>0</v>
       </c>
       <c r="R541" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O541:Q541)</f>
         <v>14</v>
       </c>
       <c r="S541" s="24">
@@ -48214,7 +48222,7 @@
         <v>30</v>
       </c>
       <c r="R542" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O542:Q542)</f>
         <v>30</v>
       </c>
       <c r="S542" s="22">
@@ -48277,7 +48285,7 @@
         <v>0</v>
       </c>
       <c r="R543" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O543:Q543)</f>
         <v>11</v>
       </c>
       <c r="S543" s="24">
@@ -48341,7 +48349,7 @@
         <v>0</v>
       </c>
       <c r="R544" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O544:Q544)</f>
         <v>43</v>
       </c>
       <c r="S544" s="22">
@@ -48404,7 +48412,7 @@
         <v>0</v>
       </c>
       <c r="R545" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O545:Q545)</f>
         <v>54</v>
       </c>
       <c r="S545" s="24">
@@ -48467,7 +48475,7 @@
         <v>0</v>
       </c>
       <c r="R546" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O546:Q546)</f>
         <v>3</v>
       </c>
       <c r="S546" s="22">
@@ -48530,7 +48538,7 @@
         <v>0</v>
       </c>
       <c r="R547" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O547:Q547)</f>
         <v>21</v>
       </c>
       <c r="S547" s="24">
@@ -48593,7 +48601,7 @@
         <v>44</v>
       </c>
       <c r="R548" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O548:Q548)</f>
         <v>44</v>
       </c>
       <c r="S548" s="22">
@@ -48656,7 +48664,7 @@
         <v>0</v>
       </c>
       <c r="R549" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O549:Q549)</f>
         <v>49</v>
       </c>
       <c r="S549" s="24">
@@ -48719,7 +48727,7 @@
         <v>0</v>
       </c>
       <c r="R550" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O550:Q550)</f>
         <v>16</v>
       </c>
       <c r="S550" s="22">
@@ -48782,7 +48790,7 @@
         <v>0</v>
       </c>
       <c r="R551" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O551:Q551)</f>
         <v>27</v>
       </c>
       <c r="S551" s="24">
@@ -48845,7 +48853,7 @@
         <v>60</v>
       </c>
       <c r="R552" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O552:Q552)</f>
         <v>114</v>
       </c>
       <c r="S552" s="22">
@@ -48908,7 +48916,7 @@
         <v>1</v>
       </c>
       <c r="R553" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O553:Q553)</f>
         <v>24</v>
       </c>
       <c r="S553" s="24">
@@ -48971,7 +48979,7 @@
         <v>0</v>
       </c>
       <c r="R554" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O554:Q554)</f>
         <v>21</v>
       </c>
       <c r="S554" s="22">
@@ -49035,7 +49043,7 @@
         <v>38</v>
       </c>
       <c r="R555" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O555:Q555)</f>
         <v>38</v>
       </c>
       <c r="S555" s="24">
@@ -49096,7 +49104,7 @@
         <v>97</v>
       </c>
       <c r="R556" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O556:Q556)</f>
         <v>97</v>
       </c>
       <c r="S556" s="22">
@@ -49160,7 +49168,7 @@
         <v>38</v>
       </c>
       <c r="R557" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O557:Q557)</f>
         <v>38</v>
       </c>
       <c r="S557" s="24">
@@ -49223,7 +49231,7 @@
         <v>0</v>
       </c>
       <c r="R558" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O558:Q558)</f>
         <v>8</v>
       </c>
       <c r="S558" s="22">
@@ -49286,7 +49294,7 @@
         <v>0</v>
       </c>
       <c r="R559" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O559:Q559)</f>
         <v>23</v>
       </c>
       <c r="S559" s="24">
@@ -49349,7 +49357,7 @@
         <v>0</v>
       </c>
       <c r="R560" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O560:Q560)</f>
         <v>20</v>
       </c>
       <c r="S560" s="22">
@@ -49412,7 +49420,7 @@
         <v>0</v>
       </c>
       <c r="R561" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O561:Q561)</f>
         <v>13</v>
       </c>
       <c r="S561" s="24">
@@ -49475,7 +49483,7 @@
         <v>79</v>
       </c>
       <c r="R562" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O562:Q562)</f>
         <v>250</v>
       </c>
       <c r="S562" s="22">
@@ -49538,7 +49546,7 @@
         <v>0</v>
       </c>
       <c r="R563" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O563:Q563)</f>
         <v>32</v>
       </c>
       <c r="S563" s="24">
@@ -49601,7 +49609,7 @@
         <v>0</v>
       </c>
       <c r="R564" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O564:Q564)</f>
         <v>41</v>
       </c>
       <c r="S564" s="22">
@@ -49664,7 +49672,7 @@
         <v>0</v>
       </c>
       <c r="R565" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O565:Q565)</f>
         <v>75</v>
       </c>
       <c r="S565" s="24">
@@ -49725,7 +49733,7 @@
         <v>0</v>
       </c>
       <c r="R566" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O566:Q566)</f>
         <v>100</v>
       </c>
       <c r="S566" s="22">
@@ -49788,7 +49796,7 @@
         <v>0</v>
       </c>
       <c r="R567" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O567:Q567)</f>
         <v>20</v>
       </c>
       <c r="S567" s="24">
@@ -49851,7 +49859,7 @@
         <v>0</v>
       </c>
       <c r="R568" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O568:Q568)</f>
         <v>40</v>
       </c>
       <c r="S568" s="22">
@@ -49914,7 +49922,7 @@
         <v>0</v>
       </c>
       <c r="R569" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O569:Q569)</f>
         <v>48</v>
       </c>
       <c r="S569" s="24">
@@ -49977,7 +49985,7 @@
         <v>0</v>
       </c>
       <c r="R570" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O570:Q570)</f>
         <v>16</v>
       </c>
       <c r="S570" s="22">
@@ -50038,7 +50046,7 @@
         <v>0</v>
       </c>
       <c r="R571" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O571:Q571)</f>
         <v>170</v>
       </c>
       <c r="S571" s="24">
@@ -50099,7 +50107,7 @@
         <v>0</v>
       </c>
       <c r="R572" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O572:Q572)</f>
         <v>80</v>
       </c>
       <c r="S572" s="22">
@@ -50160,7 +50168,7 @@
         <v>18</v>
       </c>
       <c r="R573" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O573:Q573)</f>
         <v>176</v>
       </c>
       <c r="S573" s="24">
@@ -50219,7 +50227,7 @@
         <v>0</v>
       </c>
       <c r="R574" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O574:Q574)</f>
         <v>0</v>
       </c>
       <c r="S574" s="22"/>
@@ -50280,7 +50288,7 @@
         <v>0</v>
       </c>
       <c r="R575" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O575:Q575)</f>
         <v>44</v>
       </c>
       <c r="S575" s="24">
@@ -50344,7 +50352,7 @@
         <v>33</v>
       </c>
       <c r="R576" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O576:Q576)</f>
         <v>41</v>
       </c>
       <c r="S576" s="22">
@@ -50405,7 +50413,7 @@
         <v>0</v>
       </c>
       <c r="R577" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O577:Q577)</f>
         <v>170</v>
       </c>
       <c r="S577" s="24">
@@ -50464,7 +50472,7 @@
         <v>40</v>
       </c>
       <c r="R578" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O578:Q578)</f>
         <v>40</v>
       </c>
       <c r="S578" s="22">
@@ -50523,7 +50531,7 @@
         <v>40</v>
       </c>
       <c r="R579" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O579:Q579)</f>
         <v>40</v>
       </c>
       <c r="S579" s="24">
@@ -50586,7 +50594,7 @@
         <v>0</v>
       </c>
       <c r="R580" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O580:Q580)</f>
         <v>18</v>
       </c>
       <c r="S580" s="22">
@@ -50649,7 +50657,7 @@
         <v>0</v>
       </c>
       <c r="R581" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O581:Q581)</f>
         <v>18</v>
       </c>
       <c r="S581" s="24">
@@ -50712,7 +50720,7 @@
         <v>0</v>
       </c>
       <c r="R582" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O582:Q582)</f>
         <v>38</v>
       </c>
       <c r="S582" s="22">
@@ -50775,7 +50783,7 @@
         <v>0</v>
       </c>
       <c r="R583" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O583:Q583)</f>
         <v>15</v>
       </c>
       <c r="S583" s="24">
@@ -50838,7 +50846,7 @@
         <v>31</v>
       </c>
       <c r="R584" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O584:Q584)</f>
         <v>31</v>
       </c>
       <c r="S584" s="22">
@@ -50901,7 +50909,7 @@
         <v>4</v>
       </c>
       <c r="R585" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O585:Q585)</f>
         <v>29</v>
       </c>
       <c r="S585" s="24">
@@ -50964,7 +50972,7 @@
         <v>30</v>
       </c>
       <c r="R586" s="23">
-        <f t="shared" ref="R586:R649" si="10">SUM(O586:Q586)</f>
+        <f>SUM(O586:Q586)</f>
         <v>30</v>
       </c>
       <c r="S586" s="22">
@@ -51027,7 +51035,7 @@
         <v>0</v>
       </c>
       <c r="R587" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O587:Q587)</f>
         <v>14</v>
       </c>
       <c r="S587" s="24">
@@ -51090,7 +51098,7 @@
         <v>27</v>
       </c>
       <c r="R588" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O588:Q588)</f>
         <v>27</v>
       </c>
       <c r="S588" s="22">
@@ -51153,7 +51161,7 @@
         <v>0</v>
       </c>
       <c r="R589" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O589:Q589)</f>
         <v>14</v>
       </c>
       <c r="S589" s="24">
@@ -51216,7 +51224,7 @@
         <v>0</v>
       </c>
       <c r="R590" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O590:Q590)</f>
         <v>33</v>
       </c>
       <c r="S590" s="22">
@@ -51279,7 +51287,7 @@
         <v>42</v>
       </c>
       <c r="R591" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O591:Q591)</f>
         <v>42</v>
       </c>
       <c r="S591" s="24">
@@ -51342,7 +51350,7 @@
         <v>0</v>
       </c>
       <c r="R592" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O592:Q592)</f>
         <v>22</v>
       </c>
       <c r="S592" s="22">
@@ -51405,7 +51413,7 @@
         <v>0</v>
       </c>
       <c r="R593" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O593:Q593)</f>
         <v>9</v>
       </c>
       <c r="S593" s="24">
@@ -51468,7 +51476,7 @@
         <v>0</v>
       </c>
       <c r="R594" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O594:Q594)</f>
         <v>20</v>
       </c>
       <c r="S594" s="22">
@@ -51529,7 +51537,7 @@
         <v>25</v>
       </c>
       <c r="R595" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O595:Q595)</f>
         <v>25</v>
       </c>
       <c r="S595" s="24">
@@ -51592,7 +51600,7 @@
         <v>24</v>
       </c>
       <c r="R596" s="73">
-        <f t="shared" si="10"/>
+        <f>SUM(O596:Q596)</f>
         <v>24</v>
       </c>
       <c r="S596" s="70">
@@ -51655,7 +51663,7 @@
         <v>0</v>
       </c>
       <c r="R597" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O597:Q597)</f>
         <v>46</v>
       </c>
       <c r="S597" s="24">
@@ -51718,7 +51726,7 @@
         <v>0</v>
       </c>
       <c r="R598" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O598:Q598)</f>
         <v>37</v>
       </c>
       <c r="S598" s="70">
@@ -51779,7 +51787,7 @@
         <v>0</v>
       </c>
       <c r="R599" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O599:Q599)</f>
         <v>24</v>
       </c>
       <c r="S599" s="64">
@@ -51842,7 +51850,7 @@
         <v>0</v>
       </c>
       <c r="R600" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O600:Q600)</f>
         <v>30</v>
       </c>
       <c r="S600" s="70">
@@ -51905,7 +51913,7 @@
         <v>0</v>
       </c>
       <c r="R601" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O601:Q601)</f>
         <v>21</v>
       </c>
       <c r="S601" s="64">
@@ -51968,7 +51976,7 @@
         <v>0</v>
       </c>
       <c r="R602" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O602:Q602)</f>
         <v>27</v>
       </c>
       <c r="S602" s="22">
@@ -52029,7 +52037,7 @@
         <v>0</v>
       </c>
       <c r="R603" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O603:Q603)</f>
         <v>26</v>
       </c>
       <c r="S603" s="24">
@@ -52092,7 +52100,7 @@
         <v>0</v>
       </c>
       <c r="R604" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O604:Q604)</f>
         <v>28</v>
       </c>
       <c r="S604" s="22">
@@ -52155,7 +52163,7 @@
         <v>0</v>
       </c>
       <c r="R605" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O605:Q605)</f>
         <v>20</v>
       </c>
       <c r="S605" s="24">
@@ -52216,7 +52224,7 @@
         <v>0</v>
       </c>
       <c r="R606" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O606:Q606)</f>
         <v>170</v>
       </c>
       <c r="S606" s="22">
@@ -52277,7 +52285,7 @@
         <v>0</v>
       </c>
       <c r="R607" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O607:Q607)</f>
         <v>170</v>
       </c>
       <c r="S607" s="24">
@@ -52340,7 +52348,7 @@
         <v>0</v>
       </c>
       <c r="R608" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O608:Q608)</f>
         <v>19</v>
       </c>
       <c r="S608" s="22">
@@ -52403,7 +52411,7 @@
         <v>0</v>
       </c>
       <c r="R609" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O609:Q609)</f>
         <v>19</v>
       </c>
       <c r="S609" s="24">
@@ -52464,7 +52472,7 @@
         <v>31</v>
       </c>
       <c r="R610" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O610:Q610)</f>
         <v>31</v>
       </c>
       <c r="S610" s="22">
@@ -52527,7 +52535,7 @@
         <v>0</v>
       </c>
       <c r="R611" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O611:Q611)</f>
         <v>15</v>
       </c>
       <c r="S611" s="24">
@@ -52588,7 +52596,7 @@
         <v>0</v>
       </c>
       <c r="R612" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O612:Q612)</f>
         <v>100</v>
       </c>
       <c r="S612" s="22">
@@ -52649,7 +52657,7 @@
         <v>0</v>
       </c>
       <c r="R613" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O613:Q613)</f>
         <v>114</v>
       </c>
       <c r="S613" s="24">
@@ -52712,7 +52720,7 @@
         <v>0</v>
       </c>
       <c r="R614" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O614:Q614)</f>
         <v>491</v>
       </c>
       <c r="S614" s="22">
@@ -52775,7 +52783,7 @@
         <v>0</v>
       </c>
       <c r="R615" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O615:Q615)</f>
         <v>27</v>
       </c>
       <c r="S615" s="24">
@@ -52836,7 +52844,7 @@
         <v>0</v>
       </c>
       <c r="R616" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O616:Q616)</f>
         <v>63</v>
       </c>
       <c r="S616" s="22">
@@ -52899,7 +52907,7 @@
         <v>0</v>
       </c>
       <c r="R617" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O617:Q617)</f>
         <v>42</v>
       </c>
       <c r="S617" s="24">
@@ -52962,7 +52970,7 @@
         <v>0</v>
       </c>
       <c r="R618" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O618:Q618)</f>
         <v>27</v>
       </c>
       <c r="S618" s="22">
@@ -53025,7 +53033,7 @@
         <v>0</v>
       </c>
       <c r="R619" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O619:Q619)</f>
         <v>40</v>
       </c>
       <c r="S619" s="24">
@@ -53086,7 +53094,7 @@
         <v>0</v>
       </c>
       <c r="R620" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O620:Q620)</f>
         <v>47</v>
       </c>
       <c r="S620" s="22">
@@ -53147,7 +53155,7 @@
         <v>0</v>
       </c>
       <c r="R621" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O621:Q621)</f>
         <v>23</v>
       </c>
       <c r="S621" s="24">
@@ -53208,7 +53216,7 @@
         <v>0</v>
       </c>
       <c r="R622" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O622:Q622)</f>
         <v>21</v>
       </c>
       <c r="S622" s="22">
@@ -53271,7 +53279,7 @@
         <v>0</v>
       </c>
       <c r="R623" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O623:Q623)</f>
         <v>26</v>
       </c>
       <c r="S623" s="24">
@@ -53330,7 +53338,7 @@
         <v>88</v>
       </c>
       <c r="R624" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O624:Q624)</f>
         <v>88</v>
       </c>
       <c r="S624" s="22">
@@ -53391,7 +53399,7 @@
         <v>0</v>
       </c>
       <c r="R625" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O625:Q625)</f>
         <v>33</v>
       </c>
       <c r="S625" s="24">
@@ -53450,7 +53458,7 @@
         <v>128</v>
       </c>
       <c r="R626" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O626:Q626)</f>
         <v>128</v>
       </c>
       <c r="S626" s="22">
@@ -53511,7 +53519,7 @@
         <v>0</v>
       </c>
       <c r="R627" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O627:Q627)</f>
         <v>80</v>
       </c>
       <c r="S627" s="24">
@@ -53572,7 +53580,7 @@
         <v>0</v>
       </c>
       <c r="R628" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O628:Q628)</f>
         <v>23</v>
       </c>
       <c r="S628" s="22" t="s">
@@ -53635,7 +53643,7 @@
         <v>0</v>
       </c>
       <c r="R629" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O629:Q629)</f>
         <v>49</v>
       </c>
       <c r="S629" s="24">
@@ -53696,7 +53704,7 @@
         <v>46</v>
       </c>
       <c r="R630" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O630:Q630)</f>
         <v>228</v>
       </c>
       <c r="S630" s="22">
@@ -53757,7 +53765,7 @@
         <v>0</v>
       </c>
       <c r="R631" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O631:Q631)</f>
         <v>28</v>
       </c>
       <c r="S631" s="24">
@@ -53818,7 +53826,7 @@
         <v>0</v>
       </c>
       <c r="R632" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O632:Q632)</f>
         <v>16</v>
       </c>
       <c r="S632" s="22">
@@ -53879,7 +53887,7 @@
         <v>0</v>
       </c>
       <c r="R633" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O633:Q633)</f>
         <v>40</v>
       </c>
       <c r="S633" s="24">
@@ -53942,7 +53950,7 @@
         <v>0</v>
       </c>
       <c r="R634" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O634:Q634)</f>
         <v>80</v>
       </c>
       <c r="S634" s="22">
@@ -54003,7 +54011,7 @@
         <v>0</v>
       </c>
       <c r="R635" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O635:Q635)</f>
         <v>70</v>
       </c>
       <c r="S635" s="24">
@@ -54064,7 +54072,7 @@
         <v>0</v>
       </c>
       <c r="R636" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O636:Q636)</f>
         <v>28</v>
       </c>
       <c r="S636" s="22">
@@ -54125,7 +54133,7 @@
         <v>30</v>
       </c>
       <c r="R637" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O637:Q637)</f>
         <v>30</v>
       </c>
       <c r="S637" s="24">
@@ -54188,7 +54196,7 @@
         <v>0</v>
       </c>
       <c r="R638" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O638:Q638)</f>
         <v>21</v>
       </c>
       <c r="S638" s="22" t="s">
@@ -54251,7 +54259,7 @@
         <v>40</v>
       </c>
       <c r="R639" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O639:Q639)</f>
         <v>179</v>
       </c>
       <c r="S639" s="24">
@@ -54308,7 +54316,7 @@
         <v>0</v>
       </c>
       <c r="R640" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O640:Q640)</f>
         <v>0</v>
       </c>
       <c r="S640" s="22">
@@ -54428,7 +54436,7 @@
         <v>33</v>
       </c>
       <c r="R642" s="23">
-        <f t="shared" ref="R642:R649" si="11">SUM(O642:Q642)</f>
+        <f>SUM(O642:Q642)</f>
         <v>33</v>
       </c>
       <c r="S642" s="22">
@@ -54487,7 +54495,7 @@
         <v>39</v>
       </c>
       <c r="R643" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O643:Q643)</f>
         <v>39</v>
       </c>
       <c r="S643" s="24">
@@ -54549,7 +54557,7 @@
         <v>39</v>
       </c>
       <c r="R644" s="23">
-        <f t="shared" si="11"/>
+        <f>SUM(O644:Q644)</f>
         <v>39</v>
       </c>
       <c r="S644" s="22">
@@ -54610,7 +54618,7 @@
         <v>0</v>
       </c>
       <c r="R645" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O645:Q645)</f>
         <v>170</v>
       </c>
       <c r="S645" s="24">
@@ -54673,7 +54681,7 @@
         <v>0</v>
       </c>
       <c r="R646" s="23">
-        <f t="shared" si="11"/>
+        <f>SUM(O646:Q646)</f>
         <v>13</v>
       </c>
       <c r="S646" s="22">
@@ -54734,7 +54742,7 @@
         <v>0</v>
       </c>
       <c r="R647" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O647:Q647)</f>
         <v>34</v>
       </c>
       <c r="S647" s="24">
@@ -54795,7 +54803,7 @@
         <v>0</v>
       </c>
       <c r="R648" s="23">
-        <f t="shared" si="11"/>
+        <f>SUM(O648:Q648)</f>
         <v>45</v>
       </c>
       <c r="S648" s="22">
@@ -54854,7 +54862,7 @@
         <v>0</v>
       </c>
       <c r="R649" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O649:Q649)</f>
         <v>72</v>
       </c>
       <c r="S649" s="24">
@@ -55655,7 +55663,7 @@
         <v>0</v>
       </c>
       <c r="R662" s="23">
-        <f t="shared" ref="R662:R668" si="12">SUM(O662:Q662)</f>
+        <f>SUM(O662:Q662)</f>
         <v>20</v>
       </c>
       <c r="S662" s="22">
@@ -55719,7 +55727,7 @@
         <v>0</v>
       </c>
       <c r="R663" s="25">
-        <f t="shared" si="12"/>
+        <f>SUM(O663:Q663)</f>
         <v>19</v>
       </c>
       <c r="S663" s="24">
@@ -55783,7 +55791,7 @@
         <v>0</v>
       </c>
       <c r="R664" s="23">
-        <f t="shared" si="12"/>
+        <f>SUM(O664:Q664)</f>
         <v>33</v>
       </c>
       <c r="S664" s="22">
@@ -55847,7 +55855,7 @@
         <v>0</v>
       </c>
       <c r="R665" s="25">
-        <f t="shared" si="12"/>
+        <f>SUM(O665:Q665)</f>
         <v>20</v>
       </c>
       <c r="S665" s="24">
@@ -55911,7 +55919,7 @@
         <v>0</v>
       </c>
       <c r="R666" s="23">
-        <f t="shared" si="12"/>
+        <f>SUM(O666:Q666)</f>
         <v>20</v>
       </c>
       <c r="S666" s="22">
@@ -55973,7 +55981,7 @@
         <v>14</v>
       </c>
       <c r="R667" s="25">
-        <f t="shared" si="12"/>
+        <f>SUM(O667:Q667)</f>
         <v>127</v>
       </c>
       <c r="S667" s="24">
@@ -56035,7 +56043,7 @@
         <v>34</v>
       </c>
       <c r="R668" s="23">
-        <f t="shared" si="12"/>
+        <f>SUM(O668:Q668)</f>
         <v>192</v>
       </c>
       <c r="S668" s="22">
@@ -56225,7 +56233,7 @@
         <v>0</v>
       </c>
       <c r="R671" s="25">
-        <f t="shared" ref="R671:R684" si="13">SUM(O671:Q671)</f>
+        <f>SUM(O671:Q671)</f>
         <v>22</v>
       </c>
       <c r="S671" s="24">
@@ -56289,7 +56297,7 @@
         <v>0</v>
       </c>
       <c r="R672" s="178">
-        <f t="shared" si="13"/>
+        <f>SUM(O672:Q672)</f>
         <v>1</v>
       </c>
       <c r="S672" s="172">
@@ -56341,7 +56349,7 @@
       <c r="P673" s="25"/>
       <c r="Q673" s="25"/>
       <c r="R673" s="25">
-        <f t="shared" si="13"/>
+        <f>SUM(O673:Q673)</f>
         <v>0</v>
       </c>
       <c r="S673" s="24"/>
@@ -56399,7 +56407,7 @@
         <v>80</v>
       </c>
       <c r="R674" s="23">
-        <f t="shared" si="13"/>
+        <f>SUM(O674:Q674)</f>
         <v>80</v>
       </c>
       <c r="S674" s="22">
@@ -56459,7 +56467,7 @@
         <v>80</v>
       </c>
       <c r="R675" s="23">
-        <f t="shared" si="13"/>
+        <f>SUM(O675:Q675)</f>
         <v>80</v>
       </c>
       <c r="S675" s="22">
@@ -56513,7 +56521,7 @@
       <c r="P676" s="25"/>
       <c r="Q676" s="25"/>
       <c r="R676" s="25">
-        <f t="shared" si="13"/>
+        <f>SUM(O676:Q676)</f>
         <v>0</v>
       </c>
       <c r="S676" s="24">
@@ -56575,7 +56583,7 @@
         <v>5</v>
       </c>
       <c r="R677" s="193">
-        <f t="shared" si="13"/>
+        <f>SUM(O677:Q677)</f>
         <v>100</v>
       </c>
       <c r="S677" s="186">
@@ -56639,7 +56647,7 @@
         <v>0</v>
       </c>
       <c r="R678" s="63">
-        <f t="shared" si="13"/>
+        <f>SUM(O678:Q678)</f>
         <v>17</v>
       </c>
       <c r="S678" s="64">
@@ -56703,7 +56711,7 @@
         <v>0</v>
       </c>
       <c r="R679" s="185">
-        <f t="shared" si="13"/>
+        <f>SUM(O679:Q679)</f>
         <v>32</v>
       </c>
       <c r="S679" s="180">
@@ -56757,7 +56765,7 @@
       <c r="P680" s="73"/>
       <c r="Q680" s="73"/>
       <c r="R680" s="73">
-        <f t="shared" si="13"/>
+        <f>SUM(O680:Q680)</f>
         <v>0</v>
       </c>
       <c r="S680" s="70">
@@ -56811,7 +56819,7 @@
       <c r="P681" s="193"/>
       <c r="Q681" s="193"/>
       <c r="R681" s="193">
-        <f t="shared" si="13"/>
+        <f>SUM(O681:Q681)</f>
         <v>0</v>
       </c>
       <c r="S681" s="186">
@@ -56865,7 +56873,7 @@
       <c r="P682" s="185"/>
       <c r="Q682" s="185"/>
       <c r="R682" s="185">
-        <f t="shared" si="13"/>
+        <f>SUM(O682:Q682)</f>
         <v>0</v>
       </c>
       <c r="S682" s="180">
@@ -56919,7 +56927,7 @@
       <c r="P683" s="193"/>
       <c r="Q683" s="193"/>
       <c r="R683" s="193">
-        <f t="shared" si="13"/>
+        <f>SUM(O683:Q683)</f>
         <v>0</v>
       </c>
       <c r="S683" s="186">
@@ -56969,7 +56977,7 @@
       <c r="P684" s="73"/>
       <c r="Q684" s="73"/>
       <c r="R684" s="73">
-        <f t="shared" si="13"/>
+        <f>SUM(O684:Q684)</f>
         <v>0</v>
       </c>
       <c r="S684" s="70">
@@ -57023,7 +57031,7 @@
       <c r="P685" s="217"/>
       <c r="Q685" s="217"/>
       <c r="R685" s="217">
-        <f t="shared" ref="R685:R747" si="14">IF(B685="","",SUM(O685:Q685))</f>
+        <f t="shared" ref="R685:R747" si="0">IF(B685="","",SUM(O685:Q685))</f>
         <v>0</v>
       </c>
       <c r="S685" s="210">
@@ -57080,7 +57088,7 @@
       <c r="P686" s="225"/>
       <c r="Q686" s="225"/>
       <c r="R686" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S686" s="219">
@@ -57135,7 +57143,7 @@
       <c r="P687" s="217"/>
       <c r="Q687" s="217"/>
       <c r="R687" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S687" s="210">
@@ -57192,7 +57200,7 @@
       <c r="P688" s="225"/>
       <c r="Q688" s="225"/>
       <c r="R688" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S688" s="219">
@@ -57257,7 +57265,7 @@
         <v>0</v>
       </c>
       <c r="R689" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="S689" s="210">
@@ -57314,7 +57322,7 @@
       <c r="P690" s="225"/>
       <c r="Q690" s="225"/>
       <c r="R690" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S690" s="219">
@@ -57379,7 +57387,7 @@
         <v>0</v>
       </c>
       <c r="R691" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="S691" s="210">
@@ -57444,7 +57452,7 @@
         <v>0</v>
       </c>
       <c r="R692" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S692" s="219">
@@ -57509,7 +57517,7 @@
         <v>0</v>
       </c>
       <c r="R693" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S693" s="210">
@@ -57562,7 +57570,7 @@
       <c r="P694" s="225"/>
       <c r="Q694" s="225"/>
       <c r="R694" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S694" s="219">
@@ -57615,7 +57623,7 @@
       <c r="P695" s="217"/>
       <c r="Q695" s="217"/>
       <c r="R695" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S695" s="210">
@@ -57672,7 +57680,7 @@
         <v>25</v>
       </c>
       <c r="R696" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="S696" s="219">
@@ -57733,7 +57741,7 @@
         <v>50</v>
       </c>
       <c r="R697" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="S697" s="210">
@@ -57786,7 +57794,7 @@
       <c r="P698" s="225"/>
       <c r="Q698" s="225"/>
       <c r="R698" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S698" s="219">
@@ -57841,7 +57849,7 @@
       <c r="P699" s="217"/>
       <c r="Q699" s="217"/>
       <c r="R699" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S699" s="210">
@@ -57896,7 +57904,7 @@
       <c r="P700" s="225"/>
       <c r="Q700" s="225"/>
       <c r="R700" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S700" s="219">
@@ -57931,7 +57939,7 @@
         <v>71</v>
       </c>
       <c r="H701" s="213" t="s">
-        <v>2822</v>
+        <v>2953</v>
       </c>
       <c r="I701" s="214">
         <v>46237</v>
@@ -57951,7 +57959,7 @@
       <c r="P701" s="217"/>
       <c r="Q701" s="217"/>
       <c r="R701" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S701" s="210">
@@ -57972,10 +57980,10 @@
         <v>2748</v>
       </c>
       <c r="D702" s="219" t="s">
+        <v>2822</v>
+      </c>
+      <c r="E702" s="220" t="s">
         <v>2823</v>
-      </c>
-      <c r="E702" s="220" t="s">
-        <v>2824</v>
       </c>
       <c r="F702" s="221" t="s">
         <v>23</v>
@@ -58002,14 +58010,14 @@
       <c r="P702" s="225"/>
       <c r="Q702" s="225"/>
       <c r="R702" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S702" s="219">
         <v>12</v>
       </c>
       <c r="T702" s="218" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="U702" s="203"/>
     </row>
@@ -58035,7 +58043,7 @@
       <c r="P703" s="217"/>
       <c r="Q703" s="217"/>
       <c r="R703" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S703" s="210"/>
@@ -58064,7 +58072,7 @@
       <c r="P704" s="225"/>
       <c r="Q704" s="225"/>
       <c r="R704" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S704" s="219"/>
@@ -58093,7 +58101,7 @@
       <c r="P705" s="217"/>
       <c r="Q705" s="217"/>
       <c r="R705" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S705" s="210"/>
@@ -58122,7 +58130,7 @@
       <c r="P706" s="225"/>
       <c r="Q706" s="225"/>
       <c r="R706" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S706" s="219"/>
@@ -58151,7 +58159,7 @@
       <c r="P707" s="217"/>
       <c r="Q707" s="217"/>
       <c r="R707" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S707" s="210"/>
@@ -58180,7 +58188,7 @@
       <c r="P708" s="225"/>
       <c r="Q708" s="225"/>
       <c r="R708" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S708" s="219"/>
@@ -58209,7 +58217,7 @@
       <c r="P709" s="217"/>
       <c r="Q709" s="217"/>
       <c r="R709" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S709" s="210"/>
@@ -58238,7 +58246,7 @@
       <c r="P710" s="225"/>
       <c r="Q710" s="225"/>
       <c r="R710" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S710" s="219"/>
@@ -58267,7 +58275,7 @@
       <c r="P711" s="217"/>
       <c r="Q711" s="217"/>
       <c r="R711" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S711" s="210"/>
@@ -58296,7 +58304,7 @@
       <c r="P712" s="225"/>
       <c r="Q712" s="225"/>
       <c r="R712" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S712" s="219"/>
@@ -58325,7 +58333,7 @@
       <c r="P713" s="217"/>
       <c r="Q713" s="217"/>
       <c r="R713" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S713" s="210"/>
@@ -58354,7 +58362,7 @@
       <c r="P714" s="225"/>
       <c r="Q714" s="225"/>
       <c r="R714" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S714" s="219"/>
@@ -58383,7 +58391,7 @@
       <c r="P715" s="217"/>
       <c r="Q715" s="217"/>
       <c r="R715" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S715" s="210"/>
@@ -58412,7 +58420,7 @@
       <c r="P716" s="225"/>
       <c r="Q716" s="225"/>
       <c r="R716" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S716" s="219"/>
@@ -58441,7 +58449,7 @@
       <c r="P717" s="217"/>
       <c r="Q717" s="217"/>
       <c r="R717" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S717" s="210"/>
@@ -58470,7 +58478,7 @@
       <c r="P718" s="225"/>
       <c r="Q718" s="225"/>
       <c r="R718" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S718" s="219"/>
@@ -58499,7 +58507,7 @@
       <c r="P719" s="217"/>
       <c r="Q719" s="217"/>
       <c r="R719" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S719" s="210"/>
@@ -58528,7 +58536,7 @@
       <c r="P720" s="225"/>
       <c r="Q720" s="225"/>
       <c r="R720" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S720" s="219"/>
@@ -58557,7 +58565,7 @@
       <c r="P721" s="217"/>
       <c r="Q721" s="217"/>
       <c r="R721" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S721" s="210"/>
@@ -58586,7 +58594,7 @@
       <c r="P722" s="225"/>
       <c r="Q722" s="225"/>
       <c r="R722" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S722" s="219"/>
@@ -58615,7 +58623,7 @@
       <c r="P723" s="217"/>
       <c r="Q723" s="217"/>
       <c r="R723" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S723" s="210"/>
@@ -58644,7 +58652,7 @@
       <c r="P724" s="225"/>
       <c r="Q724" s="225"/>
       <c r="R724" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S724" s="219"/>
@@ -58673,7 +58681,7 @@
       <c r="P725" s="217"/>
       <c r="Q725" s="217"/>
       <c r="R725" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S725" s="210"/>
@@ -58702,7 +58710,7 @@
       <c r="P726" s="225"/>
       <c r="Q726" s="225"/>
       <c r="R726" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S726" s="219"/>
@@ -58731,7 +58739,7 @@
       <c r="P727" s="217"/>
       <c r="Q727" s="217"/>
       <c r="R727" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S727" s="210"/>
@@ -58760,7 +58768,7 @@
       <c r="P728" s="225"/>
       <c r="Q728" s="225"/>
       <c r="R728" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S728" s="219"/>
@@ -58789,7 +58797,7 @@
       <c r="P729" s="217"/>
       <c r="Q729" s="217"/>
       <c r="R729" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S729" s="210"/>
@@ -58818,7 +58826,7 @@
       <c r="P730" s="225"/>
       <c r="Q730" s="225"/>
       <c r="R730" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S730" s="219"/>
@@ -58847,7 +58855,7 @@
       <c r="P731" s="217"/>
       <c r="Q731" s="217"/>
       <c r="R731" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S731" s="210"/>
@@ -58876,7 +58884,7 @@
       <c r="P732" s="225"/>
       <c r="Q732" s="225"/>
       <c r="R732" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S732" s="219"/>
@@ -58905,7 +58913,7 @@
       <c r="P733" s="217"/>
       <c r="Q733" s="217"/>
       <c r="R733" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S733" s="210"/>
@@ -58934,7 +58942,7 @@
       <c r="P734" s="225"/>
       <c r="Q734" s="225"/>
       <c r="R734" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S734" s="219"/>
@@ -58963,7 +58971,7 @@
       <c r="P735" s="217"/>
       <c r="Q735" s="217"/>
       <c r="R735" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S735" s="210"/>
@@ -58992,7 +59000,7 @@
       <c r="P736" s="225"/>
       <c r="Q736" s="225"/>
       <c r="R736" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S736" s="219"/>
@@ -59021,7 +59029,7 @@
       <c r="P737" s="217"/>
       <c r="Q737" s="217"/>
       <c r="R737" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S737" s="210"/>
@@ -59050,7 +59058,7 @@
       <c r="P738" s="225"/>
       <c r="Q738" s="225"/>
       <c r="R738" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S738" s="219"/>
@@ -59079,7 +59087,7 @@
       <c r="P739" s="217"/>
       <c r="Q739" s="217"/>
       <c r="R739" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S739" s="210"/>
@@ -59108,7 +59116,7 @@
       <c r="P740" s="225"/>
       <c r="Q740" s="225"/>
       <c r="R740" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S740" s="219"/>
@@ -59137,7 +59145,7 @@
       <c r="P741" s="217"/>
       <c r="Q741" s="217"/>
       <c r="R741" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S741" s="210"/>
@@ -59166,7 +59174,7 @@
       <c r="P742" s="225"/>
       <c r="Q742" s="225"/>
       <c r="R742" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S742" s="219"/>
@@ -59195,7 +59203,7 @@
       <c r="P743" s="217"/>
       <c r="Q743" s="217"/>
       <c r="R743" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S743" s="210"/>
@@ -59224,7 +59232,7 @@
       <c r="P744" s="225"/>
       <c r="Q744" s="225"/>
       <c r="R744" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S744" s="219"/>
@@ -59253,7 +59261,7 @@
       <c r="P745" s="217"/>
       <c r="Q745" s="217"/>
       <c r="R745" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S745" s="210"/>
@@ -59282,7 +59290,7 @@
       <c r="P746" s="225"/>
       <c r="Q746" s="225"/>
       <c r="R746" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S746" s="219"/>
@@ -59311,7 +59319,7 @@
       <c r="P747" s="217"/>
       <c r="Q747" s="217"/>
       <c r="R747" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S747" s="210"/>
@@ -59340,7 +59348,7 @@
       <c r="P748" s="225"/>
       <c r="Q748" s="225"/>
       <c r="R748" s="225" t="str">
-        <f t="shared" ref="R748" si="15">IF(B748="","",SUM(O748:Q748))</f>
+        <f t="shared" ref="R748" si="1">IF(B748="","",SUM(O748:Q748))</f>
         <v/>
       </c>
       <c r="S748" s="219"/>
@@ -59521,50 +59529,50 @@
         <v>1</v>
       </c>
       <c r="B1" s="96" t="s">
+        <v>2825</v>
+      </c>
+      <c r="C1" s="96" t="s">
         <v>2826</v>
-      </c>
-      <c r="C1" s="96" t="s">
-        <v>2827</v>
       </c>
       <c r="D1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="F1" s="96" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="96" t="s">
+        <v>2828</v>
+      </c>
+      <c r="H1" s="96" t="s">
         <v>2829</v>
       </c>
-      <c r="H1" s="96" t="s">
+      <c r="I1" s="96" t="s">
         <v>2830</v>
       </c>
-      <c r="I1" s="96" t="s">
+      <c r="J1" s="96" t="s">
         <v>2831</v>
       </c>
-      <c r="J1" s="96" t="s">
+      <c r="L1" s="129" t="s">
         <v>2832</v>
-      </c>
-      <c r="L1" s="129" t="s">
-        <v>2833</v>
       </c>
       <c r="M1" s="100">
         <v>2026</v>
       </c>
       <c r="U1" s="162" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="V1" s="161"/>
       <c r="X1" s="159" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="Y1" s="107"/>
       <c r="Z1" s="107"/>
       <c r="AA1" s="107"/>
       <c r="AC1" s="254" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -59600,25 +59608,25 @@
         <v>10.4</v>
       </c>
       <c r="X2" s="160" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="Y2" s="160" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="160" t="s">
+        <v>2836</v>
+      </c>
+      <c r="AA2" s="160" t="s">
         <v>2837</v>
-      </c>
-      <c r="AA2" s="160" t="s">
-        <v>2838</v>
       </c>
       <c r="AC2" s="255" t="s">
         <v>1</v>
       </c>
       <c r="AD2" s="255" t="s">
+        <v>2838</v>
+      </c>
+      <c r="AE2" s="255" t="s">
         <v>2839</v>
-      </c>
-      <c r="AE2" s="255" t="s">
-        <v>2840</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -59653,34 +59661,34 @@
         <v>5.2</v>
       </c>
       <c r="L3" s="19" t="s">
+        <v>2840</v>
+      </c>
+      <c r="M3" s="19" t="s">
         <v>2841</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="N3" s="19" t="s">
         <v>2842</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="O3" s="19" t="s">
         <v>2843</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="P3" s="19" t="s">
         <v>2844</v>
       </c>
-      <c r="P3" s="19" t="s">
+      <c r="Q3" s="19" t="s">
         <v>2845</v>
       </c>
-      <c r="Q3" s="19" t="s">
+      <c r="R3" s="19" t="s">
         <v>2846</v>
       </c>
-      <c r="R3" s="19" t="s">
+      <c r="S3" s="19" t="s">
         <v>2847</v>
       </c>
-      <c r="S3" s="19" t="s">
+      <c r="T3" s="19" t="s">
         <v>2848</v>
       </c>
-      <c r="T3" s="19" t="s">
+      <c r="X3" t="s">
         <v>2849</v>
-      </c>
-      <c r="X3" t="s">
-        <v>2850</v>
       </c>
       <c r="Y3" t="s">
         <v>2695</v>
@@ -59764,7 +59772,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="Y4" t="s">
         <v>2695</v>
@@ -59844,7 +59852,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="Y5" t="s">
         <v>2711</v>
@@ -59859,7 +59867,7 @@
         <v>2026</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="AE5" s="250">
         <v>16</v>
@@ -59924,10 +59932,10 @@
         <v>6</v>
       </c>
       <c r="X6" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="Y6" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -59939,7 +59947,7 @@
         <v>2026</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="AE6" s="250">
         <v>16</v>
@@ -60004,7 +60012,7 @@
         <v>8</v>
       </c>
       <c r="X7" s="98" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="Y7" t="s">
         <v>2695</v>
@@ -60084,7 +60092,7 @@
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="Y8" s="95" t="s">
         <v>1342</v>
@@ -60157,7 +60165,7 @@
         <v>11</v>
       </c>
       <c r="X9" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="Y9" s="95" t="s">
         <v>1022</v>
@@ -60230,7 +60238,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="Y10" s="95" t="s">
         <v>1366</v>
@@ -60303,10 +60311,10 @@
         <v>14</v>
       </c>
       <c r="X11" t="s">
+        <v>2856</v>
+      </c>
+      <c r="Y11" s="95" t="s">
         <v>2857</v>
-      </c>
-      <c r="Y11" s="95" t="s">
-        <v>2858</v>
       </c>
       <c r="AA11">
         <v>1.2</v>
@@ -60376,10 +60384,10 @@
         <v>15</v>
       </c>
       <c r="X12" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="AA12">
         <v>1.2</v>
@@ -60449,7 +60457,7 @@
         <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>1342</v>
@@ -60522,7 +60530,7 @@
         <v>18</v>
       </c>
       <c r="X14" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="Y14" s="95" t="s">
         <v>1022</v>
@@ -60595,7 +60603,7 @@
         <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="Y15" s="95" t="s">
         <v>1366</v>
@@ -60668,10 +60676,10 @@
         <v>22</v>
       </c>
       <c r="X16" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="Y16" s="95" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="AA16">
         <v>1.2</v>
@@ -60741,10 +60749,10 @@
         <v>23</v>
       </c>
       <c r="X17" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="Y17" s="95" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="AA17">
         <v>1.2</v>
@@ -60814,7 +60822,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="Y18" s="95" t="s">
         <v>1342</v>
@@ -60887,7 +60895,7 @@
         <v>33</v>
       </c>
       <c r="X19" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="Y19" s="95" t="s">
         <v>1022</v>
@@ -60960,7 +60968,7 @@
         <v>34</v>
       </c>
       <c r="X20" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="Y20" s="95" t="s">
         <v>1366</v>
@@ -61033,10 +61041,10 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="Y21" s="95" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="AA21">
         <v>1.2</v>
@@ -61106,10 +61114,10 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="Y22" s="95" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="AA22">
         <v>1.2</v>
@@ -61179,7 +61187,7 @@
         <v>39</v>
       </c>
       <c r="X23" s="98" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="Y23" s="95" t="s">
         <v>2711</v>
@@ -61252,10 +61260,10 @@
         <v>41</v>
       </c>
       <c r="X24" s="98" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="Y24" s="95" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -61325,7 +61333,7 @@
         <v>43</v>
       </c>
       <c r="X25" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="Y25" s="95" t="s">
         <v>854</v>
@@ -61398,10 +61406,10 @@
         <v>45</v>
       </c>
       <c r="X26" t="s">
+        <v>2862</v>
+      </c>
+      <c r="Y26" s="95" t="s">
         <v>2863</v>
-      </c>
-      <c r="Y26" s="95" t="s">
-        <v>2864</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -61474,7 +61482,7 @@
         <v>47</v>
       </c>
       <c r="X27" s="257" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="Y27" s="95" t="s">
         <v>2711</v>
@@ -61547,10 +61555,10 @@
         <v>49</v>
       </c>
       <c r="X28" s="257" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -61620,7 +61628,7 @@
         <v>50</v>
       </c>
       <c r="X29" s="257" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="Y29" s="95" t="s">
         <v>2711</v>
@@ -61693,10 +61701,10 @@
         <v>51</v>
       </c>
       <c r="X30" s="257" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="Y30" s="95" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -61766,7 +61774,7 @@
         <v>56</v>
       </c>
       <c r="X31" s="257" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="Y31" s="95" t="s">
         <v>471</v>
@@ -61842,7 +61850,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="257" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="Y32" t="s">
         <v>1342</v>
@@ -61918,10 +61926,10 @@
         <v>59</v>
       </c>
       <c r="X33" s="257" t="s">
+        <v>2867</v>
+      </c>
+      <c r="Y33" t="s">
         <v>2868</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>2869</v>
       </c>
       <c r="Z33">
         <v>4</v>
@@ -61931,7 +61939,7 @@
       </c>
       <c r="AC33" s="251"/>
       <c r="AD33" s="252" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="AE33" s="253">
         <f>SUM(AE3:AE32)</f>
@@ -61997,10 +62005,10 @@
         <v>60</v>
       </c>
       <c r="X34" s="257" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="Y34" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -62068,7 +62076,7 @@
         <v>62</v>
       </c>
       <c r="X35" s="257" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="Y35" t="s">
         <v>107</v>
@@ -62139,7 +62147,7 @@
         <v>63</v>
       </c>
       <c r="X36" s="257" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="Y36" t="s">
         <v>548</v>
@@ -62210,7 +62218,7 @@
         <v>64</v>
       </c>
       <c r="X37" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="Y37" t="s">
         <v>417</v>
@@ -62281,7 +62289,7 @@
         <v>65</v>
       </c>
       <c r="X38" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="Y38" s="260" t="s">
         <v>1095</v>
@@ -62334,7 +62342,7 @@
         <v>68</v>
       </c>
       <c r="X39" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="Y39" t="s">
         <v>548</v>
@@ -62384,7 +62392,7 @@
         <v/>
       </c>
       <c r="X40" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="Y40" t="s">
         <v>471</v>
@@ -64569,7 +64577,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="280" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="B1" s="280"/>
       <c r="C1" s="280"/>
@@ -64590,15 +64598,15 @@
     <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="281" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="B4" s="282"/>
       <c r="D4" s="283" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="E4" s="284"/>
       <c r="G4" s="125" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
@@ -64607,14 +64615,14 @@
         <v>46</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
         <v>28</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
@@ -64632,11 +64640,11 @@
     </row>
     <row r="8" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A8" s="278" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="B8" s="278"/>
       <c r="D8" s="278" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="E8" s="278"/>
     </row>
@@ -64651,13 +64659,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="108" t="s">
+        <v>2881</v>
+      </c>
+      <c r="D10" s="108" t="s">
         <v>2882</v>
       </c>
-      <c r="D10" s="108" t="s">
+      <c r="E10" s="108" t="s">
         <v>2883</v>
-      </c>
-      <c r="E10" s="108" t="s">
-        <v>2884</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -64669,7 +64677,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="109" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -64685,7 +64693,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -64701,7 +64709,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="109" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -64710,14 +64718,14 @@
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="113" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
         <v>28</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
@@ -64726,7 +64734,7 @@
     </row>
     <row r="30" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A30" s="278" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="B30" s="278"/>
       <c r="C30" s="278"/>
@@ -64745,16 +64753,16 @@
         <v>6</v>
       </c>
       <c r="B32" s="108" t="s">
+        <v>2890</v>
+      </c>
+      <c r="C32" s="108" t="s">
         <v>2891</v>
       </c>
-      <c r="C32" s="108" t="s">
+      <c r="D32" s="108" t="s">
         <v>2892</v>
       </c>
-      <c r="D32" s="108" t="s">
+      <c r="E32" s="108" t="s">
         <v>2893</v>
-      </c>
-      <c r="E32" s="108" t="s">
-        <v>2894</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64948,7 +64956,7 @@
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="156" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="B42" s="153">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A42)</f>
@@ -64990,7 +64998,7 @@
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="148" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="B44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,"")</f>
@@ -65011,7 +65019,7 @@
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="113" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
@@ -65062,163 +65070,163 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>2897</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2898</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>2899</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>2900</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>2901</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
+        <v>2901</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>2902</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>2903</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1728</v>
       </c>
       <c r="D2" s="12" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>2904</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>2905</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
+        <v>2901</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>2902</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>2903</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>2905</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>2906</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>2907</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
+        <v>2901</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>2902</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>2903</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>67</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
+        <v>2901</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>2902</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>2903</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>71</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>2908</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>2909</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>2910</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
+        <v>2901</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>2902</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>2903</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2725</v>
       </c>
       <c r="D6" s="12" t="s">
+        <v>2910</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>2911</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>2912</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>2913</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>2914</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>2915</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="12" t="s">
+        <v>2915</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>2916</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>2917</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>456</v>
       </c>
       <c r="D9" s="12" t="s">
+        <v>2918</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>2919</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>2920</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>198</v>
@@ -65227,15 +65235,15 @@
         <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>363</v>
@@ -65244,7 +65252,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
     </row>
   </sheetData>
@@ -65266,16 +65274,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -65286,7 +65294,7 @@
         <v>34</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>2756</v>
@@ -65300,7 +65308,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>2748</v>
@@ -65351,180 +65359,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>2897</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2898</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>2899</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>2900</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>2901</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>67</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>71</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>2688</v>
       </c>
       <c r="D5" s="18" t="s">
+        <v>2930</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>2931</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>2932</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2725</v>
       </c>
       <c r="D6" s="12" t="s">
+        <v>2910</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>2911</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>2912</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>2709</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>2932</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>2933</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>2934</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="12" t="s">
+        <v>2915</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>2916</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>2917</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>2693</v>
       </c>
       <c r="D9" s="12" t="s">
+        <v>2934</v>
+      </c>
+      <c r="E9" s="18" t="s">
         <v>2935</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>2936</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>2936</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>2894</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>2937</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>2895</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="E10" s="18" t="s">
         <v>2938</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>2939</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>198</v>
@@ -65533,15 +65541,15 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>363</v>
@@ -65550,7 +65558,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
     </row>
   </sheetData>
@@ -65569,7 +65577,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="285" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B1" s="285"/>
       <c r="C1" s="285"/>
@@ -65579,7 +65587,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="286" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="B2" s="286"/>
       <c r="C2" s="286"/>
@@ -65592,19 +65600,19 @@
         <v>19</v>
       </c>
       <c r="B4" s="102" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C4" s="102" t="s">
         <v>2830</v>
       </c>
-      <c r="C4" s="102" t="s">
+      <c r="D4" s="102" t="s">
+        <v>2941</v>
+      </c>
+      <c r="E4" s="102" t="s">
         <v>2831</v>
       </c>
-      <c r="D4" s="102" t="s">
+      <c r="F4" s="102" t="s">
         <v>2942</v>
-      </c>
-      <c r="E4" s="102" t="s">
-        <v>2832</v>
-      </c>
-      <c r="F4" s="102" t="s">
-        <v>2943</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -67856,7 +67864,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="242" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="B105" s="243">
         <f>SUM(B5:B100)</f>
@@ -67907,7 +67915,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="287" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="B1" s="287"/>
       <c r="C1" s="287"/>
@@ -67919,20 +67927,20 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="130" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="288" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="B4" s="289"/>
       <c r="D4" s="288" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="E4" s="289"/>
       <c r="G4" s="288" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="H4" s="289"/>
     </row>
@@ -67956,28 +67964,28 @@
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="143" t="s">
+        <v>2948</v>
+      </c>
+      <c r="B7" s="143" t="s">
         <v>2949</v>
-      </c>
-      <c r="B7" s="143" t="s">
-        <v>2950</v>
       </c>
       <c r="C7" s="143" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="143" t="s">
+        <v>2950</v>
+      </c>
+      <c r="E7" s="143" t="s">
         <v>2951</v>
       </c>
-      <c r="E7" s="143" t="s">
-        <v>2952</v>
-      </c>
       <c r="F7" s="143" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
       <c r="G7" s="143" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="143" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -68340,26 +68348,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052D3A7BF04652843BCB50FE90745AA50" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ef6274641b2f7d621af528393bef14e5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe686eaa-0658-4f15-b230-9e46c4d089fd" xmlns:ns3="91ce1707-6d34-452b-b217-9734c03e6729" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fa87a3bcf42251a9fb9988d55372596" ns2:_="" ns3:_="">
     <xsd:import namespace="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
@@ -68560,10 +68548,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
+    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -68580,20 +68599,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
-    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4897" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E4F425A-E175-49FE-B536-057BED796534}"/>
+  <xr:revisionPtr revIDLastSave="4900" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19E94371-9B6D-47B8-9EDC-C12484E817E8}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6519" uniqueCount="2954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6521" uniqueCount="2955">
   <si>
     <t>ID</t>
   </si>
@@ -9030,6 +9030,9 @@
   </si>
   <si>
     <t>6 e 7/08/2026</t>
+  </si>
+  <si>
+    <t>6843/2026</t>
   </si>
 </sst>
 </file>
@@ -12974,7 +12977,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14942,14 +14945,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}" name="Tabela2" displayName="Tabela2" ref="B1:T684" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="B1:T684" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}">
@@ -15361,7 +15356,7 @@
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
       <c r="R2" s="23">
-        <f>SUM(O2:Q2)</f>
+        <f t="shared" ref="R2:R65" si="0">SUM(O2:Q2)</f>
         <v>20</v>
       </c>
       <c r="S2" s="22">
@@ -15412,7 +15407,7 @@
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25">
-        <f>SUM(O3:Q3)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S3" s="24">
@@ -15463,7 +15458,7 @@
       <c r="P4" s="23"/>
       <c r="Q4" s="23"/>
       <c r="R4" s="23">
-        <f>SUM(O4:Q4)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="S4" s="22">
@@ -15514,7 +15509,7 @@
       <c r="P5" s="25"/>
       <c r="Q5" s="25"/>
       <c r="R5" s="25">
-        <f>SUM(O5:Q5)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S5" s="24">
@@ -15565,7 +15560,7 @@
       <c r="P6" s="23"/>
       <c r="Q6" s="23"/>
       <c r="R6" s="23">
-        <f>SUM(O6:Q6)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="S6" s="22">
@@ -15616,7 +15611,7 @@
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
       <c r="R7" s="25">
-        <f>SUM(O7:Q7)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S7" s="24">
@@ -15665,7 +15660,7 @@
       <c r="P8" s="23"/>
       <c r="Q8" s="23"/>
       <c r="R8" s="23">
-        <f>SUM(O8:Q8)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="S8" s="22">
@@ -15716,7 +15711,7 @@
       </c>
       <c r="Q9" s="25"/>
       <c r="R9" s="25">
-        <f>SUM(O9:Q9)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="S9" s="24">
@@ -15767,7 +15762,7 @@
       </c>
       <c r="Q10" s="23"/>
       <c r="R10" s="23">
-        <f>SUM(O10:Q10)</f>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="S10" s="22">
@@ -15820,7 +15815,7 @@
       <c r="P11" s="25"/>
       <c r="Q11" s="25"/>
       <c r="R11" s="25">
-        <f>SUM(O11:Q11)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="S11" s="24">
@@ -15875,7 +15870,7 @@
       </c>
       <c r="Q12" s="23"/>
       <c r="R12" s="23">
-        <f>SUM(O12:Q12)</f>
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="S12" s="22">
@@ -15930,7 +15925,7 @@
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
       <c r="R13" s="25">
-        <f>SUM(O13:Q13)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="S13" s="24">
@@ -15985,7 +15980,7 @@
       </c>
       <c r="Q14" s="23"/>
       <c r="R14" s="23">
-        <f>SUM(O14:Q14)</f>
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
       <c r="S14" s="22">
@@ -16040,7 +16035,7 @@
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
       <c r="R15" s="25">
-        <f>SUM(O15:Q15)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="S15" s="24">
@@ -16097,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="23">
-        <f>SUM(O16:Q16)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S16" s="22">
@@ -16150,7 +16145,7 @@
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
       <c r="R17" s="25">
-        <f>SUM(O17:Q17)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S17" s="24">
@@ -16205,7 +16200,7 @@
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
       <c r="R18" s="23">
-        <f>SUM(O18:Q18)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S18" s="22">
@@ -16260,7 +16255,7 @@
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
       <c r="R19" s="25">
-        <f>SUM(O19:Q19)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="S19" s="24">
@@ -16315,7 +16310,7 @@
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
       <c r="R20" s="23">
-        <f>SUM(O20:Q20)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="S20" s="22">
@@ -16370,7 +16365,7 @@
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
       <c r="R21" s="25">
-        <f>SUM(O21:Q21)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="S21" s="24">
@@ -16425,7 +16420,7 @@
       </c>
       <c r="Q22" s="23"/>
       <c r="R22" s="23">
-        <f>SUM(O22:Q22)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="S22" s="22">
@@ -16480,7 +16475,7 @@
       <c r="P23" s="25"/>
       <c r="Q23" s="25"/>
       <c r="R23" s="25">
-        <f>SUM(O23:Q23)</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="S23" s="24">
@@ -16535,7 +16530,7 @@
       <c r="P24" s="23"/>
       <c r="Q24" s="23"/>
       <c r="R24" s="23">
-        <f>SUM(O24:Q24)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="S24" s="22">
@@ -16590,7 +16585,7 @@
       <c r="P25" s="25"/>
       <c r="Q25" s="25"/>
       <c r="R25" s="25">
-        <f>SUM(O25:Q25)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="S25" s="24">
@@ -16645,7 +16640,7 @@
       <c r="P26" s="23"/>
       <c r="Q26" s="23"/>
       <c r="R26" s="23">
-        <f>SUM(O26:Q26)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="S26" s="22">
@@ -16698,7 +16693,7 @@
       <c r="P27" s="25"/>
       <c r="Q27" s="25"/>
       <c r="R27" s="25">
-        <f>SUM(O27:Q27)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="S27" s="24"/>
@@ -16749,7 +16744,7 @@
         <v>46</v>
       </c>
       <c r="R28" s="23">
-        <f>SUM(O28:Q28)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="S28" s="22">
@@ -16804,7 +16799,7 @@
       <c r="P29" s="25"/>
       <c r="Q29" s="25"/>
       <c r="R29" s="25">
-        <f>SUM(O29:Q29)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="S29" s="24">
@@ -16859,7 +16854,7 @@
       </c>
       <c r="Q30" s="23"/>
       <c r="R30" s="23">
-        <f>SUM(O30:Q30)</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="S30" s="22">
@@ -16912,7 +16907,7 @@
       <c r="P31" s="25"/>
       <c r="Q31" s="25"/>
       <c r="R31" s="25">
-        <f>SUM(O31:Q31)</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="S31" s="24">
@@ -16965,7 +16960,7 @@
         <v>46</v>
       </c>
       <c r="R32" s="23">
-        <f>SUM(O32:Q32)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="S32" s="22">
@@ -17018,7 +17013,7 @@
       <c r="P33" s="25"/>
       <c r="Q33" s="25"/>
       <c r="R33" s="25">
-        <f>SUM(O33:Q33)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="S33" s="24">
@@ -17069,7 +17064,7 @@
       <c r="P34" s="23"/>
       <c r="Q34" s="23"/>
       <c r="R34" s="23">
-        <f>SUM(O34:Q34)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="S34" s="22">
@@ -17120,7 +17115,7 @@
       <c r="P35" s="25"/>
       <c r="Q35" s="25"/>
       <c r="R35" s="25">
-        <f>SUM(O35:Q35)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="S35" s="24">
@@ -17175,7 +17170,7 @@
       </c>
       <c r="Q36" s="23"/>
       <c r="R36" s="23">
-        <f>SUM(O36:Q36)</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="S36" s="22">
@@ -17230,7 +17225,7 @@
       </c>
       <c r="Q37" s="25"/>
       <c r="R37" s="25">
-        <f>SUM(O37:Q37)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="S37" s="24">
@@ -17285,7 +17280,7 @@
       <c r="P38" s="23"/>
       <c r="Q38" s="23"/>
       <c r="R38" s="23">
-        <f>SUM(O38:Q38)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="S38" s="22">
@@ -17340,7 +17335,7 @@
       </c>
       <c r="Q39" s="25"/>
       <c r="R39" s="25">
-        <f>SUM(O39:Q39)</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="S39" s="24">
@@ -17395,7 +17390,7 @@
         <v>45</v>
       </c>
       <c r="R40" s="23">
-        <f>SUM(O40:Q40)</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="S40" s="22">
@@ -17450,7 +17445,7 @@
       <c r="P41" s="25"/>
       <c r="Q41" s="25"/>
       <c r="R41" s="25">
-        <f>SUM(O41:Q41)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="S41" s="24">
@@ -17505,7 +17500,7 @@
         <v>21</v>
       </c>
       <c r="R42" s="23">
-        <f>SUM(O42:Q42)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="S42" s="22">
@@ -17560,7 +17555,7 @@
       <c r="P43" s="25"/>
       <c r="Q43" s="25"/>
       <c r="R43" s="25">
-        <f>SUM(O43:Q43)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="S43" s="24">
@@ -17615,7 +17610,7 @@
       </c>
       <c r="Q44" s="23"/>
       <c r="R44" s="23">
-        <f>SUM(O44:Q44)</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="S44" s="22">
@@ -17670,7 +17665,7 @@
       <c r="P45" s="25"/>
       <c r="Q45" s="25"/>
       <c r="R45" s="25">
-        <f>SUM(O45:Q45)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="S45" s="24">
@@ -17725,7 +17720,7 @@
       <c r="P46" s="23"/>
       <c r="Q46" s="23"/>
       <c r="R46" s="23">
-        <f>SUM(O46:Q46)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="S46" s="22">
@@ -17782,7 +17777,7 @@
       </c>
       <c r="Q47" s="25"/>
       <c r="R47" s="25">
-        <f>SUM(O47:Q47)</f>
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="S47" s="24">
@@ -17841,7 +17836,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="23">
-        <f>SUM(O48:Q48)</f>
+        <f t="shared" si="0"/>
         <v>329</v>
       </c>
       <c r="S48" s="22">
@@ -17896,7 +17891,7 @@
       <c r="P49" s="25"/>
       <c r="Q49" s="25"/>
       <c r="R49" s="25">
-        <f>SUM(O49:Q49)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="S49" s="24">
@@ -17951,7 +17946,7 @@
       <c r="P50" s="23"/>
       <c r="Q50" s="23"/>
       <c r="R50" s="23">
-        <f>SUM(O50:Q50)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="S50" s="22">
@@ -18006,7 +18001,7 @@
       </c>
       <c r="Q51" s="25"/>
       <c r="R51" s="25">
-        <f>SUM(O51:Q51)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="S51" s="24">
@@ -18061,7 +18056,7 @@
       </c>
       <c r="Q52" s="23"/>
       <c r="R52" s="23">
-        <f>SUM(O52:Q52)</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="S52" s="22">
@@ -18116,7 +18111,7 @@
       <c r="P53" s="25"/>
       <c r="Q53" s="25"/>
       <c r="R53" s="25">
-        <f>SUM(O53:Q53)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="S53" s="24">
@@ -18171,7 +18166,7 @@
       <c r="P54" s="23"/>
       <c r="Q54" s="23"/>
       <c r="R54" s="23">
-        <f>SUM(O54:Q54)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="S54" s="22">
@@ -18226,7 +18221,7 @@
       <c r="P55" s="25"/>
       <c r="Q55" s="25"/>
       <c r="R55" s="25">
-        <f>SUM(O55:Q55)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S55" s="24">
@@ -18281,7 +18276,7 @@
       </c>
       <c r="Q56" s="23"/>
       <c r="R56" s="23">
-        <f>SUM(O56:Q56)</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="S56" s="22">
@@ -18336,7 +18331,7 @@
       <c r="P57" s="25"/>
       <c r="Q57" s="25"/>
       <c r="R57" s="25">
-        <f>SUM(O57:Q57)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="S57" s="24">
@@ -18391,7 +18386,7 @@
       </c>
       <c r="Q58" s="23"/>
       <c r="R58" s="23">
-        <f>SUM(O58:Q58)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="S58" s="22">
@@ -18446,7 +18441,7 @@
       <c r="P59" s="25"/>
       <c r="Q59" s="25"/>
       <c r="R59" s="25">
-        <f>SUM(O59:Q59)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="S59" s="24">
@@ -18501,7 +18496,7 @@
       </c>
       <c r="Q60" s="23"/>
       <c r="R60" s="23">
-        <f>SUM(O60:Q60)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="S60" s="22">
@@ -18556,7 +18551,7 @@
       </c>
       <c r="Q61" s="25"/>
       <c r="R61" s="25">
-        <f>SUM(O61:Q61)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="S61" s="24">
@@ -18611,7 +18606,7 @@
       </c>
       <c r="Q62" s="23"/>
       <c r="R62" s="23">
-        <f>SUM(O62:Q62)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="S62" s="22">
@@ -18666,7 +18661,7 @@
       <c r="P63" s="25"/>
       <c r="Q63" s="25"/>
       <c r="R63" s="25">
-        <f>SUM(O63:Q63)</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="S63" s="24">
@@ -18721,7 +18716,7 @@
       <c r="P64" s="23"/>
       <c r="Q64" s="23"/>
       <c r="R64" s="23">
-        <f>SUM(O64:Q64)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="S64" s="22">
@@ -18776,7 +18771,7 @@
       </c>
       <c r="Q65" s="25"/>
       <c r="R65" s="25">
-        <f>SUM(O65:Q65)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="S65" s="24">
@@ -18831,7 +18826,7 @@
       <c r="P66" s="23"/>
       <c r="Q66" s="23"/>
       <c r="R66" s="23">
-        <f>SUM(O66:Q66)</f>
+        <f t="shared" ref="R66:R129" si="1">SUM(O66:Q66)</f>
         <v>20</v>
       </c>
       <c r="S66" s="22">
@@ -18886,7 +18881,7 @@
       </c>
       <c r="Q67" s="25"/>
       <c r="R67" s="25">
-        <f>SUM(O67:Q67)</f>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="S67" s="24">
@@ -18941,7 +18936,7 @@
       <c r="P68" s="23"/>
       <c r="Q68" s="23"/>
       <c r="R68" s="23">
-        <f>SUM(O68:Q68)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="S68" s="22">
@@ -18996,7 +18991,7 @@
       <c r="P69" s="25"/>
       <c r="Q69" s="25"/>
       <c r="R69" s="25">
-        <f>SUM(O69:Q69)</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="S69" s="24">
@@ -19051,7 +19046,7 @@
       </c>
       <c r="Q70" s="23"/>
       <c r="R70" s="23">
-        <f>SUM(O70:Q70)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="S70" s="22">
@@ -19106,7 +19101,7 @@
       <c r="P71" s="25"/>
       <c r="Q71" s="25"/>
       <c r="R71" s="25">
-        <f>SUM(O71:Q71)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="S71" s="24">
@@ -19161,7 +19156,7 @@
       <c r="P72" s="23"/>
       <c r="Q72" s="23"/>
       <c r="R72" s="23">
-        <f>SUM(O72:Q72)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="S72" s="22">
@@ -19216,7 +19211,7 @@
       <c r="P73" s="25"/>
       <c r="Q73" s="25"/>
       <c r="R73" s="25">
-        <f>SUM(O73:Q73)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S73" s="24">
@@ -19271,7 +19266,7 @@
       <c r="P74" s="23"/>
       <c r="Q74" s="23"/>
       <c r="R74" s="23">
-        <f>SUM(O74:Q74)</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="S74" s="22">
@@ -19326,7 +19321,7 @@
         <v>37</v>
       </c>
       <c r="R75" s="25">
-        <f>SUM(O75:Q75)</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="S75" s="24">
@@ -19381,7 +19376,7 @@
       </c>
       <c r="Q76" s="23"/>
       <c r="R76" s="23">
-        <f>SUM(O76:Q76)</f>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="S76" s="22">
@@ -19436,7 +19431,7 @@
       <c r="P77" s="25"/>
       <c r="Q77" s="25"/>
       <c r="R77" s="25">
-        <f>SUM(O77:Q77)</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="S77" s="24">
@@ -19491,7 +19486,7 @@
       <c r="P78" s="23"/>
       <c r="Q78" s="23"/>
       <c r="R78" s="23">
-        <f>SUM(O78:Q78)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S78" s="22">
@@ -19546,7 +19541,7 @@
       </c>
       <c r="Q79" s="25"/>
       <c r="R79" s="25">
-        <f>SUM(O79:Q79)</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="S79" s="24">
@@ -19601,7 +19596,7 @@
       <c r="P80" s="23"/>
       <c r="Q80" s="23"/>
       <c r="R80" s="23">
-        <f>SUM(O80:Q80)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S80" s="22">
@@ -19656,7 +19651,7 @@
       <c r="P81" s="25"/>
       <c r="Q81" s="25"/>
       <c r="R81" s="25">
-        <f>SUM(O81:Q81)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="S81" s="24">
@@ -19711,7 +19706,7 @@
       <c r="P82" s="23"/>
       <c r="Q82" s="23"/>
       <c r="R82" s="23">
-        <f>SUM(O82:Q82)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="S82" s="22">
@@ -19766,7 +19761,7 @@
       <c r="P83" s="25"/>
       <c r="Q83" s="25"/>
       <c r="R83" s="25">
-        <f>SUM(O83:Q83)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="S83" s="24">
@@ -19821,7 +19816,7 @@
       </c>
       <c r="Q84" s="23"/>
       <c r="R84" s="23">
-        <f>SUM(O84:Q84)</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="S84" s="22">
@@ -19876,7 +19871,7 @@
         <v>49</v>
       </c>
       <c r="R85" s="25">
-        <f>SUM(O85:Q85)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="S85" s="24">
@@ -19931,7 +19926,7 @@
       </c>
       <c r="Q86" s="23"/>
       <c r="R86" s="23">
-        <f>SUM(O86:Q86)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="S86" s="22">
@@ -19986,7 +19981,7 @@
       <c r="P87" s="25"/>
       <c r="Q87" s="25"/>
       <c r="R87" s="25">
-        <f>SUM(O87:Q87)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S87" s="24">
@@ -20045,7 +20040,7 @@
         <v>0</v>
       </c>
       <c r="R88" s="23">
-        <f>SUM(O88:Q88)</f>
+        <f t="shared" si="1"/>
         <v>312</v>
       </c>
       <c r="S88" s="22">
@@ -20100,7 +20095,7 @@
       </c>
       <c r="Q89" s="25"/>
       <c r="R89" s="25">
-        <f>SUM(O89:Q89)</f>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="S89" s="24">
@@ -20155,7 +20150,7 @@
       </c>
       <c r="Q90" s="23"/>
       <c r="R90" s="23">
-        <f>SUM(O90:Q90)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="S90" s="22">
@@ -20210,7 +20205,7 @@
       <c r="P91" s="25"/>
       <c r="Q91" s="25"/>
       <c r="R91" s="25">
-        <f>SUM(O91:Q91)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S91" s="24">
@@ -20265,7 +20260,7 @@
       <c r="P92" s="23"/>
       <c r="Q92" s="23"/>
       <c r="R92" s="23">
-        <f>SUM(O92:Q92)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S92" s="22">
@@ -20320,7 +20315,7 @@
       </c>
       <c r="Q93" s="25"/>
       <c r="R93" s="25">
-        <f>SUM(O93:Q93)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="S93" s="24">
@@ -20375,7 +20370,7 @@
       </c>
       <c r="Q94" s="23"/>
       <c r="R94" s="23">
-        <f>SUM(O94:Q94)</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="S94" s="22">
@@ -20430,7 +20425,7 @@
         <v>96</v>
       </c>
       <c r="R95" s="25">
-        <f>SUM(O95:Q95)</f>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="S95" s="24">
@@ -20485,7 +20480,7 @@
       <c r="P96" s="23"/>
       <c r="Q96" s="23"/>
       <c r="R96" s="23">
-        <f>SUM(O96:Q96)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S96" s="22">
@@ -20540,7 +20535,7 @@
       </c>
       <c r="Q97" s="25"/>
       <c r="R97" s="25">
-        <f>SUM(O97:Q97)</f>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="S97" s="24">
@@ -20595,7 +20590,7 @@
       <c r="P98" s="23"/>
       <c r="Q98" s="23"/>
       <c r="R98" s="23">
-        <f>SUM(O98:Q98)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S98" s="22">
@@ -20650,7 +20645,7 @@
       <c r="P99" s="25"/>
       <c r="Q99" s="25"/>
       <c r="R99" s="25">
-        <f>SUM(O99:Q99)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S99" s="24">
@@ -20705,7 +20700,7 @@
       <c r="P100" s="23"/>
       <c r="Q100" s="23"/>
       <c r="R100" s="23">
-        <f>SUM(O100:Q100)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="S100" s="22">
@@ -20760,7 +20755,7 @@
       </c>
       <c r="Q101" s="25"/>
       <c r="R101" s="25">
-        <f>SUM(O101:Q101)</f>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="S101" s="24">
@@ -20815,7 +20810,7 @@
       <c r="P102" s="23"/>
       <c r="Q102" s="23"/>
       <c r="R102" s="23">
-        <f>SUM(O102:Q102)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S102" s="22">
@@ -20870,7 +20865,7 @@
       <c r="P103" s="25"/>
       <c r="Q103" s="25"/>
       <c r="R103" s="25">
-        <f>SUM(O103:Q103)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="S103" s="24">
@@ -20925,7 +20920,7 @@
       </c>
       <c r="Q104" s="23"/>
       <c r="R104" s="23">
-        <f>SUM(O104:Q104)</f>
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
       <c r="S104" s="22">
@@ -20980,7 +20975,7 @@
       <c r="P105" s="25"/>
       <c r="Q105" s="25"/>
       <c r="R105" s="25">
-        <f>SUM(O105:Q105)</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="S105" s="24">
@@ -21035,7 +21030,7 @@
       </c>
       <c r="Q106" s="23"/>
       <c r="R106" s="23">
-        <f>SUM(O106:Q106)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="S106" s="22">
@@ -21090,7 +21085,7 @@
       <c r="P107" s="25"/>
       <c r="Q107" s="25"/>
       <c r="R107" s="25">
-        <f>SUM(O107:Q107)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S107" s="24">
@@ -21149,7 +21144,7 @@
         <v>0</v>
       </c>
       <c r="R108" s="23">
-        <f>SUM(O108:Q108)</f>
+        <f t="shared" si="1"/>
         <v>353</v>
       </c>
       <c r="S108" s="22">
@@ -21204,7 +21199,7 @@
       <c r="P109" s="25"/>
       <c r="Q109" s="25"/>
       <c r="R109" s="25">
-        <f>SUM(O109:Q109)</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="S109" s="24">
@@ -21259,7 +21254,7 @@
       <c r="P110" s="23"/>
       <c r="Q110" s="23"/>
       <c r="R110" s="23">
-        <f>SUM(O110:Q110)</f>
+        <f t="shared" si="1"/>
         <v>215</v>
       </c>
       <c r="S110" s="22">
@@ -21314,7 +21309,7 @@
       <c r="P111" s="25"/>
       <c r="Q111" s="25"/>
       <c r="R111" s="25">
-        <f>SUM(O111:Q111)</f>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="S111" s="24">
@@ -21369,7 +21364,7 @@
       <c r="P112" s="23"/>
       <c r="Q112" s="23"/>
       <c r="R112" s="23">
-        <f>SUM(O112:Q112)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="S112" s="22">
@@ -21424,7 +21419,7 @@
       <c r="P113" s="25"/>
       <c r="Q113" s="25"/>
       <c r="R113" s="25">
-        <f>SUM(O113:Q113)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="S113" s="24">
@@ -21479,7 +21474,7 @@
       <c r="P114" s="23"/>
       <c r="Q114" s="23"/>
       <c r="R114" s="23">
-        <f>SUM(O114:Q114)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="S114" s="22">
@@ -21538,7 +21533,7 @@
         <v>0</v>
       </c>
       <c r="R115" s="25">
-        <f>SUM(O115:Q115)</f>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="S115" s="24">
@@ -21599,7 +21594,7 @@
       </c>
       <c r="Q116" s="23"/>
       <c r="R116" s="23">
-        <f>SUM(O116:Q116)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S116" s="22">
@@ -21660,7 +21655,7 @@
       </c>
       <c r="Q117" s="25"/>
       <c r="R117" s="25">
-        <f>SUM(O117:Q117)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="S117" s="24">
@@ -21721,7 +21716,7 @@
       </c>
       <c r="Q118" s="23"/>
       <c r="R118" s="23">
-        <f>SUM(O118:Q118)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="S118" s="22">
@@ -21782,7 +21777,7 @@
       </c>
       <c r="Q119" s="25"/>
       <c r="R119" s="25">
-        <f>SUM(O119:Q119)</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="S119" s="24">
@@ -21843,7 +21838,7 @@
       </c>
       <c r="Q120" s="23"/>
       <c r="R120" s="23">
-        <f>SUM(O120:Q120)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="S120" s="22">
@@ -21904,7 +21899,7 @@
       </c>
       <c r="Q121" s="25"/>
       <c r="R121" s="25">
-        <f>SUM(O121:Q121)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="S121" s="24">
@@ -21965,7 +21960,7 @@
       </c>
       <c r="Q122" s="23"/>
       <c r="R122" s="23">
-        <f>SUM(O122:Q122)</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="S122" s="22">
@@ -22026,7 +22021,7 @@
       </c>
       <c r="Q123" s="25"/>
       <c r="R123" s="25">
-        <f>SUM(O123:Q123)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="S123" s="24">
@@ -22087,7 +22082,7 @@
       </c>
       <c r="Q124" s="23"/>
       <c r="R124" s="23">
-        <f>SUM(O124:Q124)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="S124" s="22">
@@ -22148,7 +22143,7 @@
       </c>
       <c r="Q125" s="25"/>
       <c r="R125" s="25">
-        <f>SUM(O125:Q125)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S125" s="24">
@@ -22209,7 +22204,7 @@
       </c>
       <c r="Q126" s="23"/>
       <c r="R126" s="23">
-        <f>SUM(O126:Q126)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="S126" s="22">
@@ -22270,7 +22265,7 @@
       </c>
       <c r="Q127" s="25"/>
       <c r="R127" s="25">
-        <f>SUM(O127:Q127)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S127" s="24">
@@ -22331,7 +22326,7 @@
       </c>
       <c r="Q128" s="23"/>
       <c r="R128" s="23">
-        <f>SUM(O128:Q128)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="S128" s="22">
@@ -22392,7 +22387,7 @@
       </c>
       <c r="Q129" s="25"/>
       <c r="R129" s="25">
-        <f>SUM(O129:Q129)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="S129" s="24">
@@ -22453,7 +22448,7 @@
       </c>
       <c r="Q130" s="23"/>
       <c r="R130" s="23">
-        <f>SUM(O130:Q130)</f>
+        <f t="shared" ref="R130:R193" si="2">SUM(O130:Q130)</f>
         <v>25</v>
       </c>
       <c r="S130" s="22">
@@ -22514,7 +22509,7 @@
       </c>
       <c r="Q131" s="25"/>
       <c r="R131" s="25">
-        <f>SUM(O131:Q131)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="S131" s="24">
@@ -22575,7 +22570,7 @@
       </c>
       <c r="Q132" s="23"/>
       <c r="R132" s="23">
-        <f>SUM(O132:Q132)</f>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="S132" s="22">
@@ -22636,7 +22631,7 @@
       </c>
       <c r="Q133" s="25"/>
       <c r="R133" s="25">
-        <f>SUM(O133:Q133)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="S133" s="24">
@@ -22697,7 +22692,7 @@
       </c>
       <c r="Q134" s="23"/>
       <c r="R134" s="23">
-        <f>SUM(O134:Q134)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="S134" s="22">
@@ -22758,7 +22753,7 @@
       </c>
       <c r="Q135" s="25"/>
       <c r="R135" s="25">
-        <f>SUM(O135:Q135)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="S135" s="24">
@@ -22819,7 +22814,7 @@
       </c>
       <c r="Q136" s="23"/>
       <c r="R136" s="23">
-        <f>SUM(O136:Q136)</f>
+        <f t="shared" si="2"/>
         <v>182</v>
       </c>
       <c r="S136" s="22">
@@ -22880,7 +22875,7 @@
       </c>
       <c r="Q137" s="25"/>
       <c r="R137" s="25">
-        <f>SUM(O137:Q137)</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="S137" s="24">
@@ -22943,7 +22938,7 @@
         <v>0</v>
       </c>
       <c r="R138" s="23">
-        <f>SUM(O138:Q138)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="S138" s="22">
@@ -23004,7 +22999,7 @@
       </c>
       <c r="Q139" s="25"/>
       <c r="R139" s="25">
-        <f>SUM(O139:Q139)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="S139" s="24">
@@ -23065,7 +23060,7 @@
       </c>
       <c r="Q140" s="23"/>
       <c r="R140" s="23">
-        <f>SUM(O140:Q140)</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="S140" s="22">
@@ -23128,7 +23123,7 @@
         <v>0</v>
       </c>
       <c r="R141" s="25">
-        <f>SUM(O141:Q141)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="S141" s="24">
@@ -23189,7 +23184,7 @@
       </c>
       <c r="Q142" s="23"/>
       <c r="R142" s="23">
-        <f>SUM(O142:Q142)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="S142" s="22">
@@ -23250,7 +23245,7 @@
       </c>
       <c r="Q143" s="25"/>
       <c r="R143" s="25">
-        <f>SUM(O143:Q143)</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="S143" s="24">
@@ -23311,7 +23306,7 @@
       </c>
       <c r="Q144" s="23"/>
       <c r="R144" s="23">
-        <f>SUM(O144:Q144)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="S144" s="22">
@@ -23374,7 +23369,7 @@
         <v>0</v>
       </c>
       <c r="R145" s="25">
-        <f>SUM(O145:Q145)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="S145" s="24">
@@ -23435,7 +23430,7 @@
       </c>
       <c r="Q146" s="23"/>
       <c r="R146" s="23">
-        <f>SUM(O146:Q146)</f>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="S146" s="22">
@@ -23496,7 +23491,7 @@
         <v>0</v>
       </c>
       <c r="R147" s="25">
-        <f>SUM(O147:Q147)</f>
+        <f t="shared" si="2"/>
         <v>54</v>
       </c>
       <c r="S147" s="24">
@@ -23557,7 +23552,7 @@
       </c>
       <c r="Q148" s="23"/>
       <c r="R148" s="23">
-        <f>SUM(O148:Q148)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="S148" s="22">
@@ -23618,7 +23613,7 @@
       </c>
       <c r="Q149" s="25"/>
       <c r="R149" s="25">
-        <f>SUM(O149:Q149)</f>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="S149" s="24">
@@ -23679,7 +23674,7 @@
       </c>
       <c r="Q150" s="23"/>
       <c r="R150" s="23">
-        <f>SUM(O150:Q150)</f>
+        <f t="shared" si="2"/>
         <v>62</v>
       </c>
       <c r="S150" s="22">
@@ -23740,7 +23735,7 @@
       </c>
       <c r="Q151" s="25"/>
       <c r="R151" s="25">
-        <f>SUM(O151:Q151)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="S151" s="24">
@@ -23801,7 +23796,7 @@
       </c>
       <c r="Q152" s="23"/>
       <c r="R152" s="23">
-        <f>SUM(O152:Q152)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="S152" s="22">
@@ -23862,7 +23857,7 @@
       </c>
       <c r="Q153" s="25"/>
       <c r="R153" s="25">
-        <f>SUM(O153:Q153)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="S153" s="24">
@@ -23925,7 +23920,7 @@
         <v>0</v>
       </c>
       <c r="R154" s="23">
-        <f>SUM(O154:Q154)</f>
+        <f t="shared" si="2"/>
         <v>74</v>
       </c>
       <c r="S154" s="22">
@@ -23986,7 +23981,7 @@
       </c>
       <c r="Q155" s="25"/>
       <c r="R155" s="25">
-        <f>SUM(O155:Q155)</f>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="S155" s="24">
@@ -24049,7 +24044,7 @@
         <v>0</v>
       </c>
       <c r="R156" s="23">
-        <f>SUM(O156:Q156)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="S156" s="22">
@@ -24112,7 +24107,7 @@
         <v>0</v>
       </c>
       <c r="R157" s="25">
-        <f>SUM(O157:Q157)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="S157" s="24">
@@ -24175,7 +24170,7 @@
         <v>0</v>
       </c>
       <c r="R158" s="23">
-        <f>SUM(O158:Q158)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="S158" s="22">
@@ -24238,7 +24233,7 @@
         <v>78</v>
       </c>
       <c r="R159" s="25">
-        <f>SUM(O159:Q159)</f>
+        <f t="shared" si="2"/>
         <v>117</v>
       </c>
       <c r="S159" s="24">
@@ -24301,7 +24296,7 @@
         <v>0</v>
       </c>
       <c r="R160" s="23">
-        <f>SUM(O160:Q160)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="S160" s="22">
@@ -24365,7 +24360,7 @@
         <v>0</v>
       </c>
       <c r="R161" s="25">
-        <f>SUM(O161:Q161)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="S161" s="24">
@@ -24428,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="R162" s="23">
-        <f>SUM(O162:Q162)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="S162" s="22">
@@ -24491,7 +24486,7 @@
         <v>0</v>
       </c>
       <c r="R163" s="25">
-        <f>SUM(O163:Q163)</f>
+        <f t="shared" si="2"/>
         <v>59</v>
       </c>
       <c r="S163" s="24">
@@ -24554,7 +24549,7 @@
         <v>0</v>
       </c>
       <c r="R164" s="23">
-        <f>SUM(O164:Q164)</f>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="S164" s="22">
@@ -24617,7 +24612,7 @@
         <v>0</v>
       </c>
       <c r="R165" s="25">
-        <f>SUM(O165:Q165)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="S165" s="24">
@@ -24680,7 +24675,7 @@
         <v>0</v>
       </c>
       <c r="R166" s="23">
-        <f>SUM(O166:Q166)</f>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="S166" s="22">
@@ -24743,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="R167" s="25">
-        <f>SUM(O167:Q167)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="S167" s="24">
@@ -24806,7 +24801,7 @@
         <v>0</v>
       </c>
       <c r="R168" s="23">
-        <f>SUM(O168:Q168)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="S168" s="22">
@@ -24869,7 +24864,7 @@
         <v>0</v>
       </c>
       <c r="R169" s="25">
-        <f>SUM(O169:Q169)</f>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="S169" s="24">
@@ -24932,7 +24927,7 @@
         <v>0</v>
       </c>
       <c r="R170" s="23">
-        <f>SUM(O170:Q170)</f>
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="S170" s="22">
@@ -24995,7 +24990,7 @@
         <v>0</v>
       </c>
       <c r="R171" s="25">
-        <f>SUM(O171:Q171)</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="S171" s="24">
@@ -25058,7 +25053,7 @@
         <v>0</v>
       </c>
       <c r="R172" s="23">
-        <f>SUM(O172:Q172)</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="S172" s="22">
@@ -25121,7 +25116,7 @@
         <v>0</v>
       </c>
       <c r="R173" s="25">
-        <f>SUM(O173:Q173)</f>
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
       <c r="S173" s="24">
@@ -25184,7 +25179,7 @@
         <v>0</v>
       </c>
       <c r="R174" s="23">
-        <f>SUM(O174:Q174)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="S174" s="22">
@@ -25247,7 +25242,7 @@
         <v>0</v>
       </c>
       <c r="R175" s="25">
-        <f>SUM(O175:Q175)</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="S175" s="24">
@@ -25310,7 +25305,7 @@
         <v>97</v>
       </c>
       <c r="R176" s="23">
-        <f>SUM(O176:Q176)</f>
+        <f t="shared" si="2"/>
         <v>119</v>
       </c>
       <c r="S176" s="22">
@@ -25374,7 +25369,7 @@
         <v>0</v>
       </c>
       <c r="R177" s="25">
-        <f>SUM(O177:Q177)</f>
+        <f t="shared" si="2"/>
         <v>122</v>
       </c>
       <c r="S177" s="24">
@@ -25438,7 +25433,7 @@
         <v>0</v>
       </c>
       <c r="R178" s="23">
-        <f>SUM(O178:Q178)</f>
+        <f t="shared" si="2"/>
         <v>116</v>
       </c>
       <c r="S178" s="22">
@@ -25502,7 +25497,7 @@
         <v>0</v>
       </c>
       <c r="R179" s="25">
-        <f>SUM(O179:Q179)</f>
+        <f t="shared" si="2"/>
         <v>83</v>
       </c>
       <c r="S179" s="24">
@@ -25565,7 +25560,7 @@
         <v>0</v>
       </c>
       <c r="R180" s="23">
-        <f>SUM(O180:Q180)</f>
+        <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="S180" s="22">
@@ -25628,7 +25623,7 @@
         <v>0</v>
       </c>
       <c r="R181" s="25">
-        <f>SUM(O181:Q181)</f>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="S181" s="24">
@@ -25691,7 +25686,7 @@
         <v>0</v>
       </c>
       <c r="R182" s="23">
-        <f>SUM(O182:Q182)</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="S182" s="22">
@@ -25754,7 +25749,7 @@
         <v>73</v>
       </c>
       <c r="R183" s="25">
-        <f>SUM(O183:Q183)</f>
+        <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="S183" s="24">
@@ -25817,7 +25812,7 @@
         <v>0</v>
       </c>
       <c r="R184" s="23">
-        <f>SUM(O184:Q184)</f>
+        <f t="shared" si="2"/>
         <v>94</v>
       </c>
       <c r="S184" s="22">
@@ -25880,7 +25875,7 @@
         <v>0</v>
       </c>
       <c r="R185" s="25">
-        <f>SUM(O185:Q185)</f>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="S185" s="24">
@@ -25943,7 +25938,7 @@
         <v>0</v>
       </c>
       <c r="R186" s="23">
-        <f>SUM(O186:Q186)</f>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="S186" s="22">
@@ -26006,7 +26001,7 @@
         <v>0</v>
       </c>
       <c r="R187" s="25">
-        <f>SUM(O187:Q187)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="S187" s="24">
@@ -26070,7 +26065,7 @@
         <v>0</v>
       </c>
       <c r="R188" s="23">
-        <f>SUM(O188:Q188)</f>
+        <f t="shared" si="2"/>
         <v>590</v>
       </c>
       <c r="S188" s="22">
@@ -26134,7 +26129,7 @@
         <v>0</v>
       </c>
       <c r="R189" s="25">
-        <f>SUM(O189:Q189)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="S189" s="24">
@@ -26197,7 +26192,7 @@
         <v>0</v>
       </c>
       <c r="R190" s="23">
-        <f>SUM(O190:Q190)</f>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="S190" s="22">
@@ -26261,7 +26256,7 @@
         <v>36</v>
       </c>
       <c r="R191" s="25">
-        <f>SUM(O191:Q191)</f>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="S191" s="24">
@@ -26324,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="R192" s="23">
-        <f>SUM(O192:Q192)</f>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="S192" s="22">
@@ -26387,7 +26382,7 @@
         <v>0</v>
       </c>
       <c r="R193" s="25">
-        <f>SUM(O193:Q193)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="S193" s="24">
@@ -26450,7 +26445,7 @@
         <v>0</v>
       </c>
       <c r="R194" s="23">
-        <f>SUM(O194:Q194)</f>
+        <f t="shared" ref="R194:R257" si="3">SUM(O194:Q194)</f>
         <v>20</v>
       </c>
       <c r="S194" s="22">
@@ -26513,7 +26508,7 @@
         <v>0</v>
       </c>
       <c r="R195" s="25">
-        <f>SUM(O195:Q195)</f>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="S195" s="24">
@@ -26576,7 +26571,7 @@
         <v>0</v>
       </c>
       <c r="R196" s="23">
-        <f>SUM(O196:Q196)</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="S196" s="22">
@@ -26639,7 +26634,7 @@
         <v>0</v>
       </c>
       <c r="R197" s="25">
-        <f>SUM(O197:Q197)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S197" s="24">
@@ -26702,7 +26697,7 @@
         <v>0</v>
       </c>
       <c r="R198" s="23">
-        <f>SUM(O198:Q198)</f>
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="S198" s="22">
@@ -26765,7 +26760,7 @@
         <v>0</v>
       </c>
       <c r="R199" s="25">
-        <f>SUM(O199:Q199)</f>
+        <f t="shared" si="3"/>
         <v>98</v>
       </c>
       <c r="S199" s="24">
@@ -26828,7 +26823,7 @@
         <v>44</v>
       </c>
       <c r="R200" s="23">
-        <f>SUM(O200:Q200)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="S200" s="22">
@@ -26891,7 +26886,7 @@
         <v>0</v>
       </c>
       <c r="R201" s="25">
-        <f>SUM(O201:Q201)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S201" s="24">
@@ -26954,7 +26949,7 @@
         <v>0</v>
       </c>
       <c r="R202" s="23">
-        <f>SUM(O202:Q202)</f>
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
       <c r="S202" s="22">
@@ -27017,7 +27012,7 @@
         <v>0</v>
       </c>
       <c r="R203" s="25">
-        <f>SUM(O203:Q203)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="S203" s="24">
@@ -27080,7 +27075,7 @@
         <v>59</v>
       </c>
       <c r="R204" s="23">
-        <f>SUM(O204:Q204)</f>
+        <f t="shared" si="3"/>
         <v>59</v>
       </c>
       <c r="S204" s="22">
@@ -27143,7 +27138,7 @@
         <v>0</v>
       </c>
       <c r="R205" s="25">
-        <f>SUM(O205:Q205)</f>
+        <f t="shared" si="3"/>
         <v>76</v>
       </c>
       <c r="S205" s="24">
@@ -27206,7 +27201,7 @@
         <v>0</v>
       </c>
       <c r="R206" s="23">
-        <f>SUM(O206:Q206)</f>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
       <c r="S206" s="22">
@@ -27269,7 +27264,7 @@
         <v>0</v>
       </c>
       <c r="R207" s="25">
-        <f>SUM(O207:Q207)</f>
+        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="S207" s="24">
@@ -27332,7 +27327,7 @@
         <v>37</v>
       </c>
       <c r="R208" s="23">
-        <f>SUM(O208:Q208)</f>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="S208" s="22">
@@ -27395,7 +27390,7 @@
         <v>0</v>
       </c>
       <c r="R209" s="25">
-        <f>SUM(O209:Q209)</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S209" s="24">
@@ -27458,7 +27453,7 @@
         <v>0</v>
       </c>
       <c r="R210" s="23">
-        <f>SUM(O210:Q210)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S210" s="22">
@@ -27521,7 +27516,7 @@
         <v>0</v>
       </c>
       <c r="R211" s="25">
-        <f>SUM(O211:Q211)</f>
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
       <c r="S211" s="24">
@@ -27584,7 +27579,7 @@
         <v>0</v>
       </c>
       <c r="R212" s="23">
-        <f>SUM(O212:Q212)</f>
+        <f t="shared" si="3"/>
         <v>105</v>
       </c>
       <c r="S212" s="22">
@@ -27647,7 +27642,7 @@
         <v>147</v>
       </c>
       <c r="R213" s="25">
-        <f>SUM(O213:Q213)</f>
+        <f t="shared" si="3"/>
         <v>635</v>
       </c>
       <c r="S213" s="24">
@@ -27710,7 +27705,7 @@
         <v>0</v>
       </c>
       <c r="R214" s="23">
-        <f>SUM(O214:Q214)</f>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="S214" s="22">
@@ -27773,7 +27768,7 @@
         <v>0</v>
       </c>
       <c r="R215" s="25">
-        <f>SUM(O215:Q215)</f>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="S215" s="24">
@@ -27836,7 +27831,7 @@
         <v>0</v>
       </c>
       <c r="R216" s="23">
-        <f>SUM(O216:Q216)</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="S216" s="22">
@@ -27899,7 +27894,7 @@
         <v>0</v>
       </c>
       <c r="R217" s="25">
-        <f>SUM(O217:Q217)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="S217" s="24">
@@ -27962,7 +27957,7 @@
         <v>0</v>
       </c>
       <c r="R218" s="23">
-        <f>SUM(O218:Q218)</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="S218" s="22">
@@ -28026,7 +28021,7 @@
         <v>59</v>
       </c>
       <c r="R219" s="25">
-        <f>SUM(O219:Q219)</f>
+        <f t="shared" si="3"/>
         <v>59</v>
       </c>
       <c r="S219" s="24">
@@ -28089,7 +28084,7 @@
         <v>0</v>
       </c>
       <c r="R220" s="23">
-        <f>SUM(O220:Q220)</f>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="S220" s="22">
@@ -28152,7 +28147,7 @@
         <v>30</v>
       </c>
       <c r="R221" s="25">
-        <f>SUM(O221:Q221)</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="S221" s="24">
@@ -28215,7 +28210,7 @@
         <v>0</v>
       </c>
       <c r="R222" s="23">
-        <f>SUM(O222:Q222)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S222" s="22">
@@ -28278,7 +28273,7 @@
         <v>1</v>
       </c>
       <c r="R223" s="25">
-        <f>SUM(O223:Q223)</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="S223" s="24">
@@ -28341,7 +28336,7 @@
         <v>0</v>
       </c>
       <c r="R224" s="23">
-        <f>SUM(O224:Q224)</f>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="S224" s="22">
@@ -28404,7 +28399,7 @@
         <v>0</v>
       </c>
       <c r="R225" s="25">
-        <f>SUM(O225:Q225)</f>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="S225" s="24">
@@ -28467,7 +28462,7 @@
         <v>0</v>
       </c>
       <c r="R226" s="23">
-        <f>SUM(O226:Q226)</f>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="S226" s="22">
@@ -28530,7 +28525,7 @@
         <v>0</v>
       </c>
       <c r="R227" s="25">
-        <f>SUM(O227:Q227)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S227" s="24">
@@ -28593,7 +28588,7 @@
         <v>0</v>
       </c>
       <c r="R228" s="23">
-        <f>SUM(O228:Q228)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="S228" s="22">
@@ -28656,7 +28651,7 @@
         <v>0</v>
       </c>
       <c r="R229" s="25">
-        <f>SUM(O229:Q229)</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="S229" s="24">
@@ -28719,7 +28714,7 @@
         <v>5</v>
       </c>
       <c r="R230" s="23">
-        <f>SUM(O230:Q230)</f>
+        <f t="shared" si="3"/>
         <v>52</v>
       </c>
       <c r="S230" s="22">
@@ -28782,7 +28777,7 @@
         <v>0</v>
       </c>
       <c r="R231" s="25">
-        <f>SUM(O231:Q231)</f>
+        <f t="shared" si="3"/>
         <v>89</v>
       </c>
       <c r="S231" s="24">
@@ -28845,7 +28840,7 @@
         <v>0</v>
       </c>
       <c r="R232" s="23">
-        <f>SUM(O232:Q232)</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S232" s="22">
@@ -28908,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R233" s="25">
-        <f>SUM(O233:Q233)</f>
+        <f t="shared" si="3"/>
         <v>38</v>
       </c>
       <c r="S233" s="24">
@@ -28971,7 +28966,7 @@
         <v>0</v>
       </c>
       <c r="R234" s="23">
-        <f>SUM(O234:Q234)</f>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="S234" s="22">
@@ -29034,7 +29029,7 @@
         <v>0</v>
       </c>
       <c r="R235" s="25">
-        <f>SUM(O235:Q235)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="S235" s="24">
@@ -29097,7 +29092,7 @@
         <v>0</v>
       </c>
       <c r="R236" s="23">
-        <f>SUM(O236:Q236)</f>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="S236" s="22">
@@ -29160,7 +29155,7 @@
         <v>0</v>
       </c>
       <c r="R237" s="25">
-        <f>SUM(O237:Q237)</f>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="S237" s="24">
@@ -29223,7 +29218,7 @@
         <v>0</v>
       </c>
       <c r="R238" s="23">
-        <f>SUM(O238:Q238)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="S238" s="22">
@@ -29286,7 +29281,7 @@
         <v>51</v>
       </c>
       <c r="R239" s="25">
-        <f>SUM(O239:Q239)</f>
+        <f t="shared" si="3"/>
         <v>51</v>
       </c>
       <c r="S239" s="24">
@@ -29350,7 +29345,7 @@
         <v>31</v>
       </c>
       <c r="R240" s="23">
-        <f>SUM(O240:Q240)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="S240" s="22">
@@ -29413,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="R241" s="25">
-        <f>SUM(O241:Q241)</f>
+        <f t="shared" si="3"/>
         <v>140</v>
       </c>
       <c r="S241" s="24">
@@ -29476,7 +29471,7 @@
         <v>0</v>
       </c>
       <c r="R242" s="23">
-        <f>SUM(O242:Q242)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="S242" s="22">
@@ -29539,7 +29534,7 @@
         <v>0</v>
       </c>
       <c r="R243" s="25">
-        <f>SUM(O243:Q243)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="S243" s="24">
@@ -29602,7 +29597,7 @@
         <v>0</v>
       </c>
       <c r="R244" s="23">
-        <f>SUM(O244:Q244)</f>
+        <f t="shared" si="3"/>
         <v>55</v>
       </c>
       <c r="S244" s="22">
@@ -29665,7 +29660,7 @@
         <v>120</v>
       </c>
       <c r="R245" s="25">
-        <f>SUM(O245:Q245)</f>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="S245" s="24">
@@ -29728,7 +29723,7 @@
         <v>22</v>
       </c>
       <c r="R246" s="23">
-        <f>SUM(O246:Q246)</f>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="S246" s="22">
@@ -29791,7 +29786,7 @@
         <v>0</v>
       </c>
       <c r="R247" s="25">
-        <f>SUM(O247:Q247)</f>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="S247" s="24">
@@ -29854,7 +29849,7 @@
         <v>0</v>
       </c>
       <c r="R248" s="23">
-        <f>SUM(O248:Q248)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="S248" s="22">
@@ -29917,7 +29912,7 @@
         <v>0</v>
       </c>
       <c r="R249" s="25">
-        <f>SUM(O249:Q249)</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="S249" s="24">
@@ -29980,7 +29975,7 @@
         <v>0</v>
       </c>
       <c r="R250" s="23">
-        <f>SUM(O250:Q250)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="S250" s="22">
@@ -30043,7 +30038,7 @@
         <v>56</v>
       </c>
       <c r="R251" s="25">
-        <f>SUM(O251:Q251)</f>
+        <f t="shared" si="3"/>
         <v>56</v>
       </c>
       <c r="S251" s="24">
@@ -30107,7 +30102,7 @@
         <v>0</v>
       </c>
       <c r="R252" s="23">
-        <f>SUM(O252:Q252)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="S252" s="22">
@@ -30170,7 +30165,7 @@
         <v>0</v>
       </c>
       <c r="R253" s="25">
-        <f>SUM(O253:Q253)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="S253" s="24">
@@ -30233,7 +30228,7 @@
         <v>0</v>
       </c>
       <c r="R254" s="23">
-        <f>SUM(O254:Q254)</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="S254" s="22">
@@ -30294,7 +30289,7 @@
         <v>0</v>
       </c>
       <c r="R255" s="25">
-        <f>SUM(O255:Q255)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S255" s="24">
@@ -30357,7 +30352,7 @@
         <v>49</v>
       </c>
       <c r="R256" s="23">
-        <f>SUM(O256:Q256)</f>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="S256" s="22">
@@ -30420,7 +30415,7 @@
         <v>0</v>
       </c>
       <c r="R257" s="25">
-        <f>SUM(O257:Q257)</f>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="S257" s="24">
@@ -30483,7 +30478,7 @@
         <v>7</v>
       </c>
       <c r="R258" s="23">
-        <f>SUM(O258:Q258)</f>
+        <f t="shared" ref="R258:R321" si="4">SUM(O258:Q258)</f>
         <v>22</v>
       </c>
       <c r="S258" s="22">
@@ -30546,7 +30541,7 @@
         <v>0</v>
       </c>
       <c r="R259" s="25">
-        <f>SUM(O259:Q259)</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="S259" s="24">
@@ -30609,7 +30604,7 @@
         <v>31</v>
       </c>
       <c r="R260" s="23">
-        <f>SUM(O260:Q260)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="S260" s="22">
@@ -30672,7 +30667,7 @@
         <v>0</v>
       </c>
       <c r="R261" s="25">
-        <f>SUM(O261:Q261)</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="S261" s="24">
@@ -30735,7 +30730,7 @@
         <v>0</v>
       </c>
       <c r="R262" s="23">
-        <f>SUM(O262:Q262)</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="S262" s="22">
@@ -30798,7 +30793,7 @@
         <v>0</v>
       </c>
       <c r="R263" s="25">
-        <f>SUM(O263:Q263)</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="S263" s="24">
@@ -30861,7 +30856,7 @@
         <v>29</v>
       </c>
       <c r="R264" s="23">
-        <f>SUM(O264:Q264)</f>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="S264" s="22">
@@ -30924,7 +30919,7 @@
         <v>21</v>
       </c>
       <c r="R265" s="25">
-        <f>SUM(O265:Q265)</f>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="S265" s="24">
@@ -30987,7 +30982,7 @@
         <v>0</v>
       </c>
       <c r="R266" s="23">
-        <f>SUM(O266:Q266)</f>
+        <f t="shared" si="4"/>
         <v>66</v>
       </c>
       <c r="S266" s="22">
@@ -31050,7 +31045,7 @@
         <v>20</v>
       </c>
       <c r="R267" s="25">
-        <f>SUM(O267:Q267)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S267" s="24">
@@ -31113,7 +31108,7 @@
         <v>0</v>
       </c>
       <c r="R268" s="23">
-        <f>SUM(O268:Q268)</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="S268" s="22">
@@ -31176,7 +31171,7 @@
         <v>0</v>
       </c>
       <c r="R269" s="25">
-        <f>SUM(O269:Q269)</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="S269" s="24">
@@ -31239,7 +31234,7 @@
         <v>0</v>
       </c>
       <c r="R270" s="23">
-        <f>SUM(O270:Q270)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="S270" s="22">
@@ -31302,7 +31297,7 @@
         <v>0</v>
       </c>
       <c r="R271" s="25">
-        <f>SUM(O271:Q271)</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="S271" s="24">
@@ -31365,7 +31360,7 @@
         <v>0</v>
       </c>
       <c r="R272" s="23">
-        <f>SUM(O272:Q272)</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="S272" s="22">
@@ -31428,7 +31423,7 @@
         <v>0</v>
       </c>
       <c r="R273" s="25">
-        <f>SUM(O273:Q273)</f>
+        <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="S273" s="24">
@@ -31491,7 +31486,7 @@
         <v>0</v>
       </c>
       <c r="R274" s="23">
-        <f>SUM(O274:Q274)</f>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="S274" s="22">
@@ -31554,7 +31549,7 @@
         <v>0</v>
       </c>
       <c r="R275" s="25">
-        <f>SUM(O275:Q275)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S275" s="24">
@@ -31617,7 +31612,7 @@
         <v>39</v>
       </c>
       <c r="R276" s="23">
-        <f>SUM(O276:Q276)</f>
+        <f t="shared" si="4"/>
         <v>39</v>
       </c>
       <c r="S276" s="22">
@@ -31680,7 +31675,7 @@
         <v>0</v>
       </c>
       <c r="R277" s="25">
-        <f>SUM(O277:Q277)</f>
+        <f t="shared" si="4"/>
         <v>39</v>
       </c>
       <c r="S277" s="24">
@@ -31743,7 +31738,7 @@
         <v>0</v>
       </c>
       <c r="R278" s="23">
-        <f>SUM(O278:Q278)</f>
+        <f t="shared" si="4"/>
         <v>277</v>
       </c>
       <c r="S278" s="22">
@@ -31806,7 +31801,7 @@
         <v>0</v>
       </c>
       <c r="R279" s="25">
-        <f>SUM(O279:Q279)</f>
+        <f t="shared" si="4"/>
         <v>43</v>
       </c>
       <c r="S279" s="24">
@@ -31869,7 +31864,7 @@
         <v>0</v>
       </c>
       <c r="R280" s="23">
-        <f>SUM(O280:Q280)</f>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="S280" s="22">
@@ -31932,7 +31927,7 @@
         <v>84</v>
       </c>
       <c r="R281" s="25">
-        <f>SUM(O281:Q281)</f>
+        <f t="shared" si="4"/>
         <v>144</v>
       </c>
       <c r="S281" s="24">
@@ -31995,7 +31990,7 @@
         <v>0</v>
       </c>
       <c r="R282" s="23">
-        <f>SUM(O282:Q282)</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="S282" s="22">
@@ -32058,7 +32053,7 @@
         <v>64</v>
       </c>
       <c r="R283" s="25">
-        <f>SUM(O283:Q283)</f>
+        <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="S283" s="24">
@@ -32121,7 +32116,7 @@
         <v>0</v>
       </c>
       <c r="R284" s="23">
-        <f>SUM(O284:Q284)</f>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="S284" s="22">
@@ -32184,7 +32179,7 @@
         <v>193</v>
       </c>
       <c r="R285" s="25">
-        <f>SUM(O285:Q285)</f>
+        <f t="shared" si="4"/>
         <v>193</v>
       </c>
       <c r="S285" s="24">
@@ -32247,7 +32242,7 @@
         <v>0</v>
       </c>
       <c r="R286" s="23">
-        <f>SUM(O286:Q286)</f>
+        <f t="shared" si="4"/>
         <v>46</v>
       </c>
       <c r="S286" s="22">
@@ -32310,7 +32305,7 @@
         <v>20</v>
       </c>
       <c r="R287" s="25">
-        <f>SUM(O287:Q287)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S287" s="24">
@@ -32371,7 +32366,7 @@
         <v>0</v>
       </c>
       <c r="R288" s="23">
-        <f>SUM(O288:Q288)</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S288" s="22">
@@ -32432,7 +32427,7 @@
         <v>0</v>
       </c>
       <c r="R289" s="25">
-        <f>SUM(O289:Q289)</f>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="S289" s="24">
@@ -32495,7 +32490,7 @@
         <v>0</v>
       </c>
       <c r="R290" s="23">
-        <f>SUM(O290:Q290)</f>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="S290" s="22">
@@ -32558,7 +32553,7 @@
         <v>0</v>
       </c>
       <c r="R291" s="25">
-        <f>SUM(O291:Q291)</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="S291" s="24">
@@ -32621,7 +32616,7 @@
         <v>35</v>
       </c>
       <c r="R292" s="23">
-        <f>SUM(O292:Q292)</f>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="S292" s="22">
@@ -32684,7 +32679,7 @@
         <v>0</v>
       </c>
       <c r="R293" s="25">
-        <f>SUM(O293:Q293)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S293" s="24">
@@ -32747,7 +32742,7 @@
         <v>0</v>
       </c>
       <c r="R294" s="23">
-        <f>SUM(O294:Q294)</f>
+        <f t="shared" si="4"/>
         <v>188</v>
       </c>
       <c r="S294" s="22">
@@ -32810,7 +32805,7 @@
         <v>0</v>
       </c>
       <c r="R295" s="25">
-        <f>SUM(O295:Q295)</f>
+        <f t="shared" si="4"/>
         <v>42</v>
       </c>
       <c r="S295" s="24">
@@ -32873,7 +32868,7 @@
         <v>0</v>
       </c>
       <c r="R296" s="23">
-        <f>SUM(O296:Q296)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="S296" s="22">
@@ -32937,7 +32932,7 @@
         <v>0</v>
       </c>
       <c r="R297" s="25">
-        <f>SUM(O297:Q297)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S297" s="24">
@@ -32998,7 +32993,7 @@
         <v>0</v>
       </c>
       <c r="R298" s="23">
-        <f>SUM(O298:Q298)</f>
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="S298" s="22">
@@ -33061,7 +33056,7 @@
         <v>52</v>
       </c>
       <c r="R299" s="25">
-        <f>SUM(O299:Q299)</f>
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
       <c r="S299" s="24">
@@ -33124,7 +33119,7 @@
         <v>54</v>
       </c>
       <c r="R300" s="23">
-        <f>SUM(O300:Q300)</f>
+        <f t="shared" si="4"/>
         <v>54</v>
       </c>
       <c r="S300" s="22">
@@ -33187,7 +33182,7 @@
         <v>130</v>
       </c>
       <c r="R301" s="25">
-        <f>SUM(O301:Q301)</f>
+        <f t="shared" si="4"/>
         <v>153</v>
       </c>
       <c r="S301" s="24">
@@ -33250,7 +33245,7 @@
         <v>0</v>
       </c>
       <c r="R302" s="23">
-        <f>SUM(O302:Q302)</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="S302" s="22">
@@ -33313,7 +33308,7 @@
         <v>0</v>
       </c>
       <c r="R303" s="25">
-        <f>SUM(O303:Q303)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S303" s="24">
@@ -33370,7 +33365,7 @@
       <c r="P304" s="23"/>
       <c r="Q304" s="23"/>
       <c r="R304" s="23">
-        <f>SUM(O304:Q304)</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="S304" s="22">
@@ -33433,7 +33428,7 @@
         <v>0</v>
       </c>
       <c r="R305" s="25">
-        <f>SUM(O305:Q305)</f>
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="S305" s="24">
@@ -33496,7 +33491,7 @@
         <v>0</v>
       </c>
       <c r="R306" s="23">
-        <f>SUM(O306:Q306)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="S306" s="22">
@@ -33557,7 +33552,7 @@
         <v>1</v>
       </c>
       <c r="R307" s="25">
-        <f>SUM(O307:Q307)</f>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="S307" s="24">
@@ -33621,7 +33616,7 @@
         <v>0</v>
       </c>
       <c r="R308" s="23">
-        <f>SUM(O308:Q308)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="S308" s="22">
@@ -33684,7 +33679,7 @@
         <v>0</v>
       </c>
       <c r="R309" s="25">
-        <f>SUM(O309:Q309)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="S309" s="24">
@@ -33747,7 +33742,7 @@
         <v>1</v>
       </c>
       <c r="R310" s="23">
-        <f>SUM(O310:Q310)</f>
+        <f t="shared" si="4"/>
         <v>45</v>
       </c>
       <c r="S310" s="22">
@@ -33810,7 +33805,7 @@
         <v>0</v>
       </c>
       <c r="R311" s="25">
-        <f>SUM(O311:Q311)</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="S311" s="24">
@@ -33874,7 +33869,7 @@
         <v>0</v>
       </c>
       <c r="R312" s="23">
-        <f>SUM(O312:Q312)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="S312" s="22">
@@ -33937,7 +33932,7 @@
         <v>0</v>
       </c>
       <c r="R313" s="25">
-        <f>SUM(O313:Q313)</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="S313" s="24">
@@ -34001,7 +33996,7 @@
         <v>0</v>
       </c>
       <c r="R314" s="23">
-        <f>SUM(O314:Q314)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S314" s="22">
@@ -34064,7 +34059,7 @@
         <v>33</v>
       </c>
       <c r="R315" s="25">
-        <f>SUM(O315:Q315)</f>
+        <f t="shared" si="4"/>
         <v>33</v>
       </c>
       <c r="S315" s="24">
@@ -34127,7 +34122,7 @@
         <v>0</v>
       </c>
       <c r="R316" s="23">
-        <f>SUM(O316:Q316)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="S316" s="22">
@@ -34190,7 +34185,7 @@
         <v>0</v>
       </c>
       <c r="R317" s="25">
-        <f>SUM(O317:Q317)</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="S317" s="24">
@@ -34253,7 +34248,7 @@
         <v>19</v>
       </c>
       <c r="R318" s="23">
-        <f>SUM(O318:Q318)</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="S318" s="22">
@@ -34317,7 +34312,7 @@
         <v>0</v>
       </c>
       <c r="R319" s="25">
-        <f>SUM(O319:Q319)</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S319" s="24">
@@ -34381,7 +34376,7 @@
         <v>0</v>
       </c>
       <c r="R320" s="23">
-        <f>SUM(O320:Q320)</f>
+        <f t="shared" si="4"/>
         <v>49</v>
       </c>
       <c r="S320" s="22">
@@ -34445,7 +34440,7 @@
         <v>0</v>
       </c>
       <c r="R321" s="25">
-        <f>SUM(O321:Q321)</f>
+        <f t="shared" si="4"/>
         <v>126</v>
       </c>
       <c r="S321" s="24">
@@ -34508,7 +34503,7 @@
         <v>40</v>
       </c>
       <c r="R322" s="23">
-        <f>SUM(O322:Q322)</f>
+        <f t="shared" ref="R322:R385" si="5">SUM(O322:Q322)</f>
         <v>40</v>
       </c>
       <c r="S322" s="22">
@@ -34571,7 +34566,7 @@
         <v>40</v>
       </c>
       <c r="R323" s="25">
-        <f>SUM(O323:Q323)</f>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="S323" s="24">
@@ -34634,7 +34629,7 @@
         <v>60</v>
       </c>
       <c r="R324" s="23">
-        <f>SUM(O324:Q324)</f>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="S324" s="22">
@@ -34697,7 +34692,7 @@
         <v>30</v>
       </c>
       <c r="R325" s="25">
-        <f>SUM(O325:Q325)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="S325" s="24">
@@ -34760,7 +34755,7 @@
         <v>0</v>
       </c>
       <c r="R326" s="23">
-        <f>SUM(O326:Q326)</f>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="S326" s="22">
@@ -34823,7 +34818,7 @@
         <v>0</v>
       </c>
       <c r="R327" s="25">
-        <f>SUM(O327:Q327)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="S327" s="24">
@@ -34886,7 +34881,7 @@
         <v>39</v>
       </c>
       <c r="R328" s="23">
-        <f>SUM(O328:Q328)</f>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="S328" s="22">
@@ -34949,7 +34944,7 @@
         <v>0</v>
       </c>
       <c r="R329" s="25">
-        <f>SUM(O329:Q329)</f>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="S329" s="24">
@@ -35012,7 +35007,7 @@
         <v>0</v>
       </c>
       <c r="R330" s="23">
-        <f>SUM(O330:Q330)</f>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="S330" s="22">
@@ -35075,7 +35070,7 @@
         <v>0</v>
       </c>
       <c r="R331" s="25">
-        <f>SUM(O331:Q331)</f>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="S331" s="24">
@@ -35138,7 +35133,7 @@
         <v>0</v>
       </c>
       <c r="R332" s="23">
-        <f>SUM(O332:Q332)</f>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="S332" s="22">
@@ -35201,7 +35196,7 @@
         <v>0</v>
       </c>
       <c r="R333" s="25">
-        <f>SUM(O333:Q333)</f>
+        <f t="shared" si="5"/>
         <v>207</v>
       </c>
       <c r="S333" s="24">
@@ -35264,7 +35259,7 @@
         <v>0</v>
       </c>
       <c r="R334" s="23">
-        <f>SUM(O334:Q334)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="S334" s="22">
@@ -35327,7 +35322,7 @@
         <v>0</v>
       </c>
       <c r="R335" s="25">
-        <f>SUM(O335:Q335)</f>
+        <f t="shared" si="5"/>
         <v>184</v>
       </c>
       <c r="S335" s="24">
@@ -35390,7 +35385,7 @@
         <v>0</v>
       </c>
       <c r="R336" s="23">
-        <f>SUM(O336:Q336)</f>
+        <f t="shared" si="5"/>
         <v>46</v>
       </c>
       <c r="S336" s="22">
@@ -35453,7 +35448,7 @@
         <v>16</v>
       </c>
       <c r="R337" s="25">
-        <f>SUM(O337:Q337)</f>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="S337" s="24">
@@ -35516,7 +35511,7 @@
         <v>45</v>
       </c>
       <c r="R338" s="23">
-        <f>SUM(O338:Q338)</f>
+        <f t="shared" si="5"/>
         <v>48</v>
       </c>
       <c r="S338" s="22">
@@ -35571,7 +35566,7 @@
         <v>40</v>
       </c>
       <c r="R339" s="25">
-        <f>SUM(O339:Q339)</f>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="S339" s="24">
@@ -35630,7 +35625,7 @@
         <v>0</v>
       </c>
       <c r="R340" s="23">
-        <f>SUM(O340:Q340)</f>
+        <f t="shared" si="5"/>
         <v>150</v>
       </c>
       <c r="S340" s="22">
@@ -35693,7 +35688,7 @@
         <v>0</v>
       </c>
       <c r="R341" s="25">
-        <f>SUM(O341:Q341)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="S341" s="24">
@@ -35748,7 +35743,7 @@
         <v>30</v>
       </c>
       <c r="R342" s="23">
-        <f>SUM(O342:Q342)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="S342" s="22">
@@ -35812,7 +35807,7 @@
         <v>0</v>
       </c>
       <c r="R343" s="25">
-        <f>SUM(O343:Q343)</f>
+        <f t="shared" si="5"/>
         <v>67</v>
       </c>
       <c r="S343" s="24">
@@ -35875,7 +35870,7 @@
         <v>0</v>
       </c>
       <c r="R344" s="23">
-        <f>SUM(O344:Q344)</f>
+        <f t="shared" si="5"/>
         <v>67</v>
       </c>
       <c r="S344" s="22">
@@ -35938,7 +35933,7 @@
         <v>0</v>
       </c>
       <c r="R345" s="25">
-        <f>SUM(O345:Q345)</f>
+        <f t="shared" si="5"/>
         <v>57</v>
       </c>
       <c r="S345" s="24">
@@ -36001,7 +35996,7 @@
         <v>0</v>
       </c>
       <c r="R346" s="23">
-        <f>SUM(O346:Q346)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="S346" s="22">
@@ -36064,7 +36059,7 @@
         <v>0</v>
       </c>
       <c r="R347" s="25">
-        <f>SUM(O347:Q347)</f>
+        <f t="shared" si="5"/>
         <v>315</v>
       </c>
       <c r="S347" s="24">
@@ -36127,7 +36122,7 @@
         <v>0</v>
       </c>
       <c r="R348" s="23">
-        <f>SUM(O348:Q348)</f>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="S348" s="22">
@@ -36190,7 +36185,7 @@
         <v>0</v>
       </c>
       <c r="R349" s="25">
-        <f>SUM(O349:Q349)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="S349" s="24">
@@ -36254,7 +36249,7 @@
         <v>0</v>
       </c>
       <c r="R350" s="23">
-        <f>SUM(O350:Q350)</f>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="S350" s="22">
@@ -36317,7 +36312,7 @@
         <v>0</v>
       </c>
       <c r="R351" s="25">
-        <f>SUM(O351:Q351)</f>
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
       <c r="S351" s="24">
@@ -36380,7 +36375,7 @@
         <v>0</v>
       </c>
       <c r="R352" s="23">
-        <f>SUM(O352:Q352)</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="S352" s="22">
@@ -36443,7 +36438,7 @@
         <v>0</v>
       </c>
       <c r="R353" s="25">
-        <f>SUM(O353:Q353)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="S353" s="24">
@@ -36506,7 +36501,7 @@
         <v>0</v>
       </c>
       <c r="R354" s="23">
-        <f>SUM(O354:Q354)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="S354" s="22">
@@ -36569,7 +36564,7 @@
         <v>0</v>
       </c>
       <c r="R355" s="25">
-        <f>SUM(O355:Q355)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="S355" s="24">
@@ -36632,7 +36627,7 @@
         <v>0</v>
       </c>
       <c r="R356" s="23">
-        <f>SUM(O356:Q356)</f>
+        <f t="shared" si="5"/>
         <v>64</v>
       </c>
       <c r="S356" s="22">
@@ -36694,7 +36689,7 @@
         <v>0</v>
       </c>
       <c r="R357" s="25">
-        <f>SUM(O357:Q357)</f>
+        <f t="shared" si="5"/>
         <v>57</v>
       </c>
       <c r="S357" s="24">
@@ -36757,7 +36752,7 @@
         <v>0</v>
       </c>
       <c r="R358" s="23">
-        <f>SUM(O358:Q358)</f>
+        <f t="shared" si="5"/>
         <v>39</v>
       </c>
       <c r="S358" s="22">
@@ -36820,7 +36815,7 @@
         <v>0</v>
       </c>
       <c r="R359" s="25">
-        <f>SUM(O359:Q359)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="S359" s="24">
@@ -36883,7 +36878,7 @@
         <v>0</v>
       </c>
       <c r="R360" s="23">
-        <f>SUM(O360:Q360)</f>
+        <f t="shared" si="5"/>
         <v>47</v>
       </c>
       <c r="S360" s="22">
@@ -36946,7 +36941,7 @@
         <v>2</v>
       </c>
       <c r="R361" s="25">
-        <f>SUM(O361:Q361)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="S361" s="24">
@@ -37009,7 +37004,7 @@
         <v>0</v>
       </c>
       <c r="R362" s="23">
-        <f>SUM(O362:Q362)</f>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="S362" s="22">
@@ -37072,7 +37067,7 @@
         <v>43</v>
       </c>
       <c r="R363" s="25">
-        <f>SUM(O363:Q363)</f>
+        <f t="shared" si="5"/>
         <v>43</v>
       </c>
       <c r="S363" s="24">
@@ -37135,7 +37130,7 @@
         <v>0</v>
       </c>
       <c r="R364" s="23">
-        <f>SUM(O364:Q364)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="S364" s="22">
@@ -37198,7 +37193,7 @@
         <v>0</v>
       </c>
       <c r="R365" s="25">
-        <f>SUM(O365:Q365)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="S365" s="24">
@@ -37262,7 +37257,7 @@
         <v>57</v>
       </c>
       <c r="R366" s="23">
-        <f>SUM(O366:Q366)</f>
+        <f t="shared" si="5"/>
         <v>57</v>
       </c>
       <c r="S366" s="22">
@@ -37326,7 +37321,7 @@
         <v>0</v>
       </c>
       <c r="R367" s="25">
-        <f>SUM(O367:Q367)</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="S367" s="24">
@@ -37389,7 +37384,7 @@
         <v>0</v>
       </c>
       <c r="R368" s="23">
-        <f>SUM(O368:Q368)</f>
+        <f t="shared" si="5"/>
         <v>176</v>
       </c>
       <c r="S368" s="22">
@@ -37450,7 +37445,7 @@
         <v>0</v>
       </c>
       <c r="R369" s="25">
-        <f>SUM(O369:Q369)</f>
+        <f t="shared" si="5"/>
         <v>56</v>
       </c>
       <c r="S369" s="24">
@@ -37514,7 +37509,7 @@
         <v>0</v>
       </c>
       <c r="R370" s="23">
-        <f>SUM(O370:Q370)</f>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="S370" s="22">
@@ -37577,7 +37572,7 @@
         <v>39</v>
       </c>
       <c r="R371" s="25">
-        <f>SUM(O371:Q371)</f>
+        <f t="shared" si="5"/>
         <v>39</v>
       </c>
       <c r="S371" s="24">
@@ -37640,7 +37635,7 @@
         <v>0</v>
       </c>
       <c r="R372" s="23">
-        <f>SUM(O372:Q372)</f>
+        <f t="shared" si="5"/>
         <v>47</v>
       </c>
       <c r="S372" s="22">
@@ -37702,7 +37697,7 @@
         <v>53</v>
       </c>
       <c r="R373" s="25">
-        <f>SUM(O373:Q373)</f>
+        <f t="shared" si="5"/>
         <v>53</v>
       </c>
       <c r="S373" s="24">
@@ -37765,7 +37760,7 @@
         <v>0</v>
       </c>
       <c r="R374" s="23">
-        <f>SUM(O374:Q374)</f>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="S374" s="22">
@@ -37829,7 +37824,7 @@
         <v>0</v>
       </c>
       <c r="R375" s="25">
-        <f>SUM(O375:Q375)</f>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="S375" s="24">
@@ -37893,7 +37888,7 @@
         <v>53</v>
       </c>
       <c r="R376" s="23">
-        <f>SUM(O376:Q376)</f>
+        <f t="shared" si="5"/>
         <v>53</v>
       </c>
       <c r="S376" s="22">
@@ -37957,7 +37952,7 @@
         <v>0</v>
       </c>
       <c r="R377" s="25">
-        <f>SUM(O377:Q377)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="S377" s="24">
@@ -38021,7 +38016,7 @@
         <v>0</v>
       </c>
       <c r="R378" s="23">
-        <f>SUM(O378:Q378)</f>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="S378" s="22">
@@ -38076,7 +38071,7 @@
         <v>0</v>
       </c>
       <c r="R379" s="25">
-        <f>SUM(O379:Q379)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S379" s="24"/>
@@ -38135,7 +38130,7 @@
         <v>0</v>
       </c>
       <c r="R380" s="23">
-        <f>SUM(O380:Q380)</f>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="S380" s="22">
@@ -38190,7 +38185,7 @@
       <c r="P381" s="25"/>
       <c r="Q381" s="25"/>
       <c r="R381" s="25">
-        <f>SUM(O381:Q381)</f>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="S381" s="24">
@@ -38252,7 +38247,7 @@
         <v>17</v>
       </c>
       <c r="R382" s="23">
-        <f>SUM(O382:Q382)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="S382" s="22">
@@ -38316,7 +38311,7 @@
         <v>0</v>
       </c>
       <c r="R383" s="25">
-        <f>SUM(O383:Q383)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="S383" s="24">
@@ -38379,7 +38374,7 @@
         <v>0</v>
       </c>
       <c r="R384" s="23">
-        <f>SUM(O384:Q384)</f>
+        <f t="shared" si="5"/>
         <v>114</v>
       </c>
       <c r="S384" s="22">
@@ -38440,7 +38435,7 @@
         <v>0</v>
       </c>
       <c r="R385" s="25">
-        <f>SUM(O385:Q385)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="S385" s="24">
@@ -38503,7 +38498,7 @@
         <v>0</v>
       </c>
       <c r="R386" s="23">
-        <f>SUM(O386:Q386)</f>
+        <f t="shared" ref="R386:R449" si="6">SUM(O386:Q386)</f>
         <v>49</v>
       </c>
       <c r="S386" s="22">
@@ -38566,7 +38561,7 @@
         <v>0</v>
       </c>
       <c r="R387" s="25">
-        <f>SUM(O387:Q387)</f>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="S387" s="24">
@@ -38629,7 +38624,7 @@
         <v>26</v>
       </c>
       <c r="R388" s="23">
-        <f>SUM(O388:Q388)</f>
+        <f t="shared" si="6"/>
         <v>91</v>
       </c>
       <c r="S388" s="22">
@@ -38693,7 +38688,7 @@
         <v>5</v>
       </c>
       <c r="R389" s="25">
-        <f>SUM(O389:Q389)</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="S389" s="24">
@@ -38756,7 +38751,7 @@
         <v>0</v>
       </c>
       <c r="R390" s="23">
-        <f>SUM(O390:Q390)</f>
+        <f t="shared" si="6"/>
         <v>181</v>
       </c>
       <c r="S390" s="22">
@@ -38820,7 +38815,7 @@
         <v>7</v>
       </c>
       <c r="R391" s="25">
-        <f>SUM(O391:Q391)</f>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="S391" s="24">
@@ -38883,7 +38878,7 @@
         <v>0</v>
       </c>
       <c r="R392" s="23">
-        <f>SUM(O392:Q392)</f>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="S392" s="22">
@@ -39009,7 +39004,7 @@
         <v>31</v>
       </c>
       <c r="R394" s="23">
-        <f>SUM(O394:Q394)</f>
+        <f t="shared" ref="R394:R457" si="7">SUM(O394:Q394)</f>
         <v>31</v>
       </c>
       <c r="S394" s="22">
@@ -39072,7 +39067,7 @@
         <v>0</v>
       </c>
       <c r="R395" s="25">
-        <f>SUM(O395:Q395)</f>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="S395" s="24">
@@ -39135,7 +39130,7 @@
         <v>0</v>
       </c>
       <c r="R396" s="23">
-        <f>SUM(O396:Q396)</f>
+        <f t="shared" si="7"/>
         <v>45</v>
       </c>
       <c r="S396" s="22">
@@ -39198,7 +39193,7 @@
         <v>0</v>
       </c>
       <c r="R397" s="25">
-        <f>SUM(O397:Q397)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S397" s="24">
@@ -39261,7 +39256,7 @@
         <v>17</v>
       </c>
       <c r="R398" s="23">
-        <f>SUM(O398:Q398)</f>
+        <f t="shared" si="7"/>
         <v>85</v>
       </c>
       <c r="S398" s="22">
@@ -39324,7 +39319,7 @@
         <v>0</v>
       </c>
       <c r="R399" s="25">
-        <f>SUM(O399:Q399)</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="S399" s="24">
@@ -39381,7 +39376,7 @@
       <c r="P400" s="23"/>
       <c r="Q400" s="23"/>
       <c r="R400" s="23">
-        <f>SUM(O400:Q400)</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="S400" s="22">
@@ -39442,7 +39437,7 @@
         <v>0</v>
       </c>
       <c r="R401" s="25">
-        <f>SUM(O401:Q401)</f>
+        <f t="shared" si="7"/>
         <v>62</v>
       </c>
       <c r="S401" s="24">
@@ -39505,7 +39500,7 @@
         <v>68</v>
       </c>
       <c r="R402" s="23">
-        <f>SUM(O402:Q402)</f>
+        <f t="shared" si="7"/>
         <v>68</v>
       </c>
       <c r="S402" s="22">
@@ -39564,7 +39559,7 @@
         <v>0</v>
       </c>
       <c r="R403" s="25">
-        <f>SUM(O403:Q403)</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="S403" s="24">
@@ -39627,7 +39622,7 @@
         <v>0</v>
       </c>
       <c r="R404" s="23">
-        <f>SUM(O404:Q404)</f>
+        <f t="shared" si="7"/>
         <v>36</v>
       </c>
       <c r="S404" s="22">
@@ -39690,7 +39685,7 @@
         <v>0</v>
       </c>
       <c r="R405" s="25">
-        <f>SUM(O405:Q405)</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="S405" s="24">
@@ -39751,7 +39746,7 @@
         <v>44</v>
       </c>
       <c r="R406" s="23">
-        <f>SUM(O406:Q406)</f>
+        <f t="shared" si="7"/>
         <v>44</v>
       </c>
       <c r="S406" s="22">
@@ -39814,7 +39809,7 @@
         <v>0</v>
       </c>
       <c r="R407" s="25">
-        <f>SUM(O407:Q407)</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="S407" s="24">
@@ -39877,7 +39872,7 @@
         <v>0</v>
       </c>
       <c r="R408" s="23">
-        <f>SUM(O408:Q408)</f>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="S408" s="22">
@@ -39932,7 +39927,7 @@
         <v>20</v>
       </c>
       <c r="R409" s="25">
-        <f>SUM(O409:Q409)</f>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="S409" s="24">
@@ -39987,7 +39982,7 @@
         <v>0</v>
       </c>
       <c r="R410" s="23">
-        <f>SUM(O410:Q410)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S410" s="22"/>
@@ -40046,7 +40041,7 @@
         <v>0</v>
       </c>
       <c r="R411" s="25">
-        <f>SUM(O411:Q411)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="S411" s="24">
@@ -40109,7 +40104,7 @@
         <v>44</v>
       </c>
       <c r="R412" s="23">
-        <f>SUM(O412:Q412)</f>
+        <f t="shared" si="7"/>
         <v>44</v>
       </c>
       <c r="S412" s="22">
@@ -40172,7 +40167,7 @@
         <v>0</v>
       </c>
       <c r="R413" s="25">
-        <f>SUM(O413:Q413)</f>
+        <f t="shared" si="7"/>
         <v>105</v>
       </c>
       <c r="S413" s="24">
@@ -40235,7 +40230,7 @@
         <v>0</v>
       </c>
       <c r="R414" s="23">
-        <f>SUM(O414:Q414)</f>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="S414" s="22">
@@ -40298,7 +40293,7 @@
         <v>0</v>
       </c>
       <c r="R415" s="25">
-        <f>SUM(O415:Q415)</f>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="S415" s="24">
@@ -40361,7 +40356,7 @@
         <v>0</v>
       </c>
       <c r="R416" s="23">
-        <f>SUM(O416:Q416)</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="S416" s="22">
@@ -40424,7 +40419,7 @@
         <v>24</v>
       </c>
       <c r="R417" s="25">
-        <f>SUM(O417:Q417)</f>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="S417" s="24">
@@ -40487,7 +40482,7 @@
         <v>0</v>
       </c>
       <c r="R418" s="23">
-        <f>SUM(O418:Q418)</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="S418" s="22">
@@ -40551,7 +40546,7 @@
         <v>0</v>
       </c>
       <c r="R419" s="25">
-        <f>SUM(O419:Q419)</f>
+        <f t="shared" si="7"/>
         <v>49</v>
       </c>
       <c r="S419" s="24">
@@ -40614,7 +40609,7 @@
         <v>128</v>
       </c>
       <c r="R420" s="23">
-        <f>SUM(O420:Q420)</f>
+        <f t="shared" si="7"/>
         <v>128</v>
       </c>
       <c r="S420" s="22">
@@ -40677,7 +40672,7 @@
         <v>0</v>
       </c>
       <c r="R421" s="25">
-        <f>SUM(O421:Q421)</f>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
       <c r="S421" s="24">
@@ -40740,7 +40735,7 @@
         <v>0</v>
       </c>
       <c r="R422" s="23">
-        <f>SUM(O422:Q422)</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="S422" s="22">
@@ -40803,7 +40798,7 @@
         <v>0</v>
       </c>
       <c r="R423" s="25">
-        <f>SUM(O423:Q423)</f>
+        <f t="shared" si="7"/>
         <v>93</v>
       </c>
       <c r="S423" s="24">
@@ -40866,7 +40861,7 @@
         <v>0</v>
       </c>
       <c r="R424" s="23">
-        <f>SUM(O424:Q424)</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="S424" s="22">
@@ -40927,7 +40922,7 @@
         <v>0</v>
       </c>
       <c r="R425" s="25">
-        <f>SUM(O425:Q425)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S425" s="24">
@@ -40991,7 +40986,7 @@
         <v>0</v>
       </c>
       <c r="R426" s="23">
-        <f>SUM(O426:Q426)</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="S426" s="22">
@@ -41054,7 +41049,7 @@
         <v>0</v>
       </c>
       <c r="R427" s="25">
-        <f>SUM(O427:Q427)</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="S427" s="24">
@@ -41115,7 +41110,7 @@
         <v>80</v>
       </c>
       <c r="R428" s="23">
-        <f>SUM(O428:Q428)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S428" s="22">
@@ -41176,7 +41171,7 @@
         <v>80</v>
       </c>
       <c r="R429" s="25">
-        <f>SUM(O429:Q429)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S429" s="24">
@@ -41237,7 +41232,7 @@
         <v>80</v>
       </c>
       <c r="R430" s="23">
-        <f>SUM(O430:Q430)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S430" s="22">
@@ -41298,7 +41293,7 @@
         <v>80</v>
       </c>
       <c r="R431" s="25">
-        <f>SUM(O431:Q431)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S431" s="24">
@@ -41359,7 +41354,7 @@
         <v>80</v>
       </c>
       <c r="R432" s="23">
-        <f>SUM(O432:Q432)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S432" s="22">
@@ -41423,7 +41418,7 @@
         <v>0</v>
       </c>
       <c r="R433" s="25">
-        <f>SUM(O433:Q433)</f>
+        <f t="shared" si="7"/>
         <v>33</v>
       </c>
       <c r="S433" s="24">
@@ -41478,7 +41473,7 @@
         <v>0</v>
       </c>
       <c r="R434" s="23">
-        <f>SUM(O434:Q434)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S434" s="22"/>
@@ -41537,7 +41532,7 @@
         <v>62</v>
       </c>
       <c r="R435" s="25">
-        <f>SUM(O435:Q435)</f>
+        <f t="shared" si="7"/>
         <v>62</v>
       </c>
       <c r="S435" s="24">
@@ -41600,7 +41595,7 @@
         <v>0</v>
       </c>
       <c r="R436" s="23">
-        <f>SUM(O436:Q436)</f>
+        <f t="shared" si="7"/>
         <v>42</v>
       </c>
       <c r="S436" s="22">
@@ -41663,7 +41658,7 @@
         <v>0</v>
       </c>
       <c r="R437" s="25">
-        <f>SUM(O437:Q437)</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="S437" s="24">
@@ -41726,7 +41721,7 @@
         <v>0</v>
       </c>
       <c r="R438" s="23">
-        <f>SUM(O438:Q438)</f>
+        <f t="shared" si="7"/>
         <v>49</v>
       </c>
       <c r="S438" s="22">
@@ -41789,7 +41784,7 @@
         <v>0</v>
       </c>
       <c r="R439" s="25">
-        <f>SUM(O439:Q439)</f>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="S439" s="24">
@@ -41852,7 +41847,7 @@
         <v>28</v>
       </c>
       <c r="R440" s="23">
-        <f>SUM(O440:Q440)</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="S440" s="22">
@@ -41915,7 +41910,7 @@
         <v>0</v>
       </c>
       <c r="R441" s="25">
-        <f>SUM(O441:Q441)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="S441" s="24">
@@ -41979,7 +41974,7 @@
         <v>0</v>
       </c>
       <c r="R442" s="23">
-        <f>SUM(O442:Q442)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="S442" s="22">
@@ -42043,7 +42038,7 @@
         <v>0</v>
       </c>
       <c r="R443" s="25">
-        <f>SUM(O443:Q443)</f>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="S443" s="24">
@@ -42106,7 +42101,7 @@
         <v>0</v>
       </c>
       <c r="R444" s="23">
-        <f>SUM(O444:Q444)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="S444" s="22">
@@ -42169,7 +42164,7 @@
         <v>7</v>
       </c>
       <c r="R445" s="25">
-        <f>SUM(O445:Q445)</f>
+        <f t="shared" si="7"/>
         <v>155</v>
       </c>
       <c r="S445" s="24">
@@ -42233,7 +42228,7 @@
         <v>0</v>
       </c>
       <c r="R446" s="23">
-        <f>SUM(O446:Q446)</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="S446" s="22">
@@ -42296,7 +42291,7 @@
         <v>0</v>
       </c>
       <c r="R447" s="25">
-        <f>SUM(O447:Q447)</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="S447" s="24">
@@ -42359,7 +42354,7 @@
         <v>0</v>
       </c>
       <c r="R448" s="23">
-        <f>SUM(O448:Q448)</f>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="S448" s="22">
@@ -42422,7 +42417,7 @@
         <v>0</v>
       </c>
       <c r="R449" s="25">
-        <f>SUM(O449:Q449)</f>
+        <f t="shared" si="7"/>
         <v>51</v>
       </c>
       <c r="S449" s="24">
@@ -42485,7 +42480,7 @@
         <v>0</v>
       </c>
       <c r="R450" s="23">
-        <f>SUM(O450:Q450)</f>
+        <f t="shared" si="7"/>
         <v>52</v>
       </c>
       <c r="S450" s="22">
@@ -42549,7 +42544,7 @@
         <v>0</v>
       </c>
       <c r="R451" s="25">
-        <f>SUM(O451:Q451)</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="S451" s="24">
@@ -42612,7 +42607,7 @@
         <v>0</v>
       </c>
       <c r="R452" s="23">
-        <f>SUM(O452:Q452)</f>
+        <f t="shared" si="7"/>
         <v>90</v>
       </c>
       <c r="S452" s="22">
@@ -42675,7 +42670,7 @@
         <v>0</v>
       </c>
       <c r="R453" s="25">
-        <f>SUM(O453:Q453)</f>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="S453" s="24">
@@ -42738,7 +42733,7 @@
         <v>0</v>
       </c>
       <c r="R454" s="23">
-        <f>SUM(O454:Q454)</f>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="S454" s="22">
@@ -42802,7 +42797,7 @@
         <v>0</v>
       </c>
       <c r="R455" s="25">
-        <f>SUM(O455:Q455)</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="S455" s="24">
@@ -42855,7 +42850,7 @@
         <v>0</v>
       </c>
       <c r="R456" s="23">
-        <f>SUM(O456:Q456)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S456" s="22"/>
@@ -42914,7 +42909,7 @@
         <v>0</v>
       </c>
       <c r="R457" s="25">
-        <f>SUM(O457:Q457)</f>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="S457" s="24">
@@ -42977,7 +42972,7 @@
         <v>0</v>
       </c>
       <c r="R458" s="23">
-        <f>SUM(O458:Q458)</f>
+        <f t="shared" ref="R458:R521" si="8">SUM(O458:Q458)</f>
         <v>23</v>
       </c>
       <c r="S458" s="22">
@@ -43040,7 +43035,7 @@
         <v>0</v>
       </c>
       <c r="R459" s="25">
-        <f>SUM(O459:Q459)</f>
+        <f t="shared" si="8"/>
         <v>89</v>
       </c>
       <c r="S459" s="24">
@@ -43103,7 +43098,7 @@
         <v>0</v>
       </c>
       <c r="R460" s="23">
-        <f>SUM(O460:Q460)</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="S460" s="22">
@@ -43167,7 +43162,7 @@
         <v>0</v>
       </c>
       <c r="R461" s="25">
-        <f>SUM(O461:Q461)</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="S461" s="24">
@@ -43230,7 +43225,7 @@
         <v>0</v>
       </c>
       <c r="R462" s="23">
-        <f>SUM(O462:Q462)</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="S462" s="22">
@@ -43293,7 +43288,7 @@
         <v>0</v>
       </c>
       <c r="R463" s="25">
-        <f>SUM(O463:Q463)</f>
+        <f t="shared" si="8"/>
         <v>51</v>
       </c>
       <c r="S463" s="24">
@@ -43357,7 +43352,7 @@
         <v>0</v>
       </c>
       <c r="R464" s="23">
-        <f>SUM(O464:Q464)</f>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="S464" s="22">
@@ -43420,7 +43415,7 @@
         <v>0</v>
       </c>
       <c r="R465" s="25">
-        <f>SUM(O465:Q465)</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="S465" s="24">
@@ -43483,7 +43478,7 @@
         <v>156</v>
       </c>
       <c r="R466" s="23">
-        <f>SUM(O466:Q466)</f>
+        <f t="shared" si="8"/>
         <v>213</v>
       </c>
       <c r="S466" s="22">
@@ -43546,7 +43541,7 @@
         <v>70</v>
       </c>
       <c r="R467" s="25">
-        <f>SUM(O467:Q467)</f>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="S467" s="24">
@@ -43609,7 +43604,7 @@
         <v>0</v>
       </c>
       <c r="R468" s="23">
-        <f>SUM(O468:Q468)</f>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="S468" s="22">
@@ -43673,7 +43668,7 @@
         <v>0</v>
       </c>
       <c r="R469" s="25">
-        <f>SUM(O469:Q469)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="S469" s="24">
@@ -43737,7 +43732,7 @@
         <v>0</v>
       </c>
       <c r="R470" s="23">
-        <f>SUM(O470:Q470)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="S470" s="22">
@@ -43801,7 +43796,7 @@
         <v>0</v>
       </c>
       <c r="R471" s="25">
-        <f>SUM(O471:Q471)</f>
+        <f t="shared" si="8"/>
         <v>384</v>
       </c>
       <c r="S471" s="24">
@@ -43864,7 +43859,7 @@
         <v>0</v>
       </c>
       <c r="R472" s="23">
-        <f>SUM(O472:Q472)</f>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="S472" s="22">
@@ -43927,7 +43922,7 @@
         <v>0</v>
       </c>
       <c r="R473" s="25">
-        <f>SUM(O473:Q473)</f>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
       <c r="S473" s="24">
@@ -43990,7 +43985,7 @@
         <v>0</v>
       </c>
       <c r="R474" s="23">
-        <f>SUM(O474:Q474)</f>
+        <f t="shared" si="8"/>
         <v>53</v>
       </c>
       <c r="S474" s="22">
@@ -44053,7 +44048,7 @@
         <v>0</v>
       </c>
       <c r="R475" s="25">
-        <f>SUM(O475:Q475)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="S475" s="24">
@@ -44116,7 +44111,7 @@
         <v>0</v>
       </c>
       <c r="R476" s="23">
-        <f>SUM(O476:Q476)</f>
+        <f t="shared" si="8"/>
         <v>60</v>
       </c>
       <c r="S476" s="22">
@@ -44179,7 +44174,7 @@
         <v>0</v>
       </c>
       <c r="R477" s="25">
-        <f>SUM(O477:Q477)</f>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="S477" s="24">
@@ -44242,7 +44237,7 @@
         <v>0</v>
       </c>
       <c r="R478" s="23">
-        <f>SUM(O478:Q478)</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="S478" s="22">
@@ -44305,7 +44300,7 @@
         <v>56</v>
       </c>
       <c r="R479" s="25">
-        <f>SUM(O479:Q479)</f>
+        <f t="shared" si="8"/>
         <v>56</v>
       </c>
       <c r="S479" s="24">
@@ -44368,7 +44363,7 @@
         <v>0</v>
       </c>
       <c r="R480" s="23">
-        <f>SUM(O480:Q480)</f>
+        <f t="shared" si="8"/>
         <v>38</v>
       </c>
       <c r="S480" s="22">
@@ -44431,7 +44426,7 @@
         <v>0</v>
       </c>
       <c r="R481" s="25">
-        <f>SUM(O481:Q481)</f>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="S481" s="24">
@@ -44494,7 +44489,7 @@
         <v>0</v>
       </c>
       <c r="R482" s="23">
-        <f>SUM(O482:Q482)</f>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="S482" s="22">
@@ -44557,7 +44552,7 @@
         <v>0</v>
       </c>
       <c r="R483" s="25">
-        <f>SUM(O483:Q483)</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="S483" s="24">
@@ -44620,7 +44615,7 @@
         <v>0</v>
       </c>
       <c r="R484" s="23">
-        <f>SUM(O484:Q484)</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="S484" s="22">
@@ -44684,7 +44679,7 @@
         <v>0</v>
       </c>
       <c r="R485" s="25">
-        <f>SUM(O485:Q485)</f>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="S485" s="24">
@@ -44747,7 +44742,7 @@
         <v>0</v>
       </c>
       <c r="R486" s="23">
-        <f>SUM(O486:Q486)</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="S486" s="22">
@@ -44810,7 +44805,7 @@
         <v>0</v>
       </c>
       <c r="R487" s="25">
-        <f>SUM(O487:Q487)</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="S487" s="24">
@@ -44874,7 +44869,7 @@
         <v>0</v>
       </c>
       <c r="R488" s="23">
-        <f>SUM(O488:Q488)</f>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="S488" s="22">
@@ -44937,7 +44932,7 @@
         <v>0</v>
       </c>
       <c r="R489" s="25">
-        <f>SUM(O489:Q489)</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="S489" s="64">
@@ -45001,7 +44996,7 @@
         <v>61</v>
       </c>
       <c r="R490" s="23">
-        <f>SUM(O490:Q490)</f>
+        <f t="shared" si="8"/>
         <v>61</v>
       </c>
       <c r="S490" s="70">
@@ -45064,7 +45059,7 @@
         <v>0</v>
       </c>
       <c r="R491" s="25">
-        <f>SUM(O491:Q491)</f>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="S491" s="64">
@@ -45127,7 +45122,7 @@
         <v>0</v>
       </c>
       <c r="R492" s="23">
-        <f>SUM(O492:Q492)</f>
+        <f t="shared" si="8"/>
         <v>43</v>
       </c>
       <c r="S492" s="70">
@@ -45190,7 +45185,7 @@
         <v>0</v>
       </c>
       <c r="R493" s="25">
-        <f>SUM(O493:Q493)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="S493" s="64">
@@ -45251,7 +45246,7 @@
         <v>0</v>
       </c>
       <c r="R494" s="23">
-        <f>SUM(O494:Q494)</f>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="S494" s="70">
@@ -45306,7 +45301,7 @@
         <v>0</v>
       </c>
       <c r="R495" s="25">
-        <f>SUM(O495:Q495)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S495" s="24"/>
@@ -45363,7 +45358,7 @@
         <v>0</v>
       </c>
       <c r="R496" s="23">
-        <f>SUM(O496:Q496)</f>
+        <f t="shared" si="8"/>
         <v>170</v>
       </c>
       <c r="S496" s="70">
@@ -45426,7 +45421,7 @@
         <v>0</v>
       </c>
       <c r="R497" s="25">
-        <f>SUM(O497:Q497)</f>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="S497" s="64">
@@ -45489,7 +45484,7 @@
         <v>0</v>
       </c>
       <c r="R498" s="23">
-        <f>SUM(O498:Q498)</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="S498" s="70">
@@ -45552,7 +45547,7 @@
         <v>45</v>
       </c>
       <c r="R499" s="25">
-        <f>SUM(O499:Q499)</f>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="S499" s="64">
@@ -45613,7 +45608,7 @@
         <v>0</v>
       </c>
       <c r="R500" s="23">
-        <f>SUM(O500:Q500)</f>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="S500" s="70">
@@ -45677,7 +45672,7 @@
         <v>0</v>
       </c>
       <c r="R501" s="25">
-        <f>SUM(O501:Q501)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S501" s="64">
@@ -45740,7 +45735,7 @@
         <v>0</v>
       </c>
       <c r="R502" s="23">
-        <f>SUM(O502:Q502)</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="S502" s="70">
@@ -45803,7 +45798,7 @@
         <v>0</v>
       </c>
       <c r="R503" s="25">
-        <f>SUM(O503:Q503)</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="S503" s="64">
@@ -45866,7 +45861,7 @@
         <v>0</v>
       </c>
       <c r="R504" s="23">
-        <f>SUM(O504:Q504)</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="S504" s="70">
@@ -45927,7 +45922,7 @@
         <v>0</v>
       </c>
       <c r="R505" s="25">
-        <f>SUM(O505:Q505)</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="S505" s="24">
@@ -45991,7 +45986,7 @@
         <v>0</v>
       </c>
       <c r="R506" s="23">
-        <f>SUM(O506:Q506)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="S506" s="22">
@@ -46054,7 +46049,7 @@
         <v>0</v>
       </c>
       <c r="R507" s="25">
-        <f>SUM(O507:Q507)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S507" s="24">
@@ -46117,7 +46112,7 @@
         <v>0</v>
       </c>
       <c r="R508" s="23">
-        <f>SUM(O508:Q508)</f>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="S508" s="22">
@@ -46178,7 +46173,7 @@
         <v>0</v>
       </c>
       <c r="R509" s="25">
-        <f>SUM(O509:Q509)</f>
+        <f t="shared" si="8"/>
         <v>170</v>
       </c>
       <c r="S509" s="24">
@@ -46242,7 +46237,7 @@
         <v>66</v>
       </c>
       <c r="R510" s="23">
-        <f>SUM(O510:Q510)</f>
+        <f t="shared" si="8"/>
         <v>66</v>
       </c>
       <c r="S510" s="22">
@@ -46303,7 +46298,7 @@
         <v>0</v>
       </c>
       <c r="R511" s="25">
-        <f>SUM(O511:Q511)</f>
+        <f t="shared" si="8"/>
         <v>140</v>
       </c>
       <c r="S511" s="24">
@@ -46366,7 +46361,7 @@
         <v>0</v>
       </c>
       <c r="R512" s="23">
-        <f>SUM(O512:Q512)</f>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="S512" s="22">
@@ -46429,7 +46424,7 @@
         <v>0</v>
       </c>
       <c r="R513" s="25">
-        <f>SUM(O513:Q513)</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="S513" s="24">
@@ -46492,7 +46487,7 @@
         <v>0</v>
       </c>
       <c r="R514" s="23">
-        <f>SUM(O514:Q514)</f>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="S514" s="22">
@@ -46555,7 +46550,7 @@
         <v>41</v>
       </c>
       <c r="R515" s="25">
-        <f>SUM(O515:Q515)</f>
+        <f t="shared" si="8"/>
         <v>41</v>
       </c>
       <c r="S515" s="24">
@@ -46618,7 +46613,7 @@
         <v>0</v>
       </c>
       <c r="R516" s="23">
-        <f>SUM(O516:Q516)</f>
+        <f t="shared" si="8"/>
         <v>96</v>
       </c>
       <c r="S516" s="22">
@@ -46682,7 +46677,7 @@
         <v>0</v>
       </c>
       <c r="R517" s="25">
-        <f>SUM(O517:Q517)</f>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="S517" s="24">
@@ -46745,7 +46740,7 @@
         <v>0</v>
       </c>
       <c r="R518" s="23">
-        <f>SUM(O518:Q518)</f>
+        <f t="shared" si="8"/>
         <v>47</v>
       </c>
       <c r="S518" s="22">
@@ -46808,7 +46803,7 @@
         <v>0</v>
       </c>
       <c r="R519" s="25">
-        <f>SUM(O519:Q519)</f>
+        <f t="shared" si="8"/>
         <v>37</v>
       </c>
       <c r="S519" s="24">
@@ -46871,7 +46866,7 @@
         <v>0</v>
       </c>
       <c r="R520" s="23">
-        <f>SUM(O520:Q520)</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="S520" s="22">
@@ -46934,7 +46929,7 @@
         <v>0</v>
       </c>
       <c r="R521" s="25">
-        <f>SUM(O521:Q521)</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="S521" s="24">
@@ -46997,7 +46992,7 @@
         <v>0</v>
       </c>
       <c r="R522" s="23">
-        <f>SUM(O522:Q522)</f>
+        <f t="shared" ref="R522:R585" si="9">SUM(O522:Q522)</f>
         <v>0</v>
       </c>
       <c r="S522" s="22">
@@ -47060,7 +47055,7 @@
         <v>0</v>
       </c>
       <c r="R523" s="25">
-        <f>SUM(O523:Q523)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S523" s="24">
@@ -47124,7 +47119,7 @@
         <v>0</v>
       </c>
       <c r="R524" s="23">
-        <f>SUM(O524:Q524)</f>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="S524" s="22"/>
@@ -47183,7 +47178,7 @@
         <v>0</v>
       </c>
       <c r="R525" s="25">
-        <f>SUM(O525:Q525)</f>
+        <f t="shared" si="9"/>
         <v>46</v>
       </c>
       <c r="S525" s="24">
@@ -47246,7 +47241,7 @@
         <v>0</v>
       </c>
       <c r="R526" s="23">
-        <f>SUM(O526:Q526)</f>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="S526" s="22">
@@ -47301,7 +47296,7 @@
         <v>0</v>
       </c>
       <c r="R527" s="25">
-        <f>SUM(O527:Q527)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S527" s="24"/>
@@ -47362,7 +47357,7 @@
         <v>0</v>
       </c>
       <c r="R528" s="23">
-        <f>SUM(O528:Q528)</f>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="S528" s="22">
@@ -47425,7 +47420,7 @@
         <v>1</v>
       </c>
       <c r="R529" s="25">
-        <f>SUM(O529:Q529)</f>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="S529" s="24">
@@ -47486,7 +47481,7 @@
         <v>23</v>
       </c>
       <c r="R530" s="23">
-        <f>SUM(O530:Q530)</f>
+        <f t="shared" si="9"/>
         <v>138</v>
       </c>
       <c r="S530" s="22">
@@ -47549,7 +47544,7 @@
         <v>0</v>
       </c>
       <c r="R531" s="25">
-        <f>SUM(O531:Q531)</f>
+        <f t="shared" si="9"/>
         <v>19</v>
       </c>
       <c r="S531" s="24">
@@ -47612,7 +47607,7 @@
         <v>0</v>
       </c>
       <c r="R532" s="23">
-        <f>SUM(O532:Q532)</f>
+        <f t="shared" si="9"/>
         <v>118</v>
       </c>
       <c r="S532" s="22">
@@ -47676,7 +47671,7 @@
         <v>0</v>
       </c>
       <c r="R533" s="25">
-        <f>SUM(O533:Q533)</f>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="S533" s="24">
@@ -47739,7 +47734,7 @@
         <v>49</v>
       </c>
       <c r="R534" s="23">
-        <f>SUM(O534:Q534)</f>
+        <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="S534" s="22">
@@ -47803,7 +47798,7 @@
         <v>94</v>
       </c>
       <c r="R535" s="25">
-        <f>SUM(O535:Q535)</f>
+        <f t="shared" si="9"/>
         <v>94</v>
       </c>
       <c r="S535" s="24">
@@ -47858,7 +47853,7 @@
         <v>0</v>
       </c>
       <c r="R536" s="23">
-        <f>SUM(O536:Q536)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S536" s="22"/>
@@ -47917,7 +47912,7 @@
         <v>0</v>
       </c>
       <c r="R537" s="25">
-        <f>SUM(O537:Q537)</f>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="S537" s="24">
@@ -47974,7 +47969,7 @@
         <v>0</v>
       </c>
       <c r="R538" s="23">
-        <f>SUM(O538:Q538)</f>
+        <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="S538" s="22"/>
@@ -48033,7 +48028,7 @@
         <v>0</v>
       </c>
       <c r="R539" s="25">
-        <f>SUM(O539:Q539)</f>
+        <f t="shared" si="9"/>
         <v>26</v>
       </c>
       <c r="S539" s="24">
@@ -48096,7 +48091,7 @@
         <v>0</v>
       </c>
       <c r="R540" s="23">
-        <f>SUM(O540:Q540)</f>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
       <c r="S540" s="22">
@@ -48159,7 +48154,7 @@
         <v>0</v>
       </c>
       <c r="R541" s="25">
-        <f>SUM(O541:Q541)</f>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="S541" s="24">
@@ -48222,7 +48217,7 @@
         <v>30</v>
       </c>
       <c r="R542" s="23">
-        <f>SUM(O542:Q542)</f>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="S542" s="22">
@@ -48285,7 +48280,7 @@
         <v>0</v>
       </c>
       <c r="R543" s="25">
-        <f>SUM(O543:Q543)</f>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="S543" s="24">
@@ -48349,7 +48344,7 @@
         <v>0</v>
       </c>
       <c r="R544" s="23">
-        <f>SUM(O544:Q544)</f>
+        <f t="shared" si="9"/>
         <v>43</v>
       </c>
       <c r="S544" s="22">
@@ -48412,7 +48407,7 @@
         <v>0</v>
       </c>
       <c r="R545" s="25">
-        <f>SUM(O545:Q545)</f>
+        <f t="shared" si="9"/>
         <v>54</v>
       </c>
       <c r="S545" s="24">
@@ -48475,7 +48470,7 @@
         <v>0</v>
       </c>
       <c r="R546" s="23">
-        <f>SUM(O546:Q546)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="S546" s="22">
@@ -48538,7 +48533,7 @@
         <v>0</v>
       </c>
       <c r="R547" s="25">
-        <f>SUM(O547:Q547)</f>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="S547" s="24">
@@ -48601,7 +48596,7 @@
         <v>44</v>
       </c>
       <c r="R548" s="23">
-        <f>SUM(O548:Q548)</f>
+        <f t="shared" si="9"/>
         <v>44</v>
       </c>
       <c r="S548" s="22">
@@ -48664,7 +48659,7 @@
         <v>0</v>
       </c>
       <c r="R549" s="25">
-        <f>SUM(O549:Q549)</f>
+        <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="S549" s="24">
@@ -48727,7 +48722,7 @@
         <v>0</v>
       </c>
       <c r="R550" s="23">
-        <f>SUM(O550:Q550)</f>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="S550" s="22">
@@ -48790,7 +48785,7 @@
         <v>0</v>
       </c>
       <c r="R551" s="25">
-        <f>SUM(O551:Q551)</f>
+        <f t="shared" si="9"/>
         <v>27</v>
       </c>
       <c r="S551" s="24">
@@ -48853,7 +48848,7 @@
         <v>60</v>
       </c>
       <c r="R552" s="23">
-        <f>SUM(O552:Q552)</f>
+        <f t="shared" si="9"/>
         <v>114</v>
       </c>
       <c r="S552" s="22">
@@ -48916,7 +48911,7 @@
         <v>1</v>
       </c>
       <c r="R553" s="25">
-        <f>SUM(O553:Q553)</f>
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
       <c r="S553" s="24">
@@ -48979,7 +48974,7 @@
         <v>0</v>
       </c>
       <c r="R554" s="23">
-        <f>SUM(O554:Q554)</f>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="S554" s="22">
@@ -49043,7 +49038,7 @@
         <v>38</v>
       </c>
       <c r="R555" s="25">
-        <f>SUM(O555:Q555)</f>
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="S555" s="24">
@@ -49104,7 +49099,7 @@
         <v>97</v>
       </c>
       <c r="R556" s="23">
-        <f>SUM(O556:Q556)</f>
+        <f t="shared" si="9"/>
         <v>97</v>
       </c>
       <c r="S556" s="22">
@@ -49168,7 +49163,7 @@
         <v>38</v>
       </c>
       <c r="R557" s="25">
-        <f>SUM(O557:Q557)</f>
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="S557" s="24">
@@ -49231,7 +49226,7 @@
         <v>0</v>
       </c>
       <c r="R558" s="23">
-        <f>SUM(O558:Q558)</f>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
       <c r="S558" s="22">
@@ -49294,7 +49289,7 @@
         <v>0</v>
       </c>
       <c r="R559" s="25">
-        <f>SUM(O559:Q559)</f>
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
       <c r="S559" s="24">
@@ -49357,7 +49352,7 @@
         <v>0</v>
       </c>
       <c r="R560" s="23">
-        <f>SUM(O560:Q560)</f>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="S560" s="22">
@@ -49420,7 +49415,7 @@
         <v>0</v>
       </c>
       <c r="R561" s="25">
-        <f>SUM(O561:Q561)</f>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="S561" s="24">
@@ -49483,7 +49478,7 @@
         <v>79</v>
       </c>
       <c r="R562" s="23">
-        <f>SUM(O562:Q562)</f>
+        <f t="shared" si="9"/>
         <v>250</v>
       </c>
       <c r="S562" s="22">
@@ -49546,7 +49541,7 @@
         <v>0</v>
       </c>
       <c r="R563" s="25">
-        <f>SUM(O563:Q563)</f>
+        <f t="shared" si="9"/>
         <v>32</v>
       </c>
       <c r="S563" s="24">
@@ -49609,7 +49604,7 @@
         <v>0</v>
       </c>
       <c r="R564" s="23">
-        <f>SUM(O564:Q564)</f>
+        <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="S564" s="22">
@@ -49672,7 +49667,7 @@
         <v>0</v>
       </c>
       <c r="R565" s="25">
-        <f>SUM(O565:Q565)</f>
+        <f t="shared" si="9"/>
         <v>75</v>
       </c>
       <c r="S565" s="24">
@@ -49733,7 +49728,7 @@
         <v>0</v>
       </c>
       <c r="R566" s="23">
-        <f>SUM(O566:Q566)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="S566" s="22">
@@ -49796,7 +49791,7 @@
         <v>0</v>
       </c>
       <c r="R567" s="25">
-        <f>SUM(O567:Q567)</f>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="S567" s="24">
@@ -49859,7 +49854,7 @@
         <v>0</v>
       </c>
       <c r="R568" s="23">
-        <f>SUM(O568:Q568)</f>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="S568" s="22">
@@ -49922,7 +49917,7 @@
         <v>0</v>
       </c>
       <c r="R569" s="25">
-        <f>SUM(O569:Q569)</f>
+        <f t="shared" si="9"/>
         <v>48</v>
       </c>
       <c r="S569" s="24">
@@ -49985,7 +49980,7 @@
         <v>0</v>
       </c>
       <c r="R570" s="23">
-        <f>SUM(O570:Q570)</f>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="S570" s="22">
@@ -50046,7 +50041,7 @@
         <v>0</v>
       </c>
       <c r="R571" s="25">
-        <f>SUM(O571:Q571)</f>
+        <f t="shared" si="9"/>
         <v>170</v>
       </c>
       <c r="S571" s="24">
@@ -50107,7 +50102,7 @@
         <v>0</v>
       </c>
       <c r="R572" s="23">
-        <f>SUM(O572:Q572)</f>
+        <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="S572" s="22">
@@ -50168,7 +50163,7 @@
         <v>18</v>
       </c>
       <c r="R573" s="25">
-        <f>SUM(O573:Q573)</f>
+        <f t="shared" si="9"/>
         <v>176</v>
       </c>
       <c r="S573" s="24">
@@ -50227,7 +50222,7 @@
         <v>0</v>
       </c>
       <c r="R574" s="23">
-        <f>SUM(O574:Q574)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S574" s="22"/>
@@ -50288,7 +50283,7 @@
         <v>0</v>
       </c>
       <c r="R575" s="25">
-        <f>SUM(O575:Q575)</f>
+        <f t="shared" si="9"/>
         <v>44</v>
       </c>
       <c r="S575" s="24">
@@ -50352,7 +50347,7 @@
         <v>33</v>
       </c>
       <c r="R576" s="23">
-        <f>SUM(O576:Q576)</f>
+        <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="S576" s="22">
@@ -50413,7 +50408,7 @@
         <v>0</v>
       </c>
       <c r="R577" s="25">
-        <f>SUM(O577:Q577)</f>
+        <f t="shared" si="9"/>
         <v>170</v>
       </c>
       <c r="S577" s="24">
@@ -50472,7 +50467,7 @@
         <v>40</v>
       </c>
       <c r="R578" s="23">
-        <f>SUM(O578:Q578)</f>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="S578" s="22">
@@ -50531,7 +50526,7 @@
         <v>40</v>
       </c>
       <c r="R579" s="25">
-        <f>SUM(O579:Q579)</f>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="S579" s="24">
@@ -50594,7 +50589,7 @@
         <v>0</v>
       </c>
       <c r="R580" s="23">
-        <f>SUM(O580:Q580)</f>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="S580" s="22">
@@ -50657,7 +50652,7 @@
         <v>0</v>
       </c>
       <c r="R581" s="25">
-        <f>SUM(O581:Q581)</f>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="S581" s="24">
@@ -50720,7 +50715,7 @@
         <v>0</v>
       </c>
       <c r="R582" s="23">
-        <f>SUM(O582:Q582)</f>
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="S582" s="22">
@@ -50783,7 +50778,7 @@
         <v>0</v>
       </c>
       <c r="R583" s="25">
-        <f>SUM(O583:Q583)</f>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="S583" s="24">
@@ -50846,7 +50841,7 @@
         <v>31</v>
       </c>
       <c r="R584" s="23">
-        <f>SUM(O584:Q584)</f>
+        <f t="shared" si="9"/>
         <v>31</v>
       </c>
       <c r="S584" s="22">
@@ -50909,7 +50904,7 @@
         <v>4</v>
       </c>
       <c r="R585" s="25">
-        <f>SUM(O585:Q585)</f>
+        <f t="shared" si="9"/>
         <v>29</v>
       </c>
       <c r="S585" s="24">
@@ -50972,7 +50967,7 @@
         <v>30</v>
       </c>
       <c r="R586" s="23">
-        <f>SUM(O586:Q586)</f>
+        <f t="shared" ref="R586:R649" si="10">SUM(O586:Q586)</f>
         <v>30</v>
       </c>
       <c r="S586" s="22">
@@ -51035,7 +51030,7 @@
         <v>0</v>
       </c>
       <c r="R587" s="25">
-        <f>SUM(O587:Q587)</f>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="S587" s="24">
@@ -51098,7 +51093,7 @@
         <v>27</v>
       </c>
       <c r="R588" s="23">
-        <f>SUM(O588:Q588)</f>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="S588" s="22">
@@ -51161,7 +51156,7 @@
         <v>0</v>
       </c>
       <c r="R589" s="25">
-        <f>SUM(O589:Q589)</f>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="S589" s="24">
@@ -51224,7 +51219,7 @@
         <v>0</v>
       </c>
       <c r="R590" s="23">
-        <f>SUM(O590:Q590)</f>
+        <f t="shared" si="10"/>
         <v>33</v>
       </c>
       <c r="S590" s="22">
@@ -51287,7 +51282,7 @@
         <v>42</v>
       </c>
       <c r="R591" s="25">
-        <f>SUM(O591:Q591)</f>
+        <f t="shared" si="10"/>
         <v>42</v>
       </c>
       <c r="S591" s="24">
@@ -51350,7 +51345,7 @@
         <v>0</v>
       </c>
       <c r="R592" s="23">
-        <f>SUM(O592:Q592)</f>
+        <f t="shared" si="10"/>
         <v>22</v>
       </c>
       <c r="S592" s="22">
@@ -51413,7 +51408,7 @@
         <v>0</v>
       </c>
       <c r="R593" s="25">
-        <f>SUM(O593:Q593)</f>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="S593" s="24">
@@ -51476,7 +51471,7 @@
         <v>0</v>
       </c>
       <c r="R594" s="23">
-        <f>SUM(O594:Q594)</f>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="S594" s="22">
@@ -51537,7 +51532,7 @@
         <v>25</v>
       </c>
       <c r="R595" s="25">
-        <f>SUM(O595:Q595)</f>
+        <f t="shared" si="10"/>
         <v>25</v>
       </c>
       <c r="S595" s="24">
@@ -51600,7 +51595,7 @@
         <v>24</v>
       </c>
       <c r="R596" s="73">
-        <f>SUM(O596:Q596)</f>
+        <f t="shared" si="10"/>
         <v>24</v>
       </c>
       <c r="S596" s="70">
@@ -51663,7 +51658,7 @@
         <v>0</v>
       </c>
       <c r="R597" s="25">
-        <f>SUM(O597:Q597)</f>
+        <f t="shared" si="10"/>
         <v>46</v>
       </c>
       <c r="S597" s="24">
@@ -51726,7 +51721,7 @@
         <v>0</v>
       </c>
       <c r="R598" s="23">
-        <f>SUM(O598:Q598)</f>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
       <c r="S598" s="70">
@@ -51787,7 +51782,7 @@
         <v>0</v>
       </c>
       <c r="R599" s="25">
-        <f>SUM(O599:Q599)</f>
+        <f t="shared" si="10"/>
         <v>24</v>
       </c>
       <c r="S599" s="64">
@@ -51850,7 +51845,7 @@
         <v>0</v>
       </c>
       <c r="R600" s="23">
-        <f>SUM(O600:Q600)</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="S600" s="70">
@@ -51913,7 +51908,7 @@
         <v>0</v>
       </c>
       <c r="R601" s="25">
-        <f>SUM(O601:Q601)</f>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="S601" s="64">
@@ -51976,7 +51971,7 @@
         <v>0</v>
       </c>
       <c r="R602" s="23">
-        <f>SUM(O602:Q602)</f>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="S602" s="22">
@@ -52037,7 +52032,7 @@
         <v>0</v>
       </c>
       <c r="R603" s="25">
-        <f>SUM(O603:Q603)</f>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="S603" s="24">
@@ -52100,7 +52095,7 @@
         <v>0</v>
       </c>
       <c r="R604" s="23">
-        <f>SUM(O604:Q604)</f>
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="S604" s="22">
@@ -52163,7 +52158,7 @@
         <v>0</v>
       </c>
       <c r="R605" s="25">
-        <f>SUM(O605:Q605)</f>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="S605" s="24">
@@ -52224,7 +52219,7 @@
         <v>0</v>
       </c>
       <c r="R606" s="23">
-        <f>SUM(O606:Q606)</f>
+        <f t="shared" si="10"/>
         <v>170</v>
       </c>
       <c r="S606" s="22">
@@ -52285,7 +52280,7 @@
         <v>0</v>
       </c>
       <c r="R607" s="25">
-        <f>SUM(O607:Q607)</f>
+        <f t="shared" si="10"/>
         <v>170</v>
       </c>
       <c r="S607" s="24">
@@ -52348,7 +52343,7 @@
         <v>0</v>
       </c>
       <c r="R608" s="23">
-        <f>SUM(O608:Q608)</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="S608" s="22">
@@ -52411,7 +52406,7 @@
         <v>0</v>
       </c>
       <c r="R609" s="25">
-        <f>SUM(O609:Q609)</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="S609" s="24">
@@ -52472,7 +52467,7 @@
         <v>31</v>
       </c>
       <c r="R610" s="23">
-        <f>SUM(O610:Q610)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="S610" s="22">
@@ -52535,7 +52530,7 @@
         <v>0</v>
       </c>
       <c r="R611" s="25">
-        <f>SUM(O611:Q611)</f>
+        <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="S611" s="24">
@@ -52596,7 +52591,7 @@
         <v>0</v>
       </c>
       <c r="R612" s="23">
-        <f>SUM(O612:Q612)</f>
+        <f t="shared" si="10"/>
         <v>100</v>
       </c>
       <c r="S612" s="22">
@@ -52657,7 +52652,7 @@
         <v>0</v>
       </c>
       <c r="R613" s="25">
-        <f>SUM(O613:Q613)</f>
+        <f t="shared" si="10"/>
         <v>114</v>
       </c>
       <c r="S613" s="24">
@@ -52720,7 +52715,7 @@
         <v>0</v>
       </c>
       <c r="R614" s="23">
-        <f>SUM(O614:Q614)</f>
+        <f t="shared" si="10"/>
         <v>491</v>
       </c>
       <c r="S614" s="22">
@@ -52783,7 +52778,7 @@
         <v>0</v>
       </c>
       <c r="R615" s="25">
-        <f>SUM(O615:Q615)</f>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="S615" s="24">
@@ -52844,7 +52839,7 @@
         <v>0</v>
       </c>
       <c r="R616" s="23">
-        <f>SUM(O616:Q616)</f>
+        <f t="shared" si="10"/>
         <v>63</v>
       </c>
       <c r="S616" s="22">
@@ -52907,7 +52902,7 @@
         <v>0</v>
       </c>
       <c r="R617" s="25">
-        <f>SUM(O617:Q617)</f>
+        <f t="shared" si="10"/>
         <v>42</v>
       </c>
       <c r="S617" s="24">
@@ -52970,7 +52965,7 @@
         <v>0</v>
       </c>
       <c r="R618" s="23">
-        <f>SUM(O618:Q618)</f>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="S618" s="22">
@@ -53033,7 +53028,7 @@
         <v>0</v>
       </c>
       <c r="R619" s="25">
-        <f>SUM(O619:Q619)</f>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="S619" s="24">
@@ -53094,7 +53089,7 @@
         <v>0</v>
       </c>
       <c r="R620" s="23">
-        <f>SUM(O620:Q620)</f>
+        <f t="shared" si="10"/>
         <v>47</v>
       </c>
       <c r="S620" s="22">
@@ -53155,7 +53150,7 @@
         <v>0</v>
       </c>
       <c r="R621" s="25">
-        <f>SUM(O621:Q621)</f>
+        <f t="shared" si="10"/>
         <v>23</v>
       </c>
       <c r="S621" s="24">
@@ -53216,7 +53211,7 @@
         <v>0</v>
       </c>
       <c r="R622" s="23">
-        <f>SUM(O622:Q622)</f>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="S622" s="22">
@@ -53279,7 +53274,7 @@
         <v>0</v>
       </c>
       <c r="R623" s="25">
-        <f>SUM(O623:Q623)</f>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="S623" s="24">
@@ -53338,7 +53333,7 @@
         <v>88</v>
       </c>
       <c r="R624" s="23">
-        <f>SUM(O624:Q624)</f>
+        <f t="shared" si="10"/>
         <v>88</v>
       </c>
       <c r="S624" s="22">
@@ -53399,7 +53394,7 @@
         <v>0</v>
       </c>
       <c r="R625" s="25">
-        <f>SUM(O625:Q625)</f>
+        <f t="shared" si="10"/>
         <v>33</v>
       </c>
       <c r="S625" s="24">
@@ -53458,7 +53453,7 @@
         <v>128</v>
       </c>
       <c r="R626" s="23">
-        <f>SUM(O626:Q626)</f>
+        <f t="shared" si="10"/>
         <v>128</v>
       </c>
       <c r="S626" s="22">
@@ -53519,7 +53514,7 @@
         <v>0</v>
       </c>
       <c r="R627" s="25">
-        <f>SUM(O627:Q627)</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="S627" s="24">
@@ -53580,7 +53575,7 @@
         <v>0</v>
       </c>
       <c r="R628" s="23">
-        <f>SUM(O628:Q628)</f>
+        <f t="shared" si="10"/>
         <v>23</v>
       </c>
       <c r="S628" s="22" t="s">
@@ -53643,7 +53638,7 @@
         <v>0</v>
       </c>
       <c r="R629" s="25">
-        <f>SUM(O629:Q629)</f>
+        <f t="shared" si="10"/>
         <v>49</v>
       </c>
       <c r="S629" s="24">
@@ -53704,7 +53699,7 @@
         <v>46</v>
       </c>
       <c r="R630" s="23">
-        <f>SUM(O630:Q630)</f>
+        <f t="shared" si="10"/>
         <v>228</v>
       </c>
       <c r="S630" s="22">
@@ -53765,7 +53760,7 @@
         <v>0</v>
       </c>
       <c r="R631" s="25">
-        <f>SUM(O631:Q631)</f>
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="S631" s="24">
@@ -53826,7 +53821,7 @@
         <v>0</v>
       </c>
       <c r="R632" s="23">
-        <f>SUM(O632:Q632)</f>
+        <f t="shared" si="10"/>
         <v>16</v>
       </c>
       <c r="S632" s="22">
@@ -53887,7 +53882,7 @@
         <v>0</v>
       </c>
       <c r="R633" s="25">
-        <f>SUM(O633:Q633)</f>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="S633" s="24">
@@ -53950,7 +53945,7 @@
         <v>0</v>
       </c>
       <c r="R634" s="23">
-        <f>SUM(O634:Q634)</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="S634" s="22">
@@ -54011,7 +54006,7 @@
         <v>0</v>
       </c>
       <c r="R635" s="25">
-        <f>SUM(O635:Q635)</f>
+        <f t="shared" si="10"/>
         <v>70</v>
       </c>
       <c r="S635" s="24">
@@ -54072,7 +54067,7 @@
         <v>0</v>
       </c>
       <c r="R636" s="23">
-        <f>SUM(O636:Q636)</f>
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="S636" s="22">
@@ -54133,7 +54128,7 @@
         <v>30</v>
       </c>
       <c r="R637" s="25">
-        <f>SUM(O637:Q637)</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="S637" s="24">
@@ -54196,7 +54191,7 @@
         <v>0</v>
       </c>
       <c r="R638" s="23">
-        <f>SUM(O638:Q638)</f>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="S638" s="22" t="s">
@@ -54259,7 +54254,7 @@
         <v>40</v>
       </c>
       <c r="R639" s="25">
-        <f>SUM(O639:Q639)</f>
+        <f t="shared" si="10"/>
         <v>179</v>
       </c>
       <c r="S639" s="24">
@@ -54316,7 +54311,7 @@
         <v>0</v>
       </c>
       <c r="R640" s="23">
-        <f>SUM(O640:Q640)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S640" s="22">
@@ -54436,7 +54431,7 @@
         <v>33</v>
       </c>
       <c r="R642" s="23">
-        <f>SUM(O642:Q642)</f>
+        <f t="shared" ref="R642:R649" si="11">SUM(O642:Q642)</f>
         <v>33</v>
       </c>
       <c r="S642" s="22">
@@ -54495,7 +54490,7 @@
         <v>39</v>
       </c>
       <c r="R643" s="25">
-        <f>SUM(O643:Q643)</f>
+        <f t="shared" si="11"/>
         <v>39</v>
       </c>
       <c r="S643" s="24">
@@ -54557,7 +54552,7 @@
         <v>39</v>
       </c>
       <c r="R644" s="23">
-        <f>SUM(O644:Q644)</f>
+        <f t="shared" si="11"/>
         <v>39</v>
       </c>
       <c r="S644" s="22">
@@ -54618,7 +54613,7 @@
         <v>0</v>
       </c>
       <c r="R645" s="25">
-        <f>SUM(O645:Q645)</f>
+        <f t="shared" si="11"/>
         <v>170</v>
       </c>
       <c r="S645" s="24">
@@ -54681,7 +54676,7 @@
         <v>0</v>
       </c>
       <c r="R646" s="23">
-        <f>SUM(O646:Q646)</f>
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
       <c r="S646" s="22">
@@ -54742,7 +54737,7 @@
         <v>0</v>
       </c>
       <c r="R647" s="25">
-        <f>SUM(O647:Q647)</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="S647" s="24">
@@ -54803,7 +54798,7 @@
         <v>0</v>
       </c>
       <c r="R648" s="23">
-        <f>SUM(O648:Q648)</f>
+        <f t="shared" si="11"/>
         <v>45</v>
       </c>
       <c r="S648" s="22">
@@ -54862,7 +54857,7 @@
         <v>0</v>
       </c>
       <c r="R649" s="25">
-        <f>SUM(O649:Q649)</f>
+        <f t="shared" si="11"/>
         <v>72</v>
       </c>
       <c r="S649" s="24">
@@ -55663,7 +55658,7 @@
         <v>0</v>
       </c>
       <c r="R662" s="23">
-        <f>SUM(O662:Q662)</f>
+        <f t="shared" ref="R662:R668" si="12">SUM(O662:Q662)</f>
         <v>20</v>
       </c>
       <c r="S662" s="22">
@@ -55727,7 +55722,7 @@
         <v>0</v>
       </c>
       <c r="R663" s="25">
-        <f>SUM(O663:Q663)</f>
+        <f t="shared" si="12"/>
         <v>19</v>
       </c>
       <c r="S663" s="24">
@@ -55791,7 +55786,7 @@
         <v>0</v>
       </c>
       <c r="R664" s="23">
-        <f>SUM(O664:Q664)</f>
+        <f t="shared" si="12"/>
         <v>33</v>
       </c>
       <c r="S664" s="22">
@@ -55855,7 +55850,7 @@
         <v>0</v>
       </c>
       <c r="R665" s="25">
-        <f>SUM(O665:Q665)</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="S665" s="24">
@@ -55919,7 +55914,7 @@
         <v>0</v>
       </c>
       <c r="R666" s="23">
-        <f>SUM(O666:Q666)</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="S666" s="22">
@@ -55981,7 +55976,7 @@
         <v>14</v>
       </c>
       <c r="R667" s="25">
-        <f>SUM(O667:Q667)</f>
+        <f t="shared" si="12"/>
         <v>127</v>
       </c>
       <c r="S667" s="24">
@@ -56043,7 +56038,7 @@
         <v>34</v>
       </c>
       <c r="R668" s="23">
-        <f>SUM(O668:Q668)</f>
+        <f t="shared" si="12"/>
         <v>192</v>
       </c>
       <c r="S668" s="22">
@@ -56233,7 +56228,7 @@
         <v>0</v>
       </c>
       <c r="R671" s="25">
-        <f>SUM(O671:Q671)</f>
+        <f t="shared" ref="R671:R684" si="13">SUM(O671:Q671)</f>
         <v>22</v>
       </c>
       <c r="S671" s="24">
@@ -56297,7 +56292,7 @@
         <v>0</v>
       </c>
       <c r="R672" s="178">
-        <f>SUM(O672:Q672)</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="S672" s="172">
@@ -56349,7 +56344,7 @@
       <c r="P673" s="25"/>
       <c r="Q673" s="25"/>
       <c r="R673" s="25">
-        <f>SUM(O673:Q673)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S673" s="24"/>
@@ -56407,7 +56402,7 @@
         <v>80</v>
       </c>
       <c r="R674" s="23">
-        <f>SUM(O674:Q674)</f>
+        <f t="shared" si="13"/>
         <v>80</v>
       </c>
       <c r="S674" s="22">
@@ -56467,7 +56462,7 @@
         <v>80</v>
       </c>
       <c r="R675" s="23">
-        <f>SUM(O675:Q675)</f>
+        <f t="shared" si="13"/>
         <v>80</v>
       </c>
       <c r="S675" s="22">
@@ -56521,7 +56516,7 @@
       <c r="P676" s="25"/>
       <c r="Q676" s="25"/>
       <c r="R676" s="25">
-        <f>SUM(O676:Q676)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S676" s="24">
@@ -56583,7 +56578,7 @@
         <v>5</v>
       </c>
       <c r="R677" s="193">
-        <f>SUM(O677:Q677)</f>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S677" s="186">
@@ -56647,7 +56642,7 @@
         <v>0</v>
       </c>
       <c r="R678" s="63">
-        <f>SUM(O678:Q678)</f>
+        <f t="shared" si="13"/>
         <v>17</v>
       </c>
       <c r="S678" s="64">
@@ -56711,7 +56706,7 @@
         <v>0</v>
       </c>
       <c r="R679" s="185">
-        <f>SUM(O679:Q679)</f>
+        <f t="shared" si="13"/>
         <v>32</v>
       </c>
       <c r="S679" s="180">
@@ -56765,7 +56760,7 @@
       <c r="P680" s="73"/>
       <c r="Q680" s="73"/>
       <c r="R680" s="73">
-        <f>SUM(O680:Q680)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S680" s="70">
@@ -56819,7 +56814,7 @@
       <c r="P681" s="193"/>
       <c r="Q681" s="193"/>
       <c r="R681" s="193">
-        <f>SUM(O681:Q681)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S681" s="186">
@@ -56873,7 +56868,7 @@
       <c r="P682" s="185"/>
       <c r="Q682" s="185"/>
       <c r="R682" s="185">
-        <f>SUM(O682:Q682)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S682" s="180">
@@ -56927,7 +56922,7 @@
       <c r="P683" s="193"/>
       <c r="Q683" s="193"/>
       <c r="R683" s="193">
-        <f>SUM(O683:Q683)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S683" s="186">
@@ -56977,7 +56972,7 @@
       <c r="P684" s="73"/>
       <c r="Q684" s="73"/>
       <c r="R684" s="73">
-        <f>SUM(O684:Q684)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S684" s="70">
@@ -57031,7 +57026,7 @@
       <c r="P685" s="217"/>
       <c r="Q685" s="217"/>
       <c r="R685" s="217">
-        <f t="shared" ref="R685:R747" si="0">IF(B685="","",SUM(O685:Q685))</f>
+        <f t="shared" ref="R685:R747" si="14">IF(B685="","",SUM(O685:Q685))</f>
         <v>0</v>
       </c>
       <c r="S685" s="210">
@@ -57088,7 +57083,7 @@
       <c r="P686" s="225"/>
       <c r="Q686" s="225"/>
       <c r="R686" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S686" s="219">
@@ -57143,7 +57138,7 @@
       <c r="P687" s="217"/>
       <c r="Q687" s="217"/>
       <c r="R687" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S687" s="210">
@@ -57200,7 +57195,7 @@
       <c r="P688" s="225"/>
       <c r="Q688" s="225"/>
       <c r="R688" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S688" s="219">
@@ -57265,7 +57260,7 @@
         <v>0</v>
       </c>
       <c r="R689" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>22</v>
       </c>
       <c r="S689" s="210">
@@ -57322,7 +57317,7 @@
       <c r="P690" s="225"/>
       <c r="Q690" s="225"/>
       <c r="R690" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S690" s="219">
@@ -57387,7 +57382,7 @@
         <v>0</v>
       </c>
       <c r="R691" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>21</v>
       </c>
       <c r="S691" s="210">
@@ -57452,7 +57447,7 @@
         <v>0</v>
       </c>
       <c r="R692" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="S692" s="219">
@@ -57517,7 +57512,7 @@
         <v>0</v>
       </c>
       <c r="R693" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="S693" s="210">
@@ -57570,7 +57565,7 @@
       <c r="P694" s="225"/>
       <c r="Q694" s="225"/>
       <c r="R694" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S694" s="219">
@@ -57623,7 +57618,7 @@
       <c r="P695" s="217"/>
       <c r="Q695" s="217"/>
       <c r="R695" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S695" s="210">
@@ -57680,7 +57675,7 @@
         <v>25</v>
       </c>
       <c r="R696" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="S696" s="219">
@@ -57741,7 +57736,7 @@
         <v>50</v>
       </c>
       <c r="R697" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>50</v>
       </c>
       <c r="S697" s="210">
@@ -57794,7 +57789,7 @@
       <c r="P698" s="225"/>
       <c r="Q698" s="225"/>
       <c r="R698" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S698" s="219">
@@ -57849,7 +57844,7 @@
       <c r="P699" s="217"/>
       <c r="Q699" s="217"/>
       <c r="R699" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S699" s="210">
@@ -57904,7 +57899,7 @@
       <c r="P700" s="225"/>
       <c r="Q700" s="225"/>
       <c r="R700" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S700" s="219">
@@ -57959,7 +57954,7 @@
       <c r="P701" s="217"/>
       <c r="Q701" s="217"/>
       <c r="R701" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S701" s="210">
@@ -58010,7 +58005,7 @@
       <c r="P702" s="225"/>
       <c r="Q702" s="225"/>
       <c r="R702" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S702" s="219">
@@ -58024,11 +58019,17 @@
     <row r="703" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="209" t="str">
         <f>IF(B703="","",B703&amp;"-"&amp;TEXT(COUNTIF(B$2:B703,B703),"000"))</f>
-        <v/>
-      </c>
-      <c r="B703" s="210"/>
-      <c r="C703" s="219"/>
-      <c r="D703" s="210"/>
+        <v>2026-047</v>
+      </c>
+      <c r="B703" s="210">
+        <v>2026</v>
+      </c>
+      <c r="C703" s="219" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D703" s="210" t="s">
+        <v>2954</v>
+      </c>
       <c r="E703" s="211"/>
       <c r="F703" s="212"/>
       <c r="G703" s="209"/>
@@ -58042,9 +58043,9 @@
       <c r="O703" s="217"/>
       <c r="P703" s="217"/>
       <c r="Q703" s="217"/>
-      <c r="R703" s="217" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="R703" s="217">
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="S703" s="210"/>
       <c r="T703" s="209"/>
@@ -58072,7 +58073,7 @@
       <c r="P704" s="225"/>
       <c r="Q704" s="225"/>
       <c r="R704" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S704" s="219"/>
@@ -58101,7 +58102,7 @@
       <c r="P705" s="217"/>
       <c r="Q705" s="217"/>
       <c r="R705" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S705" s="210"/>
@@ -58130,7 +58131,7 @@
       <c r="P706" s="225"/>
       <c r="Q706" s="225"/>
       <c r="R706" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S706" s="219"/>
@@ -58159,7 +58160,7 @@
       <c r="P707" s="217"/>
       <c r="Q707" s="217"/>
       <c r="R707" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S707" s="210"/>
@@ -58188,7 +58189,7 @@
       <c r="P708" s="225"/>
       <c r="Q708" s="225"/>
       <c r="R708" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S708" s="219"/>
@@ -58217,7 +58218,7 @@
       <c r="P709" s="217"/>
       <c r="Q709" s="217"/>
       <c r="R709" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S709" s="210"/>
@@ -58246,7 +58247,7 @@
       <c r="P710" s="225"/>
       <c r="Q710" s="225"/>
       <c r="R710" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S710" s="219"/>
@@ -58275,7 +58276,7 @@
       <c r="P711" s="217"/>
       <c r="Q711" s="217"/>
       <c r="R711" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S711" s="210"/>
@@ -58304,7 +58305,7 @@
       <c r="P712" s="225"/>
       <c r="Q712" s="225"/>
       <c r="R712" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S712" s="219"/>
@@ -58333,7 +58334,7 @@
       <c r="P713" s="217"/>
       <c r="Q713" s="217"/>
       <c r="R713" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S713" s="210"/>
@@ -58362,7 +58363,7 @@
       <c r="P714" s="225"/>
       <c r="Q714" s="225"/>
       <c r="R714" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S714" s="219"/>
@@ -58391,7 +58392,7 @@
       <c r="P715" s="217"/>
       <c r="Q715" s="217"/>
       <c r="R715" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S715" s="210"/>
@@ -58420,7 +58421,7 @@
       <c r="P716" s="225"/>
       <c r="Q716" s="225"/>
       <c r="R716" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S716" s="219"/>
@@ -58449,7 +58450,7 @@
       <c r="P717" s="217"/>
       <c r="Q717" s="217"/>
       <c r="R717" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S717" s="210"/>
@@ -58478,7 +58479,7 @@
       <c r="P718" s="225"/>
       <c r="Q718" s="225"/>
       <c r="R718" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S718" s="219"/>
@@ -58507,7 +58508,7 @@
       <c r="P719" s="217"/>
       <c r="Q719" s="217"/>
       <c r="R719" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S719" s="210"/>
@@ -58536,7 +58537,7 @@
       <c r="P720" s="225"/>
       <c r="Q720" s="225"/>
       <c r="R720" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S720" s="219"/>
@@ -58565,7 +58566,7 @@
       <c r="P721" s="217"/>
       <c r="Q721" s="217"/>
       <c r="R721" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S721" s="210"/>
@@ -58594,7 +58595,7 @@
       <c r="P722" s="225"/>
       <c r="Q722" s="225"/>
       <c r="R722" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S722" s="219"/>
@@ -58623,7 +58624,7 @@
       <c r="P723" s="217"/>
       <c r="Q723" s="217"/>
       <c r="R723" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S723" s="210"/>
@@ -58652,7 +58653,7 @@
       <c r="P724" s="225"/>
       <c r="Q724" s="225"/>
       <c r="R724" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S724" s="219"/>
@@ -58681,7 +58682,7 @@
       <c r="P725" s="217"/>
       <c r="Q725" s="217"/>
       <c r="R725" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S725" s="210"/>
@@ -58710,7 +58711,7 @@
       <c r="P726" s="225"/>
       <c r="Q726" s="225"/>
       <c r="R726" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S726" s="219"/>
@@ -58739,7 +58740,7 @@
       <c r="P727" s="217"/>
       <c r="Q727" s="217"/>
       <c r="R727" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S727" s="210"/>
@@ -58768,7 +58769,7 @@
       <c r="P728" s="225"/>
       <c r="Q728" s="225"/>
       <c r="R728" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S728" s="219"/>
@@ -58797,7 +58798,7 @@
       <c r="P729" s="217"/>
       <c r="Q729" s="217"/>
       <c r="R729" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S729" s="210"/>
@@ -58826,7 +58827,7 @@
       <c r="P730" s="225"/>
       <c r="Q730" s="225"/>
       <c r="R730" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S730" s="219"/>
@@ -58855,7 +58856,7 @@
       <c r="P731" s="217"/>
       <c r="Q731" s="217"/>
       <c r="R731" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S731" s="210"/>
@@ -58884,7 +58885,7 @@
       <c r="P732" s="225"/>
       <c r="Q732" s="225"/>
       <c r="R732" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S732" s="219"/>
@@ -58913,7 +58914,7 @@
       <c r="P733" s="217"/>
       <c r="Q733" s="217"/>
       <c r="R733" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S733" s="210"/>
@@ -58942,7 +58943,7 @@
       <c r="P734" s="225"/>
       <c r="Q734" s="225"/>
       <c r="R734" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S734" s="219"/>
@@ -58971,7 +58972,7 @@
       <c r="P735" s="217"/>
       <c r="Q735" s="217"/>
       <c r="R735" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S735" s="210"/>
@@ -59000,7 +59001,7 @@
       <c r="P736" s="225"/>
       <c r="Q736" s="225"/>
       <c r="R736" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S736" s="219"/>
@@ -59029,7 +59030,7 @@
       <c r="P737" s="217"/>
       <c r="Q737" s="217"/>
       <c r="R737" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S737" s="210"/>
@@ -59058,7 +59059,7 @@
       <c r="P738" s="225"/>
       <c r="Q738" s="225"/>
       <c r="R738" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S738" s="219"/>
@@ -59087,7 +59088,7 @@
       <c r="P739" s="217"/>
       <c r="Q739" s="217"/>
       <c r="R739" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S739" s="210"/>
@@ -59116,7 +59117,7 @@
       <c r="P740" s="225"/>
       <c r="Q740" s="225"/>
       <c r="R740" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S740" s="219"/>
@@ -59145,7 +59146,7 @@
       <c r="P741" s="217"/>
       <c r="Q741" s="217"/>
       <c r="R741" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S741" s="210"/>
@@ -59174,7 +59175,7 @@
       <c r="P742" s="225"/>
       <c r="Q742" s="225"/>
       <c r="R742" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S742" s="219"/>
@@ -59203,7 +59204,7 @@
       <c r="P743" s="217"/>
       <c r="Q743" s="217"/>
       <c r="R743" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S743" s="210"/>
@@ -59232,7 +59233,7 @@
       <c r="P744" s="225"/>
       <c r="Q744" s="225"/>
       <c r="R744" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S744" s="219"/>
@@ -59261,7 +59262,7 @@
       <c r="P745" s="217"/>
       <c r="Q745" s="217"/>
       <c r="R745" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S745" s="210"/>
@@ -59290,7 +59291,7 @@
       <c r="P746" s="225"/>
       <c r="Q746" s="225"/>
       <c r="R746" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S746" s="219"/>
@@ -59319,7 +59320,7 @@
       <c r="P747" s="217"/>
       <c r="Q747" s="217"/>
       <c r="R747" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S747" s="210"/>
@@ -59348,7 +59349,7 @@
       <c r="P748" s="225"/>
       <c r="Q748" s="225"/>
       <c r="R748" s="225" t="str">
-        <f t="shared" ref="R748" si="1">IF(B748="","",SUM(O748:Q748))</f>
+        <f t="shared" ref="R748" si="15">IF(B748="","",SUM(O748:Q748))</f>
         <v/>
       </c>
       <c r="S748" s="219"/>
@@ -64612,7 +64613,7 @@
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A5" s="115">
         <f>COUNTIF('Ações InCompany'!B:B,2026)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" s="116" t="s">
         <v>2878</v>
@@ -64626,7 +64627,7 @@
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
@@ -64783,7 +64784,7 @@
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.22500000000000001</v>
+        <v>0.21951219512195122</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64804,7 +64805,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>7.4999999999999997E-2</v>
+        <v>7.3170731707317069E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64825,7 +64826,7 @@
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>0.12195121951219512</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64846,7 +64847,7 @@
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>0.05</v>
+        <v>4.878048780487805E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64867,7 +64868,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>0.05</v>
+        <v>4.878048780487805E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64888,7 +64889,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.17499999999999999</v>
+        <v>0.17073170731707318</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64909,7 +64910,7 @@
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>7.4999999999999997E-2</v>
+        <v>7.3170731707317069E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64930,7 +64931,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>2.5000000000000001E-2</v>
+        <v>2.4390243902439025E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64951,7 +64952,7 @@
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.15</v>
+        <v>0.14634146341463414</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64993,7 +64994,7 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>0.05</v>
+        <v>4.878048780487805E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65006,15 +65007,15 @@
       </c>
       <c r="C44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" s="149">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="150">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.4390243902439025E-2</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65027,11 +65028,11 @@
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>
@@ -68348,6 +68349,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052D3A7BF04652843BCB50FE90745AA50" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ef6274641b2f7d621af528393bef14e5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe686eaa-0658-4f15-b230-9e46c4d089fd" xmlns:ns3="91ce1707-6d34-452b-b217-9734c03e6729" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fa87a3bcf42251a9fb9988d55372596" ns2:_="" ns3:_="">
     <xsd:import namespace="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
@@ -68548,27 +68569,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
+    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -68585,23 +68605,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
-    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4900" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19E94371-9B6D-47B8-9EDC-C12484E817E8}"/>
+  <xr:revisionPtr revIDLastSave="4912" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72871A91-D530-4445-908E-BE38934510C4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6521" uniqueCount="2955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6529" uniqueCount="2959">
   <si>
     <t>ID</t>
   </si>
@@ -9033,6 +9033,18 @@
   </si>
   <si>
     <t>6843/2026</t>
+  </si>
+  <si>
+    <t>Contratações de TIC com base na jurisprudência do TCDF</t>
+  </si>
+  <si>
+    <t>01/07/2026</t>
+  </si>
+  <si>
+    <t>31/12/2026</t>
+  </si>
+  <si>
+    <t>Flávio José Fonseca de Souza; Felipe da Costa Malaquias</t>
   </si>
 </sst>
 </file>
@@ -12944,7 +12956,7 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -12977,7 +12989,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -58030,13 +58042,27 @@
       <c r="D703" s="210" t="s">
         <v>2954</v>
       </c>
-      <c r="E703" s="211"/>
-      <c r="F703" s="212"/>
-      <c r="G703" s="209"/>
-      <c r="H703" s="213"/>
-      <c r="I703" s="213"/>
-      <c r="J703" s="213"/>
-      <c r="K703" s="210"/>
+      <c r="E703" s="211" t="s">
+        <v>2955</v>
+      </c>
+      <c r="F703" s="212" t="s">
+        <v>61</v>
+      </c>
+      <c r="G703" s="209" t="s">
+        <v>71</v>
+      </c>
+      <c r="H703" s="213" t="s">
+        <v>2800</v>
+      </c>
+      <c r="I703" s="213" t="s">
+        <v>2956</v>
+      </c>
+      <c r="J703" s="213" t="s">
+        <v>2957</v>
+      </c>
+      <c r="K703" s="210" t="s">
+        <v>34</v>
+      </c>
       <c r="L703" s="224"/>
       <c r="M703" s="215"/>
       <c r="N703" s="216"/>
@@ -58047,8 +58073,12 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S703" s="210"/>
-      <c r="T703" s="209"/>
+      <c r="S703" s="210">
+        <v>17</v>
+      </c>
+      <c r="T703" s="209" t="s">
+        <v>2958</v>
+      </c>
       <c r="U703" s="203"/>
     </row>
     <row r="704" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -59578,7 +59608,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="98" cm="1">
-        <f t="array" ref="A2:J69">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
+        <f t="array" ref="A2:J71">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
         <v>2026</v>
       </c>
       <c r="B2" s="98" t="str">
@@ -59742,7 +59772,7 @@
         <v>5.2</v>
       </c>
       <c r="L4" cm="1">
-        <f t="array" ref="L4:Q38">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
+        <f t="array" ref="L4:Q39">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
         <v>2026</v>
       </c>
       <c r="M4" t="str">
@@ -59769,7 +59799,7 @@
         <v>1</v>
       </c>
       <c r="T4" cm="1">
-        <f t="array" ref="T4:T39">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
+        <f t="array" ref="T4:T40">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
         <v>0</v>
       </c>
       <c r="X4" t="s">
@@ -62333,11 +62363,29 @@
       <c r="J39" s="163">
         <v>13.8</v>
       </c>
-      <c r="R39" t="str">
-        <v/>
-      </c>
-      <c r="S39" t="str">
-        <v/>
+      <c r="L39">
+        <v>2026</v>
+      </c>
+      <c r="M39" t="str">
+        <v>2026-047</v>
+      </c>
+      <c r="N39" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="O39" t="str">
+        <v>Contratações de TIC com base na jurisprudência do TCDF</v>
+      </c>
+      <c r="P39">
+        <v>17</v>
+      </c>
+      <c r="Q39" t="str">
+        <v>Flávio José Fonseca de Souza; Felipe da Costa Malaquias</v>
+      </c>
+      <c r="R39">
+        <v>2</v>
+      </c>
+      <c r="S39">
+        <v>70</v>
       </c>
       <c r="T39">
         <v>68</v>
@@ -62392,6 +62440,9 @@
       <c r="S40" t="str">
         <v/>
       </c>
+      <c r="T40">
+        <v>70</v>
+      </c>
       <c r="X40" t="s">
         <v>2873</v>
       </c>
@@ -63508,6 +63559,36 @@
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2026</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2026-047</v>
+      </c>
+      <c r="C70" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Contratações de TIC com base na jurisprudência do TCDF</v>
+      </c>
+      <c r="E70">
+        <v>17</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Flávio José Fonseca de Souza</v>
+      </c>
+      <c r="G70">
+        <v>2</v>
+      </c>
+      <c r="H70">
+        <v>17</v>
+      </c>
+      <c r="I70">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="J70">
+        <v>19.55</v>
+      </c>
       <c r="R70" t="str">
         <v/>
       </c>
@@ -63516,6 +63597,36 @@
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2026</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2026-047</v>
+      </c>
+      <c r="C71" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Contratações de TIC com base na jurisprudência do TCDF</v>
+      </c>
+      <c r="E71">
+        <v>17</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Felipe da Costa Malaquias</v>
+      </c>
+      <c r="G71">
+        <v>2</v>
+      </c>
+      <c r="H71">
+        <v>17</v>
+      </c>
+      <c r="I71">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="J71">
+        <v>19.55</v>
+      </c>
       <c r="R71" t="str">
         <v/>
       </c>
@@ -64776,15 +64887,15 @@
       </c>
       <c r="C33" s="127">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A33)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" s="117">
         <f t="shared" ref="D33:D44" si="0">B33+C33</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.21951219512195122</v>
+        <v>0.24390243902439024</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65007,15 +65118,15 @@
       </c>
       <c r="C44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="149">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="150">
         <f t="shared" si="1"/>
-        <v>2.4390243902439025E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65618,7 +65729,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="str" cm="1">
-        <f t="array" ref="A5:A34">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32),_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32)&lt;&gt;""))),"")</f>
+        <f t="array" ref="A5:A35">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32),_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32)&lt;&gt;""))),"")</f>
         <v>0</v>
       </c>
       <c r="B5" s="103">
@@ -65873,15 +65984,15 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
-        <v>Fernanda Viana de Souza</v>
+        <v>Felipe da Costa Malaquias</v>
       </c>
       <c r="B15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>3.09</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="D15" s="256">
         <f>IF($A15="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
@@ -65889,24 +66000,24 @@
       </c>
       <c r="E15" s="241">
         <f>IF($A15="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A15)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
-        <v>18.09</v>
+        <v>19.55</v>
       </c>
       <c r="F15" s="101">
         <f>IF($A15="","",COUNTIFS('GECC 2026'!F$2:F$200,$A15))</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
-        <v>Flávio José Fonseca de Souza</v>
+        <v>Fernanda Viana de Souza</v>
       </c>
       <c r="B16" s="103">
         <f>IF($A16="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A16))</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C16" s="103">
         <f>IF($A16="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A16))</f>
-        <v>2.4</v>
+        <v>3.09</v>
       </c>
       <c r="D16" s="256">
         <f>IF($A16="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A16))</f>
@@ -65914,24 +66025,24 @@
       </c>
       <c r="E16" s="241">
         <f>IF($A16="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A16)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A16))</f>
-        <v>10.4</v>
+        <v>18.09</v>
       </c>
       <c r="F16" s="101">
         <f>IF($A16="","",COUNTIFS('GECC 2026'!F$2:F$200,$A16))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
-        <v>Gabriel Heller</v>
+        <v>Flávio José Fonseca de Souza</v>
       </c>
       <c r="B17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>1.2</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="D17" s="256">
         <f>IF($A17="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
@@ -65939,7 +66050,7 @@
       </c>
       <c r="E17" s="241">
         <f>IF($A17="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A17)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
-        <v>37.200000000000003</v>
+        <v>29.950000000000003</v>
       </c>
       <c r="F17" s="101">
         <f>IF($A17="","",COUNTIFS('GECC 2026'!F$2:F$200,$A17))</f>
@@ -65948,15 +66059,15 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
-        <v>Gustavo Takahashi</v>
+        <v>Gabriel Heller</v>
       </c>
       <c r="B18" s="103">
         <f>IF($A18="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A18))</f>
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C18" s="103">
         <f>IF($A18="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A18))</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D18" s="256">
         <f>IF($A18="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A18))</f>
@@ -65964,24 +66075,24 @@
       </c>
       <c r="E18" s="241">
         <f>IF($A18="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A18)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A18))</f>
-        <v>25</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="F18" s="101">
         <f>IF($A18="","",COUNTIFS('GECC 2026'!F$2:F$200,$A18))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
-        <v>Hamilton de Jesus Lopes Neto</v>
+        <v>Gustavo Takahashi</v>
       </c>
       <c r="B19" s="103">
         <f>IF($A19="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A19))</f>
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C19" s="103">
         <f>IF($A19="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A19))</f>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D19" s="256">
         <f>IF($A19="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A19))</f>
@@ -65989,16 +66100,16 @@
       </c>
       <c r="E19" s="241">
         <f>IF($A19="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A19)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A19))</f>
-        <v>13.2</v>
+        <v>25</v>
       </c>
       <c r="F19" s="101">
         <f>IF($A19="","",COUNTIFS('GECC 2026'!F$2:F$200,$A19))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
-        <v>Indio Artiaga do Brasil Rabelo</v>
+        <v>Hamilton de Jesus Lopes Neto</v>
       </c>
       <c r="B20" s="103">
         <f>IF($A20="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A20))</f>
@@ -66006,7 +66117,7 @@
       </c>
       <c r="C20" s="103">
         <f>IF($A20="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A20))</f>
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="D20" s="256">
         <f>IF($A20="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A20))</f>
@@ -66014,7 +66125,7 @@
       </c>
       <c r="E20" s="241">
         <f>IF($A20="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A20)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A20))</f>
-        <v>15.6</v>
+        <v>13.2</v>
       </c>
       <c r="F20" s="101">
         <f>IF($A20="","",COUNTIFS('GECC 2026'!F$2:F$200,$A20))</f>
@@ -66023,15 +66134,15 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
-        <v>Leonardo de Melo</v>
+        <v>Indio Artiaga do Brasil Rabelo</v>
       </c>
       <c r="B21" s="103">
         <f>IF($A21="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A21))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C21" s="103">
         <f>IF($A21="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A21))</f>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="D21" s="256">
         <f>IF($A21="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A21))</f>
@@ -66039,7 +66150,7 @@
       </c>
       <c r="E21" s="241">
         <f>IF($A21="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A21)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A21))</f>
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="F21" s="101">
         <f>IF($A21="","",COUNTIFS('GECC 2026'!F$2:F$200,$A21))</f>
@@ -66048,15 +66159,15 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
-        <v>Leonardo José Alves Leal Neri</v>
+        <v>Leonardo de Melo</v>
       </c>
       <c r="B22" s="103">
         <f>IF($A22="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A22))</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C22" s="103">
         <f>IF($A22="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A22))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D22" s="256">
         <f>IF($A22="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A22))</f>
@@ -66064,24 +66175,24 @@
       </c>
       <c r="E22" s="241">
         <f>IF($A22="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A22)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A22))</f>
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F22" s="101">
         <f>IF($A22="","",COUNTIFS('GECC 2026'!F$2:F$200,$A22))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
-        <v>Luciana Alvim</v>
+        <v>Leonardo José Alves Leal Neri</v>
       </c>
       <c r="B23" s="103">
         <f>IF($A23="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A23))</f>
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C23" s="103">
         <f>IF($A23="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A23))</f>
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="D23" s="256">
         <f>IF($A23="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A23))</f>
@@ -66089,41 +66200,41 @@
       </c>
       <c r="E23" s="241">
         <f>IF($A23="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A23)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A23))</f>
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="F23" s="101">
         <f>IF($A23="","",COUNTIFS('GECC 2026'!F$2:F$200,$A23))</f>
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
-        <v>Marcelo Bálbio Moraes</v>
+        <v>Luciana Alvim</v>
       </c>
       <c r="B24" s="103">
         <f>IF($A24="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A24))</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C24" s="103">
         <f>IF($A24="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A24))</f>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="D24" s="256">
         <f>IF($A24="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A24))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E24" s="241">
         <f>IF($A24="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A24)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A24))</f>
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="F24" s="101">
         <f>IF($A24="","",COUNTIFS('GECC 2026'!F$2:F$200,$A24))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
-        <v>Mauri Siqueira Montessi</v>
+        <v>Marcelo Bálbio Moraes</v>
       </c>
       <c r="B25" s="103">
         <f>IF($A25="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A25))</f>
@@ -66148,7 +66259,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
-        <v>Michel Martins de Morais</v>
+        <v>Mauri Siqueira Montessi</v>
       </c>
       <c r="B26" s="103">
         <f>IF($A26="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A26))</f>
@@ -66173,40 +66284,40 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
-        <v>Paulo José Góes Daltro</v>
+        <v>Michel Martins de Morais</v>
       </c>
       <c r="B27" s="103">
         <f>IF($A27="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A27))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C27" s="103">
         <f>IF($A27="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A27))</f>
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="D27" s="256">
         <f>IF($A27="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A27))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E27" s="241">
         <f>IF($A27="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A27)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A27))</f>
-        <v>20.8</v>
+        <v>16</v>
       </c>
       <c r="F27" s="101">
         <f>IF($A27="","",COUNTIFS('GECC 2026'!F$2:F$200,$A27))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>Priscila Nolasco</v>
+        <v>Paulo José Góes Daltro</v>
       </c>
       <c r="B28" s="103">
         <f>IF($A28="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A28))</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C28" s="103">
         <f>IF($A28="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A28))</f>
-        <v>2.6399999999999997</v>
+        <v>4.8</v>
       </c>
       <c r="D28" s="256">
         <f>IF($A28="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A28))</f>
@@ -66214,7 +66325,7 @@
       </c>
       <c r="E28" s="241">
         <f>IF($A28="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A28)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A28))</f>
-        <v>14.64</v>
+        <v>20.8</v>
       </c>
       <c r="F28" s="101">
         <f>IF($A28="","",COUNTIFS('GECC 2026'!F$2:F$200,$A28))</f>
@@ -66223,15 +66334,15 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>Reinaldo Alencar</v>
+        <v>Priscila Nolasco</v>
       </c>
       <c r="B29" s="103">
         <f>IF($A29="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A29))</f>
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C29" s="103">
         <f>IF($A29="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A29))</f>
-        <v>7.1999999999999993</v>
+        <v>2.6399999999999997</v>
       </c>
       <c r="D29" s="256">
         <f>IF($A29="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A29))</f>
@@ -66239,7 +66350,7 @@
       </c>
       <c r="E29" s="241">
         <f>IF($A29="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A29)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A29))</f>
-        <v>55.2</v>
+        <v>14.64</v>
       </c>
       <c r="F29" s="101">
         <f>IF($A29="","",COUNTIFS('GECC 2026'!F$2:F$200,$A29))</f>
@@ -66248,7 +66359,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>Rogério Ribeiro</v>
+        <v>Reinaldo Alencar</v>
       </c>
       <c r="B30" s="103">
         <f>IF($A30="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A30))</f>
@@ -66273,65 +66384,65 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <v>Rômulo Miranda Alvim</v>
+        <v>Rogério Ribeiro</v>
       </c>
       <c r="B31" s="103">
         <f>IF($A31="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A31))</f>
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C31" s="103">
         <f>IF($A31="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A31))</f>
-        <v>3.6</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="D31" s="256">
         <f>IF($A31="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E31" s="241">
         <f>IF($A31="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A31)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
-        <v>43.6</v>
+        <v>55.2</v>
       </c>
       <c r="F31" s="101">
         <f>IF($A31="","",COUNTIFS('GECC 2026'!F$2:F$200,$A31))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <v>Servidores, colaboradores e estagiários do TCDF</v>
+        <v>Rômulo Miranda Alvim</v>
       </c>
       <c r="B32" s="103">
         <f>IF($A32="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C32" s="103">
         <f>IF($A32="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="D32" s="256">
         <f>IF($A32="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E32" s="241">
         <f>IF($A32="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A32)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="F32" s="101">
         <f>IF($A32="","",COUNTIFS('GECC 2026'!F$2:F$200,$A32))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <v>Tarsila Firmino Ely</v>
+        <v>Servidores, colaboradores e estagiários do TCDF</v>
       </c>
       <c r="B33" s="103">
         <f>IF($A33="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A33))</f>
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="C33" s="103">
         <f>IF($A33="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A33))</f>
-        <v>96.4</v>
+        <v>0</v>
       </c>
       <c r="D33" s="256">
         <f>IF($A33="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A33))</f>
@@ -66339,24 +66450,24 @@
       </c>
       <c r="E33" s="241">
         <f>IF($A33="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A33)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A33))</f>
-        <v>152.4</v>
+        <v>0</v>
       </c>
       <c r="F33" s="101">
         <f>IF($A33="","",COUNTIFS('GECC 2026'!F$2:F$200,$A33))</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <v>Túllio Herbeth Teixeira Moraes</v>
+        <v>Tarsila Firmino Ely</v>
       </c>
       <c r="B34" s="103">
         <f>IF($A34="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A34))</f>
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C34" s="103">
         <f>IF($A34="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A34))</f>
-        <v>0.44999999999999996</v>
+        <v>96.4</v>
       </c>
       <c r="D34" s="256">
         <f>IF($A34="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A34))</f>
@@ -66364,33 +66475,36 @@
       </c>
       <c r="E34" s="241">
         <f>IF($A34="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A34)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A34))</f>
-        <v>3.45</v>
+        <v>152.4</v>
       </c>
       <c r="F34" s="101">
         <f>IF($A34="","",COUNTIFS('GECC 2026'!F$2:F$200,$A34))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="str">
+        <v>Túllio Herbeth Teixeira Moraes</v>
+      </c>
+      <c r="B35" s="103">
+        <f>IF($A35="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A35))</f>
+        <v>3</v>
+      </c>
+      <c r="C35" s="103">
+        <f>IF($A35="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A35))</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="D35" s="256">
+        <f>IF($A35="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A35))</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="241">
+        <f>IF($A35="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A35)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A35))</f>
+        <v>3.45</v>
+      </c>
+      <c r="F35" s="101">
+        <f>IF($A35="","",COUNTIFS('GECC 2026'!F$2:F$200,$A35))</f>
         <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="103" t="str">
-        <f>IF($A35="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A35))</f>
-        <v/>
-      </c>
-      <c r="C35" s="103" t="str">
-        <f>IF($A35="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A35))</f>
-        <v/>
-      </c>
-      <c r="D35" s="256" t="str">
-        <f>IF($A35="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A35))</f>
-        <v/>
-      </c>
-      <c r="E35" s="241" t="str">
-        <f>IF($A35="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A35)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A35))</f>
-        <v/>
-      </c>
-      <c r="F35" s="101" t="str">
-        <f>IF($A35="","",COUNTIFS('GECC 2026'!F$2:F$200,$A35))</f>
-        <v/>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -67869,11 +67983,11 @@
       </c>
       <c r="B105" s="243">
         <f>SUM(B5:B100)</f>
-        <v>584</v>
+        <v>618</v>
       </c>
       <c r="C105" s="243">
         <f>SUM(C5:C100)</f>
-        <v>275.89999999999998</v>
+        <v>280.99999999999994</v>
       </c>
       <c r="D105" s="256">
         <f>IF($A105="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A105))</f>
@@ -67885,7 +67999,7 @@
       </c>
       <c r="F105" s="244">
         <f>SUM(F5:F100)</f>
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4912" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72871A91-D530-4445-908E-BE38934510C4}"/>
+  <xr:revisionPtr revIDLastSave="4917" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A724CB1-6B24-42D1-B0FF-C1C8628BB335}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6529" uniqueCount="2959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6533" uniqueCount="2961">
   <si>
     <t>ID</t>
   </si>
@@ -9045,6 +9045,12 @@
   </si>
   <si>
     <t>Flávio José Fonseca de Souza; Felipe da Costa Malaquias</t>
+  </si>
+  <si>
+    <t>2026-047</t>
+  </si>
+  <si>
+    <t>Felipe da Costa Malaquias</t>
   </si>
 </sst>
 </file>
@@ -58074,7 +58080,7 @@
         <v>0</v>
       </c>
       <c r="S703" s="210">
-        <v>17</v>
+        <v>17.45</v>
       </c>
       <c r="T703" s="209" t="s">
         <v>2958</v>
@@ -62376,7 +62382,7 @@
         <v>Contratações de TIC com base na jurisprudência do TCDF</v>
       </c>
       <c r="P39">
-        <v>17</v>
+        <v>17.45</v>
       </c>
       <c r="Q39" t="str">
         <v>Flávio José Fonseca de Souza; Felipe da Costa Malaquias</v>
@@ -62493,6 +62499,12 @@
       <c r="S41" t="str">
         <v/>
       </c>
+      <c r="X41" t="s">
+        <v>2959</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
@@ -62531,6 +62543,12 @@
       <c r="S42" t="str">
         <v/>
       </c>
+      <c r="X42" t="s">
+        <v>2959</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>2960</v>
+      </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
@@ -63572,7 +63590,7 @@
         <v>Contratações de TIC com base na jurisprudência do TCDF</v>
       </c>
       <c r="E70">
-        <v>17</v>
+        <v>17.45</v>
       </c>
       <c r="F70" t="str">
         <v>Flávio José Fonseca de Souza</v>
@@ -63581,13 +63599,13 @@
         <v>2</v>
       </c>
       <c r="H70">
-        <v>17</v>
+        <v>17.45</v>
       </c>
       <c r="I70">
-        <v>2.5499999999999998</v>
+        <v>2.6174999999999997</v>
       </c>
       <c r="J70">
-        <v>19.55</v>
+        <v>20.067499999999999</v>
       </c>
       <c r="R70" t="str">
         <v/>
@@ -63610,7 +63628,7 @@
         <v>Contratações de TIC com base na jurisprudência do TCDF</v>
       </c>
       <c r="E71">
-        <v>17</v>
+        <v>17.45</v>
       </c>
       <c r="F71" t="str">
         <v>Felipe da Costa Malaquias</v>
@@ -63619,13 +63637,13 @@
         <v>2</v>
       </c>
       <c r="H71">
-        <v>17</v>
+        <v>17.45</v>
       </c>
       <c r="I71">
-        <v>2.5499999999999998</v>
+        <v>2.6174999999999997</v>
       </c>
       <c r="J71">
-        <v>19.55</v>
+        <v>20.067499999999999</v>
       </c>
       <c r="R71" t="str">
         <v/>
@@ -65988,11 +66006,11 @@
       </c>
       <c r="B15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>17</v>
+        <v>17.45</v>
       </c>
       <c r="C15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>2.5499999999999998</v>
+        <v>2.6174999999999997</v>
       </c>
       <c r="D15" s="256">
         <f>IF($A15="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
@@ -66000,7 +66018,7 @@
       </c>
       <c r="E15" s="241">
         <f>IF($A15="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A15)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
-        <v>19.55</v>
+        <v>20.067499999999999</v>
       </c>
       <c r="F15" s="101">
         <f>IF($A15="","",COUNTIFS('GECC 2026'!F$2:F$200,$A15))</f>
@@ -66038,11 +66056,11 @@
       </c>
       <c r="B17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>25</v>
+        <v>25.45</v>
       </c>
       <c r="C17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>4.9499999999999993</v>
+        <v>5.0175000000000001</v>
       </c>
       <c r="D17" s="256">
         <f>IF($A17="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
@@ -66050,7 +66068,7 @@
       </c>
       <c r="E17" s="241">
         <f>IF($A17="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A17)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
-        <v>29.950000000000003</v>
+        <v>30.467500000000001</v>
       </c>
       <c r="F17" s="101">
         <f>IF($A17="","",COUNTIFS('GECC 2026'!F$2:F$200,$A17))</f>
@@ -67983,11 +68001,11 @@
       </c>
       <c r="B105" s="243">
         <f>SUM(B5:B100)</f>
-        <v>618</v>
+        <v>618.9</v>
       </c>
       <c r="C105" s="243">
         <f>SUM(C5:C100)</f>
-        <v>280.99999999999994</v>
+        <v>281.13499999999993</v>
       </c>
       <c r="D105" s="256">
         <f>IF($A105="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A105))</f>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4917" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A724CB1-6B24-42D1-B0FF-C1C8628BB335}"/>
+  <xr:revisionPtr revIDLastSave="4925" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE3AF998-4E59-492A-B4BC-2CA64128A1C7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -62403,10 +62403,10 @@
         <v>548</v>
       </c>
       <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
         <v>32</v>
-      </c>
-      <c r="AA39">
-        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
@@ -62505,6 +62505,12 @@
       <c r="Y41" t="s">
         <v>1471</v>
       </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>34.9</v>
+      </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
@@ -62549,6 +62555,12 @@
       <c r="Y42" t="s">
         <v>2960</v>
       </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>34.9</v>
+      </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
@@ -63371,10 +63383,10 @@
         <v>1</v>
       </c>
       <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
         <v>32</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
       </c>
       <c r="J64">
         <v>32</v>
@@ -63599,13 +63611,13 @@
         <v>2</v>
       </c>
       <c r="H70">
-        <v>17.45</v>
+        <v>0</v>
       </c>
       <c r="I70">
-        <v>2.6174999999999997</v>
+        <v>34.9</v>
       </c>
       <c r="J70">
-        <v>20.067499999999999</v>
+        <v>34.9</v>
       </c>
       <c r="R70" t="str">
         <v/>
@@ -63637,13 +63649,13 @@
         <v>2</v>
       </c>
       <c r="H71">
-        <v>17.45</v>
+        <v>0</v>
       </c>
       <c r="I71">
-        <v>2.6174999999999997</v>
+        <v>34.9</v>
       </c>
       <c r="J71">
-        <v>20.067499999999999</v>
+        <v>34.9</v>
       </c>
       <c r="R71" t="str">
         <v/>
@@ -66006,11 +66018,11 @@
       </c>
       <c r="B15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>17.45</v>
+        <v>0</v>
       </c>
       <c r="C15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>2.6174999999999997</v>
+        <v>34.9</v>
       </c>
       <c r="D15" s="256">
         <f>IF($A15="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
@@ -66018,7 +66030,7 @@
       </c>
       <c r="E15" s="241">
         <f>IF($A15="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A15)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
-        <v>20.067499999999999</v>
+        <v>34.9</v>
       </c>
       <c r="F15" s="101">
         <f>IF($A15="","",COUNTIFS('GECC 2026'!F$2:F$200,$A15))</f>
@@ -66056,11 +66068,11 @@
       </c>
       <c r="B17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>25.45</v>
+        <v>8</v>
       </c>
       <c r="C17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>5.0175000000000001</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D17" s="256">
         <f>IF($A17="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
@@ -66068,7 +66080,7 @@
       </c>
       <c r="E17" s="241">
         <f>IF($A17="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A17)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
-        <v>30.467500000000001</v>
+        <v>45.3</v>
       </c>
       <c r="F17" s="101">
         <f>IF($A17="","",COUNTIFS('GECC 2026'!F$2:F$200,$A17))</f>
@@ -66081,11 +66093,11 @@
       </c>
       <c r="B18" s="103">
         <f>IF($A18="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A18))</f>
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C18" s="103">
         <f>IF($A18="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A18))</f>
-        <v>1.2</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="D18" s="256">
         <f>IF($A18="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A18))</f>
@@ -68001,11 +68013,11 @@
       </c>
       <c r="B105" s="243">
         <f>SUM(B5:B100)</f>
-        <v>618.9</v>
+        <v>552</v>
       </c>
       <c r="C105" s="243">
         <f>SUM(C5:C100)</f>
-        <v>281.13499999999993</v>
+        <v>377.7</v>
       </c>
       <c r="D105" s="256">
         <f>IF($A105="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A105))</f>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4925" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE3AF998-4E59-492A-B4BC-2CA64128A1C7}"/>
+  <xr:revisionPtr revIDLastSave="4929" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8EA0B5E-8766-42AE-B51E-574C39FCFF42}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -8488,9 +8488,6 @@
     <t>Maratona Temática - Obras Públicas</t>
   </si>
   <si>
-    <t>21 e 22/09/2026</t>
-  </si>
-  <si>
     <t>4392/2026</t>
   </si>
   <si>
@@ -9051,6 +9048,9 @@
   </si>
   <si>
     <t>Felipe da Costa Malaquias</t>
+  </si>
+  <si>
+    <t>26 e 27/10/2026</t>
   </si>
 </sst>
 </file>
@@ -38516,7 +38516,7 @@
         <v>0</v>
       </c>
       <c r="R386" s="23">
-        <f t="shared" ref="R386:R449" si="6">SUM(O386:Q386)</f>
+        <f t="shared" ref="R386:R392" si="6">SUM(O386:Q386)</f>
         <v>49</v>
       </c>
       <c r="S386" s="22">
@@ -50985,7 +50985,7 @@
         <v>30</v>
       </c>
       <c r="R586" s="23">
-        <f t="shared" ref="R586:R649" si="10">SUM(O586:Q586)</f>
+        <f t="shared" ref="R586:R640" si="10">SUM(O586:Q586)</f>
         <v>30</v>
       </c>
       <c r="S586" s="22">
@@ -57024,13 +57024,13 @@
         <v>71</v>
       </c>
       <c r="H685" s="213" t="s">
-        <v>2773</v>
+        <v>2960</v>
       </c>
       <c r="I685" s="214">
-        <v>46286</v>
+        <v>46321</v>
       </c>
       <c r="J685" s="214">
-        <v>46287</v>
+        <v>46322</v>
       </c>
       <c r="K685" s="24" t="s">
         <v>26</v>
@@ -57067,10 +57067,10 @@
         <v>2767</v>
       </c>
       <c r="D686" s="219" t="s">
+        <v>2773</v>
+      </c>
+      <c r="E686" s="240" t="s">
         <v>2774</v>
-      </c>
-      <c r="E686" s="240" t="s">
-        <v>2775</v>
       </c>
       <c r="F686" s="221" t="s">
         <v>23</v>
@@ -57079,7 +57079,7 @@
         <v>67</v>
       </c>
       <c r="H686" s="222" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="I686" s="223">
         <v>46167</v>
@@ -57124,10 +57124,10 @@
         <v>2741</v>
       </c>
       <c r="D687" s="210" t="s">
+        <v>2776</v>
+      </c>
+      <c r="E687" s="211" t="s">
         <v>2777</v>
-      </c>
-      <c r="E687" s="211" t="s">
-        <v>2778</v>
       </c>
       <c r="F687" s="212" t="s">
         <v>23</v>
@@ -57136,7 +57136,7 @@
         <v>67</v>
       </c>
       <c r="H687" s="213" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="I687" s="214">
         <v>46174</v>
@@ -57163,7 +57163,7 @@
         <v>25</v>
       </c>
       <c r="T687" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="U687" s="203"/>
     </row>
@@ -57179,10 +57179,10 @@
         <v>2756</v>
       </c>
       <c r="D688" s="219" t="s">
+        <v>2780</v>
+      </c>
+      <c r="E688" s="240" t="s">
         <v>2781</v>
-      </c>
-      <c r="E688" s="240" t="s">
-        <v>2782</v>
       </c>
       <c r="F688" s="221" t="s">
         <v>80</v>
@@ -57191,7 +57191,7 @@
         <v>2725</v>
       </c>
       <c r="H688" s="222" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="I688" s="223">
         <v>46204</v>
@@ -57236,10 +57236,10 @@
         <v>21</v>
       </c>
       <c r="D689" s="210" t="s">
+        <v>2783</v>
+      </c>
+      <c r="E689" s="245" t="s">
         <v>2784</v>
-      </c>
-      <c r="E689" s="245" t="s">
-        <v>2785</v>
       </c>
       <c r="F689" s="212" t="s">
         <v>23</v>
@@ -57248,7 +57248,7 @@
         <v>2709</v>
       </c>
       <c r="H689" s="247" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="I689" s="214">
         <v>46154</v>
@@ -57301,10 +57301,10 @@
         <v>2756</v>
       </c>
       <c r="D690" s="219" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="E690" s="246" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="F690" s="221" t="s">
         <v>23</v>
@@ -57313,7 +57313,7 @@
         <v>2709</v>
       </c>
       <c r="H690" s="248" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="I690" s="223">
         <v>46196</v>
@@ -57358,7 +57358,7 @@
         <v>21</v>
       </c>
       <c r="D691" s="210" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="E691" s="245" t="s">
         <v>2667</v>
@@ -57370,7 +57370,7 @@
         <v>37</v>
       </c>
       <c r="H691" s="213" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="I691" s="214">
         <v>46160</v>
@@ -57423,10 +57423,10 @@
         <v>21</v>
       </c>
       <c r="D692" s="219" t="s">
+        <v>2790</v>
+      </c>
+      <c r="E692" s="246" t="s">
         <v>2791</v>
-      </c>
-      <c r="E692" s="246" t="s">
-        <v>2792</v>
       </c>
       <c r="F692" s="221" t="s">
         <v>23</v>
@@ -57435,7 +57435,7 @@
         <v>363</v>
       </c>
       <c r="H692" s="222" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
       <c r="I692" s="223">
         <v>46140</v>
@@ -57488,10 +57488,10 @@
         <v>21</v>
       </c>
       <c r="D693" s="210" t="s">
+        <v>2793</v>
+      </c>
+      <c r="E693" s="245" t="s">
         <v>2794</v>
-      </c>
-      <c r="E693" s="245" t="s">
-        <v>2795</v>
       </c>
       <c r="F693" s="212" t="s">
         <v>23</v>
@@ -57500,7 +57500,7 @@
         <v>24</v>
       </c>
       <c r="H693" s="213" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="I693" s="214">
         <v>46148</v>
@@ -57537,7 +57537,7 @@
         <v>12</v>
       </c>
       <c r="T693" s="209" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
       <c r="U693" s="203"/>
     </row>
@@ -57553,10 +57553,10 @@
         <v>2756</v>
       </c>
       <c r="D694" s="219" t="s">
+        <v>2797</v>
+      </c>
+      <c r="E694" s="220" t="s">
         <v>2798</v>
-      </c>
-      <c r="E694" s="220" t="s">
-        <v>2799</v>
       </c>
       <c r="F694" s="221" t="s">
         <v>61</v>
@@ -57565,7 +57565,7 @@
         <v>2688</v>
       </c>
       <c r="H694" s="222" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="I694" s="223">
         <v>46157</v>
@@ -57606,10 +57606,10 @@
         <v>2756</v>
       </c>
       <c r="D695" s="210" t="s">
+        <v>2800</v>
+      </c>
+      <c r="E695" s="211" t="s">
         <v>2801</v>
-      </c>
-      <c r="E695" s="211" t="s">
-        <v>2802</v>
       </c>
       <c r="F695" s="212" t="s">
         <v>80</v>
@@ -57618,7 +57618,7 @@
         <v>2725</v>
       </c>
       <c r="H695" s="213" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="I695" s="214">
         <v>46223</v>
@@ -57659,10 +57659,10 @@
         <v>21</v>
       </c>
       <c r="D696" s="219" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E696" s="220" t="s">
         <v>2804</v>
-      </c>
-      <c r="E696" s="220" t="s">
-        <v>2805</v>
       </c>
       <c r="F696" s="221" t="s">
         <v>80</v>
@@ -57671,7 +57671,7 @@
         <v>2725</v>
       </c>
       <c r="H696" s="222" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="I696" s="223">
         <v>46167</v>
@@ -57716,10 +57716,10 @@
         <v>21</v>
       </c>
       <c r="D697" s="210" t="s">
+        <v>2806</v>
+      </c>
+      <c r="E697" s="211" t="s">
         <v>2807</v>
-      </c>
-      <c r="E697" s="211" t="s">
-        <v>2808</v>
       </c>
       <c r="F697" s="212" t="s">
         <v>80</v>
@@ -57728,7 +57728,7 @@
         <v>2725</v>
       </c>
       <c r="H697" s="213" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="I697" s="214">
         <v>46148</v>
@@ -57761,7 +57761,7 @@
         <v>3</v>
       </c>
       <c r="T697" s="209" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="U697" s="203"/>
     </row>
@@ -57777,10 +57777,10 @@
         <v>2756</v>
       </c>
       <c r="D698" s="219" t="s">
+        <v>2810</v>
+      </c>
+      <c r="E698" s="220" t="s">
         <v>2811</v>
-      </c>
-      <c r="E698" s="220" t="s">
-        <v>2812</v>
       </c>
       <c r="F698" s="221" t="s">
         <v>23</v>
@@ -57789,7 +57789,7 @@
         <v>24</v>
       </c>
       <c r="H698" s="222" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="I698" s="223">
         <v>46204</v>
@@ -57830,10 +57830,10 @@
         <v>2756</v>
       </c>
       <c r="D699" s="210" t="s">
+        <v>2812</v>
+      </c>
+      <c r="E699" s="211" t="s">
         <v>2813</v>
-      </c>
-      <c r="E699" s="211" t="s">
-        <v>2814</v>
       </c>
       <c r="F699" s="212" t="s">
         <v>23</v>
@@ -57842,7 +57842,7 @@
         <v>67</v>
       </c>
       <c r="H699" s="213" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="I699" s="214">
         <v>46244</v>
@@ -57869,7 +57869,7 @@
         <v>10</v>
       </c>
       <c r="T699" s="209" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
       <c r="U699" s="203"/>
     </row>
@@ -57885,10 +57885,10 @@
         <v>2756</v>
       </c>
       <c r="D700" s="219" t="s">
+        <v>2816</v>
+      </c>
+      <c r="E700" s="220" t="s">
         <v>2817</v>
-      </c>
-      <c r="E700" s="220" t="s">
-        <v>2818</v>
       </c>
       <c r="F700" s="221" t="s">
         <v>61</v>
@@ -57897,7 +57897,7 @@
         <v>71</v>
       </c>
       <c r="H700" s="222" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
       <c r="I700" s="223">
         <v>46223</v>
@@ -57940,10 +57940,10 @@
         <v>2756</v>
       </c>
       <c r="D701" s="210" t="s">
+        <v>2819</v>
+      </c>
+      <c r="E701" s="211" t="s">
         <v>2820</v>
-      </c>
-      <c r="E701" s="211" t="s">
-        <v>2821</v>
       </c>
       <c r="F701" s="212" t="s">
         <v>61</v>
@@ -57952,7 +57952,7 @@
         <v>71</v>
       </c>
       <c r="H701" s="213" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="I701" s="214">
         <v>46237</v>
@@ -57993,10 +57993,10 @@
         <v>2748</v>
       </c>
       <c r="D702" s="219" t="s">
+        <v>2821</v>
+      </c>
+      <c r="E702" s="220" t="s">
         <v>2822</v>
-      </c>
-      <c r="E702" s="220" t="s">
-        <v>2823</v>
       </c>
       <c r="F702" s="221" t="s">
         <v>23</v>
@@ -58030,7 +58030,7 @@
         <v>12</v>
       </c>
       <c r="T702" s="218" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="U702" s="203"/>
     </row>
@@ -58046,10 +58046,10 @@
         <v>2756</v>
       </c>
       <c r="D703" s="210" t="s">
+        <v>2953</v>
+      </c>
+      <c r="E703" s="211" t="s">
         <v>2954</v>
-      </c>
-      <c r="E703" s="211" t="s">
-        <v>2955</v>
       </c>
       <c r="F703" s="212" t="s">
         <v>61</v>
@@ -58058,13 +58058,13 @@
         <v>71</v>
       </c>
       <c r="H703" s="213" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="I703" s="213" t="s">
+        <v>2955</v>
+      </c>
+      <c r="J703" s="213" t="s">
         <v>2956</v>
-      </c>
-      <c r="J703" s="213" t="s">
-        <v>2957</v>
       </c>
       <c r="K703" s="210" t="s">
         <v>34</v>
@@ -58083,7 +58083,7 @@
         <v>17.45</v>
       </c>
       <c r="T703" s="209" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="U703" s="203"/>
     </row>
@@ -59477,7 +59477,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Clique e insira um valor de a lista de itens" sqref="F518" xr:uid="{04F4F39B-F406-4ECC-A64A-F7A18A81A48D}">
       <formula1>"Interno,Externo,Híbrido"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Erro" error="Insira uma data válida. Formato: DD/MM/AAAA" sqref="I594:J594 I647:J648 I658:J658 I662:J662 I664:I673 I644:J645 I596:J640 I573:J590 I463:J571 I2:J460 I676:J676 J664:J674 I681:J702 I704:J1048576" xr:uid="{A71E4390-A059-418C-8F5C-AD2AF445253E}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Erro" error="Insira uma data válida. Formato: DD/MM/AAAA" sqref="I594:J594 I647:J648 I658:J658 I662:J662 I664:I673 I644:J645 I596:J640 I573:J590 I463:J571 I2:J460 I676:J676 J664:J674 I704:J1048576 I681:J702" xr:uid="{A71E4390-A059-418C-8F5C-AD2AF445253E}">
       <formula1>41640</formula1>
       <formula2>47848</formula2>
     </dataValidation>
@@ -59566,50 +59566,50 @@
         <v>1</v>
       </c>
       <c r="B1" s="96" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C1" s="96" t="s">
         <v>2825</v>
-      </c>
-      <c r="C1" s="96" t="s">
-        <v>2826</v>
       </c>
       <c r="D1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
       <c r="F1" s="96" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="96" t="s">
+        <v>2827</v>
+      </c>
+      <c r="H1" s="96" t="s">
         <v>2828</v>
       </c>
-      <c r="H1" s="96" t="s">
+      <c r="I1" s="96" t="s">
         <v>2829</v>
       </c>
-      <c r="I1" s="96" t="s">
+      <c r="J1" s="96" t="s">
         <v>2830</v>
       </c>
-      <c r="J1" s="96" t="s">
+      <c r="L1" s="129" t="s">
         <v>2831</v>
-      </c>
-      <c r="L1" s="129" t="s">
-        <v>2832</v>
       </c>
       <c r="M1" s="100">
         <v>2026</v>
       </c>
       <c r="U1" s="162" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="V1" s="161"/>
       <c r="X1" s="159" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="Y1" s="107"/>
       <c r="Z1" s="107"/>
       <c r="AA1" s="107"/>
       <c r="AC1" s="254" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -59645,25 +59645,25 @@
         <v>10.4</v>
       </c>
       <c r="X2" s="160" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="Y2" s="160" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="160" t="s">
+        <v>2835</v>
+      </c>
+      <c r="AA2" s="160" t="s">
         <v>2836</v>
-      </c>
-      <c r="AA2" s="160" t="s">
-        <v>2837</v>
       </c>
       <c r="AC2" s="255" t="s">
         <v>1</v>
       </c>
       <c r="AD2" s="255" t="s">
+        <v>2837</v>
+      </c>
+      <c r="AE2" s="255" t="s">
         <v>2838</v>
-      </c>
-      <c r="AE2" s="255" t="s">
-        <v>2839</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -59698,34 +59698,34 @@
         <v>5.2</v>
       </c>
       <c r="L3" s="19" t="s">
+        <v>2839</v>
+      </c>
+      <c r="M3" s="19" t="s">
         <v>2840</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="N3" s="19" t="s">
         <v>2841</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="O3" s="19" t="s">
         <v>2842</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="P3" s="19" t="s">
         <v>2843</v>
       </c>
-      <c r="P3" s="19" t="s">
+      <c r="Q3" s="19" t="s">
         <v>2844</v>
       </c>
-      <c r="Q3" s="19" t="s">
+      <c r="R3" s="19" t="s">
         <v>2845</v>
       </c>
-      <c r="R3" s="19" t="s">
+      <c r="S3" s="19" t="s">
         <v>2846</v>
       </c>
-      <c r="S3" s="19" t="s">
+      <c r="T3" s="19" t="s">
         <v>2847</v>
       </c>
-      <c r="T3" s="19" t="s">
+      <c r="X3" t="s">
         <v>2848</v>
-      </c>
-      <c r="X3" t="s">
-        <v>2849</v>
       </c>
       <c r="Y3" t="s">
         <v>2695</v>
@@ -59809,7 +59809,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="Y4" t="s">
         <v>2695</v>
@@ -59889,7 +59889,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="Y5" t="s">
         <v>2711</v>
@@ -59904,7 +59904,7 @@
         <v>2026</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="AE5" s="250">
         <v>16</v>
@@ -59969,10 +59969,10 @@
         <v>6</v>
       </c>
       <c r="X6" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="Y6" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -59984,7 +59984,7 @@
         <v>2026</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="AE6" s="250">
         <v>16</v>
@@ -60049,7 +60049,7 @@
         <v>8</v>
       </c>
       <c r="X7" s="98" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="Y7" t="s">
         <v>2695</v>
@@ -60129,7 +60129,7 @@
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="Y8" s="95" t="s">
         <v>1342</v>
@@ -60202,7 +60202,7 @@
         <v>11</v>
       </c>
       <c r="X9" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="Y9" s="95" t="s">
         <v>1022</v>
@@ -60275,7 +60275,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="Y10" s="95" t="s">
         <v>1366</v>
@@ -60348,10 +60348,10 @@
         <v>14</v>
       </c>
       <c r="X11" t="s">
+        <v>2855</v>
+      </c>
+      <c r="Y11" s="95" t="s">
         <v>2856</v>
-      </c>
-      <c r="Y11" s="95" t="s">
-        <v>2857</v>
       </c>
       <c r="AA11">
         <v>1.2</v>
@@ -60421,10 +60421,10 @@
         <v>15</v>
       </c>
       <c r="X12" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="AA12">
         <v>1.2</v>
@@ -60494,7 +60494,7 @@
         <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>1342</v>
@@ -60567,7 +60567,7 @@
         <v>18</v>
       </c>
       <c r="X14" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="Y14" s="95" t="s">
         <v>1022</v>
@@ -60640,7 +60640,7 @@
         <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="Y15" s="95" t="s">
         <v>1366</v>
@@ -60713,10 +60713,10 @@
         <v>22</v>
       </c>
       <c r="X16" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="Y16" s="95" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="AA16">
         <v>1.2</v>
@@ -60786,10 +60786,10 @@
         <v>23</v>
       </c>
       <c r="X17" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="Y17" s="95" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="AA17">
         <v>1.2</v>
@@ -60859,7 +60859,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="Y18" s="95" t="s">
         <v>1342</v>
@@ -60932,7 +60932,7 @@
         <v>33</v>
       </c>
       <c r="X19" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="Y19" s="95" t="s">
         <v>1022</v>
@@ -61005,7 +61005,7 @@
         <v>34</v>
       </c>
       <c r="X20" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="Y20" s="95" t="s">
         <v>1366</v>
@@ -61078,10 +61078,10 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="Y21" s="95" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="AA21">
         <v>1.2</v>
@@ -61151,10 +61151,10 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="Y22" s="95" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="AA22">
         <v>1.2</v>
@@ -61224,7 +61224,7 @@
         <v>39</v>
       </c>
       <c r="X23" s="98" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="Y23" s="95" t="s">
         <v>2711</v>
@@ -61297,10 +61297,10 @@
         <v>41</v>
       </c>
       <c r="X24" s="98" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="Y24" s="95" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -61370,7 +61370,7 @@
         <v>43</v>
       </c>
       <c r="X25" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="Y25" s="95" t="s">
         <v>854</v>
@@ -61443,10 +61443,10 @@
         <v>45</v>
       </c>
       <c r="X26" t="s">
+        <v>2861</v>
+      </c>
+      <c r="Y26" s="95" t="s">
         <v>2862</v>
-      </c>
-      <c r="Y26" s="95" t="s">
-        <v>2863</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -61519,7 +61519,7 @@
         <v>47</v>
       </c>
       <c r="X27" s="257" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="Y27" s="95" t="s">
         <v>2711</v>
@@ -61592,10 +61592,10 @@
         <v>49</v>
       </c>
       <c r="X28" s="257" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -61665,7 +61665,7 @@
         <v>50</v>
       </c>
       <c r="X29" s="257" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="Y29" s="95" t="s">
         <v>2711</v>
@@ -61738,10 +61738,10 @@
         <v>51</v>
       </c>
       <c r="X30" s="257" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="Y30" s="95" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -61811,7 +61811,7 @@
         <v>56</v>
       </c>
       <c r="X31" s="257" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="Y31" s="95" t="s">
         <v>471</v>
@@ -61887,7 +61887,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="257" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="Y32" t="s">
         <v>1342</v>
@@ -61963,10 +61963,10 @@
         <v>59</v>
       </c>
       <c r="X33" s="257" t="s">
+        <v>2866</v>
+      </c>
+      <c r="Y33" t="s">
         <v>2867</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>2868</v>
       </c>
       <c r="Z33">
         <v>4</v>
@@ -61976,7 +61976,7 @@
       </c>
       <c r="AC33" s="251"/>
       <c r="AD33" s="252" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="AE33" s="253">
         <f>SUM(AE3:AE32)</f>
@@ -62042,10 +62042,10 @@
         <v>60</v>
       </c>
       <c r="X34" s="257" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="Y34" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -62113,7 +62113,7 @@
         <v>62</v>
       </c>
       <c r="X35" s="257" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="Y35" t="s">
         <v>107</v>
@@ -62184,7 +62184,7 @@
         <v>63</v>
       </c>
       <c r="X36" s="257" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="Y36" t="s">
         <v>548</v>
@@ -62255,7 +62255,7 @@
         <v>64</v>
       </c>
       <c r="X37" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="Y37" t="s">
         <v>417</v>
@@ -62326,7 +62326,7 @@
         <v>65</v>
       </c>
       <c r="X38" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="Y38" s="260" t="s">
         <v>1095</v>
@@ -62397,7 +62397,7 @@
         <v>68</v>
       </c>
       <c r="X39" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="Y39" t="s">
         <v>548</v>
@@ -62450,7 +62450,7 @@
         <v>70</v>
       </c>
       <c r="X40" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="Y40" t="s">
         <v>471</v>
@@ -62500,7 +62500,7 @@
         <v/>
       </c>
       <c r="X41" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="Y41" t="s">
         <v>1471</v>
@@ -62550,10 +62550,10 @@
         <v/>
       </c>
       <c r="X42" t="s">
+        <v>2958</v>
+      </c>
+      <c r="Y42" t="s">
         <v>2959</v>
-      </c>
-      <c r="Y42" t="s">
-        <v>2960</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -64719,7 +64719,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="280" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="B1" s="280"/>
       <c r="C1" s="280"/>
@@ -64740,15 +64740,15 @@
     <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="281" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="B4" s="282"/>
       <c r="D4" s="283" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="E4" s="284"/>
       <c r="G4" s="125" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
@@ -64757,14 +64757,14 @@
         <v>47</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
         <v>28</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
@@ -64782,11 +64782,11 @@
     </row>
     <row r="8" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A8" s="278" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="B8" s="278"/>
       <c r="D8" s="278" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="E8" s="278"/>
     </row>
@@ -64801,13 +64801,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="108" t="s">
+        <v>2880</v>
+      </c>
+      <c r="D10" s="108" t="s">
         <v>2881</v>
       </c>
-      <c r="D10" s="108" t="s">
+      <c r="E10" s="108" t="s">
         <v>2882</v>
-      </c>
-      <c r="E10" s="108" t="s">
-        <v>2883</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -64819,7 +64819,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="109" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -64835,7 +64835,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -64851,7 +64851,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="109" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -64860,14 +64860,14 @@
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="113" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
         <v>28</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
@@ -64876,7 +64876,7 @@
     </row>
     <row r="30" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A30" s="278" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="B30" s="278"/>
       <c r="C30" s="278"/>
@@ -64895,16 +64895,16 @@
         <v>6</v>
       </c>
       <c r="B32" s="108" t="s">
+        <v>2889</v>
+      </c>
+      <c r="C32" s="108" t="s">
         <v>2890</v>
       </c>
-      <c r="C32" s="108" t="s">
+      <c r="D32" s="108" t="s">
         <v>2891</v>
       </c>
-      <c r="D32" s="108" t="s">
+      <c r="E32" s="108" t="s">
         <v>2892</v>
-      </c>
-      <c r="E32" s="108" t="s">
-        <v>2893</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65098,7 +65098,7 @@
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="156" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="B42" s="153">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A42)</f>
@@ -65140,7 +65140,7 @@
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="148" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="B44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,"")</f>
@@ -65161,7 +65161,7 @@
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="113" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
@@ -65212,163 +65212,163 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>2895</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>2896</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2897</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>2898</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>2899</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>2900</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>2901</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>2902</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1728</v>
       </c>
       <c r="D2" s="12" t="s">
+        <v>2902</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>2903</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>2904</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>2901</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>2902</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>2904</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>2905</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>2906</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>2901</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>2902</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>67</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>2901</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>2902</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>71</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>2907</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>2908</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>2909</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>2901</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>2902</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2725</v>
       </c>
       <c r="D6" s="12" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>2910</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>2911</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>2913</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>2914</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="12" t="s">
+        <v>2914</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>2915</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>2916</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>456</v>
       </c>
       <c r="D9" s="12" t="s">
+        <v>2917</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>2918</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>2919</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>198</v>
@@ -65377,15 +65377,15 @@
         <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>363</v>
@@ -65394,7 +65394,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
     </row>
   </sheetData>
@@ -65416,16 +65416,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -65436,7 +65436,7 @@
         <v>34</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>2756</v>
@@ -65450,7 +65450,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>2748</v>
@@ -65501,180 +65501,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>2895</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>2896</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2897</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>2898</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>2899</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>2900</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>67</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>71</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>2688</v>
       </c>
       <c r="D5" s="18" t="s">
+        <v>2929</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>2930</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>2931</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2725</v>
       </c>
       <c r="D6" s="12" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>2910</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>2911</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>2709</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>2931</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>2932</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>2933</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="12" t="s">
+        <v>2914</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>2915</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>2916</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>2693</v>
       </c>
       <c r="D9" s="12" t="s">
+        <v>2933</v>
+      </c>
+      <c r="E9" s="18" t="s">
         <v>2934</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>2935</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>2935</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>2893</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>2936</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>2894</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="E10" s="18" t="s">
         <v>2937</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>2938</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>198</v>
@@ -65683,15 +65683,15 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>363</v>
@@ -65700,7 +65700,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
     </row>
   </sheetData>
@@ -65719,7 +65719,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="285" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="B1" s="285"/>
       <c r="C1" s="285"/>
@@ -65729,7 +65729,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="286" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="B2" s="286"/>
       <c r="C2" s="286"/>
@@ -65742,19 +65742,19 @@
         <v>19</v>
       </c>
       <c r="B4" s="102" t="s">
+        <v>2828</v>
+      </c>
+      <c r="C4" s="102" t="s">
         <v>2829</v>
       </c>
-      <c r="C4" s="102" t="s">
+      <c r="D4" s="102" t="s">
+        <v>2940</v>
+      </c>
+      <c r="E4" s="102" t="s">
         <v>2830</v>
       </c>
-      <c r="D4" s="102" t="s">
+      <c r="F4" s="102" t="s">
         <v>2941</v>
-      </c>
-      <c r="E4" s="102" t="s">
-        <v>2831</v>
-      </c>
-      <c r="F4" s="102" t="s">
-        <v>2942</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -68009,7 +68009,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="242" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="B105" s="243">
         <f>SUM(B5:B100)</f>
@@ -68060,7 +68060,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="287" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="B1" s="287"/>
       <c r="C1" s="287"/>
@@ -68072,20 +68072,20 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="130" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="288" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="B4" s="289"/>
       <c r="D4" s="288" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="E4" s="289"/>
       <c r="G4" s="288" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="H4" s="289"/>
     </row>
@@ -68109,28 +68109,28 @@
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="143" t="s">
+        <v>2947</v>
+      </c>
+      <c r="B7" s="143" t="s">
         <v>2948</v>
-      </c>
-      <c r="B7" s="143" t="s">
-        <v>2949</v>
       </c>
       <c r="C7" s="143" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="143" t="s">
+        <v>2949</v>
+      </c>
+      <c r="E7" s="143" t="s">
         <v>2950</v>
       </c>
-      <c r="E7" s="143" t="s">
-        <v>2951</v>
-      </c>
       <c r="F7" s="143" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="G7" s="143" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="143" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -68426,7 +68426,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="233">
-        <v>46286</v>
+        <v>46321</v>
       </c>
       <c r="C19" s="232">
         <v>2026</v>
@@ -68435,7 +68435,7 @@
         <v>Maratona Temática - Obras Públicas</v>
       </c>
       <c r="E19" s="232" t="str">
-        <v>21 e 22/09/2026</v>
+        <v>26 e 27/10/2026</v>
       </c>
       <c r="F19" s="232" t="str">
         <v>A realizar</v>
@@ -68493,26 +68493,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052D3A7BF04652843BCB50FE90745AA50" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ef6274641b2f7d621af528393bef14e5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe686eaa-0658-4f15-b230-9e46c4d089fd" xmlns:ns3="91ce1707-6d34-452b-b217-9734c03e6729" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fa87a3bcf42251a9fb9988d55372596" ns2:_="" ns3:_="">
     <xsd:import namespace="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
@@ -68713,10 +68693,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
+    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -68733,20 +68744,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
-    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4929" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8EA0B5E-8766-42AE-B51E-574C39FCFF42}"/>
+  <xr:revisionPtr revIDLastSave="4931" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36DF3342-E4D0-430B-BDAF-C17824D4E2C6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -14963,6 +14963,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}" name="Tabela2" displayName="Tabela2" ref="B1:T684" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="B1:T684" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}">
@@ -15374,7 +15378,7 @@
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
       <c r="R2" s="23">
-        <f t="shared" ref="R2:R65" si="0">SUM(O2:Q2)</f>
+        <f>SUM(O2:Q2)</f>
         <v>20</v>
       </c>
       <c r="S2" s="22">
@@ -15425,7 +15429,7 @@
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O3:Q3)</f>
         <v>16</v>
       </c>
       <c r="S3" s="24">
@@ -15476,7 +15480,7 @@
       <c r="P4" s="23"/>
       <c r="Q4" s="23"/>
       <c r="R4" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O4:Q4)</f>
         <v>24</v>
       </c>
       <c r="S4" s="22">
@@ -15527,7 +15531,7 @@
       <c r="P5" s="25"/>
       <c r="Q5" s="25"/>
       <c r="R5" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O5:Q5)</f>
         <v>16</v>
       </c>
       <c r="S5" s="24">
@@ -15578,7 +15582,7 @@
       <c r="P6" s="23"/>
       <c r="Q6" s="23"/>
       <c r="R6" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O6:Q6)</f>
         <v>40</v>
       </c>
       <c r="S6" s="22">
@@ -15629,7 +15633,7 @@
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
       <c r="R7" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O7:Q7)</f>
         <v>30</v>
       </c>
       <c r="S7" s="24">
@@ -15678,7 +15682,7 @@
       <c r="P8" s="23"/>
       <c r="Q8" s="23"/>
       <c r="R8" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O8:Q8)</f>
         <v>24</v>
       </c>
       <c r="S8" s="22">
@@ -15729,7 +15733,7 @@
       </c>
       <c r="Q9" s="25"/>
       <c r="R9" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O9:Q9)</f>
         <v>37</v>
       </c>
       <c r="S9" s="24">
@@ -15780,7 +15784,7 @@
       </c>
       <c r="Q10" s="23"/>
       <c r="R10" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O10:Q10)</f>
         <v>58</v>
       </c>
       <c r="S10" s="22">
@@ -15833,7 +15837,7 @@
       <c r="P11" s="25"/>
       <c r="Q11" s="25"/>
       <c r="R11" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O11:Q11)</f>
         <v>25</v>
       </c>
       <c r="S11" s="24">
@@ -15888,7 +15892,7 @@
       </c>
       <c r="Q12" s="23"/>
       <c r="R12" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O12:Q12)</f>
         <v>85</v>
       </c>
       <c r="S12" s="22">
@@ -15943,7 +15947,7 @@
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
       <c r="R13" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O13:Q13)</f>
         <v>19</v>
       </c>
       <c r="S13" s="24">
@@ -15998,7 +16002,7 @@
       </c>
       <c r="Q14" s="23"/>
       <c r="R14" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O14:Q14)</f>
         <v>89</v>
       </c>
       <c r="S14" s="22">
@@ -16053,7 +16057,7 @@
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
       <c r="R15" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O15:Q15)</f>
         <v>37</v>
       </c>
       <c r="S15" s="24">
@@ -16110,7 +16114,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O16:Q16)</f>
         <v>0</v>
       </c>
       <c r="S16" s="22">
@@ -16163,7 +16167,7 @@
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
       <c r="R17" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O17:Q17)</f>
         <v>30</v>
       </c>
       <c r="S17" s="24">
@@ -16218,7 +16222,7 @@
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
       <c r="R18" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O18:Q18)</f>
         <v>30</v>
       </c>
       <c r="S18" s="22">
@@ -16273,7 +16277,7 @@
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
       <c r="R19" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O19:Q19)</f>
         <v>15</v>
       </c>
       <c r="S19" s="24">
@@ -16328,7 +16332,7 @@
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
       <c r="R20" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O20:Q20)</f>
         <v>14</v>
       </c>
       <c r="S20" s="22">
@@ -16383,7 +16387,7 @@
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
       <c r="R21" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O21:Q21)</f>
         <v>14</v>
       </c>
       <c r="S21" s="24">
@@ -16438,7 +16442,7 @@
       </c>
       <c r="Q22" s="23"/>
       <c r="R22" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O22:Q22)</f>
         <v>49</v>
       </c>
       <c r="S22" s="22">
@@ -16493,7 +16497,7 @@
       <c r="P23" s="25"/>
       <c r="Q23" s="25"/>
       <c r="R23" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O23:Q23)</f>
         <v>43</v>
       </c>
       <c r="S23" s="24">
@@ -16548,7 +16552,7 @@
       <c r="P24" s="23"/>
       <c r="Q24" s="23"/>
       <c r="R24" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O24:Q24)</f>
         <v>25</v>
       </c>
       <c r="S24" s="22">
@@ -16603,7 +16607,7 @@
       <c r="P25" s="25"/>
       <c r="Q25" s="25"/>
       <c r="R25" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O25:Q25)</f>
         <v>35</v>
       </c>
       <c r="S25" s="24">
@@ -16658,7 +16662,7 @@
       <c r="P26" s="23"/>
       <c r="Q26" s="23"/>
       <c r="R26" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O26:Q26)</f>
         <v>35</v>
       </c>
       <c r="S26" s="22">
@@ -16711,7 +16715,7 @@
       <c r="P27" s="25"/>
       <c r="Q27" s="25"/>
       <c r="R27" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O27:Q27)</f>
         <v>87</v>
       </c>
       <c r="S27" s="24"/>
@@ -16762,7 +16766,7 @@
         <v>46</v>
       </c>
       <c r="R28" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O28:Q28)</f>
         <v>46</v>
       </c>
       <c r="S28" s="22">
@@ -16817,7 +16821,7 @@
       <c r="P29" s="25"/>
       <c r="Q29" s="25"/>
       <c r="R29" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O29:Q29)</f>
         <v>15</v>
       </c>
       <c r="S29" s="24">
@@ -16872,7 +16876,7 @@
       </c>
       <c r="Q30" s="23"/>
       <c r="R30" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O30:Q30)</f>
         <v>54</v>
       </c>
       <c r="S30" s="22">
@@ -16925,7 +16929,7 @@
       <c r="P31" s="25"/>
       <c r="Q31" s="25"/>
       <c r="R31" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O31:Q31)</f>
         <v>52</v>
       </c>
       <c r="S31" s="24">
@@ -16978,7 +16982,7 @@
         <v>46</v>
       </c>
       <c r="R32" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O32:Q32)</f>
         <v>46</v>
       </c>
       <c r="S32" s="22">
@@ -17031,7 +17035,7 @@
       <c r="P33" s="25"/>
       <c r="Q33" s="25"/>
       <c r="R33" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O33:Q33)</f>
         <v>14</v>
       </c>
       <c r="S33" s="24">
@@ -17082,7 +17086,7 @@
       <c r="P34" s="23"/>
       <c r="Q34" s="23"/>
       <c r="R34" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O34:Q34)</f>
         <v>25</v>
       </c>
       <c r="S34" s="22">
@@ -17133,7 +17137,7 @@
       <c r="P35" s="25"/>
       <c r="Q35" s="25"/>
       <c r="R35" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O35:Q35)</f>
         <v>17</v>
       </c>
       <c r="S35" s="24">
@@ -17188,7 +17192,7 @@
       </c>
       <c r="Q36" s="23"/>
       <c r="R36" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O36:Q36)</f>
         <v>75</v>
       </c>
       <c r="S36" s="22">
@@ -17243,7 +17247,7 @@
       </c>
       <c r="Q37" s="25"/>
       <c r="R37" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O37:Q37)</f>
         <v>18</v>
       </c>
       <c r="S37" s="24">
@@ -17298,7 +17302,7 @@
       <c r="P38" s="23"/>
       <c r="Q38" s="23"/>
       <c r="R38" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O38:Q38)</f>
         <v>33</v>
       </c>
       <c r="S38" s="22">
@@ -17353,7 +17357,7 @@
       </c>
       <c r="Q39" s="25"/>
       <c r="R39" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O39:Q39)</f>
         <v>55</v>
       </c>
       <c r="S39" s="24">
@@ -17408,7 +17412,7 @@
         <v>45</v>
       </c>
       <c r="R40" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O40:Q40)</f>
         <v>45</v>
       </c>
       <c r="S40" s="22">
@@ -17463,7 +17467,7 @@
       <c r="P41" s="25"/>
       <c r="Q41" s="25"/>
       <c r="R41" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O41:Q41)</f>
         <v>15</v>
       </c>
       <c r="S41" s="24">
@@ -17518,7 +17522,7 @@
         <v>21</v>
       </c>
       <c r="R42" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O42:Q42)</f>
         <v>21</v>
       </c>
       <c r="S42" s="22">
@@ -17573,7 +17577,7 @@
       <c r="P43" s="25"/>
       <c r="Q43" s="25"/>
       <c r="R43" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O43:Q43)</f>
         <v>40</v>
       </c>
       <c r="S43" s="24">
@@ -17628,7 +17632,7 @@
       </c>
       <c r="Q44" s="23"/>
       <c r="R44" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O44:Q44)</f>
         <v>45</v>
       </c>
       <c r="S44" s="22">
@@ -17683,7 +17687,7 @@
       <c r="P45" s="25"/>
       <c r="Q45" s="25"/>
       <c r="R45" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O45:Q45)</f>
         <v>13</v>
       </c>
       <c r="S45" s="24">
@@ -17738,7 +17742,7 @@
       <c r="P46" s="23"/>
       <c r="Q46" s="23"/>
       <c r="R46" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O46:Q46)</f>
         <v>35</v>
       </c>
       <c r="S46" s="22">
@@ -17795,7 +17799,7 @@
       </c>
       <c r="Q47" s="25"/>
       <c r="R47" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O47:Q47)</f>
         <v>71</v>
       </c>
       <c r="S47" s="24">
@@ -17854,7 +17858,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O48:Q48)</f>
         <v>329</v>
       </c>
       <c r="S48" s="22">
@@ -17909,7 +17913,7 @@
       <c r="P49" s="25"/>
       <c r="Q49" s="25"/>
       <c r="R49" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O49:Q49)</f>
         <v>26</v>
       </c>
       <c r="S49" s="24">
@@ -17964,7 +17968,7 @@
       <c r="P50" s="23"/>
       <c r="Q50" s="23"/>
       <c r="R50" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O50:Q50)</f>
         <v>35</v>
       </c>
       <c r="S50" s="22">
@@ -18019,7 +18023,7 @@
       </c>
       <c r="Q51" s="25"/>
       <c r="R51" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O51:Q51)</f>
         <v>46</v>
       </c>
       <c r="S51" s="24">
@@ -18074,7 +18078,7 @@
       </c>
       <c r="Q52" s="23"/>
       <c r="R52" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O52:Q52)</f>
         <v>52</v>
       </c>
       <c r="S52" s="22">
@@ -18129,7 +18133,7 @@
       <c r="P53" s="25"/>
       <c r="Q53" s="25"/>
       <c r="R53" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O53:Q53)</f>
         <v>34</v>
       </c>
       <c r="S53" s="24">
@@ -18184,7 +18188,7 @@
       <c r="P54" s="23"/>
       <c r="Q54" s="23"/>
       <c r="R54" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O54:Q54)</f>
         <v>27</v>
       </c>
       <c r="S54" s="22">
@@ -18239,7 +18243,7 @@
       <c r="P55" s="25"/>
       <c r="Q55" s="25"/>
       <c r="R55" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O55:Q55)</f>
         <v>16</v>
       </c>
       <c r="S55" s="24">
@@ -18294,7 +18298,7 @@
       </c>
       <c r="Q56" s="23"/>
       <c r="R56" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O56:Q56)</f>
         <v>55</v>
       </c>
       <c r="S56" s="22">
@@ -18349,7 +18353,7 @@
       <c r="P57" s="25"/>
       <c r="Q57" s="25"/>
       <c r="R57" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O57:Q57)</f>
         <v>14</v>
       </c>
       <c r="S57" s="24">
@@ -18404,7 +18408,7 @@
       </c>
       <c r="Q58" s="23"/>
       <c r="R58" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O58:Q58)</f>
         <v>47</v>
       </c>
       <c r="S58" s="22">
@@ -18459,7 +18463,7 @@
       <c r="P59" s="25"/>
       <c r="Q59" s="25"/>
       <c r="R59" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O59:Q59)</f>
         <v>31</v>
       </c>
       <c r="S59" s="24">
@@ -18514,7 +18518,7 @@
       </c>
       <c r="Q60" s="23"/>
       <c r="R60" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O60:Q60)</f>
         <v>28</v>
       </c>
       <c r="S60" s="22">
@@ -18569,7 +18573,7 @@
       </c>
       <c r="Q61" s="25"/>
       <c r="R61" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O61:Q61)</f>
         <v>34</v>
       </c>
       <c r="S61" s="24">
@@ -18624,7 +18628,7 @@
       </c>
       <c r="Q62" s="23"/>
       <c r="R62" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O62:Q62)</f>
         <v>60</v>
       </c>
       <c r="S62" s="22">
@@ -18679,7 +18683,7 @@
       <c r="P63" s="25"/>
       <c r="Q63" s="25"/>
       <c r="R63" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O63:Q63)</f>
         <v>29</v>
       </c>
       <c r="S63" s="24">
@@ -18734,7 +18738,7 @@
       <c r="P64" s="23"/>
       <c r="Q64" s="23"/>
       <c r="R64" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O64:Q64)</f>
         <v>26</v>
       </c>
       <c r="S64" s="22">
@@ -18789,7 +18793,7 @@
       </c>
       <c r="Q65" s="25"/>
       <c r="R65" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O65:Q65)</f>
         <v>47</v>
       </c>
       <c r="S65" s="24">
@@ -18844,7 +18848,7 @@
       <c r="P66" s="23"/>
       <c r="Q66" s="23"/>
       <c r="R66" s="23">
-        <f t="shared" ref="R66:R129" si="1">SUM(O66:Q66)</f>
+        <f>SUM(O66:Q66)</f>
         <v>20</v>
       </c>
       <c r="S66" s="22">
@@ -18899,7 +18903,7 @@
       </c>
       <c r="Q67" s="25"/>
       <c r="R67" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O67:Q67)</f>
         <v>43</v>
       </c>
       <c r="S67" s="24">
@@ -18954,7 +18958,7 @@
       <c r="P68" s="23"/>
       <c r="Q68" s="23"/>
       <c r="R68" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O68:Q68)</f>
         <v>15</v>
       </c>
       <c r="S68" s="22">
@@ -19009,7 +19013,7 @@
       <c r="P69" s="25"/>
       <c r="Q69" s="25"/>
       <c r="R69" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O69:Q69)</f>
         <v>29</v>
       </c>
       <c r="S69" s="24">
@@ -19064,7 +19068,7 @@
       </c>
       <c r="Q70" s="23"/>
       <c r="R70" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O70:Q70)</f>
         <v>46</v>
       </c>
       <c r="S70" s="22">
@@ -19119,7 +19123,7 @@
       <c r="P71" s="25"/>
       <c r="Q71" s="25"/>
       <c r="R71" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O71:Q71)</f>
         <v>14</v>
       </c>
       <c r="S71" s="24">
@@ -19174,7 +19178,7 @@
       <c r="P72" s="23"/>
       <c r="Q72" s="23"/>
       <c r="R72" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O72:Q72)</f>
         <v>12</v>
       </c>
       <c r="S72" s="22">
@@ -19229,7 +19233,7 @@
       <c r="P73" s="25"/>
       <c r="Q73" s="25"/>
       <c r="R73" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O73:Q73)</f>
         <v>18</v>
       </c>
       <c r="S73" s="24">
@@ -19284,7 +19288,7 @@
       <c r="P74" s="23"/>
       <c r="Q74" s="23"/>
       <c r="R74" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O74:Q74)</f>
         <v>30</v>
       </c>
       <c r="S74" s="22">
@@ -19339,7 +19343,7 @@
         <v>37</v>
       </c>
       <c r="R75" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O75:Q75)</f>
         <v>37</v>
       </c>
       <c r="S75" s="24">
@@ -19394,7 +19398,7 @@
       </c>
       <c r="Q76" s="23"/>
       <c r="R76" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O76:Q76)</f>
         <v>47</v>
       </c>
       <c r="S76" s="22">
@@ -19449,7 +19453,7 @@
       <c r="P77" s="25"/>
       <c r="Q77" s="25"/>
       <c r="R77" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O77:Q77)</f>
         <v>30</v>
       </c>
       <c r="S77" s="24">
@@ -19504,7 +19508,7 @@
       <c r="P78" s="23"/>
       <c r="Q78" s="23"/>
       <c r="R78" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O78:Q78)</f>
         <v>19</v>
       </c>
       <c r="S78" s="22">
@@ -19559,7 +19563,7 @@
       </c>
       <c r="Q79" s="25"/>
       <c r="R79" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O79:Q79)</f>
         <v>37</v>
       </c>
       <c r="S79" s="24">
@@ -19614,7 +19618,7 @@
       <c r="P80" s="23"/>
       <c r="Q80" s="23"/>
       <c r="R80" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O80:Q80)</f>
         <v>19</v>
       </c>
       <c r="S80" s="22">
@@ -19669,7 +19673,7 @@
       <c r="P81" s="25"/>
       <c r="Q81" s="25"/>
       <c r="R81" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O81:Q81)</f>
         <v>20</v>
       </c>
       <c r="S81" s="24">
@@ -19724,7 +19728,7 @@
       <c r="P82" s="23"/>
       <c r="Q82" s="23"/>
       <c r="R82" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O82:Q82)</f>
         <v>50</v>
       </c>
       <c r="S82" s="22">
@@ -19779,7 +19783,7 @@
       <c r="P83" s="25"/>
       <c r="Q83" s="25"/>
       <c r="R83" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O83:Q83)</f>
         <v>17</v>
       </c>
       <c r="S83" s="24">
@@ -19834,7 +19838,7 @@
       </c>
       <c r="Q84" s="23"/>
       <c r="R84" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O84:Q84)</f>
         <v>25</v>
       </c>
       <c r="S84" s="22">
@@ -19889,7 +19893,7 @@
         <v>49</v>
       </c>
       <c r="R85" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O85:Q85)</f>
         <v>49</v>
       </c>
       <c r="S85" s="24">
@@ -19944,7 +19948,7 @@
       </c>
       <c r="Q86" s="23"/>
       <c r="R86" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O86:Q86)</f>
         <v>34</v>
       </c>
       <c r="S86" s="22">
@@ -19999,7 +20003,7 @@
       <c r="P87" s="25"/>
       <c r="Q87" s="25"/>
       <c r="R87" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O87:Q87)</f>
         <v>19</v>
       </c>
       <c r="S87" s="24">
@@ -20058,7 +20062,7 @@
         <v>0</v>
       </c>
       <c r="R88" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O88:Q88)</f>
         <v>312</v>
       </c>
       <c r="S88" s="22">
@@ -20113,7 +20117,7 @@
       </c>
       <c r="Q89" s="25"/>
       <c r="R89" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O89:Q89)</f>
         <v>57</v>
       </c>
       <c r="S89" s="24">
@@ -20168,7 +20172,7 @@
       </c>
       <c r="Q90" s="23"/>
       <c r="R90" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O90:Q90)</f>
         <v>50</v>
       </c>
       <c r="S90" s="22">
@@ -20223,7 +20227,7 @@
       <c r="P91" s="25"/>
       <c r="Q91" s="25"/>
       <c r="R91" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O91:Q91)</f>
         <v>18</v>
       </c>
       <c r="S91" s="24">
@@ -20278,7 +20282,7 @@
       <c r="P92" s="23"/>
       <c r="Q92" s="23"/>
       <c r="R92" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O92:Q92)</f>
         <v>18</v>
       </c>
       <c r="S92" s="22">
@@ -20333,7 +20337,7 @@
       </c>
       <c r="Q93" s="25"/>
       <c r="R93" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O93:Q93)</f>
         <v>40</v>
       </c>
       <c r="S93" s="24">
@@ -20388,7 +20392,7 @@
       </c>
       <c r="Q94" s="23"/>
       <c r="R94" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O94:Q94)</f>
         <v>37</v>
       </c>
       <c r="S94" s="22">
@@ -20443,7 +20447,7 @@
         <v>96</v>
       </c>
       <c r="R95" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O95:Q95)</f>
         <v>96</v>
       </c>
       <c r="S95" s="24">
@@ -20498,7 +20502,7 @@
       <c r="P96" s="23"/>
       <c r="Q96" s="23"/>
       <c r="R96" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O96:Q96)</f>
         <v>19</v>
       </c>
       <c r="S96" s="22">
@@ -20553,7 +20557,7 @@
       </c>
       <c r="Q97" s="25"/>
       <c r="R97" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O97:Q97)</f>
         <v>65</v>
       </c>
       <c r="S97" s="24">
@@ -20608,7 +20612,7 @@
       <c r="P98" s="23"/>
       <c r="Q98" s="23"/>
       <c r="R98" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O98:Q98)</f>
         <v>19</v>
       </c>
       <c r="S98" s="22">
@@ -20663,7 +20667,7 @@
       <c r="P99" s="25"/>
       <c r="Q99" s="25"/>
       <c r="R99" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O99:Q99)</f>
         <v>19</v>
       </c>
       <c r="S99" s="24">
@@ -20718,7 +20722,7 @@
       <c r="P100" s="23"/>
       <c r="Q100" s="23"/>
       <c r="R100" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O100:Q100)</f>
         <v>20</v>
       </c>
       <c r="S100" s="22">
@@ -20773,7 +20777,7 @@
       </c>
       <c r="Q101" s="25"/>
       <c r="R101" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O101:Q101)</f>
         <v>63</v>
       </c>
       <c r="S101" s="24">
@@ -20828,7 +20832,7 @@
       <c r="P102" s="23"/>
       <c r="Q102" s="23"/>
       <c r="R102" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O102:Q102)</f>
         <v>18</v>
       </c>
       <c r="S102" s="22">
@@ -20883,7 +20887,7 @@
       <c r="P103" s="25"/>
       <c r="Q103" s="25"/>
       <c r="R103" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O103:Q103)</f>
         <v>31</v>
       </c>
       <c r="S103" s="24">
@@ -20938,7 +20942,7 @@
       </c>
       <c r="Q104" s="23"/>
       <c r="R104" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O104:Q104)</f>
         <v>59</v>
       </c>
       <c r="S104" s="22">
@@ -20993,7 +20997,7 @@
       <c r="P105" s="25"/>
       <c r="Q105" s="25"/>
       <c r="R105" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O105:Q105)</f>
         <v>25</v>
       </c>
       <c r="S105" s="24">
@@ -21048,7 +21052,7 @@
       </c>
       <c r="Q106" s="23"/>
       <c r="R106" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O106:Q106)</f>
         <v>34</v>
       </c>
       <c r="S106" s="22">
@@ -21103,7 +21107,7 @@
       <c r="P107" s="25"/>
       <c r="Q107" s="25"/>
       <c r="R107" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O107:Q107)</f>
         <v>19</v>
       </c>
       <c r="S107" s="24">
@@ -21162,7 +21166,7 @@
         <v>0</v>
       </c>
       <c r="R108" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O108:Q108)</f>
         <v>353</v>
       </c>
       <c r="S108" s="22">
@@ -21217,7 +21221,7 @@
       <c r="P109" s="25"/>
       <c r="Q109" s="25"/>
       <c r="R109" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O109:Q109)</f>
         <v>28</v>
       </c>
       <c r="S109" s="24">
@@ -21272,7 +21276,7 @@
       <c r="P110" s="23"/>
       <c r="Q110" s="23"/>
       <c r="R110" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O110:Q110)</f>
         <v>215</v>
       </c>
       <c r="S110" s="22">
@@ -21327,7 +21331,7 @@
       <c r="P111" s="25"/>
       <c r="Q111" s="25"/>
       <c r="R111" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O111:Q111)</f>
         <v>55</v>
       </c>
       <c r="S111" s="24">
@@ -21382,7 +21386,7 @@
       <c r="P112" s="23"/>
       <c r="Q112" s="23"/>
       <c r="R112" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O112:Q112)</f>
         <v>11</v>
       </c>
       <c r="S112" s="22">
@@ -21437,7 +21441,7 @@
       <c r="P113" s="25"/>
       <c r="Q113" s="25"/>
       <c r="R113" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O113:Q113)</f>
         <v>26</v>
       </c>
       <c r="S113" s="24">
@@ -21492,7 +21496,7 @@
       <c r="P114" s="23"/>
       <c r="Q114" s="23"/>
       <c r="R114" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O114:Q114)</f>
         <v>8</v>
       </c>
       <c r="S114" s="22">
@@ -21551,7 +21555,7 @@
         <v>0</v>
       </c>
       <c r="R115" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O115:Q115)</f>
         <v>38</v>
       </c>
       <c r="S115" s="24">
@@ -21612,7 +21616,7 @@
       </c>
       <c r="Q116" s="23"/>
       <c r="R116" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O116:Q116)</f>
         <v>18</v>
       </c>
       <c r="S116" s="22">
@@ -21673,7 +21677,7 @@
       </c>
       <c r="Q117" s="25"/>
       <c r="R117" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O117:Q117)</f>
         <v>45</v>
       </c>
       <c r="S117" s="24">
@@ -21734,7 +21738,7 @@
       </c>
       <c r="Q118" s="23"/>
       <c r="R118" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O118:Q118)</f>
         <v>45</v>
       </c>
       <c r="S118" s="22">
@@ -21795,7 +21799,7 @@
       </c>
       <c r="Q119" s="25"/>
       <c r="R119" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O119:Q119)</f>
         <v>44</v>
       </c>
       <c r="S119" s="24">
@@ -21856,7 +21860,7 @@
       </c>
       <c r="Q120" s="23"/>
       <c r="R120" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O120:Q120)</f>
         <v>50</v>
       </c>
       <c r="S120" s="22">
@@ -21917,7 +21921,7 @@
       </c>
       <c r="Q121" s="25"/>
       <c r="R121" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O121:Q121)</f>
         <v>41</v>
       </c>
       <c r="S121" s="24">
@@ -21978,7 +21982,7 @@
       </c>
       <c r="Q122" s="23"/>
       <c r="R122" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O122:Q122)</f>
         <v>44</v>
       </c>
       <c r="S122" s="22">
@@ -22039,7 +22043,7 @@
       </c>
       <c r="Q123" s="25"/>
       <c r="R123" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O123:Q123)</f>
         <v>40</v>
       </c>
       <c r="S123" s="24">
@@ -22100,7 +22104,7 @@
       </c>
       <c r="Q124" s="23"/>
       <c r="R124" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O124:Q124)</f>
         <v>12</v>
       </c>
       <c r="S124" s="22">
@@ -22161,7 +22165,7 @@
       </c>
       <c r="Q125" s="25"/>
       <c r="R125" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O125:Q125)</f>
         <v>19</v>
       </c>
       <c r="S125" s="24">
@@ -22222,7 +22226,7 @@
       </c>
       <c r="Q126" s="23"/>
       <c r="R126" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O126:Q126)</f>
         <v>14</v>
       </c>
       <c r="S126" s="22">
@@ -22283,7 +22287,7 @@
       </c>
       <c r="Q127" s="25"/>
       <c r="R127" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O127:Q127)</f>
         <v>19</v>
       </c>
       <c r="S127" s="24">
@@ -22344,7 +22348,7 @@
       </c>
       <c r="Q128" s="23"/>
       <c r="R128" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O128:Q128)</f>
         <v>9</v>
       </c>
       <c r="S128" s="22">
@@ -22405,7 +22409,7 @@
       </c>
       <c r="Q129" s="25"/>
       <c r="R129" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O129:Q129)</f>
         <v>45</v>
       </c>
       <c r="S129" s="24">
@@ -22466,7 +22470,7 @@
       </c>
       <c r="Q130" s="23"/>
       <c r="R130" s="23">
-        <f t="shared" ref="R130:R193" si="2">SUM(O130:Q130)</f>
+        <f>SUM(O130:Q130)</f>
         <v>25</v>
       </c>
       <c r="S130" s="22">
@@ -22527,7 +22531,7 @@
       </c>
       <c r="Q131" s="25"/>
       <c r="R131" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O131:Q131)</f>
         <v>15</v>
       </c>
       <c r="S131" s="24">
@@ -22588,7 +22592,7 @@
       </c>
       <c r="Q132" s="23"/>
       <c r="R132" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O132:Q132)</f>
         <v>26</v>
       </c>
       <c r="S132" s="22">
@@ -22649,7 +22653,7 @@
       </c>
       <c r="Q133" s="25"/>
       <c r="R133" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O133:Q133)</f>
         <v>16</v>
       </c>
       <c r="S133" s="24">
@@ -22710,7 +22714,7 @@
       </c>
       <c r="Q134" s="23"/>
       <c r="R134" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O134:Q134)</f>
         <v>15</v>
       </c>
       <c r="S134" s="22">
@@ -22771,7 +22775,7 @@
       </c>
       <c r="Q135" s="25"/>
       <c r="R135" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O135:Q135)</f>
         <v>14</v>
       </c>
       <c r="S135" s="24">
@@ -22832,7 +22836,7 @@
       </c>
       <c r="Q136" s="23"/>
       <c r="R136" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O136:Q136)</f>
         <v>182</v>
       </c>
       <c r="S136" s="22">
@@ -22893,7 +22897,7 @@
       </c>
       <c r="Q137" s="25"/>
       <c r="R137" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O137:Q137)</f>
         <v>34</v>
       </c>
       <c r="S137" s="24">
@@ -22956,7 +22960,7 @@
         <v>0</v>
       </c>
       <c r="R138" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O138:Q138)</f>
         <v>17</v>
       </c>
       <c r="S138" s="22">
@@ -23017,7 +23021,7 @@
       </c>
       <c r="Q139" s="25"/>
       <c r="R139" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O139:Q139)</f>
         <v>20</v>
       </c>
       <c r="S139" s="24">
@@ -23078,7 +23082,7 @@
       </c>
       <c r="Q140" s="23"/>
       <c r="R140" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O140:Q140)</f>
         <v>40</v>
       </c>
       <c r="S140" s="22">
@@ -23141,7 +23145,7 @@
         <v>0</v>
       </c>
       <c r="R141" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O141:Q141)</f>
         <v>12</v>
       </c>
       <c r="S141" s="24">
@@ -23202,7 +23206,7 @@
       </c>
       <c r="Q142" s="23"/>
       <c r="R142" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O142:Q142)</f>
         <v>12</v>
       </c>
       <c r="S142" s="22">
@@ -23263,7 +23267,7 @@
       </c>
       <c r="Q143" s="25"/>
       <c r="R143" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O143:Q143)</f>
         <v>19</v>
       </c>
       <c r="S143" s="24">
@@ -23324,7 +23328,7 @@
       </c>
       <c r="Q144" s="23"/>
       <c r="R144" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O144:Q144)</f>
         <v>12</v>
       </c>
       <c r="S144" s="22">
@@ -23387,7 +23391,7 @@
         <v>0</v>
       </c>
       <c r="R145" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O145:Q145)</f>
         <v>31</v>
       </c>
       <c r="S145" s="24">
@@ -23448,7 +23452,7 @@
       </c>
       <c r="Q146" s="23"/>
       <c r="R146" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O146:Q146)</f>
         <v>27</v>
       </c>
       <c r="S146" s="22">
@@ -23509,7 +23513,7 @@
         <v>0</v>
       </c>
       <c r="R147" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O147:Q147)</f>
         <v>54</v>
       </c>
       <c r="S147" s="24">
@@ -23570,7 +23574,7 @@
       </c>
       <c r="Q148" s="23"/>
       <c r="R148" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O148:Q148)</f>
         <v>9</v>
       </c>
       <c r="S148" s="22">
@@ -23631,7 +23635,7 @@
       </c>
       <c r="Q149" s="25"/>
       <c r="R149" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O149:Q149)</f>
         <v>38</v>
       </c>
       <c r="S149" s="24">
@@ -23692,7 +23696,7 @@
       </c>
       <c r="Q150" s="23"/>
       <c r="R150" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O150:Q150)</f>
         <v>62</v>
       </c>
       <c r="S150" s="22">
@@ -23753,7 +23757,7 @@
       </c>
       <c r="Q151" s="25"/>
       <c r="R151" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O151:Q151)</f>
         <v>13</v>
       </c>
       <c r="S151" s="24">
@@ -23814,7 +23818,7 @@
       </c>
       <c r="Q152" s="23"/>
       <c r="R152" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O152:Q152)</f>
         <v>8</v>
       </c>
       <c r="S152" s="22">
@@ -23875,7 +23879,7 @@
       </c>
       <c r="Q153" s="25"/>
       <c r="R153" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O153:Q153)</f>
         <v>20</v>
       </c>
       <c r="S153" s="24">
@@ -23938,7 +23942,7 @@
         <v>0</v>
       </c>
       <c r="R154" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O154:Q154)</f>
         <v>74</v>
       </c>
       <c r="S154" s="22">
@@ -23999,7 +24003,7 @@
       </c>
       <c r="Q155" s="25"/>
       <c r="R155" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O155:Q155)</f>
         <v>24</v>
       </c>
       <c r="S155" s="24">
@@ -24062,7 +24066,7 @@
         <v>0</v>
       </c>
       <c r="R156" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O156:Q156)</f>
         <v>21</v>
       </c>
       <c r="S156" s="22">
@@ -24125,7 +24129,7 @@
         <v>0</v>
       </c>
       <c r="R157" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O157:Q157)</f>
         <v>21</v>
       </c>
       <c r="S157" s="24">
@@ -24188,7 +24192,7 @@
         <v>0</v>
       </c>
       <c r="R158" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O158:Q158)</f>
         <v>13</v>
       </c>
       <c r="S158" s="22">
@@ -24251,7 +24255,7 @@
         <v>78</v>
       </c>
       <c r="R159" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O159:Q159)</f>
         <v>117</v>
       </c>
       <c r="S159" s="24">
@@ -24314,7 +24318,7 @@
         <v>0</v>
       </c>
       <c r="R160" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O160:Q160)</f>
         <v>20</v>
       </c>
       <c r="S160" s="22">
@@ -24378,7 +24382,7 @@
         <v>0</v>
       </c>
       <c r="R161" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O161:Q161)</f>
         <v>22</v>
       </c>
       <c r="S161" s="24">
@@ -24441,7 +24445,7 @@
         <v>0</v>
       </c>
       <c r="R162" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O162:Q162)</f>
         <v>21</v>
       </c>
       <c r="S162" s="22">
@@ -24504,7 +24508,7 @@
         <v>0</v>
       </c>
       <c r="R163" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O163:Q163)</f>
         <v>59</v>
       </c>
       <c r="S163" s="24">
@@ -24567,7 +24571,7 @@
         <v>0</v>
       </c>
       <c r="R164" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O164:Q164)</f>
         <v>24</v>
       </c>
       <c r="S164" s="22">
@@ -24630,7 +24634,7 @@
         <v>0</v>
       </c>
       <c r="R165" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O165:Q165)</f>
         <v>41</v>
       </c>
       <c r="S165" s="24">
@@ -24693,7 +24697,7 @@
         <v>0</v>
       </c>
       <c r="R166" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O166:Q166)</f>
         <v>35</v>
       </c>
       <c r="S166" s="22">
@@ -24756,7 +24760,7 @@
         <v>0</v>
       </c>
       <c r="R167" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O167:Q167)</f>
         <v>15</v>
       </c>
       <c r="S167" s="24">
@@ -24819,7 +24823,7 @@
         <v>0</v>
       </c>
       <c r="R168" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O168:Q168)</f>
         <v>23</v>
       </c>
       <c r="S168" s="22">
@@ -24882,7 +24886,7 @@
         <v>0</v>
       </c>
       <c r="R169" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O169:Q169)</f>
         <v>36</v>
       </c>
       <c r="S169" s="24">
@@ -24945,7 +24949,7 @@
         <v>0</v>
       </c>
       <c r="R170" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O170:Q170)</f>
         <v>84</v>
       </c>
       <c r="S170" s="22">
@@ -25008,7 +25012,7 @@
         <v>0</v>
       </c>
       <c r="R171" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O171:Q171)</f>
         <v>40</v>
       </c>
       <c r="S171" s="24">
@@ -25071,7 +25075,7 @@
         <v>0</v>
       </c>
       <c r="R172" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O172:Q172)</f>
         <v>40</v>
       </c>
       <c r="S172" s="22">
@@ -25134,7 +25138,7 @@
         <v>0</v>
       </c>
       <c r="R173" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O173:Q173)</f>
         <v>44</v>
       </c>
       <c r="S173" s="24">
@@ -25197,7 +25201,7 @@
         <v>0</v>
       </c>
       <c r="R174" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O174:Q174)</f>
         <v>31</v>
       </c>
       <c r="S174" s="22">
@@ -25260,7 +25264,7 @@
         <v>0</v>
       </c>
       <c r="R175" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O175:Q175)</f>
         <v>29</v>
       </c>
       <c r="S175" s="24">
@@ -25323,7 +25327,7 @@
         <v>97</v>
       </c>
       <c r="R176" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O176:Q176)</f>
         <v>119</v>
       </c>
       <c r="S176" s="22">
@@ -25387,7 +25391,7 @@
         <v>0</v>
       </c>
       <c r="R177" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O177:Q177)</f>
         <v>122</v>
       </c>
       <c r="S177" s="24">
@@ -25451,7 +25455,7 @@
         <v>0</v>
       </c>
       <c r="R178" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O178:Q178)</f>
         <v>116</v>
       </c>
       <c r="S178" s="22">
@@ -25515,7 +25519,7 @@
         <v>0</v>
       </c>
       <c r="R179" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O179:Q179)</f>
         <v>83</v>
       </c>
       <c r="S179" s="24">
@@ -25578,7 +25582,7 @@
         <v>0</v>
       </c>
       <c r="R180" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O180:Q180)</f>
         <v>69</v>
       </c>
       <c r="S180" s="22">
@@ -25641,7 +25645,7 @@
         <v>0</v>
       </c>
       <c r="R181" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O181:Q181)</f>
         <v>48</v>
       </c>
       <c r="S181" s="24">
@@ -25704,7 +25708,7 @@
         <v>0</v>
       </c>
       <c r="R182" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O182:Q182)</f>
         <v>19</v>
       </c>
       <c r="S182" s="22">
@@ -25767,7 +25771,7 @@
         <v>73</v>
       </c>
       <c r="R183" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O183:Q183)</f>
         <v>73</v>
       </c>
       <c r="S183" s="24">
@@ -25830,7 +25834,7 @@
         <v>0</v>
       </c>
       <c r="R184" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O184:Q184)</f>
         <v>94</v>
       </c>
       <c r="S184" s="22">
@@ -25893,7 +25897,7 @@
         <v>0</v>
       </c>
       <c r="R185" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O185:Q185)</f>
         <v>42</v>
       </c>
       <c r="S185" s="24">
@@ -25956,7 +25960,7 @@
         <v>0</v>
       </c>
       <c r="R186" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O186:Q186)</f>
         <v>32</v>
       </c>
       <c r="S186" s="22">
@@ -26019,7 +26023,7 @@
         <v>0</v>
       </c>
       <c r="R187" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O187:Q187)</f>
         <v>22</v>
       </c>
       <c r="S187" s="24">
@@ -26083,7 +26087,7 @@
         <v>0</v>
       </c>
       <c r="R188" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O188:Q188)</f>
         <v>590</v>
       </c>
       <c r="S188" s="22">
@@ -26147,7 +26151,7 @@
         <v>0</v>
       </c>
       <c r="R189" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O189:Q189)</f>
         <v>41</v>
       </c>
       <c r="S189" s="24">
@@ -26210,7 +26214,7 @@
         <v>0</v>
       </c>
       <c r="R190" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O190:Q190)</f>
         <v>80</v>
       </c>
       <c r="S190" s="22">
@@ -26274,7 +26278,7 @@
         <v>36</v>
       </c>
       <c r="R191" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O191:Q191)</f>
         <v>36</v>
       </c>
       <c r="S191" s="24">
@@ -26337,7 +26341,7 @@
         <v>0</v>
       </c>
       <c r="R192" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O192:Q192)</f>
         <v>70</v>
       </c>
       <c r="S192" s="22">
@@ -26400,7 +26404,7 @@
         <v>0</v>
       </c>
       <c r="R193" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O193:Q193)</f>
         <v>21</v>
       </c>
       <c r="S193" s="24">
@@ -26463,7 +26467,7 @@
         <v>0</v>
       </c>
       <c r="R194" s="23">
-        <f t="shared" ref="R194:R257" si="3">SUM(O194:Q194)</f>
+        <f>SUM(O194:Q194)</f>
         <v>20</v>
       </c>
       <c r="S194" s="22">
@@ -26526,7 +26530,7 @@
         <v>0</v>
       </c>
       <c r="R195" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O195:Q195)</f>
         <v>28</v>
       </c>
       <c r="S195" s="24">
@@ -26589,7 +26593,7 @@
         <v>0</v>
       </c>
       <c r="R196" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O196:Q196)</f>
         <v>25</v>
       </c>
       <c r="S196" s="22">
@@ -26652,7 +26656,7 @@
         <v>0</v>
       </c>
       <c r="R197" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O197:Q197)</f>
         <v>14</v>
       </c>
       <c r="S197" s="24">
@@ -26715,7 +26719,7 @@
         <v>0</v>
       </c>
       <c r="R198" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O198:Q198)</f>
         <v>46</v>
       </c>
       <c r="S198" s="22">
@@ -26778,7 +26782,7 @@
         <v>0</v>
       </c>
       <c r="R199" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O199:Q199)</f>
         <v>98</v>
       </c>
       <c r="S199" s="24">
@@ -26841,7 +26845,7 @@
         <v>44</v>
       </c>
       <c r="R200" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O200:Q200)</f>
         <v>50</v>
       </c>
       <c r="S200" s="22">
@@ -26904,7 +26908,7 @@
         <v>0</v>
       </c>
       <c r="R201" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O201:Q201)</f>
         <v>17</v>
       </c>
       <c r="S201" s="24">
@@ -26967,7 +26971,7 @@
         <v>0</v>
       </c>
       <c r="R202" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O202:Q202)</f>
         <v>53</v>
       </c>
       <c r="S202" s="22">
@@ -27030,7 +27034,7 @@
         <v>0</v>
       </c>
       <c r="R203" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O203:Q203)</f>
         <v>16</v>
       </c>
       <c r="S203" s="24">
@@ -27093,7 +27097,7 @@
         <v>59</v>
       </c>
       <c r="R204" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O204:Q204)</f>
         <v>59</v>
       </c>
       <c r="S204" s="22">
@@ -27156,7 +27160,7 @@
         <v>0</v>
       </c>
       <c r="R205" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O205:Q205)</f>
         <v>76</v>
       </c>
       <c r="S205" s="24">
@@ -27219,7 +27223,7 @@
         <v>0</v>
       </c>
       <c r="R206" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O206:Q206)</f>
         <v>33</v>
       </c>
       <c r="S206" s="22">
@@ -27282,7 +27286,7 @@
         <v>0</v>
       </c>
       <c r="R207" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O207:Q207)</f>
         <v>58</v>
       </c>
       <c r="S207" s="24">
@@ -27345,7 +27349,7 @@
         <v>37</v>
       </c>
       <c r="R208" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O208:Q208)</f>
         <v>60</v>
       </c>
       <c r="S208" s="22">
@@ -27408,7 +27412,7 @@
         <v>0</v>
       </c>
       <c r="R209" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O209:Q209)</f>
         <v>13</v>
       </c>
       <c r="S209" s="24">
@@ -27471,7 +27475,7 @@
         <v>0</v>
       </c>
       <c r="R210" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O210:Q210)</f>
         <v>14</v>
       </c>
       <c r="S210" s="22">
@@ -27534,7 +27538,7 @@
         <v>0</v>
       </c>
       <c r="R211" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O211:Q211)</f>
         <v>53</v>
       </c>
       <c r="S211" s="24">
@@ -27597,7 +27601,7 @@
         <v>0</v>
       </c>
       <c r="R212" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O212:Q212)</f>
         <v>105</v>
       </c>
       <c r="S212" s="22">
@@ -27660,7 +27664,7 @@
         <v>147</v>
       </c>
       <c r="R213" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O213:Q213)</f>
         <v>635</v>
       </c>
       <c r="S213" s="24">
@@ -27723,7 +27727,7 @@
         <v>0</v>
       </c>
       <c r="R214" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O214:Q214)</f>
         <v>34</v>
       </c>
       <c r="S214" s="22">
@@ -27786,7 +27790,7 @@
         <v>0</v>
       </c>
       <c r="R215" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O215:Q215)</f>
         <v>32</v>
       </c>
       <c r="S215" s="24">
@@ -27849,7 +27853,7 @@
         <v>0</v>
       </c>
       <c r="R216" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O216:Q216)</f>
         <v>10</v>
       </c>
       <c r="S216" s="22">
@@ -27912,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="R217" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O217:Q217)</f>
         <v>16</v>
       </c>
       <c r="S217" s="24">
@@ -27975,7 +27979,7 @@
         <v>0</v>
       </c>
       <c r="R218" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O218:Q218)</f>
         <v>20</v>
       </c>
       <c r="S218" s="22">
@@ -28039,7 +28043,7 @@
         <v>59</v>
       </c>
       <c r="R219" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O219:Q219)</f>
         <v>59</v>
       </c>
       <c r="S219" s="24">
@@ -28102,7 +28106,7 @@
         <v>0</v>
       </c>
       <c r="R220" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O220:Q220)</f>
         <v>70</v>
       </c>
       <c r="S220" s="22">
@@ -28165,7 +28169,7 @@
         <v>30</v>
       </c>
       <c r="R221" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O221:Q221)</f>
         <v>30</v>
       </c>
       <c r="S221" s="24">
@@ -28228,7 +28232,7 @@
         <v>0</v>
       </c>
       <c r="R222" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O222:Q222)</f>
         <v>14</v>
       </c>
       <c r="S222" s="22">
@@ -28291,7 +28295,7 @@
         <v>1</v>
       </c>
       <c r="R223" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O223:Q223)</f>
         <v>29</v>
       </c>
       <c r="S223" s="24">
@@ -28354,7 +28358,7 @@
         <v>0</v>
       </c>
       <c r="R224" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O224:Q224)</f>
         <v>37</v>
       </c>
       <c r="S224" s="22">
@@ -28417,7 +28421,7 @@
         <v>0</v>
       </c>
       <c r="R225" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O225:Q225)</f>
         <v>24</v>
       </c>
       <c r="S225" s="24">
@@ -28480,7 +28484,7 @@
         <v>0</v>
       </c>
       <c r="R226" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O226:Q226)</f>
         <v>32</v>
       </c>
       <c r="S226" s="22">
@@ -28543,7 +28547,7 @@
         <v>0</v>
       </c>
       <c r="R227" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O227:Q227)</f>
         <v>14</v>
       </c>
       <c r="S227" s="24">
@@ -28606,7 +28610,7 @@
         <v>0</v>
       </c>
       <c r="R228" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O228:Q228)</f>
         <v>31</v>
       </c>
       <c r="S228" s="22">
@@ -28669,7 +28673,7 @@
         <v>0</v>
       </c>
       <c r="R229" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O229:Q229)</f>
         <v>30</v>
       </c>
       <c r="S229" s="24">
@@ -28732,7 +28736,7 @@
         <v>5</v>
       </c>
       <c r="R230" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O230:Q230)</f>
         <v>52</v>
       </c>
       <c r="S230" s="22">
@@ -28795,7 +28799,7 @@
         <v>0</v>
       </c>
       <c r="R231" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O231:Q231)</f>
         <v>89</v>
       </c>
       <c r="S231" s="24">
@@ -28858,7 +28862,7 @@
         <v>0</v>
       </c>
       <c r="R232" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O232:Q232)</f>
         <v>13</v>
       </c>
       <c r="S232" s="22">
@@ -28921,7 +28925,7 @@
         <v>0</v>
       </c>
       <c r="R233" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O233:Q233)</f>
         <v>38</v>
       </c>
       <c r="S233" s="24">
@@ -28984,7 +28988,7 @@
         <v>0</v>
       </c>
       <c r="R234" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O234:Q234)</f>
         <v>44</v>
       </c>
       <c r="S234" s="22">
@@ -29047,7 +29051,7 @@
         <v>0</v>
       </c>
       <c r="R235" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O235:Q235)</f>
         <v>21</v>
       </c>
       <c r="S235" s="24">
@@ -29110,7 +29114,7 @@
         <v>0</v>
       </c>
       <c r="R236" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O236:Q236)</f>
         <v>45</v>
       </c>
       <c r="S236" s="22">
@@ -29173,7 +29177,7 @@
         <v>0</v>
       </c>
       <c r="R237" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O237:Q237)</f>
         <v>70</v>
       </c>
       <c r="S237" s="24">
@@ -29236,7 +29240,7 @@
         <v>0</v>
       </c>
       <c r="R238" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O238:Q238)</f>
         <v>15</v>
       </c>
       <c r="S238" s="22">
@@ -29299,7 +29303,7 @@
         <v>51</v>
       </c>
       <c r="R239" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O239:Q239)</f>
         <v>51</v>
       </c>
       <c r="S239" s="24">
@@ -29363,7 +29367,7 @@
         <v>31</v>
       </c>
       <c r="R240" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O240:Q240)</f>
         <v>31</v>
       </c>
       <c r="S240" s="22">
@@ -29426,7 +29430,7 @@
         <v>0</v>
       </c>
       <c r="R241" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O241:Q241)</f>
         <v>140</v>
       </c>
       <c r="S241" s="24">
@@ -29489,7 +29493,7 @@
         <v>0</v>
       </c>
       <c r="R242" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O242:Q242)</f>
         <v>15</v>
       </c>
       <c r="S242" s="22">
@@ -29552,7 +29556,7 @@
         <v>0</v>
       </c>
       <c r="R243" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O243:Q243)</f>
         <v>18</v>
       </c>
       <c r="S243" s="24">
@@ -29615,7 +29619,7 @@
         <v>0</v>
       </c>
       <c r="R244" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O244:Q244)</f>
         <v>55</v>
       </c>
       <c r="S244" s="22">
@@ -29678,7 +29682,7 @@
         <v>120</v>
       </c>
       <c r="R245" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O245:Q245)</f>
         <v>120</v>
       </c>
       <c r="S245" s="24">
@@ -29741,7 +29745,7 @@
         <v>22</v>
       </c>
       <c r="R246" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O246:Q246)</f>
         <v>34</v>
       </c>
       <c r="S246" s="22">
@@ -29804,7 +29808,7 @@
         <v>0</v>
       </c>
       <c r="R247" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O247:Q247)</f>
         <v>37</v>
       </c>
       <c r="S247" s="24">
@@ -29867,7 +29871,7 @@
         <v>0</v>
       </c>
       <c r="R248" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O248:Q248)</f>
         <v>6</v>
       </c>
       <c r="S248" s="22">
@@ -29930,7 +29934,7 @@
         <v>0</v>
       </c>
       <c r="R249" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O249:Q249)</f>
         <v>25</v>
       </c>
       <c r="S249" s="24">
@@ -29993,7 +29997,7 @@
         <v>0</v>
       </c>
       <c r="R250" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O250:Q250)</f>
         <v>26</v>
       </c>
       <c r="S250" s="22">
@@ -30056,7 +30060,7 @@
         <v>56</v>
       </c>
       <c r="R251" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O251:Q251)</f>
         <v>56</v>
       </c>
       <c r="S251" s="24">
@@ -30120,7 +30124,7 @@
         <v>0</v>
       </c>
       <c r="R252" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O252:Q252)</f>
         <v>26</v>
       </c>
       <c r="S252" s="22">
@@ -30183,7 +30187,7 @@
         <v>0</v>
       </c>
       <c r="R253" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O253:Q253)</f>
         <v>26</v>
       </c>
       <c r="S253" s="24">
@@ -30246,7 +30250,7 @@
         <v>0</v>
       </c>
       <c r="R254" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O254:Q254)</f>
         <v>11</v>
       </c>
       <c r="S254" s="22">
@@ -30307,7 +30311,7 @@
         <v>0</v>
       </c>
       <c r="R255" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O255:Q255)</f>
         <v>14</v>
       </c>
       <c r="S255" s="24">
@@ -30370,7 +30374,7 @@
         <v>49</v>
       </c>
       <c r="R256" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O256:Q256)</f>
         <v>49</v>
       </c>
       <c r="S256" s="22">
@@ -30433,7 +30437,7 @@
         <v>0</v>
       </c>
       <c r="R257" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O257:Q257)</f>
         <v>27</v>
       </c>
       <c r="S257" s="24">
@@ -30496,7 +30500,7 @@
         <v>7</v>
       </c>
       <c r="R258" s="23">
-        <f t="shared" ref="R258:R321" si="4">SUM(O258:Q258)</f>
+        <f>SUM(O258:Q258)</f>
         <v>22</v>
       </c>
       <c r="S258" s="22">
@@ -30559,7 +30563,7 @@
         <v>0</v>
       </c>
       <c r="R259" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O259:Q259)</f>
         <v>18</v>
       </c>
       <c r="S259" s="24">
@@ -30622,7 +30626,7 @@
         <v>31</v>
       </c>
       <c r="R260" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O260:Q260)</f>
         <v>31</v>
       </c>
       <c r="S260" s="22">
@@ -30685,7 +30689,7 @@
         <v>0</v>
       </c>
       <c r="R261" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O261:Q261)</f>
         <v>25</v>
       </c>
       <c r="S261" s="24">
@@ -30748,7 +30752,7 @@
         <v>0</v>
       </c>
       <c r="R262" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O262:Q262)</f>
         <v>9</v>
       </c>
       <c r="S262" s="22">
@@ -30811,7 +30815,7 @@
         <v>0</v>
       </c>
       <c r="R263" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O263:Q263)</f>
         <v>8</v>
       </c>
       <c r="S263" s="24">
@@ -30874,7 +30878,7 @@
         <v>29</v>
       </c>
       <c r="R264" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O264:Q264)</f>
         <v>29</v>
       </c>
       <c r="S264" s="22">
@@ -30937,7 +30941,7 @@
         <v>21</v>
       </c>
       <c r="R265" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O265:Q265)</f>
         <v>24</v>
       </c>
       <c r="S265" s="24">
@@ -31000,7 +31004,7 @@
         <v>0</v>
       </c>
       <c r="R266" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O266:Q266)</f>
         <v>66</v>
       </c>
       <c r="S266" s="22">
@@ -31063,7 +31067,7 @@
         <v>20</v>
       </c>
       <c r="R267" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O267:Q267)</f>
         <v>20</v>
       </c>
       <c r="S267" s="24">
@@ -31126,7 +31130,7 @@
         <v>0</v>
       </c>
       <c r="R268" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O268:Q268)</f>
         <v>13</v>
       </c>
       <c r="S268" s="22">
@@ -31189,7 +31193,7 @@
         <v>0</v>
       </c>
       <c r="R269" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O269:Q269)</f>
         <v>15</v>
       </c>
       <c r="S269" s="24">
@@ -31252,7 +31256,7 @@
         <v>0</v>
       </c>
       <c r="R270" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O270:Q270)</f>
         <v>5</v>
       </c>
       <c r="S270" s="22">
@@ -31315,7 +31319,7 @@
         <v>0</v>
       </c>
       <c r="R271" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O271:Q271)</f>
         <v>18</v>
       </c>
       <c r="S271" s="24">
@@ -31378,7 +31382,7 @@
         <v>0</v>
       </c>
       <c r="R272" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O272:Q272)</f>
         <v>8</v>
       </c>
       <c r="S272" s="22">
@@ -31441,7 +31445,7 @@
         <v>0</v>
       </c>
       <c r="R273" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O273:Q273)</f>
         <v>83</v>
       </c>
       <c r="S273" s="24">
@@ -31504,7 +31508,7 @@
         <v>0</v>
       </c>
       <c r="R274" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O274:Q274)</f>
         <v>24</v>
       </c>
       <c r="S274" s="22">
@@ -31567,7 +31571,7 @@
         <v>0</v>
       </c>
       <c r="R275" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O275:Q275)</f>
         <v>20</v>
       </c>
       <c r="S275" s="24">
@@ -31630,7 +31634,7 @@
         <v>39</v>
       </c>
       <c r="R276" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O276:Q276)</f>
         <v>39</v>
       </c>
       <c r="S276" s="22">
@@ -31693,7 +31697,7 @@
         <v>0</v>
       </c>
       <c r="R277" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O277:Q277)</f>
         <v>39</v>
       </c>
       <c r="S277" s="24">
@@ -31756,7 +31760,7 @@
         <v>0</v>
       </c>
       <c r="R278" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O278:Q278)</f>
         <v>277</v>
       </c>
       <c r="S278" s="22">
@@ -31819,7 +31823,7 @@
         <v>0</v>
       </c>
       <c r="R279" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O279:Q279)</f>
         <v>43</v>
       </c>
       <c r="S279" s="24">
@@ -31882,7 +31886,7 @@
         <v>0</v>
       </c>
       <c r="R280" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O280:Q280)</f>
         <v>21</v>
       </c>
       <c r="S280" s="22">
@@ -31945,7 +31949,7 @@
         <v>84</v>
       </c>
       <c r="R281" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O281:Q281)</f>
         <v>144</v>
       </c>
       <c r="S281" s="24">
@@ -32008,7 +32012,7 @@
         <v>0</v>
       </c>
       <c r="R282" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O282:Q282)</f>
         <v>19</v>
       </c>
       <c r="S282" s="22">
@@ -32071,7 +32075,7 @@
         <v>64</v>
       </c>
       <c r="R283" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O283:Q283)</f>
         <v>65</v>
       </c>
       <c r="S283" s="24">
@@ -32134,7 +32138,7 @@
         <v>0</v>
       </c>
       <c r="R284" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O284:Q284)</f>
         <v>72</v>
       </c>
       <c r="S284" s="22">
@@ -32197,7 +32201,7 @@
         <v>193</v>
       </c>
       <c r="R285" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O285:Q285)</f>
         <v>193</v>
       </c>
       <c r="S285" s="24">
@@ -32260,7 +32264,7 @@
         <v>0</v>
       </c>
       <c r="R286" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O286:Q286)</f>
         <v>46</v>
       </c>
       <c r="S286" s="22">
@@ -32323,7 +32327,7 @@
         <v>20</v>
       </c>
       <c r="R287" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O287:Q287)</f>
         <v>20</v>
       </c>
       <c r="S287" s="24">
@@ -32384,7 +32388,7 @@
         <v>0</v>
       </c>
       <c r="R288" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O288:Q288)</f>
         <v>23</v>
       </c>
       <c r="S288" s="22">
@@ -32445,7 +32449,7 @@
         <v>0</v>
       </c>
       <c r="R289" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O289:Q289)</f>
         <v>80</v>
       </c>
       <c r="S289" s="24">
@@ -32508,7 +32512,7 @@
         <v>0</v>
       </c>
       <c r="R290" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O290:Q290)</f>
         <v>21</v>
       </c>
       <c r="S290" s="22">
@@ -32571,7 +32575,7 @@
         <v>0</v>
       </c>
       <c r="R291" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O291:Q291)</f>
         <v>28</v>
       </c>
       <c r="S291" s="24">
@@ -32634,7 +32638,7 @@
         <v>35</v>
       </c>
       <c r="R292" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O292:Q292)</f>
         <v>35</v>
       </c>
       <c r="S292" s="22">
@@ -32697,7 +32701,7 @@
         <v>0</v>
       </c>
       <c r="R293" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O293:Q293)</f>
         <v>20</v>
       </c>
       <c r="S293" s="24">
@@ -32760,7 +32764,7 @@
         <v>0</v>
       </c>
       <c r="R294" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O294:Q294)</f>
         <v>188</v>
       </c>
       <c r="S294" s="22">
@@ -32823,7 +32827,7 @@
         <v>0</v>
       </c>
       <c r="R295" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O295:Q295)</f>
         <v>42</v>
       </c>
       <c r="S295" s="24">
@@ -32886,7 +32890,7 @@
         <v>0</v>
       </c>
       <c r="R296" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O296:Q296)</f>
         <v>31</v>
       </c>
       <c r="S296" s="22">
@@ -32950,7 +32954,7 @@
         <v>0</v>
       </c>
       <c r="R297" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O297:Q297)</f>
         <v>20</v>
       </c>
       <c r="S297" s="24">
@@ -33011,7 +33015,7 @@
         <v>0</v>
       </c>
       <c r="R298" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O298:Q298)</f>
         <v>70</v>
       </c>
       <c r="S298" s="22">
@@ -33074,7 +33078,7 @@
         <v>52</v>
       </c>
       <c r="R299" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O299:Q299)</f>
         <v>85</v>
       </c>
       <c r="S299" s="24">
@@ -33137,7 +33141,7 @@
         <v>54</v>
       </c>
       <c r="R300" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O300:Q300)</f>
         <v>54</v>
       </c>
       <c r="S300" s="22">
@@ -33200,7 +33204,7 @@
         <v>130</v>
       </c>
       <c r="R301" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O301:Q301)</f>
         <v>153</v>
       </c>
       <c r="S301" s="24">
@@ -33263,7 +33267,7 @@
         <v>0</v>
       </c>
       <c r="R302" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O302:Q302)</f>
         <v>19</v>
       </c>
       <c r="S302" s="22">
@@ -33326,7 +33330,7 @@
         <v>0</v>
       </c>
       <c r="R303" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O303:Q303)</f>
         <v>20</v>
       </c>
       <c r="S303" s="24">
@@ -33383,7 +33387,7 @@
       <c r="P304" s="23"/>
       <c r="Q304" s="23"/>
       <c r="R304" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O304:Q304)</f>
         <v>25</v>
       </c>
       <c r="S304" s="22">
@@ -33446,7 +33450,7 @@
         <v>0</v>
       </c>
       <c r="R305" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O305:Q305)</f>
         <v>70</v>
       </c>
       <c r="S305" s="24">
@@ -33509,7 +33513,7 @@
         <v>0</v>
       </c>
       <c r="R306" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O306:Q306)</f>
         <v>17</v>
       </c>
       <c r="S306" s="22">
@@ -33570,7 +33574,7 @@
         <v>1</v>
       </c>
       <c r="R307" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O307:Q307)</f>
         <v>24</v>
       </c>
       <c r="S307" s="24">
@@ -33634,7 +33638,7 @@
         <v>0</v>
       </c>
       <c r="R308" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O308:Q308)</f>
         <v>17</v>
       </c>
       <c r="S308" s="22">
@@ -33697,7 +33701,7 @@
         <v>0</v>
       </c>
       <c r="R309" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O309:Q309)</f>
         <v>17</v>
       </c>
       <c r="S309" s="24">
@@ -33760,7 +33764,7 @@
         <v>1</v>
       </c>
       <c r="R310" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O310:Q310)</f>
         <v>45</v>
       </c>
       <c r="S310" s="22">
@@ -33823,7 +33827,7 @@
         <v>0</v>
       </c>
       <c r="R311" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O311:Q311)</f>
         <v>26</v>
       </c>
       <c r="S311" s="24">
@@ -33887,7 +33891,7 @@
         <v>0</v>
       </c>
       <c r="R312" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O312:Q312)</f>
         <v>17</v>
       </c>
       <c r="S312" s="22">
@@ -33950,7 +33954,7 @@
         <v>0</v>
       </c>
       <c r="R313" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O313:Q313)</f>
         <v>30</v>
       </c>
       <c r="S313" s="24">
@@ -34014,7 +34018,7 @@
         <v>0</v>
       </c>
       <c r="R314" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O314:Q314)</f>
         <v>20</v>
       </c>
       <c r="S314" s="22">
@@ -34077,7 +34081,7 @@
         <v>33</v>
       </c>
       <c r="R315" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O315:Q315)</f>
         <v>33</v>
       </c>
       <c r="S315" s="24">
@@ -34140,7 +34144,7 @@
         <v>0</v>
       </c>
       <c r="R316" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O316:Q316)</f>
         <v>17</v>
       </c>
       <c r="S316" s="22">
@@ -34203,7 +34207,7 @@
         <v>0</v>
       </c>
       <c r="R317" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O317:Q317)</f>
         <v>15</v>
       </c>
       <c r="S317" s="24">
@@ -34266,7 +34270,7 @@
         <v>19</v>
       </c>
       <c r="R318" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O318:Q318)</f>
         <v>19</v>
       </c>
       <c r="S318" s="22">
@@ -34330,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="R319" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O319:Q319)</f>
         <v>16</v>
       </c>
       <c r="S319" s="24">
@@ -34394,7 +34398,7 @@
         <v>0</v>
       </c>
       <c r="R320" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O320:Q320)</f>
         <v>49</v>
       </c>
       <c r="S320" s="22">
@@ -34458,7 +34462,7 @@
         <v>0</v>
       </c>
       <c r="R321" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O321:Q321)</f>
         <v>126</v>
       </c>
       <c r="S321" s="24">
@@ -34521,7 +34525,7 @@
         <v>40</v>
       </c>
       <c r="R322" s="23">
-        <f t="shared" ref="R322:R385" si="5">SUM(O322:Q322)</f>
+        <f>SUM(O322:Q322)</f>
         <v>40</v>
       </c>
       <c r="S322" s="22">
@@ -34584,7 +34588,7 @@
         <v>40</v>
       </c>
       <c r="R323" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O323:Q323)</f>
         <v>40</v>
       </c>
       <c r="S323" s="24">
@@ -34647,7 +34651,7 @@
         <v>60</v>
       </c>
       <c r="R324" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O324:Q324)</f>
         <v>60</v>
       </c>
       <c r="S324" s="22">
@@ -34710,7 +34714,7 @@
         <v>30</v>
       </c>
       <c r="R325" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O325:Q325)</f>
         <v>30</v>
       </c>
       <c r="S325" s="24">
@@ -34773,7 +34777,7 @@
         <v>0</v>
       </c>
       <c r="R326" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O326:Q326)</f>
         <v>21</v>
       </c>
       <c r="S326" s="22">
@@ -34836,7 +34840,7 @@
         <v>0</v>
       </c>
       <c r="R327" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O327:Q327)</f>
         <v>20</v>
       </c>
       <c r="S327" s="24">
@@ -34899,7 +34903,7 @@
         <v>39</v>
       </c>
       <c r="R328" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O328:Q328)</f>
         <v>40</v>
       </c>
       <c r="S328" s="22">
@@ -34962,7 +34966,7 @@
         <v>0</v>
       </c>
       <c r="R329" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O329:Q329)</f>
         <v>80</v>
       </c>
       <c r="S329" s="24">
@@ -35025,7 +35029,7 @@
         <v>0</v>
       </c>
       <c r="R330" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O330:Q330)</f>
         <v>26</v>
       </c>
       <c r="S330" s="22">
@@ -35088,7 +35092,7 @@
         <v>0</v>
       </c>
       <c r="R331" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O331:Q331)</f>
         <v>15</v>
       </c>
       <c r="S331" s="24">
@@ -35151,7 +35155,7 @@
         <v>0</v>
       </c>
       <c r="R332" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O332:Q332)</f>
         <v>23</v>
       </c>
       <c r="S332" s="22">
@@ -35214,7 +35218,7 @@
         <v>0</v>
       </c>
       <c r="R333" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O333:Q333)</f>
         <v>207</v>
       </c>
       <c r="S333" s="24">
@@ -35277,7 +35281,7 @@
         <v>0</v>
       </c>
       <c r="R334" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O334:Q334)</f>
         <v>13</v>
       </c>
       <c r="S334" s="22">
@@ -35340,7 +35344,7 @@
         <v>0</v>
       </c>
       <c r="R335" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O335:Q335)</f>
         <v>184</v>
       </c>
       <c r="S335" s="24">
@@ -35403,7 +35407,7 @@
         <v>0</v>
       </c>
       <c r="R336" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O336:Q336)</f>
         <v>46</v>
       </c>
       <c r="S336" s="22">
@@ -35466,7 +35470,7 @@
         <v>16</v>
       </c>
       <c r="R337" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O337:Q337)</f>
         <v>60</v>
       </c>
       <c r="S337" s="24">
@@ -35529,7 +35533,7 @@
         <v>45</v>
       </c>
       <c r="R338" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O338:Q338)</f>
         <v>48</v>
       </c>
       <c r="S338" s="22">
@@ -35584,7 +35588,7 @@
         <v>40</v>
       </c>
       <c r="R339" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O339:Q339)</f>
         <v>40</v>
       </c>
       <c r="S339" s="24">
@@ -35643,7 +35647,7 @@
         <v>0</v>
       </c>
       <c r="R340" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O340:Q340)</f>
         <v>150</v>
       </c>
       <c r="S340" s="22">
@@ -35706,7 +35710,7 @@
         <v>0</v>
       </c>
       <c r="R341" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O341:Q341)</f>
         <v>20</v>
       </c>
       <c r="S341" s="24">
@@ -35761,7 +35765,7 @@
         <v>30</v>
       </c>
       <c r="R342" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O342:Q342)</f>
         <v>30</v>
       </c>
       <c r="S342" s="22">
@@ -35825,7 +35829,7 @@
         <v>0</v>
       </c>
       <c r="R343" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O343:Q343)</f>
         <v>67</v>
       </c>
       <c r="S343" s="24">
@@ -35888,7 +35892,7 @@
         <v>0</v>
       </c>
       <c r="R344" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O344:Q344)</f>
         <v>67</v>
       </c>
       <c r="S344" s="22">
@@ -35951,7 +35955,7 @@
         <v>0</v>
       </c>
       <c r="R345" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O345:Q345)</f>
         <v>57</v>
       </c>
       <c r="S345" s="24">
@@ -36014,7 +36018,7 @@
         <v>0</v>
       </c>
       <c r="R346" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O346:Q346)</f>
         <v>20</v>
       </c>
       <c r="S346" s="22">
@@ -36077,7 +36081,7 @@
         <v>0</v>
       </c>
       <c r="R347" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O347:Q347)</f>
         <v>315</v>
       </c>
       <c r="S347" s="24">
@@ -36140,7 +36144,7 @@
         <v>0</v>
       </c>
       <c r="R348" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O348:Q348)</f>
         <v>35</v>
       </c>
       <c r="S348" s="22">
@@ -36203,7 +36207,7 @@
         <v>0</v>
       </c>
       <c r="R349" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O349:Q349)</f>
         <v>17</v>
       </c>
       <c r="S349" s="24">
@@ -36267,7 +36271,7 @@
         <v>0</v>
       </c>
       <c r="R350" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O350:Q350)</f>
         <v>27</v>
       </c>
       <c r="S350" s="22">
@@ -36330,7 +36334,7 @@
         <v>0</v>
       </c>
       <c r="R351" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O351:Q351)</f>
         <v>45</v>
       </c>
       <c r="S351" s="24">
@@ -36393,7 +36397,7 @@
         <v>0</v>
       </c>
       <c r="R352" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O352:Q352)</f>
         <v>51</v>
       </c>
       <c r="S352" s="22">
@@ -36456,7 +36460,7 @@
         <v>0</v>
       </c>
       <c r="R353" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O353:Q353)</f>
         <v>5</v>
       </c>
       <c r="S353" s="24">
@@ -36519,7 +36523,7 @@
         <v>0</v>
       </c>
       <c r="R354" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O354:Q354)</f>
         <v>16</v>
       </c>
       <c r="S354" s="22">
@@ -36582,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="R355" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O355:Q355)</f>
         <v>30</v>
       </c>
       <c r="S355" s="24">
@@ -36645,7 +36649,7 @@
         <v>0</v>
       </c>
       <c r="R356" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O356:Q356)</f>
         <v>64</v>
       </c>
       <c r="S356" s="22">
@@ -36707,7 +36711,7 @@
         <v>0</v>
       </c>
       <c r="R357" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O357:Q357)</f>
         <v>57</v>
       </c>
       <c r="S357" s="24">
@@ -36770,7 +36774,7 @@
         <v>0</v>
       </c>
       <c r="R358" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O358:Q358)</f>
         <v>39</v>
       </c>
       <c r="S358" s="22">
@@ -36833,7 +36837,7 @@
         <v>0</v>
       </c>
       <c r="R359" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O359:Q359)</f>
         <v>16</v>
       </c>
       <c r="S359" s="24">
@@ -36896,7 +36900,7 @@
         <v>0</v>
       </c>
       <c r="R360" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O360:Q360)</f>
         <v>47</v>
       </c>
       <c r="S360" s="22">
@@ -36959,7 +36963,7 @@
         <v>2</v>
       </c>
       <c r="R361" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O361:Q361)</f>
         <v>13</v>
       </c>
       <c r="S361" s="24">
@@ -37022,7 +37026,7 @@
         <v>0</v>
       </c>
       <c r="R362" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O362:Q362)</f>
         <v>26</v>
       </c>
       <c r="S362" s="22">
@@ -37085,7 +37089,7 @@
         <v>43</v>
       </c>
       <c r="R363" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O363:Q363)</f>
         <v>43</v>
       </c>
       <c r="S363" s="24">
@@ -37148,7 +37152,7 @@
         <v>0</v>
       </c>
       <c r="R364" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O364:Q364)</f>
         <v>11</v>
       </c>
       <c r="S364" s="22">
@@ -37211,7 +37215,7 @@
         <v>0</v>
       </c>
       <c r="R365" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O365:Q365)</f>
         <v>11</v>
       </c>
       <c r="S365" s="24">
@@ -37275,7 +37279,7 @@
         <v>57</v>
       </c>
       <c r="R366" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O366:Q366)</f>
         <v>57</v>
       </c>
       <c r="S366" s="22">
@@ -37339,7 +37343,7 @@
         <v>0</v>
       </c>
       <c r="R367" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O367:Q367)</f>
         <v>22</v>
       </c>
       <c r="S367" s="24">
@@ -37402,7 +37406,7 @@
         <v>0</v>
       </c>
       <c r="R368" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O368:Q368)</f>
         <v>176</v>
       </c>
       <c r="S368" s="22">
@@ -37463,7 +37467,7 @@
         <v>0</v>
       </c>
       <c r="R369" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O369:Q369)</f>
         <v>56</v>
       </c>
       <c r="S369" s="24">
@@ -37527,7 +37531,7 @@
         <v>0</v>
       </c>
       <c r="R370" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O370:Q370)</f>
         <v>23</v>
       </c>
       <c r="S370" s="22">
@@ -37590,7 +37594,7 @@
         <v>39</v>
       </c>
       <c r="R371" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O371:Q371)</f>
         <v>39</v>
       </c>
       <c r="S371" s="24">
@@ -37653,7 +37657,7 @@
         <v>0</v>
       </c>
       <c r="R372" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O372:Q372)</f>
         <v>47</v>
       </c>
       <c r="S372" s="22">
@@ -37715,7 +37719,7 @@
         <v>53</v>
       </c>
       <c r="R373" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O373:Q373)</f>
         <v>53</v>
       </c>
       <c r="S373" s="24">
@@ -37778,7 +37782,7 @@
         <v>0</v>
       </c>
       <c r="R374" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O374:Q374)</f>
         <v>28</v>
       </c>
       <c r="S374" s="22">
@@ -37842,7 +37846,7 @@
         <v>0</v>
       </c>
       <c r="R375" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O375:Q375)</f>
         <v>18</v>
       </c>
       <c r="S375" s="24">
@@ -37906,7 +37910,7 @@
         <v>53</v>
       </c>
       <c r="R376" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O376:Q376)</f>
         <v>53</v>
       </c>
       <c r="S376" s="22">
@@ -37970,7 +37974,7 @@
         <v>0</v>
       </c>
       <c r="R377" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O377:Q377)</f>
         <v>10</v>
       </c>
       <c r="S377" s="24">
@@ -38034,7 +38038,7 @@
         <v>0</v>
       </c>
       <c r="R378" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O378:Q378)</f>
         <v>34</v>
       </c>
       <c r="S378" s="22">
@@ -38089,7 +38093,7 @@
         <v>0</v>
       </c>
       <c r="R379" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O379:Q379)</f>
         <v>0</v>
       </c>
       <c r="S379" s="24"/>
@@ -38148,7 +38152,7 @@
         <v>0</v>
       </c>
       <c r="R380" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O380:Q380)</f>
         <v>15</v>
       </c>
       <c r="S380" s="22">
@@ -38203,7 +38207,7 @@
       <c r="P381" s="25"/>
       <c r="Q381" s="25"/>
       <c r="R381" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O381:Q381)</f>
         <v>21</v>
       </c>
       <c r="S381" s="24">
@@ -38265,7 +38269,7 @@
         <v>17</v>
       </c>
       <c r="R382" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O382:Q382)</f>
         <v>17</v>
       </c>
       <c r="S382" s="22">
@@ -38329,7 +38333,7 @@
         <v>0</v>
       </c>
       <c r="R383" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O383:Q383)</f>
         <v>13</v>
       </c>
       <c r="S383" s="24">
@@ -38392,7 +38396,7 @@
         <v>0</v>
       </c>
       <c r="R384" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O384:Q384)</f>
         <v>114</v>
       </c>
       <c r="S384" s="22">
@@ -38453,7 +38457,7 @@
         <v>0</v>
       </c>
       <c r="R385" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O385:Q385)</f>
         <v>5</v>
       </c>
       <c r="S385" s="24">
@@ -38516,7 +38520,7 @@
         <v>0</v>
       </c>
       <c r="R386" s="23">
-        <f t="shared" ref="R386:R392" si="6">SUM(O386:Q386)</f>
+        <f>SUM(O386:Q386)</f>
         <v>49</v>
       </c>
       <c r="S386" s="22">
@@ -38579,7 +38583,7 @@
         <v>0</v>
       </c>
       <c r="R387" s="25">
-        <f t="shared" si="6"/>
+        <f>SUM(O387:Q387)</f>
         <v>22</v>
       </c>
       <c r="S387" s="24">
@@ -38642,7 +38646,7 @@
         <v>26</v>
       </c>
       <c r="R388" s="23">
-        <f t="shared" si="6"/>
+        <f>SUM(O388:Q388)</f>
         <v>91</v>
       </c>
       <c r="S388" s="22">
@@ -38706,7 +38710,7 @@
         <v>5</v>
       </c>
       <c r="R389" s="25">
-        <f t="shared" si="6"/>
+        <f>SUM(O389:Q389)</f>
         <v>5</v>
       </c>
       <c r="S389" s="24">
@@ -38769,7 +38773,7 @@
         <v>0</v>
       </c>
       <c r="R390" s="23">
-        <f t="shared" si="6"/>
+        <f>SUM(O390:Q390)</f>
         <v>181</v>
       </c>
       <c r="S390" s="22">
@@ -38833,7 +38837,7 @@
         <v>7</v>
       </c>
       <c r="R391" s="25">
-        <f t="shared" si="6"/>
+        <f>SUM(O391:Q391)</f>
         <v>7</v>
       </c>
       <c r="S391" s="24">
@@ -38896,7 +38900,7 @@
         <v>0</v>
       </c>
       <c r="R392" s="23">
-        <f t="shared" si="6"/>
+        <f>SUM(O392:Q392)</f>
         <v>9</v>
       </c>
       <c r="S392" s="22">
@@ -39022,7 +39026,7 @@
         <v>31</v>
       </c>
       <c r="R394" s="23">
-        <f t="shared" ref="R394:R457" si="7">SUM(O394:Q394)</f>
+        <f>SUM(O394:Q394)</f>
         <v>31</v>
       </c>
       <c r="S394" s="22">
@@ -39085,7 +39089,7 @@
         <v>0</v>
       </c>
       <c r="R395" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O395:Q395)</f>
         <v>19</v>
       </c>
       <c r="S395" s="24">
@@ -39148,7 +39152,7 @@
         <v>0</v>
       </c>
       <c r="R396" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O396:Q396)</f>
         <v>45</v>
       </c>
       <c r="S396" s="22">
@@ -39211,7 +39215,7 @@
         <v>0</v>
       </c>
       <c r="R397" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O397:Q397)</f>
         <v>0</v>
       </c>
       <c r="S397" s="24">
@@ -39274,7 +39278,7 @@
         <v>17</v>
       </c>
       <c r="R398" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O398:Q398)</f>
         <v>85</v>
       </c>
       <c r="S398" s="22">
@@ -39337,7 +39341,7 @@
         <v>0</v>
       </c>
       <c r="R399" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O399:Q399)</f>
         <v>7</v>
       </c>
       <c r="S399" s="24">
@@ -39394,7 +39398,7 @@
       <c r="P400" s="23"/>
       <c r="Q400" s="23"/>
       <c r="R400" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O400:Q400)</f>
         <v>30</v>
       </c>
       <c r="S400" s="22">
@@ -39455,7 +39459,7 @@
         <v>0</v>
       </c>
       <c r="R401" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O401:Q401)</f>
         <v>62</v>
       </c>
       <c r="S401" s="24">
@@ -39518,7 +39522,7 @@
         <v>68</v>
       </c>
       <c r="R402" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O402:Q402)</f>
         <v>68</v>
       </c>
       <c r="S402" s="22">
@@ -39577,7 +39581,7 @@
         <v>0</v>
       </c>
       <c r="R403" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O403:Q403)</f>
         <v>2</v>
       </c>
       <c r="S403" s="24">
@@ -39640,7 +39644,7 @@
         <v>0</v>
       </c>
       <c r="R404" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O404:Q404)</f>
         <v>36</v>
       </c>
       <c r="S404" s="22">
@@ -39703,7 +39707,7 @@
         <v>0</v>
       </c>
       <c r="R405" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O405:Q405)</f>
         <v>14</v>
       </c>
       <c r="S405" s="24">
@@ -39764,7 +39768,7 @@
         <v>44</v>
       </c>
       <c r="R406" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O406:Q406)</f>
         <v>44</v>
       </c>
       <c r="S406" s="22">
@@ -39827,7 +39831,7 @@
         <v>0</v>
       </c>
       <c r="R407" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O407:Q407)</f>
         <v>26</v>
       </c>
       <c r="S407" s="24">
@@ -39890,7 +39894,7 @@
         <v>0</v>
       </c>
       <c r="R408" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O408:Q408)</f>
         <v>23</v>
       </c>
       <c r="S408" s="22">
@@ -39945,7 +39949,7 @@
         <v>20</v>
       </c>
       <c r="R409" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O409:Q409)</f>
         <v>20</v>
       </c>
       <c r="S409" s="24">
@@ -40000,7 +40004,7 @@
         <v>0</v>
       </c>
       <c r="R410" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O410:Q410)</f>
         <v>0</v>
       </c>
       <c r="S410" s="22"/>
@@ -40059,7 +40063,7 @@
         <v>0</v>
       </c>
       <c r="R411" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O411:Q411)</f>
         <v>16</v>
       </c>
       <c r="S411" s="24">
@@ -40122,7 +40126,7 @@
         <v>44</v>
       </c>
       <c r="R412" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O412:Q412)</f>
         <v>44</v>
       </c>
       <c r="S412" s="22">
@@ -40185,7 +40189,7 @@
         <v>0</v>
       </c>
       <c r="R413" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O413:Q413)</f>
         <v>105</v>
       </c>
       <c r="S413" s="24">
@@ -40248,7 +40252,7 @@
         <v>0</v>
       </c>
       <c r="R414" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O414:Q414)</f>
         <v>50</v>
       </c>
       <c r="S414" s="22">
@@ -40311,7 +40315,7 @@
         <v>0</v>
       </c>
       <c r="R415" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O415:Q415)</f>
         <v>25</v>
       </c>
       <c r="S415" s="24">
@@ -40374,7 +40378,7 @@
         <v>0</v>
       </c>
       <c r="R416" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O416:Q416)</f>
         <v>9</v>
       </c>
       <c r="S416" s="22">
@@ -40437,7 +40441,7 @@
         <v>24</v>
       </c>
       <c r="R417" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O417:Q417)</f>
         <v>25</v>
       </c>
       <c r="S417" s="24">
@@ -40500,7 +40504,7 @@
         <v>0</v>
       </c>
       <c r="R418" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O418:Q418)</f>
         <v>13</v>
       </c>
       <c r="S418" s="22">
@@ -40564,7 +40568,7 @@
         <v>0</v>
       </c>
       <c r="R419" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O419:Q419)</f>
         <v>49</v>
       </c>
       <c r="S419" s="24">
@@ -40627,7 +40631,7 @@
         <v>128</v>
       </c>
       <c r="R420" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O420:Q420)</f>
         <v>128</v>
       </c>
       <c r="S420" s="22">
@@ -40690,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="R421" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O421:Q421)</f>
         <v>21</v>
       </c>
       <c r="S421" s="24">
@@ -40753,7 +40757,7 @@
         <v>0</v>
       </c>
       <c r="R422" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O422:Q422)</f>
         <v>8</v>
       </c>
       <c r="S422" s="22">
@@ -40816,7 +40820,7 @@
         <v>0</v>
       </c>
       <c r="R423" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O423:Q423)</f>
         <v>93</v>
       </c>
       <c r="S423" s="24">
@@ -40879,7 +40883,7 @@
         <v>0</v>
       </c>
       <c r="R424" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O424:Q424)</f>
         <v>6</v>
       </c>
       <c r="S424" s="22">
@@ -40940,7 +40944,7 @@
         <v>0</v>
       </c>
       <c r="R425" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O425:Q425)</f>
         <v>80</v>
       </c>
       <c r="S425" s="24">
@@ -41004,7 +41008,7 @@
         <v>0</v>
       </c>
       <c r="R426" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O426:Q426)</f>
         <v>8</v>
       </c>
       <c r="S426" s="22">
@@ -41067,7 +41071,7 @@
         <v>0</v>
       </c>
       <c r="R427" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O427:Q427)</f>
         <v>10</v>
       </c>
       <c r="S427" s="24">
@@ -41128,7 +41132,7 @@
         <v>80</v>
       </c>
       <c r="R428" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O428:Q428)</f>
         <v>80</v>
       </c>
       <c r="S428" s="22">
@@ -41189,7 +41193,7 @@
         <v>80</v>
       </c>
       <c r="R429" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O429:Q429)</f>
         <v>80</v>
       </c>
       <c r="S429" s="24">
@@ -41250,7 +41254,7 @@
         <v>80</v>
       </c>
       <c r="R430" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O430:Q430)</f>
         <v>80</v>
       </c>
       <c r="S430" s="22">
@@ -41311,7 +41315,7 @@
         <v>80</v>
       </c>
       <c r="R431" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O431:Q431)</f>
         <v>80</v>
       </c>
       <c r="S431" s="24">
@@ -41372,7 +41376,7 @@
         <v>80</v>
       </c>
       <c r="R432" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O432:Q432)</f>
         <v>80</v>
       </c>
       <c r="S432" s="22">
@@ -41436,7 +41440,7 @@
         <v>0</v>
       </c>
       <c r="R433" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O433:Q433)</f>
         <v>33</v>
       </c>
       <c r="S433" s="24">
@@ -41491,7 +41495,7 @@
         <v>0</v>
       </c>
       <c r="R434" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O434:Q434)</f>
         <v>0</v>
       </c>
       <c r="S434" s="22"/>
@@ -41550,7 +41554,7 @@
         <v>62</v>
       </c>
       <c r="R435" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O435:Q435)</f>
         <v>62</v>
       </c>
       <c r="S435" s="24">
@@ -41613,7 +41617,7 @@
         <v>0</v>
       </c>
       <c r="R436" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O436:Q436)</f>
         <v>42</v>
       </c>
       <c r="S436" s="22">
@@ -41676,7 +41680,7 @@
         <v>0</v>
       </c>
       <c r="R437" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O437:Q437)</f>
         <v>6</v>
       </c>
       <c r="S437" s="24">
@@ -41739,7 +41743,7 @@
         <v>0</v>
       </c>
       <c r="R438" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O438:Q438)</f>
         <v>49</v>
       </c>
       <c r="S438" s="22">
@@ -41802,7 +41806,7 @@
         <v>0</v>
       </c>
       <c r="R439" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O439:Q439)</f>
         <v>20</v>
       </c>
       <c r="S439" s="24">
@@ -41865,7 +41869,7 @@
         <v>28</v>
       </c>
       <c r="R440" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O440:Q440)</f>
         <v>28</v>
       </c>
       <c r="S440" s="22">
@@ -41928,7 +41932,7 @@
         <v>0</v>
       </c>
       <c r="R441" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O441:Q441)</f>
         <v>17</v>
       </c>
       <c r="S441" s="24">
@@ -41992,7 +41996,7 @@
         <v>0</v>
       </c>
       <c r="R442" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O442:Q442)</f>
         <v>17</v>
       </c>
       <c r="S442" s="22">
@@ -42056,7 +42060,7 @@
         <v>0</v>
       </c>
       <c r="R443" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O443:Q443)</f>
         <v>24</v>
       </c>
       <c r="S443" s="24">
@@ -42119,7 +42123,7 @@
         <v>0</v>
       </c>
       <c r="R444" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O444:Q444)</f>
         <v>16</v>
       </c>
       <c r="S444" s="22">
@@ -42182,7 +42186,7 @@
         <v>7</v>
       </c>
       <c r="R445" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O445:Q445)</f>
         <v>155</v>
       </c>
       <c r="S445" s="24">
@@ -42246,7 +42250,7 @@
         <v>0</v>
       </c>
       <c r="R446" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O446:Q446)</f>
         <v>8</v>
       </c>
       <c r="S446" s="22">
@@ -42309,7 +42313,7 @@
         <v>0</v>
       </c>
       <c r="R447" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O447:Q447)</f>
         <v>10</v>
       </c>
       <c r="S447" s="24">
@@ -42372,7 +42376,7 @@
         <v>0</v>
       </c>
       <c r="R448" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O448:Q448)</f>
         <v>15</v>
       </c>
       <c r="S448" s="22">
@@ -42435,7 +42439,7 @@
         <v>0</v>
       </c>
       <c r="R449" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O449:Q449)</f>
         <v>51</v>
       </c>
       <c r="S449" s="24">
@@ -42498,7 +42502,7 @@
         <v>0</v>
       </c>
       <c r="R450" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O450:Q450)</f>
         <v>52</v>
       </c>
       <c r="S450" s="22">
@@ -42562,7 +42566,7 @@
         <v>0</v>
       </c>
       <c r="R451" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O451:Q451)</f>
         <v>13</v>
       </c>
       <c r="S451" s="24">
@@ -42625,7 +42629,7 @@
         <v>0</v>
       </c>
       <c r="R452" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O452:Q452)</f>
         <v>90</v>
       </c>
       <c r="S452" s="22">
@@ -42688,7 +42692,7 @@
         <v>0</v>
       </c>
       <c r="R453" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O453:Q453)</f>
         <v>11</v>
       </c>
       <c r="S453" s="24">
@@ -42751,7 +42755,7 @@
         <v>0</v>
       </c>
       <c r="R454" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O454:Q454)</f>
         <v>50</v>
       </c>
       <c r="S454" s="22">
@@ -42815,7 +42819,7 @@
         <v>0</v>
       </c>
       <c r="R455" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O455:Q455)</f>
         <v>8</v>
       </c>
       <c r="S455" s="24">
@@ -42868,7 +42872,7 @@
         <v>0</v>
       </c>
       <c r="R456" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O456:Q456)</f>
         <v>0</v>
       </c>
       <c r="S456" s="22"/>
@@ -42927,7 +42931,7 @@
         <v>0</v>
       </c>
       <c r="R457" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O457:Q457)</f>
         <v>23</v>
       </c>
       <c r="S457" s="24">
@@ -42990,7 +42994,7 @@
         <v>0</v>
       </c>
       <c r="R458" s="23">
-        <f t="shared" ref="R458:R521" si="8">SUM(O458:Q458)</f>
+        <f>SUM(O458:Q458)</f>
         <v>23</v>
       </c>
       <c r="S458" s="22">
@@ -43053,7 +43057,7 @@
         <v>0</v>
       </c>
       <c r="R459" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O459:Q459)</f>
         <v>89</v>
       </c>
       <c r="S459" s="24">
@@ -43116,7 +43120,7 @@
         <v>0</v>
       </c>
       <c r="R460" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O460:Q460)</f>
         <v>22</v>
       </c>
       <c r="S460" s="22">
@@ -43180,7 +43184,7 @@
         <v>0</v>
       </c>
       <c r="R461" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O461:Q461)</f>
         <v>11</v>
       </c>
       <c r="S461" s="24">
@@ -43243,7 +43247,7 @@
         <v>0</v>
       </c>
       <c r="R462" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O462:Q462)</f>
         <v>21</v>
       </c>
       <c r="S462" s="22">
@@ -43306,7 +43310,7 @@
         <v>0</v>
       </c>
       <c r="R463" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O463:Q463)</f>
         <v>51</v>
       </c>
       <c r="S463" s="24">
@@ -43370,7 +43374,7 @@
         <v>0</v>
       </c>
       <c r="R464" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O464:Q464)</f>
         <v>7</v>
       </c>
       <c r="S464" s="22">
@@ -43433,7 +43437,7 @@
         <v>0</v>
       </c>
       <c r="R465" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O465:Q465)</f>
         <v>22</v>
       </c>
       <c r="S465" s="24">
@@ -43496,7 +43500,7 @@
         <v>156</v>
       </c>
       <c r="R466" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O466:Q466)</f>
         <v>213</v>
       </c>
       <c r="S466" s="22">
@@ -43559,7 +43563,7 @@
         <v>70</v>
       </c>
       <c r="R467" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O467:Q467)</f>
         <v>92</v>
       </c>
       <c r="S467" s="24">
@@ -43622,7 +43626,7 @@
         <v>0</v>
       </c>
       <c r="R468" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O468:Q468)</f>
         <v>18</v>
       </c>
       <c r="S468" s="22">
@@ -43686,7 +43690,7 @@
         <v>0</v>
       </c>
       <c r="R469" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O469:Q469)</f>
         <v>8</v>
       </c>
       <c r="S469" s="24">
@@ -43750,7 +43754,7 @@
         <v>0</v>
       </c>
       <c r="R470" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O470:Q470)</f>
         <v>8</v>
       </c>
       <c r="S470" s="22">
@@ -43814,7 +43818,7 @@
         <v>0</v>
       </c>
       <c r="R471" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O471:Q471)</f>
         <v>384</v>
       </c>
       <c r="S471" s="24">
@@ -43877,7 +43881,7 @@
         <v>0</v>
       </c>
       <c r="R472" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O472:Q472)</f>
         <v>24</v>
       </c>
       <c r="S472" s="22">
@@ -43940,7 +43944,7 @@
         <v>0</v>
       </c>
       <c r="R473" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O473:Q473)</f>
         <v>35</v>
       </c>
       <c r="S473" s="24">
@@ -44003,7 +44007,7 @@
         <v>0</v>
       </c>
       <c r="R474" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O474:Q474)</f>
         <v>53</v>
       </c>
       <c r="S474" s="22">
@@ -44066,7 +44070,7 @@
         <v>0</v>
       </c>
       <c r="R475" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O475:Q475)</f>
         <v>12</v>
       </c>
       <c r="S475" s="24">
@@ -44129,7 +44133,7 @@
         <v>0</v>
       </c>
       <c r="R476" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O476:Q476)</f>
         <v>60</v>
       </c>
       <c r="S476" s="22">
@@ -44192,7 +44196,7 @@
         <v>0</v>
       </c>
       <c r="R477" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O477:Q477)</f>
         <v>14</v>
       </c>
       <c r="S477" s="24">
@@ -44255,7 +44259,7 @@
         <v>0</v>
       </c>
       <c r="R478" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O478:Q478)</f>
         <v>20</v>
       </c>
       <c r="S478" s="22">
@@ -44318,7 +44322,7 @@
         <v>56</v>
       </c>
       <c r="R479" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O479:Q479)</f>
         <v>56</v>
       </c>
       <c r="S479" s="24">
@@ -44381,7 +44385,7 @@
         <v>0</v>
       </c>
       <c r="R480" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O480:Q480)</f>
         <v>38</v>
       </c>
       <c r="S480" s="22">
@@ -44444,7 +44448,7 @@
         <v>0</v>
       </c>
       <c r="R481" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O481:Q481)</f>
         <v>13</v>
       </c>
       <c r="S481" s="24">
@@ -44507,7 +44511,7 @@
         <v>0</v>
       </c>
       <c r="R482" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O482:Q482)</f>
         <v>24</v>
       </c>
       <c r="S482" s="22">
@@ -44570,7 +44574,7 @@
         <v>0</v>
       </c>
       <c r="R483" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O483:Q483)</f>
         <v>19</v>
       </c>
       <c r="S483" s="24">
@@ -44633,7 +44637,7 @@
         <v>0</v>
       </c>
       <c r="R484" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O484:Q484)</f>
         <v>10</v>
       </c>
       <c r="S484" s="22">
@@ -44697,7 +44701,7 @@
         <v>0</v>
       </c>
       <c r="R485" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O485:Q485)</f>
         <v>5</v>
       </c>
       <c r="S485" s="24">
@@ -44760,7 +44764,7 @@
         <v>0</v>
       </c>
       <c r="R486" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O486:Q486)</f>
         <v>21</v>
       </c>
       <c r="S486" s="22">
@@ -44823,7 +44827,7 @@
         <v>0</v>
       </c>
       <c r="R487" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O487:Q487)</f>
         <v>19</v>
       </c>
       <c r="S487" s="24">
@@ -44887,7 +44891,7 @@
         <v>0</v>
       </c>
       <c r="R488" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O488:Q488)</f>
         <v>7</v>
       </c>
       <c r="S488" s="22">
@@ -44950,7 +44954,7 @@
         <v>0</v>
       </c>
       <c r="R489" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O489:Q489)</f>
         <v>19</v>
       </c>
       <c r="S489" s="64">
@@ -45014,7 +45018,7 @@
         <v>61</v>
       </c>
       <c r="R490" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O490:Q490)</f>
         <v>61</v>
       </c>
       <c r="S490" s="70">
@@ -45077,7 +45081,7 @@
         <v>0</v>
       </c>
       <c r="R491" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O491:Q491)</f>
         <v>32</v>
       </c>
       <c r="S491" s="64">
@@ -45140,7 +45144,7 @@
         <v>0</v>
       </c>
       <c r="R492" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O492:Q492)</f>
         <v>43</v>
       </c>
       <c r="S492" s="70">
@@ -45203,7 +45207,7 @@
         <v>0</v>
       </c>
       <c r="R493" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O493:Q493)</f>
         <v>8</v>
       </c>
       <c r="S493" s="64">
@@ -45264,7 +45268,7 @@
         <v>0</v>
       </c>
       <c r="R494" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O494:Q494)</f>
         <v>80</v>
       </c>
       <c r="S494" s="70">
@@ -45319,7 +45323,7 @@
         <v>0</v>
       </c>
       <c r="R495" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O495:Q495)</f>
         <v>0</v>
       </c>
       <c r="S495" s="24"/>
@@ -45376,7 +45380,7 @@
         <v>0</v>
       </c>
       <c r="R496" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O496:Q496)</f>
         <v>170</v>
       </c>
       <c r="S496" s="70">
@@ -45439,7 +45443,7 @@
         <v>0</v>
       </c>
       <c r="R497" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O497:Q497)</f>
         <v>31</v>
       </c>
       <c r="S497" s="64">
@@ -45502,7 +45506,7 @@
         <v>0</v>
       </c>
       <c r="R498" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O498:Q498)</f>
         <v>11</v>
       </c>
       <c r="S498" s="70">
@@ -45565,7 +45569,7 @@
         <v>45</v>
       </c>
       <c r="R499" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O499:Q499)</f>
         <v>45</v>
       </c>
       <c r="S499" s="64">
@@ -45626,7 +45630,7 @@
         <v>0</v>
       </c>
       <c r="R500" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O500:Q500)</f>
         <v>40</v>
       </c>
       <c r="S500" s="70">
@@ -45690,7 +45694,7 @@
         <v>0</v>
       </c>
       <c r="R501" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O501:Q501)</f>
         <v>0</v>
       </c>
       <c r="S501" s="64">
@@ -45753,7 +45757,7 @@
         <v>0</v>
       </c>
       <c r="R502" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O502:Q502)</f>
         <v>34</v>
       </c>
       <c r="S502" s="70">
@@ -45816,7 +45820,7 @@
         <v>0</v>
       </c>
       <c r="R503" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O503:Q503)</f>
         <v>21</v>
       </c>
       <c r="S503" s="64">
@@ -45879,7 +45883,7 @@
         <v>0</v>
       </c>
       <c r="R504" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O504:Q504)</f>
         <v>16</v>
       </c>
       <c r="S504" s="70">
@@ -45940,7 +45944,7 @@
         <v>0</v>
       </c>
       <c r="R505" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O505:Q505)</f>
         <v>20</v>
       </c>
       <c r="S505" s="24">
@@ -46004,7 +46008,7 @@
         <v>0</v>
       </c>
       <c r="R506" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O506:Q506)</f>
         <v>8</v>
       </c>
       <c r="S506" s="22">
@@ -46067,7 +46071,7 @@
         <v>0</v>
       </c>
       <c r="R507" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O507:Q507)</f>
         <v>0</v>
       </c>
       <c r="S507" s="24">
@@ -46130,7 +46134,7 @@
         <v>0</v>
       </c>
       <c r="R508" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O508:Q508)</f>
         <v>13</v>
       </c>
       <c r="S508" s="22">
@@ -46191,7 +46195,7 @@
         <v>0</v>
       </c>
       <c r="R509" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O509:Q509)</f>
         <v>170</v>
       </c>
       <c r="S509" s="24">
@@ -46255,7 +46259,7 @@
         <v>66</v>
       </c>
       <c r="R510" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O510:Q510)</f>
         <v>66</v>
       </c>
       <c r="S510" s="22">
@@ -46316,7 +46320,7 @@
         <v>0</v>
       </c>
       <c r="R511" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O511:Q511)</f>
         <v>140</v>
       </c>
       <c r="S511" s="24">
@@ -46379,7 +46383,7 @@
         <v>0</v>
       </c>
       <c r="R512" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O512:Q512)</f>
         <v>45</v>
       </c>
       <c r="S512" s="22">
@@ -46442,7 +46446,7 @@
         <v>0</v>
       </c>
       <c r="R513" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O513:Q513)</f>
         <v>19</v>
       </c>
       <c r="S513" s="24">
@@ -46505,7 +46509,7 @@
         <v>0</v>
       </c>
       <c r="R514" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O514:Q514)</f>
         <v>15</v>
       </c>
       <c r="S514" s="22">
@@ -46568,7 +46572,7 @@
         <v>41</v>
       </c>
       <c r="R515" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O515:Q515)</f>
         <v>41</v>
       </c>
       <c r="S515" s="24">
@@ -46631,7 +46635,7 @@
         <v>0</v>
       </c>
       <c r="R516" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O516:Q516)</f>
         <v>96</v>
       </c>
       <c r="S516" s="22">
@@ -46695,7 +46699,7 @@
         <v>0</v>
       </c>
       <c r="R517" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O517:Q517)</f>
         <v>6</v>
       </c>
       <c r="S517" s="24">
@@ -46758,7 +46762,7 @@
         <v>0</v>
       </c>
       <c r="R518" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O518:Q518)</f>
         <v>47</v>
       </c>
       <c r="S518" s="22">
@@ -46821,7 +46825,7 @@
         <v>0</v>
       </c>
       <c r="R519" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O519:Q519)</f>
         <v>37</v>
       </c>
       <c r="S519" s="24">
@@ -46884,7 +46888,7 @@
         <v>0</v>
       </c>
       <c r="R520" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O520:Q520)</f>
         <v>20</v>
       </c>
       <c r="S520" s="22">
@@ -46947,7 +46951,7 @@
         <v>0</v>
       </c>
       <c r="R521" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O521:Q521)</f>
         <v>19</v>
       </c>
       <c r="S521" s="24">
@@ -47010,7 +47014,7 @@
         <v>0</v>
       </c>
       <c r="R522" s="23">
-        <f t="shared" ref="R522:R585" si="9">SUM(O522:Q522)</f>
+        <f>SUM(O522:Q522)</f>
         <v>0</v>
       </c>
       <c r="S522" s="22">
@@ -47073,7 +47077,7 @@
         <v>0</v>
       </c>
       <c r="R523" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O523:Q523)</f>
         <v>0</v>
       </c>
       <c r="S523" s="24">
@@ -47137,7 +47141,7 @@
         <v>0</v>
       </c>
       <c r="R524" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O524:Q524)</f>
         <v>6</v>
       </c>
       <c r="S524" s="22"/>
@@ -47196,7 +47200,7 @@
         <v>0</v>
       </c>
       <c r="R525" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O525:Q525)</f>
         <v>46</v>
       </c>
       <c r="S525" s="24">
@@ -47259,7 +47263,7 @@
         <v>0</v>
       </c>
       <c r="R526" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O526:Q526)</f>
         <v>20</v>
       </c>
       <c r="S526" s="22">
@@ -47314,7 +47318,7 @@
         <v>0</v>
       </c>
       <c r="R527" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O527:Q527)</f>
         <v>0</v>
       </c>
       <c r="S527" s="24"/>
@@ -47375,7 +47379,7 @@
         <v>0</v>
       </c>
       <c r="R528" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O528:Q528)</f>
         <v>20</v>
       </c>
       <c r="S528" s="22">
@@ -47438,7 +47442,7 @@
         <v>1</v>
       </c>
       <c r="R529" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O529:Q529)</f>
         <v>28</v>
       </c>
       <c r="S529" s="24">
@@ -47499,7 +47503,7 @@
         <v>23</v>
       </c>
       <c r="R530" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O530:Q530)</f>
         <v>138</v>
       </c>
       <c r="S530" s="22">
@@ -47562,7 +47566,7 @@
         <v>0</v>
       </c>
       <c r="R531" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O531:Q531)</f>
         <v>19</v>
       </c>
       <c r="S531" s="24">
@@ -47625,7 +47629,7 @@
         <v>0</v>
       </c>
       <c r="R532" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O532:Q532)</f>
         <v>118</v>
       </c>
       <c r="S532" s="22">
@@ -47689,7 +47693,7 @@
         <v>0</v>
       </c>
       <c r="R533" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O533:Q533)</f>
         <v>4</v>
       </c>
       <c r="S533" s="24">
@@ -47752,7 +47756,7 @@
         <v>49</v>
       </c>
       <c r="R534" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O534:Q534)</f>
         <v>49</v>
       </c>
       <c r="S534" s="22">
@@ -47816,7 +47820,7 @@
         <v>94</v>
       </c>
       <c r="R535" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O535:Q535)</f>
         <v>94</v>
       </c>
       <c r="S535" s="24">
@@ -47871,7 +47875,7 @@
         <v>0</v>
       </c>
       <c r="R536" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O536:Q536)</f>
         <v>0</v>
       </c>
       <c r="S536" s="22"/>
@@ -47930,7 +47934,7 @@
         <v>0</v>
       </c>
       <c r="R537" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O537:Q537)</f>
         <v>21</v>
       </c>
       <c r="S537" s="24">
@@ -47987,7 +47991,7 @@
         <v>0</v>
       </c>
       <c r="R538" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O538:Q538)</f>
         <v>49</v>
       </c>
       <c r="S538" s="22"/>
@@ -48046,7 +48050,7 @@
         <v>0</v>
       </c>
       <c r="R539" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O539:Q539)</f>
         <v>26</v>
       </c>
       <c r="S539" s="24">
@@ -48109,7 +48113,7 @@
         <v>0</v>
       </c>
       <c r="R540" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O540:Q540)</f>
         <v>8</v>
       </c>
       <c r="S540" s="22">
@@ -48172,7 +48176,7 @@
         <v>0</v>
       </c>
       <c r="R541" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O541:Q541)</f>
         <v>14</v>
       </c>
       <c r="S541" s="24">
@@ -48235,7 +48239,7 @@
         <v>30</v>
       </c>
       <c r="R542" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O542:Q542)</f>
         <v>30</v>
       </c>
       <c r="S542" s="22">
@@ -48298,7 +48302,7 @@
         <v>0</v>
       </c>
       <c r="R543" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O543:Q543)</f>
         <v>11</v>
       </c>
       <c r="S543" s="24">
@@ -48362,7 +48366,7 @@
         <v>0</v>
       </c>
       <c r="R544" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O544:Q544)</f>
         <v>43</v>
       </c>
       <c r="S544" s="22">
@@ -48425,7 +48429,7 @@
         <v>0</v>
       </c>
       <c r="R545" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O545:Q545)</f>
         <v>54</v>
       </c>
       <c r="S545" s="24">
@@ -48488,7 +48492,7 @@
         <v>0</v>
       </c>
       <c r="R546" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O546:Q546)</f>
         <v>3</v>
       </c>
       <c r="S546" s="22">
@@ -48551,7 +48555,7 @@
         <v>0</v>
       </c>
       <c r="R547" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O547:Q547)</f>
         <v>21</v>
       </c>
       <c r="S547" s="24">
@@ -48614,7 +48618,7 @@
         <v>44</v>
       </c>
       <c r="R548" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O548:Q548)</f>
         <v>44</v>
       </c>
       <c r="S548" s="22">
@@ -48677,7 +48681,7 @@
         <v>0</v>
       </c>
       <c r="R549" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O549:Q549)</f>
         <v>49</v>
       </c>
       <c r="S549" s="24">
@@ -48740,7 +48744,7 @@
         <v>0</v>
       </c>
       <c r="R550" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O550:Q550)</f>
         <v>16</v>
       </c>
       <c r="S550" s="22">
@@ -48803,7 +48807,7 @@
         <v>0</v>
       </c>
       <c r="R551" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O551:Q551)</f>
         <v>27</v>
       </c>
       <c r="S551" s="24">
@@ -48866,7 +48870,7 @@
         <v>60</v>
       </c>
       <c r="R552" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O552:Q552)</f>
         <v>114</v>
       </c>
       <c r="S552" s="22">
@@ -48929,7 +48933,7 @@
         <v>1</v>
       </c>
       <c r="R553" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O553:Q553)</f>
         <v>24</v>
       </c>
       <c r="S553" s="24">
@@ -48992,7 +48996,7 @@
         <v>0</v>
       </c>
       <c r="R554" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O554:Q554)</f>
         <v>21</v>
       </c>
       <c r="S554" s="22">
@@ -49056,7 +49060,7 @@
         <v>38</v>
       </c>
       <c r="R555" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O555:Q555)</f>
         <v>38</v>
       </c>
       <c r="S555" s="24">
@@ -49117,7 +49121,7 @@
         <v>97</v>
       </c>
       <c r="R556" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O556:Q556)</f>
         <v>97</v>
       </c>
       <c r="S556" s="22">
@@ -49181,7 +49185,7 @@
         <v>38</v>
       </c>
       <c r="R557" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O557:Q557)</f>
         <v>38</v>
       </c>
       <c r="S557" s="24">
@@ -49244,7 +49248,7 @@
         <v>0</v>
       </c>
       <c r="R558" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O558:Q558)</f>
         <v>8</v>
       </c>
       <c r="S558" s="22">
@@ -49307,7 +49311,7 @@
         <v>0</v>
       </c>
       <c r="R559" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O559:Q559)</f>
         <v>23</v>
       </c>
       <c r="S559" s="24">
@@ -49370,7 +49374,7 @@
         <v>0</v>
       </c>
       <c r="R560" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O560:Q560)</f>
         <v>20</v>
       </c>
       <c r="S560" s="22">
@@ -49433,7 +49437,7 @@
         <v>0</v>
       </c>
       <c r="R561" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O561:Q561)</f>
         <v>13</v>
       </c>
       <c r="S561" s="24">
@@ -49496,7 +49500,7 @@
         <v>79</v>
       </c>
       <c r="R562" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O562:Q562)</f>
         <v>250</v>
       </c>
       <c r="S562" s="22">
@@ -49559,7 +49563,7 @@
         <v>0</v>
       </c>
       <c r="R563" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O563:Q563)</f>
         <v>32</v>
       </c>
       <c r="S563" s="24">
@@ -49622,7 +49626,7 @@
         <v>0</v>
       </c>
       <c r="R564" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O564:Q564)</f>
         <v>41</v>
       </c>
       <c r="S564" s="22">
@@ -49685,7 +49689,7 @@
         <v>0</v>
       </c>
       <c r="R565" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O565:Q565)</f>
         <v>75</v>
       </c>
       <c r="S565" s="24">
@@ -49746,7 +49750,7 @@
         <v>0</v>
       </c>
       <c r="R566" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O566:Q566)</f>
         <v>100</v>
       </c>
       <c r="S566" s="22">
@@ -49809,7 +49813,7 @@
         <v>0</v>
       </c>
       <c r="R567" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O567:Q567)</f>
         <v>20</v>
       </c>
       <c r="S567" s="24">
@@ -49872,7 +49876,7 @@
         <v>0</v>
       </c>
       <c r="R568" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O568:Q568)</f>
         <v>40</v>
       </c>
       <c r="S568" s="22">
@@ -49935,7 +49939,7 @@
         <v>0</v>
       </c>
       <c r="R569" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O569:Q569)</f>
         <v>48</v>
       </c>
       <c r="S569" s="24">
@@ -49998,7 +50002,7 @@
         <v>0</v>
       </c>
       <c r="R570" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O570:Q570)</f>
         <v>16</v>
       </c>
       <c r="S570" s="22">
@@ -50059,7 +50063,7 @@
         <v>0</v>
       </c>
       <c r="R571" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O571:Q571)</f>
         <v>170</v>
       </c>
       <c r="S571" s="24">
@@ -50120,7 +50124,7 @@
         <v>0</v>
       </c>
       <c r="R572" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O572:Q572)</f>
         <v>80</v>
       </c>
       <c r="S572" s="22">
@@ -50181,7 +50185,7 @@
         <v>18</v>
       </c>
       <c r="R573" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O573:Q573)</f>
         <v>176</v>
       </c>
       <c r="S573" s="24">
@@ -50240,7 +50244,7 @@
         <v>0</v>
       </c>
       <c r="R574" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O574:Q574)</f>
         <v>0</v>
       </c>
       <c r="S574" s="22"/>
@@ -50301,7 +50305,7 @@
         <v>0</v>
       </c>
       <c r="R575" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O575:Q575)</f>
         <v>44</v>
       </c>
       <c r="S575" s="24">
@@ -50365,7 +50369,7 @@
         <v>33</v>
       </c>
       <c r="R576" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O576:Q576)</f>
         <v>41</v>
       </c>
       <c r="S576" s="22">
@@ -50426,7 +50430,7 @@
         <v>0</v>
       </c>
       <c r="R577" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O577:Q577)</f>
         <v>170</v>
       </c>
       <c r="S577" s="24">
@@ -50485,7 +50489,7 @@
         <v>40</v>
       </c>
       <c r="R578" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O578:Q578)</f>
         <v>40</v>
       </c>
       <c r="S578" s="22">
@@ -50544,7 +50548,7 @@
         <v>40</v>
       </c>
       <c r="R579" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O579:Q579)</f>
         <v>40</v>
       </c>
       <c r="S579" s="24">
@@ -50607,7 +50611,7 @@
         <v>0</v>
       </c>
       <c r="R580" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O580:Q580)</f>
         <v>18</v>
       </c>
       <c r="S580" s="22">
@@ -50670,7 +50674,7 @@
         <v>0</v>
       </c>
       <c r="R581" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O581:Q581)</f>
         <v>18</v>
       </c>
       <c r="S581" s="24">
@@ -50733,7 +50737,7 @@
         <v>0</v>
       </c>
       <c r="R582" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O582:Q582)</f>
         <v>38</v>
       </c>
       <c r="S582" s="22">
@@ -50796,7 +50800,7 @@
         <v>0</v>
       </c>
       <c r="R583" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O583:Q583)</f>
         <v>15</v>
       </c>
       <c r="S583" s="24">
@@ -50859,7 +50863,7 @@
         <v>31</v>
       </c>
       <c r="R584" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O584:Q584)</f>
         <v>31</v>
       </c>
       <c r="S584" s="22">
@@ -50922,7 +50926,7 @@
         <v>4</v>
       </c>
       <c r="R585" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O585:Q585)</f>
         <v>29</v>
       </c>
       <c r="S585" s="24">
@@ -50985,7 +50989,7 @@
         <v>30</v>
       </c>
       <c r="R586" s="23">
-        <f t="shared" ref="R586:R640" si="10">SUM(O586:Q586)</f>
+        <f>SUM(O586:Q586)</f>
         <v>30</v>
       </c>
       <c r="S586" s="22">
@@ -51048,7 +51052,7 @@
         <v>0</v>
       </c>
       <c r="R587" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O587:Q587)</f>
         <v>14</v>
       </c>
       <c r="S587" s="24">
@@ -51111,7 +51115,7 @@
         <v>27</v>
       </c>
       <c r="R588" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O588:Q588)</f>
         <v>27</v>
       </c>
       <c r="S588" s="22">
@@ -51174,7 +51178,7 @@
         <v>0</v>
       </c>
       <c r="R589" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O589:Q589)</f>
         <v>14</v>
       </c>
       <c r="S589" s="24">
@@ -51237,7 +51241,7 @@
         <v>0</v>
       </c>
       <c r="R590" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O590:Q590)</f>
         <v>33</v>
       </c>
       <c r="S590" s="22">
@@ -51300,7 +51304,7 @@
         <v>42</v>
       </c>
       <c r="R591" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O591:Q591)</f>
         <v>42</v>
       </c>
       <c r="S591" s="24">
@@ -51363,7 +51367,7 @@
         <v>0</v>
       </c>
       <c r="R592" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O592:Q592)</f>
         <v>22</v>
       </c>
       <c r="S592" s="22">
@@ -51426,7 +51430,7 @@
         <v>0</v>
       </c>
       <c r="R593" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O593:Q593)</f>
         <v>9</v>
       </c>
       <c r="S593" s="24">
@@ -51489,7 +51493,7 @@
         <v>0</v>
       </c>
       <c r="R594" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O594:Q594)</f>
         <v>20</v>
       </c>
       <c r="S594" s="22">
@@ -51550,7 +51554,7 @@
         <v>25</v>
       </c>
       <c r="R595" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O595:Q595)</f>
         <v>25</v>
       </c>
       <c r="S595" s="24">
@@ -51613,7 +51617,7 @@
         <v>24</v>
       </c>
       <c r="R596" s="73">
-        <f t="shared" si="10"/>
+        <f>SUM(O596:Q596)</f>
         <v>24</v>
       </c>
       <c r="S596" s="70">
@@ -51676,7 +51680,7 @@
         <v>0</v>
       </c>
       <c r="R597" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O597:Q597)</f>
         <v>46</v>
       </c>
       <c r="S597" s="24">
@@ -51739,7 +51743,7 @@
         <v>0</v>
       </c>
       <c r="R598" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O598:Q598)</f>
         <v>37</v>
       </c>
       <c r="S598" s="70">
@@ -51800,7 +51804,7 @@
         <v>0</v>
       </c>
       <c r="R599" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O599:Q599)</f>
         <v>24</v>
       </c>
       <c r="S599" s="64">
@@ -51863,7 +51867,7 @@
         <v>0</v>
       </c>
       <c r="R600" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O600:Q600)</f>
         <v>30</v>
       </c>
       <c r="S600" s="70">
@@ -51926,7 +51930,7 @@
         <v>0</v>
       </c>
       <c r="R601" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O601:Q601)</f>
         <v>21</v>
       </c>
       <c r="S601" s="64">
@@ -51989,7 +51993,7 @@
         <v>0</v>
       </c>
       <c r="R602" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O602:Q602)</f>
         <v>27</v>
       </c>
       <c r="S602" s="22">
@@ -52050,7 +52054,7 @@
         <v>0</v>
       </c>
       <c r="R603" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O603:Q603)</f>
         <v>26</v>
       </c>
       <c r="S603" s="24">
@@ -52113,7 +52117,7 @@
         <v>0</v>
       </c>
       <c r="R604" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O604:Q604)</f>
         <v>28</v>
       </c>
       <c r="S604" s="22">
@@ -52176,7 +52180,7 @@
         <v>0</v>
       </c>
       <c r="R605" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O605:Q605)</f>
         <v>20</v>
       </c>
       <c r="S605" s="24">
@@ -52237,7 +52241,7 @@
         <v>0</v>
       </c>
       <c r="R606" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O606:Q606)</f>
         <v>170</v>
       </c>
       <c r="S606" s="22">
@@ -52298,7 +52302,7 @@
         <v>0</v>
       </c>
       <c r="R607" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O607:Q607)</f>
         <v>170</v>
       </c>
       <c r="S607" s="24">
@@ -52361,7 +52365,7 @@
         <v>0</v>
       </c>
       <c r="R608" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O608:Q608)</f>
         <v>19</v>
       </c>
       <c r="S608" s="22">
@@ -52424,7 +52428,7 @@
         <v>0</v>
       </c>
       <c r="R609" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O609:Q609)</f>
         <v>19</v>
       </c>
       <c r="S609" s="24">
@@ -52485,7 +52489,7 @@
         <v>31</v>
       </c>
       <c r="R610" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O610:Q610)</f>
         <v>31</v>
       </c>
       <c r="S610" s="22">
@@ -52548,7 +52552,7 @@
         <v>0</v>
       </c>
       <c r="R611" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O611:Q611)</f>
         <v>15</v>
       </c>
       <c r="S611" s="24">
@@ -52609,7 +52613,7 @@
         <v>0</v>
       </c>
       <c r="R612" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O612:Q612)</f>
         <v>100</v>
       </c>
       <c r="S612" s="22">
@@ -52670,7 +52674,7 @@
         <v>0</v>
       </c>
       <c r="R613" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O613:Q613)</f>
         <v>114</v>
       </c>
       <c r="S613" s="24">
@@ -52733,7 +52737,7 @@
         <v>0</v>
       </c>
       <c r="R614" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O614:Q614)</f>
         <v>491</v>
       </c>
       <c r="S614" s="22">
@@ -52796,7 +52800,7 @@
         <v>0</v>
       </c>
       <c r="R615" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O615:Q615)</f>
         <v>27</v>
       </c>
       <c r="S615" s="24">
@@ -52857,7 +52861,7 @@
         <v>0</v>
       </c>
       <c r="R616" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O616:Q616)</f>
         <v>63</v>
       </c>
       <c r="S616" s="22">
@@ -52920,7 +52924,7 @@
         <v>0</v>
       </c>
       <c r="R617" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O617:Q617)</f>
         <v>42</v>
       </c>
       <c r="S617" s="24">
@@ -52983,7 +52987,7 @@
         <v>0</v>
       </c>
       <c r="R618" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O618:Q618)</f>
         <v>27</v>
       </c>
       <c r="S618" s="22">
@@ -53046,7 +53050,7 @@
         <v>0</v>
       </c>
       <c r="R619" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O619:Q619)</f>
         <v>40</v>
       </c>
       <c r="S619" s="24">
@@ -53107,7 +53111,7 @@
         <v>0</v>
       </c>
       <c r="R620" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O620:Q620)</f>
         <v>47</v>
       </c>
       <c r="S620" s="22">
@@ -53168,7 +53172,7 @@
         <v>0</v>
       </c>
       <c r="R621" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O621:Q621)</f>
         <v>23</v>
       </c>
       <c r="S621" s="24">
@@ -53229,7 +53233,7 @@
         <v>0</v>
       </c>
       <c r="R622" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O622:Q622)</f>
         <v>21</v>
       </c>
       <c r="S622" s="22">
@@ -53292,7 +53296,7 @@
         <v>0</v>
       </c>
       <c r="R623" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O623:Q623)</f>
         <v>26</v>
       </c>
       <c r="S623" s="24">
@@ -53351,7 +53355,7 @@
         <v>88</v>
       </c>
       <c r="R624" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O624:Q624)</f>
         <v>88</v>
       </c>
       <c r="S624" s="22">
@@ -53412,7 +53416,7 @@
         <v>0</v>
       </c>
       <c r="R625" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O625:Q625)</f>
         <v>33</v>
       </c>
       <c r="S625" s="24">
@@ -53471,7 +53475,7 @@
         <v>128</v>
       </c>
       <c r="R626" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O626:Q626)</f>
         <v>128</v>
       </c>
       <c r="S626" s="22">
@@ -53532,7 +53536,7 @@
         <v>0</v>
       </c>
       <c r="R627" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O627:Q627)</f>
         <v>80</v>
       </c>
       <c r="S627" s="24">
@@ -53593,7 +53597,7 @@
         <v>0</v>
       </c>
       <c r="R628" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O628:Q628)</f>
         <v>23</v>
       </c>
       <c r="S628" s="22" t="s">
@@ -53656,7 +53660,7 @@
         <v>0</v>
       </c>
       <c r="R629" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O629:Q629)</f>
         <v>49</v>
       </c>
       <c r="S629" s="24">
@@ -53717,7 +53721,7 @@
         <v>46</v>
       </c>
       <c r="R630" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O630:Q630)</f>
         <v>228</v>
       </c>
       <c r="S630" s="22">
@@ -53778,7 +53782,7 @@
         <v>0</v>
       </c>
       <c r="R631" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O631:Q631)</f>
         <v>28</v>
       </c>
       <c r="S631" s="24">
@@ -53839,7 +53843,7 @@
         <v>0</v>
       </c>
       <c r="R632" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O632:Q632)</f>
         <v>16</v>
       </c>
       <c r="S632" s="22">
@@ -53900,7 +53904,7 @@
         <v>0</v>
       </c>
       <c r="R633" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O633:Q633)</f>
         <v>40</v>
       </c>
       <c r="S633" s="24">
@@ -53963,7 +53967,7 @@
         <v>0</v>
       </c>
       <c r="R634" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O634:Q634)</f>
         <v>80</v>
       </c>
       <c r="S634" s="22">
@@ -54024,7 +54028,7 @@
         <v>0</v>
       </c>
       <c r="R635" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O635:Q635)</f>
         <v>70</v>
       </c>
       <c r="S635" s="24">
@@ -54085,7 +54089,7 @@
         <v>0</v>
       </c>
       <c r="R636" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O636:Q636)</f>
         <v>28</v>
       </c>
       <c r="S636" s="22">
@@ -54146,7 +54150,7 @@
         <v>30</v>
       </c>
       <c r="R637" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O637:Q637)</f>
         <v>30</v>
       </c>
       <c r="S637" s="24">
@@ -54209,7 +54213,7 @@
         <v>0</v>
       </c>
       <c r="R638" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O638:Q638)</f>
         <v>21</v>
       </c>
       <c r="S638" s="22" t="s">
@@ -54272,7 +54276,7 @@
         <v>40</v>
       </c>
       <c r="R639" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O639:Q639)</f>
         <v>179</v>
       </c>
       <c r="S639" s="24">
@@ -54329,7 +54333,7 @@
         <v>0</v>
       </c>
       <c r="R640" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O640:Q640)</f>
         <v>0</v>
       </c>
       <c r="S640" s="22">
@@ -54449,7 +54453,7 @@
         <v>33</v>
       </c>
       <c r="R642" s="23">
-        <f t="shared" ref="R642:R649" si="11">SUM(O642:Q642)</f>
+        <f>SUM(O642:Q642)</f>
         <v>33</v>
       </c>
       <c r="S642" s="22">
@@ -54508,7 +54512,7 @@
         <v>39</v>
       </c>
       <c r="R643" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O643:Q643)</f>
         <v>39</v>
       </c>
       <c r="S643" s="24">
@@ -54570,7 +54574,7 @@
         <v>39</v>
       </c>
       <c r="R644" s="23">
-        <f t="shared" si="11"/>
+        <f>SUM(O644:Q644)</f>
         <v>39</v>
       </c>
       <c r="S644" s="22">
@@ -54631,7 +54635,7 @@
         <v>0</v>
       </c>
       <c r="R645" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O645:Q645)</f>
         <v>170</v>
       </c>
       <c r="S645" s="24">
@@ -54694,7 +54698,7 @@
         <v>0</v>
       </c>
       <c r="R646" s="23">
-        <f t="shared" si="11"/>
+        <f>SUM(O646:Q646)</f>
         <v>13</v>
       </c>
       <c r="S646" s="22">
@@ -54755,7 +54759,7 @@
         <v>0</v>
       </c>
       <c r="R647" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O647:Q647)</f>
         <v>34</v>
       </c>
       <c r="S647" s="24">
@@ -54816,7 +54820,7 @@
         <v>0</v>
       </c>
       <c r="R648" s="23">
-        <f t="shared" si="11"/>
+        <f>SUM(O648:Q648)</f>
         <v>45</v>
       </c>
       <c r="S648" s="22">
@@ -54875,7 +54879,7 @@
         <v>0</v>
       </c>
       <c r="R649" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O649:Q649)</f>
         <v>72</v>
       </c>
       <c r="S649" s="24">
@@ -55676,7 +55680,7 @@
         <v>0</v>
       </c>
       <c r="R662" s="23">
-        <f t="shared" ref="R662:R668" si="12">SUM(O662:Q662)</f>
+        <f>SUM(O662:Q662)</f>
         <v>20</v>
       </c>
       <c r="S662" s="22">
@@ -55740,7 +55744,7 @@
         <v>0</v>
       </c>
       <c r="R663" s="25">
-        <f t="shared" si="12"/>
+        <f>SUM(O663:Q663)</f>
         <v>19</v>
       </c>
       <c r="S663" s="24">
@@ -55804,7 +55808,7 @@
         <v>0</v>
       </c>
       <c r="R664" s="23">
-        <f t="shared" si="12"/>
+        <f>SUM(O664:Q664)</f>
         <v>33</v>
       </c>
       <c r="S664" s="22">
@@ -55868,7 +55872,7 @@
         <v>0</v>
       </c>
       <c r="R665" s="25">
-        <f t="shared" si="12"/>
+        <f>SUM(O665:Q665)</f>
         <v>20</v>
       </c>
       <c r="S665" s="24">
@@ -55932,7 +55936,7 @@
         <v>0</v>
       </c>
       <c r="R666" s="23">
-        <f t="shared" si="12"/>
+        <f>SUM(O666:Q666)</f>
         <v>20</v>
       </c>
       <c r="S666" s="22">
@@ -55994,7 +55998,7 @@
         <v>14</v>
       </c>
       <c r="R667" s="25">
-        <f t="shared" si="12"/>
+        <f>SUM(O667:Q667)</f>
         <v>127</v>
       </c>
       <c r="S667" s="24">
@@ -56056,7 +56060,7 @@
         <v>34</v>
       </c>
       <c r="R668" s="23">
-        <f t="shared" si="12"/>
+        <f>SUM(O668:Q668)</f>
         <v>192</v>
       </c>
       <c r="S668" s="22">
@@ -56246,7 +56250,7 @@
         <v>0</v>
       </c>
       <c r="R671" s="25">
-        <f t="shared" ref="R671:R684" si="13">SUM(O671:Q671)</f>
+        <f>SUM(O671:Q671)</f>
         <v>22</v>
       </c>
       <c r="S671" s="24">
@@ -56310,7 +56314,7 @@
         <v>0</v>
       </c>
       <c r="R672" s="178">
-        <f t="shared" si="13"/>
+        <f>SUM(O672:Q672)</f>
         <v>1</v>
       </c>
       <c r="S672" s="172">
@@ -56362,7 +56366,7 @@
       <c r="P673" s="25"/>
       <c r="Q673" s="25"/>
       <c r="R673" s="25">
-        <f t="shared" si="13"/>
+        <f>SUM(O673:Q673)</f>
         <v>0</v>
       </c>
       <c r="S673" s="24"/>
@@ -56420,7 +56424,7 @@
         <v>80</v>
       </c>
       <c r="R674" s="23">
-        <f t="shared" si="13"/>
+        <f>SUM(O674:Q674)</f>
         <v>80</v>
       </c>
       <c r="S674" s="22">
@@ -56480,7 +56484,7 @@
         <v>80</v>
       </c>
       <c r="R675" s="23">
-        <f t="shared" si="13"/>
+        <f>SUM(O675:Q675)</f>
         <v>80</v>
       </c>
       <c r="S675" s="22">
@@ -56534,7 +56538,7 @@
       <c r="P676" s="25"/>
       <c r="Q676" s="25"/>
       <c r="R676" s="25">
-        <f t="shared" si="13"/>
+        <f>SUM(O676:Q676)</f>
         <v>0</v>
       </c>
       <c r="S676" s="24">
@@ -56596,7 +56600,7 @@
         <v>5</v>
       </c>
       <c r="R677" s="193">
-        <f t="shared" si="13"/>
+        <f>SUM(O677:Q677)</f>
         <v>100</v>
       </c>
       <c r="S677" s="186">
@@ -56660,7 +56664,7 @@
         <v>0</v>
       </c>
       <c r="R678" s="63">
-        <f t="shared" si="13"/>
+        <f>SUM(O678:Q678)</f>
         <v>17</v>
       </c>
       <c r="S678" s="64">
@@ -56724,7 +56728,7 @@
         <v>0</v>
       </c>
       <c r="R679" s="185">
-        <f t="shared" si="13"/>
+        <f>SUM(O679:Q679)</f>
         <v>32</v>
       </c>
       <c r="S679" s="180">
@@ -56778,7 +56782,7 @@
       <c r="P680" s="73"/>
       <c r="Q680" s="73"/>
       <c r="R680" s="73">
-        <f t="shared" si="13"/>
+        <f>SUM(O680:Q680)</f>
         <v>0</v>
       </c>
       <c r="S680" s="70">
@@ -56832,7 +56836,7 @@
       <c r="P681" s="193"/>
       <c r="Q681" s="193"/>
       <c r="R681" s="193">
-        <f t="shared" si="13"/>
+        <f>SUM(O681:Q681)</f>
         <v>0</v>
       </c>
       <c r="S681" s="186">
@@ -56886,7 +56890,7 @@
       <c r="P682" s="185"/>
       <c r="Q682" s="185"/>
       <c r="R682" s="185">
-        <f t="shared" si="13"/>
+        <f>SUM(O682:Q682)</f>
         <v>0</v>
       </c>
       <c r="S682" s="180">
@@ -56940,7 +56944,7 @@
       <c r="P683" s="193"/>
       <c r="Q683" s="193"/>
       <c r="R683" s="193">
-        <f t="shared" si="13"/>
+        <f>SUM(O683:Q683)</f>
         <v>0</v>
       </c>
       <c r="S683" s="186">
@@ -56990,7 +56994,7 @@
       <c r="P684" s="73"/>
       <c r="Q684" s="73"/>
       <c r="R684" s="73">
-        <f t="shared" si="13"/>
+        <f>SUM(O684:Q684)</f>
         <v>0</v>
       </c>
       <c r="S684" s="70">
@@ -57044,7 +57048,7 @@
       <c r="P685" s="217"/>
       <c r="Q685" s="217"/>
       <c r="R685" s="217">
-        <f t="shared" ref="R685:R747" si="14">IF(B685="","",SUM(O685:Q685))</f>
+        <f t="shared" ref="R685:R747" si="0">IF(B685="","",SUM(O685:Q685))</f>
         <v>0</v>
       </c>
       <c r="S685" s="210">
@@ -57101,7 +57105,7 @@
       <c r="P686" s="225"/>
       <c r="Q686" s="225"/>
       <c r="R686" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S686" s="219">
@@ -57156,7 +57160,7 @@
       <c r="P687" s="217"/>
       <c r="Q687" s="217"/>
       <c r="R687" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S687" s="210">
@@ -57213,7 +57217,7 @@
       <c r="P688" s="225"/>
       <c r="Q688" s="225"/>
       <c r="R688" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S688" s="219">
@@ -57278,7 +57282,7 @@
         <v>0</v>
       </c>
       <c r="R689" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="S689" s="210">
@@ -57335,7 +57339,7 @@
       <c r="P690" s="225"/>
       <c r="Q690" s="225"/>
       <c r="R690" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S690" s="219">
@@ -57400,7 +57404,7 @@
         <v>0</v>
       </c>
       <c r="R691" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="S691" s="210">
@@ -57465,7 +57469,7 @@
         <v>0</v>
       </c>
       <c r="R692" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S692" s="219">
@@ -57530,7 +57534,7 @@
         <v>0</v>
       </c>
       <c r="R693" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S693" s="210">
@@ -57583,7 +57587,7 @@
       <c r="P694" s="225"/>
       <c r="Q694" s="225"/>
       <c r="R694" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S694" s="219">
@@ -57636,7 +57640,7 @@
       <c r="P695" s="217"/>
       <c r="Q695" s="217"/>
       <c r="R695" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S695" s="210">
@@ -57693,7 +57697,7 @@
         <v>25</v>
       </c>
       <c r="R696" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="S696" s="219">
@@ -57754,7 +57758,7 @@
         <v>50</v>
       </c>
       <c r="R697" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="S697" s="210">
@@ -57807,7 +57811,7 @@
       <c r="P698" s="225"/>
       <c r="Q698" s="225"/>
       <c r="R698" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S698" s="219">
@@ -57862,7 +57866,7 @@
       <c r="P699" s="217"/>
       <c r="Q699" s="217"/>
       <c r="R699" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S699" s="210">
@@ -57917,7 +57921,7 @@
       <c r="P700" s="225"/>
       <c r="Q700" s="225"/>
       <c r="R700" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S700" s="219">
@@ -57972,7 +57976,7 @@
       <c r="P701" s="217"/>
       <c r="Q701" s="217"/>
       <c r="R701" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S701" s="210">
@@ -58018,12 +58022,14 @@
       </c>
       <c r="L702" s="224"/>
       <c r="M702" s="215"/>
-      <c r="N702" s="226"/>
+      <c r="N702" s="226">
+        <v>20</v>
+      </c>
       <c r="O702" s="225"/>
       <c r="P702" s="225"/>
       <c r="Q702" s="225"/>
       <c r="R702" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S702" s="219">
@@ -58076,7 +58082,7 @@
       <c r="P703" s="217"/>
       <c r="Q703" s="217"/>
       <c r="R703" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S703" s="210">
@@ -58109,7 +58115,7 @@
       <c r="P704" s="225"/>
       <c r="Q704" s="225"/>
       <c r="R704" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S704" s="219"/>
@@ -58138,7 +58144,7 @@
       <c r="P705" s="217"/>
       <c r="Q705" s="217"/>
       <c r="R705" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S705" s="210"/>
@@ -58167,7 +58173,7 @@
       <c r="P706" s="225"/>
       <c r="Q706" s="225"/>
       <c r="R706" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S706" s="219"/>
@@ -58196,7 +58202,7 @@
       <c r="P707" s="217"/>
       <c r="Q707" s="217"/>
       <c r="R707" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S707" s="210"/>
@@ -58225,7 +58231,7 @@
       <c r="P708" s="225"/>
       <c r="Q708" s="225"/>
       <c r="R708" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S708" s="219"/>
@@ -58254,7 +58260,7 @@
       <c r="P709" s="217"/>
       <c r="Q709" s="217"/>
       <c r="R709" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S709" s="210"/>
@@ -58283,7 +58289,7 @@
       <c r="P710" s="225"/>
       <c r="Q710" s="225"/>
       <c r="R710" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S710" s="219"/>
@@ -58312,7 +58318,7 @@
       <c r="P711" s="217"/>
       <c r="Q711" s="217"/>
       <c r="R711" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S711" s="210"/>
@@ -58341,7 +58347,7 @@
       <c r="P712" s="225"/>
       <c r="Q712" s="225"/>
       <c r="R712" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S712" s="219"/>
@@ -58370,7 +58376,7 @@
       <c r="P713" s="217"/>
       <c r="Q713" s="217"/>
       <c r="R713" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S713" s="210"/>
@@ -58399,7 +58405,7 @@
       <c r="P714" s="225"/>
       <c r="Q714" s="225"/>
       <c r="R714" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S714" s="219"/>
@@ -58428,7 +58434,7 @@
       <c r="P715" s="217"/>
       <c r="Q715" s="217"/>
       <c r="R715" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S715" s="210"/>
@@ -58457,7 +58463,7 @@
       <c r="P716" s="225"/>
       <c r="Q716" s="225"/>
       <c r="R716" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S716" s="219"/>
@@ -58486,7 +58492,7 @@
       <c r="P717" s="217"/>
       <c r="Q717" s="217"/>
       <c r="R717" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S717" s="210"/>
@@ -58515,7 +58521,7 @@
       <c r="P718" s="225"/>
       <c r="Q718" s="225"/>
       <c r="R718" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S718" s="219"/>
@@ -58544,7 +58550,7 @@
       <c r="P719" s="217"/>
       <c r="Q719" s="217"/>
       <c r="R719" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S719" s="210"/>
@@ -58573,7 +58579,7 @@
       <c r="P720" s="225"/>
       <c r="Q720" s="225"/>
       <c r="R720" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S720" s="219"/>
@@ -58602,7 +58608,7 @@
       <c r="P721" s="217"/>
       <c r="Q721" s="217"/>
       <c r="R721" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S721" s="210"/>
@@ -58631,7 +58637,7 @@
       <c r="P722" s="225"/>
       <c r="Q722" s="225"/>
       <c r="R722" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S722" s="219"/>
@@ -58660,7 +58666,7 @@
       <c r="P723" s="217"/>
       <c r="Q723" s="217"/>
       <c r="R723" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S723" s="210"/>
@@ -58689,7 +58695,7 @@
       <c r="P724" s="225"/>
       <c r="Q724" s="225"/>
       <c r="R724" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S724" s="219"/>
@@ -58718,7 +58724,7 @@
       <c r="P725" s="217"/>
       <c r="Q725" s="217"/>
       <c r="R725" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S725" s="210"/>
@@ -58747,7 +58753,7 @@
       <c r="P726" s="225"/>
       <c r="Q726" s="225"/>
       <c r="R726" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S726" s="219"/>
@@ -58776,7 +58782,7 @@
       <c r="P727" s="217"/>
       <c r="Q727" s="217"/>
       <c r="R727" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S727" s="210"/>
@@ -58805,7 +58811,7 @@
       <c r="P728" s="225"/>
       <c r="Q728" s="225"/>
       <c r="R728" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S728" s="219"/>
@@ -58834,7 +58840,7 @@
       <c r="P729" s="217"/>
       <c r="Q729" s="217"/>
       <c r="R729" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S729" s="210"/>
@@ -58863,7 +58869,7 @@
       <c r="P730" s="225"/>
       <c r="Q730" s="225"/>
       <c r="R730" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S730" s="219"/>
@@ -58892,7 +58898,7 @@
       <c r="P731" s="217"/>
       <c r="Q731" s="217"/>
       <c r="R731" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S731" s="210"/>
@@ -58921,7 +58927,7 @@
       <c r="P732" s="225"/>
       <c r="Q732" s="225"/>
       <c r="R732" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S732" s="219"/>
@@ -58950,7 +58956,7 @@
       <c r="P733" s="217"/>
       <c r="Q733" s="217"/>
       <c r="R733" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S733" s="210"/>
@@ -58979,7 +58985,7 @@
       <c r="P734" s="225"/>
       <c r="Q734" s="225"/>
       <c r="R734" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S734" s="219"/>
@@ -59008,7 +59014,7 @@
       <c r="P735" s="217"/>
       <c r="Q735" s="217"/>
       <c r="R735" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S735" s="210"/>
@@ -59037,7 +59043,7 @@
       <c r="P736" s="225"/>
       <c r="Q736" s="225"/>
       <c r="R736" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S736" s="219"/>
@@ -59066,7 +59072,7 @@
       <c r="P737" s="217"/>
       <c r="Q737" s="217"/>
       <c r="R737" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S737" s="210"/>
@@ -59095,7 +59101,7 @@
       <c r="P738" s="225"/>
       <c r="Q738" s="225"/>
       <c r="R738" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S738" s="219"/>
@@ -59124,7 +59130,7 @@
       <c r="P739" s="217"/>
       <c r="Q739" s="217"/>
       <c r="R739" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S739" s="210"/>
@@ -59153,7 +59159,7 @@
       <c r="P740" s="225"/>
       <c r="Q740" s="225"/>
       <c r="R740" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S740" s="219"/>
@@ -59182,7 +59188,7 @@
       <c r="P741" s="217"/>
       <c r="Q741" s="217"/>
       <c r="R741" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S741" s="210"/>
@@ -59211,7 +59217,7 @@
       <c r="P742" s="225"/>
       <c r="Q742" s="225"/>
       <c r="R742" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S742" s="219"/>
@@ -59240,7 +59246,7 @@
       <c r="P743" s="217"/>
       <c r="Q743" s="217"/>
       <c r="R743" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S743" s="210"/>
@@ -59269,7 +59275,7 @@
       <c r="P744" s="225"/>
       <c r="Q744" s="225"/>
       <c r="R744" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S744" s="219"/>
@@ -59298,7 +59304,7 @@
       <c r="P745" s="217"/>
       <c r="Q745" s="217"/>
       <c r="R745" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S745" s="210"/>
@@ -59327,7 +59333,7 @@
       <c r="P746" s="225"/>
       <c r="Q746" s="225"/>
       <c r="R746" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S746" s="219"/>
@@ -59356,7 +59362,7 @@
       <c r="P747" s="217"/>
       <c r="Q747" s="217"/>
       <c r="R747" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S747" s="210"/>
@@ -59385,7 +59391,7 @@
       <c r="P748" s="225"/>
       <c r="Q748" s="225"/>
       <c r="R748" s="225" t="str">
-        <f t="shared" ref="R748" si="15">IF(B748="","",SUM(O748:Q748))</f>
+        <f t="shared" ref="R748" si="1">IF(B748="","",SUM(O748:Q748))</f>
         <v/>
       </c>
       <c r="S748" s="219"/>
@@ -68694,6 +68700,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
@@ -68702,15 +68717,6 @@
     <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -68733,6 +68739,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -68741,12 +68755,4 @@
     <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4931" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36DF3342-E4D0-430B-BDAF-C17824D4E2C6}"/>
+  <xr:revisionPtr revIDLastSave="4932" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED2B6AC2-5233-4A86-A889-63D1929E9A9C}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12971,7 +12971,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -56747,7 +56747,7 @@
         <v>2026</v>
       </c>
       <c r="C680" s="228" t="s">
-        <v>2756</v>
+        <v>2767</v>
       </c>
       <c r="D680" s="70" t="s">
         <v>2742</v>
@@ -61136,7 +61136,7 @@
         <v>2026-024</v>
       </c>
       <c r="N22" t="str">
-        <v>A realizar</v>
+        <v>Adiado</v>
       </c>
       <c r="O22" t="str">
         <v>Escola de Instrutores - Design Instrucional</v>
@@ -62423,7 +62423,7 @@
         <v>2026-024</v>
       </c>
       <c r="C40" s="163" t="str">
-        <v>A realizar</v>
+        <v>Adiado</v>
       </c>
       <c r="D40" t="str">
         <v>Escola de Instrutores - Design Instrucional</v>
@@ -64774,7 +64774,7 @@
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
@@ -64931,7 +64931,7 @@
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.24390243902439024</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64952,7 +64952,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>7.3170731707317069E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64973,7 +64973,7 @@
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>0.12195121951219512</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64986,15 +64986,15 @@
       </c>
       <c r="C36" s="128">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A36)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="119">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>4.878048780487805E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65015,7 +65015,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>4.878048780487805E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65036,7 +65036,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.17073170731707318</v>
+        <v>0.17499999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65057,7 +65057,7 @@
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>7.3170731707317069E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65078,7 +65078,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>2.4390243902439025E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65099,7 +65099,7 @@
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.14634146341463414</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65141,7 +65141,7 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>4.878048780487805E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65175,11 +65175,11 @@
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4932" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED2B6AC2-5233-4A86-A889-63D1929E9A9C}"/>
+  <xr:revisionPtr revIDLastSave="4933" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB92450F-28A6-46E8-9B93-558AF1098EAA}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -68499,6 +68499,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052D3A7BF04652843BCB50FE90745AA50" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ef6274641b2f7d621af528393bef14e5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe686eaa-0658-4f15-b230-9e46c4d089fd" xmlns:ns3="91ce1707-6d34-452b-b217-9734c03e6729" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fa87a3bcf42251a9fb9988d55372596" ns2:_="" ns3:_="">
     <xsd:import namespace="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
@@ -68699,27 +68719,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
+    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -68736,23 +68755,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
-    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4933" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB92450F-28A6-46E8-9B93-558AF1098EAA}"/>
+  <xr:revisionPtr revIDLastSave="4936" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92512C2A-3FCF-4554-83D9-C0C35767D110}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6533" uniqueCount="2961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6535" uniqueCount="2962">
   <si>
     <t>ID</t>
   </si>
@@ -9051,6 +9051,9 @@
   </si>
   <si>
     <t>26 e 27/10/2026</t>
+  </si>
+  <si>
+    <t>6761/2026</t>
   </si>
 </sst>
 </file>
@@ -12995,7 +12998,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14963,10 +14966,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}" name="Tabela2" displayName="Tabela2" ref="B1:T684" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="B1:T684" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}">
@@ -15378,7 +15377,7 @@
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
       <c r="R2" s="23">
-        <f>SUM(O2:Q2)</f>
+        <f t="shared" ref="R2:R65" si="0">SUM(O2:Q2)</f>
         <v>20</v>
       </c>
       <c r="S2" s="22">
@@ -15429,7 +15428,7 @@
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25">
-        <f>SUM(O3:Q3)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S3" s="24">
@@ -15480,7 +15479,7 @@
       <c r="P4" s="23"/>
       <c r="Q4" s="23"/>
       <c r="R4" s="23">
-        <f>SUM(O4:Q4)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="S4" s="22">
@@ -15531,7 +15530,7 @@
       <c r="P5" s="25"/>
       <c r="Q5" s="25"/>
       <c r="R5" s="25">
-        <f>SUM(O5:Q5)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S5" s="24">
@@ -15582,7 +15581,7 @@
       <c r="P6" s="23"/>
       <c r="Q6" s="23"/>
       <c r="R6" s="23">
-        <f>SUM(O6:Q6)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="S6" s="22">
@@ -15633,7 +15632,7 @@
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
       <c r="R7" s="25">
-        <f>SUM(O7:Q7)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S7" s="24">
@@ -15682,7 +15681,7 @@
       <c r="P8" s="23"/>
       <c r="Q8" s="23"/>
       <c r="R8" s="23">
-        <f>SUM(O8:Q8)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="S8" s="22">
@@ -15733,7 +15732,7 @@
       </c>
       <c r="Q9" s="25"/>
       <c r="R9" s="25">
-        <f>SUM(O9:Q9)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="S9" s="24">
@@ -15784,7 +15783,7 @@
       </c>
       <c r="Q10" s="23"/>
       <c r="R10" s="23">
-        <f>SUM(O10:Q10)</f>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="S10" s="22">
@@ -15837,7 +15836,7 @@
       <c r="P11" s="25"/>
       <c r="Q11" s="25"/>
       <c r="R11" s="25">
-        <f>SUM(O11:Q11)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="S11" s="24">
@@ -15892,7 +15891,7 @@
       </c>
       <c r="Q12" s="23"/>
       <c r="R12" s="23">
-        <f>SUM(O12:Q12)</f>
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="S12" s="22">
@@ -15947,7 +15946,7 @@
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
       <c r="R13" s="25">
-        <f>SUM(O13:Q13)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="S13" s="24">
@@ -16002,7 +16001,7 @@
       </c>
       <c r="Q14" s="23"/>
       <c r="R14" s="23">
-        <f>SUM(O14:Q14)</f>
+        <f t="shared" si="0"/>
         <v>89</v>
       </c>
       <c r="S14" s="22">
@@ -16057,7 +16056,7 @@
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
       <c r="R15" s="25">
-        <f>SUM(O15:Q15)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="S15" s="24">
@@ -16114,7 +16113,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="23">
-        <f>SUM(O16:Q16)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S16" s="22">
@@ -16167,7 +16166,7 @@
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
       <c r="R17" s="25">
-        <f>SUM(O17:Q17)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S17" s="24">
@@ -16222,7 +16221,7 @@
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
       <c r="R18" s="23">
-        <f>SUM(O18:Q18)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S18" s="22">
@@ -16277,7 +16276,7 @@
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
       <c r="R19" s="25">
-        <f>SUM(O19:Q19)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="S19" s="24">
@@ -16332,7 +16331,7 @@
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
       <c r="R20" s="23">
-        <f>SUM(O20:Q20)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="S20" s="22">
@@ -16387,7 +16386,7 @@
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
       <c r="R21" s="25">
-        <f>SUM(O21:Q21)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="S21" s="24">
@@ -16442,7 +16441,7 @@
       </c>
       <c r="Q22" s="23"/>
       <c r="R22" s="23">
-        <f>SUM(O22:Q22)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="S22" s="22">
@@ -16497,7 +16496,7 @@
       <c r="P23" s="25"/>
       <c r="Q23" s="25"/>
       <c r="R23" s="25">
-        <f>SUM(O23:Q23)</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="S23" s="24">
@@ -16552,7 +16551,7 @@
       <c r="P24" s="23"/>
       <c r="Q24" s="23"/>
       <c r="R24" s="23">
-        <f>SUM(O24:Q24)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="S24" s="22">
@@ -16607,7 +16606,7 @@
       <c r="P25" s="25"/>
       <c r="Q25" s="25"/>
       <c r="R25" s="25">
-        <f>SUM(O25:Q25)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="S25" s="24">
@@ -16662,7 +16661,7 @@
       <c r="P26" s="23"/>
       <c r="Q26" s="23"/>
       <c r="R26" s="23">
-        <f>SUM(O26:Q26)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="S26" s="22">
@@ -16715,7 +16714,7 @@
       <c r="P27" s="25"/>
       <c r="Q27" s="25"/>
       <c r="R27" s="25">
-        <f>SUM(O27:Q27)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="S27" s="24"/>
@@ -16766,7 +16765,7 @@
         <v>46</v>
       </c>
       <c r="R28" s="23">
-        <f>SUM(O28:Q28)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="S28" s="22">
@@ -16821,7 +16820,7 @@
       <c r="P29" s="25"/>
       <c r="Q29" s="25"/>
       <c r="R29" s="25">
-        <f>SUM(O29:Q29)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="S29" s="24">
@@ -16876,7 +16875,7 @@
       </c>
       <c r="Q30" s="23"/>
       <c r="R30" s="23">
-        <f>SUM(O30:Q30)</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="S30" s="22">
@@ -16929,7 +16928,7 @@
       <c r="P31" s="25"/>
       <c r="Q31" s="25"/>
       <c r="R31" s="25">
-        <f>SUM(O31:Q31)</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="S31" s="24">
@@ -16982,7 +16981,7 @@
         <v>46</v>
       </c>
       <c r="R32" s="23">
-        <f>SUM(O32:Q32)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="S32" s="22">
@@ -17035,7 +17034,7 @@
       <c r="P33" s="25"/>
       <c r="Q33" s="25"/>
       <c r="R33" s="25">
-        <f>SUM(O33:Q33)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="S33" s="24">
@@ -17086,7 +17085,7 @@
       <c r="P34" s="23"/>
       <c r="Q34" s="23"/>
       <c r="R34" s="23">
-        <f>SUM(O34:Q34)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="S34" s="22">
@@ -17137,7 +17136,7 @@
       <c r="P35" s="25"/>
       <c r="Q35" s="25"/>
       <c r="R35" s="25">
-        <f>SUM(O35:Q35)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="S35" s="24">
@@ -17192,7 +17191,7 @@
       </c>
       <c r="Q36" s="23"/>
       <c r="R36" s="23">
-        <f>SUM(O36:Q36)</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="S36" s="22">
@@ -17247,7 +17246,7 @@
       </c>
       <c r="Q37" s="25"/>
       <c r="R37" s="25">
-        <f>SUM(O37:Q37)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="S37" s="24">
@@ -17302,7 +17301,7 @@
       <c r="P38" s="23"/>
       <c r="Q38" s="23"/>
       <c r="R38" s="23">
-        <f>SUM(O38:Q38)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="S38" s="22">
@@ -17357,7 +17356,7 @@
       </c>
       <c r="Q39" s="25"/>
       <c r="R39" s="25">
-        <f>SUM(O39:Q39)</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="S39" s="24">
@@ -17412,7 +17411,7 @@
         <v>45</v>
       </c>
       <c r="R40" s="23">
-        <f>SUM(O40:Q40)</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="S40" s="22">
@@ -17467,7 +17466,7 @@
       <c r="P41" s="25"/>
       <c r="Q41" s="25"/>
       <c r="R41" s="25">
-        <f>SUM(O41:Q41)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="S41" s="24">
@@ -17522,7 +17521,7 @@
         <v>21</v>
       </c>
       <c r="R42" s="23">
-        <f>SUM(O42:Q42)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="S42" s="22">
@@ -17577,7 +17576,7 @@
       <c r="P43" s="25"/>
       <c r="Q43" s="25"/>
       <c r="R43" s="25">
-        <f>SUM(O43:Q43)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="S43" s="24">
@@ -17632,7 +17631,7 @@
       </c>
       <c r="Q44" s="23"/>
       <c r="R44" s="23">
-        <f>SUM(O44:Q44)</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="S44" s="22">
@@ -17687,7 +17686,7 @@
       <c r="P45" s="25"/>
       <c r="Q45" s="25"/>
       <c r="R45" s="25">
-        <f>SUM(O45:Q45)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="S45" s="24">
@@ -17742,7 +17741,7 @@
       <c r="P46" s="23"/>
       <c r="Q46" s="23"/>
       <c r="R46" s="23">
-        <f>SUM(O46:Q46)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="S46" s="22">
@@ -17799,7 +17798,7 @@
       </c>
       <c r="Q47" s="25"/>
       <c r="R47" s="25">
-        <f>SUM(O47:Q47)</f>
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="S47" s="24">
@@ -17858,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="23">
-        <f>SUM(O48:Q48)</f>
+        <f t="shared" si="0"/>
         <v>329</v>
       </c>
       <c r="S48" s="22">
@@ -17913,7 +17912,7 @@
       <c r="P49" s="25"/>
       <c r="Q49" s="25"/>
       <c r="R49" s="25">
-        <f>SUM(O49:Q49)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="S49" s="24">
@@ -17968,7 +17967,7 @@
       <c r="P50" s="23"/>
       <c r="Q50" s="23"/>
       <c r="R50" s="23">
-        <f>SUM(O50:Q50)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="S50" s="22">
@@ -18023,7 +18022,7 @@
       </c>
       <c r="Q51" s="25"/>
       <c r="R51" s="25">
-        <f>SUM(O51:Q51)</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="S51" s="24">
@@ -18078,7 +18077,7 @@
       </c>
       <c r="Q52" s="23"/>
       <c r="R52" s="23">
-        <f>SUM(O52:Q52)</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="S52" s="22">
@@ -18133,7 +18132,7 @@
       <c r="P53" s="25"/>
       <c r="Q53" s="25"/>
       <c r="R53" s="25">
-        <f>SUM(O53:Q53)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="S53" s="24">
@@ -18188,7 +18187,7 @@
       <c r="P54" s="23"/>
       <c r="Q54" s="23"/>
       <c r="R54" s="23">
-        <f>SUM(O54:Q54)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="S54" s="22">
@@ -18243,7 +18242,7 @@
       <c r="P55" s="25"/>
       <c r="Q55" s="25"/>
       <c r="R55" s="25">
-        <f>SUM(O55:Q55)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S55" s="24">
@@ -18298,7 +18297,7 @@
       </c>
       <c r="Q56" s="23"/>
       <c r="R56" s="23">
-        <f>SUM(O56:Q56)</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="S56" s="22">
@@ -18353,7 +18352,7 @@
       <c r="P57" s="25"/>
       <c r="Q57" s="25"/>
       <c r="R57" s="25">
-        <f>SUM(O57:Q57)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="S57" s="24">
@@ -18408,7 +18407,7 @@
       </c>
       <c r="Q58" s="23"/>
       <c r="R58" s="23">
-        <f>SUM(O58:Q58)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="S58" s="22">
@@ -18463,7 +18462,7 @@
       <c r="P59" s="25"/>
       <c r="Q59" s="25"/>
       <c r="R59" s="25">
-        <f>SUM(O59:Q59)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="S59" s="24">
@@ -18518,7 +18517,7 @@
       </c>
       <c r="Q60" s="23"/>
       <c r="R60" s="23">
-        <f>SUM(O60:Q60)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="S60" s="22">
@@ -18573,7 +18572,7 @@
       </c>
       <c r="Q61" s="25"/>
       <c r="R61" s="25">
-        <f>SUM(O61:Q61)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="S61" s="24">
@@ -18628,7 +18627,7 @@
       </c>
       <c r="Q62" s="23"/>
       <c r="R62" s="23">
-        <f>SUM(O62:Q62)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="S62" s="22">
@@ -18683,7 +18682,7 @@
       <c r="P63" s="25"/>
       <c r="Q63" s="25"/>
       <c r="R63" s="25">
-        <f>SUM(O63:Q63)</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="S63" s="24">
@@ -18738,7 +18737,7 @@
       <c r="P64" s="23"/>
       <c r="Q64" s="23"/>
       <c r="R64" s="23">
-        <f>SUM(O64:Q64)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="S64" s="22">
@@ -18793,7 +18792,7 @@
       </c>
       <c r="Q65" s="25"/>
       <c r="R65" s="25">
-        <f>SUM(O65:Q65)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="S65" s="24">
@@ -18848,7 +18847,7 @@
       <c r="P66" s="23"/>
       <c r="Q66" s="23"/>
       <c r="R66" s="23">
-        <f>SUM(O66:Q66)</f>
+        <f t="shared" ref="R66:R129" si="1">SUM(O66:Q66)</f>
         <v>20</v>
       </c>
       <c r="S66" s="22">
@@ -18903,7 +18902,7 @@
       </c>
       <c r="Q67" s="25"/>
       <c r="R67" s="25">
-        <f>SUM(O67:Q67)</f>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="S67" s="24">
@@ -18958,7 +18957,7 @@
       <c r="P68" s="23"/>
       <c r="Q68" s="23"/>
       <c r="R68" s="23">
-        <f>SUM(O68:Q68)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="S68" s="22">
@@ -19013,7 +19012,7 @@
       <c r="P69" s="25"/>
       <c r="Q69" s="25"/>
       <c r="R69" s="25">
-        <f>SUM(O69:Q69)</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="S69" s="24">
@@ -19068,7 +19067,7 @@
       </c>
       <c r="Q70" s="23"/>
       <c r="R70" s="23">
-        <f>SUM(O70:Q70)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="S70" s="22">
@@ -19123,7 +19122,7 @@
       <c r="P71" s="25"/>
       <c r="Q71" s="25"/>
       <c r="R71" s="25">
-        <f>SUM(O71:Q71)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="S71" s="24">
@@ -19178,7 +19177,7 @@
       <c r="P72" s="23"/>
       <c r="Q72" s="23"/>
       <c r="R72" s="23">
-        <f>SUM(O72:Q72)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="S72" s="22">
@@ -19233,7 +19232,7 @@
       <c r="P73" s="25"/>
       <c r="Q73" s="25"/>
       <c r="R73" s="25">
-        <f>SUM(O73:Q73)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S73" s="24">
@@ -19288,7 +19287,7 @@
       <c r="P74" s="23"/>
       <c r="Q74" s="23"/>
       <c r="R74" s="23">
-        <f>SUM(O74:Q74)</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="S74" s="22">
@@ -19343,7 +19342,7 @@
         <v>37</v>
       </c>
       <c r="R75" s="25">
-        <f>SUM(O75:Q75)</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="S75" s="24">
@@ -19398,7 +19397,7 @@
       </c>
       <c r="Q76" s="23"/>
       <c r="R76" s="23">
-        <f>SUM(O76:Q76)</f>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="S76" s="22">
@@ -19453,7 +19452,7 @@
       <c r="P77" s="25"/>
       <c r="Q77" s="25"/>
       <c r="R77" s="25">
-        <f>SUM(O77:Q77)</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="S77" s="24">
@@ -19508,7 +19507,7 @@
       <c r="P78" s="23"/>
       <c r="Q78" s="23"/>
       <c r="R78" s="23">
-        <f>SUM(O78:Q78)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S78" s="22">
@@ -19563,7 +19562,7 @@
       </c>
       <c r="Q79" s="25"/>
       <c r="R79" s="25">
-        <f>SUM(O79:Q79)</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="S79" s="24">
@@ -19618,7 +19617,7 @@
       <c r="P80" s="23"/>
       <c r="Q80" s="23"/>
       <c r="R80" s="23">
-        <f>SUM(O80:Q80)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S80" s="22">
@@ -19673,7 +19672,7 @@
       <c r="P81" s="25"/>
       <c r="Q81" s="25"/>
       <c r="R81" s="25">
-        <f>SUM(O81:Q81)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="S81" s="24">
@@ -19728,7 +19727,7 @@
       <c r="P82" s="23"/>
       <c r="Q82" s="23"/>
       <c r="R82" s="23">
-        <f>SUM(O82:Q82)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="S82" s="22">
@@ -19783,7 +19782,7 @@
       <c r="P83" s="25"/>
       <c r="Q83" s="25"/>
       <c r="R83" s="25">
-        <f>SUM(O83:Q83)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="S83" s="24">
@@ -19838,7 +19837,7 @@
       </c>
       <c r="Q84" s="23"/>
       <c r="R84" s="23">
-        <f>SUM(O84:Q84)</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="S84" s="22">
@@ -19893,7 +19892,7 @@
         <v>49</v>
       </c>
       <c r="R85" s="25">
-        <f>SUM(O85:Q85)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="S85" s="24">
@@ -19948,7 +19947,7 @@
       </c>
       <c r="Q86" s="23"/>
       <c r="R86" s="23">
-        <f>SUM(O86:Q86)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="S86" s="22">
@@ -20003,7 +20002,7 @@
       <c r="P87" s="25"/>
       <c r="Q87" s="25"/>
       <c r="R87" s="25">
-        <f>SUM(O87:Q87)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S87" s="24">
@@ -20062,7 +20061,7 @@
         <v>0</v>
       </c>
       <c r="R88" s="23">
-        <f>SUM(O88:Q88)</f>
+        <f t="shared" si="1"/>
         <v>312</v>
       </c>
       <c r="S88" s="22">
@@ -20117,7 +20116,7 @@
       </c>
       <c r="Q89" s="25"/>
       <c r="R89" s="25">
-        <f>SUM(O89:Q89)</f>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="S89" s="24">
@@ -20172,7 +20171,7 @@
       </c>
       <c r="Q90" s="23"/>
       <c r="R90" s="23">
-        <f>SUM(O90:Q90)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="S90" s="22">
@@ -20227,7 +20226,7 @@
       <c r="P91" s="25"/>
       <c r="Q91" s="25"/>
       <c r="R91" s="25">
-        <f>SUM(O91:Q91)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S91" s="24">
@@ -20282,7 +20281,7 @@
       <c r="P92" s="23"/>
       <c r="Q92" s="23"/>
       <c r="R92" s="23">
-        <f>SUM(O92:Q92)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S92" s="22">
@@ -20337,7 +20336,7 @@
       </c>
       <c r="Q93" s="25"/>
       <c r="R93" s="25">
-        <f>SUM(O93:Q93)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="S93" s="24">
@@ -20392,7 +20391,7 @@
       </c>
       <c r="Q94" s="23"/>
       <c r="R94" s="23">
-        <f>SUM(O94:Q94)</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="S94" s="22">
@@ -20447,7 +20446,7 @@
         <v>96</v>
       </c>
       <c r="R95" s="25">
-        <f>SUM(O95:Q95)</f>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="S95" s="24">
@@ -20502,7 +20501,7 @@
       <c r="P96" s="23"/>
       <c r="Q96" s="23"/>
       <c r="R96" s="23">
-        <f>SUM(O96:Q96)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S96" s="22">
@@ -20557,7 +20556,7 @@
       </c>
       <c r="Q97" s="25"/>
       <c r="R97" s="25">
-        <f>SUM(O97:Q97)</f>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="S97" s="24">
@@ -20612,7 +20611,7 @@
       <c r="P98" s="23"/>
       <c r="Q98" s="23"/>
       <c r="R98" s="23">
-        <f>SUM(O98:Q98)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S98" s="22">
@@ -20667,7 +20666,7 @@
       <c r="P99" s="25"/>
       <c r="Q99" s="25"/>
       <c r="R99" s="25">
-        <f>SUM(O99:Q99)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S99" s="24">
@@ -20722,7 +20721,7 @@
       <c r="P100" s="23"/>
       <c r="Q100" s="23"/>
       <c r="R100" s="23">
-        <f>SUM(O100:Q100)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="S100" s="22">
@@ -20777,7 +20776,7 @@
       </c>
       <c r="Q101" s="25"/>
       <c r="R101" s="25">
-        <f>SUM(O101:Q101)</f>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="S101" s="24">
@@ -20832,7 +20831,7 @@
       <c r="P102" s="23"/>
       <c r="Q102" s="23"/>
       <c r="R102" s="23">
-        <f>SUM(O102:Q102)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S102" s="22">
@@ -20887,7 +20886,7 @@
       <c r="P103" s="25"/>
       <c r="Q103" s="25"/>
       <c r="R103" s="25">
-        <f>SUM(O103:Q103)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="S103" s="24">
@@ -20942,7 +20941,7 @@
       </c>
       <c r="Q104" s="23"/>
       <c r="R104" s="23">
-        <f>SUM(O104:Q104)</f>
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
       <c r="S104" s="22">
@@ -20997,7 +20996,7 @@
       <c r="P105" s="25"/>
       <c r="Q105" s="25"/>
       <c r="R105" s="25">
-        <f>SUM(O105:Q105)</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="S105" s="24">
@@ -21052,7 +21051,7 @@
       </c>
       <c r="Q106" s="23"/>
       <c r="R106" s="23">
-        <f>SUM(O106:Q106)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="S106" s="22">
@@ -21107,7 +21106,7 @@
       <c r="P107" s="25"/>
       <c r="Q107" s="25"/>
       <c r="R107" s="25">
-        <f>SUM(O107:Q107)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S107" s="24">
@@ -21166,7 +21165,7 @@
         <v>0</v>
       </c>
       <c r="R108" s="23">
-        <f>SUM(O108:Q108)</f>
+        <f t="shared" si="1"/>
         <v>353</v>
       </c>
       <c r="S108" s="22">
@@ -21221,7 +21220,7 @@
       <c r="P109" s="25"/>
       <c r="Q109" s="25"/>
       <c r="R109" s="25">
-        <f>SUM(O109:Q109)</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="S109" s="24">
@@ -21276,7 +21275,7 @@
       <c r="P110" s="23"/>
       <c r="Q110" s="23"/>
       <c r="R110" s="23">
-        <f>SUM(O110:Q110)</f>
+        <f t="shared" si="1"/>
         <v>215</v>
       </c>
       <c r="S110" s="22">
@@ -21331,7 +21330,7 @@
       <c r="P111" s="25"/>
       <c r="Q111" s="25"/>
       <c r="R111" s="25">
-        <f>SUM(O111:Q111)</f>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="S111" s="24">
@@ -21386,7 +21385,7 @@
       <c r="P112" s="23"/>
       <c r="Q112" s="23"/>
       <c r="R112" s="23">
-        <f>SUM(O112:Q112)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="S112" s="22">
@@ -21441,7 +21440,7 @@
       <c r="P113" s="25"/>
       <c r="Q113" s="25"/>
       <c r="R113" s="25">
-        <f>SUM(O113:Q113)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="S113" s="24">
@@ -21496,7 +21495,7 @@
       <c r="P114" s="23"/>
       <c r="Q114" s="23"/>
       <c r="R114" s="23">
-        <f>SUM(O114:Q114)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="S114" s="22">
@@ -21555,7 +21554,7 @@
         <v>0</v>
       </c>
       <c r="R115" s="25">
-        <f>SUM(O115:Q115)</f>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="S115" s="24">
@@ -21616,7 +21615,7 @@
       </c>
       <c r="Q116" s="23"/>
       <c r="R116" s="23">
-        <f>SUM(O116:Q116)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S116" s="22">
@@ -21677,7 +21676,7 @@
       </c>
       <c r="Q117" s="25"/>
       <c r="R117" s="25">
-        <f>SUM(O117:Q117)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="S117" s="24">
@@ -21738,7 +21737,7 @@
       </c>
       <c r="Q118" s="23"/>
       <c r="R118" s="23">
-        <f>SUM(O118:Q118)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="S118" s="22">
@@ -21799,7 +21798,7 @@
       </c>
       <c r="Q119" s="25"/>
       <c r="R119" s="25">
-        <f>SUM(O119:Q119)</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="S119" s="24">
@@ -21860,7 +21859,7 @@
       </c>
       <c r="Q120" s="23"/>
       <c r="R120" s="23">
-        <f>SUM(O120:Q120)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="S120" s="22">
@@ -21921,7 +21920,7 @@
       </c>
       <c r="Q121" s="25"/>
       <c r="R121" s="25">
-        <f>SUM(O121:Q121)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="S121" s="24">
@@ -21982,7 +21981,7 @@
       </c>
       <c r="Q122" s="23"/>
       <c r="R122" s="23">
-        <f>SUM(O122:Q122)</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="S122" s="22">
@@ -22043,7 +22042,7 @@
       </c>
       <c r="Q123" s="25"/>
       <c r="R123" s="25">
-        <f>SUM(O123:Q123)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="S123" s="24">
@@ -22104,7 +22103,7 @@
       </c>
       <c r="Q124" s="23"/>
       <c r="R124" s="23">
-        <f>SUM(O124:Q124)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="S124" s="22">
@@ -22165,7 +22164,7 @@
       </c>
       <c r="Q125" s="25"/>
       <c r="R125" s="25">
-        <f>SUM(O125:Q125)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S125" s="24">
@@ -22226,7 +22225,7 @@
       </c>
       <c r="Q126" s="23"/>
       <c r="R126" s="23">
-        <f>SUM(O126:Q126)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="S126" s="22">
@@ -22287,7 +22286,7 @@
       </c>
       <c r="Q127" s="25"/>
       <c r="R127" s="25">
-        <f>SUM(O127:Q127)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="S127" s="24">
@@ -22348,7 +22347,7 @@
       </c>
       <c r="Q128" s="23"/>
       <c r="R128" s="23">
-        <f>SUM(O128:Q128)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="S128" s="22">
@@ -22409,7 +22408,7 @@
       </c>
       <c r="Q129" s="25"/>
       <c r="R129" s="25">
-        <f>SUM(O129:Q129)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="S129" s="24">
@@ -22470,7 +22469,7 @@
       </c>
       <c r="Q130" s="23"/>
       <c r="R130" s="23">
-        <f>SUM(O130:Q130)</f>
+        <f t="shared" ref="R130:R193" si="2">SUM(O130:Q130)</f>
         <v>25</v>
       </c>
       <c r="S130" s="22">
@@ -22531,7 +22530,7 @@
       </c>
       <c r="Q131" s="25"/>
       <c r="R131" s="25">
-        <f>SUM(O131:Q131)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="S131" s="24">
@@ -22592,7 +22591,7 @@
       </c>
       <c r="Q132" s="23"/>
       <c r="R132" s="23">
-        <f>SUM(O132:Q132)</f>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="S132" s="22">
@@ -22653,7 +22652,7 @@
       </c>
       <c r="Q133" s="25"/>
       <c r="R133" s="25">
-        <f>SUM(O133:Q133)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="S133" s="24">
@@ -22714,7 +22713,7 @@
       </c>
       <c r="Q134" s="23"/>
       <c r="R134" s="23">
-        <f>SUM(O134:Q134)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="S134" s="22">
@@ -22775,7 +22774,7 @@
       </c>
       <c r="Q135" s="25"/>
       <c r="R135" s="25">
-        <f>SUM(O135:Q135)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="S135" s="24">
@@ -22836,7 +22835,7 @@
       </c>
       <c r="Q136" s="23"/>
       <c r="R136" s="23">
-        <f>SUM(O136:Q136)</f>
+        <f t="shared" si="2"/>
         <v>182</v>
       </c>
       <c r="S136" s="22">
@@ -22897,7 +22896,7 @@
       </c>
       <c r="Q137" s="25"/>
       <c r="R137" s="25">
-        <f>SUM(O137:Q137)</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="S137" s="24">
@@ -22960,7 +22959,7 @@
         <v>0</v>
       </c>
       <c r="R138" s="23">
-        <f>SUM(O138:Q138)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="S138" s="22">
@@ -23021,7 +23020,7 @@
       </c>
       <c r="Q139" s="25"/>
       <c r="R139" s="25">
-        <f>SUM(O139:Q139)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="S139" s="24">
@@ -23082,7 +23081,7 @@
       </c>
       <c r="Q140" s="23"/>
       <c r="R140" s="23">
-        <f>SUM(O140:Q140)</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="S140" s="22">
@@ -23145,7 +23144,7 @@
         <v>0</v>
       </c>
       <c r="R141" s="25">
-        <f>SUM(O141:Q141)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="S141" s="24">
@@ -23206,7 +23205,7 @@
       </c>
       <c r="Q142" s="23"/>
       <c r="R142" s="23">
-        <f>SUM(O142:Q142)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="S142" s="22">
@@ -23267,7 +23266,7 @@
       </c>
       <c r="Q143" s="25"/>
       <c r="R143" s="25">
-        <f>SUM(O143:Q143)</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="S143" s="24">
@@ -23328,7 +23327,7 @@
       </c>
       <c r="Q144" s="23"/>
       <c r="R144" s="23">
-        <f>SUM(O144:Q144)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="S144" s="22">
@@ -23391,7 +23390,7 @@
         <v>0</v>
       </c>
       <c r="R145" s="25">
-        <f>SUM(O145:Q145)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="S145" s="24">
@@ -23452,7 +23451,7 @@
       </c>
       <c r="Q146" s="23"/>
       <c r="R146" s="23">
-        <f>SUM(O146:Q146)</f>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="S146" s="22">
@@ -23513,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="R147" s="25">
-        <f>SUM(O147:Q147)</f>
+        <f t="shared" si="2"/>
         <v>54</v>
       </c>
       <c r="S147" s="24">
@@ -23574,7 +23573,7 @@
       </c>
       <c r="Q148" s="23"/>
       <c r="R148" s="23">
-        <f>SUM(O148:Q148)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="S148" s="22">
@@ -23635,7 +23634,7 @@
       </c>
       <c r="Q149" s="25"/>
       <c r="R149" s="25">
-        <f>SUM(O149:Q149)</f>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="S149" s="24">
@@ -23696,7 +23695,7 @@
       </c>
       <c r="Q150" s="23"/>
       <c r="R150" s="23">
-        <f>SUM(O150:Q150)</f>
+        <f t="shared" si="2"/>
         <v>62</v>
       </c>
       <c r="S150" s="22">
@@ -23757,7 +23756,7 @@
       </c>
       <c r="Q151" s="25"/>
       <c r="R151" s="25">
-        <f>SUM(O151:Q151)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="S151" s="24">
@@ -23818,7 +23817,7 @@
       </c>
       <c r="Q152" s="23"/>
       <c r="R152" s="23">
-        <f>SUM(O152:Q152)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="S152" s="22">
@@ -23879,7 +23878,7 @@
       </c>
       <c r="Q153" s="25"/>
       <c r="R153" s="25">
-        <f>SUM(O153:Q153)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="S153" s="24">
@@ -23942,7 +23941,7 @@
         <v>0</v>
       </c>
       <c r="R154" s="23">
-        <f>SUM(O154:Q154)</f>
+        <f t="shared" si="2"/>
         <v>74</v>
       </c>
       <c r="S154" s="22">
@@ -24003,7 +24002,7 @@
       </c>
       <c r="Q155" s="25"/>
       <c r="R155" s="25">
-        <f>SUM(O155:Q155)</f>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="S155" s="24">
@@ -24066,7 +24065,7 @@
         <v>0</v>
       </c>
       <c r="R156" s="23">
-        <f>SUM(O156:Q156)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="S156" s="22">
@@ -24129,7 +24128,7 @@
         <v>0</v>
       </c>
       <c r="R157" s="25">
-        <f>SUM(O157:Q157)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="S157" s="24">
@@ -24192,7 +24191,7 @@
         <v>0</v>
       </c>
       <c r="R158" s="23">
-        <f>SUM(O158:Q158)</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="S158" s="22">
@@ -24255,7 +24254,7 @@
         <v>78</v>
       </c>
       <c r="R159" s="25">
-        <f>SUM(O159:Q159)</f>
+        <f t="shared" si="2"/>
         <v>117</v>
       </c>
       <c r="S159" s="24">
@@ -24318,7 +24317,7 @@
         <v>0</v>
       </c>
       <c r="R160" s="23">
-        <f>SUM(O160:Q160)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="S160" s="22">
@@ -24382,7 +24381,7 @@
         <v>0</v>
       </c>
       <c r="R161" s="25">
-        <f>SUM(O161:Q161)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="S161" s="24">
@@ -24445,7 +24444,7 @@
         <v>0</v>
       </c>
       <c r="R162" s="23">
-        <f>SUM(O162:Q162)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="S162" s="22">
@@ -24508,7 +24507,7 @@
         <v>0</v>
       </c>
       <c r="R163" s="25">
-        <f>SUM(O163:Q163)</f>
+        <f t="shared" si="2"/>
         <v>59</v>
       </c>
       <c r="S163" s="24">
@@ -24571,7 +24570,7 @@
         <v>0</v>
       </c>
       <c r="R164" s="23">
-        <f>SUM(O164:Q164)</f>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="S164" s="22">
@@ -24634,7 +24633,7 @@
         <v>0</v>
       </c>
       <c r="R165" s="25">
-        <f>SUM(O165:Q165)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="S165" s="24">
@@ -24697,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="R166" s="23">
-        <f>SUM(O166:Q166)</f>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="S166" s="22">
@@ -24760,7 +24759,7 @@
         <v>0</v>
       </c>
       <c r="R167" s="25">
-        <f>SUM(O167:Q167)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="S167" s="24">
@@ -24823,7 +24822,7 @@
         <v>0</v>
       </c>
       <c r="R168" s="23">
-        <f>SUM(O168:Q168)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="S168" s="22">
@@ -24886,7 +24885,7 @@
         <v>0</v>
       </c>
       <c r="R169" s="25">
-        <f>SUM(O169:Q169)</f>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="S169" s="24">
@@ -24949,7 +24948,7 @@
         <v>0</v>
       </c>
       <c r="R170" s="23">
-        <f>SUM(O170:Q170)</f>
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="S170" s="22">
@@ -25012,7 +25011,7 @@
         <v>0</v>
       </c>
       <c r="R171" s="25">
-        <f>SUM(O171:Q171)</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="S171" s="24">
@@ -25075,7 +25074,7 @@
         <v>0</v>
       </c>
       <c r="R172" s="23">
-        <f>SUM(O172:Q172)</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="S172" s="22">
@@ -25138,7 +25137,7 @@
         <v>0</v>
       </c>
       <c r="R173" s="25">
-        <f>SUM(O173:Q173)</f>
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
       <c r="S173" s="24">
@@ -25201,7 +25200,7 @@
         <v>0</v>
       </c>
       <c r="R174" s="23">
-        <f>SUM(O174:Q174)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="S174" s="22">
@@ -25264,7 +25263,7 @@
         <v>0</v>
       </c>
       <c r="R175" s="25">
-        <f>SUM(O175:Q175)</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="S175" s="24">
@@ -25327,7 +25326,7 @@
         <v>97</v>
       </c>
       <c r="R176" s="23">
-        <f>SUM(O176:Q176)</f>
+        <f t="shared" si="2"/>
         <v>119</v>
       </c>
       <c r="S176" s="22">
@@ -25391,7 +25390,7 @@
         <v>0</v>
       </c>
       <c r="R177" s="25">
-        <f>SUM(O177:Q177)</f>
+        <f t="shared" si="2"/>
         <v>122</v>
       </c>
       <c r="S177" s="24">
@@ -25455,7 +25454,7 @@
         <v>0</v>
       </c>
       <c r="R178" s="23">
-        <f>SUM(O178:Q178)</f>
+        <f t="shared" si="2"/>
         <v>116</v>
       </c>
       <c r="S178" s="22">
@@ -25519,7 +25518,7 @@
         <v>0</v>
       </c>
       <c r="R179" s="25">
-        <f>SUM(O179:Q179)</f>
+        <f t="shared" si="2"/>
         <v>83</v>
       </c>
       <c r="S179" s="24">
@@ -25582,7 +25581,7 @@
         <v>0</v>
       </c>
       <c r="R180" s="23">
-        <f>SUM(O180:Q180)</f>
+        <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="S180" s="22">
@@ -25645,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="R181" s="25">
-        <f>SUM(O181:Q181)</f>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="S181" s="24">
@@ -25708,7 +25707,7 @@
         <v>0</v>
       </c>
       <c r="R182" s="23">
-        <f>SUM(O182:Q182)</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="S182" s="22">
@@ -25771,7 +25770,7 @@
         <v>73</v>
       </c>
       <c r="R183" s="25">
-        <f>SUM(O183:Q183)</f>
+        <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="S183" s="24">
@@ -25834,7 +25833,7 @@
         <v>0</v>
       </c>
       <c r="R184" s="23">
-        <f>SUM(O184:Q184)</f>
+        <f t="shared" si="2"/>
         <v>94</v>
       </c>
       <c r="S184" s="22">
@@ -25897,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="R185" s="25">
-        <f>SUM(O185:Q185)</f>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="S185" s="24">
@@ -25960,7 +25959,7 @@
         <v>0</v>
       </c>
       <c r="R186" s="23">
-        <f>SUM(O186:Q186)</f>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="S186" s="22">
@@ -26023,7 +26022,7 @@
         <v>0</v>
       </c>
       <c r="R187" s="25">
-        <f>SUM(O187:Q187)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="S187" s="24">
@@ -26087,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="R188" s="23">
-        <f>SUM(O188:Q188)</f>
+        <f t="shared" si="2"/>
         <v>590</v>
       </c>
       <c r="S188" s="22">
@@ -26151,7 +26150,7 @@
         <v>0</v>
       </c>
       <c r="R189" s="25">
-        <f>SUM(O189:Q189)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="S189" s="24">
@@ -26214,7 +26213,7 @@
         <v>0</v>
       </c>
       <c r="R190" s="23">
-        <f>SUM(O190:Q190)</f>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="S190" s="22">
@@ -26278,7 +26277,7 @@
         <v>36</v>
       </c>
       <c r="R191" s="25">
-        <f>SUM(O191:Q191)</f>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="S191" s="24">
@@ -26341,7 +26340,7 @@
         <v>0</v>
       </c>
       <c r="R192" s="23">
-        <f>SUM(O192:Q192)</f>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="S192" s="22">
@@ -26404,7 +26403,7 @@
         <v>0</v>
       </c>
       <c r="R193" s="25">
-        <f>SUM(O193:Q193)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="S193" s="24">
@@ -26467,7 +26466,7 @@
         <v>0</v>
       </c>
       <c r="R194" s="23">
-        <f>SUM(O194:Q194)</f>
+        <f t="shared" ref="R194:R257" si="3">SUM(O194:Q194)</f>
         <v>20</v>
       </c>
       <c r="S194" s="22">
@@ -26530,7 +26529,7 @@
         <v>0</v>
       </c>
       <c r="R195" s="25">
-        <f>SUM(O195:Q195)</f>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="S195" s="24">
@@ -26593,7 +26592,7 @@
         <v>0</v>
       </c>
       <c r="R196" s="23">
-        <f>SUM(O196:Q196)</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="S196" s="22">
@@ -26656,7 +26655,7 @@
         <v>0</v>
       </c>
       <c r="R197" s="25">
-        <f>SUM(O197:Q197)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S197" s="24">
@@ -26719,7 +26718,7 @@
         <v>0</v>
       </c>
       <c r="R198" s="23">
-        <f>SUM(O198:Q198)</f>
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="S198" s="22">
@@ -26782,7 +26781,7 @@
         <v>0</v>
       </c>
       <c r="R199" s="25">
-        <f>SUM(O199:Q199)</f>
+        <f t="shared" si="3"/>
         <v>98</v>
       </c>
       <c r="S199" s="24">
@@ -26845,7 +26844,7 @@
         <v>44</v>
       </c>
       <c r="R200" s="23">
-        <f>SUM(O200:Q200)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="S200" s="22">
@@ -26908,7 +26907,7 @@
         <v>0</v>
       </c>
       <c r="R201" s="25">
-        <f>SUM(O201:Q201)</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S201" s="24">
@@ -26971,7 +26970,7 @@
         <v>0</v>
       </c>
       <c r="R202" s="23">
-        <f>SUM(O202:Q202)</f>
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
       <c r="S202" s="22">
@@ -27034,7 +27033,7 @@
         <v>0</v>
       </c>
       <c r="R203" s="25">
-        <f>SUM(O203:Q203)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="S203" s="24">
@@ -27097,7 +27096,7 @@
         <v>59</v>
       </c>
       <c r="R204" s="23">
-        <f>SUM(O204:Q204)</f>
+        <f t="shared" si="3"/>
         <v>59</v>
       </c>
       <c r="S204" s="22">
@@ -27160,7 +27159,7 @@
         <v>0</v>
       </c>
       <c r="R205" s="25">
-        <f>SUM(O205:Q205)</f>
+        <f t="shared" si="3"/>
         <v>76</v>
       </c>
       <c r="S205" s="24">
@@ -27223,7 +27222,7 @@
         <v>0</v>
       </c>
       <c r="R206" s="23">
-        <f>SUM(O206:Q206)</f>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
       <c r="S206" s="22">
@@ -27286,7 +27285,7 @@
         <v>0</v>
       </c>
       <c r="R207" s="25">
-        <f>SUM(O207:Q207)</f>
+        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="S207" s="24">
@@ -27349,7 +27348,7 @@
         <v>37</v>
       </c>
       <c r="R208" s="23">
-        <f>SUM(O208:Q208)</f>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="S208" s="22">
@@ -27412,7 +27411,7 @@
         <v>0</v>
       </c>
       <c r="R209" s="25">
-        <f>SUM(O209:Q209)</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S209" s="24">
@@ -27475,7 +27474,7 @@
         <v>0</v>
       </c>
       <c r="R210" s="23">
-        <f>SUM(O210:Q210)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S210" s="22">
@@ -27538,7 +27537,7 @@
         <v>0</v>
       </c>
       <c r="R211" s="25">
-        <f>SUM(O211:Q211)</f>
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
       <c r="S211" s="24">
@@ -27601,7 +27600,7 @@
         <v>0</v>
       </c>
       <c r="R212" s="23">
-        <f>SUM(O212:Q212)</f>
+        <f t="shared" si="3"/>
         <v>105</v>
       </c>
       <c r="S212" s="22">
@@ -27664,7 +27663,7 @@
         <v>147</v>
       </c>
       <c r="R213" s="25">
-        <f>SUM(O213:Q213)</f>
+        <f t="shared" si="3"/>
         <v>635</v>
       </c>
       <c r="S213" s="24">
@@ -27727,7 +27726,7 @@
         <v>0</v>
       </c>
       <c r="R214" s="23">
-        <f>SUM(O214:Q214)</f>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="S214" s="22">
@@ -27790,7 +27789,7 @@
         <v>0</v>
       </c>
       <c r="R215" s="25">
-        <f>SUM(O215:Q215)</f>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="S215" s="24">
@@ -27853,7 +27852,7 @@
         <v>0</v>
       </c>
       <c r="R216" s="23">
-        <f>SUM(O216:Q216)</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="S216" s="22">
@@ -27916,7 +27915,7 @@
         <v>0</v>
       </c>
       <c r="R217" s="25">
-        <f>SUM(O217:Q217)</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="S217" s="24">
@@ -27979,7 +27978,7 @@
         <v>0</v>
       </c>
       <c r="R218" s="23">
-        <f>SUM(O218:Q218)</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="S218" s="22">
@@ -28043,7 +28042,7 @@
         <v>59</v>
       </c>
       <c r="R219" s="25">
-        <f>SUM(O219:Q219)</f>
+        <f t="shared" si="3"/>
         <v>59</v>
       </c>
       <c r="S219" s="24">
@@ -28106,7 +28105,7 @@
         <v>0</v>
       </c>
       <c r="R220" s="23">
-        <f>SUM(O220:Q220)</f>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="S220" s="22">
@@ -28169,7 +28168,7 @@
         <v>30</v>
       </c>
       <c r="R221" s="25">
-        <f>SUM(O221:Q221)</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="S221" s="24">
@@ -28232,7 +28231,7 @@
         <v>0</v>
       </c>
       <c r="R222" s="23">
-        <f>SUM(O222:Q222)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S222" s="22">
@@ -28295,7 +28294,7 @@
         <v>1</v>
       </c>
       <c r="R223" s="25">
-        <f>SUM(O223:Q223)</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="S223" s="24">
@@ -28358,7 +28357,7 @@
         <v>0</v>
       </c>
       <c r="R224" s="23">
-        <f>SUM(O224:Q224)</f>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="S224" s="22">
@@ -28421,7 +28420,7 @@
         <v>0</v>
       </c>
       <c r="R225" s="25">
-        <f>SUM(O225:Q225)</f>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="S225" s="24">
@@ -28484,7 +28483,7 @@
         <v>0</v>
       </c>
       <c r="R226" s="23">
-        <f>SUM(O226:Q226)</f>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="S226" s="22">
@@ -28547,7 +28546,7 @@
         <v>0</v>
       </c>
       <c r="R227" s="25">
-        <f>SUM(O227:Q227)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S227" s="24">
@@ -28610,7 +28609,7 @@
         <v>0</v>
       </c>
       <c r="R228" s="23">
-        <f>SUM(O228:Q228)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="S228" s="22">
@@ -28673,7 +28672,7 @@
         <v>0</v>
       </c>
       <c r="R229" s="25">
-        <f>SUM(O229:Q229)</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="S229" s="24">
@@ -28736,7 +28735,7 @@
         <v>5</v>
       </c>
       <c r="R230" s="23">
-        <f>SUM(O230:Q230)</f>
+        <f t="shared" si="3"/>
         <v>52</v>
       </c>
       <c r="S230" s="22">
@@ -28799,7 +28798,7 @@
         <v>0</v>
       </c>
       <c r="R231" s="25">
-        <f>SUM(O231:Q231)</f>
+        <f t="shared" si="3"/>
         <v>89</v>
       </c>
       <c r="S231" s="24">
@@ -28862,7 +28861,7 @@
         <v>0</v>
       </c>
       <c r="R232" s="23">
-        <f>SUM(O232:Q232)</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S232" s="22">
@@ -28925,7 +28924,7 @@
         <v>0</v>
       </c>
       <c r="R233" s="25">
-        <f>SUM(O233:Q233)</f>
+        <f t="shared" si="3"/>
         <v>38</v>
       </c>
       <c r="S233" s="24">
@@ -28988,7 +28987,7 @@
         <v>0</v>
       </c>
       <c r="R234" s="23">
-        <f>SUM(O234:Q234)</f>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="S234" s="22">
@@ -29051,7 +29050,7 @@
         <v>0</v>
       </c>
       <c r="R235" s="25">
-        <f>SUM(O235:Q235)</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="S235" s="24">
@@ -29114,7 +29113,7 @@
         <v>0</v>
       </c>
       <c r="R236" s="23">
-        <f>SUM(O236:Q236)</f>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="S236" s="22">
@@ -29177,7 +29176,7 @@
         <v>0</v>
       </c>
       <c r="R237" s="25">
-        <f>SUM(O237:Q237)</f>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="S237" s="24">
@@ -29240,7 +29239,7 @@
         <v>0</v>
       </c>
       <c r="R238" s="23">
-        <f>SUM(O238:Q238)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="S238" s="22">
@@ -29303,7 +29302,7 @@
         <v>51</v>
       </c>
       <c r="R239" s="25">
-        <f>SUM(O239:Q239)</f>
+        <f t="shared" si="3"/>
         <v>51</v>
       </c>
       <c r="S239" s="24">
@@ -29367,7 +29366,7 @@
         <v>31</v>
       </c>
       <c r="R240" s="23">
-        <f>SUM(O240:Q240)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="S240" s="22">
@@ -29430,7 +29429,7 @@
         <v>0</v>
       </c>
       <c r="R241" s="25">
-        <f>SUM(O241:Q241)</f>
+        <f t="shared" si="3"/>
         <v>140</v>
       </c>
       <c r="S241" s="24">
@@ -29493,7 +29492,7 @@
         <v>0</v>
       </c>
       <c r="R242" s="23">
-        <f>SUM(O242:Q242)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="S242" s="22">
@@ -29556,7 +29555,7 @@
         <v>0</v>
       </c>
       <c r="R243" s="25">
-        <f>SUM(O243:Q243)</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="S243" s="24">
@@ -29619,7 +29618,7 @@
         <v>0</v>
       </c>
       <c r="R244" s="23">
-        <f>SUM(O244:Q244)</f>
+        <f t="shared" si="3"/>
         <v>55</v>
       </c>
       <c r="S244" s="22">
@@ -29682,7 +29681,7 @@
         <v>120</v>
       </c>
       <c r="R245" s="25">
-        <f>SUM(O245:Q245)</f>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="S245" s="24">
@@ -29745,7 +29744,7 @@
         <v>22</v>
       </c>
       <c r="R246" s="23">
-        <f>SUM(O246:Q246)</f>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="S246" s="22">
@@ -29808,7 +29807,7 @@
         <v>0</v>
       </c>
       <c r="R247" s="25">
-        <f>SUM(O247:Q247)</f>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="S247" s="24">
@@ -29871,7 +29870,7 @@
         <v>0</v>
       </c>
       <c r="R248" s="23">
-        <f>SUM(O248:Q248)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="S248" s="22">
@@ -29934,7 +29933,7 @@
         <v>0</v>
       </c>
       <c r="R249" s="25">
-        <f>SUM(O249:Q249)</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="S249" s="24">
@@ -29997,7 +29996,7 @@
         <v>0</v>
       </c>
       <c r="R250" s="23">
-        <f>SUM(O250:Q250)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="S250" s="22">
@@ -30060,7 +30059,7 @@
         <v>56</v>
       </c>
       <c r="R251" s="25">
-        <f>SUM(O251:Q251)</f>
+        <f t="shared" si="3"/>
         <v>56</v>
       </c>
       <c r="S251" s="24">
@@ -30124,7 +30123,7 @@
         <v>0</v>
       </c>
       <c r="R252" s="23">
-        <f>SUM(O252:Q252)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="S252" s="22">
@@ -30187,7 +30186,7 @@
         <v>0</v>
       </c>
       <c r="R253" s="25">
-        <f>SUM(O253:Q253)</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="S253" s="24">
@@ -30250,7 +30249,7 @@
         <v>0</v>
       </c>
       <c r="R254" s="23">
-        <f>SUM(O254:Q254)</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="S254" s="22">
@@ -30311,7 +30310,7 @@
         <v>0</v>
       </c>
       <c r="R255" s="25">
-        <f>SUM(O255:Q255)</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S255" s="24">
@@ -30374,7 +30373,7 @@
         <v>49</v>
       </c>
       <c r="R256" s="23">
-        <f>SUM(O256:Q256)</f>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="S256" s="22">
@@ -30437,7 +30436,7 @@
         <v>0</v>
       </c>
       <c r="R257" s="25">
-        <f>SUM(O257:Q257)</f>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="S257" s="24">
@@ -30500,7 +30499,7 @@
         <v>7</v>
       </c>
       <c r="R258" s="23">
-        <f>SUM(O258:Q258)</f>
+        <f t="shared" ref="R258:R321" si="4">SUM(O258:Q258)</f>
         <v>22</v>
       </c>
       <c r="S258" s="22">
@@ -30563,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R259" s="25">
-        <f>SUM(O259:Q259)</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="S259" s="24">
@@ -30626,7 +30625,7 @@
         <v>31</v>
       </c>
       <c r="R260" s="23">
-        <f>SUM(O260:Q260)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="S260" s="22">
@@ -30689,7 +30688,7 @@
         <v>0</v>
       </c>
       <c r="R261" s="25">
-        <f>SUM(O261:Q261)</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="S261" s="24">
@@ -30752,7 +30751,7 @@
         <v>0</v>
       </c>
       <c r="R262" s="23">
-        <f>SUM(O262:Q262)</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="S262" s="22">
@@ -30815,7 +30814,7 @@
         <v>0</v>
       </c>
       <c r="R263" s="25">
-        <f>SUM(O263:Q263)</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="S263" s="24">
@@ -30878,7 +30877,7 @@
         <v>29</v>
       </c>
       <c r="R264" s="23">
-        <f>SUM(O264:Q264)</f>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="S264" s="22">
@@ -30941,7 +30940,7 @@
         <v>21</v>
       </c>
       <c r="R265" s="25">
-        <f>SUM(O265:Q265)</f>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="S265" s="24">
@@ -31004,7 +31003,7 @@
         <v>0</v>
       </c>
       <c r="R266" s="23">
-        <f>SUM(O266:Q266)</f>
+        <f t="shared" si="4"/>
         <v>66</v>
       </c>
       <c r="S266" s="22">
@@ -31067,7 +31066,7 @@
         <v>20</v>
       </c>
       <c r="R267" s="25">
-        <f>SUM(O267:Q267)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S267" s="24">
@@ -31130,7 +31129,7 @@
         <v>0</v>
       </c>
       <c r="R268" s="23">
-        <f>SUM(O268:Q268)</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="S268" s="22">
@@ -31193,7 +31192,7 @@
         <v>0</v>
       </c>
       <c r="R269" s="25">
-        <f>SUM(O269:Q269)</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="S269" s="24">
@@ -31256,7 +31255,7 @@
         <v>0</v>
       </c>
       <c r="R270" s="23">
-        <f>SUM(O270:Q270)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="S270" s="22">
@@ -31319,7 +31318,7 @@
         <v>0</v>
       </c>
       <c r="R271" s="25">
-        <f>SUM(O271:Q271)</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="S271" s="24">
@@ -31382,7 +31381,7 @@
         <v>0</v>
       </c>
       <c r="R272" s="23">
-        <f>SUM(O272:Q272)</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="S272" s="22">
@@ -31445,7 +31444,7 @@
         <v>0</v>
       </c>
       <c r="R273" s="25">
-        <f>SUM(O273:Q273)</f>
+        <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="S273" s="24">
@@ -31508,7 +31507,7 @@
         <v>0</v>
       </c>
       <c r="R274" s="23">
-        <f>SUM(O274:Q274)</f>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="S274" s="22">
@@ -31571,7 +31570,7 @@
         <v>0</v>
       </c>
       <c r="R275" s="25">
-        <f>SUM(O275:Q275)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S275" s="24">
@@ -31634,7 +31633,7 @@
         <v>39</v>
       </c>
       <c r="R276" s="23">
-        <f>SUM(O276:Q276)</f>
+        <f t="shared" si="4"/>
         <v>39</v>
       </c>
       <c r="S276" s="22">
@@ -31697,7 +31696,7 @@
         <v>0</v>
       </c>
       <c r="R277" s="25">
-        <f>SUM(O277:Q277)</f>
+        <f t="shared" si="4"/>
         <v>39</v>
       </c>
       <c r="S277" s="24">
@@ -31760,7 +31759,7 @@
         <v>0</v>
       </c>
       <c r="R278" s="23">
-        <f>SUM(O278:Q278)</f>
+        <f t="shared" si="4"/>
         <v>277</v>
       </c>
       <c r="S278" s="22">
@@ -31823,7 +31822,7 @@
         <v>0</v>
       </c>
       <c r="R279" s="25">
-        <f>SUM(O279:Q279)</f>
+        <f t="shared" si="4"/>
         <v>43</v>
       </c>
       <c r="S279" s="24">
@@ -31886,7 +31885,7 @@
         <v>0</v>
       </c>
       <c r="R280" s="23">
-        <f>SUM(O280:Q280)</f>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="S280" s="22">
@@ -31949,7 +31948,7 @@
         <v>84</v>
       </c>
       <c r="R281" s="25">
-        <f>SUM(O281:Q281)</f>
+        <f t="shared" si="4"/>
         <v>144</v>
       </c>
       <c r="S281" s="24">
@@ -32012,7 +32011,7 @@
         <v>0</v>
       </c>
       <c r="R282" s="23">
-        <f>SUM(O282:Q282)</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="S282" s="22">
@@ -32075,7 +32074,7 @@
         <v>64</v>
       </c>
       <c r="R283" s="25">
-        <f>SUM(O283:Q283)</f>
+        <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="S283" s="24">
@@ -32138,7 +32137,7 @@
         <v>0</v>
       </c>
       <c r="R284" s="23">
-        <f>SUM(O284:Q284)</f>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="S284" s="22">
@@ -32201,7 +32200,7 @@
         <v>193</v>
       </c>
       <c r="R285" s="25">
-        <f>SUM(O285:Q285)</f>
+        <f t="shared" si="4"/>
         <v>193</v>
       </c>
       <c r="S285" s="24">
@@ -32264,7 +32263,7 @@
         <v>0</v>
       </c>
       <c r="R286" s="23">
-        <f>SUM(O286:Q286)</f>
+        <f t="shared" si="4"/>
         <v>46</v>
       </c>
       <c r="S286" s="22">
@@ -32327,7 +32326,7 @@
         <v>20</v>
       </c>
       <c r="R287" s="25">
-        <f>SUM(O287:Q287)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S287" s="24">
@@ -32388,7 +32387,7 @@
         <v>0</v>
       </c>
       <c r="R288" s="23">
-        <f>SUM(O288:Q288)</f>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="S288" s="22">
@@ -32449,7 +32448,7 @@
         <v>0</v>
       </c>
       <c r="R289" s="25">
-        <f>SUM(O289:Q289)</f>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="S289" s="24">
@@ -32512,7 +32511,7 @@
         <v>0</v>
       </c>
       <c r="R290" s="23">
-        <f>SUM(O290:Q290)</f>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="S290" s="22">
@@ -32575,7 +32574,7 @@
         <v>0</v>
       </c>
       <c r="R291" s="25">
-        <f>SUM(O291:Q291)</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="S291" s="24">
@@ -32638,7 +32637,7 @@
         <v>35</v>
       </c>
       <c r="R292" s="23">
-        <f>SUM(O292:Q292)</f>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="S292" s="22">
@@ -32701,7 +32700,7 @@
         <v>0</v>
       </c>
       <c r="R293" s="25">
-        <f>SUM(O293:Q293)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S293" s="24">
@@ -32764,7 +32763,7 @@
         <v>0</v>
       </c>
       <c r="R294" s="23">
-        <f>SUM(O294:Q294)</f>
+        <f t="shared" si="4"/>
         <v>188</v>
       </c>
       <c r="S294" s="22">
@@ -32827,7 +32826,7 @@
         <v>0</v>
       </c>
       <c r="R295" s="25">
-        <f>SUM(O295:Q295)</f>
+        <f t="shared" si="4"/>
         <v>42</v>
       </c>
       <c r="S295" s="24">
@@ -32890,7 +32889,7 @@
         <v>0</v>
       </c>
       <c r="R296" s="23">
-        <f>SUM(O296:Q296)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="S296" s="22">
@@ -32954,7 +32953,7 @@
         <v>0</v>
       </c>
       <c r="R297" s="25">
-        <f>SUM(O297:Q297)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S297" s="24">
@@ -33015,7 +33014,7 @@
         <v>0</v>
       </c>
       <c r="R298" s="23">
-        <f>SUM(O298:Q298)</f>
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="S298" s="22">
@@ -33078,7 +33077,7 @@
         <v>52</v>
       </c>
       <c r="R299" s="25">
-        <f>SUM(O299:Q299)</f>
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
       <c r="S299" s="24">
@@ -33141,7 +33140,7 @@
         <v>54</v>
       </c>
       <c r="R300" s="23">
-        <f>SUM(O300:Q300)</f>
+        <f t="shared" si="4"/>
         <v>54</v>
       </c>
       <c r="S300" s="22">
@@ -33204,7 +33203,7 @@
         <v>130</v>
       </c>
       <c r="R301" s="25">
-        <f>SUM(O301:Q301)</f>
+        <f t="shared" si="4"/>
         <v>153</v>
       </c>
       <c r="S301" s="24">
@@ -33267,7 +33266,7 @@
         <v>0</v>
       </c>
       <c r="R302" s="23">
-        <f>SUM(O302:Q302)</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="S302" s="22">
@@ -33330,7 +33329,7 @@
         <v>0</v>
       </c>
       <c r="R303" s="25">
-        <f>SUM(O303:Q303)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S303" s="24">
@@ -33387,7 +33386,7 @@
       <c r="P304" s="23"/>
       <c r="Q304" s="23"/>
       <c r="R304" s="23">
-        <f>SUM(O304:Q304)</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="S304" s="22">
@@ -33450,7 +33449,7 @@
         <v>0</v>
       </c>
       <c r="R305" s="25">
-        <f>SUM(O305:Q305)</f>
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="S305" s="24">
@@ -33513,7 +33512,7 @@
         <v>0</v>
       </c>
       <c r="R306" s="23">
-        <f>SUM(O306:Q306)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="S306" s="22">
@@ -33574,7 +33573,7 @@
         <v>1</v>
       </c>
       <c r="R307" s="25">
-        <f>SUM(O307:Q307)</f>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="S307" s="24">
@@ -33638,7 +33637,7 @@
         <v>0</v>
       </c>
       <c r="R308" s="23">
-        <f>SUM(O308:Q308)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="S308" s="22">
@@ -33701,7 +33700,7 @@
         <v>0</v>
       </c>
       <c r="R309" s="25">
-        <f>SUM(O309:Q309)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="S309" s="24">
@@ -33764,7 +33763,7 @@
         <v>1</v>
       </c>
       <c r="R310" s="23">
-        <f>SUM(O310:Q310)</f>
+        <f t="shared" si="4"/>
         <v>45</v>
       </c>
       <c r="S310" s="22">
@@ -33827,7 +33826,7 @@
         <v>0</v>
       </c>
       <c r="R311" s="25">
-        <f>SUM(O311:Q311)</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="S311" s="24">
@@ -33891,7 +33890,7 @@
         <v>0</v>
       </c>
       <c r="R312" s="23">
-        <f>SUM(O312:Q312)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="S312" s="22">
@@ -33954,7 +33953,7 @@
         <v>0</v>
       </c>
       <c r="R313" s="25">
-        <f>SUM(O313:Q313)</f>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="S313" s="24">
@@ -34018,7 +34017,7 @@
         <v>0</v>
       </c>
       <c r="R314" s="23">
-        <f>SUM(O314:Q314)</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="S314" s="22">
@@ -34081,7 +34080,7 @@
         <v>33</v>
       </c>
       <c r="R315" s="25">
-        <f>SUM(O315:Q315)</f>
+        <f t="shared" si="4"/>
         <v>33</v>
       </c>
       <c r="S315" s="24">
@@ -34144,7 +34143,7 @@
         <v>0</v>
       </c>
       <c r="R316" s="23">
-        <f>SUM(O316:Q316)</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="S316" s="22">
@@ -34207,7 +34206,7 @@
         <v>0</v>
       </c>
       <c r="R317" s="25">
-        <f>SUM(O317:Q317)</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="S317" s="24">
@@ -34270,7 +34269,7 @@
         <v>19</v>
       </c>
       <c r="R318" s="23">
-        <f>SUM(O318:Q318)</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="S318" s="22">
@@ -34334,7 +34333,7 @@
         <v>0</v>
       </c>
       <c r="R319" s="25">
-        <f>SUM(O319:Q319)</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S319" s="24">
@@ -34398,7 +34397,7 @@
         <v>0</v>
       </c>
       <c r="R320" s="23">
-        <f>SUM(O320:Q320)</f>
+        <f t="shared" si="4"/>
         <v>49</v>
       </c>
       <c r="S320" s="22">
@@ -34462,7 +34461,7 @@
         <v>0</v>
       </c>
       <c r="R321" s="25">
-        <f>SUM(O321:Q321)</f>
+        <f t="shared" si="4"/>
         <v>126</v>
       </c>
       <c r="S321" s="24">
@@ -34525,7 +34524,7 @@
         <v>40</v>
       </c>
       <c r="R322" s="23">
-        <f>SUM(O322:Q322)</f>
+        <f t="shared" ref="R322:R385" si="5">SUM(O322:Q322)</f>
         <v>40</v>
       </c>
       <c r="S322" s="22">
@@ -34588,7 +34587,7 @@
         <v>40</v>
       </c>
       <c r="R323" s="25">
-        <f>SUM(O323:Q323)</f>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="S323" s="24">
@@ -34651,7 +34650,7 @@
         <v>60</v>
       </c>
       <c r="R324" s="23">
-        <f>SUM(O324:Q324)</f>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="S324" s="22">
@@ -34714,7 +34713,7 @@
         <v>30</v>
       </c>
       <c r="R325" s="25">
-        <f>SUM(O325:Q325)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="S325" s="24">
@@ -34777,7 +34776,7 @@
         <v>0</v>
       </c>
       <c r="R326" s="23">
-        <f>SUM(O326:Q326)</f>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="S326" s="22">
@@ -34840,7 +34839,7 @@
         <v>0</v>
       </c>
       <c r="R327" s="25">
-        <f>SUM(O327:Q327)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="S327" s="24">
@@ -34903,7 +34902,7 @@
         <v>39</v>
       </c>
       <c r="R328" s="23">
-        <f>SUM(O328:Q328)</f>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="S328" s="22">
@@ -34966,7 +34965,7 @@
         <v>0</v>
       </c>
       <c r="R329" s="25">
-        <f>SUM(O329:Q329)</f>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="S329" s="24">
@@ -35029,7 +35028,7 @@
         <v>0</v>
       </c>
       <c r="R330" s="23">
-        <f>SUM(O330:Q330)</f>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="S330" s="22">
@@ -35092,7 +35091,7 @@
         <v>0</v>
       </c>
       <c r="R331" s="25">
-        <f>SUM(O331:Q331)</f>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="S331" s="24">
@@ -35155,7 +35154,7 @@
         <v>0</v>
       </c>
       <c r="R332" s="23">
-        <f>SUM(O332:Q332)</f>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="S332" s="22">
@@ -35218,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="R333" s="25">
-        <f>SUM(O333:Q333)</f>
+        <f t="shared" si="5"/>
         <v>207</v>
       </c>
       <c r="S333" s="24">
@@ -35281,7 +35280,7 @@
         <v>0</v>
       </c>
       <c r="R334" s="23">
-        <f>SUM(O334:Q334)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="S334" s="22">
@@ -35344,7 +35343,7 @@
         <v>0</v>
       </c>
       <c r="R335" s="25">
-        <f>SUM(O335:Q335)</f>
+        <f t="shared" si="5"/>
         <v>184</v>
       </c>
       <c r="S335" s="24">
@@ -35407,7 +35406,7 @@
         <v>0</v>
       </c>
       <c r="R336" s="23">
-        <f>SUM(O336:Q336)</f>
+        <f t="shared" si="5"/>
         <v>46</v>
       </c>
       <c r="S336" s="22">
@@ -35470,7 +35469,7 @@
         <v>16</v>
       </c>
       <c r="R337" s="25">
-        <f>SUM(O337:Q337)</f>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="S337" s="24">
@@ -35533,7 +35532,7 @@
         <v>45</v>
       </c>
       <c r="R338" s="23">
-        <f>SUM(O338:Q338)</f>
+        <f t="shared" si="5"/>
         <v>48</v>
       </c>
       <c r="S338" s="22">
@@ -35588,7 +35587,7 @@
         <v>40</v>
       </c>
       <c r="R339" s="25">
-        <f>SUM(O339:Q339)</f>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="S339" s="24">
@@ -35647,7 +35646,7 @@
         <v>0</v>
       </c>
       <c r="R340" s="23">
-        <f>SUM(O340:Q340)</f>
+        <f t="shared" si="5"/>
         <v>150</v>
       </c>
       <c r="S340" s="22">
@@ -35710,7 +35709,7 @@
         <v>0</v>
       </c>
       <c r="R341" s="25">
-        <f>SUM(O341:Q341)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="S341" s="24">
@@ -35765,7 +35764,7 @@
         <v>30</v>
       </c>
       <c r="R342" s="23">
-        <f>SUM(O342:Q342)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="S342" s="22">
@@ -35829,7 +35828,7 @@
         <v>0</v>
       </c>
       <c r="R343" s="25">
-        <f>SUM(O343:Q343)</f>
+        <f t="shared" si="5"/>
         <v>67</v>
       </c>
       <c r="S343" s="24">
@@ -35892,7 +35891,7 @@
         <v>0</v>
       </c>
       <c r="R344" s="23">
-        <f>SUM(O344:Q344)</f>
+        <f t="shared" si="5"/>
         <v>67</v>
       </c>
       <c r="S344" s="22">
@@ -35955,7 +35954,7 @@
         <v>0</v>
       </c>
       <c r="R345" s="25">
-        <f>SUM(O345:Q345)</f>
+        <f t="shared" si="5"/>
         <v>57</v>
       </c>
       <c r="S345" s="24">
@@ -36018,7 +36017,7 @@
         <v>0</v>
       </c>
       <c r="R346" s="23">
-        <f>SUM(O346:Q346)</f>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="S346" s="22">
@@ -36081,7 +36080,7 @@
         <v>0</v>
       </c>
       <c r="R347" s="25">
-        <f>SUM(O347:Q347)</f>
+        <f t="shared" si="5"/>
         <v>315</v>
       </c>
       <c r="S347" s="24">
@@ -36144,7 +36143,7 @@
         <v>0</v>
       </c>
       <c r="R348" s="23">
-        <f>SUM(O348:Q348)</f>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="S348" s="22">
@@ -36207,7 +36206,7 @@
         <v>0</v>
       </c>
       <c r="R349" s="25">
-        <f>SUM(O349:Q349)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="S349" s="24">
@@ -36271,7 +36270,7 @@
         <v>0</v>
       </c>
       <c r="R350" s="23">
-        <f>SUM(O350:Q350)</f>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="S350" s="22">
@@ -36334,7 +36333,7 @@
         <v>0</v>
       </c>
       <c r="R351" s="25">
-        <f>SUM(O351:Q351)</f>
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
       <c r="S351" s="24">
@@ -36397,7 +36396,7 @@
         <v>0</v>
       </c>
       <c r="R352" s="23">
-        <f>SUM(O352:Q352)</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="S352" s="22">
@@ -36460,7 +36459,7 @@
         <v>0</v>
       </c>
       <c r="R353" s="25">
-        <f>SUM(O353:Q353)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="S353" s="24">
@@ -36523,7 +36522,7 @@
         <v>0</v>
       </c>
       <c r="R354" s="23">
-        <f>SUM(O354:Q354)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="S354" s="22">
@@ -36586,7 +36585,7 @@
         <v>0</v>
       </c>
       <c r="R355" s="25">
-        <f>SUM(O355:Q355)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="S355" s="24">
@@ -36649,7 +36648,7 @@
         <v>0</v>
       </c>
       <c r="R356" s="23">
-        <f>SUM(O356:Q356)</f>
+        <f t="shared" si="5"/>
         <v>64</v>
       </c>
       <c r="S356" s="22">
@@ -36711,7 +36710,7 @@
         <v>0</v>
       </c>
       <c r="R357" s="25">
-        <f>SUM(O357:Q357)</f>
+        <f t="shared" si="5"/>
         <v>57</v>
       </c>
       <c r="S357" s="24">
@@ -36774,7 +36773,7 @@
         <v>0</v>
       </c>
       <c r="R358" s="23">
-        <f>SUM(O358:Q358)</f>
+        <f t="shared" si="5"/>
         <v>39</v>
       </c>
       <c r="S358" s="22">
@@ -36837,7 +36836,7 @@
         <v>0</v>
       </c>
       <c r="R359" s="25">
-        <f>SUM(O359:Q359)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="S359" s="24">
@@ -36900,7 +36899,7 @@
         <v>0</v>
       </c>
       <c r="R360" s="23">
-        <f>SUM(O360:Q360)</f>
+        <f t="shared" si="5"/>
         <v>47</v>
       </c>
       <c r="S360" s="22">
@@ -36963,7 +36962,7 @@
         <v>2</v>
       </c>
       <c r="R361" s="25">
-        <f>SUM(O361:Q361)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="S361" s="24">
@@ -37026,7 +37025,7 @@
         <v>0</v>
       </c>
       <c r="R362" s="23">
-        <f>SUM(O362:Q362)</f>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="S362" s="22">
@@ -37089,7 +37088,7 @@
         <v>43</v>
       </c>
       <c r="R363" s="25">
-        <f>SUM(O363:Q363)</f>
+        <f t="shared" si="5"/>
         <v>43</v>
       </c>
       <c r="S363" s="24">
@@ -37152,7 +37151,7 @@
         <v>0</v>
       </c>
       <c r="R364" s="23">
-        <f>SUM(O364:Q364)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="S364" s="22">
@@ -37215,7 +37214,7 @@
         <v>0</v>
       </c>
       <c r="R365" s="25">
-        <f>SUM(O365:Q365)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="S365" s="24">
@@ -37279,7 +37278,7 @@
         <v>57</v>
       </c>
       <c r="R366" s="23">
-        <f>SUM(O366:Q366)</f>
+        <f t="shared" si="5"/>
         <v>57</v>
       </c>
       <c r="S366" s="22">
@@ -37343,7 +37342,7 @@
         <v>0</v>
       </c>
       <c r="R367" s="25">
-        <f>SUM(O367:Q367)</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="S367" s="24">
@@ -37406,7 +37405,7 @@
         <v>0</v>
       </c>
       <c r="R368" s="23">
-        <f>SUM(O368:Q368)</f>
+        <f t="shared" si="5"/>
         <v>176</v>
       </c>
       <c r="S368" s="22">
@@ -37467,7 +37466,7 @@
         <v>0</v>
       </c>
       <c r="R369" s="25">
-        <f>SUM(O369:Q369)</f>
+        <f t="shared" si="5"/>
         <v>56</v>
       </c>
       <c r="S369" s="24">
@@ -37531,7 +37530,7 @@
         <v>0</v>
       </c>
       <c r="R370" s="23">
-        <f>SUM(O370:Q370)</f>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="S370" s="22">
@@ -37594,7 +37593,7 @@
         <v>39</v>
       </c>
       <c r="R371" s="25">
-        <f>SUM(O371:Q371)</f>
+        <f t="shared" si="5"/>
         <v>39</v>
       </c>
       <c r="S371" s="24">
@@ -37657,7 +37656,7 @@
         <v>0</v>
       </c>
       <c r="R372" s="23">
-        <f>SUM(O372:Q372)</f>
+        <f t="shared" si="5"/>
         <v>47</v>
       </c>
       <c r="S372" s="22">
@@ -37719,7 +37718,7 @@
         <v>53</v>
       </c>
       <c r="R373" s="25">
-        <f>SUM(O373:Q373)</f>
+        <f t="shared" si="5"/>
         <v>53</v>
       </c>
       <c r="S373" s="24">
@@ -37782,7 +37781,7 @@
         <v>0</v>
       </c>
       <c r="R374" s="23">
-        <f>SUM(O374:Q374)</f>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="S374" s="22">
@@ -37846,7 +37845,7 @@
         <v>0</v>
       </c>
       <c r="R375" s="25">
-        <f>SUM(O375:Q375)</f>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="S375" s="24">
@@ -37910,7 +37909,7 @@
         <v>53</v>
       </c>
       <c r="R376" s="23">
-        <f>SUM(O376:Q376)</f>
+        <f t="shared" si="5"/>
         <v>53</v>
       </c>
       <c r="S376" s="22">
@@ -37974,7 +37973,7 @@
         <v>0</v>
       </c>
       <c r="R377" s="25">
-        <f>SUM(O377:Q377)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="S377" s="24">
@@ -38038,7 +38037,7 @@
         <v>0</v>
       </c>
       <c r="R378" s="23">
-        <f>SUM(O378:Q378)</f>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="S378" s="22">
@@ -38093,7 +38092,7 @@
         <v>0</v>
       </c>
       <c r="R379" s="25">
-        <f>SUM(O379:Q379)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S379" s="24"/>
@@ -38152,7 +38151,7 @@
         <v>0</v>
       </c>
       <c r="R380" s="23">
-        <f>SUM(O380:Q380)</f>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="S380" s="22">
@@ -38207,7 +38206,7 @@
       <c r="P381" s="25"/>
       <c r="Q381" s="25"/>
       <c r="R381" s="25">
-        <f>SUM(O381:Q381)</f>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="S381" s="24">
@@ -38269,7 +38268,7 @@
         <v>17</v>
       </c>
       <c r="R382" s="23">
-        <f>SUM(O382:Q382)</f>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="S382" s="22">
@@ -38333,7 +38332,7 @@
         <v>0</v>
       </c>
       <c r="R383" s="25">
-        <f>SUM(O383:Q383)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="S383" s="24">
@@ -38396,7 +38395,7 @@
         <v>0</v>
       </c>
       <c r="R384" s="23">
-        <f>SUM(O384:Q384)</f>
+        <f t="shared" si="5"/>
         <v>114</v>
       </c>
       <c r="S384" s="22">
@@ -38457,7 +38456,7 @@
         <v>0</v>
       </c>
       <c r="R385" s="25">
-        <f>SUM(O385:Q385)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="S385" s="24">
@@ -38520,7 +38519,7 @@
         <v>0</v>
       </c>
       <c r="R386" s="23">
-        <f>SUM(O386:Q386)</f>
+        <f t="shared" ref="R386:R449" si="6">SUM(O386:Q386)</f>
         <v>49</v>
       </c>
       <c r="S386" s="22">
@@ -38583,7 +38582,7 @@
         <v>0</v>
       </c>
       <c r="R387" s="25">
-        <f>SUM(O387:Q387)</f>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="S387" s="24">
@@ -38646,7 +38645,7 @@
         <v>26</v>
       </c>
       <c r="R388" s="23">
-        <f>SUM(O388:Q388)</f>
+        <f t="shared" si="6"/>
         <v>91</v>
       </c>
       <c r="S388" s="22">
@@ -38710,7 +38709,7 @@
         <v>5</v>
       </c>
       <c r="R389" s="25">
-        <f>SUM(O389:Q389)</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="S389" s="24">
@@ -38773,7 +38772,7 @@
         <v>0</v>
       </c>
       <c r="R390" s="23">
-        <f>SUM(O390:Q390)</f>
+        <f t="shared" si="6"/>
         <v>181</v>
       </c>
       <c r="S390" s="22">
@@ -38837,7 +38836,7 @@
         <v>7</v>
       </c>
       <c r="R391" s="25">
-        <f>SUM(O391:Q391)</f>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="S391" s="24">
@@ -38900,7 +38899,7 @@
         <v>0</v>
       </c>
       <c r="R392" s="23">
-        <f>SUM(O392:Q392)</f>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="S392" s="22">
@@ -39026,7 +39025,7 @@
         <v>31</v>
       </c>
       <c r="R394" s="23">
-        <f>SUM(O394:Q394)</f>
+        <f t="shared" ref="R394:R457" si="7">SUM(O394:Q394)</f>
         <v>31</v>
       </c>
       <c r="S394" s="22">
@@ -39089,7 +39088,7 @@
         <v>0</v>
       </c>
       <c r="R395" s="25">
-        <f>SUM(O395:Q395)</f>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="S395" s="24">
@@ -39152,7 +39151,7 @@
         <v>0</v>
       </c>
       <c r="R396" s="23">
-        <f>SUM(O396:Q396)</f>
+        <f t="shared" si="7"/>
         <v>45</v>
       </c>
       <c r="S396" s="22">
@@ -39215,7 +39214,7 @@
         <v>0</v>
       </c>
       <c r="R397" s="25">
-        <f>SUM(O397:Q397)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S397" s="24">
@@ -39278,7 +39277,7 @@
         <v>17</v>
       </c>
       <c r="R398" s="23">
-        <f>SUM(O398:Q398)</f>
+        <f t="shared" si="7"/>
         <v>85</v>
       </c>
       <c r="S398" s="22">
@@ -39341,7 +39340,7 @@
         <v>0</v>
       </c>
       <c r="R399" s="25">
-        <f>SUM(O399:Q399)</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="S399" s="24">
@@ -39398,7 +39397,7 @@
       <c r="P400" s="23"/>
       <c r="Q400" s="23"/>
       <c r="R400" s="23">
-        <f>SUM(O400:Q400)</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="S400" s="22">
@@ -39459,7 +39458,7 @@
         <v>0</v>
       </c>
       <c r="R401" s="25">
-        <f>SUM(O401:Q401)</f>
+        <f t="shared" si="7"/>
         <v>62</v>
       </c>
       <c r="S401" s="24">
@@ -39522,7 +39521,7 @@
         <v>68</v>
       </c>
       <c r="R402" s="23">
-        <f>SUM(O402:Q402)</f>
+        <f t="shared" si="7"/>
         <v>68</v>
       </c>
       <c r="S402" s="22">
@@ -39581,7 +39580,7 @@
         <v>0</v>
       </c>
       <c r="R403" s="25">
-        <f>SUM(O403:Q403)</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="S403" s="24">
@@ -39644,7 +39643,7 @@
         <v>0</v>
       </c>
       <c r="R404" s="23">
-        <f>SUM(O404:Q404)</f>
+        <f t="shared" si="7"/>
         <v>36</v>
       </c>
       <c r="S404" s="22">
@@ -39707,7 +39706,7 @@
         <v>0</v>
       </c>
       <c r="R405" s="25">
-        <f>SUM(O405:Q405)</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="S405" s="24">
@@ -39768,7 +39767,7 @@
         <v>44</v>
       </c>
       <c r="R406" s="23">
-        <f>SUM(O406:Q406)</f>
+        <f t="shared" si="7"/>
         <v>44</v>
       </c>
       <c r="S406" s="22">
@@ -39831,7 +39830,7 @@
         <v>0</v>
       </c>
       <c r="R407" s="25">
-        <f>SUM(O407:Q407)</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="S407" s="24">
@@ -39894,7 +39893,7 @@
         <v>0</v>
       </c>
       <c r="R408" s="23">
-        <f>SUM(O408:Q408)</f>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="S408" s="22">
@@ -39949,7 +39948,7 @@
         <v>20</v>
       </c>
       <c r="R409" s="25">
-        <f>SUM(O409:Q409)</f>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="S409" s="24">
@@ -40004,7 +40003,7 @@
         <v>0</v>
       </c>
       <c r="R410" s="23">
-        <f>SUM(O410:Q410)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S410" s="22"/>
@@ -40063,7 +40062,7 @@
         <v>0</v>
       </c>
       <c r="R411" s="25">
-        <f>SUM(O411:Q411)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="S411" s="24">
@@ -40126,7 +40125,7 @@
         <v>44</v>
       </c>
       <c r="R412" s="23">
-        <f>SUM(O412:Q412)</f>
+        <f t="shared" si="7"/>
         <v>44</v>
       </c>
       <c r="S412" s="22">
@@ -40189,7 +40188,7 @@
         <v>0</v>
       </c>
       <c r="R413" s="25">
-        <f>SUM(O413:Q413)</f>
+        <f t="shared" si="7"/>
         <v>105</v>
       </c>
       <c r="S413" s="24">
@@ -40252,7 +40251,7 @@
         <v>0</v>
       </c>
       <c r="R414" s="23">
-        <f>SUM(O414:Q414)</f>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="S414" s="22">
@@ -40315,7 +40314,7 @@
         <v>0</v>
       </c>
       <c r="R415" s="25">
-        <f>SUM(O415:Q415)</f>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="S415" s="24">
@@ -40378,7 +40377,7 @@
         <v>0</v>
       </c>
       <c r="R416" s="23">
-        <f>SUM(O416:Q416)</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="S416" s="22">
@@ -40441,7 +40440,7 @@
         <v>24</v>
       </c>
       <c r="R417" s="25">
-        <f>SUM(O417:Q417)</f>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="S417" s="24">
@@ -40504,7 +40503,7 @@
         <v>0</v>
       </c>
       <c r="R418" s="23">
-        <f>SUM(O418:Q418)</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="S418" s="22">
@@ -40568,7 +40567,7 @@
         <v>0</v>
       </c>
       <c r="R419" s="25">
-        <f>SUM(O419:Q419)</f>
+        <f t="shared" si="7"/>
         <v>49</v>
       </c>
       <c r="S419" s="24">
@@ -40631,7 +40630,7 @@
         <v>128</v>
       </c>
       <c r="R420" s="23">
-        <f>SUM(O420:Q420)</f>
+        <f t="shared" si="7"/>
         <v>128</v>
       </c>
       <c r="S420" s="22">
@@ -40694,7 +40693,7 @@
         <v>0</v>
       </c>
       <c r="R421" s="25">
-        <f>SUM(O421:Q421)</f>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
       <c r="S421" s="24">
@@ -40757,7 +40756,7 @@
         <v>0</v>
       </c>
       <c r="R422" s="23">
-        <f>SUM(O422:Q422)</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="S422" s="22">
@@ -40820,7 +40819,7 @@
         <v>0</v>
       </c>
       <c r="R423" s="25">
-        <f>SUM(O423:Q423)</f>
+        <f t="shared" si="7"/>
         <v>93</v>
       </c>
       <c r="S423" s="24">
@@ -40883,7 +40882,7 @@
         <v>0</v>
       </c>
       <c r="R424" s="23">
-        <f>SUM(O424:Q424)</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="S424" s="22">
@@ -40944,7 +40943,7 @@
         <v>0</v>
       </c>
       <c r="R425" s="25">
-        <f>SUM(O425:Q425)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S425" s="24">
@@ -41008,7 +41007,7 @@
         <v>0</v>
       </c>
       <c r="R426" s="23">
-        <f>SUM(O426:Q426)</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="S426" s="22">
@@ -41071,7 +41070,7 @@
         <v>0</v>
       </c>
       <c r="R427" s="25">
-        <f>SUM(O427:Q427)</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="S427" s="24">
@@ -41132,7 +41131,7 @@
         <v>80</v>
       </c>
       <c r="R428" s="23">
-        <f>SUM(O428:Q428)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S428" s="22">
@@ -41193,7 +41192,7 @@
         <v>80</v>
       </c>
       <c r="R429" s="25">
-        <f>SUM(O429:Q429)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S429" s="24">
@@ -41254,7 +41253,7 @@
         <v>80</v>
       </c>
       <c r="R430" s="23">
-        <f>SUM(O430:Q430)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S430" s="22">
@@ -41315,7 +41314,7 @@
         <v>80</v>
       </c>
       <c r="R431" s="25">
-        <f>SUM(O431:Q431)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S431" s="24">
@@ -41376,7 +41375,7 @@
         <v>80</v>
       </c>
       <c r="R432" s="23">
-        <f>SUM(O432:Q432)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S432" s="22">
@@ -41440,7 +41439,7 @@
         <v>0</v>
       </c>
       <c r="R433" s="25">
-        <f>SUM(O433:Q433)</f>
+        <f t="shared" si="7"/>
         <v>33</v>
       </c>
       <c r="S433" s="24">
@@ -41495,7 +41494,7 @@
         <v>0</v>
       </c>
       <c r="R434" s="23">
-        <f>SUM(O434:Q434)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S434" s="22"/>
@@ -41554,7 +41553,7 @@
         <v>62</v>
       </c>
       <c r="R435" s="25">
-        <f>SUM(O435:Q435)</f>
+        <f t="shared" si="7"/>
         <v>62</v>
       </c>
       <c r="S435" s="24">
@@ -41617,7 +41616,7 @@
         <v>0</v>
       </c>
       <c r="R436" s="23">
-        <f>SUM(O436:Q436)</f>
+        <f t="shared" si="7"/>
         <v>42</v>
       </c>
       <c r="S436" s="22">
@@ -41680,7 +41679,7 @@
         <v>0</v>
       </c>
       <c r="R437" s="25">
-        <f>SUM(O437:Q437)</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="S437" s="24">
@@ -41743,7 +41742,7 @@
         <v>0</v>
       </c>
       <c r="R438" s="23">
-        <f>SUM(O438:Q438)</f>
+        <f t="shared" si="7"/>
         <v>49</v>
       </c>
       <c r="S438" s="22">
@@ -41806,7 +41805,7 @@
         <v>0</v>
       </c>
       <c r="R439" s="25">
-        <f>SUM(O439:Q439)</f>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="S439" s="24">
@@ -41869,7 +41868,7 @@
         <v>28</v>
       </c>
       <c r="R440" s="23">
-        <f>SUM(O440:Q440)</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="S440" s="22">
@@ -41932,7 +41931,7 @@
         <v>0</v>
       </c>
       <c r="R441" s="25">
-        <f>SUM(O441:Q441)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="S441" s="24">
@@ -41996,7 +41995,7 @@
         <v>0</v>
       </c>
       <c r="R442" s="23">
-        <f>SUM(O442:Q442)</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="S442" s="22">
@@ -42060,7 +42059,7 @@
         <v>0</v>
       </c>
       <c r="R443" s="25">
-        <f>SUM(O443:Q443)</f>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="S443" s="24">
@@ -42123,7 +42122,7 @@
         <v>0</v>
       </c>
       <c r="R444" s="23">
-        <f>SUM(O444:Q444)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="S444" s="22">
@@ -42186,7 +42185,7 @@
         <v>7</v>
       </c>
       <c r="R445" s="25">
-        <f>SUM(O445:Q445)</f>
+        <f t="shared" si="7"/>
         <v>155</v>
       </c>
       <c r="S445" s="24">
@@ -42250,7 +42249,7 @@
         <v>0</v>
       </c>
       <c r="R446" s="23">
-        <f>SUM(O446:Q446)</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="S446" s="22">
@@ -42313,7 +42312,7 @@
         <v>0</v>
       </c>
       <c r="R447" s="25">
-        <f>SUM(O447:Q447)</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="S447" s="24">
@@ -42376,7 +42375,7 @@
         <v>0</v>
       </c>
       <c r="R448" s="23">
-        <f>SUM(O448:Q448)</f>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="S448" s="22">
@@ -42439,7 +42438,7 @@
         <v>0</v>
       </c>
       <c r="R449" s="25">
-        <f>SUM(O449:Q449)</f>
+        <f t="shared" si="7"/>
         <v>51</v>
       </c>
       <c r="S449" s="24">
@@ -42502,7 +42501,7 @@
         <v>0</v>
       </c>
       <c r="R450" s="23">
-        <f>SUM(O450:Q450)</f>
+        <f t="shared" si="7"/>
         <v>52</v>
       </c>
       <c r="S450" s="22">
@@ -42566,7 +42565,7 @@
         <v>0</v>
       </c>
       <c r="R451" s="25">
-        <f>SUM(O451:Q451)</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="S451" s="24">
@@ -42629,7 +42628,7 @@
         <v>0</v>
       </c>
       <c r="R452" s="23">
-        <f>SUM(O452:Q452)</f>
+        <f t="shared" si="7"/>
         <v>90</v>
       </c>
       <c r="S452" s="22">
@@ -42692,7 +42691,7 @@
         <v>0</v>
       </c>
       <c r="R453" s="25">
-        <f>SUM(O453:Q453)</f>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="S453" s="24">
@@ -42755,7 +42754,7 @@
         <v>0</v>
       </c>
       <c r="R454" s="23">
-        <f>SUM(O454:Q454)</f>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="S454" s="22">
@@ -42819,7 +42818,7 @@
         <v>0</v>
       </c>
       <c r="R455" s="25">
-        <f>SUM(O455:Q455)</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="S455" s="24">
@@ -42872,7 +42871,7 @@
         <v>0</v>
       </c>
       <c r="R456" s="23">
-        <f>SUM(O456:Q456)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S456" s="22"/>
@@ -42931,7 +42930,7 @@
         <v>0</v>
       </c>
       <c r="R457" s="25">
-        <f>SUM(O457:Q457)</f>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="S457" s="24">
@@ -42994,7 +42993,7 @@
         <v>0</v>
       </c>
       <c r="R458" s="23">
-        <f>SUM(O458:Q458)</f>
+        <f t="shared" ref="R458:R521" si="8">SUM(O458:Q458)</f>
         <v>23</v>
       </c>
       <c r="S458" s="22">
@@ -43057,7 +43056,7 @@
         <v>0</v>
       </c>
       <c r="R459" s="25">
-        <f>SUM(O459:Q459)</f>
+        <f t="shared" si="8"/>
         <v>89</v>
       </c>
       <c r="S459" s="24">
@@ -43120,7 +43119,7 @@
         <v>0</v>
       </c>
       <c r="R460" s="23">
-        <f>SUM(O460:Q460)</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="S460" s="22">
@@ -43184,7 +43183,7 @@
         <v>0</v>
       </c>
       <c r="R461" s="25">
-        <f>SUM(O461:Q461)</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="S461" s="24">
@@ -43247,7 +43246,7 @@
         <v>0</v>
       </c>
       <c r="R462" s="23">
-        <f>SUM(O462:Q462)</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="S462" s="22">
@@ -43310,7 +43309,7 @@
         <v>0</v>
       </c>
       <c r="R463" s="25">
-        <f>SUM(O463:Q463)</f>
+        <f t="shared" si="8"/>
         <v>51</v>
       </c>
       <c r="S463" s="24">
@@ -43374,7 +43373,7 @@
         <v>0</v>
       </c>
       <c r="R464" s="23">
-        <f>SUM(O464:Q464)</f>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="S464" s="22">
@@ -43437,7 +43436,7 @@
         <v>0</v>
       </c>
       <c r="R465" s="25">
-        <f>SUM(O465:Q465)</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="S465" s="24">
@@ -43500,7 +43499,7 @@
         <v>156</v>
       </c>
       <c r="R466" s="23">
-        <f>SUM(O466:Q466)</f>
+        <f t="shared" si="8"/>
         <v>213</v>
       </c>
       <c r="S466" s="22">
@@ -43563,7 +43562,7 @@
         <v>70</v>
       </c>
       <c r="R467" s="25">
-        <f>SUM(O467:Q467)</f>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="S467" s="24">
@@ -43626,7 +43625,7 @@
         <v>0</v>
       </c>
       <c r="R468" s="23">
-        <f>SUM(O468:Q468)</f>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="S468" s="22">
@@ -43690,7 +43689,7 @@
         <v>0</v>
       </c>
       <c r="R469" s="25">
-        <f>SUM(O469:Q469)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="S469" s="24">
@@ -43754,7 +43753,7 @@
         <v>0</v>
       </c>
       <c r="R470" s="23">
-        <f>SUM(O470:Q470)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="S470" s="22">
@@ -43818,7 +43817,7 @@
         <v>0</v>
       </c>
       <c r="R471" s="25">
-        <f>SUM(O471:Q471)</f>
+        <f t="shared" si="8"/>
         <v>384</v>
       </c>
       <c r="S471" s="24">
@@ -43881,7 +43880,7 @@
         <v>0</v>
       </c>
       <c r="R472" s="23">
-        <f>SUM(O472:Q472)</f>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="S472" s="22">
@@ -43944,7 +43943,7 @@
         <v>0</v>
       </c>
       <c r="R473" s="25">
-        <f>SUM(O473:Q473)</f>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
       <c r="S473" s="24">
@@ -44007,7 +44006,7 @@
         <v>0</v>
       </c>
       <c r="R474" s="23">
-        <f>SUM(O474:Q474)</f>
+        <f t="shared" si="8"/>
         <v>53</v>
       </c>
       <c r="S474" s="22">
@@ -44070,7 +44069,7 @@
         <v>0</v>
       </c>
       <c r="R475" s="25">
-        <f>SUM(O475:Q475)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="S475" s="24">
@@ -44133,7 +44132,7 @@
         <v>0</v>
       </c>
       <c r="R476" s="23">
-        <f>SUM(O476:Q476)</f>
+        <f t="shared" si="8"/>
         <v>60</v>
       </c>
       <c r="S476" s="22">
@@ -44196,7 +44195,7 @@
         <v>0</v>
       </c>
       <c r="R477" s="25">
-        <f>SUM(O477:Q477)</f>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="S477" s="24">
@@ -44259,7 +44258,7 @@
         <v>0</v>
       </c>
       <c r="R478" s="23">
-        <f>SUM(O478:Q478)</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="S478" s="22">
@@ -44322,7 +44321,7 @@
         <v>56</v>
       </c>
       <c r="R479" s="25">
-        <f>SUM(O479:Q479)</f>
+        <f t="shared" si="8"/>
         <v>56</v>
       </c>
       <c r="S479" s="24">
@@ -44385,7 +44384,7 @@
         <v>0</v>
       </c>
       <c r="R480" s="23">
-        <f>SUM(O480:Q480)</f>
+        <f t="shared" si="8"/>
         <v>38</v>
       </c>
       <c r="S480" s="22">
@@ -44448,7 +44447,7 @@
         <v>0</v>
       </c>
       <c r="R481" s="25">
-        <f>SUM(O481:Q481)</f>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="S481" s="24">
@@ -44511,7 +44510,7 @@
         <v>0</v>
       </c>
       <c r="R482" s="23">
-        <f>SUM(O482:Q482)</f>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="S482" s="22">
@@ -44574,7 +44573,7 @@
         <v>0</v>
       </c>
       <c r="R483" s="25">
-        <f>SUM(O483:Q483)</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="S483" s="24">
@@ -44637,7 +44636,7 @@
         <v>0</v>
       </c>
       <c r="R484" s="23">
-        <f>SUM(O484:Q484)</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="S484" s="22">
@@ -44701,7 +44700,7 @@
         <v>0</v>
       </c>
       <c r="R485" s="25">
-        <f>SUM(O485:Q485)</f>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="S485" s="24">
@@ -44764,7 +44763,7 @@
         <v>0</v>
       </c>
       <c r="R486" s="23">
-        <f>SUM(O486:Q486)</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="S486" s="22">
@@ -44827,7 +44826,7 @@
         <v>0</v>
       </c>
       <c r="R487" s="25">
-        <f>SUM(O487:Q487)</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="S487" s="24">
@@ -44891,7 +44890,7 @@
         <v>0</v>
       </c>
       <c r="R488" s="23">
-        <f>SUM(O488:Q488)</f>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="S488" s="22">
@@ -44954,7 +44953,7 @@
         <v>0</v>
       </c>
       <c r="R489" s="25">
-        <f>SUM(O489:Q489)</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="S489" s="64">
@@ -45018,7 +45017,7 @@
         <v>61</v>
       </c>
       <c r="R490" s="23">
-        <f>SUM(O490:Q490)</f>
+        <f t="shared" si="8"/>
         <v>61</v>
       </c>
       <c r="S490" s="70">
@@ -45081,7 +45080,7 @@
         <v>0</v>
       </c>
       <c r="R491" s="25">
-        <f>SUM(O491:Q491)</f>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="S491" s="64">
@@ -45144,7 +45143,7 @@
         <v>0</v>
       </c>
       <c r="R492" s="23">
-        <f>SUM(O492:Q492)</f>
+        <f t="shared" si="8"/>
         <v>43</v>
       </c>
       <c r="S492" s="70">
@@ -45207,7 +45206,7 @@
         <v>0</v>
       </c>
       <c r="R493" s="25">
-        <f>SUM(O493:Q493)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="S493" s="64">
@@ -45268,7 +45267,7 @@
         <v>0</v>
       </c>
       <c r="R494" s="23">
-        <f>SUM(O494:Q494)</f>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="S494" s="70">
@@ -45323,7 +45322,7 @@
         <v>0</v>
       </c>
       <c r="R495" s="25">
-        <f>SUM(O495:Q495)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S495" s="24"/>
@@ -45380,7 +45379,7 @@
         <v>0</v>
       </c>
       <c r="R496" s="23">
-        <f>SUM(O496:Q496)</f>
+        <f t="shared" si="8"/>
         <v>170</v>
       </c>
       <c r="S496" s="70">
@@ -45443,7 +45442,7 @@
         <v>0</v>
       </c>
       <c r="R497" s="25">
-        <f>SUM(O497:Q497)</f>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="S497" s="64">
@@ -45506,7 +45505,7 @@
         <v>0</v>
       </c>
       <c r="R498" s="23">
-        <f>SUM(O498:Q498)</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="S498" s="70">
@@ -45569,7 +45568,7 @@
         <v>45</v>
       </c>
       <c r="R499" s="25">
-        <f>SUM(O499:Q499)</f>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="S499" s="64">
@@ -45630,7 +45629,7 @@
         <v>0</v>
       </c>
       <c r="R500" s="23">
-        <f>SUM(O500:Q500)</f>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="S500" s="70">
@@ -45694,7 +45693,7 @@
         <v>0</v>
       </c>
       <c r="R501" s="25">
-        <f>SUM(O501:Q501)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S501" s="64">
@@ -45757,7 +45756,7 @@
         <v>0</v>
       </c>
       <c r="R502" s="23">
-        <f>SUM(O502:Q502)</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="S502" s="70">
@@ -45820,7 +45819,7 @@
         <v>0</v>
       </c>
       <c r="R503" s="25">
-        <f>SUM(O503:Q503)</f>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="S503" s="64">
@@ -45883,7 +45882,7 @@
         <v>0</v>
       </c>
       <c r="R504" s="23">
-        <f>SUM(O504:Q504)</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="S504" s="70">
@@ -45944,7 +45943,7 @@
         <v>0</v>
       </c>
       <c r="R505" s="25">
-        <f>SUM(O505:Q505)</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="S505" s="24">
@@ -46008,7 +46007,7 @@
         <v>0</v>
       </c>
       <c r="R506" s="23">
-        <f>SUM(O506:Q506)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="S506" s="22">
@@ -46071,7 +46070,7 @@
         <v>0</v>
       </c>
       <c r="R507" s="25">
-        <f>SUM(O507:Q507)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S507" s="24">
@@ -46134,7 +46133,7 @@
         <v>0</v>
       </c>
       <c r="R508" s="23">
-        <f>SUM(O508:Q508)</f>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="S508" s="22">
@@ -46195,7 +46194,7 @@
         <v>0</v>
       </c>
       <c r="R509" s="25">
-        <f>SUM(O509:Q509)</f>
+        <f t="shared" si="8"/>
         <v>170</v>
       </c>
       <c r="S509" s="24">
@@ -46259,7 +46258,7 @@
         <v>66</v>
       </c>
       <c r="R510" s="23">
-        <f>SUM(O510:Q510)</f>
+        <f t="shared" si="8"/>
         <v>66</v>
       </c>
       <c r="S510" s="22">
@@ -46320,7 +46319,7 @@
         <v>0</v>
       </c>
       <c r="R511" s="25">
-        <f>SUM(O511:Q511)</f>
+        <f t="shared" si="8"/>
         <v>140</v>
       </c>
       <c r="S511" s="24">
@@ -46383,7 +46382,7 @@
         <v>0</v>
       </c>
       <c r="R512" s="23">
-        <f>SUM(O512:Q512)</f>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="S512" s="22">
@@ -46446,7 +46445,7 @@
         <v>0</v>
       </c>
       <c r="R513" s="25">
-        <f>SUM(O513:Q513)</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="S513" s="24">
@@ -46509,7 +46508,7 @@
         <v>0</v>
       </c>
       <c r="R514" s="23">
-        <f>SUM(O514:Q514)</f>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="S514" s="22">
@@ -46572,7 +46571,7 @@
         <v>41</v>
       </c>
       <c r="R515" s="25">
-        <f>SUM(O515:Q515)</f>
+        <f t="shared" si="8"/>
         <v>41</v>
       </c>
       <c r="S515" s="24">
@@ -46635,7 +46634,7 @@
         <v>0</v>
       </c>
       <c r="R516" s="23">
-        <f>SUM(O516:Q516)</f>
+        <f t="shared" si="8"/>
         <v>96</v>
       </c>
       <c r="S516" s="22">
@@ -46699,7 +46698,7 @@
         <v>0</v>
       </c>
       <c r="R517" s="25">
-        <f>SUM(O517:Q517)</f>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="S517" s="24">
@@ -46762,7 +46761,7 @@
         <v>0</v>
       </c>
       <c r="R518" s="23">
-        <f>SUM(O518:Q518)</f>
+        <f t="shared" si="8"/>
         <v>47</v>
       </c>
       <c r="S518" s="22">
@@ -46825,7 +46824,7 @@
         <v>0</v>
       </c>
       <c r="R519" s="25">
-        <f>SUM(O519:Q519)</f>
+        <f t="shared" si="8"/>
         <v>37</v>
       </c>
       <c r="S519" s="24">
@@ -46888,7 +46887,7 @@
         <v>0</v>
       </c>
       <c r="R520" s="23">
-        <f>SUM(O520:Q520)</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="S520" s="22">
@@ -46951,7 +46950,7 @@
         <v>0</v>
       </c>
       <c r="R521" s="25">
-        <f>SUM(O521:Q521)</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="S521" s="24">
@@ -47014,7 +47013,7 @@
         <v>0</v>
       </c>
       <c r="R522" s="23">
-        <f>SUM(O522:Q522)</f>
+        <f t="shared" ref="R522:R585" si="9">SUM(O522:Q522)</f>
         <v>0</v>
       </c>
       <c r="S522" s="22">
@@ -47077,7 +47076,7 @@
         <v>0</v>
       </c>
       <c r="R523" s="25">
-        <f>SUM(O523:Q523)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S523" s="24">
@@ -47141,7 +47140,7 @@
         <v>0</v>
       </c>
       <c r="R524" s="23">
-        <f>SUM(O524:Q524)</f>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="S524" s="22"/>
@@ -47200,7 +47199,7 @@
         <v>0</v>
       </c>
       <c r="R525" s="25">
-        <f>SUM(O525:Q525)</f>
+        <f t="shared" si="9"/>
         <v>46</v>
       </c>
       <c r="S525" s="24">
@@ -47263,7 +47262,7 @@
         <v>0</v>
       </c>
       <c r="R526" s="23">
-        <f>SUM(O526:Q526)</f>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="S526" s="22">
@@ -47318,7 +47317,7 @@
         <v>0</v>
       </c>
       <c r="R527" s="25">
-        <f>SUM(O527:Q527)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S527" s="24"/>
@@ -47379,7 +47378,7 @@
         <v>0</v>
       </c>
       <c r="R528" s="23">
-        <f>SUM(O528:Q528)</f>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="S528" s="22">
@@ -47442,7 +47441,7 @@
         <v>1</v>
       </c>
       <c r="R529" s="25">
-        <f>SUM(O529:Q529)</f>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="S529" s="24">
@@ -47503,7 +47502,7 @@
         <v>23</v>
       </c>
       <c r="R530" s="23">
-        <f>SUM(O530:Q530)</f>
+        <f t="shared" si="9"/>
         <v>138</v>
       </c>
       <c r="S530" s="22">
@@ -47566,7 +47565,7 @@
         <v>0</v>
       </c>
       <c r="R531" s="25">
-        <f>SUM(O531:Q531)</f>
+        <f t="shared" si="9"/>
         <v>19</v>
       </c>
       <c r="S531" s="24">
@@ -47629,7 +47628,7 @@
         <v>0</v>
       </c>
       <c r="R532" s="23">
-        <f>SUM(O532:Q532)</f>
+        <f t="shared" si="9"/>
         <v>118</v>
       </c>
       <c r="S532" s="22">
@@ -47693,7 +47692,7 @@
         <v>0</v>
       </c>
       <c r="R533" s="25">
-        <f>SUM(O533:Q533)</f>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="S533" s="24">
@@ -47756,7 +47755,7 @@
         <v>49</v>
       </c>
       <c r="R534" s="23">
-        <f>SUM(O534:Q534)</f>
+        <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="S534" s="22">
@@ -47820,7 +47819,7 @@
         <v>94</v>
       </c>
       <c r="R535" s="25">
-        <f>SUM(O535:Q535)</f>
+        <f t="shared" si="9"/>
         <v>94</v>
       </c>
       <c r="S535" s="24">
@@ -47875,7 +47874,7 @@
         <v>0</v>
       </c>
       <c r="R536" s="23">
-        <f>SUM(O536:Q536)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S536" s="22"/>
@@ -47934,7 +47933,7 @@
         <v>0</v>
       </c>
       <c r="R537" s="25">
-        <f>SUM(O537:Q537)</f>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="S537" s="24">
@@ -47991,7 +47990,7 @@
         <v>0</v>
       </c>
       <c r="R538" s="23">
-        <f>SUM(O538:Q538)</f>
+        <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="S538" s="22"/>
@@ -48050,7 +48049,7 @@
         <v>0</v>
       </c>
       <c r="R539" s="25">
-        <f>SUM(O539:Q539)</f>
+        <f t="shared" si="9"/>
         <v>26</v>
       </c>
       <c r="S539" s="24">
@@ -48113,7 +48112,7 @@
         <v>0</v>
       </c>
       <c r="R540" s="23">
-        <f>SUM(O540:Q540)</f>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
       <c r="S540" s="22">
@@ -48176,7 +48175,7 @@
         <v>0</v>
       </c>
       <c r="R541" s="25">
-        <f>SUM(O541:Q541)</f>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="S541" s="24">
@@ -48239,7 +48238,7 @@
         <v>30</v>
       </c>
       <c r="R542" s="23">
-        <f>SUM(O542:Q542)</f>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="S542" s="22">
@@ -48302,7 +48301,7 @@
         <v>0</v>
       </c>
       <c r="R543" s="25">
-        <f>SUM(O543:Q543)</f>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="S543" s="24">
@@ -48366,7 +48365,7 @@
         <v>0</v>
       </c>
       <c r="R544" s="23">
-        <f>SUM(O544:Q544)</f>
+        <f t="shared" si="9"/>
         <v>43</v>
       </c>
       <c r="S544" s="22">
@@ -48429,7 +48428,7 @@
         <v>0</v>
       </c>
       <c r="R545" s="25">
-        <f>SUM(O545:Q545)</f>
+        <f t="shared" si="9"/>
         <v>54</v>
       </c>
       <c r="S545" s="24">
@@ -48492,7 +48491,7 @@
         <v>0</v>
       </c>
       <c r="R546" s="23">
-        <f>SUM(O546:Q546)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="S546" s="22">
@@ -48555,7 +48554,7 @@
         <v>0</v>
       </c>
       <c r="R547" s="25">
-        <f>SUM(O547:Q547)</f>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="S547" s="24">
@@ -48618,7 +48617,7 @@
         <v>44</v>
       </c>
       <c r="R548" s="23">
-        <f>SUM(O548:Q548)</f>
+        <f t="shared" si="9"/>
         <v>44</v>
       </c>
       <c r="S548" s="22">
@@ -48681,7 +48680,7 @@
         <v>0</v>
       </c>
       <c r="R549" s="25">
-        <f>SUM(O549:Q549)</f>
+        <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="S549" s="24">
@@ -48744,7 +48743,7 @@
         <v>0</v>
       </c>
       <c r="R550" s="23">
-        <f>SUM(O550:Q550)</f>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="S550" s="22">
@@ -48807,7 +48806,7 @@
         <v>0</v>
       </c>
       <c r="R551" s="25">
-        <f>SUM(O551:Q551)</f>
+        <f t="shared" si="9"/>
         <v>27</v>
       </c>
       <c r="S551" s="24">
@@ -48870,7 +48869,7 @@
         <v>60</v>
       </c>
       <c r="R552" s="23">
-        <f>SUM(O552:Q552)</f>
+        <f t="shared" si="9"/>
         <v>114</v>
       </c>
       <c r="S552" s="22">
@@ -48933,7 +48932,7 @@
         <v>1</v>
       </c>
       <c r="R553" s="25">
-        <f>SUM(O553:Q553)</f>
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
       <c r="S553" s="24">
@@ -48996,7 +48995,7 @@
         <v>0</v>
       </c>
       <c r="R554" s="23">
-        <f>SUM(O554:Q554)</f>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="S554" s="22">
@@ -49060,7 +49059,7 @@
         <v>38</v>
       </c>
       <c r="R555" s="25">
-        <f>SUM(O555:Q555)</f>
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="S555" s="24">
@@ -49121,7 +49120,7 @@
         <v>97</v>
       </c>
       <c r="R556" s="23">
-        <f>SUM(O556:Q556)</f>
+        <f t="shared" si="9"/>
         <v>97</v>
       </c>
       <c r="S556" s="22">
@@ -49185,7 +49184,7 @@
         <v>38</v>
       </c>
       <c r="R557" s="25">
-        <f>SUM(O557:Q557)</f>
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="S557" s="24">
@@ -49248,7 +49247,7 @@
         <v>0</v>
       </c>
       <c r="R558" s="23">
-        <f>SUM(O558:Q558)</f>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
       <c r="S558" s="22">
@@ -49311,7 +49310,7 @@
         <v>0</v>
       </c>
       <c r="R559" s="25">
-        <f>SUM(O559:Q559)</f>
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
       <c r="S559" s="24">
@@ -49374,7 +49373,7 @@
         <v>0</v>
       </c>
       <c r="R560" s="23">
-        <f>SUM(O560:Q560)</f>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="S560" s="22">
@@ -49437,7 +49436,7 @@
         <v>0</v>
       </c>
       <c r="R561" s="25">
-        <f>SUM(O561:Q561)</f>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="S561" s="24">
@@ -49500,7 +49499,7 @@
         <v>79</v>
       </c>
       <c r="R562" s="23">
-        <f>SUM(O562:Q562)</f>
+        <f t="shared" si="9"/>
         <v>250</v>
       </c>
       <c r="S562" s="22">
@@ -49563,7 +49562,7 @@
         <v>0</v>
       </c>
       <c r="R563" s="25">
-        <f>SUM(O563:Q563)</f>
+        <f t="shared" si="9"/>
         <v>32</v>
       </c>
       <c r="S563" s="24">
@@ -49626,7 +49625,7 @@
         <v>0</v>
       </c>
       <c r="R564" s="23">
-        <f>SUM(O564:Q564)</f>
+        <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="S564" s="22">
@@ -49689,7 +49688,7 @@
         <v>0</v>
       </c>
       <c r="R565" s="25">
-        <f>SUM(O565:Q565)</f>
+        <f t="shared" si="9"/>
         <v>75</v>
       </c>
       <c r="S565" s="24">
@@ -49750,7 +49749,7 @@
         <v>0</v>
       </c>
       <c r="R566" s="23">
-        <f>SUM(O566:Q566)</f>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="S566" s="22">
@@ -49813,7 +49812,7 @@
         <v>0</v>
       </c>
       <c r="R567" s="25">
-        <f>SUM(O567:Q567)</f>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="S567" s="24">
@@ -49876,7 +49875,7 @@
         <v>0</v>
       </c>
       <c r="R568" s="23">
-        <f>SUM(O568:Q568)</f>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="S568" s="22">
@@ -49939,7 +49938,7 @@
         <v>0</v>
       </c>
       <c r="R569" s="25">
-        <f>SUM(O569:Q569)</f>
+        <f t="shared" si="9"/>
         <v>48</v>
       </c>
       <c r="S569" s="24">
@@ -50002,7 +50001,7 @@
         <v>0</v>
       </c>
       <c r="R570" s="23">
-        <f>SUM(O570:Q570)</f>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="S570" s="22">
@@ -50063,7 +50062,7 @@
         <v>0</v>
       </c>
       <c r="R571" s="25">
-        <f>SUM(O571:Q571)</f>
+        <f t="shared" si="9"/>
         <v>170</v>
       </c>
       <c r="S571" s="24">
@@ -50124,7 +50123,7 @@
         <v>0</v>
       </c>
       <c r="R572" s="23">
-        <f>SUM(O572:Q572)</f>
+        <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="S572" s="22">
@@ -50185,7 +50184,7 @@
         <v>18</v>
       </c>
       <c r="R573" s="25">
-        <f>SUM(O573:Q573)</f>
+        <f t="shared" si="9"/>
         <v>176</v>
       </c>
       <c r="S573" s="24">
@@ -50244,7 +50243,7 @@
         <v>0</v>
       </c>
       <c r="R574" s="23">
-        <f>SUM(O574:Q574)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S574" s="22"/>
@@ -50305,7 +50304,7 @@
         <v>0</v>
       </c>
       <c r="R575" s="25">
-        <f>SUM(O575:Q575)</f>
+        <f t="shared" si="9"/>
         <v>44</v>
       </c>
       <c r="S575" s="24">
@@ -50369,7 +50368,7 @@
         <v>33</v>
       </c>
       <c r="R576" s="23">
-        <f>SUM(O576:Q576)</f>
+        <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="S576" s="22">
@@ -50430,7 +50429,7 @@
         <v>0</v>
       </c>
       <c r="R577" s="25">
-        <f>SUM(O577:Q577)</f>
+        <f t="shared" si="9"/>
         <v>170</v>
       </c>
       <c r="S577" s="24">
@@ -50489,7 +50488,7 @@
         <v>40</v>
       </c>
       <c r="R578" s="23">
-        <f>SUM(O578:Q578)</f>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="S578" s="22">
@@ -50548,7 +50547,7 @@
         <v>40</v>
       </c>
       <c r="R579" s="25">
-        <f>SUM(O579:Q579)</f>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="S579" s="24">
@@ -50611,7 +50610,7 @@
         <v>0</v>
       </c>
       <c r="R580" s="23">
-        <f>SUM(O580:Q580)</f>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="S580" s="22">
@@ -50674,7 +50673,7 @@
         <v>0</v>
       </c>
       <c r="R581" s="25">
-        <f>SUM(O581:Q581)</f>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="S581" s="24">
@@ -50737,7 +50736,7 @@
         <v>0</v>
       </c>
       <c r="R582" s="23">
-        <f>SUM(O582:Q582)</f>
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="S582" s="22">
@@ -50800,7 +50799,7 @@
         <v>0</v>
       </c>
       <c r="R583" s="25">
-        <f>SUM(O583:Q583)</f>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="S583" s="24">
@@ -50863,7 +50862,7 @@
         <v>31</v>
       </c>
       <c r="R584" s="23">
-        <f>SUM(O584:Q584)</f>
+        <f t="shared" si="9"/>
         <v>31</v>
       </c>
       <c r="S584" s="22">
@@ -50926,7 +50925,7 @@
         <v>4</v>
       </c>
       <c r="R585" s="25">
-        <f>SUM(O585:Q585)</f>
+        <f t="shared" si="9"/>
         <v>29</v>
       </c>
       <c r="S585" s="24">
@@ -50989,7 +50988,7 @@
         <v>30</v>
       </c>
       <c r="R586" s="23">
-        <f>SUM(O586:Q586)</f>
+        <f t="shared" ref="R586:R649" si="10">SUM(O586:Q586)</f>
         <v>30</v>
       </c>
       <c r="S586" s="22">
@@ -51052,7 +51051,7 @@
         <v>0</v>
       </c>
       <c r="R587" s="25">
-        <f>SUM(O587:Q587)</f>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="S587" s="24">
@@ -51115,7 +51114,7 @@
         <v>27</v>
       </c>
       <c r="R588" s="23">
-        <f>SUM(O588:Q588)</f>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="S588" s="22">
@@ -51178,7 +51177,7 @@
         <v>0</v>
       </c>
       <c r="R589" s="25">
-        <f>SUM(O589:Q589)</f>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="S589" s="24">
@@ -51241,7 +51240,7 @@
         <v>0</v>
       </c>
       <c r="R590" s="23">
-        <f>SUM(O590:Q590)</f>
+        <f t="shared" si="10"/>
         <v>33</v>
       </c>
       <c r="S590" s="22">
@@ -51304,7 +51303,7 @@
         <v>42</v>
       </c>
       <c r="R591" s="25">
-        <f>SUM(O591:Q591)</f>
+        <f t="shared" si="10"/>
         <v>42</v>
       </c>
       <c r="S591" s="24">
@@ -51367,7 +51366,7 @@
         <v>0</v>
       </c>
       <c r="R592" s="23">
-        <f>SUM(O592:Q592)</f>
+        <f t="shared" si="10"/>
         <v>22</v>
       </c>
       <c r="S592" s="22">
@@ -51430,7 +51429,7 @@
         <v>0</v>
       </c>
       <c r="R593" s="25">
-        <f>SUM(O593:Q593)</f>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
       <c r="S593" s="24">
@@ -51493,7 +51492,7 @@
         <v>0</v>
       </c>
       <c r="R594" s="23">
-        <f>SUM(O594:Q594)</f>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="S594" s="22">
@@ -51554,7 +51553,7 @@
         <v>25</v>
       </c>
       <c r="R595" s="25">
-        <f>SUM(O595:Q595)</f>
+        <f t="shared" si="10"/>
         <v>25</v>
       </c>
       <c r="S595" s="24">
@@ -51617,7 +51616,7 @@
         <v>24</v>
       </c>
       <c r="R596" s="73">
-        <f>SUM(O596:Q596)</f>
+        <f t="shared" si="10"/>
         <v>24</v>
       </c>
       <c r="S596" s="70">
@@ -51680,7 +51679,7 @@
         <v>0</v>
       </c>
       <c r="R597" s="25">
-        <f>SUM(O597:Q597)</f>
+        <f t="shared" si="10"/>
         <v>46</v>
       </c>
       <c r="S597" s="24">
@@ -51743,7 +51742,7 @@
         <v>0</v>
       </c>
       <c r="R598" s="23">
-        <f>SUM(O598:Q598)</f>
+        <f t="shared" si="10"/>
         <v>37</v>
       </c>
       <c r="S598" s="70">
@@ -51804,7 +51803,7 @@
         <v>0</v>
       </c>
       <c r="R599" s="25">
-        <f>SUM(O599:Q599)</f>
+        <f t="shared" si="10"/>
         <v>24</v>
       </c>
       <c r="S599" s="64">
@@ -51867,7 +51866,7 @@
         <v>0</v>
       </c>
       <c r="R600" s="23">
-        <f>SUM(O600:Q600)</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="S600" s="70">
@@ -51930,7 +51929,7 @@
         <v>0</v>
       </c>
       <c r="R601" s="25">
-        <f>SUM(O601:Q601)</f>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="S601" s="64">
@@ -51993,7 +51992,7 @@
         <v>0</v>
       </c>
       <c r="R602" s="23">
-        <f>SUM(O602:Q602)</f>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="S602" s="22">
@@ -52054,7 +52053,7 @@
         <v>0</v>
       </c>
       <c r="R603" s="25">
-        <f>SUM(O603:Q603)</f>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="S603" s="24">
@@ -52117,7 +52116,7 @@
         <v>0</v>
       </c>
       <c r="R604" s="23">
-        <f>SUM(O604:Q604)</f>
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="S604" s="22">
@@ -52180,7 +52179,7 @@
         <v>0</v>
       </c>
       <c r="R605" s="25">
-        <f>SUM(O605:Q605)</f>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="S605" s="24">
@@ -52241,7 +52240,7 @@
         <v>0</v>
       </c>
       <c r="R606" s="23">
-        <f>SUM(O606:Q606)</f>
+        <f t="shared" si="10"/>
         <v>170</v>
       </c>
       <c r="S606" s="22">
@@ -52302,7 +52301,7 @@
         <v>0</v>
       </c>
       <c r="R607" s="25">
-        <f>SUM(O607:Q607)</f>
+        <f t="shared" si="10"/>
         <v>170</v>
       </c>
       <c r="S607" s="24">
@@ -52365,7 +52364,7 @@
         <v>0</v>
       </c>
       <c r="R608" s="23">
-        <f>SUM(O608:Q608)</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="S608" s="22">
@@ -52428,7 +52427,7 @@
         <v>0</v>
       </c>
       <c r="R609" s="25">
-        <f>SUM(O609:Q609)</f>
+        <f t="shared" si="10"/>
         <v>19</v>
       </c>
       <c r="S609" s="24">
@@ -52489,7 +52488,7 @@
         <v>31</v>
       </c>
       <c r="R610" s="23">
-        <f>SUM(O610:Q610)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="S610" s="22">
@@ -52552,7 +52551,7 @@
         <v>0</v>
       </c>
       <c r="R611" s="25">
-        <f>SUM(O611:Q611)</f>
+        <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="S611" s="24">
@@ -52613,7 +52612,7 @@
         <v>0</v>
       </c>
       <c r="R612" s="23">
-        <f>SUM(O612:Q612)</f>
+        <f t="shared" si="10"/>
         <v>100</v>
       </c>
       <c r="S612" s="22">
@@ -52674,7 +52673,7 @@
         <v>0</v>
       </c>
       <c r="R613" s="25">
-        <f>SUM(O613:Q613)</f>
+        <f t="shared" si="10"/>
         <v>114</v>
       </c>
       <c r="S613" s="24">
@@ -52737,7 +52736,7 @@
         <v>0</v>
       </c>
       <c r="R614" s="23">
-        <f>SUM(O614:Q614)</f>
+        <f t="shared" si="10"/>
         <v>491</v>
       </c>
       <c r="S614" s="22">
@@ -52800,7 +52799,7 @@
         <v>0</v>
       </c>
       <c r="R615" s="25">
-        <f>SUM(O615:Q615)</f>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="S615" s="24">
@@ -52861,7 +52860,7 @@
         <v>0</v>
       </c>
       <c r="R616" s="23">
-        <f>SUM(O616:Q616)</f>
+        <f t="shared" si="10"/>
         <v>63</v>
       </c>
       <c r="S616" s="22">
@@ -52924,7 +52923,7 @@
         <v>0</v>
       </c>
       <c r="R617" s="25">
-        <f>SUM(O617:Q617)</f>
+        <f t="shared" si="10"/>
         <v>42</v>
       </c>
       <c r="S617" s="24">
@@ -52987,7 +52986,7 @@
         <v>0</v>
       </c>
       <c r="R618" s="23">
-        <f>SUM(O618:Q618)</f>
+        <f t="shared" si="10"/>
         <v>27</v>
       </c>
       <c r="S618" s="22">
@@ -53050,7 +53049,7 @@
         <v>0</v>
       </c>
       <c r="R619" s="25">
-        <f>SUM(O619:Q619)</f>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="S619" s="24">
@@ -53111,7 +53110,7 @@
         <v>0</v>
       </c>
       <c r="R620" s="23">
-        <f>SUM(O620:Q620)</f>
+        <f t="shared" si="10"/>
         <v>47</v>
       </c>
       <c r="S620" s="22">
@@ -53172,7 +53171,7 @@
         <v>0</v>
       </c>
       <c r="R621" s="25">
-        <f>SUM(O621:Q621)</f>
+        <f t="shared" si="10"/>
         <v>23</v>
       </c>
       <c r="S621" s="24">
@@ -53233,7 +53232,7 @@
         <v>0</v>
       </c>
       <c r="R622" s="23">
-        <f>SUM(O622:Q622)</f>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="S622" s="22">
@@ -53296,7 +53295,7 @@
         <v>0</v>
       </c>
       <c r="R623" s="25">
-        <f>SUM(O623:Q623)</f>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="S623" s="24">
@@ -53355,7 +53354,7 @@
         <v>88</v>
       </c>
       <c r="R624" s="23">
-        <f>SUM(O624:Q624)</f>
+        <f t="shared" si="10"/>
         <v>88</v>
       </c>
       <c r="S624" s="22">
@@ -53416,7 +53415,7 @@
         <v>0</v>
       </c>
       <c r="R625" s="25">
-        <f>SUM(O625:Q625)</f>
+        <f t="shared" si="10"/>
         <v>33</v>
       </c>
       <c r="S625" s="24">
@@ -53475,7 +53474,7 @@
         <v>128</v>
       </c>
       <c r="R626" s="23">
-        <f>SUM(O626:Q626)</f>
+        <f t="shared" si="10"/>
         <v>128</v>
       </c>
       <c r="S626" s="22">
@@ -53536,7 +53535,7 @@
         <v>0</v>
       </c>
       <c r="R627" s="25">
-        <f>SUM(O627:Q627)</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="S627" s="24">
@@ -53597,7 +53596,7 @@
         <v>0</v>
       </c>
       <c r="R628" s="23">
-        <f>SUM(O628:Q628)</f>
+        <f t="shared" si="10"/>
         <v>23</v>
       </c>
       <c r="S628" s="22" t="s">
@@ -53660,7 +53659,7 @@
         <v>0</v>
       </c>
       <c r="R629" s="25">
-        <f>SUM(O629:Q629)</f>
+        <f t="shared" si="10"/>
         <v>49</v>
       </c>
       <c r="S629" s="24">
@@ -53721,7 +53720,7 @@
         <v>46</v>
       </c>
       <c r="R630" s="23">
-        <f>SUM(O630:Q630)</f>
+        <f t="shared" si="10"/>
         <v>228</v>
       </c>
       <c r="S630" s="22">
@@ -53782,7 +53781,7 @@
         <v>0</v>
       </c>
       <c r="R631" s="25">
-        <f>SUM(O631:Q631)</f>
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="S631" s="24">
@@ -53843,7 +53842,7 @@
         <v>0</v>
       </c>
       <c r="R632" s="23">
-        <f>SUM(O632:Q632)</f>
+        <f t="shared" si="10"/>
         <v>16</v>
       </c>
       <c r="S632" s="22">
@@ -53904,7 +53903,7 @@
         <v>0</v>
       </c>
       <c r="R633" s="25">
-        <f>SUM(O633:Q633)</f>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="S633" s="24">
@@ -53967,7 +53966,7 @@
         <v>0</v>
       </c>
       <c r="R634" s="23">
-        <f>SUM(O634:Q634)</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="S634" s="22">
@@ -54028,7 +54027,7 @@
         <v>0</v>
       </c>
       <c r="R635" s="25">
-        <f>SUM(O635:Q635)</f>
+        <f t="shared" si="10"/>
         <v>70</v>
       </c>
       <c r="S635" s="24">
@@ -54089,7 +54088,7 @@
         <v>0</v>
       </c>
       <c r="R636" s="23">
-        <f>SUM(O636:Q636)</f>
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="S636" s="22">
@@ -54150,7 +54149,7 @@
         <v>30</v>
       </c>
       <c r="R637" s="25">
-        <f>SUM(O637:Q637)</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="S637" s="24">
@@ -54213,7 +54212,7 @@
         <v>0</v>
       </c>
       <c r="R638" s="23">
-        <f>SUM(O638:Q638)</f>
+        <f t="shared" si="10"/>
         <v>21</v>
       </c>
       <c r="S638" s="22" t="s">
@@ -54276,7 +54275,7 @@
         <v>40</v>
       </c>
       <c r="R639" s="25">
-        <f>SUM(O639:Q639)</f>
+        <f t="shared" si="10"/>
         <v>179</v>
       </c>
       <c r="S639" s="24">
@@ -54333,7 +54332,7 @@
         <v>0</v>
       </c>
       <c r="R640" s="23">
-        <f>SUM(O640:Q640)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S640" s="22">
@@ -54453,7 +54452,7 @@
         <v>33</v>
       </c>
       <c r="R642" s="23">
-        <f>SUM(O642:Q642)</f>
+        <f t="shared" ref="R642:R649" si="11">SUM(O642:Q642)</f>
         <v>33</v>
       </c>
       <c r="S642" s="22">
@@ -54512,7 +54511,7 @@
         <v>39</v>
       </c>
       <c r="R643" s="25">
-        <f>SUM(O643:Q643)</f>
+        <f t="shared" si="11"/>
         <v>39</v>
       </c>
       <c r="S643" s="24">
@@ -54574,7 +54573,7 @@
         <v>39</v>
       </c>
       <c r="R644" s="23">
-        <f>SUM(O644:Q644)</f>
+        <f t="shared" si="11"/>
         <v>39</v>
       </c>
       <c r="S644" s="22">
@@ -54635,7 +54634,7 @@
         <v>0</v>
       </c>
       <c r="R645" s="25">
-        <f>SUM(O645:Q645)</f>
+        <f t="shared" si="11"/>
         <v>170</v>
       </c>
       <c r="S645" s="24">
@@ -54698,7 +54697,7 @@
         <v>0</v>
       </c>
       <c r="R646" s="23">
-        <f>SUM(O646:Q646)</f>
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
       <c r="S646" s="22">
@@ -54759,7 +54758,7 @@
         <v>0</v>
       </c>
       <c r="R647" s="25">
-        <f>SUM(O647:Q647)</f>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="S647" s="24">
@@ -54820,7 +54819,7 @@
         <v>0</v>
       </c>
       <c r="R648" s="23">
-        <f>SUM(O648:Q648)</f>
+        <f t="shared" si="11"/>
         <v>45</v>
       </c>
       <c r="S648" s="22">
@@ -54879,7 +54878,7 @@
         <v>0</v>
       </c>
       <c r="R649" s="25">
-        <f>SUM(O649:Q649)</f>
+        <f t="shared" si="11"/>
         <v>72</v>
       </c>
       <c r="S649" s="24">
@@ -55680,7 +55679,7 @@
         <v>0</v>
       </c>
       <c r="R662" s="23">
-        <f>SUM(O662:Q662)</f>
+        <f t="shared" ref="R662:R668" si="12">SUM(O662:Q662)</f>
         <v>20</v>
       </c>
       <c r="S662" s="22">
@@ -55744,7 +55743,7 @@
         <v>0</v>
       </c>
       <c r="R663" s="25">
-        <f>SUM(O663:Q663)</f>
+        <f t="shared" si="12"/>
         <v>19</v>
       </c>
       <c r="S663" s="24">
@@ -55808,7 +55807,7 @@
         <v>0</v>
       </c>
       <c r="R664" s="23">
-        <f>SUM(O664:Q664)</f>
+        <f t="shared" si="12"/>
         <v>33</v>
       </c>
       <c r="S664" s="22">
@@ -55872,7 +55871,7 @@
         <v>0</v>
       </c>
       <c r="R665" s="25">
-        <f>SUM(O665:Q665)</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="S665" s="24">
@@ -55936,7 +55935,7 @@
         <v>0</v>
       </c>
       <c r="R666" s="23">
-        <f>SUM(O666:Q666)</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="S666" s="22">
@@ -55998,7 +55997,7 @@
         <v>14</v>
       </c>
       <c r="R667" s="25">
-        <f>SUM(O667:Q667)</f>
+        <f t="shared" si="12"/>
         <v>127</v>
       </c>
       <c r="S667" s="24">
@@ -56060,7 +56059,7 @@
         <v>34</v>
       </c>
       <c r="R668" s="23">
-        <f>SUM(O668:Q668)</f>
+        <f t="shared" si="12"/>
         <v>192</v>
       </c>
       <c r="S668" s="22">
@@ -56250,7 +56249,7 @@
         <v>0</v>
       </c>
       <c r="R671" s="25">
-        <f>SUM(O671:Q671)</f>
+        <f t="shared" ref="R671:R684" si="13">SUM(O671:Q671)</f>
         <v>22</v>
       </c>
       <c r="S671" s="24">
@@ -56314,7 +56313,7 @@
         <v>0</v>
       </c>
       <c r="R672" s="178">
-        <f>SUM(O672:Q672)</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="S672" s="172">
@@ -56366,7 +56365,7 @@
       <c r="P673" s="25"/>
       <c r="Q673" s="25"/>
       <c r="R673" s="25">
-        <f>SUM(O673:Q673)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S673" s="24"/>
@@ -56424,7 +56423,7 @@
         <v>80</v>
       </c>
       <c r="R674" s="23">
-        <f>SUM(O674:Q674)</f>
+        <f t="shared" si="13"/>
         <v>80</v>
       </c>
       <c r="S674" s="22">
@@ -56484,7 +56483,7 @@
         <v>80</v>
       </c>
       <c r="R675" s="23">
-        <f>SUM(O675:Q675)</f>
+        <f t="shared" si="13"/>
         <v>80</v>
       </c>
       <c r="S675" s="22">
@@ -56538,7 +56537,7 @@
       <c r="P676" s="25"/>
       <c r="Q676" s="25"/>
       <c r="R676" s="25">
-        <f>SUM(O676:Q676)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S676" s="24">
@@ -56600,7 +56599,7 @@
         <v>5</v>
       </c>
       <c r="R677" s="193">
-        <f>SUM(O677:Q677)</f>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="S677" s="186">
@@ -56664,7 +56663,7 @@
         <v>0</v>
       </c>
       <c r="R678" s="63">
-        <f>SUM(O678:Q678)</f>
+        <f t="shared" si="13"/>
         <v>17</v>
       </c>
       <c r="S678" s="64">
@@ -56728,7 +56727,7 @@
         <v>0</v>
       </c>
       <c r="R679" s="185">
-        <f>SUM(O679:Q679)</f>
+        <f t="shared" si="13"/>
         <v>32</v>
       </c>
       <c r="S679" s="180">
@@ -56782,7 +56781,7 @@
       <c r="P680" s="73"/>
       <c r="Q680" s="73"/>
       <c r="R680" s="73">
-        <f>SUM(O680:Q680)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S680" s="70">
@@ -56836,7 +56835,7 @@
       <c r="P681" s="193"/>
       <c r="Q681" s="193"/>
       <c r="R681" s="193">
-        <f>SUM(O681:Q681)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S681" s="186">
@@ -56890,7 +56889,7 @@
       <c r="P682" s="185"/>
       <c r="Q682" s="185"/>
       <c r="R682" s="185">
-        <f>SUM(O682:Q682)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S682" s="180">
@@ -56944,7 +56943,7 @@
       <c r="P683" s="193"/>
       <c r="Q683" s="193"/>
       <c r="R683" s="193">
-        <f>SUM(O683:Q683)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S683" s="186">
@@ -56994,7 +56993,7 @@
       <c r="P684" s="73"/>
       <c r="Q684" s="73"/>
       <c r="R684" s="73">
-        <f>SUM(O684:Q684)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S684" s="70">
@@ -57048,7 +57047,7 @@
       <c r="P685" s="217"/>
       <c r="Q685" s="217"/>
       <c r="R685" s="217">
-        <f t="shared" ref="R685:R747" si="0">IF(B685="","",SUM(O685:Q685))</f>
+        <f t="shared" ref="R685:R747" si="14">IF(B685="","",SUM(O685:Q685))</f>
         <v>0</v>
       </c>
       <c r="S685" s="210">
@@ -57105,7 +57104,7 @@
       <c r="P686" s="225"/>
       <c r="Q686" s="225"/>
       <c r="R686" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S686" s="219">
@@ -57160,7 +57159,7 @@
       <c r="P687" s="217"/>
       <c r="Q687" s="217"/>
       <c r="R687" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S687" s="210">
@@ -57217,7 +57216,7 @@
       <c r="P688" s="225"/>
       <c r="Q688" s="225"/>
       <c r="R688" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S688" s="219">
@@ -57282,7 +57281,7 @@
         <v>0</v>
       </c>
       <c r="R689" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>22</v>
       </c>
       <c r="S689" s="210">
@@ -57339,7 +57338,7 @@
       <c r="P690" s="225"/>
       <c r="Q690" s="225"/>
       <c r="R690" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S690" s="219">
@@ -57404,7 +57403,7 @@
         <v>0</v>
       </c>
       <c r="R691" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>21</v>
       </c>
       <c r="S691" s="210">
@@ -57469,7 +57468,7 @@
         <v>0</v>
       </c>
       <c r="R692" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="S692" s="219">
@@ -57534,7 +57533,7 @@
         <v>0</v>
       </c>
       <c r="R693" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="S693" s="210">
@@ -57587,7 +57586,7 @@
       <c r="P694" s="225"/>
       <c r="Q694" s="225"/>
       <c r="R694" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S694" s="219">
@@ -57640,7 +57639,7 @@
       <c r="P695" s="217"/>
       <c r="Q695" s="217"/>
       <c r="R695" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S695" s="210">
@@ -57697,7 +57696,7 @@
         <v>25</v>
       </c>
       <c r="R696" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="S696" s="219">
@@ -57758,7 +57757,7 @@
         <v>50</v>
       </c>
       <c r="R697" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>50</v>
       </c>
       <c r="S697" s="210">
@@ -57811,7 +57810,7 @@
       <c r="P698" s="225"/>
       <c r="Q698" s="225"/>
       <c r="R698" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S698" s="219">
@@ -57866,7 +57865,7 @@
       <c r="P699" s="217"/>
       <c r="Q699" s="217"/>
       <c r="R699" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S699" s="210">
@@ -57921,7 +57920,7 @@
       <c r="P700" s="225"/>
       <c r="Q700" s="225"/>
       <c r="R700" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S700" s="219">
@@ -57976,7 +57975,7 @@
       <c r="P701" s="217"/>
       <c r="Q701" s="217"/>
       <c r="R701" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S701" s="210">
@@ -58029,7 +58028,7 @@
       <c r="P702" s="225"/>
       <c r="Q702" s="225"/>
       <c r="R702" s="225">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S702" s="219">
@@ -58082,7 +58081,7 @@
       <c r="P703" s="217"/>
       <c r="Q703" s="217"/>
       <c r="R703" s="217">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="S703" s="210">
@@ -58096,11 +58095,17 @@
     <row r="704" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="218" t="str">
         <f>IF(B704="","",B704&amp;"-"&amp;TEXT(COUNTIF(B$2:B704,B704),"000"))</f>
-        <v/>
-      </c>
-      <c r="B704" s="219"/>
-      <c r="C704" s="219"/>
-      <c r="D704" s="219"/>
+        <v>2026-048</v>
+      </c>
+      <c r="B704" s="219">
+        <v>2026</v>
+      </c>
+      <c r="C704" s="219" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D704" s="219" t="s">
+        <v>2961</v>
+      </c>
       <c r="E704" s="220"/>
       <c r="F704" s="221"/>
       <c r="G704" s="218"/>
@@ -58114,9 +58119,9 @@
       <c r="O704" s="225"/>
       <c r="P704" s="225"/>
       <c r="Q704" s="225"/>
-      <c r="R704" s="225" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="R704" s="225">
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="S704" s="219"/>
       <c r="T704" s="218"/>
@@ -58144,7 +58149,7 @@
       <c r="P705" s="217"/>
       <c r="Q705" s="217"/>
       <c r="R705" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S705" s="210"/>
@@ -58173,7 +58178,7 @@
       <c r="P706" s="225"/>
       <c r="Q706" s="225"/>
       <c r="R706" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S706" s="219"/>
@@ -58202,7 +58207,7 @@
       <c r="P707" s="217"/>
       <c r="Q707" s="217"/>
       <c r="R707" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S707" s="210"/>
@@ -58231,7 +58236,7 @@
       <c r="P708" s="225"/>
       <c r="Q708" s="225"/>
       <c r="R708" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S708" s="219"/>
@@ -58260,7 +58265,7 @@
       <c r="P709" s="217"/>
       <c r="Q709" s="217"/>
       <c r="R709" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S709" s="210"/>
@@ -58289,7 +58294,7 @@
       <c r="P710" s="225"/>
       <c r="Q710" s="225"/>
       <c r="R710" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S710" s="219"/>
@@ -58318,7 +58323,7 @@
       <c r="P711" s="217"/>
       <c r="Q711" s="217"/>
       <c r="R711" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S711" s="210"/>
@@ -58347,7 +58352,7 @@
       <c r="P712" s="225"/>
       <c r="Q712" s="225"/>
       <c r="R712" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S712" s="219"/>
@@ -58376,7 +58381,7 @@
       <c r="P713" s="217"/>
       <c r="Q713" s="217"/>
       <c r="R713" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S713" s="210"/>
@@ -58405,7 +58410,7 @@
       <c r="P714" s="225"/>
       <c r="Q714" s="225"/>
       <c r="R714" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S714" s="219"/>
@@ -58434,7 +58439,7 @@
       <c r="P715" s="217"/>
       <c r="Q715" s="217"/>
       <c r="R715" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S715" s="210"/>
@@ -58463,7 +58468,7 @@
       <c r="P716" s="225"/>
       <c r="Q716" s="225"/>
       <c r="R716" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S716" s="219"/>
@@ -58492,7 +58497,7 @@
       <c r="P717" s="217"/>
       <c r="Q717" s="217"/>
       <c r="R717" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S717" s="210"/>
@@ -58521,7 +58526,7 @@
       <c r="P718" s="225"/>
       <c r="Q718" s="225"/>
       <c r="R718" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S718" s="219"/>
@@ -58550,7 +58555,7 @@
       <c r="P719" s="217"/>
       <c r="Q719" s="217"/>
       <c r="R719" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S719" s="210"/>
@@ -58579,7 +58584,7 @@
       <c r="P720" s="225"/>
       <c r="Q720" s="225"/>
       <c r="R720" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S720" s="219"/>
@@ -58608,7 +58613,7 @@
       <c r="P721" s="217"/>
       <c r="Q721" s="217"/>
       <c r="R721" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S721" s="210"/>
@@ -58637,7 +58642,7 @@
       <c r="P722" s="225"/>
       <c r="Q722" s="225"/>
       <c r="R722" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S722" s="219"/>
@@ -58666,7 +58671,7 @@
       <c r="P723" s="217"/>
       <c r="Q723" s="217"/>
       <c r="R723" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S723" s="210"/>
@@ -58695,7 +58700,7 @@
       <c r="P724" s="225"/>
       <c r="Q724" s="225"/>
       <c r="R724" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S724" s="219"/>
@@ -58724,7 +58729,7 @@
       <c r="P725" s="217"/>
       <c r="Q725" s="217"/>
       <c r="R725" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S725" s="210"/>
@@ -58753,7 +58758,7 @@
       <c r="P726" s="225"/>
       <c r="Q726" s="225"/>
       <c r="R726" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S726" s="219"/>
@@ -58782,7 +58787,7 @@
       <c r="P727" s="217"/>
       <c r="Q727" s="217"/>
       <c r="R727" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S727" s="210"/>
@@ -58811,7 +58816,7 @@
       <c r="P728" s="225"/>
       <c r="Q728" s="225"/>
       <c r="R728" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S728" s="219"/>
@@ -58840,7 +58845,7 @@
       <c r="P729" s="217"/>
       <c r="Q729" s="217"/>
       <c r="R729" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S729" s="210"/>
@@ -58869,7 +58874,7 @@
       <c r="P730" s="225"/>
       <c r="Q730" s="225"/>
       <c r="R730" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S730" s="219"/>
@@ -58898,7 +58903,7 @@
       <c r="P731" s="217"/>
       <c r="Q731" s="217"/>
       <c r="R731" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S731" s="210"/>
@@ -58927,7 +58932,7 @@
       <c r="P732" s="225"/>
       <c r="Q732" s="225"/>
       <c r="R732" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S732" s="219"/>
@@ -58956,7 +58961,7 @@
       <c r="P733" s="217"/>
       <c r="Q733" s="217"/>
       <c r="R733" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S733" s="210"/>
@@ -58985,7 +58990,7 @@
       <c r="P734" s="225"/>
       <c r="Q734" s="225"/>
       <c r="R734" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S734" s="219"/>
@@ -59014,7 +59019,7 @@
       <c r="P735" s="217"/>
       <c r="Q735" s="217"/>
       <c r="R735" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S735" s="210"/>
@@ -59043,7 +59048,7 @@
       <c r="P736" s="225"/>
       <c r="Q736" s="225"/>
       <c r="R736" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S736" s="219"/>
@@ -59072,7 +59077,7 @@
       <c r="P737" s="217"/>
       <c r="Q737" s="217"/>
       <c r="R737" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S737" s="210"/>
@@ -59101,7 +59106,7 @@
       <c r="P738" s="225"/>
       <c r="Q738" s="225"/>
       <c r="R738" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S738" s="219"/>
@@ -59130,7 +59135,7 @@
       <c r="P739" s="217"/>
       <c r="Q739" s="217"/>
       <c r="R739" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S739" s="210"/>
@@ -59159,7 +59164,7 @@
       <c r="P740" s="225"/>
       <c r="Q740" s="225"/>
       <c r="R740" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S740" s="219"/>
@@ -59188,7 +59193,7 @@
       <c r="P741" s="217"/>
       <c r="Q741" s="217"/>
       <c r="R741" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S741" s="210"/>
@@ -59217,7 +59222,7 @@
       <c r="P742" s="225"/>
       <c r="Q742" s="225"/>
       <c r="R742" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S742" s="219"/>
@@ -59246,7 +59251,7 @@
       <c r="P743" s="217"/>
       <c r="Q743" s="217"/>
       <c r="R743" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S743" s="210"/>
@@ -59275,7 +59280,7 @@
       <c r="P744" s="225"/>
       <c r="Q744" s="225"/>
       <c r="R744" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S744" s="219"/>
@@ -59304,7 +59309,7 @@
       <c r="P745" s="217"/>
       <c r="Q745" s="217"/>
       <c r="R745" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S745" s="210"/>
@@ -59333,7 +59338,7 @@
       <c r="P746" s="225"/>
       <c r="Q746" s="225"/>
       <c r="R746" s="225" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S746" s="219"/>
@@ -59362,7 +59367,7 @@
       <c r="P747" s="217"/>
       <c r="Q747" s="217"/>
       <c r="R747" s="217" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S747" s="210"/>
@@ -59391,7 +59396,7 @@
       <c r="P748" s="225"/>
       <c r="Q748" s="225"/>
       <c r="R748" s="225" t="str">
-        <f t="shared" ref="R748" si="1">IF(B748="","",SUM(O748:Q748))</f>
+        <f t="shared" ref="R748" si="15">IF(B748="","",SUM(O748:Q748))</f>
         <v/>
       </c>
       <c r="S748" s="219"/>
@@ -64760,7 +64765,7 @@
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A5" s="115">
         <f>COUNTIF('Ações InCompany'!B:B,2026)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="116" t="s">
         <v>2877</v>
@@ -64774,7 +64779,7 @@
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
@@ -64931,7 +64936,7 @@
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.25</v>
+        <v>0.24390243902439024</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64952,7 +64957,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>7.4999999999999997E-2</v>
+        <v>7.3170731707317069E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64973,7 +64978,7 @@
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>0.12195121951219512</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -64994,7 +64999,7 @@
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>2.5000000000000001E-2</v>
+        <v>2.4390243902439025E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65015,7 +65020,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>0.05</v>
+        <v>4.878048780487805E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65036,7 +65041,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.17499999999999999</v>
+        <v>0.17073170731707318</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65057,7 +65062,7 @@
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>7.4999999999999997E-2</v>
+        <v>7.3170731707317069E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65078,7 +65083,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>2.5000000000000001E-2</v>
+        <v>2.4390243902439025E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65099,7 +65104,7 @@
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.15</v>
+        <v>0.14634146341463414</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65141,7 +65146,7 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>0.05</v>
+        <v>4.878048780487805E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65154,15 +65159,15 @@
       </c>
       <c r="C44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" s="149">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="150">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.4390243902439025E-2</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65175,11 +65180,11 @@
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>
@@ -68499,26 +68504,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052D3A7BF04652843BCB50FE90745AA50" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ef6274641b2f7d621af528393bef14e5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe686eaa-0658-4f15-b230-9e46c4d089fd" xmlns:ns3="91ce1707-6d34-452b-b217-9734c03e6729" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fa87a3bcf42251a9fb9988d55372596" ns2:_="" ns3:_="">
     <xsd:import namespace="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
@@ -68719,26 +68704,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
-    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -68755,4 +68741,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
+    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4936" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92512C2A-3FCF-4554-83D9-C0C35767D110}"/>
+  <xr:revisionPtr revIDLastSave="4951" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C374D43-3147-46B0-9D2D-EEF0D94A2C48}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6535" uniqueCount="2962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6545" uniqueCount="2965">
   <si>
     <t>ID</t>
   </si>
@@ -9054,6 +9054,15 @@
   </si>
   <si>
     <t>6761/2026</t>
+  </si>
+  <si>
+    <t>Introdução à Engenharia de Prompt - SEE</t>
+  </si>
+  <si>
+    <t>30/06/2026 e 02/07/2026</t>
+  </si>
+  <si>
+    <t>2026-048</t>
   </si>
 </sst>
 </file>
@@ -12965,7 +12974,7 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -12998,7 +13007,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -58106,16 +58115,32 @@
       <c r="D704" s="219" t="s">
         <v>2961</v>
       </c>
-      <c r="E704" s="220"/>
-      <c r="F704" s="221"/>
-      <c r="G704" s="218"/>
-      <c r="H704" s="222"/>
-      <c r="I704" s="223"/>
-      <c r="J704" s="223"/>
-      <c r="K704" s="219"/>
+      <c r="E704" s="220" t="s">
+        <v>2962</v>
+      </c>
+      <c r="F704" s="221" t="s">
+        <v>61</v>
+      </c>
+      <c r="G704" s="218" t="s">
+        <v>71</v>
+      </c>
+      <c r="H704" s="222" t="s">
+        <v>2963</v>
+      </c>
+      <c r="I704" s="223">
+        <v>46203</v>
+      </c>
+      <c r="J704" s="223">
+        <v>46205</v>
+      </c>
+      <c r="K704" s="219" t="s">
+        <v>34</v>
+      </c>
       <c r="L704" s="224"/>
       <c r="M704" s="215"/>
-      <c r="N704" s="226"/>
+      <c r="N704" s="226">
+        <v>20</v>
+      </c>
       <c r="O704" s="225"/>
       <c r="P704" s="225"/>
       <c r="Q704" s="225"/>
@@ -58123,8 +58148,12 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S704" s="219"/>
-      <c r="T704" s="218"/>
+      <c r="S704" s="219">
+        <v>8</v>
+      </c>
+      <c r="T704" s="104" t="s">
+        <v>2729</v>
+      </c>
       <c r="U704" s="203"/>
     </row>
     <row r="705" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -59625,7 +59654,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="98" cm="1">
-        <f t="array" ref="A2:J71">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
+        <f t="array" ref="A2:J73">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
         <v>2026</v>
       </c>
       <c r="B2" s="98" t="str">
@@ -59789,7 +59818,7 @@
         <v>5.2</v>
       </c>
       <c r="L4" cm="1">
-        <f t="array" ref="L4:Q39">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
+        <f t="array" ref="L4:Q40">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
         <v>2026</v>
       </c>
       <c r="M4" t="str">
@@ -59816,7 +59845,7 @@
         <v>1</v>
       </c>
       <c r="T4" cm="1">
-        <f t="array" ref="T4:T40">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
+        <f t="array" ref="T4:T41">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
         <v>0</v>
       </c>
       <c r="X4" t="s">
@@ -62451,11 +62480,29 @@
       <c r="J40" s="163">
         <v>0</v>
       </c>
-      <c r="R40" t="str">
-        <v/>
-      </c>
-      <c r="S40" t="str">
-        <v/>
+      <c r="L40">
+        <v>2026</v>
+      </c>
+      <c r="M40" t="str">
+        <v>2026-048</v>
+      </c>
+      <c r="N40" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="O40" t="str">
+        <v>Introdução à Engenharia de Prompt - SEE</v>
+      </c>
+      <c r="P40">
+        <v>8</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>Arthur Wú; Gustavo Takahashi</v>
+      </c>
+      <c r="R40">
+        <v>2</v>
+      </c>
+      <c r="S40">
+        <v>72</v>
       </c>
       <c r="T40">
         <v>70</v>
@@ -62510,6 +62557,9 @@
       <c r="S41" t="str">
         <v/>
       </c>
+      <c r="T41">
+        <v>72</v>
+      </c>
       <c r="X41" t="s">
         <v>2958</v>
       </c>
@@ -62610,6 +62660,15 @@
       <c r="S43" t="str">
         <v/>
       </c>
+      <c r="X43" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Y43" s="95" t="s">
+        <v>2711</v>
+      </c>
+      <c r="AA43">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44">
@@ -62648,6 +62707,15 @@
       <c r="S44" t="str">
         <v/>
       </c>
+      <c r="X44" t="s">
+        <v>2964</v>
+      </c>
+      <c r="Y44" s="95" t="s">
+        <v>2852</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A45">
@@ -63676,6 +63744,36 @@
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2026</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2026-048</v>
+      </c>
+      <c r="C72" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Introdução à Engenharia de Prompt - SEE</v>
+      </c>
+      <c r="E72">
+        <v>8</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Arthur Wú</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
+      </c>
+      <c r="H72">
+        <v>8</v>
+      </c>
+      <c r="I72">
+        <v>2.4</v>
+      </c>
+      <c r="J72">
+        <v>10.4</v>
+      </c>
       <c r="R72" t="str">
         <v/>
       </c>
@@ -63684,6 +63782,36 @@
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2026</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2026-048</v>
+      </c>
+      <c r="C73" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Introdução à Engenharia de Prompt - SEE</v>
+      </c>
+      <c r="E73">
+        <v>8</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Gustavo Takahashi</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73">
+        <v>8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>8</v>
+      </c>
       <c r="R73" t="str">
         <v/>
       </c>
@@ -64928,15 +65056,15 @@
       </c>
       <c r="C33" s="127">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A33)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" s="117">
         <f t="shared" ref="D33:D44" si="0">B33+C33</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.24390243902439024</v>
+        <v>0.26829268292682928</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65159,15 +65287,15 @@
       </c>
       <c r="C44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="149">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="150">
         <f t="shared" si="1"/>
-        <v>2.4390243902439025E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65854,11 +65982,11 @@
       </c>
       <c r="B8" s="103">
         <f>IF($A8="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A8))</f>
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C8" s="103">
         <f>IF($A8="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A8))</f>
-        <v>10.199999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="D8" s="256">
         <f>IF($A8="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A8))</f>
@@ -65866,11 +65994,11 @@
       </c>
       <c r="E8" s="241">
         <f>IF($A8="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A8)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A8))</f>
-        <v>43.2</v>
+        <v>53.6</v>
       </c>
       <c r="F8" s="101">
         <f>IF($A8="","",COUNTIFS('GECC 2026'!F$2:F$200,$A8))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -66129,7 +66257,7 @@
       </c>
       <c r="B19" s="103">
         <f>IF($A19="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A19))</f>
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C19" s="103">
         <f>IF($A19="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A19))</f>
@@ -66141,11 +66269,11 @@
       </c>
       <c r="E19" s="241">
         <f>IF($A19="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A19)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A19))</f>
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F19" s="101">
         <f>IF($A19="","",COUNTIFS('GECC 2026'!F$2:F$200,$A19))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -68024,11 +68152,11 @@
       </c>
       <c r="B105" s="243">
         <f>SUM(B5:B100)</f>
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="C105" s="243">
         <f>SUM(C5:C100)</f>
-        <v>377.7</v>
+        <v>380.09999999999997</v>
       </c>
       <c r="D105" s="256">
         <f>IF($A105="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A105))</f>
@@ -68040,7 +68168,7 @@
       </c>
       <c r="F105" s="244">
         <f>SUM(F5:F100)</f>
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4951" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C374D43-3147-46B0-9D2D-EEF0D94A2C48}"/>
+  <xr:revisionPtr revIDLastSave="4952" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B86F03D-09AA-42A2-9956-43D22E40A03F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -14975,6 +14975,14 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}" name="Tabela2" displayName="Tabela2" ref="B1:T684" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="B1:T684" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}">
@@ -15386,7 +15394,7 @@
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
       <c r="R2" s="23">
-        <f t="shared" ref="R2:R65" si="0">SUM(O2:Q2)</f>
+        <f>SUM(O2:Q2)</f>
         <v>20</v>
       </c>
       <c r="S2" s="22">
@@ -15437,7 +15445,7 @@
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O3:Q3)</f>
         <v>16</v>
       </c>
       <c r="S3" s="24">
@@ -15488,7 +15496,7 @@
       <c r="P4" s="23"/>
       <c r="Q4" s="23"/>
       <c r="R4" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O4:Q4)</f>
         <v>24</v>
       </c>
       <c r="S4" s="22">
@@ -15539,7 +15547,7 @@
       <c r="P5" s="25"/>
       <c r="Q5" s="25"/>
       <c r="R5" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O5:Q5)</f>
         <v>16</v>
       </c>
       <c r="S5" s="24">
@@ -15590,7 +15598,7 @@
       <c r="P6" s="23"/>
       <c r="Q6" s="23"/>
       <c r="R6" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O6:Q6)</f>
         <v>40</v>
       </c>
       <c r="S6" s="22">
@@ -15641,7 +15649,7 @@
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
       <c r="R7" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O7:Q7)</f>
         <v>30</v>
       </c>
       <c r="S7" s="24">
@@ -15690,7 +15698,7 @@
       <c r="P8" s="23"/>
       <c r="Q8" s="23"/>
       <c r="R8" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O8:Q8)</f>
         <v>24</v>
       </c>
       <c r="S8" s="22">
@@ -15741,7 +15749,7 @@
       </c>
       <c r="Q9" s="25"/>
       <c r="R9" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O9:Q9)</f>
         <v>37</v>
       </c>
       <c r="S9" s="24">
@@ -15792,7 +15800,7 @@
       </c>
       <c r="Q10" s="23"/>
       <c r="R10" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O10:Q10)</f>
         <v>58</v>
       </c>
       <c r="S10" s="22">
@@ -15845,7 +15853,7 @@
       <c r="P11" s="25"/>
       <c r="Q11" s="25"/>
       <c r="R11" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O11:Q11)</f>
         <v>25</v>
       </c>
       <c r="S11" s="24">
@@ -15900,7 +15908,7 @@
       </c>
       <c r="Q12" s="23"/>
       <c r="R12" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O12:Q12)</f>
         <v>85</v>
       </c>
       <c r="S12" s="22">
@@ -15955,7 +15963,7 @@
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
       <c r="R13" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O13:Q13)</f>
         <v>19</v>
       </c>
       <c r="S13" s="24">
@@ -16010,7 +16018,7 @@
       </c>
       <c r="Q14" s="23"/>
       <c r="R14" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O14:Q14)</f>
         <v>89</v>
       </c>
       <c r="S14" s="22">
@@ -16065,7 +16073,7 @@
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
       <c r="R15" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O15:Q15)</f>
         <v>37</v>
       </c>
       <c r="S15" s="24">
@@ -16122,7 +16130,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O16:Q16)</f>
         <v>0</v>
       </c>
       <c r="S16" s="22">
@@ -16175,7 +16183,7 @@
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
       <c r="R17" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O17:Q17)</f>
         <v>30</v>
       </c>
       <c r="S17" s="24">
@@ -16230,7 +16238,7 @@
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
       <c r="R18" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O18:Q18)</f>
         <v>30</v>
       </c>
       <c r="S18" s="22">
@@ -16285,7 +16293,7 @@
       <c r="P19" s="25"/>
       <c r="Q19" s="25"/>
       <c r="R19" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O19:Q19)</f>
         <v>15</v>
       </c>
       <c r="S19" s="24">
@@ -16340,7 +16348,7 @@
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
       <c r="R20" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O20:Q20)</f>
         <v>14</v>
       </c>
       <c r="S20" s="22">
@@ -16395,7 +16403,7 @@
       <c r="P21" s="25"/>
       <c r="Q21" s="25"/>
       <c r="R21" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O21:Q21)</f>
         <v>14</v>
       </c>
       <c r="S21" s="24">
@@ -16450,7 +16458,7 @@
       </c>
       <c r="Q22" s="23"/>
       <c r="R22" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O22:Q22)</f>
         <v>49</v>
       </c>
       <c r="S22" s="22">
@@ -16505,7 +16513,7 @@
       <c r="P23" s="25"/>
       <c r="Q23" s="25"/>
       <c r="R23" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O23:Q23)</f>
         <v>43</v>
       </c>
       <c r="S23" s="24">
@@ -16560,7 +16568,7 @@
       <c r="P24" s="23"/>
       <c r="Q24" s="23"/>
       <c r="R24" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O24:Q24)</f>
         <v>25</v>
       </c>
       <c r="S24" s="22">
@@ -16615,7 +16623,7 @@
       <c r="P25" s="25"/>
       <c r="Q25" s="25"/>
       <c r="R25" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O25:Q25)</f>
         <v>35</v>
       </c>
       <c r="S25" s="24">
@@ -16670,7 +16678,7 @@
       <c r="P26" s="23"/>
       <c r="Q26" s="23"/>
       <c r="R26" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O26:Q26)</f>
         <v>35</v>
       </c>
       <c r="S26" s="22">
@@ -16723,7 +16731,7 @@
       <c r="P27" s="25"/>
       <c r="Q27" s="25"/>
       <c r="R27" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O27:Q27)</f>
         <v>87</v>
       </c>
       <c r="S27" s="24"/>
@@ -16774,7 +16782,7 @@
         <v>46</v>
       </c>
       <c r="R28" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O28:Q28)</f>
         <v>46</v>
       </c>
       <c r="S28" s="22">
@@ -16829,7 +16837,7 @@
       <c r="P29" s="25"/>
       <c r="Q29" s="25"/>
       <c r="R29" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O29:Q29)</f>
         <v>15</v>
       </c>
       <c r="S29" s="24">
@@ -16884,7 +16892,7 @@
       </c>
       <c r="Q30" s="23"/>
       <c r="R30" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O30:Q30)</f>
         <v>54</v>
       </c>
       <c r="S30" s="22">
@@ -16937,7 +16945,7 @@
       <c r="P31" s="25"/>
       <c r="Q31" s="25"/>
       <c r="R31" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O31:Q31)</f>
         <v>52</v>
       </c>
       <c r="S31" s="24">
@@ -16990,7 +16998,7 @@
         <v>46</v>
       </c>
       <c r="R32" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O32:Q32)</f>
         <v>46</v>
       </c>
       <c r="S32" s="22">
@@ -17043,7 +17051,7 @@
       <c r="P33" s="25"/>
       <c r="Q33" s="25"/>
       <c r="R33" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O33:Q33)</f>
         <v>14</v>
       </c>
       <c r="S33" s="24">
@@ -17094,7 +17102,7 @@
       <c r="P34" s="23"/>
       <c r="Q34" s="23"/>
       <c r="R34" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O34:Q34)</f>
         <v>25</v>
       </c>
       <c r="S34" s="22">
@@ -17145,7 +17153,7 @@
       <c r="P35" s="25"/>
       <c r="Q35" s="25"/>
       <c r="R35" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O35:Q35)</f>
         <v>17</v>
       </c>
       <c r="S35" s="24">
@@ -17200,7 +17208,7 @@
       </c>
       <c r="Q36" s="23"/>
       <c r="R36" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O36:Q36)</f>
         <v>75</v>
       </c>
       <c r="S36" s="22">
@@ -17255,7 +17263,7 @@
       </c>
       <c r="Q37" s="25"/>
       <c r="R37" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O37:Q37)</f>
         <v>18</v>
       </c>
       <c r="S37" s="24">
@@ -17310,7 +17318,7 @@
       <c r="P38" s="23"/>
       <c r="Q38" s="23"/>
       <c r="R38" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O38:Q38)</f>
         <v>33</v>
       </c>
       <c r="S38" s="22">
@@ -17365,7 +17373,7 @@
       </c>
       <c r="Q39" s="25"/>
       <c r="R39" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O39:Q39)</f>
         <v>55</v>
       </c>
       <c r="S39" s="24">
@@ -17420,7 +17428,7 @@
         <v>45</v>
       </c>
       <c r="R40" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O40:Q40)</f>
         <v>45</v>
       </c>
       <c r="S40" s="22">
@@ -17475,7 +17483,7 @@
       <c r="P41" s="25"/>
       <c r="Q41" s="25"/>
       <c r="R41" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O41:Q41)</f>
         <v>15</v>
       </c>
       <c r="S41" s="24">
@@ -17530,7 +17538,7 @@
         <v>21</v>
       </c>
       <c r="R42" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O42:Q42)</f>
         <v>21</v>
       </c>
       <c r="S42" s="22">
@@ -17585,7 +17593,7 @@
       <c r="P43" s="25"/>
       <c r="Q43" s="25"/>
       <c r="R43" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O43:Q43)</f>
         <v>40</v>
       </c>
       <c r="S43" s="24">
@@ -17640,7 +17648,7 @@
       </c>
       <c r="Q44" s="23"/>
       <c r="R44" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O44:Q44)</f>
         <v>45</v>
       </c>
       <c r="S44" s="22">
@@ -17695,7 +17703,7 @@
       <c r="P45" s="25"/>
       <c r="Q45" s="25"/>
       <c r="R45" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O45:Q45)</f>
         <v>13</v>
       </c>
       <c r="S45" s="24">
@@ -17750,7 +17758,7 @@
       <c r="P46" s="23"/>
       <c r="Q46" s="23"/>
       <c r="R46" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O46:Q46)</f>
         <v>35</v>
       </c>
       <c r="S46" s="22">
@@ -17807,7 +17815,7 @@
       </c>
       <c r="Q47" s="25"/>
       <c r="R47" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O47:Q47)</f>
         <v>71</v>
       </c>
       <c r="S47" s="24">
@@ -17866,7 +17874,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O48:Q48)</f>
         <v>329</v>
       </c>
       <c r="S48" s="22">
@@ -17921,7 +17929,7 @@
       <c r="P49" s="25"/>
       <c r="Q49" s="25"/>
       <c r="R49" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O49:Q49)</f>
         <v>26</v>
       </c>
       <c r="S49" s="24">
@@ -17976,7 +17984,7 @@
       <c r="P50" s="23"/>
       <c r="Q50" s="23"/>
       <c r="R50" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O50:Q50)</f>
         <v>35</v>
       </c>
       <c r="S50" s="22">
@@ -18031,7 +18039,7 @@
       </c>
       <c r="Q51" s="25"/>
       <c r="R51" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O51:Q51)</f>
         <v>46</v>
       </c>
       <c r="S51" s="24">
@@ -18086,7 +18094,7 @@
       </c>
       <c r="Q52" s="23"/>
       <c r="R52" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O52:Q52)</f>
         <v>52</v>
       </c>
       <c r="S52" s="22">
@@ -18141,7 +18149,7 @@
       <c r="P53" s="25"/>
       <c r="Q53" s="25"/>
       <c r="R53" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O53:Q53)</f>
         <v>34</v>
       </c>
       <c r="S53" s="24">
@@ -18196,7 +18204,7 @@
       <c r="P54" s="23"/>
       <c r="Q54" s="23"/>
       <c r="R54" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O54:Q54)</f>
         <v>27</v>
       </c>
       <c r="S54" s="22">
@@ -18251,7 +18259,7 @@
       <c r="P55" s="25"/>
       <c r="Q55" s="25"/>
       <c r="R55" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O55:Q55)</f>
         <v>16</v>
       </c>
       <c r="S55" s="24">
@@ -18306,7 +18314,7 @@
       </c>
       <c r="Q56" s="23"/>
       <c r="R56" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O56:Q56)</f>
         <v>55</v>
       </c>
       <c r="S56" s="22">
@@ -18361,7 +18369,7 @@
       <c r="P57" s="25"/>
       <c r="Q57" s="25"/>
       <c r="R57" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O57:Q57)</f>
         <v>14</v>
       </c>
       <c r="S57" s="24">
@@ -18416,7 +18424,7 @@
       </c>
       <c r="Q58" s="23"/>
       <c r="R58" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O58:Q58)</f>
         <v>47</v>
       </c>
       <c r="S58" s="22">
@@ -18471,7 +18479,7 @@
       <c r="P59" s="25"/>
       <c r="Q59" s="25"/>
       <c r="R59" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O59:Q59)</f>
         <v>31</v>
       </c>
       <c r="S59" s="24">
@@ -18526,7 +18534,7 @@
       </c>
       <c r="Q60" s="23"/>
       <c r="R60" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O60:Q60)</f>
         <v>28</v>
       </c>
       <c r="S60" s="22">
@@ -18581,7 +18589,7 @@
       </c>
       <c r="Q61" s="25"/>
       <c r="R61" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O61:Q61)</f>
         <v>34</v>
       </c>
       <c r="S61" s="24">
@@ -18636,7 +18644,7 @@
       </c>
       <c r="Q62" s="23"/>
       <c r="R62" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O62:Q62)</f>
         <v>60</v>
       </c>
       <c r="S62" s="22">
@@ -18691,7 +18699,7 @@
       <c r="P63" s="25"/>
       <c r="Q63" s="25"/>
       <c r="R63" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O63:Q63)</f>
         <v>29</v>
       </c>
       <c r="S63" s="24">
@@ -18746,7 +18754,7 @@
       <c r="P64" s="23"/>
       <c r="Q64" s="23"/>
       <c r="R64" s="23">
-        <f t="shared" si="0"/>
+        <f>SUM(O64:Q64)</f>
         <v>26</v>
       </c>
       <c r="S64" s="22">
@@ -18801,7 +18809,7 @@
       </c>
       <c r="Q65" s="25"/>
       <c r="R65" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(O65:Q65)</f>
         <v>47</v>
       </c>
       <c r="S65" s="24">
@@ -18856,7 +18864,7 @@
       <c r="P66" s="23"/>
       <c r="Q66" s="23"/>
       <c r="R66" s="23">
-        <f t="shared" ref="R66:R129" si="1">SUM(O66:Q66)</f>
+        <f>SUM(O66:Q66)</f>
         <v>20</v>
       </c>
       <c r="S66" s="22">
@@ -18911,7 +18919,7 @@
       </c>
       <c r="Q67" s="25"/>
       <c r="R67" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O67:Q67)</f>
         <v>43</v>
       </c>
       <c r="S67" s="24">
@@ -18966,7 +18974,7 @@
       <c r="P68" s="23"/>
       <c r="Q68" s="23"/>
       <c r="R68" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O68:Q68)</f>
         <v>15</v>
       </c>
       <c r="S68" s="22">
@@ -19021,7 +19029,7 @@
       <c r="P69" s="25"/>
       <c r="Q69" s="25"/>
       <c r="R69" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O69:Q69)</f>
         <v>29</v>
       </c>
       <c r="S69" s="24">
@@ -19076,7 +19084,7 @@
       </c>
       <c r="Q70" s="23"/>
       <c r="R70" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O70:Q70)</f>
         <v>46</v>
       </c>
       <c r="S70" s="22">
@@ -19131,7 +19139,7 @@
       <c r="P71" s="25"/>
       <c r="Q71" s="25"/>
       <c r="R71" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O71:Q71)</f>
         <v>14</v>
       </c>
       <c r="S71" s="24">
@@ -19186,7 +19194,7 @@
       <c r="P72" s="23"/>
       <c r="Q72" s="23"/>
       <c r="R72" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O72:Q72)</f>
         <v>12</v>
       </c>
       <c r="S72" s="22">
@@ -19241,7 +19249,7 @@
       <c r="P73" s="25"/>
       <c r="Q73" s="25"/>
       <c r="R73" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O73:Q73)</f>
         <v>18</v>
       </c>
       <c r="S73" s="24">
@@ -19296,7 +19304,7 @@
       <c r="P74" s="23"/>
       <c r="Q74" s="23"/>
       <c r="R74" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O74:Q74)</f>
         <v>30</v>
       </c>
       <c r="S74" s="22">
@@ -19351,7 +19359,7 @@
         <v>37</v>
       </c>
       <c r="R75" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O75:Q75)</f>
         <v>37</v>
       </c>
       <c r="S75" s="24">
@@ -19406,7 +19414,7 @@
       </c>
       <c r="Q76" s="23"/>
       <c r="R76" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O76:Q76)</f>
         <v>47</v>
       </c>
       <c r="S76" s="22">
@@ -19461,7 +19469,7 @@
       <c r="P77" s="25"/>
       <c r="Q77" s="25"/>
       <c r="R77" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O77:Q77)</f>
         <v>30</v>
       </c>
       <c r="S77" s="24">
@@ -19516,7 +19524,7 @@
       <c r="P78" s="23"/>
       <c r="Q78" s="23"/>
       <c r="R78" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O78:Q78)</f>
         <v>19</v>
       </c>
       <c r="S78" s="22">
@@ -19571,7 +19579,7 @@
       </c>
       <c r="Q79" s="25"/>
       <c r="R79" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O79:Q79)</f>
         <v>37</v>
       </c>
       <c r="S79" s="24">
@@ -19626,7 +19634,7 @@
       <c r="P80" s="23"/>
       <c r="Q80" s="23"/>
       <c r="R80" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O80:Q80)</f>
         <v>19</v>
       </c>
       <c r="S80" s="22">
@@ -19681,7 +19689,7 @@
       <c r="P81" s="25"/>
       <c r="Q81" s="25"/>
       <c r="R81" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O81:Q81)</f>
         <v>20</v>
       </c>
       <c r="S81" s="24">
@@ -19736,7 +19744,7 @@
       <c r="P82" s="23"/>
       <c r="Q82" s="23"/>
       <c r="R82" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O82:Q82)</f>
         <v>50</v>
       </c>
       <c r="S82" s="22">
@@ -19791,7 +19799,7 @@
       <c r="P83" s="25"/>
       <c r="Q83" s="25"/>
       <c r="R83" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O83:Q83)</f>
         <v>17</v>
       </c>
       <c r="S83" s="24">
@@ -19846,7 +19854,7 @@
       </c>
       <c r="Q84" s="23"/>
       <c r="R84" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O84:Q84)</f>
         <v>25</v>
       </c>
       <c r="S84" s="22">
@@ -19901,7 +19909,7 @@
         <v>49</v>
       </c>
       <c r="R85" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O85:Q85)</f>
         <v>49</v>
       </c>
       <c r="S85" s="24">
@@ -19956,7 +19964,7 @@
       </c>
       <c r="Q86" s="23"/>
       <c r="R86" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O86:Q86)</f>
         <v>34</v>
       </c>
       <c r="S86" s="22">
@@ -20011,7 +20019,7 @@
       <c r="P87" s="25"/>
       <c r="Q87" s="25"/>
       <c r="R87" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O87:Q87)</f>
         <v>19</v>
       </c>
       <c r="S87" s="24">
@@ -20070,7 +20078,7 @@
         <v>0</v>
       </c>
       <c r="R88" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O88:Q88)</f>
         <v>312</v>
       </c>
       <c r="S88" s="22">
@@ -20125,7 +20133,7 @@
       </c>
       <c r="Q89" s="25"/>
       <c r="R89" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O89:Q89)</f>
         <v>57</v>
       </c>
       <c r="S89" s="24">
@@ -20180,7 +20188,7 @@
       </c>
       <c r="Q90" s="23"/>
       <c r="R90" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O90:Q90)</f>
         <v>50</v>
       </c>
       <c r="S90" s="22">
@@ -20235,7 +20243,7 @@
       <c r="P91" s="25"/>
       <c r="Q91" s="25"/>
       <c r="R91" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O91:Q91)</f>
         <v>18</v>
       </c>
       <c r="S91" s="24">
@@ -20290,7 +20298,7 @@
       <c r="P92" s="23"/>
       <c r="Q92" s="23"/>
       <c r="R92" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O92:Q92)</f>
         <v>18</v>
       </c>
       <c r="S92" s="22">
@@ -20345,7 +20353,7 @@
       </c>
       <c r="Q93" s="25"/>
       <c r="R93" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O93:Q93)</f>
         <v>40</v>
       </c>
       <c r="S93" s="24">
@@ -20400,7 +20408,7 @@
       </c>
       <c r="Q94" s="23"/>
       <c r="R94" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O94:Q94)</f>
         <v>37</v>
       </c>
       <c r="S94" s="22">
@@ -20455,7 +20463,7 @@
         <v>96</v>
       </c>
       <c r="R95" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O95:Q95)</f>
         <v>96</v>
       </c>
       <c r="S95" s="24">
@@ -20510,7 +20518,7 @@
       <c r="P96" s="23"/>
       <c r="Q96" s="23"/>
       <c r="R96" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O96:Q96)</f>
         <v>19</v>
       </c>
       <c r="S96" s="22">
@@ -20565,7 +20573,7 @@
       </c>
       <c r="Q97" s="25"/>
       <c r="R97" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O97:Q97)</f>
         <v>65</v>
       </c>
       <c r="S97" s="24">
@@ -20620,7 +20628,7 @@
       <c r="P98" s="23"/>
       <c r="Q98" s="23"/>
       <c r="R98" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O98:Q98)</f>
         <v>19</v>
       </c>
       <c r="S98" s="22">
@@ -20675,7 +20683,7 @@
       <c r="P99" s="25"/>
       <c r="Q99" s="25"/>
       <c r="R99" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O99:Q99)</f>
         <v>19</v>
       </c>
       <c r="S99" s="24">
@@ -20730,7 +20738,7 @@
       <c r="P100" s="23"/>
       <c r="Q100" s="23"/>
       <c r="R100" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O100:Q100)</f>
         <v>20</v>
       </c>
       <c r="S100" s="22">
@@ -20785,7 +20793,7 @@
       </c>
       <c r="Q101" s="25"/>
       <c r="R101" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O101:Q101)</f>
         <v>63</v>
       </c>
       <c r="S101" s="24">
@@ -20840,7 +20848,7 @@
       <c r="P102" s="23"/>
       <c r="Q102" s="23"/>
       <c r="R102" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O102:Q102)</f>
         <v>18</v>
       </c>
       <c r="S102" s="22">
@@ -20895,7 +20903,7 @@
       <c r="P103" s="25"/>
       <c r="Q103" s="25"/>
       <c r="R103" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O103:Q103)</f>
         <v>31</v>
       </c>
       <c r="S103" s="24">
@@ -20950,7 +20958,7 @@
       </c>
       <c r="Q104" s="23"/>
       <c r="R104" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O104:Q104)</f>
         <v>59</v>
       </c>
       <c r="S104" s="22">
@@ -21005,7 +21013,7 @@
       <c r="P105" s="25"/>
       <c r="Q105" s="25"/>
       <c r="R105" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O105:Q105)</f>
         <v>25</v>
       </c>
       <c r="S105" s="24">
@@ -21060,7 +21068,7 @@
       </c>
       <c r="Q106" s="23"/>
       <c r="R106" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O106:Q106)</f>
         <v>34</v>
       </c>
       <c r="S106" s="22">
@@ -21115,7 +21123,7 @@
       <c r="P107" s="25"/>
       <c r="Q107" s="25"/>
       <c r="R107" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O107:Q107)</f>
         <v>19</v>
       </c>
       <c r="S107" s="24">
@@ -21174,7 +21182,7 @@
         <v>0</v>
       </c>
       <c r="R108" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O108:Q108)</f>
         <v>353</v>
       </c>
       <c r="S108" s="22">
@@ -21229,7 +21237,7 @@
       <c r="P109" s="25"/>
       <c r="Q109" s="25"/>
       <c r="R109" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O109:Q109)</f>
         <v>28</v>
       </c>
       <c r="S109" s="24">
@@ -21284,7 +21292,7 @@
       <c r="P110" s="23"/>
       <c r="Q110" s="23"/>
       <c r="R110" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O110:Q110)</f>
         <v>215</v>
       </c>
       <c r="S110" s="22">
@@ -21339,7 +21347,7 @@
       <c r="P111" s="25"/>
       <c r="Q111" s="25"/>
       <c r="R111" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O111:Q111)</f>
         <v>55</v>
       </c>
       <c r="S111" s="24">
@@ -21394,7 +21402,7 @@
       <c r="P112" s="23"/>
       <c r="Q112" s="23"/>
       <c r="R112" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O112:Q112)</f>
         <v>11</v>
       </c>
       <c r="S112" s="22">
@@ -21449,7 +21457,7 @@
       <c r="P113" s="25"/>
       <c r="Q113" s="25"/>
       <c r="R113" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O113:Q113)</f>
         <v>26</v>
       </c>
       <c r="S113" s="24">
@@ -21504,7 +21512,7 @@
       <c r="P114" s="23"/>
       <c r="Q114" s="23"/>
       <c r="R114" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O114:Q114)</f>
         <v>8</v>
       </c>
       <c r="S114" s="22">
@@ -21563,7 +21571,7 @@
         <v>0</v>
       </c>
       <c r="R115" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O115:Q115)</f>
         <v>38</v>
       </c>
       <c r="S115" s="24">
@@ -21624,7 +21632,7 @@
       </c>
       <c r="Q116" s="23"/>
       <c r="R116" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O116:Q116)</f>
         <v>18</v>
       </c>
       <c r="S116" s="22">
@@ -21685,7 +21693,7 @@
       </c>
       <c r="Q117" s="25"/>
       <c r="R117" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O117:Q117)</f>
         <v>45</v>
       </c>
       <c r="S117" s="24">
@@ -21746,7 +21754,7 @@
       </c>
       <c r="Q118" s="23"/>
       <c r="R118" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O118:Q118)</f>
         <v>45</v>
       </c>
       <c r="S118" s="22">
@@ -21807,7 +21815,7 @@
       </c>
       <c r="Q119" s="25"/>
       <c r="R119" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O119:Q119)</f>
         <v>44</v>
       </c>
       <c r="S119" s="24">
@@ -21868,7 +21876,7 @@
       </c>
       <c r="Q120" s="23"/>
       <c r="R120" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O120:Q120)</f>
         <v>50</v>
       </c>
       <c r="S120" s="22">
@@ -21929,7 +21937,7 @@
       </c>
       <c r="Q121" s="25"/>
       <c r="R121" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O121:Q121)</f>
         <v>41</v>
       </c>
       <c r="S121" s="24">
@@ -21990,7 +21998,7 @@
       </c>
       <c r="Q122" s="23"/>
       <c r="R122" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O122:Q122)</f>
         <v>44</v>
       </c>
       <c r="S122" s="22">
@@ -22051,7 +22059,7 @@
       </c>
       <c r="Q123" s="25"/>
       <c r="R123" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O123:Q123)</f>
         <v>40</v>
       </c>
       <c r="S123" s="24">
@@ -22112,7 +22120,7 @@
       </c>
       <c r="Q124" s="23"/>
       <c r="R124" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O124:Q124)</f>
         <v>12</v>
       </c>
       <c r="S124" s="22">
@@ -22173,7 +22181,7 @@
       </c>
       <c r="Q125" s="25"/>
       <c r="R125" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O125:Q125)</f>
         <v>19</v>
       </c>
       <c r="S125" s="24">
@@ -22234,7 +22242,7 @@
       </c>
       <c r="Q126" s="23"/>
       <c r="R126" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O126:Q126)</f>
         <v>14</v>
       </c>
       <c r="S126" s="22">
@@ -22295,7 +22303,7 @@
       </c>
       <c r="Q127" s="25"/>
       <c r="R127" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O127:Q127)</f>
         <v>19</v>
       </c>
       <c r="S127" s="24">
@@ -22356,7 +22364,7 @@
       </c>
       <c r="Q128" s="23"/>
       <c r="R128" s="23">
-        <f t="shared" si="1"/>
+        <f>SUM(O128:Q128)</f>
         <v>9</v>
       </c>
       <c r="S128" s="22">
@@ -22417,7 +22425,7 @@
       </c>
       <c r="Q129" s="25"/>
       <c r="R129" s="25">
-        <f t="shared" si="1"/>
+        <f>SUM(O129:Q129)</f>
         <v>45</v>
       </c>
       <c r="S129" s="24">
@@ -22478,7 +22486,7 @@
       </c>
       <c r="Q130" s="23"/>
       <c r="R130" s="23">
-        <f t="shared" ref="R130:R193" si="2">SUM(O130:Q130)</f>
+        <f>SUM(O130:Q130)</f>
         <v>25</v>
       </c>
       <c r="S130" s="22">
@@ -22539,7 +22547,7 @@
       </c>
       <c r="Q131" s="25"/>
       <c r="R131" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O131:Q131)</f>
         <v>15</v>
       </c>
       <c r="S131" s="24">
@@ -22600,7 +22608,7 @@
       </c>
       <c r="Q132" s="23"/>
       <c r="R132" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O132:Q132)</f>
         <v>26</v>
       </c>
       <c r="S132" s="22">
@@ -22661,7 +22669,7 @@
       </c>
       <c r="Q133" s="25"/>
       <c r="R133" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O133:Q133)</f>
         <v>16</v>
       </c>
       <c r="S133" s="24">
@@ -22722,7 +22730,7 @@
       </c>
       <c r="Q134" s="23"/>
       <c r="R134" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O134:Q134)</f>
         <v>15</v>
       </c>
       <c r="S134" s="22">
@@ -22783,7 +22791,7 @@
       </c>
       <c r="Q135" s="25"/>
       <c r="R135" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O135:Q135)</f>
         <v>14</v>
       </c>
       <c r="S135" s="24">
@@ -22844,7 +22852,7 @@
       </c>
       <c r="Q136" s="23"/>
       <c r="R136" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O136:Q136)</f>
         <v>182</v>
       </c>
       <c r="S136" s="22">
@@ -22905,7 +22913,7 @@
       </c>
       <c r="Q137" s="25"/>
       <c r="R137" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O137:Q137)</f>
         <v>34</v>
       </c>
       <c r="S137" s="24">
@@ -22968,7 +22976,7 @@
         <v>0</v>
       </c>
       <c r="R138" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O138:Q138)</f>
         <v>17</v>
       </c>
       <c r="S138" s="22">
@@ -23029,7 +23037,7 @@
       </c>
       <c r="Q139" s="25"/>
       <c r="R139" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O139:Q139)</f>
         <v>20</v>
       </c>
       <c r="S139" s="24">
@@ -23090,7 +23098,7 @@
       </c>
       <c r="Q140" s="23"/>
       <c r="R140" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O140:Q140)</f>
         <v>40</v>
       </c>
       <c r="S140" s="22">
@@ -23153,7 +23161,7 @@
         <v>0</v>
       </c>
       <c r="R141" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O141:Q141)</f>
         <v>12</v>
       </c>
       <c r="S141" s="24">
@@ -23214,7 +23222,7 @@
       </c>
       <c r="Q142" s="23"/>
       <c r="R142" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O142:Q142)</f>
         <v>12</v>
       </c>
       <c r="S142" s="22">
@@ -23275,7 +23283,7 @@
       </c>
       <c r="Q143" s="25"/>
       <c r="R143" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O143:Q143)</f>
         <v>19</v>
       </c>
       <c r="S143" s="24">
@@ -23336,7 +23344,7 @@
       </c>
       <c r="Q144" s="23"/>
       <c r="R144" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O144:Q144)</f>
         <v>12</v>
       </c>
       <c r="S144" s="22">
@@ -23399,7 +23407,7 @@
         <v>0</v>
       </c>
       <c r="R145" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O145:Q145)</f>
         <v>31</v>
       </c>
       <c r="S145" s="24">
@@ -23460,7 +23468,7 @@
       </c>
       <c r="Q146" s="23"/>
       <c r="R146" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O146:Q146)</f>
         <v>27</v>
       </c>
       <c r="S146" s="22">
@@ -23521,7 +23529,7 @@
         <v>0</v>
       </c>
       <c r="R147" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O147:Q147)</f>
         <v>54</v>
       </c>
       <c r="S147" s="24">
@@ -23582,7 +23590,7 @@
       </c>
       <c r="Q148" s="23"/>
       <c r="R148" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O148:Q148)</f>
         <v>9</v>
       </c>
       <c r="S148" s="22">
@@ -23643,7 +23651,7 @@
       </c>
       <c r="Q149" s="25"/>
       <c r="R149" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O149:Q149)</f>
         <v>38</v>
       </c>
       <c r="S149" s="24">
@@ -23704,7 +23712,7 @@
       </c>
       <c r="Q150" s="23"/>
       <c r="R150" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O150:Q150)</f>
         <v>62</v>
       </c>
       <c r="S150" s="22">
@@ -23765,7 +23773,7 @@
       </c>
       <c r="Q151" s="25"/>
       <c r="R151" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O151:Q151)</f>
         <v>13</v>
       </c>
       <c r="S151" s="24">
@@ -23826,7 +23834,7 @@
       </c>
       <c r="Q152" s="23"/>
       <c r="R152" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O152:Q152)</f>
         <v>8</v>
       </c>
       <c r="S152" s="22">
@@ -23887,7 +23895,7 @@
       </c>
       <c r="Q153" s="25"/>
       <c r="R153" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O153:Q153)</f>
         <v>20</v>
       </c>
       <c r="S153" s="24">
@@ -23950,7 +23958,7 @@
         <v>0</v>
       </c>
       <c r="R154" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O154:Q154)</f>
         <v>74</v>
       </c>
       <c r="S154" s="22">
@@ -24011,7 +24019,7 @@
       </c>
       <c r="Q155" s="25"/>
       <c r="R155" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O155:Q155)</f>
         <v>24</v>
       </c>
       <c r="S155" s="24">
@@ -24074,7 +24082,7 @@
         <v>0</v>
       </c>
       <c r="R156" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O156:Q156)</f>
         <v>21</v>
       </c>
       <c r="S156" s="22">
@@ -24137,7 +24145,7 @@
         <v>0</v>
       </c>
       <c r="R157" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O157:Q157)</f>
         <v>21</v>
       </c>
       <c r="S157" s="24">
@@ -24200,7 +24208,7 @@
         <v>0</v>
       </c>
       <c r="R158" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O158:Q158)</f>
         <v>13</v>
       </c>
       <c r="S158" s="22">
@@ -24263,7 +24271,7 @@
         <v>78</v>
       </c>
       <c r="R159" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O159:Q159)</f>
         <v>117</v>
       </c>
       <c r="S159" s="24">
@@ -24326,7 +24334,7 @@
         <v>0</v>
       </c>
       <c r="R160" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O160:Q160)</f>
         <v>20</v>
       </c>
       <c r="S160" s="22">
@@ -24390,7 +24398,7 @@
         <v>0</v>
       </c>
       <c r="R161" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O161:Q161)</f>
         <v>22</v>
       </c>
       <c r="S161" s="24">
@@ -24453,7 +24461,7 @@
         <v>0</v>
       </c>
       <c r="R162" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O162:Q162)</f>
         <v>21</v>
       </c>
       <c r="S162" s="22">
@@ -24516,7 +24524,7 @@
         <v>0</v>
       </c>
       <c r="R163" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O163:Q163)</f>
         <v>59</v>
       </c>
       <c r="S163" s="24">
@@ -24579,7 +24587,7 @@
         <v>0</v>
       </c>
       <c r="R164" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O164:Q164)</f>
         <v>24</v>
       </c>
       <c r="S164" s="22">
@@ -24642,7 +24650,7 @@
         <v>0</v>
       </c>
       <c r="R165" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O165:Q165)</f>
         <v>41</v>
       </c>
       <c r="S165" s="24">
@@ -24705,7 +24713,7 @@
         <v>0</v>
       </c>
       <c r="R166" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O166:Q166)</f>
         <v>35</v>
       </c>
       <c r="S166" s="22">
@@ -24768,7 +24776,7 @@
         <v>0</v>
       </c>
       <c r="R167" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O167:Q167)</f>
         <v>15</v>
       </c>
       <c r="S167" s="24">
@@ -24831,7 +24839,7 @@
         <v>0</v>
       </c>
       <c r="R168" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O168:Q168)</f>
         <v>23</v>
       </c>
       <c r="S168" s="22">
@@ -24894,7 +24902,7 @@
         <v>0</v>
       </c>
       <c r="R169" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O169:Q169)</f>
         <v>36</v>
       </c>
       <c r="S169" s="24">
@@ -24957,7 +24965,7 @@
         <v>0</v>
       </c>
       <c r="R170" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O170:Q170)</f>
         <v>84</v>
       </c>
       <c r="S170" s="22">
@@ -25020,7 +25028,7 @@
         <v>0</v>
       </c>
       <c r="R171" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O171:Q171)</f>
         <v>40</v>
       </c>
       <c r="S171" s="24">
@@ -25083,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="R172" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O172:Q172)</f>
         <v>40</v>
       </c>
       <c r="S172" s="22">
@@ -25146,7 +25154,7 @@
         <v>0</v>
       </c>
       <c r="R173" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O173:Q173)</f>
         <v>44</v>
       </c>
       <c r="S173" s="24">
@@ -25209,7 +25217,7 @@
         <v>0</v>
       </c>
       <c r="R174" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O174:Q174)</f>
         <v>31</v>
       </c>
       <c r="S174" s="22">
@@ -25272,7 +25280,7 @@
         <v>0</v>
       </c>
       <c r="R175" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O175:Q175)</f>
         <v>29</v>
       </c>
       <c r="S175" s="24">
@@ -25335,7 +25343,7 @@
         <v>97</v>
       </c>
       <c r="R176" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O176:Q176)</f>
         <v>119</v>
       </c>
       <c r="S176" s="22">
@@ -25399,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="R177" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O177:Q177)</f>
         <v>122</v>
       </c>
       <c r="S177" s="24">
@@ -25463,7 +25471,7 @@
         <v>0</v>
       </c>
       <c r="R178" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O178:Q178)</f>
         <v>116</v>
       </c>
       <c r="S178" s="22">
@@ -25527,7 +25535,7 @@
         <v>0</v>
       </c>
       <c r="R179" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O179:Q179)</f>
         <v>83</v>
       </c>
       <c r="S179" s="24">
@@ -25590,7 +25598,7 @@
         <v>0</v>
       </c>
       <c r="R180" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O180:Q180)</f>
         <v>69</v>
       </c>
       <c r="S180" s="22">
@@ -25653,7 +25661,7 @@
         <v>0</v>
       </c>
       <c r="R181" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O181:Q181)</f>
         <v>48</v>
       </c>
       <c r="S181" s="24">
@@ -25716,7 +25724,7 @@
         <v>0</v>
       </c>
       <c r="R182" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O182:Q182)</f>
         <v>19</v>
       </c>
       <c r="S182" s="22">
@@ -25779,7 +25787,7 @@
         <v>73</v>
       </c>
       <c r="R183" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O183:Q183)</f>
         <v>73</v>
       </c>
       <c r="S183" s="24">
@@ -25842,7 +25850,7 @@
         <v>0</v>
       </c>
       <c r="R184" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O184:Q184)</f>
         <v>94</v>
       </c>
       <c r="S184" s="22">
@@ -25905,7 +25913,7 @@
         <v>0</v>
       </c>
       <c r="R185" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O185:Q185)</f>
         <v>42</v>
       </c>
       <c r="S185" s="24">
@@ -25968,7 +25976,7 @@
         <v>0</v>
       </c>
       <c r="R186" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O186:Q186)</f>
         <v>32</v>
       </c>
       <c r="S186" s="22">
@@ -26031,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="R187" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O187:Q187)</f>
         <v>22</v>
       </c>
       <c r="S187" s="24">
@@ -26095,7 +26103,7 @@
         <v>0</v>
       </c>
       <c r="R188" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O188:Q188)</f>
         <v>590</v>
       </c>
       <c r="S188" s="22">
@@ -26159,7 +26167,7 @@
         <v>0</v>
       </c>
       <c r="R189" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O189:Q189)</f>
         <v>41</v>
       </c>
       <c r="S189" s="24">
@@ -26222,7 +26230,7 @@
         <v>0</v>
       </c>
       <c r="R190" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O190:Q190)</f>
         <v>80</v>
       </c>
       <c r="S190" s="22">
@@ -26286,7 +26294,7 @@
         <v>36</v>
       </c>
       <c r="R191" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O191:Q191)</f>
         <v>36</v>
       </c>
       <c r="S191" s="24">
@@ -26349,7 +26357,7 @@
         <v>0</v>
       </c>
       <c r="R192" s="23">
-        <f t="shared" si="2"/>
+        <f>SUM(O192:Q192)</f>
         <v>70</v>
       </c>
       <c r="S192" s="22">
@@ -26412,7 +26420,7 @@
         <v>0</v>
       </c>
       <c r="R193" s="25">
-        <f t="shared" si="2"/>
+        <f>SUM(O193:Q193)</f>
         <v>21</v>
       </c>
       <c r="S193" s="24">
@@ -26475,7 +26483,7 @@
         <v>0</v>
       </c>
       <c r="R194" s="23">
-        <f t="shared" ref="R194:R257" si="3">SUM(O194:Q194)</f>
+        <f>SUM(O194:Q194)</f>
         <v>20</v>
       </c>
       <c r="S194" s="22">
@@ -26538,7 +26546,7 @@
         <v>0</v>
       </c>
       <c r="R195" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O195:Q195)</f>
         <v>28</v>
       </c>
       <c r="S195" s="24">
@@ -26601,7 +26609,7 @@
         <v>0</v>
       </c>
       <c r="R196" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O196:Q196)</f>
         <v>25</v>
       </c>
       <c r="S196" s="22">
@@ -26664,7 +26672,7 @@
         <v>0</v>
       </c>
       <c r="R197" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O197:Q197)</f>
         <v>14</v>
       </c>
       <c r="S197" s="24">
@@ -26727,7 +26735,7 @@
         <v>0</v>
       </c>
       <c r="R198" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O198:Q198)</f>
         <v>46</v>
       </c>
       <c r="S198" s="22">
@@ -26790,7 +26798,7 @@
         <v>0</v>
       </c>
       <c r="R199" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O199:Q199)</f>
         <v>98</v>
       </c>
       <c r="S199" s="24">
@@ -26853,7 +26861,7 @@
         <v>44</v>
       </c>
       <c r="R200" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O200:Q200)</f>
         <v>50</v>
       </c>
       <c r="S200" s="22">
@@ -26916,7 +26924,7 @@
         <v>0</v>
       </c>
       <c r="R201" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O201:Q201)</f>
         <v>17</v>
       </c>
       <c r="S201" s="24">
@@ -26979,7 +26987,7 @@
         <v>0</v>
       </c>
       <c r="R202" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O202:Q202)</f>
         <v>53</v>
       </c>
       <c r="S202" s="22">
@@ -27042,7 +27050,7 @@
         <v>0</v>
       </c>
       <c r="R203" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O203:Q203)</f>
         <v>16</v>
       </c>
       <c r="S203" s="24">
@@ -27105,7 +27113,7 @@
         <v>59</v>
       </c>
       <c r="R204" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O204:Q204)</f>
         <v>59</v>
       </c>
       <c r="S204" s="22">
@@ -27168,7 +27176,7 @@
         <v>0</v>
       </c>
       <c r="R205" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O205:Q205)</f>
         <v>76</v>
       </c>
       <c r="S205" s="24">
@@ -27231,7 +27239,7 @@
         <v>0</v>
       </c>
       <c r="R206" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O206:Q206)</f>
         <v>33</v>
       </c>
       <c r="S206" s="22">
@@ -27294,7 +27302,7 @@
         <v>0</v>
       </c>
       <c r="R207" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O207:Q207)</f>
         <v>58</v>
       </c>
       <c r="S207" s="24">
@@ -27357,7 +27365,7 @@
         <v>37</v>
       </c>
       <c r="R208" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O208:Q208)</f>
         <v>60</v>
       </c>
       <c r="S208" s="22">
@@ -27420,7 +27428,7 @@
         <v>0</v>
       </c>
       <c r="R209" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O209:Q209)</f>
         <v>13</v>
       </c>
       <c r="S209" s="24">
@@ -27483,7 +27491,7 @@
         <v>0</v>
       </c>
       <c r="R210" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O210:Q210)</f>
         <v>14</v>
       </c>
       <c r="S210" s="22">
@@ -27546,7 +27554,7 @@
         <v>0</v>
       </c>
       <c r="R211" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O211:Q211)</f>
         <v>53</v>
       </c>
       <c r="S211" s="24">
@@ -27609,7 +27617,7 @@
         <v>0</v>
       </c>
       <c r="R212" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O212:Q212)</f>
         <v>105</v>
       </c>
       <c r="S212" s="22">
@@ -27672,7 +27680,7 @@
         <v>147</v>
       </c>
       <c r="R213" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O213:Q213)</f>
         <v>635</v>
       </c>
       <c r="S213" s="24">
@@ -27735,7 +27743,7 @@
         <v>0</v>
       </c>
       <c r="R214" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O214:Q214)</f>
         <v>34</v>
       </c>
       <c r="S214" s="22">
@@ -27798,7 +27806,7 @@
         <v>0</v>
       </c>
       <c r="R215" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O215:Q215)</f>
         <v>32</v>
       </c>
       <c r="S215" s="24">
@@ -27861,7 +27869,7 @@
         <v>0</v>
       </c>
       <c r="R216" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O216:Q216)</f>
         <v>10</v>
       </c>
       <c r="S216" s="22">
@@ -27924,7 +27932,7 @@
         <v>0</v>
       </c>
       <c r="R217" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O217:Q217)</f>
         <v>16</v>
       </c>
       <c r="S217" s="24">
@@ -27987,7 +27995,7 @@
         <v>0</v>
       </c>
       <c r="R218" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O218:Q218)</f>
         <v>20</v>
       </c>
       <c r="S218" s="22">
@@ -28051,7 +28059,7 @@
         <v>59</v>
       </c>
       <c r="R219" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O219:Q219)</f>
         <v>59</v>
       </c>
       <c r="S219" s="24">
@@ -28114,7 +28122,7 @@
         <v>0</v>
       </c>
       <c r="R220" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O220:Q220)</f>
         <v>70</v>
       </c>
       <c r="S220" s="22">
@@ -28177,7 +28185,7 @@
         <v>30</v>
       </c>
       <c r="R221" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O221:Q221)</f>
         <v>30</v>
       </c>
       <c r="S221" s="24">
@@ -28240,7 +28248,7 @@
         <v>0</v>
       </c>
       <c r="R222" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O222:Q222)</f>
         <v>14</v>
       </c>
       <c r="S222" s="22">
@@ -28303,7 +28311,7 @@
         <v>1</v>
       </c>
       <c r="R223" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O223:Q223)</f>
         <v>29</v>
       </c>
       <c r="S223" s="24">
@@ -28366,7 +28374,7 @@
         <v>0</v>
       </c>
       <c r="R224" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O224:Q224)</f>
         <v>37</v>
       </c>
       <c r="S224" s="22">
@@ -28429,7 +28437,7 @@
         <v>0</v>
       </c>
       <c r="R225" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O225:Q225)</f>
         <v>24</v>
       </c>
       <c r="S225" s="24">
@@ -28492,7 +28500,7 @@
         <v>0</v>
       </c>
       <c r="R226" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O226:Q226)</f>
         <v>32</v>
       </c>
       <c r="S226" s="22">
@@ -28555,7 +28563,7 @@
         <v>0</v>
       </c>
       <c r="R227" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O227:Q227)</f>
         <v>14</v>
       </c>
       <c r="S227" s="24">
@@ -28618,7 +28626,7 @@
         <v>0</v>
       </c>
       <c r="R228" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O228:Q228)</f>
         <v>31</v>
       </c>
       <c r="S228" s="22">
@@ -28681,7 +28689,7 @@
         <v>0</v>
       </c>
       <c r="R229" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O229:Q229)</f>
         <v>30</v>
       </c>
       <c r="S229" s="24">
@@ -28744,7 +28752,7 @@
         <v>5</v>
       </c>
       <c r="R230" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O230:Q230)</f>
         <v>52</v>
       </c>
       <c r="S230" s="22">
@@ -28807,7 +28815,7 @@
         <v>0</v>
       </c>
       <c r="R231" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O231:Q231)</f>
         <v>89</v>
       </c>
       <c r="S231" s="24">
@@ -28870,7 +28878,7 @@
         <v>0</v>
       </c>
       <c r="R232" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O232:Q232)</f>
         <v>13</v>
       </c>
       <c r="S232" s="22">
@@ -28933,7 +28941,7 @@
         <v>0</v>
       </c>
       <c r="R233" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O233:Q233)</f>
         <v>38</v>
       </c>
       <c r="S233" s="24">
@@ -28996,7 +29004,7 @@
         <v>0</v>
       </c>
       <c r="R234" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O234:Q234)</f>
         <v>44</v>
       </c>
       <c r="S234" s="22">
@@ -29059,7 +29067,7 @@
         <v>0</v>
       </c>
       <c r="R235" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O235:Q235)</f>
         <v>21</v>
       </c>
       <c r="S235" s="24">
@@ -29122,7 +29130,7 @@
         <v>0</v>
       </c>
       <c r="R236" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O236:Q236)</f>
         <v>45</v>
       </c>
       <c r="S236" s="22">
@@ -29185,7 +29193,7 @@
         <v>0</v>
       </c>
       <c r="R237" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O237:Q237)</f>
         <v>70</v>
       </c>
       <c r="S237" s="24">
@@ -29248,7 +29256,7 @@
         <v>0</v>
       </c>
       <c r="R238" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O238:Q238)</f>
         <v>15</v>
       </c>
       <c r="S238" s="22">
@@ -29311,7 +29319,7 @@
         <v>51</v>
       </c>
       <c r="R239" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O239:Q239)</f>
         <v>51</v>
       </c>
       <c r="S239" s="24">
@@ -29375,7 +29383,7 @@
         <v>31</v>
       </c>
       <c r="R240" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O240:Q240)</f>
         <v>31</v>
       </c>
       <c r="S240" s="22">
@@ -29438,7 +29446,7 @@
         <v>0</v>
       </c>
       <c r="R241" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O241:Q241)</f>
         <v>140</v>
       </c>
       <c r="S241" s="24">
@@ -29501,7 +29509,7 @@
         <v>0</v>
       </c>
       <c r="R242" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O242:Q242)</f>
         <v>15</v>
       </c>
       <c r="S242" s="22">
@@ -29564,7 +29572,7 @@
         <v>0</v>
       </c>
       <c r="R243" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O243:Q243)</f>
         <v>18</v>
       </c>
       <c r="S243" s="24">
@@ -29627,7 +29635,7 @@
         <v>0</v>
       </c>
       <c r="R244" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O244:Q244)</f>
         <v>55</v>
       </c>
       <c r="S244" s="22">
@@ -29690,7 +29698,7 @@
         <v>120</v>
       </c>
       <c r="R245" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O245:Q245)</f>
         <v>120</v>
       </c>
       <c r="S245" s="24">
@@ -29753,7 +29761,7 @@
         <v>22</v>
       </c>
       <c r="R246" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O246:Q246)</f>
         <v>34</v>
       </c>
       <c r="S246" s="22">
@@ -29816,7 +29824,7 @@
         <v>0</v>
       </c>
       <c r="R247" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O247:Q247)</f>
         <v>37</v>
       </c>
       <c r="S247" s="24">
@@ -29879,7 +29887,7 @@
         <v>0</v>
       </c>
       <c r="R248" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O248:Q248)</f>
         <v>6</v>
       </c>
       <c r="S248" s="22">
@@ -29942,7 +29950,7 @@
         <v>0</v>
       </c>
       <c r="R249" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O249:Q249)</f>
         <v>25</v>
       </c>
       <c r="S249" s="24">
@@ -30005,7 +30013,7 @@
         <v>0</v>
       </c>
       <c r="R250" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O250:Q250)</f>
         <v>26</v>
       </c>
       <c r="S250" s="22">
@@ -30068,7 +30076,7 @@
         <v>56</v>
       </c>
       <c r="R251" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O251:Q251)</f>
         <v>56</v>
       </c>
       <c r="S251" s="24">
@@ -30132,7 +30140,7 @@
         <v>0</v>
       </c>
       <c r="R252" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O252:Q252)</f>
         <v>26</v>
       </c>
       <c r="S252" s="22">
@@ -30195,7 +30203,7 @@
         <v>0</v>
       </c>
       <c r="R253" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O253:Q253)</f>
         <v>26</v>
       </c>
       <c r="S253" s="24">
@@ -30258,7 +30266,7 @@
         <v>0</v>
       </c>
       <c r="R254" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O254:Q254)</f>
         <v>11</v>
       </c>
       <c r="S254" s="22">
@@ -30319,7 +30327,7 @@
         <v>0</v>
       </c>
       <c r="R255" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O255:Q255)</f>
         <v>14</v>
       </c>
       <c r="S255" s="24">
@@ -30382,7 +30390,7 @@
         <v>49</v>
       </c>
       <c r="R256" s="23">
-        <f t="shared" si="3"/>
+        <f>SUM(O256:Q256)</f>
         <v>49</v>
       </c>
       <c r="S256" s="22">
@@ -30445,7 +30453,7 @@
         <v>0</v>
       </c>
       <c r="R257" s="25">
-        <f t="shared" si="3"/>
+        <f>SUM(O257:Q257)</f>
         <v>27</v>
       </c>
       <c r="S257" s="24">
@@ -30508,7 +30516,7 @@
         <v>7</v>
       </c>
       <c r="R258" s="23">
-        <f t="shared" ref="R258:R321" si="4">SUM(O258:Q258)</f>
+        <f>SUM(O258:Q258)</f>
         <v>22</v>
       </c>
       <c r="S258" s="22">
@@ -30571,7 +30579,7 @@
         <v>0</v>
       </c>
       <c r="R259" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O259:Q259)</f>
         <v>18</v>
       </c>
       <c r="S259" s="24">
@@ -30634,7 +30642,7 @@
         <v>31</v>
       </c>
       <c r="R260" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O260:Q260)</f>
         <v>31</v>
       </c>
       <c r="S260" s="22">
@@ -30697,7 +30705,7 @@
         <v>0</v>
       </c>
       <c r="R261" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O261:Q261)</f>
         <v>25</v>
       </c>
       <c r="S261" s="24">
@@ -30760,7 +30768,7 @@
         <v>0</v>
       </c>
       <c r="R262" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O262:Q262)</f>
         <v>9</v>
       </c>
       <c r="S262" s="22">
@@ -30823,7 +30831,7 @@
         <v>0</v>
       </c>
       <c r="R263" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O263:Q263)</f>
         <v>8</v>
       </c>
       <c r="S263" s="24">
@@ -30886,7 +30894,7 @@
         <v>29</v>
       </c>
       <c r="R264" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O264:Q264)</f>
         <v>29</v>
       </c>
       <c r="S264" s="22">
@@ -30949,7 +30957,7 @@
         <v>21</v>
       </c>
       <c r="R265" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O265:Q265)</f>
         <v>24</v>
       </c>
       <c r="S265" s="24">
@@ -31012,7 +31020,7 @@
         <v>0</v>
       </c>
       <c r="R266" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O266:Q266)</f>
         <v>66</v>
       </c>
       <c r="S266" s="22">
@@ -31075,7 +31083,7 @@
         <v>20</v>
       </c>
       <c r="R267" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O267:Q267)</f>
         <v>20</v>
       </c>
       <c r="S267" s="24">
@@ -31138,7 +31146,7 @@
         <v>0</v>
       </c>
       <c r="R268" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O268:Q268)</f>
         <v>13</v>
       </c>
       <c r="S268" s="22">
@@ -31201,7 +31209,7 @@
         <v>0</v>
       </c>
       <c r="R269" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O269:Q269)</f>
         <v>15</v>
       </c>
       <c r="S269" s="24">
@@ -31264,7 +31272,7 @@
         <v>0</v>
       </c>
       <c r="R270" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O270:Q270)</f>
         <v>5</v>
       </c>
       <c r="S270" s="22">
@@ -31327,7 +31335,7 @@
         <v>0</v>
       </c>
       <c r="R271" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O271:Q271)</f>
         <v>18</v>
       </c>
       <c r="S271" s="24">
@@ -31390,7 +31398,7 @@
         <v>0</v>
       </c>
       <c r="R272" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O272:Q272)</f>
         <v>8</v>
       </c>
       <c r="S272" s="22">
@@ -31453,7 +31461,7 @@
         <v>0</v>
       </c>
       <c r="R273" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O273:Q273)</f>
         <v>83</v>
       </c>
       <c r="S273" s="24">
@@ -31516,7 +31524,7 @@
         <v>0</v>
       </c>
       <c r="R274" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O274:Q274)</f>
         <v>24</v>
       </c>
       <c r="S274" s="22">
@@ -31579,7 +31587,7 @@
         <v>0</v>
       </c>
       <c r="R275" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O275:Q275)</f>
         <v>20</v>
       </c>
       <c r="S275" s="24">
@@ -31642,7 +31650,7 @@
         <v>39</v>
       </c>
       <c r="R276" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O276:Q276)</f>
         <v>39</v>
       </c>
       <c r="S276" s="22">
@@ -31705,7 +31713,7 @@
         <v>0</v>
       </c>
       <c r="R277" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O277:Q277)</f>
         <v>39</v>
       </c>
       <c r="S277" s="24">
@@ -31768,7 +31776,7 @@
         <v>0</v>
       </c>
       <c r="R278" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O278:Q278)</f>
         <v>277</v>
       </c>
       <c r="S278" s="22">
@@ -31831,7 +31839,7 @@
         <v>0</v>
       </c>
       <c r="R279" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O279:Q279)</f>
         <v>43</v>
       </c>
       <c r="S279" s="24">
@@ -31894,7 +31902,7 @@
         <v>0</v>
       </c>
       <c r="R280" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O280:Q280)</f>
         <v>21</v>
       </c>
       <c r="S280" s="22">
@@ -31957,7 +31965,7 @@
         <v>84</v>
       </c>
       <c r="R281" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O281:Q281)</f>
         <v>144</v>
       </c>
       <c r="S281" s="24">
@@ -32020,7 +32028,7 @@
         <v>0</v>
       </c>
       <c r="R282" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O282:Q282)</f>
         <v>19</v>
       </c>
       <c r="S282" s="22">
@@ -32083,7 +32091,7 @@
         <v>64</v>
       </c>
       <c r="R283" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O283:Q283)</f>
         <v>65</v>
       </c>
       <c r="S283" s="24">
@@ -32146,7 +32154,7 @@
         <v>0</v>
       </c>
       <c r="R284" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O284:Q284)</f>
         <v>72</v>
       </c>
       <c r="S284" s="22">
@@ -32209,7 +32217,7 @@
         <v>193</v>
       </c>
       <c r="R285" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O285:Q285)</f>
         <v>193</v>
       </c>
       <c r="S285" s="24">
@@ -32272,7 +32280,7 @@
         <v>0</v>
       </c>
       <c r="R286" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O286:Q286)</f>
         <v>46</v>
       </c>
       <c r="S286" s="22">
@@ -32335,7 +32343,7 @@
         <v>20</v>
       </c>
       <c r="R287" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O287:Q287)</f>
         <v>20</v>
       </c>
       <c r="S287" s="24">
@@ -32396,7 +32404,7 @@
         <v>0</v>
       </c>
       <c r="R288" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O288:Q288)</f>
         <v>23</v>
       </c>
       <c r="S288" s="22">
@@ -32457,7 +32465,7 @@
         <v>0</v>
       </c>
       <c r="R289" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O289:Q289)</f>
         <v>80</v>
       </c>
       <c r="S289" s="24">
@@ -32520,7 +32528,7 @@
         <v>0</v>
       </c>
       <c r="R290" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O290:Q290)</f>
         <v>21</v>
       </c>
       <c r="S290" s="22">
@@ -32583,7 +32591,7 @@
         <v>0</v>
       </c>
       <c r="R291" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O291:Q291)</f>
         <v>28</v>
       </c>
       <c r="S291" s="24">
@@ -32646,7 +32654,7 @@
         <v>35</v>
       </c>
       <c r="R292" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O292:Q292)</f>
         <v>35</v>
       </c>
       <c r="S292" s="22">
@@ -32709,7 +32717,7 @@
         <v>0</v>
       </c>
       <c r="R293" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O293:Q293)</f>
         <v>20</v>
       </c>
       <c r="S293" s="24">
@@ -32772,7 +32780,7 @@
         <v>0</v>
       </c>
       <c r="R294" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O294:Q294)</f>
         <v>188</v>
       </c>
       <c r="S294" s="22">
@@ -32835,7 +32843,7 @@
         <v>0</v>
       </c>
       <c r="R295" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O295:Q295)</f>
         <v>42</v>
       </c>
       <c r="S295" s="24">
@@ -32898,7 +32906,7 @@
         <v>0</v>
       </c>
       <c r="R296" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O296:Q296)</f>
         <v>31</v>
       </c>
       <c r="S296" s="22">
@@ -32962,7 +32970,7 @@
         <v>0</v>
       </c>
       <c r="R297" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O297:Q297)</f>
         <v>20</v>
       </c>
       <c r="S297" s="24">
@@ -33023,7 +33031,7 @@
         <v>0</v>
       </c>
       <c r="R298" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O298:Q298)</f>
         <v>70</v>
       </c>
       <c r="S298" s="22">
@@ -33086,7 +33094,7 @@
         <v>52</v>
       </c>
       <c r="R299" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O299:Q299)</f>
         <v>85</v>
       </c>
       <c r="S299" s="24">
@@ -33149,7 +33157,7 @@
         <v>54</v>
       </c>
       <c r="R300" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O300:Q300)</f>
         <v>54</v>
       </c>
       <c r="S300" s="22">
@@ -33212,7 +33220,7 @@
         <v>130</v>
       </c>
       <c r="R301" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O301:Q301)</f>
         <v>153</v>
       </c>
       <c r="S301" s="24">
@@ -33275,7 +33283,7 @@
         <v>0</v>
       </c>
       <c r="R302" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O302:Q302)</f>
         <v>19</v>
       </c>
       <c r="S302" s="22">
@@ -33338,7 +33346,7 @@
         <v>0</v>
       </c>
       <c r="R303" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O303:Q303)</f>
         <v>20</v>
       </c>
       <c r="S303" s="24">
@@ -33395,7 +33403,7 @@
       <c r="P304" s="23"/>
       <c r="Q304" s="23"/>
       <c r="R304" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O304:Q304)</f>
         <v>25</v>
       </c>
       <c r="S304" s="22">
@@ -33458,7 +33466,7 @@
         <v>0</v>
       </c>
       <c r="R305" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O305:Q305)</f>
         <v>70</v>
       </c>
       <c r="S305" s="24">
@@ -33521,7 +33529,7 @@
         <v>0</v>
       </c>
       <c r="R306" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O306:Q306)</f>
         <v>17</v>
       </c>
       <c r="S306" s="22">
@@ -33582,7 +33590,7 @@
         <v>1</v>
       </c>
       <c r="R307" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O307:Q307)</f>
         <v>24</v>
       </c>
       <c r="S307" s="24">
@@ -33646,7 +33654,7 @@
         <v>0</v>
       </c>
       <c r="R308" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O308:Q308)</f>
         <v>17</v>
       </c>
       <c r="S308" s="22">
@@ -33709,7 +33717,7 @@
         <v>0</v>
       </c>
       <c r="R309" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O309:Q309)</f>
         <v>17</v>
       </c>
       <c r="S309" s="24">
@@ -33772,7 +33780,7 @@
         <v>1</v>
       </c>
       <c r="R310" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O310:Q310)</f>
         <v>45</v>
       </c>
       <c r="S310" s="22">
@@ -33835,7 +33843,7 @@
         <v>0</v>
       </c>
       <c r="R311" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O311:Q311)</f>
         <v>26</v>
       </c>
       <c r="S311" s="24">
@@ -33899,7 +33907,7 @@
         <v>0</v>
       </c>
       <c r="R312" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O312:Q312)</f>
         <v>17</v>
       </c>
       <c r="S312" s="22">
@@ -33962,7 +33970,7 @@
         <v>0</v>
       </c>
       <c r="R313" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O313:Q313)</f>
         <v>30</v>
       </c>
       <c r="S313" s="24">
@@ -34026,7 +34034,7 @@
         <v>0</v>
       </c>
       <c r="R314" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O314:Q314)</f>
         <v>20</v>
       </c>
       <c r="S314" s="22">
@@ -34089,7 +34097,7 @@
         <v>33</v>
       </c>
       <c r="R315" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O315:Q315)</f>
         <v>33</v>
       </c>
       <c r="S315" s="24">
@@ -34152,7 +34160,7 @@
         <v>0</v>
       </c>
       <c r="R316" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O316:Q316)</f>
         <v>17</v>
       </c>
       <c r="S316" s="22">
@@ -34215,7 +34223,7 @@
         <v>0</v>
       </c>
       <c r="R317" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O317:Q317)</f>
         <v>15</v>
       </c>
       <c r="S317" s="24">
@@ -34278,7 +34286,7 @@
         <v>19</v>
       </c>
       <c r="R318" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O318:Q318)</f>
         <v>19</v>
       </c>
       <c r="S318" s="22">
@@ -34342,7 +34350,7 @@
         <v>0</v>
       </c>
       <c r="R319" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O319:Q319)</f>
         <v>16</v>
       </c>
       <c r="S319" s="24">
@@ -34406,7 +34414,7 @@
         <v>0</v>
       </c>
       <c r="R320" s="23">
-        <f t="shared" si="4"/>
+        <f>SUM(O320:Q320)</f>
         <v>49</v>
       </c>
       <c r="S320" s="22">
@@ -34470,7 +34478,7 @@
         <v>0</v>
       </c>
       <c r="R321" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O321:Q321)</f>
         <v>126</v>
       </c>
       <c r="S321" s="24">
@@ -34533,7 +34541,7 @@
         <v>40</v>
       </c>
       <c r="R322" s="23">
-        <f t="shared" ref="R322:R385" si="5">SUM(O322:Q322)</f>
+        <f>SUM(O322:Q322)</f>
         <v>40</v>
       </c>
       <c r="S322" s="22">
@@ -34596,7 +34604,7 @@
         <v>40</v>
       </c>
       <c r="R323" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O323:Q323)</f>
         <v>40</v>
       </c>
       <c r="S323" s="24">
@@ -34659,7 +34667,7 @@
         <v>60</v>
       </c>
       <c r="R324" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O324:Q324)</f>
         <v>60</v>
       </c>
       <c r="S324" s="22">
@@ -34722,7 +34730,7 @@
         <v>30</v>
       </c>
       <c r="R325" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O325:Q325)</f>
         <v>30</v>
       </c>
       <c r="S325" s="24">
@@ -34785,7 +34793,7 @@
         <v>0</v>
       </c>
       <c r="R326" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O326:Q326)</f>
         <v>21</v>
       </c>
       <c r="S326" s="22">
@@ -34848,7 +34856,7 @@
         <v>0</v>
       </c>
       <c r="R327" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O327:Q327)</f>
         <v>20</v>
       </c>
       <c r="S327" s="24">
@@ -34911,7 +34919,7 @@
         <v>39</v>
       </c>
       <c r="R328" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O328:Q328)</f>
         <v>40</v>
       </c>
       <c r="S328" s="22">
@@ -34974,7 +34982,7 @@
         <v>0</v>
       </c>
       <c r="R329" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O329:Q329)</f>
         <v>80</v>
       </c>
       <c r="S329" s="24">
@@ -35037,7 +35045,7 @@
         <v>0</v>
       </c>
       <c r="R330" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O330:Q330)</f>
         <v>26</v>
       </c>
       <c r="S330" s="22">
@@ -35100,7 +35108,7 @@
         <v>0</v>
       </c>
       <c r="R331" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O331:Q331)</f>
         <v>15</v>
       </c>
       <c r="S331" s="24">
@@ -35163,7 +35171,7 @@
         <v>0</v>
       </c>
       <c r="R332" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O332:Q332)</f>
         <v>23</v>
       </c>
       <c r="S332" s="22">
@@ -35226,7 +35234,7 @@
         <v>0</v>
       </c>
       <c r="R333" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O333:Q333)</f>
         <v>207</v>
       </c>
       <c r="S333" s="24">
@@ -35289,7 +35297,7 @@
         <v>0</v>
       </c>
       <c r="R334" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O334:Q334)</f>
         <v>13</v>
       </c>
       <c r="S334" s="22">
@@ -35352,7 +35360,7 @@
         <v>0</v>
       </c>
       <c r="R335" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O335:Q335)</f>
         <v>184</v>
       </c>
       <c r="S335" s="24">
@@ -35415,7 +35423,7 @@
         <v>0</v>
       </c>
       <c r="R336" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O336:Q336)</f>
         <v>46</v>
       </c>
       <c r="S336" s="22">
@@ -35478,7 +35486,7 @@
         <v>16</v>
       </c>
       <c r="R337" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O337:Q337)</f>
         <v>60</v>
       </c>
       <c r="S337" s="24">
@@ -35541,7 +35549,7 @@
         <v>45</v>
       </c>
       <c r="R338" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O338:Q338)</f>
         <v>48</v>
       </c>
       <c r="S338" s="22">
@@ -35596,7 +35604,7 @@
         <v>40</v>
       </c>
       <c r="R339" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O339:Q339)</f>
         <v>40</v>
       </c>
       <c r="S339" s="24">
@@ -35655,7 +35663,7 @@
         <v>0</v>
       </c>
       <c r="R340" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O340:Q340)</f>
         <v>150</v>
       </c>
       <c r="S340" s="22">
@@ -35718,7 +35726,7 @@
         <v>0</v>
       </c>
       <c r="R341" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O341:Q341)</f>
         <v>20</v>
       </c>
       <c r="S341" s="24">
@@ -35773,7 +35781,7 @@
         <v>30</v>
       </c>
       <c r="R342" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O342:Q342)</f>
         <v>30</v>
       </c>
       <c r="S342" s="22">
@@ -35837,7 +35845,7 @@
         <v>0</v>
       </c>
       <c r="R343" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O343:Q343)</f>
         <v>67</v>
       </c>
       <c r="S343" s="24">
@@ -35900,7 +35908,7 @@
         <v>0</v>
       </c>
       <c r="R344" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O344:Q344)</f>
         <v>67</v>
       </c>
       <c r="S344" s="22">
@@ -35963,7 +35971,7 @@
         <v>0</v>
       </c>
       <c r="R345" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O345:Q345)</f>
         <v>57</v>
       </c>
       <c r="S345" s="24">
@@ -36026,7 +36034,7 @@
         <v>0</v>
       </c>
       <c r="R346" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O346:Q346)</f>
         <v>20</v>
       </c>
       <c r="S346" s="22">
@@ -36089,7 +36097,7 @@
         <v>0</v>
       </c>
       <c r="R347" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O347:Q347)</f>
         <v>315</v>
       </c>
       <c r="S347" s="24">
@@ -36152,7 +36160,7 @@
         <v>0</v>
       </c>
       <c r="R348" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O348:Q348)</f>
         <v>35</v>
       </c>
       <c r="S348" s="22">
@@ -36215,7 +36223,7 @@
         <v>0</v>
       </c>
       <c r="R349" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O349:Q349)</f>
         <v>17</v>
       </c>
       <c r="S349" s="24">
@@ -36279,7 +36287,7 @@
         <v>0</v>
       </c>
       <c r="R350" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O350:Q350)</f>
         <v>27</v>
       </c>
       <c r="S350" s="22">
@@ -36342,7 +36350,7 @@
         <v>0</v>
       </c>
       <c r="R351" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O351:Q351)</f>
         <v>45</v>
       </c>
       <c r="S351" s="24">
@@ -36405,7 +36413,7 @@
         <v>0</v>
       </c>
       <c r="R352" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O352:Q352)</f>
         <v>51</v>
       </c>
       <c r="S352" s="22">
@@ -36468,7 +36476,7 @@
         <v>0</v>
       </c>
       <c r="R353" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O353:Q353)</f>
         <v>5</v>
       </c>
       <c r="S353" s="24">
@@ -36531,7 +36539,7 @@
         <v>0</v>
       </c>
       <c r="R354" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O354:Q354)</f>
         <v>16</v>
       </c>
       <c r="S354" s="22">
@@ -36594,7 +36602,7 @@
         <v>0</v>
       </c>
       <c r="R355" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O355:Q355)</f>
         <v>30</v>
       </c>
       <c r="S355" s="24">
@@ -36657,7 +36665,7 @@
         <v>0</v>
       </c>
       <c r="R356" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O356:Q356)</f>
         <v>64</v>
       </c>
       <c r="S356" s="22">
@@ -36719,7 +36727,7 @@
         <v>0</v>
       </c>
       <c r="R357" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O357:Q357)</f>
         <v>57</v>
       </c>
       <c r="S357" s="24">
@@ -36782,7 +36790,7 @@
         <v>0</v>
       </c>
       <c r="R358" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O358:Q358)</f>
         <v>39</v>
       </c>
       <c r="S358" s="22">
@@ -36845,7 +36853,7 @@
         <v>0</v>
       </c>
       <c r="R359" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O359:Q359)</f>
         <v>16</v>
       </c>
       <c r="S359" s="24">
@@ -36908,7 +36916,7 @@
         <v>0</v>
       </c>
       <c r="R360" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O360:Q360)</f>
         <v>47</v>
       </c>
       <c r="S360" s="22">
@@ -36971,7 +36979,7 @@
         <v>2</v>
       </c>
       <c r="R361" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O361:Q361)</f>
         <v>13</v>
       </c>
       <c r="S361" s="24">
@@ -37034,7 +37042,7 @@
         <v>0</v>
       </c>
       <c r="R362" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O362:Q362)</f>
         <v>26</v>
       </c>
       <c r="S362" s="22">
@@ -37097,7 +37105,7 @@
         <v>43</v>
       </c>
       <c r="R363" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O363:Q363)</f>
         <v>43</v>
       </c>
       <c r="S363" s="24">
@@ -37160,7 +37168,7 @@
         <v>0</v>
       </c>
       <c r="R364" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O364:Q364)</f>
         <v>11</v>
       </c>
       <c r="S364" s="22">
@@ -37223,7 +37231,7 @@
         <v>0</v>
       </c>
       <c r="R365" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O365:Q365)</f>
         <v>11</v>
       </c>
       <c r="S365" s="24">
@@ -37287,7 +37295,7 @@
         <v>57</v>
       </c>
       <c r="R366" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O366:Q366)</f>
         <v>57</v>
       </c>
       <c r="S366" s="22">
@@ -37351,7 +37359,7 @@
         <v>0</v>
       </c>
       <c r="R367" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O367:Q367)</f>
         <v>22</v>
       </c>
       <c r="S367" s="24">
@@ -37414,7 +37422,7 @@
         <v>0</v>
       </c>
       <c r="R368" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O368:Q368)</f>
         <v>176</v>
       </c>
       <c r="S368" s="22">
@@ -37475,7 +37483,7 @@
         <v>0</v>
       </c>
       <c r="R369" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O369:Q369)</f>
         <v>56</v>
       </c>
       <c r="S369" s="24">
@@ -37539,7 +37547,7 @@
         <v>0</v>
       </c>
       <c r="R370" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O370:Q370)</f>
         <v>23</v>
       </c>
       <c r="S370" s="22">
@@ -37602,7 +37610,7 @@
         <v>39</v>
       </c>
       <c r="R371" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O371:Q371)</f>
         <v>39</v>
       </c>
       <c r="S371" s="24">
@@ -37665,7 +37673,7 @@
         <v>0</v>
       </c>
       <c r="R372" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O372:Q372)</f>
         <v>47</v>
       </c>
       <c r="S372" s="22">
@@ -37727,7 +37735,7 @@
         <v>53</v>
       </c>
       <c r="R373" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O373:Q373)</f>
         <v>53</v>
       </c>
       <c r="S373" s="24">
@@ -37790,7 +37798,7 @@
         <v>0</v>
       </c>
       <c r="R374" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O374:Q374)</f>
         <v>28</v>
       </c>
       <c r="S374" s="22">
@@ -37854,7 +37862,7 @@
         <v>0</v>
       </c>
       <c r="R375" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O375:Q375)</f>
         <v>18</v>
       </c>
       <c r="S375" s="24">
@@ -37918,7 +37926,7 @@
         <v>53</v>
       </c>
       <c r="R376" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O376:Q376)</f>
         <v>53</v>
       </c>
       <c r="S376" s="22">
@@ -37982,7 +37990,7 @@
         <v>0</v>
       </c>
       <c r="R377" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O377:Q377)</f>
         <v>10</v>
       </c>
       <c r="S377" s="24">
@@ -38046,7 +38054,7 @@
         <v>0</v>
       </c>
       <c r="R378" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O378:Q378)</f>
         <v>34</v>
       </c>
       <c r="S378" s="22">
@@ -38101,7 +38109,7 @@
         <v>0</v>
       </c>
       <c r="R379" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O379:Q379)</f>
         <v>0</v>
       </c>
       <c r="S379" s="24"/>
@@ -38160,7 +38168,7 @@
         <v>0</v>
       </c>
       <c r="R380" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O380:Q380)</f>
         <v>15</v>
       </c>
       <c r="S380" s="22">
@@ -38215,7 +38223,7 @@
       <c r="P381" s="25"/>
       <c r="Q381" s="25"/>
       <c r="R381" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O381:Q381)</f>
         <v>21</v>
       </c>
       <c r="S381" s="24">
@@ -38277,7 +38285,7 @@
         <v>17</v>
       </c>
       <c r="R382" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O382:Q382)</f>
         <v>17</v>
       </c>
       <c r="S382" s="22">
@@ -38341,7 +38349,7 @@
         <v>0</v>
       </c>
       <c r="R383" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O383:Q383)</f>
         <v>13</v>
       </c>
       <c r="S383" s="24">
@@ -38404,7 +38412,7 @@
         <v>0</v>
       </c>
       <c r="R384" s="23">
-        <f t="shared" si="5"/>
+        <f>SUM(O384:Q384)</f>
         <v>114</v>
       </c>
       <c r="S384" s="22">
@@ -38465,7 +38473,7 @@
         <v>0</v>
       </c>
       <c r="R385" s="25">
-        <f t="shared" si="5"/>
+        <f>SUM(O385:Q385)</f>
         <v>5</v>
       </c>
       <c r="S385" s="24">
@@ -38528,7 +38536,7 @@
         <v>0</v>
       </c>
       <c r="R386" s="23">
-        <f t="shared" ref="R386:R449" si="6">SUM(O386:Q386)</f>
+        <f>SUM(O386:Q386)</f>
         <v>49</v>
       </c>
       <c r="S386" s="22">
@@ -38591,7 +38599,7 @@
         <v>0</v>
       </c>
       <c r="R387" s="25">
-        <f t="shared" si="6"/>
+        <f>SUM(O387:Q387)</f>
         <v>22</v>
       </c>
       <c r="S387" s="24">
@@ -38654,7 +38662,7 @@
         <v>26</v>
       </c>
       <c r="R388" s="23">
-        <f t="shared" si="6"/>
+        <f>SUM(O388:Q388)</f>
         <v>91</v>
       </c>
       <c r="S388" s="22">
@@ -38718,7 +38726,7 @@
         <v>5</v>
       </c>
       <c r="R389" s="25">
-        <f t="shared" si="6"/>
+        <f>SUM(O389:Q389)</f>
         <v>5</v>
       </c>
       <c r="S389" s="24">
@@ -38781,7 +38789,7 @@
         <v>0</v>
       </c>
       <c r="R390" s="23">
-        <f t="shared" si="6"/>
+        <f>SUM(O390:Q390)</f>
         <v>181</v>
       </c>
       <c r="S390" s="22">
@@ -38845,7 +38853,7 @@
         <v>7</v>
       </c>
       <c r="R391" s="25">
-        <f t="shared" si="6"/>
+        <f>SUM(O391:Q391)</f>
         <v>7</v>
       </c>
       <c r="S391" s="24">
@@ -38908,7 +38916,7 @@
         <v>0</v>
       </c>
       <c r="R392" s="23">
-        <f t="shared" si="6"/>
+        <f>SUM(O392:Q392)</f>
         <v>9</v>
       </c>
       <c r="S392" s="22">
@@ -39034,7 +39042,7 @@
         <v>31</v>
       </c>
       <c r="R394" s="23">
-        <f t="shared" ref="R394:R457" si="7">SUM(O394:Q394)</f>
+        <f>SUM(O394:Q394)</f>
         <v>31</v>
       </c>
       <c r="S394" s="22">
@@ -39097,7 +39105,7 @@
         <v>0</v>
       </c>
       <c r="R395" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O395:Q395)</f>
         <v>19</v>
       </c>
       <c r="S395" s="24">
@@ -39160,7 +39168,7 @@
         <v>0</v>
       </c>
       <c r="R396" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O396:Q396)</f>
         <v>45</v>
       </c>
       <c r="S396" s="22">
@@ -39223,7 +39231,7 @@
         <v>0</v>
       </c>
       <c r="R397" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O397:Q397)</f>
         <v>0</v>
       </c>
       <c r="S397" s="24">
@@ -39286,7 +39294,7 @@
         <v>17</v>
       </c>
       <c r="R398" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O398:Q398)</f>
         <v>85</v>
       </c>
       <c r="S398" s="22">
@@ -39349,7 +39357,7 @@
         <v>0</v>
       </c>
       <c r="R399" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O399:Q399)</f>
         <v>7</v>
       </c>
       <c r="S399" s="24">
@@ -39406,7 +39414,7 @@
       <c r="P400" s="23"/>
       <c r="Q400" s="23"/>
       <c r="R400" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O400:Q400)</f>
         <v>30</v>
       </c>
       <c r="S400" s="22">
@@ -39467,7 +39475,7 @@
         <v>0</v>
       </c>
       <c r="R401" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O401:Q401)</f>
         <v>62</v>
       </c>
       <c r="S401" s="24">
@@ -39530,7 +39538,7 @@
         <v>68</v>
       </c>
       <c r="R402" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O402:Q402)</f>
         <v>68</v>
       </c>
       <c r="S402" s="22">
@@ -39589,7 +39597,7 @@
         <v>0</v>
       </c>
       <c r="R403" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O403:Q403)</f>
         <v>2</v>
       </c>
       <c r="S403" s="24">
@@ -39652,7 +39660,7 @@
         <v>0</v>
       </c>
       <c r="R404" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O404:Q404)</f>
         <v>36</v>
       </c>
       <c r="S404" s="22">
@@ -39715,7 +39723,7 @@
         <v>0</v>
       </c>
       <c r="R405" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O405:Q405)</f>
         <v>14</v>
       </c>
       <c r="S405" s="24">
@@ -39776,7 +39784,7 @@
         <v>44</v>
       </c>
       <c r="R406" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O406:Q406)</f>
         <v>44</v>
       </c>
       <c r="S406" s="22">
@@ -39839,7 +39847,7 @@
         <v>0</v>
       </c>
       <c r="R407" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O407:Q407)</f>
         <v>26</v>
       </c>
       <c r="S407" s="24">
@@ -39902,7 +39910,7 @@
         <v>0</v>
       </c>
       <c r="R408" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O408:Q408)</f>
         <v>23</v>
       </c>
       <c r="S408" s="22">
@@ -39957,7 +39965,7 @@
         <v>20</v>
       </c>
       <c r="R409" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O409:Q409)</f>
         <v>20</v>
       </c>
       <c r="S409" s="24">
@@ -40012,7 +40020,7 @@
         <v>0</v>
       </c>
       <c r="R410" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O410:Q410)</f>
         <v>0</v>
       </c>
       <c r="S410" s="22"/>
@@ -40071,7 +40079,7 @@
         <v>0</v>
       </c>
       <c r="R411" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O411:Q411)</f>
         <v>16</v>
       </c>
       <c r="S411" s="24">
@@ -40134,7 +40142,7 @@
         <v>44</v>
       </c>
       <c r="R412" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O412:Q412)</f>
         <v>44</v>
       </c>
       <c r="S412" s="22">
@@ -40197,7 +40205,7 @@
         <v>0</v>
       </c>
       <c r="R413" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O413:Q413)</f>
         <v>105</v>
       </c>
       <c r="S413" s="24">
@@ -40260,7 +40268,7 @@
         <v>0</v>
       </c>
       <c r="R414" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O414:Q414)</f>
         <v>50</v>
       </c>
       <c r="S414" s="22">
@@ -40323,7 +40331,7 @@
         <v>0</v>
       </c>
       <c r="R415" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O415:Q415)</f>
         <v>25</v>
       </c>
       <c r="S415" s="24">
@@ -40386,7 +40394,7 @@
         <v>0</v>
       </c>
       <c r="R416" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O416:Q416)</f>
         <v>9</v>
       </c>
       <c r="S416" s="22">
@@ -40449,7 +40457,7 @@
         <v>24</v>
       </c>
       <c r="R417" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O417:Q417)</f>
         <v>25</v>
       </c>
       <c r="S417" s="24">
@@ -40512,7 +40520,7 @@
         <v>0</v>
       </c>
       <c r="R418" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O418:Q418)</f>
         <v>13</v>
       </c>
       <c r="S418" s="22">
@@ -40576,7 +40584,7 @@
         <v>0</v>
       </c>
       <c r="R419" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O419:Q419)</f>
         <v>49</v>
       </c>
       <c r="S419" s="24">
@@ -40639,7 +40647,7 @@
         <v>128</v>
       </c>
       <c r="R420" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O420:Q420)</f>
         <v>128</v>
       </c>
       <c r="S420" s="22">
@@ -40702,7 +40710,7 @@
         <v>0</v>
       </c>
       <c r="R421" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O421:Q421)</f>
         <v>21</v>
       </c>
       <c r="S421" s="24">
@@ -40765,7 +40773,7 @@
         <v>0</v>
       </c>
       <c r="R422" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O422:Q422)</f>
         <v>8</v>
       </c>
       <c r="S422" s="22">
@@ -40828,7 +40836,7 @@
         <v>0</v>
       </c>
       <c r="R423" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O423:Q423)</f>
         <v>93</v>
       </c>
       <c r="S423" s="24">
@@ -40891,7 +40899,7 @@
         <v>0</v>
       </c>
       <c r="R424" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O424:Q424)</f>
         <v>6</v>
       </c>
       <c r="S424" s="22">
@@ -40952,7 +40960,7 @@
         <v>0</v>
       </c>
       <c r="R425" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O425:Q425)</f>
         <v>80</v>
       </c>
       <c r="S425" s="24">
@@ -41016,7 +41024,7 @@
         <v>0</v>
       </c>
       <c r="R426" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O426:Q426)</f>
         <v>8</v>
       </c>
       <c r="S426" s="22">
@@ -41079,7 +41087,7 @@
         <v>0</v>
       </c>
       <c r="R427" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O427:Q427)</f>
         <v>10</v>
       </c>
       <c r="S427" s="24">
@@ -41140,7 +41148,7 @@
         <v>80</v>
       </c>
       <c r="R428" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O428:Q428)</f>
         <v>80</v>
       </c>
       <c r="S428" s="22">
@@ -41201,7 +41209,7 @@
         <v>80</v>
       </c>
       <c r="R429" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O429:Q429)</f>
         <v>80</v>
       </c>
       <c r="S429" s="24">
@@ -41262,7 +41270,7 @@
         <v>80</v>
       </c>
       <c r="R430" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O430:Q430)</f>
         <v>80</v>
       </c>
       <c r="S430" s="22">
@@ -41323,7 +41331,7 @@
         <v>80</v>
       </c>
       <c r="R431" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O431:Q431)</f>
         <v>80</v>
       </c>
       <c r="S431" s="24">
@@ -41384,7 +41392,7 @@
         <v>80</v>
       </c>
       <c r="R432" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O432:Q432)</f>
         <v>80</v>
       </c>
       <c r="S432" s="22">
@@ -41448,7 +41456,7 @@
         <v>0</v>
       </c>
       <c r="R433" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O433:Q433)</f>
         <v>33</v>
       </c>
       <c r="S433" s="24">
@@ -41503,7 +41511,7 @@
         <v>0</v>
       </c>
       <c r="R434" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O434:Q434)</f>
         <v>0</v>
       </c>
       <c r="S434" s="22"/>
@@ -41562,7 +41570,7 @@
         <v>62</v>
       </c>
       <c r="R435" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O435:Q435)</f>
         <v>62</v>
       </c>
       <c r="S435" s="24">
@@ -41625,7 +41633,7 @@
         <v>0</v>
       </c>
       <c r="R436" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O436:Q436)</f>
         <v>42</v>
       </c>
       <c r="S436" s="22">
@@ -41688,7 +41696,7 @@
         <v>0</v>
       </c>
       <c r="R437" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O437:Q437)</f>
         <v>6</v>
       </c>
       <c r="S437" s="24">
@@ -41751,7 +41759,7 @@
         <v>0</v>
       </c>
       <c r="R438" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O438:Q438)</f>
         <v>49</v>
       </c>
       <c r="S438" s="22">
@@ -41814,7 +41822,7 @@
         <v>0</v>
       </c>
       <c r="R439" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O439:Q439)</f>
         <v>20</v>
       </c>
       <c r="S439" s="24">
@@ -41877,7 +41885,7 @@
         <v>28</v>
       </c>
       <c r="R440" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O440:Q440)</f>
         <v>28</v>
       </c>
       <c r="S440" s="22">
@@ -41940,7 +41948,7 @@
         <v>0</v>
       </c>
       <c r="R441" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O441:Q441)</f>
         <v>17</v>
       </c>
       <c r="S441" s="24">
@@ -42004,7 +42012,7 @@
         <v>0</v>
       </c>
       <c r="R442" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O442:Q442)</f>
         <v>17</v>
       </c>
       <c r="S442" s="22">
@@ -42068,7 +42076,7 @@
         <v>0</v>
       </c>
       <c r="R443" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O443:Q443)</f>
         <v>24</v>
       </c>
       <c r="S443" s="24">
@@ -42131,7 +42139,7 @@
         <v>0</v>
       </c>
       <c r="R444" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O444:Q444)</f>
         <v>16</v>
       </c>
       <c r="S444" s="22">
@@ -42194,7 +42202,7 @@
         <v>7</v>
       </c>
       <c r="R445" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O445:Q445)</f>
         <v>155</v>
       </c>
       <c r="S445" s="24">
@@ -42258,7 +42266,7 @@
         <v>0</v>
       </c>
       <c r="R446" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O446:Q446)</f>
         <v>8</v>
       </c>
       <c r="S446" s="22">
@@ -42321,7 +42329,7 @@
         <v>0</v>
       </c>
       <c r="R447" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O447:Q447)</f>
         <v>10</v>
       </c>
       <c r="S447" s="24">
@@ -42384,7 +42392,7 @@
         <v>0</v>
       </c>
       <c r="R448" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O448:Q448)</f>
         <v>15</v>
       </c>
       <c r="S448" s="22">
@@ -42447,7 +42455,7 @@
         <v>0</v>
       </c>
       <c r="R449" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O449:Q449)</f>
         <v>51</v>
       </c>
       <c r="S449" s="24">
@@ -42510,7 +42518,7 @@
         <v>0</v>
       </c>
       <c r="R450" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O450:Q450)</f>
         <v>52</v>
       </c>
       <c r="S450" s="22">
@@ -42574,7 +42582,7 @@
         <v>0</v>
       </c>
       <c r="R451" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O451:Q451)</f>
         <v>13</v>
       </c>
       <c r="S451" s="24">
@@ -42637,7 +42645,7 @@
         <v>0</v>
       </c>
       <c r="R452" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O452:Q452)</f>
         <v>90</v>
       </c>
       <c r="S452" s="22">
@@ -42700,7 +42708,7 @@
         <v>0</v>
       </c>
       <c r="R453" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O453:Q453)</f>
         <v>11</v>
       </c>
       <c r="S453" s="24">
@@ -42763,7 +42771,7 @@
         <v>0</v>
       </c>
       <c r="R454" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O454:Q454)</f>
         <v>50</v>
       </c>
       <c r="S454" s="22">
@@ -42827,7 +42835,7 @@
         <v>0</v>
       </c>
       <c r="R455" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O455:Q455)</f>
         <v>8</v>
       </c>
       <c r="S455" s="24">
@@ -42880,7 +42888,7 @@
         <v>0</v>
       </c>
       <c r="R456" s="23">
-        <f t="shared" si="7"/>
+        <f>SUM(O456:Q456)</f>
         <v>0</v>
       </c>
       <c r="S456" s="22"/>
@@ -42939,7 +42947,7 @@
         <v>0</v>
       </c>
       <c r="R457" s="25">
-        <f t="shared" si="7"/>
+        <f>SUM(O457:Q457)</f>
         <v>23</v>
       </c>
       <c r="S457" s="24">
@@ -43002,7 +43010,7 @@
         <v>0</v>
       </c>
       <c r="R458" s="23">
-        <f t="shared" ref="R458:R521" si="8">SUM(O458:Q458)</f>
+        <f>SUM(O458:Q458)</f>
         <v>23</v>
       </c>
       <c r="S458" s="22">
@@ -43065,7 +43073,7 @@
         <v>0</v>
       </c>
       <c r="R459" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O459:Q459)</f>
         <v>89</v>
       </c>
       <c r="S459" s="24">
@@ -43128,7 +43136,7 @@
         <v>0</v>
       </c>
       <c r="R460" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O460:Q460)</f>
         <v>22</v>
       </c>
       <c r="S460" s="22">
@@ -43192,7 +43200,7 @@
         <v>0</v>
       </c>
       <c r="R461" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O461:Q461)</f>
         <v>11</v>
       </c>
       <c r="S461" s="24">
@@ -43255,7 +43263,7 @@
         <v>0</v>
       </c>
       <c r="R462" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O462:Q462)</f>
         <v>21</v>
       </c>
       <c r="S462" s="22">
@@ -43318,7 +43326,7 @@
         <v>0</v>
       </c>
       <c r="R463" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O463:Q463)</f>
         <v>51</v>
       </c>
       <c r="S463" s="24">
@@ -43382,7 +43390,7 @@
         <v>0</v>
       </c>
       <c r="R464" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O464:Q464)</f>
         <v>7</v>
       </c>
       <c r="S464" s="22">
@@ -43445,7 +43453,7 @@
         <v>0</v>
       </c>
       <c r="R465" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O465:Q465)</f>
         <v>22</v>
       </c>
       <c r="S465" s="24">
@@ -43508,7 +43516,7 @@
         <v>156</v>
       </c>
       <c r="R466" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O466:Q466)</f>
         <v>213</v>
       </c>
       <c r="S466" s="22">
@@ -43571,7 +43579,7 @@
         <v>70</v>
       </c>
       <c r="R467" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O467:Q467)</f>
         <v>92</v>
       </c>
       <c r="S467" s="24">
@@ -43634,7 +43642,7 @@
         <v>0</v>
       </c>
       <c r="R468" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O468:Q468)</f>
         <v>18</v>
       </c>
       <c r="S468" s="22">
@@ -43698,7 +43706,7 @@
         <v>0</v>
       </c>
       <c r="R469" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O469:Q469)</f>
         <v>8</v>
       </c>
       <c r="S469" s="24">
@@ -43762,7 +43770,7 @@
         <v>0</v>
       </c>
       <c r="R470" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O470:Q470)</f>
         <v>8</v>
       </c>
       <c r="S470" s="22">
@@ -43826,7 +43834,7 @@
         <v>0</v>
       </c>
       <c r="R471" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O471:Q471)</f>
         <v>384</v>
       </c>
       <c r="S471" s="24">
@@ -43889,7 +43897,7 @@
         <v>0</v>
       </c>
       <c r="R472" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O472:Q472)</f>
         <v>24</v>
       </c>
       <c r="S472" s="22">
@@ -43952,7 +43960,7 @@
         <v>0</v>
       </c>
       <c r="R473" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O473:Q473)</f>
         <v>35</v>
       </c>
       <c r="S473" s="24">
@@ -44015,7 +44023,7 @@
         <v>0</v>
       </c>
       <c r="R474" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O474:Q474)</f>
         <v>53</v>
       </c>
       <c r="S474" s="22">
@@ -44078,7 +44086,7 @@
         <v>0</v>
       </c>
       <c r="R475" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O475:Q475)</f>
         <v>12</v>
       </c>
       <c r="S475" s="24">
@@ -44141,7 +44149,7 @@
         <v>0</v>
       </c>
       <c r="R476" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O476:Q476)</f>
         <v>60</v>
       </c>
       <c r="S476" s="22">
@@ -44204,7 +44212,7 @@
         <v>0</v>
       </c>
       <c r="R477" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O477:Q477)</f>
         <v>14</v>
       </c>
       <c r="S477" s="24">
@@ -44267,7 +44275,7 @@
         <v>0</v>
       </c>
       <c r="R478" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O478:Q478)</f>
         <v>20</v>
       </c>
       <c r="S478" s="22">
@@ -44330,7 +44338,7 @@
         <v>56</v>
       </c>
       <c r="R479" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O479:Q479)</f>
         <v>56</v>
       </c>
       <c r="S479" s="24">
@@ -44393,7 +44401,7 @@
         <v>0</v>
       </c>
       <c r="R480" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O480:Q480)</f>
         <v>38</v>
       </c>
       <c r="S480" s="22">
@@ -44456,7 +44464,7 @@
         <v>0</v>
       </c>
       <c r="R481" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O481:Q481)</f>
         <v>13</v>
       </c>
       <c r="S481" s="24">
@@ -44519,7 +44527,7 @@
         <v>0</v>
       </c>
       <c r="R482" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O482:Q482)</f>
         <v>24</v>
       </c>
       <c r="S482" s="22">
@@ -44582,7 +44590,7 @@
         <v>0</v>
       </c>
       <c r="R483" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O483:Q483)</f>
         <v>19</v>
       </c>
       <c r="S483" s="24">
@@ -44645,7 +44653,7 @@
         <v>0</v>
       </c>
       <c r="R484" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O484:Q484)</f>
         <v>10</v>
       </c>
       <c r="S484" s="22">
@@ -44709,7 +44717,7 @@
         <v>0</v>
       </c>
       <c r="R485" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O485:Q485)</f>
         <v>5</v>
       </c>
       <c r="S485" s="24">
@@ -44772,7 +44780,7 @@
         <v>0</v>
       </c>
       <c r="R486" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O486:Q486)</f>
         <v>21</v>
       </c>
       <c r="S486" s="22">
@@ -44835,7 +44843,7 @@
         <v>0</v>
       </c>
       <c r="R487" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O487:Q487)</f>
         <v>19</v>
       </c>
       <c r="S487" s="24">
@@ -44899,7 +44907,7 @@
         <v>0</v>
       </c>
       <c r="R488" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O488:Q488)</f>
         <v>7</v>
       </c>
       <c r="S488" s="22">
@@ -44962,7 +44970,7 @@
         <v>0</v>
       </c>
       <c r="R489" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O489:Q489)</f>
         <v>19</v>
       </c>
       <c r="S489" s="64">
@@ -45026,7 +45034,7 @@
         <v>61</v>
       </c>
       <c r="R490" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O490:Q490)</f>
         <v>61</v>
       </c>
       <c r="S490" s="70">
@@ -45089,7 +45097,7 @@
         <v>0</v>
       </c>
       <c r="R491" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O491:Q491)</f>
         <v>32</v>
       </c>
       <c r="S491" s="64">
@@ -45152,7 +45160,7 @@
         <v>0</v>
       </c>
       <c r="R492" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O492:Q492)</f>
         <v>43</v>
       </c>
       <c r="S492" s="70">
@@ -45215,7 +45223,7 @@
         <v>0</v>
       </c>
       <c r="R493" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O493:Q493)</f>
         <v>8</v>
       </c>
       <c r="S493" s="64">
@@ -45276,7 +45284,7 @@
         <v>0</v>
       </c>
       <c r="R494" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O494:Q494)</f>
         <v>80</v>
       </c>
       <c r="S494" s="70">
@@ -45331,7 +45339,7 @@
         <v>0</v>
       </c>
       <c r="R495" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O495:Q495)</f>
         <v>0</v>
       </c>
       <c r="S495" s="24"/>
@@ -45388,7 +45396,7 @@
         <v>0</v>
       </c>
       <c r="R496" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O496:Q496)</f>
         <v>170</v>
       </c>
       <c r="S496" s="70">
@@ -45451,7 +45459,7 @@
         <v>0</v>
       </c>
       <c r="R497" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O497:Q497)</f>
         <v>31</v>
       </c>
       <c r="S497" s="64">
@@ -45514,7 +45522,7 @@
         <v>0</v>
       </c>
       <c r="R498" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O498:Q498)</f>
         <v>11</v>
       </c>
       <c r="S498" s="70">
@@ -45577,7 +45585,7 @@
         <v>45</v>
       </c>
       <c r="R499" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O499:Q499)</f>
         <v>45</v>
       </c>
       <c r="S499" s="64">
@@ -45638,7 +45646,7 @@
         <v>0</v>
       </c>
       <c r="R500" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O500:Q500)</f>
         <v>40</v>
       </c>
       <c r="S500" s="70">
@@ -45702,7 +45710,7 @@
         <v>0</v>
       </c>
       <c r="R501" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O501:Q501)</f>
         <v>0</v>
       </c>
       <c r="S501" s="64">
@@ -45765,7 +45773,7 @@
         <v>0</v>
       </c>
       <c r="R502" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O502:Q502)</f>
         <v>34</v>
       </c>
       <c r="S502" s="70">
@@ -45828,7 +45836,7 @@
         <v>0</v>
       </c>
       <c r="R503" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O503:Q503)</f>
         <v>21</v>
       </c>
       <c r="S503" s="64">
@@ -45891,7 +45899,7 @@
         <v>0</v>
       </c>
       <c r="R504" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O504:Q504)</f>
         <v>16</v>
       </c>
       <c r="S504" s="70">
@@ -45952,7 +45960,7 @@
         <v>0</v>
       </c>
       <c r="R505" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O505:Q505)</f>
         <v>20</v>
       </c>
       <c r="S505" s="24">
@@ -46016,7 +46024,7 @@
         <v>0</v>
       </c>
       <c r="R506" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O506:Q506)</f>
         <v>8</v>
       </c>
       <c r="S506" s="22">
@@ -46079,7 +46087,7 @@
         <v>0</v>
       </c>
       <c r="R507" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O507:Q507)</f>
         <v>0</v>
       </c>
       <c r="S507" s="24">
@@ -46142,7 +46150,7 @@
         <v>0</v>
       </c>
       <c r="R508" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O508:Q508)</f>
         <v>13</v>
       </c>
       <c r="S508" s="22">
@@ -46203,7 +46211,7 @@
         <v>0</v>
       </c>
       <c r="R509" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O509:Q509)</f>
         <v>170</v>
       </c>
       <c r="S509" s="24">
@@ -46267,7 +46275,7 @@
         <v>66</v>
       </c>
       <c r="R510" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O510:Q510)</f>
         <v>66</v>
       </c>
       <c r="S510" s="22">
@@ -46328,7 +46336,7 @@
         <v>0</v>
       </c>
       <c r="R511" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O511:Q511)</f>
         <v>140</v>
       </c>
       <c r="S511" s="24">
@@ -46391,7 +46399,7 @@
         <v>0</v>
       </c>
       <c r="R512" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O512:Q512)</f>
         <v>45</v>
       </c>
       <c r="S512" s="22">
@@ -46454,7 +46462,7 @@
         <v>0</v>
       </c>
       <c r="R513" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O513:Q513)</f>
         <v>19</v>
       </c>
       <c r="S513" s="24">
@@ -46517,7 +46525,7 @@
         <v>0</v>
       </c>
       <c r="R514" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O514:Q514)</f>
         <v>15</v>
       </c>
       <c r="S514" s="22">
@@ -46580,7 +46588,7 @@
         <v>41</v>
       </c>
       <c r="R515" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O515:Q515)</f>
         <v>41</v>
       </c>
       <c r="S515" s="24">
@@ -46643,7 +46651,7 @@
         <v>0</v>
       </c>
       <c r="R516" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O516:Q516)</f>
         <v>96</v>
       </c>
       <c r="S516" s="22">
@@ -46707,7 +46715,7 @@
         <v>0</v>
       </c>
       <c r="R517" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O517:Q517)</f>
         <v>6</v>
       </c>
       <c r="S517" s="24">
@@ -46770,7 +46778,7 @@
         <v>0</v>
       </c>
       <c r="R518" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O518:Q518)</f>
         <v>47</v>
       </c>
       <c r="S518" s="22">
@@ -46833,7 +46841,7 @@
         <v>0</v>
       </c>
       <c r="R519" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O519:Q519)</f>
         <v>37</v>
       </c>
       <c r="S519" s="24">
@@ -46896,7 +46904,7 @@
         <v>0</v>
       </c>
       <c r="R520" s="23">
-        <f t="shared" si="8"/>
+        <f>SUM(O520:Q520)</f>
         <v>20</v>
       </c>
       <c r="S520" s="22">
@@ -46959,7 +46967,7 @@
         <v>0</v>
       </c>
       <c r="R521" s="25">
-        <f t="shared" si="8"/>
+        <f>SUM(O521:Q521)</f>
         <v>19</v>
       </c>
       <c r="S521" s="24">
@@ -47022,7 +47030,7 @@
         <v>0</v>
       </c>
       <c r="R522" s="23">
-        <f t="shared" ref="R522:R585" si="9">SUM(O522:Q522)</f>
+        <f>SUM(O522:Q522)</f>
         <v>0</v>
       </c>
       <c r="S522" s="22">
@@ -47085,7 +47093,7 @@
         <v>0</v>
       </c>
       <c r="R523" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O523:Q523)</f>
         <v>0</v>
       </c>
       <c r="S523" s="24">
@@ -47149,7 +47157,7 @@
         <v>0</v>
       </c>
       <c r="R524" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O524:Q524)</f>
         <v>6</v>
       </c>
       <c r="S524" s="22"/>
@@ -47208,7 +47216,7 @@
         <v>0</v>
       </c>
       <c r="R525" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O525:Q525)</f>
         <v>46</v>
       </c>
       <c r="S525" s="24">
@@ -47271,7 +47279,7 @@
         <v>0</v>
       </c>
       <c r="R526" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O526:Q526)</f>
         <v>20</v>
       </c>
       <c r="S526" s="22">
@@ -47326,7 +47334,7 @@
         <v>0</v>
       </c>
       <c r="R527" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O527:Q527)</f>
         <v>0</v>
       </c>
       <c r="S527" s="24"/>
@@ -47387,7 +47395,7 @@
         <v>0</v>
       </c>
       <c r="R528" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O528:Q528)</f>
         <v>20</v>
       </c>
       <c r="S528" s="22">
@@ -47450,7 +47458,7 @@
         <v>1</v>
       </c>
       <c r="R529" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O529:Q529)</f>
         <v>28</v>
       </c>
       <c r="S529" s="24">
@@ -47511,7 +47519,7 @@
         <v>23</v>
       </c>
       <c r="R530" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O530:Q530)</f>
         <v>138</v>
       </c>
       <c r="S530" s="22">
@@ -47574,7 +47582,7 @@
         <v>0</v>
       </c>
       <c r="R531" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O531:Q531)</f>
         <v>19</v>
       </c>
       <c r="S531" s="24">
@@ -47637,7 +47645,7 @@
         <v>0</v>
       </c>
       <c r="R532" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O532:Q532)</f>
         <v>118</v>
       </c>
       <c r="S532" s="22">
@@ -47701,7 +47709,7 @@
         <v>0</v>
       </c>
       <c r="R533" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O533:Q533)</f>
         <v>4</v>
       </c>
       <c r="S533" s="24">
@@ -47764,7 +47772,7 @@
         <v>49</v>
       </c>
       <c r="R534" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O534:Q534)</f>
         <v>49</v>
       </c>
       <c r="S534" s="22">
@@ -47828,7 +47836,7 @@
         <v>94</v>
       </c>
       <c r="R535" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O535:Q535)</f>
         <v>94</v>
       </c>
       <c r="S535" s="24">
@@ -47883,7 +47891,7 @@
         <v>0</v>
       </c>
       <c r="R536" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O536:Q536)</f>
         <v>0</v>
       </c>
       <c r="S536" s="22"/>
@@ -47942,7 +47950,7 @@
         <v>0</v>
       </c>
       <c r="R537" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O537:Q537)</f>
         <v>21</v>
       </c>
       <c r="S537" s="24">
@@ -47999,7 +48007,7 @@
         <v>0</v>
       </c>
       <c r="R538" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O538:Q538)</f>
         <v>49</v>
       </c>
       <c r="S538" s="22"/>
@@ -48058,7 +48066,7 @@
         <v>0</v>
       </c>
       <c r="R539" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O539:Q539)</f>
         <v>26</v>
       </c>
       <c r="S539" s="24">
@@ -48121,7 +48129,7 @@
         <v>0</v>
       </c>
       <c r="R540" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O540:Q540)</f>
         <v>8</v>
       </c>
       <c r="S540" s="22">
@@ -48184,7 +48192,7 @@
         <v>0</v>
       </c>
       <c r="R541" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O541:Q541)</f>
         <v>14</v>
       </c>
       <c r="S541" s="24">
@@ -48247,7 +48255,7 @@
         <v>30</v>
       </c>
       <c r="R542" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O542:Q542)</f>
         <v>30</v>
       </c>
       <c r="S542" s="22">
@@ -48310,7 +48318,7 @@
         <v>0</v>
       </c>
       <c r="R543" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O543:Q543)</f>
         <v>11</v>
       </c>
       <c r="S543" s="24">
@@ -48374,7 +48382,7 @@
         <v>0</v>
       </c>
       <c r="R544" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O544:Q544)</f>
         <v>43</v>
       </c>
       <c r="S544" s="22">
@@ -48437,7 +48445,7 @@
         <v>0</v>
       </c>
       <c r="R545" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O545:Q545)</f>
         <v>54</v>
       </c>
       <c r="S545" s="24">
@@ -48500,7 +48508,7 @@
         <v>0</v>
       </c>
       <c r="R546" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O546:Q546)</f>
         <v>3</v>
       </c>
       <c r="S546" s="22">
@@ -48563,7 +48571,7 @@
         <v>0</v>
       </c>
       <c r="R547" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O547:Q547)</f>
         <v>21</v>
       </c>
       <c r="S547" s="24">
@@ -48626,7 +48634,7 @@
         <v>44</v>
       </c>
       <c r="R548" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O548:Q548)</f>
         <v>44</v>
       </c>
       <c r="S548" s="22">
@@ -48689,7 +48697,7 @@
         <v>0</v>
       </c>
       <c r="R549" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O549:Q549)</f>
         <v>49</v>
       </c>
       <c r="S549" s="24">
@@ -48752,7 +48760,7 @@
         <v>0</v>
       </c>
       <c r="R550" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O550:Q550)</f>
         <v>16</v>
       </c>
       <c r="S550" s="22">
@@ -48815,7 +48823,7 @@
         <v>0</v>
       </c>
       <c r="R551" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O551:Q551)</f>
         <v>27</v>
       </c>
       <c r="S551" s="24">
@@ -48878,7 +48886,7 @@
         <v>60</v>
       </c>
       <c r="R552" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O552:Q552)</f>
         <v>114</v>
       </c>
       <c r="S552" s="22">
@@ -48941,7 +48949,7 @@
         <v>1</v>
       </c>
       <c r="R553" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O553:Q553)</f>
         <v>24</v>
       </c>
       <c r="S553" s="24">
@@ -49004,7 +49012,7 @@
         <v>0</v>
       </c>
       <c r="R554" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O554:Q554)</f>
         <v>21</v>
       </c>
       <c r="S554" s="22">
@@ -49068,7 +49076,7 @@
         <v>38</v>
       </c>
       <c r="R555" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O555:Q555)</f>
         <v>38</v>
       </c>
       <c r="S555" s="24">
@@ -49129,7 +49137,7 @@
         <v>97</v>
       </c>
       <c r="R556" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O556:Q556)</f>
         <v>97</v>
       </c>
       <c r="S556" s="22">
@@ -49193,7 +49201,7 @@
         <v>38</v>
       </c>
       <c r="R557" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O557:Q557)</f>
         <v>38</v>
       </c>
       <c r="S557" s="24">
@@ -49256,7 +49264,7 @@
         <v>0</v>
       </c>
       <c r="R558" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O558:Q558)</f>
         <v>8</v>
       </c>
       <c r="S558" s="22">
@@ -49319,7 +49327,7 @@
         <v>0</v>
       </c>
       <c r="R559" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O559:Q559)</f>
         <v>23</v>
       </c>
       <c r="S559" s="24">
@@ -49382,7 +49390,7 @@
         <v>0</v>
       </c>
       <c r="R560" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O560:Q560)</f>
         <v>20</v>
       </c>
       <c r="S560" s="22">
@@ -49445,7 +49453,7 @@
         <v>0</v>
       </c>
       <c r="R561" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O561:Q561)</f>
         <v>13</v>
       </c>
       <c r="S561" s="24">
@@ -49508,7 +49516,7 @@
         <v>79</v>
       </c>
       <c r="R562" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O562:Q562)</f>
         <v>250</v>
       </c>
       <c r="S562" s="22">
@@ -49571,7 +49579,7 @@
         <v>0</v>
       </c>
       <c r="R563" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O563:Q563)</f>
         <v>32</v>
       </c>
       <c r="S563" s="24">
@@ -49634,7 +49642,7 @@
         <v>0</v>
       </c>
       <c r="R564" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O564:Q564)</f>
         <v>41</v>
       </c>
       <c r="S564" s="22">
@@ -49697,7 +49705,7 @@
         <v>0</v>
       </c>
       <c r="R565" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O565:Q565)</f>
         <v>75</v>
       </c>
       <c r="S565" s="24">
@@ -49758,7 +49766,7 @@
         <v>0</v>
       </c>
       <c r="R566" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O566:Q566)</f>
         <v>100</v>
       </c>
       <c r="S566" s="22">
@@ -49821,7 +49829,7 @@
         <v>0</v>
       </c>
       <c r="R567" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O567:Q567)</f>
         <v>20</v>
       </c>
       <c r="S567" s="24">
@@ -49884,7 +49892,7 @@
         <v>0</v>
       </c>
       <c r="R568" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O568:Q568)</f>
         <v>40</v>
       </c>
       <c r="S568" s="22">
@@ -49947,7 +49955,7 @@
         <v>0</v>
       </c>
       <c r="R569" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O569:Q569)</f>
         <v>48</v>
       </c>
       <c r="S569" s="24">
@@ -50010,7 +50018,7 @@
         <v>0</v>
       </c>
       <c r="R570" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O570:Q570)</f>
         <v>16</v>
       </c>
       <c r="S570" s="22">
@@ -50071,7 +50079,7 @@
         <v>0</v>
       </c>
       <c r="R571" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O571:Q571)</f>
         <v>170</v>
       </c>
       <c r="S571" s="24">
@@ -50132,7 +50140,7 @@
         <v>0</v>
       </c>
       <c r="R572" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O572:Q572)</f>
         <v>80</v>
       </c>
       <c r="S572" s="22">
@@ -50193,7 +50201,7 @@
         <v>18</v>
       </c>
       <c r="R573" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O573:Q573)</f>
         <v>176</v>
       </c>
       <c r="S573" s="24">
@@ -50252,7 +50260,7 @@
         <v>0</v>
       </c>
       <c r="R574" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O574:Q574)</f>
         <v>0</v>
       </c>
       <c r="S574" s="22"/>
@@ -50313,7 +50321,7 @@
         <v>0</v>
       </c>
       <c r="R575" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O575:Q575)</f>
         <v>44</v>
       </c>
       <c r="S575" s="24">
@@ -50377,7 +50385,7 @@
         <v>33</v>
       </c>
       <c r="R576" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O576:Q576)</f>
         <v>41</v>
       </c>
       <c r="S576" s="22">
@@ -50438,7 +50446,7 @@
         <v>0</v>
       </c>
       <c r="R577" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O577:Q577)</f>
         <v>170</v>
       </c>
       <c r="S577" s="24">
@@ -50497,7 +50505,7 @@
         <v>40</v>
       </c>
       <c r="R578" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O578:Q578)</f>
         <v>40</v>
       </c>
       <c r="S578" s="22">
@@ -50556,7 +50564,7 @@
         <v>40</v>
       </c>
       <c r="R579" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O579:Q579)</f>
         <v>40</v>
       </c>
       <c r="S579" s="24">
@@ -50619,7 +50627,7 @@
         <v>0</v>
       </c>
       <c r="R580" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O580:Q580)</f>
         <v>18</v>
       </c>
       <c r="S580" s="22">
@@ -50682,7 +50690,7 @@
         <v>0</v>
       </c>
       <c r="R581" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O581:Q581)</f>
         <v>18</v>
       </c>
       <c r="S581" s="24">
@@ -50745,7 +50753,7 @@
         <v>0</v>
       </c>
       <c r="R582" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O582:Q582)</f>
         <v>38</v>
       </c>
       <c r="S582" s="22">
@@ -50808,7 +50816,7 @@
         <v>0</v>
       </c>
       <c r="R583" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O583:Q583)</f>
         <v>15</v>
       </c>
       <c r="S583" s="24">
@@ -50871,7 +50879,7 @@
         <v>31</v>
       </c>
       <c r="R584" s="23">
-        <f t="shared" si="9"/>
+        <f>SUM(O584:Q584)</f>
         <v>31</v>
       </c>
       <c r="S584" s="22">
@@ -50934,7 +50942,7 @@
         <v>4</v>
       </c>
       <c r="R585" s="25">
-        <f t="shared" si="9"/>
+        <f>SUM(O585:Q585)</f>
         <v>29</v>
       </c>
       <c r="S585" s="24">
@@ -50997,7 +51005,7 @@
         <v>30</v>
       </c>
       <c r="R586" s="23">
-        <f t="shared" ref="R586:R649" si="10">SUM(O586:Q586)</f>
+        <f>SUM(O586:Q586)</f>
         <v>30</v>
       </c>
       <c r="S586" s="22">
@@ -51060,7 +51068,7 @@
         <v>0</v>
       </c>
       <c r="R587" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O587:Q587)</f>
         <v>14</v>
       </c>
       <c r="S587" s="24">
@@ -51123,7 +51131,7 @@
         <v>27</v>
       </c>
       <c r="R588" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O588:Q588)</f>
         <v>27</v>
       </c>
       <c r="S588" s="22">
@@ -51186,7 +51194,7 @@
         <v>0</v>
       </c>
       <c r="R589" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O589:Q589)</f>
         <v>14</v>
       </c>
       <c r="S589" s="24">
@@ -51249,7 +51257,7 @@
         <v>0</v>
       </c>
       <c r="R590" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O590:Q590)</f>
         <v>33</v>
       </c>
       <c r="S590" s="22">
@@ -51312,7 +51320,7 @@
         <v>42</v>
       </c>
       <c r="R591" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O591:Q591)</f>
         <v>42</v>
       </c>
       <c r="S591" s="24">
@@ -51375,7 +51383,7 @@
         <v>0</v>
       </c>
       <c r="R592" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O592:Q592)</f>
         <v>22</v>
       </c>
       <c r="S592" s="22">
@@ -51438,7 +51446,7 @@
         <v>0</v>
       </c>
       <c r="R593" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O593:Q593)</f>
         <v>9</v>
       </c>
       <c r="S593" s="24">
@@ -51501,7 +51509,7 @@
         <v>0</v>
       </c>
       <c r="R594" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O594:Q594)</f>
         <v>20</v>
       </c>
       <c r="S594" s="22">
@@ -51562,7 +51570,7 @@
         <v>25</v>
       </c>
       <c r="R595" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O595:Q595)</f>
         <v>25</v>
       </c>
       <c r="S595" s="24">
@@ -51625,7 +51633,7 @@
         <v>24</v>
       </c>
       <c r="R596" s="73">
-        <f t="shared" si="10"/>
+        <f>SUM(O596:Q596)</f>
         <v>24</v>
       </c>
       <c r="S596" s="70">
@@ -51688,7 +51696,7 @@
         <v>0</v>
       </c>
       <c r="R597" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O597:Q597)</f>
         <v>46</v>
       </c>
       <c r="S597" s="24">
@@ -51751,7 +51759,7 @@
         <v>0</v>
       </c>
       <c r="R598" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O598:Q598)</f>
         <v>37</v>
       </c>
       <c r="S598" s="70">
@@ -51812,7 +51820,7 @@
         <v>0</v>
       </c>
       <c r="R599" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O599:Q599)</f>
         <v>24</v>
       </c>
       <c r="S599" s="64">
@@ -51875,7 +51883,7 @@
         <v>0</v>
       </c>
       <c r="R600" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O600:Q600)</f>
         <v>30</v>
       </c>
       <c r="S600" s="70">
@@ -51938,7 +51946,7 @@
         <v>0</v>
       </c>
       <c r="R601" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O601:Q601)</f>
         <v>21</v>
       </c>
       <c r="S601" s="64">
@@ -52001,7 +52009,7 @@
         <v>0</v>
       </c>
       <c r="R602" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O602:Q602)</f>
         <v>27</v>
       </c>
       <c r="S602" s="22">
@@ -52062,7 +52070,7 @@
         <v>0</v>
       </c>
       <c r="R603" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O603:Q603)</f>
         <v>26</v>
       </c>
       <c r="S603" s="24">
@@ -52125,7 +52133,7 @@
         <v>0</v>
       </c>
       <c r="R604" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O604:Q604)</f>
         <v>28</v>
       </c>
       <c r="S604" s="22">
@@ -52188,7 +52196,7 @@
         <v>0</v>
       </c>
       <c r="R605" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O605:Q605)</f>
         <v>20</v>
       </c>
       <c r="S605" s="24">
@@ -52249,7 +52257,7 @@
         <v>0</v>
       </c>
       <c r="R606" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O606:Q606)</f>
         <v>170</v>
       </c>
       <c r="S606" s="22">
@@ -52310,7 +52318,7 @@
         <v>0</v>
       </c>
       <c r="R607" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O607:Q607)</f>
         <v>170</v>
       </c>
       <c r="S607" s="24">
@@ -52373,7 +52381,7 @@
         <v>0</v>
       </c>
       <c r="R608" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O608:Q608)</f>
         <v>19</v>
       </c>
       <c r="S608" s="22">
@@ -52436,7 +52444,7 @@
         <v>0</v>
       </c>
       <c r="R609" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O609:Q609)</f>
         <v>19</v>
       </c>
       <c r="S609" s="24">
@@ -52497,7 +52505,7 @@
         <v>31</v>
       </c>
       <c r="R610" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O610:Q610)</f>
         <v>31</v>
       </c>
       <c r="S610" s="22">
@@ -52560,7 +52568,7 @@
         <v>0</v>
       </c>
       <c r="R611" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O611:Q611)</f>
         <v>15</v>
       </c>
       <c r="S611" s="24">
@@ -52621,7 +52629,7 @@
         <v>0</v>
       </c>
       <c r="R612" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O612:Q612)</f>
         <v>100</v>
       </c>
       <c r="S612" s="22">
@@ -52682,7 +52690,7 @@
         <v>0</v>
       </c>
       <c r="R613" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O613:Q613)</f>
         <v>114</v>
       </c>
       <c r="S613" s="24">
@@ -52745,7 +52753,7 @@
         <v>0</v>
       </c>
       <c r="R614" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O614:Q614)</f>
         <v>491</v>
       </c>
       <c r="S614" s="22">
@@ -52808,7 +52816,7 @@
         <v>0</v>
       </c>
       <c r="R615" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O615:Q615)</f>
         <v>27</v>
       </c>
       <c r="S615" s="24">
@@ -52869,7 +52877,7 @@
         <v>0</v>
       </c>
       <c r="R616" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O616:Q616)</f>
         <v>63</v>
       </c>
       <c r="S616" s="22">
@@ -52932,7 +52940,7 @@
         <v>0</v>
       </c>
       <c r="R617" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O617:Q617)</f>
         <v>42</v>
       </c>
       <c r="S617" s="24">
@@ -52995,7 +53003,7 @@
         <v>0</v>
       </c>
       <c r="R618" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O618:Q618)</f>
         <v>27</v>
       </c>
       <c r="S618" s="22">
@@ -53058,7 +53066,7 @@
         <v>0</v>
       </c>
       <c r="R619" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O619:Q619)</f>
         <v>40</v>
       </c>
       <c r="S619" s="24">
@@ -53119,7 +53127,7 @@
         <v>0</v>
       </c>
       <c r="R620" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O620:Q620)</f>
         <v>47</v>
       </c>
       <c r="S620" s="22">
@@ -53180,7 +53188,7 @@
         <v>0</v>
       </c>
       <c r="R621" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O621:Q621)</f>
         <v>23</v>
       </c>
       <c r="S621" s="24">
@@ -53241,7 +53249,7 @@
         <v>0</v>
       </c>
       <c r="R622" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O622:Q622)</f>
         <v>21</v>
       </c>
       <c r="S622" s="22">
@@ -53304,7 +53312,7 @@
         <v>0</v>
       </c>
       <c r="R623" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O623:Q623)</f>
         <v>26</v>
       </c>
       <c r="S623" s="24">
@@ -53363,7 +53371,7 @@
         <v>88</v>
       </c>
       <c r="R624" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O624:Q624)</f>
         <v>88</v>
       </c>
       <c r="S624" s="22">
@@ -53424,7 +53432,7 @@
         <v>0</v>
       </c>
       <c r="R625" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O625:Q625)</f>
         <v>33</v>
       </c>
       <c r="S625" s="24">
@@ -53483,7 +53491,7 @@
         <v>128</v>
       </c>
       <c r="R626" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O626:Q626)</f>
         <v>128</v>
       </c>
       <c r="S626" s="22">
@@ -53544,7 +53552,7 @@
         <v>0</v>
       </c>
       <c r="R627" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O627:Q627)</f>
         <v>80</v>
       </c>
       <c r="S627" s="24">
@@ -53605,7 +53613,7 @@
         <v>0</v>
       </c>
       <c r="R628" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O628:Q628)</f>
         <v>23</v>
       </c>
       <c r="S628" s="22" t="s">
@@ -53668,7 +53676,7 @@
         <v>0</v>
       </c>
       <c r="R629" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O629:Q629)</f>
         <v>49</v>
       </c>
       <c r="S629" s="24">
@@ -53729,7 +53737,7 @@
         <v>46</v>
       </c>
       <c r="R630" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O630:Q630)</f>
         <v>228</v>
       </c>
       <c r="S630" s="22">
@@ -53790,7 +53798,7 @@
         <v>0</v>
       </c>
       <c r="R631" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O631:Q631)</f>
         <v>28</v>
       </c>
       <c r="S631" s="24">
@@ -53851,7 +53859,7 @@
         <v>0</v>
       </c>
       <c r="R632" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O632:Q632)</f>
         <v>16</v>
       </c>
       <c r="S632" s="22">
@@ -53912,7 +53920,7 @@
         <v>0</v>
       </c>
       <c r="R633" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O633:Q633)</f>
         <v>40</v>
       </c>
       <c r="S633" s="24">
@@ -53975,7 +53983,7 @@
         <v>0</v>
       </c>
       <c r="R634" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O634:Q634)</f>
         <v>80</v>
       </c>
       <c r="S634" s="22">
@@ -54036,7 +54044,7 @@
         <v>0</v>
       </c>
       <c r="R635" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O635:Q635)</f>
         <v>70</v>
       </c>
       <c r="S635" s="24">
@@ -54097,7 +54105,7 @@
         <v>0</v>
       </c>
       <c r="R636" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O636:Q636)</f>
         <v>28</v>
       </c>
       <c r="S636" s="22">
@@ -54158,7 +54166,7 @@
         <v>30</v>
       </c>
       <c r="R637" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O637:Q637)</f>
         <v>30</v>
       </c>
       <c r="S637" s="24">
@@ -54221,7 +54229,7 @@
         <v>0</v>
       </c>
       <c r="R638" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O638:Q638)</f>
         <v>21</v>
       </c>
       <c r="S638" s="22" t="s">
@@ -54284,7 +54292,7 @@
         <v>40</v>
       </c>
       <c r="R639" s="25">
-        <f t="shared" si="10"/>
+        <f>SUM(O639:Q639)</f>
         <v>179</v>
       </c>
       <c r="S639" s="24">
@@ -54341,7 +54349,7 @@
         <v>0</v>
       </c>
       <c r="R640" s="23">
-        <f t="shared" si="10"/>
+        <f>SUM(O640:Q640)</f>
         <v>0</v>
       </c>
       <c r="S640" s="22">
@@ -54461,7 +54469,7 @@
         <v>33</v>
       </c>
       <c r="R642" s="23">
-        <f t="shared" ref="R642:R649" si="11">SUM(O642:Q642)</f>
+        <f>SUM(O642:Q642)</f>
         <v>33</v>
       </c>
       <c r="S642" s="22">
@@ -54520,7 +54528,7 @@
         <v>39</v>
       </c>
       <c r="R643" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O643:Q643)</f>
         <v>39</v>
       </c>
       <c r="S643" s="24">
@@ -54582,7 +54590,7 @@
         <v>39</v>
       </c>
       <c r="R644" s="23">
-        <f t="shared" si="11"/>
+        <f>SUM(O644:Q644)</f>
         <v>39</v>
       </c>
       <c r="S644" s="22">
@@ -54643,7 +54651,7 @@
         <v>0</v>
       </c>
       <c r="R645" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O645:Q645)</f>
         <v>170</v>
       </c>
       <c r="S645" s="24">
@@ -54706,7 +54714,7 @@
         <v>0</v>
       </c>
       <c r="R646" s="23">
-        <f t="shared" si="11"/>
+        <f>SUM(O646:Q646)</f>
         <v>13</v>
       </c>
       <c r="S646" s="22">
@@ -54767,7 +54775,7 @@
         <v>0</v>
       </c>
       <c r="R647" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O647:Q647)</f>
         <v>34</v>
       </c>
       <c r="S647" s="24">
@@ -54828,7 +54836,7 @@
         <v>0</v>
       </c>
       <c r="R648" s="23">
-        <f t="shared" si="11"/>
+        <f>SUM(O648:Q648)</f>
         <v>45</v>
       </c>
       <c r="S648" s="22">
@@ -54887,7 +54895,7 @@
         <v>0</v>
       </c>
       <c r="R649" s="25">
-        <f t="shared" si="11"/>
+        <f>SUM(O649:Q649)</f>
         <v>72</v>
       </c>
       <c r="S649" s="24">
@@ -55090,7 +55098,7 @@
         <v>2025</v>
       </c>
       <c r="C653" s="92" t="s">
-        <v>21</v>
+        <v>2748</v>
       </c>
       <c r="D653" s="24" t="s">
         <v>2663</v>
@@ -55688,7 +55696,7 @@
         <v>0</v>
       </c>
       <c r="R662" s="23">
-        <f t="shared" ref="R662:R668" si="12">SUM(O662:Q662)</f>
+        <f>SUM(O662:Q662)</f>
         <v>20</v>
       </c>
       <c r="S662" s="22">
@@ -55752,7 +55760,7 @@
         <v>0</v>
       </c>
       <c r="R663" s="25">
-        <f t="shared" si="12"/>
+        <f>SUM(O663:Q663)</f>
         <v>19</v>
       </c>
       <c r="S663" s="24">
@@ -55816,7 +55824,7 @@
         <v>0</v>
       </c>
       <c r="R664" s="23">
-        <f t="shared" si="12"/>
+        <f>SUM(O664:Q664)</f>
         <v>33</v>
       </c>
       <c r="S664" s="22">
@@ -55880,7 +55888,7 @@
         <v>0</v>
       </c>
       <c r="R665" s="25">
-        <f t="shared" si="12"/>
+        <f>SUM(O665:Q665)</f>
         <v>20</v>
       </c>
       <c r="S665" s="24">
@@ -55944,7 +55952,7 @@
         <v>0</v>
       </c>
       <c r="R666" s="23">
-        <f t="shared" si="12"/>
+        <f>SUM(O666:Q666)</f>
         <v>20</v>
       </c>
       <c r="S666" s="22">
@@ -56006,7 +56014,7 @@
         <v>14</v>
       </c>
       <c r="R667" s="25">
-        <f t="shared" si="12"/>
+        <f>SUM(O667:Q667)</f>
         <v>127</v>
       </c>
       <c r="S667" s="24">
@@ -56068,7 +56076,7 @@
         <v>34</v>
       </c>
       <c r="R668" s="23">
-        <f t="shared" si="12"/>
+        <f>SUM(O668:Q668)</f>
         <v>192</v>
       </c>
       <c r="S668" s="22">
@@ -56258,7 +56266,7 @@
         <v>0</v>
       </c>
       <c r="R671" s="25">
-        <f t="shared" ref="R671:R684" si="13">SUM(O671:Q671)</f>
+        <f>SUM(O671:Q671)</f>
         <v>22</v>
       </c>
       <c r="S671" s="24">
@@ -56322,7 +56330,7 @@
         <v>0</v>
       </c>
       <c r="R672" s="178">
-        <f t="shared" si="13"/>
+        <f>SUM(O672:Q672)</f>
         <v>1</v>
       </c>
       <c r="S672" s="172">
@@ -56374,7 +56382,7 @@
       <c r="P673" s="25"/>
       <c r="Q673" s="25"/>
       <c r="R673" s="25">
-        <f t="shared" si="13"/>
+        <f>SUM(O673:Q673)</f>
         <v>0</v>
       </c>
       <c r="S673" s="24"/>
@@ -56432,7 +56440,7 @@
         <v>80</v>
       </c>
       <c r="R674" s="23">
-        <f t="shared" si="13"/>
+        <f>SUM(O674:Q674)</f>
         <v>80</v>
       </c>
       <c r="S674" s="22">
@@ -56492,7 +56500,7 @@
         <v>80</v>
       </c>
       <c r="R675" s="23">
-        <f t="shared" si="13"/>
+        <f>SUM(O675:Q675)</f>
         <v>80</v>
       </c>
       <c r="S675" s="22">
@@ -56546,7 +56554,7 @@
       <c r="P676" s="25"/>
       <c r="Q676" s="25"/>
       <c r="R676" s="25">
-        <f t="shared" si="13"/>
+        <f>SUM(O676:Q676)</f>
         <v>0</v>
       </c>
       <c r="S676" s="24">
@@ -56608,7 +56616,7 @@
         <v>5</v>
       </c>
       <c r="R677" s="193">
-        <f t="shared" si="13"/>
+        <f>SUM(O677:Q677)</f>
         <v>100</v>
       </c>
       <c r="S677" s="186">
@@ -56672,7 +56680,7 @@
         <v>0</v>
       </c>
       <c r="R678" s="63">
-        <f t="shared" si="13"/>
+        <f>SUM(O678:Q678)</f>
         <v>17</v>
       </c>
       <c r="S678" s="64">
@@ -56736,7 +56744,7 @@
         <v>0</v>
       </c>
       <c r="R679" s="185">
-        <f t="shared" si="13"/>
+        <f>SUM(O679:Q679)</f>
         <v>32</v>
       </c>
       <c r="S679" s="180">
@@ -56790,7 +56798,7 @@
       <c r="P680" s="73"/>
       <c r="Q680" s="73"/>
       <c r="R680" s="73">
-        <f t="shared" si="13"/>
+        <f>SUM(O680:Q680)</f>
         <v>0</v>
       </c>
       <c r="S680" s="70">
@@ -56844,7 +56852,7 @@
       <c r="P681" s="193"/>
       <c r="Q681" s="193"/>
       <c r="R681" s="193">
-        <f t="shared" si="13"/>
+        <f>SUM(O681:Q681)</f>
         <v>0</v>
       </c>
       <c r="S681" s="186">
@@ -56898,7 +56906,7 @@
       <c r="P682" s="185"/>
       <c r="Q682" s="185"/>
       <c r="R682" s="185">
-        <f t="shared" si="13"/>
+        <f>SUM(O682:Q682)</f>
         <v>0</v>
       </c>
       <c r="S682" s="180">
@@ -56952,7 +56960,7 @@
       <c r="P683" s="193"/>
       <c r="Q683" s="193"/>
       <c r="R683" s="193">
-        <f t="shared" si="13"/>
+        <f>SUM(O683:Q683)</f>
         <v>0</v>
       </c>
       <c r="S683" s="186">
@@ -57002,7 +57010,7 @@
       <c r="P684" s="73"/>
       <c r="Q684" s="73"/>
       <c r="R684" s="73">
-        <f t="shared" si="13"/>
+        <f>SUM(O684:Q684)</f>
         <v>0</v>
       </c>
       <c r="S684" s="70">
@@ -57056,7 +57064,7 @@
       <c r="P685" s="217"/>
       <c r="Q685" s="217"/>
       <c r="R685" s="217">
-        <f t="shared" ref="R685:R747" si="14">IF(B685="","",SUM(O685:Q685))</f>
+        <f t="shared" ref="R685:R747" si="0">IF(B685="","",SUM(O685:Q685))</f>
         <v>0</v>
       </c>
       <c r="S685" s="210">
@@ -57113,7 +57121,7 @@
       <c r="P686" s="225"/>
       <c r="Q686" s="225"/>
       <c r="R686" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S686" s="219">
@@ -57168,7 +57176,7 @@
       <c r="P687" s="217"/>
       <c r="Q687" s="217"/>
       <c r="R687" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S687" s="210">
@@ -57225,7 +57233,7 @@
       <c r="P688" s="225"/>
       <c r="Q688" s="225"/>
       <c r="R688" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S688" s="219">
@@ -57290,7 +57298,7 @@
         <v>0</v>
       </c>
       <c r="R689" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="S689" s="210">
@@ -57347,7 +57355,7 @@
       <c r="P690" s="225"/>
       <c r="Q690" s="225"/>
       <c r="R690" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S690" s="219">
@@ -57412,7 +57420,7 @@
         <v>0</v>
       </c>
       <c r="R691" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="S691" s="210">
@@ -57477,7 +57485,7 @@
         <v>0</v>
       </c>
       <c r="R692" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S692" s="219">
@@ -57542,7 +57550,7 @@
         <v>0</v>
       </c>
       <c r="R693" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S693" s="210">
@@ -57595,7 +57603,7 @@
       <c r="P694" s="225"/>
       <c r="Q694" s="225"/>
       <c r="R694" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S694" s="219">
@@ -57648,7 +57656,7 @@
       <c r="P695" s="217"/>
       <c r="Q695" s="217"/>
       <c r="R695" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S695" s="210">
@@ -57705,7 +57713,7 @@
         <v>25</v>
       </c>
       <c r="R696" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="S696" s="219">
@@ -57766,7 +57774,7 @@
         <v>50</v>
       </c>
       <c r="R697" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="S697" s="210">
@@ -57819,7 +57827,7 @@
       <c r="P698" s="225"/>
       <c r="Q698" s="225"/>
       <c r="R698" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S698" s="219">
@@ -57874,7 +57882,7 @@
       <c r="P699" s="217"/>
       <c r="Q699" s="217"/>
       <c r="R699" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S699" s="210">
@@ -57929,7 +57937,7 @@
       <c r="P700" s="225"/>
       <c r="Q700" s="225"/>
       <c r="R700" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S700" s="219">
@@ -57984,7 +57992,7 @@
       <c r="P701" s="217"/>
       <c r="Q701" s="217"/>
       <c r="R701" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S701" s="210">
@@ -58037,7 +58045,7 @@
       <c r="P702" s="225"/>
       <c r="Q702" s="225"/>
       <c r="R702" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S702" s="219">
@@ -58090,7 +58098,7 @@
       <c r="P703" s="217"/>
       <c r="Q703" s="217"/>
       <c r="R703" s="217">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S703" s="210">
@@ -58145,7 +58153,7 @@
       <c r="P704" s="225"/>
       <c r="Q704" s="225"/>
       <c r="R704" s="225">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S704" s="219">
@@ -58178,7 +58186,7 @@
       <c r="P705" s="217"/>
       <c r="Q705" s="217"/>
       <c r="R705" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S705" s="210"/>
@@ -58207,7 +58215,7 @@
       <c r="P706" s="225"/>
       <c r="Q706" s="225"/>
       <c r="R706" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S706" s="219"/>
@@ -58236,7 +58244,7 @@
       <c r="P707" s="217"/>
       <c r="Q707" s="217"/>
       <c r="R707" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S707" s="210"/>
@@ -58265,7 +58273,7 @@
       <c r="P708" s="225"/>
       <c r="Q708" s="225"/>
       <c r="R708" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S708" s="219"/>
@@ -58294,7 +58302,7 @@
       <c r="P709" s="217"/>
       <c r="Q709" s="217"/>
       <c r="R709" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S709" s="210"/>
@@ -58323,7 +58331,7 @@
       <c r="P710" s="225"/>
       <c r="Q710" s="225"/>
       <c r="R710" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S710" s="219"/>
@@ -58352,7 +58360,7 @@
       <c r="P711" s="217"/>
       <c r="Q711" s="217"/>
       <c r="R711" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S711" s="210"/>
@@ -58381,7 +58389,7 @@
       <c r="P712" s="225"/>
       <c r="Q712" s="225"/>
       <c r="R712" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S712" s="219"/>
@@ -58410,7 +58418,7 @@
       <c r="P713" s="217"/>
       <c r="Q713" s="217"/>
       <c r="R713" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S713" s="210"/>
@@ -58439,7 +58447,7 @@
       <c r="P714" s="225"/>
       <c r="Q714" s="225"/>
       <c r="R714" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S714" s="219"/>
@@ -58468,7 +58476,7 @@
       <c r="P715" s="217"/>
       <c r="Q715" s="217"/>
       <c r="R715" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S715" s="210"/>
@@ -58497,7 +58505,7 @@
       <c r="P716" s="225"/>
       <c r="Q716" s="225"/>
       <c r="R716" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S716" s="219"/>
@@ -58526,7 +58534,7 @@
       <c r="P717" s="217"/>
       <c r="Q717" s="217"/>
       <c r="R717" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S717" s="210"/>
@@ -58555,7 +58563,7 @@
       <c r="P718" s="225"/>
       <c r="Q718" s="225"/>
       <c r="R718" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S718" s="219"/>
@@ -58584,7 +58592,7 @@
       <c r="P719" s="217"/>
       <c r="Q719" s="217"/>
       <c r="R719" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S719" s="210"/>
@@ -58613,7 +58621,7 @@
       <c r="P720" s="225"/>
       <c r="Q720" s="225"/>
       <c r="R720" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S720" s="219"/>
@@ -58642,7 +58650,7 @@
       <c r="P721" s="217"/>
       <c r="Q721" s="217"/>
       <c r="R721" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S721" s="210"/>
@@ -58671,7 +58679,7 @@
       <c r="P722" s="225"/>
       <c r="Q722" s="225"/>
       <c r="R722" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S722" s="219"/>
@@ -58700,7 +58708,7 @@
       <c r="P723" s="217"/>
       <c r="Q723" s="217"/>
       <c r="R723" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S723" s="210"/>
@@ -58729,7 +58737,7 @@
       <c r="P724" s="225"/>
       <c r="Q724" s="225"/>
       <c r="R724" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S724" s="219"/>
@@ -58758,7 +58766,7 @@
       <c r="P725" s="217"/>
       <c r="Q725" s="217"/>
       <c r="R725" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S725" s="210"/>
@@ -58787,7 +58795,7 @@
       <c r="P726" s="225"/>
       <c r="Q726" s="225"/>
       <c r="R726" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S726" s="219"/>
@@ -58816,7 +58824,7 @@
       <c r="P727" s="217"/>
       <c r="Q727" s="217"/>
       <c r="R727" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S727" s="210"/>
@@ -58845,7 +58853,7 @@
       <c r="P728" s="225"/>
       <c r="Q728" s="225"/>
       <c r="R728" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S728" s="219"/>
@@ -58874,7 +58882,7 @@
       <c r="P729" s="217"/>
       <c r="Q729" s="217"/>
       <c r="R729" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S729" s="210"/>
@@ -58903,7 +58911,7 @@
       <c r="P730" s="225"/>
       <c r="Q730" s="225"/>
       <c r="R730" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S730" s="219"/>
@@ -58932,7 +58940,7 @@
       <c r="P731" s="217"/>
       <c r="Q731" s="217"/>
       <c r="R731" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S731" s="210"/>
@@ -58961,7 +58969,7 @@
       <c r="P732" s="225"/>
       <c r="Q732" s="225"/>
       <c r="R732" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S732" s="219"/>
@@ -58990,7 +58998,7 @@
       <c r="P733" s="217"/>
       <c r="Q733" s="217"/>
       <c r="R733" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S733" s="210"/>
@@ -59019,7 +59027,7 @@
       <c r="P734" s="225"/>
       <c r="Q734" s="225"/>
       <c r="R734" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S734" s="219"/>
@@ -59048,7 +59056,7 @@
       <c r="P735" s="217"/>
       <c r="Q735" s="217"/>
       <c r="R735" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S735" s="210"/>
@@ -59077,7 +59085,7 @@
       <c r="P736" s="225"/>
       <c r="Q736" s="225"/>
       <c r="R736" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S736" s="219"/>
@@ -59106,7 +59114,7 @@
       <c r="P737" s="217"/>
       <c r="Q737" s="217"/>
       <c r="R737" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S737" s="210"/>
@@ -59135,7 +59143,7 @@
       <c r="P738" s="225"/>
       <c r="Q738" s="225"/>
       <c r="R738" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S738" s="219"/>
@@ -59164,7 +59172,7 @@
       <c r="P739" s="217"/>
       <c r="Q739" s="217"/>
       <c r="R739" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S739" s="210"/>
@@ -59193,7 +59201,7 @@
       <c r="P740" s="225"/>
       <c r="Q740" s="225"/>
       <c r="R740" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S740" s="219"/>
@@ -59222,7 +59230,7 @@
       <c r="P741" s="217"/>
       <c r="Q741" s="217"/>
       <c r="R741" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S741" s="210"/>
@@ -59251,7 +59259,7 @@
       <c r="P742" s="225"/>
       <c r="Q742" s="225"/>
       <c r="R742" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S742" s="219"/>
@@ -59280,7 +59288,7 @@
       <c r="P743" s="217"/>
       <c r="Q743" s="217"/>
       <c r="R743" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S743" s="210"/>
@@ -59309,7 +59317,7 @@
       <c r="P744" s="225"/>
       <c r="Q744" s="225"/>
       <c r="R744" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S744" s="219"/>
@@ -59338,7 +59346,7 @@
       <c r="P745" s="217"/>
       <c r="Q745" s="217"/>
       <c r="R745" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S745" s="210"/>
@@ -59367,7 +59375,7 @@
       <c r="P746" s="225"/>
       <c r="Q746" s="225"/>
       <c r="R746" s="225" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S746" s="219"/>
@@ -59396,7 +59404,7 @@
       <c r="P747" s="217"/>
       <c r="Q747" s="217"/>
       <c r="R747" s="217" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="S747" s="210"/>
@@ -59425,7 +59433,7 @@
       <c r="P748" s="225"/>
       <c r="Q748" s="225"/>
       <c r="R748" s="225" t="str">
-        <f t="shared" ref="R748" si="15">IF(B748="","",SUM(O748:Q748))</f>
+        <f t="shared" ref="R748" si="1">IF(B748="","",SUM(O748:Q748))</f>
         <v/>
       </c>
       <c r="S748" s="219"/>
@@ -68632,6 +68640,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052D3A7BF04652843BCB50FE90745AA50" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ef6274641b2f7d621af528393bef14e5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe686eaa-0658-4f15-b230-9e46c4d089fd" xmlns:ns3="91ce1707-6d34-452b-b217-9734c03e6729" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fa87a3bcf42251a9fb9988d55372596" ns2:_="" ns3:_="">
     <xsd:import namespace="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
@@ -68832,27 +68860,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
+    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -68869,23 +68896,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
-    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4952" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B86F03D-09AA-42A2-9956-43D22E40A03F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-28800" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4952" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B86F03D-09AA-42A2-9956-43D22E40A03F}"/>
+  <xr:revisionPtr revIDLastSave="4953" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C66F068-B9FC-4F70-A586-A4DA4954F3B2}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-28800" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -12292,7 +12292,7 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>14</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>9</c:v>
@@ -12873,7 +12873,7 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -58010,7 +58010,7 @@
         <v>2026</v>
       </c>
       <c r="C702" s="219" t="s">
-        <v>2748</v>
+        <v>21</v>
       </c>
       <c r="D702" s="219" t="s">
         <v>2821</v>
@@ -62353,7 +62353,7 @@
         <v>2026-046</v>
       </c>
       <c r="N38" t="str">
-        <v>Em andamento</v>
+        <v>Realizado</v>
       </c>
       <c r="O38" t="str">
         <v>Curso “Sisaudit na Prática”</v>
@@ -63569,7 +63569,7 @@
         <v>2026-046</v>
       </c>
       <c r="C67" t="str">
-        <v>Em andamento</v>
+        <v>Realizado</v>
       </c>
       <c r="D67" t="str">
         <v>Curso “Sisaudit na Prática”</v>
@@ -63607,7 +63607,7 @@
         <v>2026-046</v>
       </c>
       <c r="C68" t="str">
-        <v>Em andamento</v>
+        <v>Realizado</v>
       </c>
       <c r="D68" t="str">
         <v>Curso “Sisaudit na Prática”</v>
@@ -63645,7 +63645,7 @@
         <v>2026-046</v>
       </c>
       <c r="C69" t="str">
-        <v>Em andamento</v>
+        <v>Realizado</v>
       </c>
       <c r="D69" t="str">
         <v>Curso “Sisaudit na Prática”</v>
@@ -64908,7 +64908,7 @@
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="124" t="s">
         <v>2877</v>
@@ -64963,7 +64963,7 @@
       </c>
       <c r="B11" s="110">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!F:F,"Servidores do TCDF")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="109" t="s">
         <v>2883</v>
@@ -65011,7 +65011,7 @@
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="113" t="s">
         <v>2887</v>
@@ -65072,7 +65072,7 @@
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.26829268292682928</v>
+        <v>0.26190476190476192</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65093,7 +65093,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>7.3170731707317069E-2</v>
+        <v>7.1428571428571425E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65114,7 +65114,7 @@
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>0.12195121951219512</v>
+        <v>0.11904761904761904</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65135,7 +65135,7 @@
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>2.4390243902439025E-2</v>
+        <v>2.3809523809523808E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65156,7 +65156,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>4.878048780487805E-2</v>
+        <v>4.7619047619047616E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65177,7 +65177,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.17073170731707318</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65186,7 +65186,7 @@
       </c>
       <c r="B39" s="145">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A39)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" s="146">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A39)</f>
@@ -65194,11 +65194,11 @@
       </c>
       <c r="D39" s="145">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>7.3170731707317069E-2</v>
+        <v>9.5238095238095233E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65219,7 +65219,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>2.4390243902439025E-2</v>
+        <v>2.3809523809523808E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65240,7 +65240,7 @@
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.14634146341463414</v>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65282,7 +65282,7 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>4.878048780487805E-2</v>
+        <v>4.7619047619047616E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65312,7 +65312,7 @@
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
@@ -65320,11 +65320,11 @@
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4953" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C66F068-B9FC-4F70-A586-A4DA4954F3B2}"/>
+  <xr:revisionPtr revIDLastSave="4954" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC9B89C7-E23A-4B89-8CC0-62C3F83EB0EA}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12295,7 +12295,7 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -12879,7 +12879,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -56817,7 +56817,7 @@
         <v>2026</v>
       </c>
       <c r="C681" s="70" t="s">
-        <v>2748</v>
+        <v>21</v>
       </c>
       <c r="D681" s="186" t="s">
         <v>2753</v>
@@ -61251,7 +61251,7 @@
         <v>2026-025</v>
       </c>
       <c r="N23" t="str">
-        <v>Em andamento</v>
+        <v>Realizado</v>
       </c>
       <c r="O23" t="str">
         <v>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T3</v>
@@ -62536,7 +62536,7 @@
         <v>2026-025</v>
       </c>
       <c r="C41" s="163" t="str">
-        <v>Em andamento</v>
+        <v>Realizado</v>
       </c>
       <c r="D41" t="str">
         <v>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T3</v>
@@ -62589,7 +62589,7 @@
         <v>2026-025</v>
       </c>
       <c r="C42" s="163" t="str">
-        <v>Em andamento</v>
+        <v>Realizado</v>
       </c>
       <c r="D42" t="str">
         <v>Curso de formação para gestores e fiscais de Contrato em equipamentos nas unidades hospitalares - T3</v>
@@ -64908,7 +64908,7 @@
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="124" t="s">
         <v>2877</v>
@@ -64979,7 +64979,7 @@
       </c>
       <c r="B12" s="112">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!F:F,"Jurisdicionados")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="111" t="s">
         <v>2884</v>
@@ -65011,7 +65011,7 @@
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="113" t="s">
         <v>2887</v>
@@ -65072,7 +65072,7 @@
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.26190476190476192</v>
+        <v>0.2558139534883721</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65093,7 +65093,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>7.1428571428571425E-2</v>
+        <v>6.9767441860465115E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65114,7 +65114,7 @@
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>0.11904761904761904</v>
+        <v>0.11627906976744186</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65135,7 +65135,7 @@
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>2.3809523809523808E-2</v>
+        <v>2.3255813953488372E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65156,7 +65156,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>4.7619047619047616E-2</v>
+        <v>4.6511627906976744E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65177,7 +65177,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>0.16279069767441862</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65198,7 +65198,7 @@
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>9.5238095238095233E-2</v>
+        <v>9.3023255813953487E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65219,7 +65219,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>2.3809523809523808E-2</v>
+        <v>2.3255813953488372E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65228,7 +65228,7 @@
       </c>
       <c r="B41" s="151">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A41)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C41" s="152">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A41)</f>
@@ -65236,11 +65236,11 @@
       </c>
       <c r="D41" s="151">
         <f>B41+C41</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.14285714285714285</v>
+        <v>0.16279069767441862</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65282,7 +65282,7 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>4.7619047619047616E-2</v>
+        <v>4.6511627906976744E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65312,7 +65312,7 @@
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
@@ -65320,7 +65320,7 @@
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4954" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC9B89C7-E23A-4B89-8CC0-62C3F83EB0EA}"/>
+  <xr:revisionPtr revIDLastSave="4959" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAD4F254-6D07-4700-BE5D-6CD77750A874}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4959" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAD4F254-6D07-4700-BE5D-6CD77750A874}"/>
+  <xr:revisionPtr revIDLastSave="4963" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DADFCD7-77D8-49AA-BD75-7734A2EC0074}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12521,7 +12521,7 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>417</c:v>
+                  <c:v>461</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>403</c:v>
@@ -56847,13 +56847,21 @@
         <v>9211.69</v>
       </c>
       <c r="M681" s="197"/>
-      <c r="N681" s="192"/>
-      <c r="O681" s="193"/>
-      <c r="P681" s="193"/>
-      <c r="Q681" s="193"/>
+      <c r="N681" s="192">
+        <v>30</v>
+      </c>
+      <c r="O681" s="193">
+        <v>44</v>
+      </c>
+      <c r="P681" s="193">
+        <v>0</v>
+      </c>
+      <c r="Q681" s="193">
+        <v>0</v>
+      </c>
       <c r="R681" s="193">
         <f>SUM(O681:Q681)</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="S681" s="186">
         <v>12</v>
@@ -64970,7 +64978,7 @@
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>417</v>
+        <v>461</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -65018,7 +65026,7 @@
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
-        <v>1190</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4963" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DADFCD7-77D8-49AA-BD75-7734A2EC0074}"/>
+  <xr:revisionPtr revIDLastSave="4969" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A72A948-B865-4D76-8A38-0F68C3BE43FE}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12521,10 +12521,10 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>461</c:v>
+                  <c:v>437</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>403</c:v>
+                  <c:v>447</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>370</c:v>
@@ -56851,10 +56851,10 @@
         <v>30</v>
       </c>
       <c r="O681" s="193">
+        <v>0</v>
+      </c>
+      <c r="P681" s="193">
         <v>44</v>
-      </c>
-      <c r="P681" s="193">
-        <v>0</v>
       </c>
       <c r="Q681" s="193">
         <v>0</v>
@@ -58049,12 +58049,18 @@
       <c r="N702" s="226">
         <v>20</v>
       </c>
-      <c r="O702" s="225"/>
-      <c r="P702" s="225"/>
-      <c r="Q702" s="225"/>
+      <c r="O702" s="225">
+        <v>20</v>
+      </c>
+      <c r="P702" s="225">
+        <v>0</v>
+      </c>
+      <c r="Q702" s="225">
+        <v>0</v>
+      </c>
       <c r="R702" s="225">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S702" s="219">
         <v>12</v>
@@ -64978,7 +64984,7 @@
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -64994,7 +65000,7 @@
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>403</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -65026,7 +65032,7 @@
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
-        <v>1234</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4969" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A72A948-B865-4D76-8A38-0F68C3BE43FE}"/>
+  <xr:revisionPtr revIDLastSave="4970" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1409C99E-45A8-45F9-9F68-D8C1D4B0BA0C}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58044,7 +58044,9 @@
       <c r="K702" s="219" t="s">
         <v>34</v>
       </c>
-      <c r="L702" s="224"/>
+      <c r="L702" s="224">
+        <v>17867.79</v>
+      </c>
       <c r="M702" s="215"/>
       <c r="N702" s="226">
         <v>20</v>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4970" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1409C99E-45A8-45F9-9F68-D8C1D4B0BA0C}"/>
+  <xr:revisionPtr revIDLastSave="4972" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4D990A1-A76C-4B2D-8328-55B756D2437A}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58045,7 +58045,7 @@
         <v>34</v>
       </c>
       <c r="L702" s="224">
-        <v>17867.79</v>
+        <v>9746.07</v>
       </c>
       <c r="M702" s="215"/>
       <c r="N702" s="226">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4972" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4D990A1-A76C-4B2D-8328-55B756D2437A}"/>
+  <xr:revisionPtr revIDLastSave="4973" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76422104-D22E-4146-9B0D-E6C28B7B9778}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -14979,10 +14979,6 @@
 <namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}" name="Tabela2" displayName="Tabela2" ref="B1:T684" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="B1:T684" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}">
@@ -68656,26 +68652,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052D3A7BF04652843BCB50FE90745AA50" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ef6274641b2f7d621af528393bef14e5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe686eaa-0658-4f15-b230-9e46c4d089fd" xmlns:ns3="91ce1707-6d34-452b-b217-9734c03e6729" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fa87a3bcf42251a9fb9988d55372596" ns2:_="" ns3:_="">
     <xsd:import namespace="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
@@ -68876,26 +68852,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
-    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -68912,4 +68889,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
+    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4989" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE4DC3ED-9E3A-4570-8677-91AEDE30D705}"/>
+  <xr:revisionPtr revIDLastSave="4990" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B97BF320-871C-4240-8B7B-0CEE61BE455C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6545" uniqueCount="2965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6546" uniqueCount="2966">
   <si>
     <t>ID</t>
   </si>
@@ -9063,6 +9063,9 @@
   </si>
   <si>
     <t>Participantes</t>
+  </si>
+  <si>
+    <t>José Roberto Alcuri Júnior; Felipe Ramos Barbosa; Carolina Pereira de Oliveira; Eustáquio Rabelo de Souza; Alinne Patrícia de Andrade Carvalho; Silvia Lima Damasceno; Marcelo Santana; Cinthia Thomazi; Igor Queiroz; Guilherme Bride Fernandes</t>
   </si>
 </sst>
 </file>
@@ -58004,7 +58007,9 @@
       <c r="S701" s="210">
         <v>8</v>
       </c>
-      <c r="T701" s="209"/>
+      <c r="T701" s="209" t="s">
+        <v>2965</v>
+      </c>
       <c r="U701" s="203"/>
     </row>
     <row r="702" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -59676,7 +59681,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="98" cm="1">
-        <f t="array" ref="A2:J73">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
+        <f t="array" ref="A2:J82">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
         <v>2026</v>
       </c>
       <c r="B2" s="98" t="str">
@@ -62304,14 +62309,14 @@
       <c r="P37">
         <v>8</v>
       </c>
-      <c r="Q37">
-        <v>0</v>
+      <c r="Q37" t="str">
+        <v>José Roberto Alcuri Júnior; Felipe Ramos Barbosa; Carolina Pereira de Oliveira; Eustáquio Rabelo de Souza; Alinne Patrícia de Andrade Carvalho; Silvia Lima Damasceno; Marcelo Santana; Cinthia Thomazi; Igor Queiroz; Guilherme Bride Fernandes</v>
       </c>
       <c r="R37">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="T37">
         <v>64</v>
@@ -62382,10 +62387,10 @@
         <v>3</v>
       </c>
       <c r="S38">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="T38">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="X38" t="s">
         <v>2880</v>
@@ -62453,10 +62458,10 @@
         <v>2</v>
       </c>
       <c r="S39">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="T39">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="X39" t="s">
         <v>2881</v>
@@ -62524,10 +62529,10 @@
         <v>2</v>
       </c>
       <c r="S40">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="T40">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="X40" t="s">
         <v>2882</v>
@@ -62580,7 +62585,7 @@
         <v/>
       </c>
       <c r="T41">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="X41" t="s">
         <v>2883</v>
@@ -63554,19 +63559,19 @@
         <v>8</v>
       </c>
       <c r="F66" t="str">
-        <v>0</v>
+        <v>José Roberto Alcuri Júnior</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H66">
         <v>8</v>
       </c>
       <c r="I66">
-        <v>2.4</v>
+        <v>0.24</v>
       </c>
       <c r="J66">
-        <v>10.4</v>
+        <v>8.24</v>
       </c>
       <c r="R66" t="str">
         <v/>
@@ -63580,31 +63585,31 @@
         <v>2026</v>
       </c>
       <c r="B67" t="str">
-        <v>2026-046</v>
+        <v>2026-045</v>
       </c>
       <c r="C67" t="str">
-        <v>Realizado</v>
+        <v>A realizar</v>
       </c>
       <c r="D67" t="str">
-        <v>Curso “Sisaudit na Prática”</v>
+        <v>31º SEMAT</v>
       </c>
       <c r="E67">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F67" t="str">
-        <v>Davi Assunção Salvador Nery de Castro</v>
+        <v>Felipe Ramos Barbosa</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H67">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I67">
-        <v>1.2</v>
+        <v>0.24</v>
       </c>
       <c r="J67">
-        <v>13.2</v>
+        <v>8.24</v>
       </c>
       <c r="R67" t="str">
         <v/>
@@ -63618,31 +63623,31 @@
         <v>2026</v>
       </c>
       <c r="B68" t="str">
-        <v>2026-046</v>
+        <v>2026-045</v>
       </c>
       <c r="C68" t="str">
-        <v>Realizado</v>
+        <v>A realizar</v>
       </c>
       <c r="D68" t="str">
-        <v>Curso “Sisaudit na Prática”</v>
+        <v>31º SEMAT</v>
       </c>
       <c r="E68">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F68" t="str">
-        <v>David da Silva de Araújo</v>
+        <v>Carolina Pereira de Oliveira</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H68">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I68">
-        <v>1.2</v>
+        <v>0.24</v>
       </c>
       <c r="J68">
-        <v>13.2</v>
+        <v>8.24</v>
       </c>
       <c r="R68" t="str">
         <v/>
@@ -63656,31 +63661,31 @@
         <v>2026</v>
       </c>
       <c r="B69" t="str">
-        <v>2026-046</v>
+        <v>2026-045</v>
       </c>
       <c r="C69" t="str">
-        <v>Realizado</v>
+        <v>A realizar</v>
       </c>
       <c r="D69" t="str">
-        <v>Curso “Sisaudit na Prática”</v>
+        <v>31º SEMAT</v>
       </c>
       <c r="E69">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F69" t="str">
-        <v>Hamilton de Jesus Lopes Neto</v>
+        <v>Eustáquio Rabelo de Souza</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H69">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I69">
-        <v>1.2</v>
+        <v>0.24</v>
       </c>
       <c r="J69">
-        <v>13.2</v>
+        <v>8.24</v>
       </c>
       <c r="R69" t="str">
         <v/>
@@ -63694,31 +63699,31 @@
         <v>2026</v>
       </c>
       <c r="B70" t="str">
-        <v>2026-047</v>
+        <v>2026-045</v>
       </c>
       <c r="C70" t="str">
         <v>A realizar</v>
       </c>
       <c r="D70" t="str">
-        <v>Contratações de TIC com base na jurisprudência do TCDF</v>
+        <v>31º SEMAT</v>
       </c>
       <c r="E70">
-        <v>17.45</v>
+        <v>8</v>
       </c>
       <c r="F70" t="str">
-        <v>Flávio José Fonseca de Souza</v>
+        <v>Alinne Patrícia de Andrade Carvalho</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I70">
-        <v>34.9</v>
+        <v>0.24</v>
       </c>
       <c r="J70">
-        <v>34.9</v>
+        <v>8.24</v>
       </c>
       <c r="R70" t="str">
         <v/>
@@ -63732,31 +63737,31 @@
         <v>2026</v>
       </c>
       <c r="B71" t="str">
-        <v>2026-047</v>
+        <v>2026-045</v>
       </c>
       <c r="C71" t="str">
         <v>A realizar</v>
       </c>
       <c r="D71" t="str">
-        <v>Contratações de TIC com base na jurisprudência do TCDF</v>
+        <v>31º SEMAT</v>
       </c>
       <c r="E71">
-        <v>17.45</v>
+        <v>8</v>
       </c>
       <c r="F71" t="str">
-        <v>Felipe da Costa Malaquias</v>
+        <v>Silvia Lima Damasceno</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I71">
-        <v>34.9</v>
+        <v>0.24</v>
       </c>
       <c r="J71">
-        <v>34.9</v>
+        <v>8.24</v>
       </c>
       <c r="R71" t="str">
         <v/>
@@ -63770,31 +63775,31 @@
         <v>2026</v>
       </c>
       <c r="B72" t="str">
-        <v>2026-048</v>
+        <v>2026-045</v>
       </c>
       <c r="C72" t="str">
         <v>A realizar</v>
       </c>
       <c r="D72" t="str">
-        <v>Introdução à Engenharia de Prompt - SEE</v>
+        <v>31º SEMAT</v>
       </c>
       <c r="E72">
         <v>8</v>
       </c>
       <c r="F72" t="str">
-        <v>Arthur Wú</v>
+        <v>Marcelo Santana</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H72">
         <v>8</v>
       </c>
       <c r="I72">
-        <v>2.4</v>
+        <v>0.24</v>
       </c>
       <c r="J72">
-        <v>10.4</v>
+        <v>8.24</v>
       </c>
       <c r="R72" t="str">
         <v/>
@@ -63808,40 +63813,70 @@
         <v>2026</v>
       </c>
       <c r="B73" t="str">
-        <v>2026-048</v>
+        <v>2026-045</v>
       </c>
       <c r="C73" t="str">
         <v>A realizar</v>
       </c>
       <c r="D73" t="str">
-        <v>Introdução à Engenharia de Prompt - SEE</v>
+        <v>31º SEMAT</v>
       </c>
       <c r="E73">
         <v>8</v>
       </c>
       <c r="F73" t="str">
-        <v>Gustavo Takahashi</v>
+        <v>Cinthia Thomazi</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H73">
         <v>8</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="J73">
+        <v>8.24</v>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
+      <c r="S73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2026</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2026-045</v>
+      </c>
+      <c r="C74" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D74" t="str">
+        <v>31º SEMAT</v>
+      </c>
+      <c r="E74">
         <v>8</v>
       </c>
-      <c r="R73" t="str">
-        <v/>
-      </c>
-      <c r="S73" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F74" t="str">
+        <v>Igor Queiroz</v>
+      </c>
+      <c r="G74">
+        <v>10</v>
+      </c>
+      <c r="H74">
+        <v>8</v>
+      </c>
+      <c r="I74">
+        <v>0.24</v>
+      </c>
+      <c r="J74">
+        <v>8.24</v>
+      </c>
       <c r="R74" t="str">
         <v/>
       </c>
@@ -63850,6 +63885,36 @@
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2026</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2026-045</v>
+      </c>
+      <c r="C75" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D75" t="str">
+        <v>31º SEMAT</v>
+      </c>
+      <c r="E75">
+        <v>8</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Guilherme Bride Fernandes</v>
+      </c>
+      <c r="G75">
+        <v>10</v>
+      </c>
+      <c r="H75">
+        <v>8</v>
+      </c>
+      <c r="I75">
+        <v>0.24</v>
+      </c>
+      <c r="J75">
+        <v>8.24</v>
+      </c>
       <c r="R75" t="str">
         <v/>
       </c>
@@ -63858,6 +63923,36 @@
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2026</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2026-046</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Realizado</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Curso “Sisaudit na Prática”</v>
+      </c>
+      <c r="E76">
+        <v>12</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Davi Assunção Salvador Nery de Castro</v>
+      </c>
+      <c r="G76">
+        <v>3</v>
+      </c>
+      <c r="H76">
+        <v>12</v>
+      </c>
+      <c r="I76">
+        <v>1.2</v>
+      </c>
+      <c r="J76">
+        <v>13.2</v>
+      </c>
       <c r="R76" t="str">
         <v/>
       </c>
@@ -63866,6 +63961,36 @@
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2026</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2026-046</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Realizado</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Curso “Sisaudit na Prática”</v>
+      </c>
+      <c r="E77">
+        <v>12</v>
+      </c>
+      <c r="F77" t="str">
+        <v>David da Silva de Araújo</v>
+      </c>
+      <c r="G77">
+        <v>3</v>
+      </c>
+      <c r="H77">
+        <v>12</v>
+      </c>
+      <c r="I77">
+        <v>1.2</v>
+      </c>
+      <c r="J77">
+        <v>13.2</v>
+      </c>
       <c r="R77" t="str">
         <v/>
       </c>
@@ -63874,6 +63999,36 @@
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2026</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2026-046</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Realizado</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Curso “Sisaudit na Prática”</v>
+      </c>
+      <c r="E78">
+        <v>12</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Hamilton de Jesus Lopes Neto</v>
+      </c>
+      <c r="G78">
+        <v>3</v>
+      </c>
+      <c r="H78">
+        <v>12</v>
+      </c>
+      <c r="I78">
+        <v>1.2</v>
+      </c>
+      <c r="J78">
+        <v>13.2</v>
+      </c>
       <c r="R78" t="str">
         <v/>
       </c>
@@ -63882,6 +64037,36 @@
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>2026</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2026-047</v>
+      </c>
+      <c r="C79" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Contratações de TIC com base na jurisprudência do TCDF</v>
+      </c>
+      <c r="E79">
+        <v>17.45</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Flávio José Fonseca de Souza</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>34.9</v>
+      </c>
+      <c r="J79">
+        <v>34.9</v>
+      </c>
       <c r="R79" t="str">
         <v/>
       </c>
@@ -63890,6 +64075,36 @@
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2026</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2026-047</v>
+      </c>
+      <c r="C80" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Contratações de TIC com base na jurisprudência do TCDF</v>
+      </c>
+      <c r="E80">
+        <v>17.45</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Felipe da Costa Malaquias</v>
+      </c>
+      <c r="G80">
+        <v>2</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>34.9</v>
+      </c>
+      <c r="J80">
+        <v>34.9</v>
+      </c>
       <c r="R80" t="str">
         <v/>
       </c>
@@ -63897,7 +64112,37 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>2026</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2026-048</v>
+      </c>
+      <c r="C81" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Introdução à Engenharia de Prompt - SEE</v>
+      </c>
+      <c r="E81">
+        <v>8</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Arthur Wú</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81">
+        <v>8</v>
+      </c>
+      <c r="I81">
+        <v>2.4</v>
+      </c>
+      <c r="J81">
+        <v>10.4</v>
+      </c>
       <c r="R81" t="str">
         <v/>
       </c>
@@ -63905,7 +64150,37 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>2026</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2026-048</v>
+      </c>
+      <c r="C82" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Introdução à Engenharia de Prompt - SEE</v>
+      </c>
+      <c r="E82">
+        <v>8</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Gustavo Takahashi</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>8</v>
+      </c>
       <c r="R82" t="str">
         <v/>
       </c>
@@ -63913,7 +64188,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R83" t="str">
         <v/>
       </c>
@@ -63921,7 +64196,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R84" t="str">
         <v/>
       </c>
@@ -63929,7 +64204,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R85" t="str">
         <v/>
       </c>
@@ -63937,7 +64212,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R86" t="str">
         <v/>
       </c>
@@ -63945,7 +64220,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R87" t="str">
         <v/>
       </c>
@@ -63953,7 +64228,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R88" t="str">
         <v/>
       </c>
@@ -63961,7 +64236,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R89" t="str">
         <v/>
       </c>
@@ -63969,7 +64244,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R90" t="str">
         <v/>
       </c>
@@ -63977,7 +64252,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R91" t="str">
         <v/>
       </c>
@@ -63985,7 +64260,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R92" t="str">
         <v/>
       </c>
@@ -63993,7 +64268,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R93" t="str">
         <v/>
       </c>
@@ -64001,7 +64276,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R94" t="str">
         <v/>
       </c>
@@ -64009,7 +64284,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R95" t="str">
         <v/>
       </c>
@@ -64017,7 +64292,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="18:19" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R96" t="str">
         <v/>
       </c>
@@ -65920,16 +66195,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="str" cm="1">
-        <f t="array" ref="A5:A35">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32),_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32)&lt;&gt;""))),"")</f>
-        <v>0</v>
+        <f t="array" ref="A5:A44">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32),_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32)&lt;&gt;""))),"")</f>
+        <v>Adriana Cuoco Portugal</v>
       </c>
       <c r="B5" s="103">
         <f>IF($A5="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A5))</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C5" s="103">
         <f>IF($A5="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A5))</f>
-        <v>2.4</v>
+        <v>3.84</v>
       </c>
       <c r="D5" s="256">
         <f>IF($A5="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A5))</f>
@@ -65937,11 +66212,11 @@
       </c>
       <c r="E5" s="241">
         <f>IF($A5="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A5)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A5))</f>
-        <v>10.4</v>
+        <v>19.84</v>
       </c>
       <c r="F5" s="101">
         <f>IF($A5="","",COUNTIFS('GECC 2026'!F$2:F$200,$A5))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5" s="101">
         <f>IF($A5="","",COUNTIFS('GECC 2026'!G$2:G$200,$A5))</f>
@@ -65950,15 +66225,15 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <v>Adriana Cuoco Portugal</v>
+        <v>Adriana Magalhães</v>
       </c>
       <c r="B6" s="103">
         <f>IF($A6="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A6))</f>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C6" s="103">
         <f>IF($A6="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A6))</f>
-        <v>3.84</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="D6" s="256">
         <f>IF($A6="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A6))</f>
@@ -65966,24 +66241,24 @@
       </c>
       <c r="E6" s="241">
         <f>IF($A6="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A6)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A6))</f>
-        <v>19.84</v>
+        <v>27.6</v>
       </c>
       <c r="F6" s="101">
         <f>IF($A6="","",COUNTIFS('GECC 2026'!F$2:F$200,$A6))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <v>Adriana Magalhães</v>
+        <v>Alinne Patrícia de Andrade Carvalho</v>
       </c>
       <c r="B7" s="103">
         <f>IF($A7="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A7))</f>
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C7" s="103">
         <f>IF($A7="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A7))</f>
-        <v>3.5999999999999996</v>
+        <v>0.24</v>
       </c>
       <c r="D7" s="256">
         <f>IF($A7="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A7))</f>
@@ -65991,11 +66266,11 @@
       </c>
       <c r="E7" s="241">
         <f>IF($A7="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A7)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A7))</f>
-        <v>27.6</v>
+        <v>8.24</v>
       </c>
       <c r="F7" s="101">
         <f>IF($A7="","",COUNTIFS('GECC 2026'!F$2:F$200,$A7))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -66025,23 +66300,23 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
-        <v>Cássio Murilo Alves Costa Filho</v>
+        <v>Carolina Pereira de Oliveira</v>
       </c>
       <c r="B9" s="103">
         <f>IF($A9="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A9))</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C9" s="103">
         <f>IF($A9="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A9))</f>
-        <v>4.8</v>
+        <v>0.24</v>
       </c>
       <c r="D9" s="256">
         <f>IF($A9="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A9))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E9" s="241">
         <f>IF($A9="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A9)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A9))</f>
-        <v>36.799999999999997</v>
+        <v>8.24</v>
       </c>
       <c r="F9" s="101">
         <f>IF($A9="","",COUNTIFS('GECC 2026'!F$2:F$200,$A9))</f>
@@ -66050,40 +66325,40 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
-        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
+        <v>Cássio Murilo Alves Costa Filho</v>
       </c>
       <c r="B10" s="103">
         <f>IF($A10="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A10))</f>
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C10" s="103">
         <f>IF($A10="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A10))</f>
-        <v>6.24</v>
+        <v>4.8</v>
       </c>
       <c r="D10" s="256">
         <f>IF($A10="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A10))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E10" s="241">
         <f>IF($A10="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A10)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A10))</f>
-        <v>42.24</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="F10" s="101">
         <f>IF($A10="","",COUNTIFS('GECC 2026'!F$2:F$200,$A10))</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
-        <v>Davi Assunção Salvador Nery de Castro</v>
+        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
       </c>
       <c r="B11" s="103">
         <f>IF($A11="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A11))</f>
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C11" s="103">
         <f>IF($A11="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A11))</f>
-        <v>1.2</v>
+        <v>6.24</v>
       </c>
       <c r="D11" s="256">
         <f>IF($A11="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A11))</f>
@@ -66091,24 +66366,24 @@
       </c>
       <c r="E11" s="241">
         <f>IF($A11="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A11)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A11))</f>
-        <v>13.2</v>
+        <v>42.24</v>
       </c>
       <c r="F11" s="101">
         <f>IF($A11="","",COUNTIFS('GECC 2026'!F$2:F$200,$A11))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
-        <v>David da Silva de Araújo</v>
+        <v>Cinthia Thomazi</v>
       </c>
       <c r="B12" s="103">
         <f>IF($A12="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A12))</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C12" s="103">
         <f>IF($A12="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A12))</f>
-        <v>1.2</v>
+        <v>0.24</v>
       </c>
       <c r="D12" s="256">
         <f>IF($A12="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A12))</f>
@@ -66116,7 +66391,7 @@
       </c>
       <c r="E12" s="241">
         <f>IF($A12="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A12)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A12))</f>
-        <v>13.2</v>
+        <v>8.24</v>
       </c>
       <c r="F12" s="101">
         <f>IF($A12="","",COUNTIFS('GECC 2026'!F$2:F$200,$A12))</f>
@@ -66125,7 +66400,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
-        <v>Denise Duarte Guirra Kuhlmann</v>
+        <v>Davi Assunção Salvador Nery de Castro</v>
       </c>
       <c r="B13" s="103">
         <f>IF($A13="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A13))</f>
@@ -66133,7 +66408,7 @@
       </c>
       <c r="C13" s="103">
         <f>IF($A13="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A13))</f>
-        <v>2.6399999999999997</v>
+        <v>1.2</v>
       </c>
       <c r="D13" s="256">
         <f>IF($A13="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A13))</f>
@@ -66141,24 +66416,24 @@
       </c>
       <c r="E13" s="241">
         <f>IF($A13="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A13)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A13))</f>
-        <v>14.64</v>
+        <v>13.2</v>
       </c>
       <c r="F13" s="101">
         <f>IF($A13="","",COUNTIFS('GECC 2026'!F$2:F$200,$A13))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
-        <v>Diversos</v>
+        <v>David da Silva de Araújo</v>
       </c>
       <c r="B14" s="103">
         <f>IF($A14="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A14))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C14" s="103">
         <f>IF($A14="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A14))</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D14" s="256">
         <f>IF($A14="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A14))</f>
@@ -66166,24 +66441,24 @@
       </c>
       <c r="E14" s="241">
         <f>IF($A14="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A14)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A14))</f>
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="F14" s="101">
         <f>IF($A14="","",COUNTIFS('GECC 2026'!F$2:F$200,$A14))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
-        <v>Felipe da Costa Malaquias</v>
+        <v>Denise Duarte Guirra Kuhlmann</v>
       </c>
       <c r="B15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>34.9</v>
+        <v>2.6399999999999997</v>
       </c>
       <c r="D15" s="256">
         <f>IF($A15="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
@@ -66191,24 +66466,24 @@
       </c>
       <c r="E15" s="241">
         <f>IF($A15="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A15)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
-        <v>34.9</v>
+        <v>14.64</v>
       </c>
       <c r="F15" s="101">
         <f>IF($A15="","",COUNTIFS('GECC 2026'!F$2:F$200,$A15))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
-        <v>Fernanda Viana de Souza</v>
+        <v>Diversos</v>
       </c>
       <c r="B16" s="103">
         <f>IF($A16="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A16))</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C16" s="103">
         <f>IF($A16="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A16))</f>
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="D16" s="256">
         <f>IF($A16="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A16))</f>
@@ -66216,16 +66491,16 @@
       </c>
       <c r="E16" s="241">
         <f>IF($A16="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A16)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A16))</f>
-        <v>18.09</v>
+        <v>0</v>
       </c>
       <c r="F16" s="101">
         <f>IF($A16="","",COUNTIFS('GECC 2026'!F$2:F$200,$A16))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
-        <v>Flávio José Fonseca de Souza</v>
+        <v>Eustáquio Rabelo de Souza</v>
       </c>
       <c r="B17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A17))</f>
@@ -66233,7 +66508,7 @@
       </c>
       <c r="C17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>37.299999999999997</v>
+        <v>0.24</v>
       </c>
       <c r="D17" s="256">
         <f>IF($A17="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
@@ -66241,24 +66516,24 @@
       </c>
       <c r="E17" s="241">
         <f>IF($A17="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A17)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
-        <v>45.3</v>
+        <v>8.24</v>
       </c>
       <c r="F17" s="101">
         <f>IF($A17="","",COUNTIFS('GECC 2026'!F$2:F$200,$A17))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
-        <v>Gabriel Heller</v>
+        <v>Felipe da Costa Malaquias</v>
       </c>
       <c r="B18" s="103">
         <f>IF($A18="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A18))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C18" s="103">
         <f>IF($A18="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A18))</f>
-        <v>33.200000000000003</v>
+        <v>34.9</v>
       </c>
       <c r="D18" s="256">
         <f>IF($A18="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A18))</f>
@@ -66266,24 +66541,24 @@
       </c>
       <c r="E18" s="241">
         <f>IF($A18="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A18)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A18))</f>
-        <v>37.200000000000003</v>
+        <v>34.9</v>
       </c>
       <c r="F18" s="101">
         <f>IF($A18="","",COUNTIFS('GECC 2026'!F$2:F$200,$A18))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
-        <v>Gustavo Takahashi</v>
+        <v>Felipe Ramos Barbosa</v>
       </c>
       <c r="B19" s="103">
         <f>IF($A19="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A19))</f>
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C19" s="103">
         <f>IF($A19="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A19))</f>
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="D19" s="256">
         <f>IF($A19="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A19))</f>
@@ -66291,24 +66566,24 @@
       </c>
       <c r="E19" s="241">
         <f>IF($A19="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A19)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A19))</f>
-        <v>33</v>
+        <v>8.24</v>
       </c>
       <c r="F19" s="101">
         <f>IF($A19="","",COUNTIFS('GECC 2026'!F$2:F$200,$A19))</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
-        <v>Hamilton de Jesus Lopes Neto</v>
+        <v>Fernanda Viana de Souza</v>
       </c>
       <c r="B20" s="103">
         <f>IF($A20="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A20))</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C20" s="103">
         <f>IF($A20="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A20))</f>
-        <v>1.2</v>
+        <v>3.09</v>
       </c>
       <c r="D20" s="256">
         <f>IF($A20="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A20))</f>
@@ -66316,24 +66591,24 @@
       </c>
       <c r="E20" s="241">
         <f>IF($A20="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A20)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A20))</f>
-        <v>13.2</v>
+        <v>18.09</v>
       </c>
       <c r="F20" s="101">
         <f>IF($A20="","",COUNTIFS('GECC 2026'!F$2:F$200,$A20))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
-        <v>Indio Artiaga do Brasil Rabelo</v>
+        <v>Flávio José Fonseca de Souza</v>
       </c>
       <c r="B21" s="103">
         <f>IF($A21="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A21))</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C21" s="103">
         <f>IF($A21="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A21))</f>
-        <v>3.6</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D21" s="256">
         <f>IF($A21="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A21))</f>
@@ -66341,24 +66616,24 @@
       </c>
       <c r="E21" s="241">
         <f>IF($A21="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A21)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A21))</f>
-        <v>15.6</v>
+        <v>45.3</v>
       </c>
       <c r="F21" s="101">
         <f>IF($A21="","",COUNTIFS('GECC 2026'!F$2:F$200,$A21))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
-        <v>Leonardo de Melo</v>
+        <v>Gabriel Heller</v>
       </c>
       <c r="B22" s="103">
         <f>IF($A22="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A22))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C22" s="103">
         <f>IF($A22="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A22))</f>
-        <v>0</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="D22" s="256">
         <f>IF($A22="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A22))</f>
@@ -66366,24 +66641,24 @@
       </c>
       <c r="E22" s="241">
         <f>IF($A22="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A22)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A22))</f>
-        <v>0</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="F22" s="101">
         <f>IF($A22="","",COUNTIFS('GECC 2026'!F$2:F$200,$A22))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
-        <v>Leonardo José Alves Leal Neri</v>
+        <v>Guilherme Bride Fernandes</v>
       </c>
       <c r="B23" s="103">
         <f>IF($A23="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A23))</f>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C23" s="103">
         <f>IF($A23="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A23))</f>
-        <v>12</v>
+        <v>0.24</v>
       </c>
       <c r="D23" s="256">
         <f>IF($A23="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A23))</f>
@@ -66391,24 +66666,24 @@
       </c>
       <c r="E23" s="241">
         <f>IF($A23="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A23)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A23))</f>
-        <v>52</v>
+        <v>8.24</v>
       </c>
       <c r="F23" s="101">
         <f>IF($A23="","",COUNTIFS('GECC 2026'!F$2:F$200,$A23))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
-        <v>Luciana Alvim</v>
+        <v>Gustavo Takahashi</v>
       </c>
       <c r="B24" s="103">
         <f>IF($A24="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A24))</f>
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C24" s="103">
         <f>IF($A24="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A24))</f>
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D24" s="256">
         <f>IF($A24="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A24))</f>
@@ -66416,99 +66691,99 @@
       </c>
       <c r="E24" s="241">
         <f>IF($A24="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A24)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A24))</f>
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="F24" s="101">
         <f>IF($A24="","",COUNTIFS('GECC 2026'!F$2:F$200,$A24))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
-        <v>Marcelo Bálbio Moraes</v>
+        <v>Hamilton de Jesus Lopes Neto</v>
       </c>
       <c r="B25" s="103">
         <f>IF($A25="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A25))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C25" s="103">
         <f>IF($A25="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A25))</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D25" s="256">
         <f>IF($A25="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A25))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E25" s="241">
         <f>IF($A25="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A25)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A25))</f>
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="F25" s="101">
         <f>IF($A25="","",COUNTIFS('GECC 2026'!F$2:F$200,$A25))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
-        <v>Mauri Siqueira Montessi</v>
+        <v>Igor Queiroz</v>
       </c>
       <c r="B26" s="103">
         <f>IF($A26="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A26))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C26" s="103">
         <f>IF($A26="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A26))</f>
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="D26" s="256">
         <f>IF($A26="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A26))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E26" s="241">
         <f>IF($A26="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A26)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A26))</f>
-        <v>16</v>
+        <v>8.24</v>
       </c>
       <c r="F26" s="101">
         <f>IF($A26="","",COUNTIFS('GECC 2026'!F$2:F$200,$A26))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
-        <v>Michel Martins de Morais</v>
+        <v>Indio Artiaga do Brasil Rabelo</v>
       </c>
       <c r="B27" s="103">
         <f>IF($A27="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A27))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C27" s="103">
         <f>IF($A27="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A27))</f>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="D27" s="256">
         <f>IF($A27="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A27))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E27" s="241">
         <f>IF($A27="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A27)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A27))</f>
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="F27" s="101">
         <f>IF($A27="","",COUNTIFS('GECC 2026'!F$2:F$200,$A27))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>Paulo José Góes Daltro</v>
+        <v>José Roberto Alcuri Júnior</v>
       </c>
       <c r="B28" s="103">
         <f>IF($A28="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A28))</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C28" s="103">
         <f>IF($A28="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A28))</f>
-        <v>4.8</v>
+        <v>0.24</v>
       </c>
       <c r="D28" s="256">
         <f>IF($A28="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A28))</f>
@@ -66516,24 +66791,24 @@
       </c>
       <c r="E28" s="241">
         <f>IF($A28="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A28)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A28))</f>
-        <v>20.8</v>
+        <v>8.24</v>
       </c>
       <c r="F28" s="101">
         <f>IF($A28="","",COUNTIFS('GECC 2026'!F$2:F$200,$A28))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>Priscila Nolasco</v>
+        <v>Leonardo de Melo</v>
       </c>
       <c r="B29" s="103">
         <f>IF($A29="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A29))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C29" s="103">
         <f>IF($A29="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A29))</f>
-        <v>2.6399999999999997</v>
+        <v>0</v>
       </c>
       <c r="D29" s="256">
         <f>IF($A29="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A29))</f>
@@ -66541,24 +66816,24 @@
       </c>
       <c r="E29" s="241">
         <f>IF($A29="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A29)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A29))</f>
-        <v>14.64</v>
+        <v>0</v>
       </c>
       <c r="F29" s="101">
         <f>IF($A29="","",COUNTIFS('GECC 2026'!F$2:F$200,$A29))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>Reinaldo Alencar</v>
+        <v>Leonardo José Alves Leal Neri</v>
       </c>
       <c r="B30" s="103">
         <f>IF($A30="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A30))</f>
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C30" s="103">
         <f>IF($A30="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A30))</f>
-        <v>7.1999999999999993</v>
+        <v>12</v>
       </c>
       <c r="D30" s="256">
         <f>IF($A30="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A30))</f>
@@ -66566,24 +66841,24 @@
       </c>
       <c r="E30" s="241">
         <f>IF($A30="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A30)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A30))</f>
-        <v>55.2</v>
+        <v>52</v>
       </c>
       <c r="F30" s="101">
         <f>IF($A30="","",COUNTIFS('GECC 2026'!F$2:F$200,$A30))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <v>Rogério Ribeiro</v>
+        <v>Luciana Alvim</v>
       </c>
       <c r="B31" s="103">
         <f>IF($A31="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A31))</f>
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C31" s="103">
         <f>IF($A31="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A31))</f>
-        <v>7.1999999999999993</v>
+        <v>94</v>
       </c>
       <c r="D31" s="256">
         <f>IF($A31="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
@@ -66591,24 +66866,24 @@
       </c>
       <c r="E31" s="241">
         <f>IF($A31="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A31)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
-        <v>55.2</v>
+        <v>154</v>
       </c>
       <c r="F31" s="101">
         <f>IF($A31="","",COUNTIFS('GECC 2026'!F$2:F$200,$A31))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <v>Rômulo Miranda Alvim</v>
+        <v>Marcelo Bálbio Moraes</v>
       </c>
       <c r="B32" s="103">
         <f>IF($A32="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C32" s="103">
         <f>IF($A32="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="D32" s="256">
         <f>IF($A32="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
@@ -66616,24 +66891,24 @@
       </c>
       <c r="E32" s="241">
         <f>IF($A32="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A32)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
-        <v>43.6</v>
+        <v>16</v>
       </c>
       <c r="F32" s="101">
         <f>IF($A32="","",COUNTIFS('GECC 2026'!F$2:F$200,$A32))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <v>Servidores, colaboradores e estagiários do TCDF</v>
+        <v>Marcelo Santana</v>
       </c>
       <c r="B33" s="103">
         <f>IF($A33="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A33))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C33" s="103">
         <f>IF($A33="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A33))</f>
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="D33" s="256">
         <f>IF($A33="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A33))</f>
@@ -66641,7 +66916,7 @@
       </c>
       <c r="E33" s="241">
         <f>IF($A33="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A33)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A33))</f>
-        <v>0</v>
+        <v>8.24</v>
       </c>
       <c r="F33" s="101">
         <f>IF($A33="","",COUNTIFS('GECC 2026'!F$2:F$200,$A33))</f>
@@ -66650,250 +66925,277 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <v>Tarsila Firmino Ely</v>
+        <v>Mauri Siqueira Montessi</v>
       </c>
       <c r="B34" s="103">
         <f>IF($A34="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A34))</f>
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="C34" s="103">
         <f>IF($A34="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A34))</f>
-        <v>96.4</v>
+        <v>0</v>
       </c>
       <c r="D34" s="256">
         <f>IF($A34="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A34))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E34" s="241">
         <f>IF($A34="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A34)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A34))</f>
-        <v>152.4</v>
+        <v>16</v>
       </c>
       <c r="F34" s="101">
         <f>IF($A34="","",COUNTIFS('GECC 2026'!F$2:F$200,$A34))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <v>Túllio Herbeth Teixeira Moraes</v>
+        <v>Michel Martins de Morais</v>
       </c>
       <c r="B35" s="103">
         <f>IF($A35="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A35))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C35" s="103">
         <f>IF($A35="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A35))</f>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="D35" s="256">
         <f>IF($A35="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A35))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E35" s="241">
         <f>IF($A35="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A35)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A35))</f>
-        <v>3.45</v>
+        <v>16</v>
       </c>
       <c r="F35" s="101">
         <f>IF($A35="","",COUNTIFS('GECC 2026'!F$2:F$200,$A35))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <v>Paulo José Góes Daltro</v>
+      </c>
+      <c r="B36" s="103">
+        <f>IF($A36="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A36))</f>
+        <v>16</v>
+      </c>
+      <c r="C36" s="103">
+        <f>IF($A36="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A36))</f>
+        <v>4.8</v>
+      </c>
+      <c r="D36" s="256">
+        <f>IF($A36="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A36))</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="241">
+        <f>IF($A36="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A36)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A36))</f>
+        <v>20.8</v>
+      </c>
+      <c r="F36" s="101">
+        <f>IF($A36="","",COUNTIFS('GECC 2026'!F$2:F$200,$A36))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="str">
+        <v>Priscila Nolasco</v>
+      </c>
+      <c r="B37" s="103">
+        <f>IF($A37="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A37))</f>
+        <v>12</v>
+      </c>
+      <c r="C37" s="103">
+        <f>IF($A37="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A37))</f>
+        <v>2.6399999999999997</v>
+      </c>
+      <c r="D37" s="256">
+        <f>IF($A37="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A37))</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="241">
+        <f>IF($A37="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A37)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A37))</f>
+        <v>14.64</v>
+      </c>
+      <c r="F37" s="101">
+        <f>IF($A37="","",COUNTIFS('GECC 2026'!F$2:F$200,$A37))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="str">
+        <v>Reinaldo Alencar</v>
+      </c>
+      <c r="B38" s="103">
+        <f>IF($A38="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A38))</f>
+        <v>48</v>
+      </c>
+      <c r="C38" s="103">
+        <f>IF($A38="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A38))</f>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="D38" s="256">
+        <f>IF($A38="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A38))</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="241">
+        <f>IF($A38="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A38)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A38))</f>
+        <v>55.2</v>
+      </c>
+      <c r="F38" s="101">
+        <f>IF($A38="","",COUNTIFS('GECC 2026'!F$2:F$200,$A38))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
+        <v>Rogério Ribeiro</v>
+      </c>
+      <c r="B39" s="103">
+        <f>IF($A39="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A39))</f>
+        <v>48</v>
+      </c>
+      <c r="C39" s="103">
+        <f>IF($A39="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A39))</f>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="D39" s="256">
+        <f>IF($A39="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A39))</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="241">
+        <f>IF($A39="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A39)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A39))</f>
+        <v>55.2</v>
+      </c>
+      <c r="F39" s="101">
+        <f>IF($A39="","",COUNTIFS('GECC 2026'!F$2:F$200,$A39))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="str">
+        <v>Rômulo Miranda Alvim</v>
+      </c>
+      <c r="B40" s="103">
+        <f>IF($A40="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A40))</f>
+        <v>24</v>
+      </c>
+      <c r="C40" s="103">
+        <f>IF($A40="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A40))</f>
+        <v>3.6</v>
+      </c>
+      <c r="D40" s="256">
+        <f>IF($A40="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A40))</f>
+        <v>16</v>
+      </c>
+      <c r="E40" s="241">
+        <f>IF($A40="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A40)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A40))</f>
+        <v>43.6</v>
+      </c>
+      <c r="F40" s="101">
+        <f>IF($A40="","",COUNTIFS('GECC 2026'!F$2:F$200,$A40))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="str">
+        <v>Servidores, colaboradores e estagiários do TCDF</v>
+      </c>
+      <c r="B41" s="103">
+        <f>IF($A41="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A41))</f>
+        <v>0</v>
+      </c>
+      <c r="C41" s="103">
+        <f>IF($A41="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A41))</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="256">
+        <f>IF($A41="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A41))</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="241">
+        <f>IF($A41="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A41)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A41))</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="101">
+        <f>IF($A41="","",COUNTIFS('GECC 2026'!F$2:F$200,$A41))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="103" t="str">
-        <f>IF($A36="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A36))</f>
-        <v/>
-      </c>
-      <c r="C36" s="103" t="str">
-        <f>IF($A36="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A36))</f>
-        <v/>
-      </c>
-      <c r="D36" s="256" t="str">
-        <f>IF($A36="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A36))</f>
-        <v/>
-      </c>
-      <c r="E36" s="241" t="str">
-        <f>IF($A36="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A36)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A36))</f>
-        <v/>
-      </c>
-      <c r="F36" s="101" t="str">
-        <f>IF($A36="","",COUNTIFS('GECC 2026'!F$2:F$200,$A36))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="103" t="str">
-        <f>IF($A37="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A37))</f>
-        <v/>
-      </c>
-      <c r="C37" s="103" t="str">
-        <f>IF($A37="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A37))</f>
-        <v/>
-      </c>
-      <c r="D37" s="256" t="str">
-        <f>IF($A37="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A37))</f>
-        <v/>
-      </c>
-      <c r="E37" s="241" t="str">
-        <f>IF($A37="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A37)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A37))</f>
-        <v/>
-      </c>
-      <c r="F37" s="101" t="str">
-        <f>IF($A37="","",COUNTIFS('GECC 2026'!F$2:F$200,$A37))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="103" t="str">
-        <f>IF($A38="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A38))</f>
-        <v/>
-      </c>
-      <c r="C38" s="103" t="str">
-        <f>IF($A38="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A38))</f>
-        <v/>
-      </c>
-      <c r="D38" s="256" t="str">
-        <f>IF($A38="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A38))</f>
-        <v/>
-      </c>
-      <c r="E38" s="241" t="str">
-        <f>IF($A38="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A38)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A38))</f>
-        <v/>
-      </c>
-      <c r="F38" s="101" t="str">
-        <f>IF($A38="","",COUNTIFS('GECC 2026'!F$2:F$200,$A38))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="103" t="str">
-        <f>IF($A39="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A39))</f>
-        <v/>
-      </c>
-      <c r="C39" s="103" t="str">
-        <f>IF($A39="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A39))</f>
-        <v/>
-      </c>
-      <c r="D39" s="256" t="str">
-        <f>IF($A39="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A39))</f>
-        <v/>
-      </c>
-      <c r="E39" s="241" t="str">
-        <f>IF($A39="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A39)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A39))</f>
-        <v/>
-      </c>
-      <c r="F39" s="101" t="str">
-        <f>IF($A39="","",COUNTIFS('GECC 2026'!F$2:F$200,$A39))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="103" t="str">
-        <f>IF($A40="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A40))</f>
-        <v/>
-      </c>
-      <c r="C40" s="103" t="str">
-        <f>IF($A40="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A40))</f>
-        <v/>
-      </c>
-      <c r="D40" s="256" t="str">
-        <f>IF($A40="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A40))</f>
-        <v/>
-      </c>
-      <c r="E40" s="241" t="str">
-        <f>IF($A40="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A40)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A40))</f>
-        <v/>
-      </c>
-      <c r="F40" s="101" t="str">
-        <f>IF($A40="","",COUNTIFS('GECC 2026'!F$2:F$200,$A40))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B41" s="103" t="str">
-        <f>IF($A41="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A41))</f>
-        <v/>
-      </c>
-      <c r="C41" s="103" t="str">
-        <f>IF($A41="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A41))</f>
-        <v/>
-      </c>
-      <c r="D41" s="256" t="str">
-        <f>IF($A41="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A41))</f>
-        <v/>
-      </c>
-      <c r="E41" s="241" t="str">
-        <f>IF($A41="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A41)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A41))</f>
-        <v/>
-      </c>
-      <c r="F41" s="101" t="str">
-        <f>IF($A41="","",COUNTIFS('GECC 2026'!F$2:F$200,$A41))</f>
-        <v/>
-      </c>
-    </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="103" t="str">
+      <c r="A42" t="str">
+        <v>Silvia Lima Damasceno</v>
+      </c>
+      <c r="B42" s="103">
         <f>IF($A42="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A42))</f>
-        <v/>
-      </c>
-      <c r="C42" s="103" t="str">
+        <v>8</v>
+      </c>
+      <c r="C42" s="103">
         <f>IF($A42="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A42))</f>
-        <v/>
-      </c>
-      <c r="D42" s="256" t="str">
+        <v>0.24</v>
+      </c>
+      <c r="D42" s="256">
         <f>IF($A42="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A42))</f>
-        <v/>
-      </c>
-      <c r="E42" s="241" t="str">
+        <v>0</v>
+      </c>
+      <c r="E42" s="241">
         <f>IF($A42="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A42)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A42))</f>
-        <v/>
-      </c>
-      <c r="F42" s="101" t="str">
+        <v>8.24</v>
+      </c>
+      <c r="F42" s="101">
         <f>IF($A42="","",COUNTIFS('GECC 2026'!F$2:F$200,$A42))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B43" s="103" t="str">
+      <c r="A43" t="str">
+        <v>Tarsila Firmino Ely</v>
+      </c>
+      <c r="B43" s="103">
         <f>IF($A43="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A43))</f>
-        <v/>
-      </c>
-      <c r="C43" s="103" t="str">
+        <v>56</v>
+      </c>
+      <c r="C43" s="103">
         <f>IF($A43="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A43))</f>
-        <v/>
-      </c>
-      <c r="D43" s="256" t="str">
+        <v>96.4</v>
+      </c>
+      <c r="D43" s="256">
         <f>IF($A43="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A43))</f>
-        <v/>
-      </c>
-      <c r="E43" s="241" t="str">
+        <v>0</v>
+      </c>
+      <c r="E43" s="241">
         <f>IF($A43="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A43)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A43))</f>
-        <v/>
-      </c>
-      <c r="F43" s="101" t="str">
+        <v>152.4</v>
+      </c>
+      <c r="F43" s="101">
         <f>IF($A43="","",COUNTIFS('GECC 2026'!F$2:F$200,$A43))</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B44" s="103" t="str">
+      <c r="A44" t="str">
+        <v>Túllio Herbeth Teixeira Moraes</v>
+      </c>
+      <c r="B44" s="103">
         <f>IF($A44="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A44))</f>
-        <v/>
-      </c>
-      <c r="C44" s="103" t="str">
+        <v>3</v>
+      </c>
+      <c r="C44" s="103">
         <f>IF($A44="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A44))</f>
-        <v/>
-      </c>
-      <c r="D44" s="256" t="str">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="D44" s="256">
         <f>IF($A44="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A44))</f>
-        <v/>
-      </c>
-      <c r="E44" s="241" t="str">
+        <v>0</v>
+      </c>
+      <c r="E44" s="241">
         <f>IF($A44="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A44)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A44))</f>
-        <v/>
-      </c>
-      <c r="F44" s="101" t="str">
+        <v>3.45</v>
+      </c>
+      <c r="F44" s="101">
         <f>IF($A44="","",COUNTIFS('GECC 2026'!F$2:F$200,$A44))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -68174,11 +68476,11 @@
       </c>
       <c r="B105" s="243">
         <f>SUM(B5:B100)</f>
-        <v>568</v>
+        <v>640</v>
       </c>
       <c r="C105" s="243">
         <f>SUM(C5:C100)</f>
-        <v>380.09999999999997</v>
+        <v>380.10000000000008</v>
       </c>
       <c r="D105" s="256">
         <f>IF($A105="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A105))</f>
@@ -68190,7 +68492,7 @@
       </c>
       <c r="F105" s="244">
         <f>SUM(F5:F100)</f>
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -68654,12 +68956,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -68864,20 +69168,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
+    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -68902,12 +69207,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
-    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4990" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B97BF320-871C-4240-8B7B-0CEE61BE455C}"/>
+  <xr:revisionPtr revIDLastSave="5032" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53BD1C0B-93AF-413F-A11A-246C9E2FD502}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6546" uniqueCount="2966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6566" uniqueCount="2975">
   <si>
     <t>ID</t>
   </si>
@@ -9065,7 +9065,34 @@
     <t>Participantes</t>
   </si>
   <si>
-    <t>José Roberto Alcuri Júnior; Felipe Ramos Barbosa; Carolina Pereira de Oliveira; Eustáquio Rabelo de Souza; Alinne Patrícia de Andrade Carvalho; Silvia Lima Damasceno; Marcelo Santana; Cinthia Thomazi; Igor Queiroz; Guilherme Bride Fernandes</t>
+    <t>José Roberto Alcuri Júnior; Felipe Ramos Barbosa; Carolina Pereira de Oliveira; Eustáquio Rabelo de Souza; Alinne Patrícia de Andrade Carvalho; Silvia Lima Damasceno Carvalho; Marcelo Santana; Cinthia Thais de Carvalho Luz Thomazi; Igor Queiroz; Guilherme Bride Fernandes</t>
+  </si>
+  <si>
+    <t>2026-045</t>
+  </si>
+  <si>
+    <t>Felipe Ramos Barbosa</t>
+  </si>
+  <si>
+    <t>Carolina Pereira de Oliveira</t>
+  </si>
+  <si>
+    <t>Eustáquio Rabelo de Souza</t>
+  </si>
+  <si>
+    <t>Alinne Patrícia de Andrade Carvalho</t>
+  </si>
+  <si>
+    <t>Marcelo Santana</t>
+  </si>
+  <si>
+    <t>Igor Queiroz</t>
+  </si>
+  <si>
+    <t>Guilherme Bride Fernandes</t>
+  </si>
+  <si>
+    <t>José Roberto Alcuri Júnior</t>
   </si>
 </sst>
 </file>
@@ -62310,7 +62337,7 @@
         <v>8</v>
       </c>
       <c r="Q37" t="str">
-        <v>José Roberto Alcuri Júnior; Felipe Ramos Barbosa; Carolina Pereira de Oliveira; Eustáquio Rabelo de Souza; Alinne Patrícia de Andrade Carvalho; Silvia Lima Damasceno; Marcelo Santana; Cinthia Thomazi; Igor Queiroz; Guilherme Bride Fernandes</v>
+        <v>José Roberto Alcuri Júnior; Felipe Ramos Barbosa; Carolina Pereira de Oliveira; Eustáquio Rabelo de Souza; Alinne Patrícia de Andrade Carvalho; Silvia Lima Damasceno Carvalho; Marcelo Santana; Cinthia Thais de Carvalho Luz Thomazi; Igor Queiroz; Guilherme Bride Fernandes</v>
       </c>
       <c r="R37">
         <v>10</v>
@@ -62781,6 +62808,18 @@
       <c r="S45" t="str">
         <v/>
       </c>
+      <c r="X45" t="s">
+        <v>2966</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>2974</v>
+      </c>
+      <c r="Z45">
+        <v>1</v>
+      </c>
+      <c r="AA45">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A46">
@@ -62819,6 +62858,18 @@
       <c r="S46" t="str">
         <v/>
       </c>
+      <c r="X46" t="s">
+        <v>2966</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>2967</v>
+      </c>
+      <c r="Z46">
+        <v>1</v>
+      </c>
+      <c r="AA46">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A47">
@@ -62857,6 +62908,18 @@
       <c r="S47" t="str">
         <v/>
       </c>
+      <c r="X47" t="s">
+        <v>2966</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>2968</v>
+      </c>
+      <c r="Z47">
+        <v>1</v>
+      </c>
+      <c r="AA47">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48">
@@ -62895,8 +62958,20 @@
       <c r="S48" t="str">
         <v/>
       </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="X48" t="s">
+        <v>2966</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>2969</v>
+      </c>
+      <c r="Z48">
+        <v>1</v>
+      </c>
+      <c r="AA48">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2026</v>
       </c>
@@ -62933,8 +63008,14 @@
       <c r="S49" t="str">
         <v/>
       </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="X49" t="s">
+        <v>2966</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2026</v>
       </c>
@@ -62971,8 +63052,14 @@
       <c r="S50" t="str">
         <v/>
       </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="X50" t="s">
+        <v>2966</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2026</v>
       </c>
@@ -63009,8 +63096,14 @@
       <c r="S51" t="str">
         <v/>
       </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="X51" t="s">
+        <v>2966</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2026</v>
       </c>
@@ -63047,8 +63140,20 @@
       <c r="S52" t="str">
         <v/>
       </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="X52" t="s">
+        <v>2966</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>1342</v>
+      </c>
+      <c r="Z52">
+        <v>1</v>
+      </c>
+      <c r="AA52">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2026</v>
       </c>
@@ -63085,8 +63190,14 @@
       <c r="S53" t="str">
         <v/>
       </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="X53" t="s">
+        <v>2966</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2026</v>
       </c>
@@ -63123,8 +63234,14 @@
       <c r="S54" t="str">
         <v/>
       </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="X54" t="s">
+        <v>2966</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2026</v>
       </c>
@@ -63162,7 +63279,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2026</v>
       </c>
@@ -63200,7 +63317,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2026</v>
       </c>
@@ -63238,7 +63355,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2026</v>
       </c>
@@ -63276,7 +63393,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2026</v>
       </c>
@@ -63314,7 +63431,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2026</v>
       </c>
@@ -63352,7 +63469,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2026</v>
       </c>
@@ -63390,7 +63507,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2026</v>
       </c>
@@ -63428,7 +63545,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2026</v>
       </c>
@@ -63466,7 +63583,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2026</v>
       </c>
@@ -63565,13 +63682,13 @@
         <v>10</v>
       </c>
       <c r="H66">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="J66">
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="R66" t="str">
         <v/>
@@ -63603,13 +63720,13 @@
         <v>10</v>
       </c>
       <c r="H67">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="J67">
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="R67" t="str">
         <v/>
@@ -63641,13 +63758,13 @@
         <v>10</v>
       </c>
       <c r="H68">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I68">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="J68">
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="R68" t="str">
         <v/>
@@ -63679,13 +63796,13 @@
         <v>10</v>
       </c>
       <c r="H69">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I69">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="J69">
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="R69" t="str">
         <v/>
@@ -63749,7 +63866,7 @@
         <v>8</v>
       </c>
       <c r="F71" t="str">
-        <v>Silvia Lima Damasceno</v>
+        <v>Silvia Lima Damasceno Carvalho</v>
       </c>
       <c r="G71">
         <v>10</v>
@@ -63825,19 +63942,19 @@
         <v>8</v>
       </c>
       <c r="F73" t="str">
-        <v>Cinthia Thomazi</v>
+        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
       </c>
       <c r="G73">
         <v>10</v>
       </c>
       <c r="H73">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I73">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="J73">
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="R73" t="str">
         <v/>
@@ -66195,7 +66312,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="str" cm="1">
-        <f t="array" ref="A5:A44">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32),_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32)&lt;&gt;""))),"")</f>
+        <f t="array" ref="A5:A43">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32),_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32)&lt;&gt;""))),"")</f>
         <v>Adriana Cuoco Portugal</v>
       </c>
       <c r="B5" s="103">
@@ -66304,11 +66421,11 @@
       </c>
       <c r="B9" s="103">
         <f>IF($A9="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A9))</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C9" s="103">
         <f>IF($A9="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A9))</f>
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D9" s="256">
         <f>IF($A9="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A9))</f>
@@ -66316,7 +66433,7 @@
       </c>
       <c r="E9" s="241">
         <f>IF($A9="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A9)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A9))</f>
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="F9" s="101">
         <f>IF($A9="","",COUNTIFS('GECC 2026'!F$2:F$200,$A9))</f>
@@ -66354,11 +66471,11 @@
       </c>
       <c r="B11" s="103">
         <f>IF($A11="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A11))</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="103">
         <f>IF($A11="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A11))</f>
-        <v>6.24</v>
+        <v>6.54</v>
       </c>
       <c r="D11" s="256">
         <f>IF($A11="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A11))</f>
@@ -66366,24 +66483,24 @@
       </c>
       <c r="E11" s="241">
         <f>IF($A11="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A11)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A11))</f>
-        <v>42.24</v>
+        <v>43.54</v>
       </c>
       <c r="F11" s="101">
         <f>IF($A11="","",COUNTIFS('GECC 2026'!F$2:F$200,$A11))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
-        <v>Cinthia Thomazi</v>
+        <v>Davi Assunção Salvador Nery de Castro</v>
       </c>
       <c r="B12" s="103">
         <f>IF($A12="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A12))</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C12" s="103">
         <f>IF($A12="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A12))</f>
-        <v>0.24</v>
+        <v>1.2</v>
       </c>
       <c r="D12" s="256">
         <f>IF($A12="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A12))</f>
@@ -66391,7 +66508,7 @@
       </c>
       <c r="E12" s="241">
         <f>IF($A12="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A12)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A12))</f>
-        <v>8.24</v>
+        <v>13.2</v>
       </c>
       <c r="F12" s="101">
         <f>IF($A12="","",COUNTIFS('GECC 2026'!F$2:F$200,$A12))</f>
@@ -66400,7 +66517,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
-        <v>Davi Assunção Salvador Nery de Castro</v>
+        <v>David da Silva de Araújo</v>
       </c>
       <c r="B13" s="103">
         <f>IF($A13="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A13))</f>
@@ -66425,7 +66542,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
-        <v>David da Silva de Araújo</v>
+        <v>Denise Duarte Guirra Kuhlmann</v>
       </c>
       <c r="B14" s="103">
         <f>IF($A14="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A14))</f>
@@ -66433,7 +66550,7 @@
       </c>
       <c r="C14" s="103">
         <f>IF($A14="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A14))</f>
-        <v>1.2</v>
+        <v>2.6399999999999997</v>
       </c>
       <c r="D14" s="256">
         <f>IF($A14="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A14))</f>
@@ -66441,24 +66558,24 @@
       </c>
       <c r="E14" s="241">
         <f>IF($A14="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A14)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A14))</f>
-        <v>13.2</v>
+        <v>14.64</v>
       </c>
       <c r="F14" s="101">
         <f>IF($A14="","",COUNTIFS('GECC 2026'!F$2:F$200,$A14))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
-        <v>Denise Duarte Guirra Kuhlmann</v>
+        <v>Diversos</v>
       </c>
       <c r="B15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C15" s="103">
         <f>IF($A15="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A15))</f>
-        <v>2.6399999999999997</v>
+        <v>0</v>
       </c>
       <c r="D15" s="256">
         <f>IF($A15="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
@@ -66466,24 +66583,24 @@
       </c>
       <c r="E15" s="241">
         <f>IF($A15="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A15)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A15))</f>
-        <v>14.64</v>
+        <v>0</v>
       </c>
       <c r="F15" s="101">
         <f>IF($A15="","",COUNTIFS('GECC 2026'!F$2:F$200,$A15))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
-        <v>Diversos</v>
+        <v>Eustáquio Rabelo de Souza</v>
       </c>
       <c r="B16" s="103">
         <f>IF($A16="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A16))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="103">
         <f>IF($A16="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A16))</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D16" s="256">
         <f>IF($A16="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A16))</f>
@@ -66491,24 +66608,24 @@
       </c>
       <c r="E16" s="241">
         <f>IF($A16="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A16)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A16))</f>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="F16" s="101">
         <f>IF($A16="","",COUNTIFS('GECC 2026'!F$2:F$200,$A16))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
-        <v>Eustáquio Rabelo de Souza</v>
+        <v>Felipe da Costa Malaquias</v>
       </c>
       <c r="B17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>0.24</v>
+        <v>34.9</v>
       </c>
       <c r="D17" s="256">
         <f>IF($A17="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
@@ -66516,7 +66633,7 @@
       </c>
       <c r="E17" s="241">
         <f>IF($A17="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A17)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
-        <v>8.24</v>
+        <v>34.9</v>
       </c>
       <c r="F17" s="101">
         <f>IF($A17="","",COUNTIFS('GECC 2026'!F$2:F$200,$A17))</f>
@@ -66525,15 +66642,15 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
-        <v>Felipe da Costa Malaquias</v>
+        <v>Felipe Ramos Barbosa</v>
       </c>
       <c r="B18" s="103">
         <f>IF($A18="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A18))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" s="103">
         <f>IF($A18="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A18))</f>
-        <v>34.9</v>
+        <v>0.3</v>
       </c>
       <c r="D18" s="256">
         <f>IF($A18="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A18))</f>
@@ -66541,7 +66658,7 @@
       </c>
       <c r="E18" s="241">
         <f>IF($A18="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A18)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A18))</f>
-        <v>34.9</v>
+        <v>1.3</v>
       </c>
       <c r="F18" s="101">
         <f>IF($A18="","",COUNTIFS('GECC 2026'!F$2:F$200,$A18))</f>
@@ -66550,15 +66667,15 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
-        <v>Felipe Ramos Barbosa</v>
+        <v>Fernanda Viana de Souza</v>
       </c>
       <c r="B19" s="103">
         <f>IF($A19="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A19))</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C19" s="103">
         <f>IF($A19="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A19))</f>
-        <v>0.24</v>
+        <v>3.09</v>
       </c>
       <c r="D19" s="256">
         <f>IF($A19="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A19))</f>
@@ -66566,24 +66683,24 @@
       </c>
       <c r="E19" s="241">
         <f>IF($A19="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A19)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A19))</f>
-        <v>8.24</v>
+        <v>18.09</v>
       </c>
       <c r="F19" s="101">
         <f>IF($A19="","",COUNTIFS('GECC 2026'!F$2:F$200,$A19))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
-        <v>Fernanda Viana de Souza</v>
+        <v>Flávio José Fonseca de Souza</v>
       </c>
       <c r="B20" s="103">
         <f>IF($A20="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A20))</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C20" s="103">
         <f>IF($A20="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A20))</f>
-        <v>3.09</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D20" s="256">
         <f>IF($A20="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A20))</f>
@@ -66591,24 +66708,24 @@
       </c>
       <c r="E20" s="241">
         <f>IF($A20="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A20)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A20))</f>
-        <v>18.09</v>
+        <v>45.3</v>
       </c>
       <c r="F20" s="101">
         <f>IF($A20="","",COUNTIFS('GECC 2026'!F$2:F$200,$A20))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
-        <v>Flávio José Fonseca de Souza</v>
+        <v>Gabriel Heller</v>
       </c>
       <c r="B21" s="103">
         <f>IF($A21="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A21))</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C21" s="103">
         <f>IF($A21="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A21))</f>
-        <v>37.299999999999997</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="D21" s="256">
         <f>IF($A21="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A21))</f>
@@ -66616,7 +66733,7 @@
       </c>
       <c r="E21" s="241">
         <f>IF($A21="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A21)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A21))</f>
-        <v>45.3</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="F21" s="101">
         <f>IF($A21="","",COUNTIFS('GECC 2026'!F$2:F$200,$A21))</f>
@@ -66625,15 +66742,15 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
-        <v>Gabriel Heller</v>
+        <v>Guilherme Bride Fernandes</v>
       </c>
       <c r="B22" s="103">
         <f>IF($A22="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A22))</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C22" s="103">
         <f>IF($A22="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A22))</f>
-        <v>33.200000000000003</v>
+        <v>0.24</v>
       </c>
       <c r="D22" s="256">
         <f>IF($A22="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A22))</f>
@@ -66641,24 +66758,24 @@
       </c>
       <c r="E22" s="241">
         <f>IF($A22="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A22)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A22))</f>
-        <v>37.200000000000003</v>
+        <v>8.24</v>
       </c>
       <c r="F22" s="101">
         <f>IF($A22="","",COUNTIFS('GECC 2026'!F$2:F$200,$A22))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
-        <v>Guilherme Bride Fernandes</v>
+        <v>Gustavo Takahashi</v>
       </c>
       <c r="B23" s="103">
         <f>IF($A23="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A23))</f>
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C23" s="103">
         <f>IF($A23="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A23))</f>
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="D23" s="256">
         <f>IF($A23="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A23))</f>
@@ -66666,24 +66783,24 @@
       </c>
       <c r="E23" s="241">
         <f>IF($A23="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A23)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A23))</f>
-        <v>8.24</v>
+        <v>33</v>
       </c>
       <c r="F23" s="101">
         <f>IF($A23="","",COUNTIFS('GECC 2026'!F$2:F$200,$A23))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
-        <v>Gustavo Takahashi</v>
+        <v>Hamilton de Jesus Lopes Neto</v>
       </c>
       <c r="B24" s="103">
         <f>IF($A24="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A24))</f>
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C24" s="103">
         <f>IF($A24="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A24))</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D24" s="256">
         <f>IF($A24="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A24))</f>
@@ -66691,24 +66808,24 @@
       </c>
       <c r="E24" s="241">
         <f>IF($A24="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A24)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A24))</f>
-        <v>33</v>
+        <v>13.2</v>
       </c>
       <c r="F24" s="101">
         <f>IF($A24="","",COUNTIFS('GECC 2026'!F$2:F$200,$A24))</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
-        <v>Hamilton de Jesus Lopes Neto</v>
+        <v>Igor Queiroz</v>
       </c>
       <c r="B25" s="103">
         <f>IF($A25="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A25))</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C25" s="103">
         <f>IF($A25="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A25))</f>
-        <v>1.2</v>
+        <v>0.24</v>
       </c>
       <c r="D25" s="256">
         <f>IF($A25="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A25))</f>
@@ -66716,7 +66833,7 @@
       </c>
       <c r="E25" s="241">
         <f>IF($A25="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A25)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A25))</f>
-        <v>13.2</v>
+        <v>8.24</v>
       </c>
       <c r="F25" s="101">
         <f>IF($A25="","",COUNTIFS('GECC 2026'!F$2:F$200,$A25))</f>
@@ -66725,15 +66842,15 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
-        <v>Igor Queiroz</v>
+        <v>Indio Artiaga do Brasil Rabelo</v>
       </c>
       <c r="B26" s="103">
         <f>IF($A26="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A26))</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C26" s="103">
         <f>IF($A26="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A26))</f>
-        <v>0.24</v>
+        <v>3.6</v>
       </c>
       <c r="D26" s="256">
         <f>IF($A26="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A26))</f>
@@ -66741,7 +66858,7 @@
       </c>
       <c r="E26" s="241">
         <f>IF($A26="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A26)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A26))</f>
-        <v>8.24</v>
+        <v>15.6</v>
       </c>
       <c r="F26" s="101">
         <f>IF($A26="","",COUNTIFS('GECC 2026'!F$2:F$200,$A26))</f>
@@ -66750,15 +66867,15 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
-        <v>Indio Artiaga do Brasil Rabelo</v>
+        <v>José Roberto Alcuri Júnior</v>
       </c>
       <c r="B27" s="103">
         <f>IF($A27="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A27))</f>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C27" s="103">
         <f>IF($A27="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A27))</f>
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="D27" s="256">
         <f>IF($A27="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A27))</f>
@@ -66766,7 +66883,7 @@
       </c>
       <c r="E27" s="241">
         <f>IF($A27="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A27)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A27))</f>
-        <v>15.6</v>
+        <v>1.3</v>
       </c>
       <c r="F27" s="101">
         <f>IF($A27="","",COUNTIFS('GECC 2026'!F$2:F$200,$A27))</f>
@@ -66775,15 +66892,15 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>José Roberto Alcuri Júnior</v>
+        <v>Leonardo de Melo</v>
       </c>
       <c r="B28" s="103">
         <f>IF($A28="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A28))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C28" s="103">
         <f>IF($A28="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A28))</f>
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="D28" s="256">
         <f>IF($A28="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A28))</f>
@@ -66791,7 +66908,7 @@
       </c>
       <c r="E28" s="241">
         <f>IF($A28="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A28)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A28))</f>
-        <v>8.24</v>
+        <v>0</v>
       </c>
       <c r="F28" s="101">
         <f>IF($A28="","",COUNTIFS('GECC 2026'!F$2:F$200,$A28))</f>
@@ -66800,15 +66917,15 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>Leonardo de Melo</v>
+        <v>Leonardo José Alves Leal Neri</v>
       </c>
       <c r="B29" s="103">
         <f>IF($A29="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A29))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C29" s="103">
         <f>IF($A29="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A29))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D29" s="256">
         <f>IF($A29="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A29))</f>
@@ -66816,24 +66933,24 @@
       </c>
       <c r="E29" s="241">
         <f>IF($A29="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A29)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A29))</f>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F29" s="101">
         <f>IF($A29="","",COUNTIFS('GECC 2026'!F$2:F$200,$A29))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>Leonardo José Alves Leal Neri</v>
+        <v>Luciana Alvim</v>
       </c>
       <c r="B30" s="103">
         <f>IF($A30="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A30))</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C30" s="103">
         <f>IF($A30="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A30))</f>
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="D30" s="256">
         <f>IF($A30="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A30))</f>
@@ -66841,91 +66958,91 @@
       </c>
       <c r="E30" s="241">
         <f>IF($A30="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A30)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A30))</f>
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="F30" s="101">
         <f>IF($A30="","",COUNTIFS('GECC 2026'!F$2:F$200,$A30))</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <v>Luciana Alvim</v>
+        <v>Marcelo Bálbio Moraes</v>
       </c>
       <c r="B31" s="103">
         <f>IF($A31="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A31))</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C31" s="103">
         <f>IF($A31="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A31))</f>
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D31" s="256">
         <f>IF($A31="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E31" s="241">
         <f>IF($A31="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A31)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
-        <v>154</v>
+        <v>16</v>
       </c>
       <c r="F31" s="101">
         <f>IF($A31="","",COUNTIFS('GECC 2026'!F$2:F$200,$A31))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <v>Marcelo Bálbio Moraes</v>
+        <v>Marcelo Santana</v>
       </c>
       <c r="B32" s="103">
         <f>IF($A32="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C32" s="103">
         <f>IF($A32="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="D32" s="256">
         <f>IF($A32="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E32" s="241">
         <f>IF($A32="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A32)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
-        <v>16</v>
+        <v>8.24</v>
       </c>
       <c r="F32" s="101">
         <f>IF($A32="","",COUNTIFS('GECC 2026'!F$2:F$200,$A32))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <v>Marcelo Santana</v>
+        <v>Mauri Siqueira Montessi</v>
       </c>
       <c r="B33" s="103">
         <f>IF($A33="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A33))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C33" s="103">
         <f>IF($A33="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A33))</f>
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="D33" s="256">
         <f>IF($A33="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A33))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E33" s="241">
         <f>IF($A33="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A33)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A33))</f>
-        <v>8.24</v>
+        <v>16</v>
       </c>
       <c r="F33" s="101">
         <f>IF($A33="","",COUNTIFS('GECC 2026'!F$2:F$200,$A33))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <v>Mauri Siqueira Montessi</v>
+        <v>Michel Martins de Morais</v>
       </c>
       <c r="B34" s="103">
         <f>IF($A34="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A34))</f>
@@ -66950,40 +67067,40 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <v>Michel Martins de Morais</v>
+        <v>Paulo José Góes Daltro</v>
       </c>
       <c r="B35" s="103">
         <f>IF($A35="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A35))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C35" s="103">
         <f>IF($A35="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A35))</f>
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="D35" s="256">
         <f>IF($A35="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A35))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E35" s="241">
         <f>IF($A35="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A35)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A35))</f>
-        <v>16</v>
+        <v>20.8</v>
       </c>
       <c r="F35" s="101">
         <f>IF($A35="","",COUNTIFS('GECC 2026'!F$2:F$200,$A35))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
-        <v>Paulo José Góes Daltro</v>
+        <v>Priscila Nolasco</v>
       </c>
       <c r="B36" s="103">
         <f>IF($A36="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A36))</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C36" s="103">
         <f>IF($A36="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A36))</f>
-        <v>4.8</v>
+        <v>2.6399999999999997</v>
       </c>
       <c r="D36" s="256">
         <f>IF($A36="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A36))</f>
@@ -66991,7 +67108,7 @@
       </c>
       <c r="E36" s="241">
         <f>IF($A36="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A36)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A36))</f>
-        <v>20.8</v>
+        <v>14.64</v>
       </c>
       <c r="F36" s="101">
         <f>IF($A36="","",COUNTIFS('GECC 2026'!F$2:F$200,$A36))</f>
@@ -67000,15 +67117,15 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
-        <v>Priscila Nolasco</v>
+        <v>Reinaldo Alencar</v>
       </c>
       <c r="B37" s="103">
         <f>IF($A37="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A37))</f>
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C37" s="103">
         <f>IF($A37="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A37))</f>
-        <v>2.6399999999999997</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="D37" s="256">
         <f>IF($A37="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A37))</f>
@@ -67016,7 +67133,7 @@
       </c>
       <c r="E37" s="241">
         <f>IF($A37="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A37)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A37))</f>
-        <v>14.64</v>
+        <v>55.2</v>
       </c>
       <c r="F37" s="101">
         <f>IF($A37="","",COUNTIFS('GECC 2026'!F$2:F$200,$A37))</f>
@@ -67025,7 +67142,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
-        <v>Reinaldo Alencar</v>
+        <v>Rogério Ribeiro</v>
       </c>
       <c r="B38" s="103">
         <f>IF($A38="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A38))</f>
@@ -67050,65 +67167,65 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
-        <v>Rogério Ribeiro</v>
+        <v>Rômulo Miranda Alvim</v>
       </c>
       <c r="B39" s="103">
         <f>IF($A39="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A39))</f>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C39" s="103">
         <f>IF($A39="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A39))</f>
-        <v>7.1999999999999993</v>
+        <v>3.6</v>
       </c>
       <c r="D39" s="256">
         <f>IF($A39="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A39))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E39" s="241">
         <f>IF($A39="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A39)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A39))</f>
-        <v>55.2</v>
+        <v>43.6</v>
       </c>
       <c r="F39" s="101">
         <f>IF($A39="","",COUNTIFS('GECC 2026'!F$2:F$200,$A39))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
-        <v>Rômulo Miranda Alvim</v>
+        <v>Servidores, colaboradores e estagiários do TCDF</v>
       </c>
       <c r="B40" s="103">
         <f>IF($A40="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A40))</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C40" s="103">
         <f>IF($A40="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A40))</f>
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="D40" s="256">
         <f>IF($A40="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A40))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E40" s="241">
         <f>IF($A40="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A40)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A40))</f>
-        <v>43.6</v>
+        <v>0</v>
       </c>
       <c r="F40" s="101">
         <f>IF($A40="","",COUNTIFS('GECC 2026'!F$2:F$200,$A40))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
-        <v>Servidores, colaboradores e estagiários do TCDF</v>
+        <v>Silvia Lima Damasceno Carvalho</v>
       </c>
       <c r="B41" s="103">
         <f>IF($A41="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A41))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C41" s="103">
         <f>IF($A41="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A41))</f>
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="D41" s="256">
         <f>IF($A41="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A41))</f>
@@ -67116,7 +67233,7 @@
       </c>
       <c r="E41" s="241">
         <f>IF($A41="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A41)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A41))</f>
-        <v>0</v>
+        <v>8.24</v>
       </c>
       <c r="F41" s="101">
         <f>IF($A41="","",COUNTIFS('GECC 2026'!F$2:F$200,$A41))</f>
@@ -67125,15 +67242,15 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
-        <v>Silvia Lima Damasceno</v>
+        <v>Tarsila Firmino Ely</v>
       </c>
       <c r="B42" s="103">
         <f>IF($A42="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A42))</f>
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="C42" s="103">
         <f>IF($A42="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A42))</f>
-        <v>0.24</v>
+        <v>96.4</v>
       </c>
       <c r="D42" s="256">
         <f>IF($A42="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A42))</f>
@@ -67141,24 +67258,24 @@
       </c>
       <c r="E42" s="241">
         <f>IF($A42="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A42)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A42))</f>
-        <v>8.24</v>
+        <v>152.4</v>
       </c>
       <c r="F42" s="101">
         <f>IF($A42="","",COUNTIFS('GECC 2026'!F$2:F$200,$A42))</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
-        <v>Tarsila Firmino Ely</v>
+        <v>Túllio Herbeth Teixeira Moraes</v>
       </c>
       <c r="B43" s="103">
         <f>IF($A43="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A43))</f>
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C43" s="103">
         <f>IF($A43="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A43))</f>
-        <v>96.4</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="D43" s="256">
         <f>IF($A43="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A43))</f>
@@ -67166,36 +67283,33 @@
       </c>
       <c r="E43" s="241">
         <f>IF($A43="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A43)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A43))</f>
-        <v>152.4</v>
+        <v>3.45</v>
       </c>
       <c r="F43" s="101">
         <f>IF($A43="","",COUNTIFS('GECC 2026'!F$2:F$200,$A43))</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="str">
-        <v>Túllio Herbeth Teixeira Moraes</v>
-      </c>
-      <c r="B44" s="103">
+      <c r="B44" s="103" t="str">
         <f>IF($A44="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A44))</f>
-        <v>3</v>
-      </c>
-      <c r="C44" s="103">
+        <v/>
+      </c>
+      <c r="C44" s="103" t="str">
         <f>IF($A44="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A44))</f>
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="D44" s="256">
+        <v/>
+      </c>
+      <c r="D44" s="256" t="str">
         <f>IF($A44="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A44))</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="241">
+        <v/>
+      </c>
+      <c r="E44" s="241" t="str">
         <f>IF($A44="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A44)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A44))</f>
-        <v>3.45</v>
-      </c>
-      <c r="F44" s="101">
+        <v/>
+      </c>
+      <c r="F44" s="101" t="str">
         <f>IF($A44="","",COUNTIFS('GECC 2026'!F$2:F$200,$A44))</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -68476,11 +68590,11 @@
       </c>
       <c r="B105" s="243">
         <f>SUM(B5:B100)</f>
-        <v>640</v>
+        <v>605</v>
       </c>
       <c r="C105" s="243">
         <f>SUM(C5:C100)</f>
-        <v>380.10000000000008</v>
+        <v>380.40000000000003</v>
       </c>
       <c r="D105" s="256">
         <f>IF($A105="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A105))</f>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5032" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53BD1C0B-93AF-413F-A11A-246C9E2FD502}"/>
+  <xr:revisionPtr revIDLastSave="5039" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0F87CE-CAE1-4E4A-8FEF-B53C03044D13}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -63014,6 +63014,12 @@
       <c r="Y49" t="s">
         <v>2970</v>
       </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50">
@@ -63058,6 +63064,12 @@
       <c r="Y50" t="s">
         <v>934</v>
       </c>
+      <c r="Z50">
+        <v>1</v>
+      </c>
+      <c r="AA50">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51">
@@ -63102,6 +63114,12 @@
       <c r="Y51" t="s">
         <v>2971</v>
       </c>
+      <c r="Z51">
+        <v>1</v>
+      </c>
+      <c r="AA51">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52">
@@ -63196,6 +63214,12 @@
       <c r="Y53" t="s">
         <v>2972</v>
       </c>
+      <c r="Z53">
+        <v>1</v>
+      </c>
+      <c r="AA53">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54">
@@ -63240,6 +63264,12 @@
       <c r="Y54" t="s">
         <v>2973</v>
       </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55">
@@ -63834,13 +63864,13 @@
         <v>10</v>
       </c>
       <c r="H70">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I70">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="J70">
-        <v>8.24</v>
+        <v>0</v>
       </c>
       <c r="R70" t="str">
         <v/>
@@ -63872,13 +63902,13 @@
         <v>10</v>
       </c>
       <c r="H71">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I71">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="J71">
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="R71" t="str">
         <v/>
@@ -63910,13 +63940,13 @@
         <v>10</v>
       </c>
       <c r="H72">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="J72">
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="R72" t="str">
         <v/>
@@ -63986,13 +64016,13 @@
         <v>10</v>
       </c>
       <c r="H74">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I74">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="J74">
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="R74" t="str">
         <v/>
@@ -64024,13 +64054,13 @@
         <v>10</v>
       </c>
       <c r="H75">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I75">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="J75">
-        <v>8.24</v>
+        <v>0</v>
       </c>
       <c r="R75" t="str">
         <v/>
@@ -66371,11 +66401,11 @@
       </c>
       <c r="B7" s="103">
         <f>IF($A7="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A7))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C7" s="103">
         <f>IF($A7="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A7))</f>
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="D7" s="256">
         <f>IF($A7="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A7))</f>
@@ -66383,7 +66413,7 @@
       </c>
       <c r="E7" s="241">
         <f>IF($A7="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A7)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A7))</f>
-        <v>8.24</v>
+        <v>0</v>
       </c>
       <c r="F7" s="101">
         <f>IF($A7="","",COUNTIFS('GECC 2026'!F$2:F$200,$A7))</f>
@@ -66746,11 +66776,11 @@
       </c>
       <c r="B22" s="103">
         <f>IF($A22="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A22))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C22" s="103">
         <f>IF($A22="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A22))</f>
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="D22" s="256">
         <f>IF($A22="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A22))</f>
@@ -66758,7 +66788,7 @@
       </c>
       <c r="E22" s="241">
         <f>IF($A22="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A22)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A22))</f>
-        <v>8.24</v>
+        <v>0</v>
       </c>
       <c r="F22" s="101">
         <f>IF($A22="","",COUNTIFS('GECC 2026'!F$2:F$200,$A22))</f>
@@ -66821,11 +66851,11 @@
       </c>
       <c r="B25" s="103">
         <f>IF($A25="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A25))</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C25" s="103">
         <f>IF($A25="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A25))</f>
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D25" s="256">
         <f>IF($A25="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A25))</f>
@@ -66833,7 +66863,7 @@
       </c>
       <c r="E25" s="241">
         <f>IF($A25="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A25)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A25))</f>
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="F25" s="101">
         <f>IF($A25="","",COUNTIFS('GECC 2026'!F$2:F$200,$A25))</f>
@@ -66996,11 +67026,11 @@
       </c>
       <c r="B32" s="103">
         <f>IF($A32="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C32" s="103">
         <f>IF($A32="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D32" s="256">
         <f>IF($A32="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
@@ -67008,7 +67038,7 @@
       </c>
       <c r="E32" s="241">
         <f>IF($A32="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A32)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="F32" s="101">
         <f>IF($A32="","",COUNTIFS('GECC 2026'!F$2:F$200,$A32))</f>
@@ -67221,11 +67251,11 @@
       </c>
       <c r="B41" s="103">
         <f>IF($A41="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A41))</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C41" s="103">
         <f>IF($A41="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A41))</f>
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D41" s="256">
         <f>IF($A41="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A41))</f>
@@ -67233,7 +67263,7 @@
       </c>
       <c r="E41" s="241">
         <f>IF($A41="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A41)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A41))</f>
-        <v>8.24</v>
+        <v>1.3</v>
       </c>
       <c r="F41" s="101">
         <f>IF($A41="","",COUNTIFS('GECC 2026'!F$2:F$200,$A41))</f>
@@ -68590,11 +68620,11 @@
       </c>
       <c r="B105" s="243">
         <f>SUM(B5:B100)</f>
-        <v>605</v>
+        <v>568</v>
       </c>
       <c r="C105" s="243">
         <f>SUM(C5:C100)</f>
-        <v>380.40000000000003</v>
+        <v>380.10000000000008</v>
       </c>
       <c r="D105" s="256">
         <f>IF($A105="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A105))</f>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="5039" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0F87CE-CAE1-4E4A-8FEF-B53C03044D13}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -15005,6 +15005,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}" name="Tabela2" displayName="Tabela2" ref="B1:T684" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="B1:T684" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}">
@@ -69100,14 +69104,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69312,21 +69314,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
-    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -69351,9 +69352,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
+    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5039" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0F87CE-CAE1-4E4A-8FEF-B53C03044D13}"/>
+  <xr:revisionPtr revIDLastSave="5040" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C54C7982-6C40-412A-9658-1673E872D61F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -58081,7 +58081,9 @@
       <c r="L702" s="224">
         <v>9746.07</v>
       </c>
-      <c r="M702" s="215"/>
+      <c r="M702" s="215">
+        <v>4.67</v>
+      </c>
       <c r="N702" s="226">
         <v>20</v>
       </c>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5040" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C54C7982-6C40-412A-9658-1673E872D61F}"/>
+  <xr:revisionPtr revIDLastSave="5041" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D4BACF1-0FC0-4FDA-86E0-AD548A6B4710}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56872,7 +56872,9 @@
       <c r="L681" s="61">
         <v>9211.69</v>
       </c>
-      <c r="M681" s="197"/>
+      <c r="M681" s="197">
+        <v>4.84</v>
+      </c>
       <c r="N681" s="192">
         <v>30</v>
       </c>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5041" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D4BACF1-0FC0-4FDA-86E0-AD548A6B4710}"/>
+  <xr:revisionPtr revIDLastSave="5042" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65B95AEC-9F25-41D0-BB42-05A25EE24021}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -12322,7 +12322,7 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>15</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>11</c:v>
@@ -12551,7 +12551,7 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>437</c:v>
+                  <c:v>461</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>447</c:v>
@@ -12891,7 +12891,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -15005,10 +15005,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}" name="Tabela2" displayName="Tabela2" ref="B1:T684" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" totalsRowDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="B1:T684" xr:uid="{D1BD5F14-CD6F-4B62-85D2-128A9D3B5FF1}">
@@ -57354,7 +57350,7 @@
         <v>2026</v>
       </c>
       <c r="C690" s="219" t="s">
-        <v>2663</v>
+        <v>21</v>
       </c>
       <c r="D690" s="219" t="s">
         <v>2784</v>
@@ -61600,7 +61596,7 @@
         <v>2026-034</v>
       </c>
       <c r="N27" t="str">
-        <v>Em andamento</v>
+        <v>Realizado</v>
       </c>
       <c r="O27" t="str">
         <v>Introdução à Engenharia de Prompt - T4</v>
@@ -62987,7 +62983,7 @@
         <v>2026-034</v>
       </c>
       <c r="C49" t="str">
-        <v>Em andamento</v>
+        <v>Realizado</v>
       </c>
       <c r="D49" t="str">
         <v>Introdução à Engenharia de Prompt - T4</v>
@@ -63037,7 +63033,7 @@
         <v>2026-034</v>
       </c>
       <c r="C50" t="str">
-        <v>Em andamento</v>
+        <v>Realizado</v>
       </c>
       <c r="D50" t="str">
         <v>Introdução à Engenharia de Prompt - T4</v>
@@ -65352,7 +65348,7 @@
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="124" t="s">
         <v>2890</v>
@@ -65407,14 +65403,14 @@
       </c>
       <c r="B11" s="110">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!F:F,"Servidores do TCDF")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="109" t="s">
         <v>2896</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>437</v>
+        <v>461</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -65455,14 +65451,14 @@
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="113" t="s">
         <v>2900</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
-        <v>1254</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
@@ -65516,7 +65512,7 @@
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.2558139534883721</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65537,7 +65533,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>6.9767441860465115E-2</v>
+        <v>6.8181818181818177E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65546,7 +65542,7 @@
       </c>
       <c r="B35" s="117">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A35)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" s="127">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A35)</f>
@@ -65554,11 +65550,11 @@
       </c>
       <c r="D35" s="117">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>9.3023255813953487E-2</v>
+        <v>0.11363636363636363</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65579,7 +65575,7 @@
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>2.3255813953488372E-2</v>
+        <v>2.2727272727272728E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65600,7 +65596,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>4.6511627906976744E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65621,7 +65617,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.16279069767441862</v>
+        <v>0.15909090909090909</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65642,7 +65638,7 @@
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>9.3023255813953487E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65663,7 +65659,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>4.6511627906976744E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65684,7 +65680,7 @@
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.16279069767441862</v>
+        <v>0.15909090909090909</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65726,7 +65722,7 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>4.6511627906976744E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -65756,7 +65752,7 @@
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
@@ -65764,7 +65760,7 @@
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>
@@ -69108,12 +69104,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69318,20 +69316,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
+    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -69356,12 +69355,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
-    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5042" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65B95AEC-9F25-41D0-BB42-05A25EE24021}"/>
+  <xr:revisionPtr revIDLastSave="5043" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{758B20BA-524B-422F-893E-0C4C07DD21D6}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -56930,7 +56930,9 @@
         <v>26</v>
       </c>
       <c r="L682" s="202"/>
-      <c r="M682" s="197"/>
+      <c r="M682" s="197">
+        <v>4.8600000000000003</v>
+      </c>
       <c r="N682" s="184">
         <v>200</v>
       </c>
@@ -69104,14 +69106,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69316,21 +69316,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
-    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -69355,9 +69354,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
+    <ds:schemaRef ds:uri="91ce1707-6d34-452b-b217-9734c03e6729"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5045" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59852861-B114-4FBD-8065-501AC41E53AD}"/>
+  <xr:revisionPtr revIDLastSave="5046" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A03132B7-A167-4C11-9D4F-A4C69B3C5AB8}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15287,7 +15287,7 @@
   <dimension ref="A1:V749"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10" style="2" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="21.42578125" style="3" customWidth="1"/>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5059" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D84FDA52-54CD-4B4C-BAFF-2CC533F4B806}"/>
+  <xr:revisionPtr revIDLastSave="5062" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F84018E-D42C-42CF-ABF8-97278F155659}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6567" uniqueCount="2976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6569" uniqueCount="2977">
   <si>
     <t>ID</t>
   </si>
@@ -8675,6 +8675,9 @@
   </si>
   <si>
     <t>30/06/2026 e 02/07/2026</t>
+  </si>
+  <si>
+    <t>TCendo o Futuro</t>
   </si>
   <si>
     <t>ID Ação</t>
@@ -13024,7 +13027,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -58187,12 +58190,18 @@
     <row r="705" spans="1:20" ht="23.25" customHeight="1">
       <c r="A705" s="208" t="str">
         <f>IF(B705="","",B705&amp;"-"&amp;TEXT(COUNTIF(B$2:B705,B705),"000"))</f>
-        <v/>
-      </c>
-      <c r="B705" s="209"/>
-      <c r="C705" s="218"/>
+        <v>2026-049</v>
+      </c>
+      <c r="B705" s="209">
+        <v>2026</v>
+      </c>
+      <c r="C705" s="218" t="s">
+        <v>2765</v>
+      </c>
       <c r="D705" s="209"/>
-      <c r="E705" s="210"/>
+      <c r="E705" s="210" t="s">
+        <v>2836</v>
+      </c>
       <c r="F705" s="211"/>
       <c r="G705" s="208"/>
       <c r="H705" s="212"/>
@@ -58205,9 +58214,9 @@
       <c r="O705" s="216"/>
       <c r="P705" s="216"/>
       <c r="Q705" s="216"/>
-      <c r="R705" s="216" t="str">
+      <c r="R705" s="216">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S705" s="209"/>
       <c r="T705" s="208"/>
@@ -59580,50 +59589,50 @@
         <v>1</v>
       </c>
       <c r="B1" s="96" t="s">
-        <v>2836</v>
+        <v>2837</v>
       </c>
       <c r="C1" s="96" t="s">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="D1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="F1" s="96" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="96" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="H1" s="96" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="I1" s="96" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="J1" s="96" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="L1" s="129" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="M1" s="100">
         <v>2026</v>
       </c>
       <c r="U1" s="162" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="V1" s="161"/>
       <c r="X1" s="159" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="Y1" s="107"/>
       <c r="Z1" s="107"/>
       <c r="AA1" s="107"/>
       <c r="AC1" s="253" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="2" spans="1:31">
@@ -59659,25 +59668,25 @@
         <v>10.4</v>
       </c>
       <c r="X2" s="160" t="s">
-        <v>2836</v>
+        <v>2837</v>
       </c>
       <c r="Y2" s="160" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="160" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="AA2" s="160" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="AC2" s="254" t="s">
         <v>1</v>
       </c>
       <c r="AD2" s="254" t="s">
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="AE2" s="254" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -59712,34 +59721,34 @@
         <v>5.2</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>2852</v>
+        <v>2853</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>2855</v>
+        <v>2856</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>2857</v>
+        <v>2858</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>2858</v>
+        <v>2859</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="X3" t="s">
-        <v>2860</v>
+        <v>2861</v>
       </c>
       <c r="Y3" t="s">
         <v>2697</v>
@@ -59823,7 +59832,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>2861</v>
+        <v>2862</v>
       </c>
       <c r="Y4" t="s">
         <v>2697</v>
@@ -59903,7 +59912,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="Y5" t="s">
         <v>2713</v>
@@ -59918,7 +59927,7 @@
         <v>2026</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="AE5" s="249">
         <v>16</v>
@@ -59983,10 +59992,10 @@
         <v>6</v>
       </c>
       <c r="X6" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="Y6" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -59998,7 +60007,7 @@
         <v>2026</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="AE6" s="249">
         <v>16</v>
@@ -60063,7 +60072,7 @@
         <v>8</v>
       </c>
       <c r="X7" s="98" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="Y7" t="s">
         <v>2697</v>
@@ -60143,7 +60152,7 @@
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="Y8" s="95" t="s">
         <v>1343</v>
@@ -60216,7 +60225,7 @@
         <v>11</v>
       </c>
       <c r="X9" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="Y9" s="95" t="s">
         <v>1023</v>
@@ -60289,7 +60298,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="Y10" s="95" t="s">
         <v>1367</v>
@@ -60362,10 +60371,10 @@
         <v>14</v>
       </c>
       <c r="X11" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="Y11" s="95" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="AA11">
         <v>1.2</v>
@@ -60435,10 +60444,10 @@
         <v>15</v>
       </c>
       <c r="X12" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="AA12">
         <v>1.2</v>
@@ -60508,7 +60517,7 @@
         <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>1343</v>
@@ -60581,7 +60590,7 @@
         <v>18</v>
       </c>
       <c r="X14" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="Y14" s="95" t="s">
         <v>1023</v>
@@ -60654,7 +60663,7 @@
         <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="Y15" s="95" t="s">
         <v>1367</v>
@@ -60727,10 +60736,10 @@
         <v>22</v>
       </c>
       <c r="X16" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="Y16" s="95" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="AA16">
         <v>1.2</v>
@@ -60800,10 +60809,10 @@
         <v>23</v>
       </c>
       <c r="X17" t="s">
+        <v>2871</v>
+      </c>
+      <c r="Y17" s="95" t="s">
         <v>2870</v>
-      </c>
-      <c r="Y17" s="95" t="s">
-        <v>2869</v>
       </c>
       <c r="AA17">
         <v>1.2</v>
@@ -60873,7 +60882,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y18" s="95" t="s">
         <v>1343</v>
@@ -60946,7 +60955,7 @@
         <v>33</v>
       </c>
       <c r="X19" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y19" s="95" t="s">
         <v>1023</v>
@@ -61019,7 +61028,7 @@
         <v>34</v>
       </c>
       <c r="X20" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y20" s="95" t="s">
         <v>1367</v>
@@ -61092,10 +61101,10 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y21" s="95" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="AA21">
         <v>1.2</v>
@@ -61165,10 +61174,10 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y22" s="95" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="AA22">
         <v>1.2</v>
@@ -61238,7 +61247,7 @@
         <v>39</v>
       </c>
       <c r="X23" s="98" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y23" s="95" t="s">
         <v>2713</v>
@@ -61311,10 +61320,10 @@
         <v>41</v>
       </c>
       <c r="X24" s="98" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y24" s="95" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -61384,7 +61393,7 @@
         <v>43</v>
       </c>
       <c r="X25" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y25" s="95" t="s">
         <v>855</v>
@@ -61457,10 +61466,10 @@
         <v>45</v>
       </c>
       <c r="X26" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y26" s="95" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -61533,7 +61542,7 @@
         <v>47</v>
       </c>
       <c r="X27" s="256" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y27" s="95" t="s">
         <v>2713</v>
@@ -61606,10 +61615,10 @@
         <v>49</v>
       </c>
       <c r="X28" s="256" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -61679,7 +61688,7 @@
         <v>50</v>
       </c>
       <c r="X29" s="256" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y29" s="95" t="s">
         <v>2713</v>
@@ -61752,10 +61761,10 @@
         <v>51</v>
       </c>
       <c r="X30" s="256" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y30" s="95" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -61825,7 +61834,7 @@
         <v>56</v>
       </c>
       <c r="X31" s="256" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="Y31" s="95" t="s">
         <v>472</v>
@@ -61901,7 +61910,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="256" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y32" t="s">
         <v>1343</v>
@@ -61977,10 +61986,10 @@
         <v>59</v>
       </c>
       <c r="X33" s="256" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y33" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Z33">
         <v>4</v>
@@ -61990,7 +61999,7 @@
       </c>
       <c r="AC33" s="250"/>
       <c r="AD33" s="251" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="AE33" s="252">
         <f>SUM(AE3:AE32)</f>
@@ -62056,10 +62065,10 @@
         <v>60</v>
       </c>
       <c r="X34" s="256" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y34" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -62127,7 +62136,7 @@
         <v>62</v>
       </c>
       <c r="X35" s="256" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y35" t="s">
         <v>108</v>
@@ -62198,7 +62207,7 @@
         <v>63</v>
       </c>
       <c r="X36" s="256" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y36" t="s">
         <v>549</v>
@@ -62269,7 +62278,7 @@
         <v>64</v>
       </c>
       <c r="X37" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="Y37" t="s">
         <v>418</v>
@@ -62340,7 +62349,7 @@
         <v>74</v>
       </c>
       <c r="X38" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="Y38" s="259" t="s">
         <v>1096</v>
@@ -62411,7 +62420,7 @@
         <v>77</v>
       </c>
       <c r="X39" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="Y39" t="s">
         <v>549</v>
@@ -62482,7 +62491,7 @@
         <v>79</v>
       </c>
       <c r="X40" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="Y40" t="s">
         <v>472</v>
@@ -62535,7 +62544,7 @@
         <v>81</v>
       </c>
       <c r="X41" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="Y41" t="s">
         <v>1472</v>
@@ -62585,10 +62594,10 @@
         <v/>
       </c>
       <c r="X42" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="Y42" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -62635,7 +62644,7 @@
         <v/>
       </c>
       <c r="X43" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="Y43" s="95" t="s">
         <v>2713</v>
@@ -62682,10 +62691,10 @@
         <v/>
       </c>
       <c r="X44" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="Y44" s="95" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="AA44">
         <v>0</v>
@@ -62729,10 +62738,10 @@
         <v/>
       </c>
       <c r="X45" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y45" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Z45">
         <v>1</v>
@@ -62779,10 +62788,10 @@
         <v/>
       </c>
       <c r="X46" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y46" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Z46">
         <v>1</v>
@@ -62829,10 +62838,10 @@
         <v/>
       </c>
       <c r="X47" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y47" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Z47">
         <v>1</v>
@@ -62879,10 +62888,10 @@
         <v/>
       </c>
       <c r="X48" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y48" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Z48">
         <v>1</v>
@@ -62929,10 +62938,10 @@
         <v/>
       </c>
       <c r="X49" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y49" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -62979,7 +62988,7 @@
         <v/>
       </c>
       <c r="X50" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y50" t="s">
         <v>935</v>
@@ -63029,10 +63038,10 @@
         <v/>
       </c>
       <c r="X51" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y51" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="Z51">
         <v>1</v>
@@ -63079,7 +63088,7 @@
         <v/>
       </c>
       <c r="X52" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y52" t="s">
         <v>1343</v>
@@ -63129,10 +63138,10 @@
         <v/>
       </c>
       <c r="X53" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y53" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="Z53">
         <v>1</v>
@@ -63179,10 +63188,10 @@
         <v/>
       </c>
       <c r="X54" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y54" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -65222,7 +65231,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1">
       <c r="A1" s="278" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="B1" s="278"/>
       <c r="C1" s="278"/>
@@ -65243,35 +65252,35 @@
     <row r="3" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1">
       <c r="A4" s="279" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="B4" s="280"/>
       <c r="D4" s="281" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="E4" s="282"/>
       <c r="G4" s="125" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1">
       <c r="A5" s="115">
         <f>COUNTIF('Ações InCompany'!B:B,2026)</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
         <v>32</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="5.0999999999999996" customHeight="1">
@@ -65285,11 +65294,11 @@
     </row>
     <row r="8" spans="1:7" ht="17.25">
       <c r="A8" s="277" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="B8" s="277"/>
       <c r="D8" s="277" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="E8" s="277"/>
     </row>
@@ -65304,13 +65313,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="108" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="D10" s="108" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="E10" s="108" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.95" customHeight="1">
@@ -65322,7 +65331,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="109" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -65338,7 +65347,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -65354,7 +65363,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="109" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -65363,14 +65372,14 @@
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1">
       <c r="A14" s="113" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
         <v>32</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
@@ -65379,7 +65388,7 @@
     </row>
     <row r="30" spans="1:5" ht="17.25">
       <c r="A30" s="277" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="B30" s="277"/>
       <c r="C30" s="277"/>
@@ -65398,16 +65407,16 @@
         <v>6</v>
       </c>
       <c r="B32" s="108" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="C32" s="108" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="D32" s="108" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1">
@@ -65428,7 +65437,7 @@
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.23255813953488372</v>
+        <v>0.22727272727272727</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1">
@@ -65449,7 +65458,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>6.9767441860465115E-2</v>
+        <v>6.8181818181818177E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1">
@@ -65470,7 +65479,7 @@
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>0.11627906976744186</v>
+        <v>0.11363636363636363</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1">
@@ -65491,7 +65500,7 @@
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>2.3255813953488372E-2</v>
+        <v>2.2727272727272728E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1">
@@ -65512,7 +65521,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>4.6511627906976744E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1">
@@ -65533,7 +65542,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.16279069767441862</v>
+        <v>0.15909090909090909</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1">
@@ -65554,7 +65563,7 @@
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>9.3023255813953487E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1">
@@ -65575,7 +65584,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>4.6511627906976744E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1">
@@ -65596,12 +65605,12 @@
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.16279069767441862</v>
+        <v>0.15909090909090909</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1">
       <c r="A42" s="156" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="B42" s="153">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A42)</f>
@@ -65638,12 +65647,12 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>4.6511627906976744E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1">
       <c r="A44" s="148" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="B44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,"")</f>
@@ -65651,20 +65660,20 @@
       </c>
       <c r="C44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" s="149">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="150">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.2727272727272728E-2</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1">
       <c r="A45" s="113" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
@@ -65672,11 +65681,11 @@
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>
@@ -65715,163 +65724,163 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1729</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>457</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>199</v>
@@ -65880,15 +65889,15 @@
         <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>364</v>
@@ -65897,7 +65906,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
     </row>
   </sheetData>
@@ -65919,16 +65928,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>2837</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1">
@@ -65939,7 +65948,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>2765</v>
@@ -65953,7 +65962,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>2664</v>
@@ -66004,180 +66013,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>2690</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>2711</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>2695</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>199</v>
@@ -66186,15 +66195,15 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>364</v>
@@ -66203,7 +66212,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
     </row>
   </sheetData>
@@ -66222,7 +66231,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
       <c r="A1" s="290" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="B1" s="290"/>
       <c r="C1" s="290"/>
@@ -66232,7 +66241,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="291" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
       <c r="B2" s="291"/>
       <c r="C2" s="291"/>
@@ -66245,19 +66254,19 @@
         <v>19</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="E4" s="102" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="F4" s="102" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -68536,7 +68545,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="241" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="B105" s="242">
         <f>SUM(B5:B100)</f>
@@ -68587,7 +68596,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1">
       <c r="A1" s="283" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="B1" s="283"/>
       <c r="C1" s="283"/>
@@ -68599,20 +68608,20 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="130" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1">
       <c r="A4" s="284" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="B4" s="285"/>
       <c r="D4" s="284" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="E4" s="285"/>
       <c r="G4" s="284" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="H4" s="285"/>
     </row>
@@ -68636,28 +68645,28 @@
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1">
       <c r="A7" s="143" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="C7" s="143" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="143" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="E7" s="143" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="F7" s="143" t="s">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="G7" s="143" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="143" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -69020,6 +69029,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052D3A7BF04652843BCB50FE90745AA50" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ef6274641b2f7d621af528393bef14e5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe686eaa-0658-4f15-b230-9e46c4d089fd" xmlns:ns3="91ce1707-6d34-452b-b217-9734c03e6729" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fa87a3bcf42251a9fb9988d55372596" ns2:_="" ns3:_="">
     <xsd:import namespace="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
@@ -69220,28 +69249,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69249,5 +69258,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}"/>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5062" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F84018E-D42C-42CF-ABF8-97278F155659}"/>
+  <xr:revisionPtr revIDLastSave="5064" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27A1D697-DB8A-4CA0-AD2F-4E9D5A441CCC}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6569" uniqueCount="2977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6571" uniqueCount="2977">
   <si>
     <t>ID</t>
   </si>
@@ -13009,7 +13009,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
@@ -13027,7 +13027,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -58202,8 +58202,12 @@
       <c r="E705" s="210" t="s">
         <v>2836</v>
       </c>
-      <c r="F705" s="211"/>
-      <c r="G705" s="208"/>
+      <c r="F705" s="211" t="s">
+        <v>81</v>
+      </c>
+      <c r="G705" s="260" t="s">
+        <v>2727</v>
+      </c>
       <c r="H705" s="212"/>
       <c r="I705" s="213"/>
       <c r="J705" s="213"/>
@@ -65534,15 +65538,15 @@
       </c>
       <c r="C38" s="128">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A38)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" s="119">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.15909090909090909</v>
+        <v>0.18181818181818182</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1">
@@ -65660,15 +65664,15 @@
       </c>
       <c r="C44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="149">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="150">
         <f t="shared" si="1"/>
-        <v>2.2727272727272728E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5064" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27A1D697-DB8A-4CA0-AD2F-4E9D5A441CCC}"/>
+  <xr:revisionPtr revIDLastSave="5065" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0C55DDF-8CAF-4983-8469-8E6E1CED1E13}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6571" uniqueCount="2977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6572" uniqueCount="2977">
   <si>
     <t>ID</t>
   </si>
@@ -58223,7 +58223,9 @@
         <v>0</v>
       </c>
       <c r="S705" s="209"/>
-      <c r="T705" s="208"/>
+      <c r="T705" s="43" t="s">
+        <v>2741</v>
+      </c>
     </row>
     <row r="706" spans="1:20" ht="23.25" customHeight="1">
       <c r="A706" s="217" t="str">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5065" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0C55DDF-8CAF-4983-8469-8E6E1CED1E13}"/>
+  <xr:revisionPtr revIDLastSave="5070" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56A22FF4-A15C-4859-A755-F5E74EACC5ED}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6572" uniqueCount="2977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6574" uniqueCount="2978">
   <si>
     <t>ID</t>
   </si>
@@ -8678,6 +8678,9 @@
   </si>
   <si>
     <t>TCendo o Futuro</t>
+  </si>
+  <si>
+    <t>20/08/2026 e 21/08/2026</t>
   </si>
   <si>
     <t>ID Ação</t>
@@ -9881,7 +9884,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="292">
+  <cellXfs count="293">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10688,6 +10691,9 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -58208,13 +58214,23 @@
       <c r="G705" s="260" t="s">
         <v>2727</v>
       </c>
-      <c r="H705" s="212"/>
-      <c r="I705" s="213"/>
-      <c r="J705" s="213"/>
-      <c r="K705" s="209"/>
+      <c r="H705" s="289" t="s">
+        <v>2837</v>
+      </c>
+      <c r="I705" s="213">
+        <v>46254</v>
+      </c>
+      <c r="J705" s="213">
+        <v>46255</v>
+      </c>
+      <c r="K705" s="209" t="s">
+        <v>35</v>
+      </c>
       <c r="L705" s="223"/>
       <c r="M705" s="214"/>
-      <c r="N705" s="215"/>
+      <c r="N705" s="215">
+        <v>80</v>
+      </c>
       <c r="O705" s="216"/>
       <c r="P705" s="216"/>
       <c r="Q705" s="216"/>
@@ -59595,55 +59611,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="96" t="s">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="C1" s="96" t="s">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="D1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="F1" s="96" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="96" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="H1" s="96" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="I1" s="96" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="J1" s="96" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="L1" s="129" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="M1" s="100">
         <v>2026</v>
       </c>
       <c r="U1" s="162" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="V1" s="161"/>
       <c r="X1" s="159" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="Y1" s="107"/>
       <c r="Z1" s="107"/>
       <c r="AA1" s="107"/>
       <c r="AC1" s="253" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="2" spans="1:31">
       <c r="A2" s="98" cm="1">
-        <f t="array" ref="A2:J82">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
+        <f t="array" ref="A2:J87">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
         <v>2026</v>
       </c>
       <c r="B2" s="98" t="str">
@@ -59674,25 +59690,25 @@
         <v>10.4</v>
       </c>
       <c r="X2" s="160" t="s">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="Y2" s="160" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="160" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="AA2" s="160" t="s">
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="AC2" s="254" t="s">
         <v>1</v>
       </c>
       <c r="AD2" s="254" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
       <c r="AE2" s="254" t="s">
-        <v>2851</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -59727,34 +59743,34 @@
         <v>5.2</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>2852</v>
+        <v>2853</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>2855</v>
+        <v>2856</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>2857</v>
+        <v>2858</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>2858</v>
+        <v>2859</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>2860</v>
+        <v>2861</v>
       </c>
       <c r="X3" t="s">
-        <v>2861</v>
+        <v>2862</v>
       </c>
       <c r="Y3" t="s">
         <v>2697</v>
@@ -59807,7 +59823,7 @@
         <v>5.2</v>
       </c>
       <c r="L4" cm="1">
-        <f t="array" ref="L4:Q40">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
+        <f t="array" ref="L4:Q41">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
         <v>2026</v>
       </c>
       <c r="M4" t="str">
@@ -59834,11 +59850,11 @@
         <v>1</v>
       </c>
       <c r="T4" cm="1">
-        <f t="array" ref="T4:T41">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
+        <f t="array" ref="T4:T42">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="Y4" t="s">
         <v>2697</v>
@@ -59918,7 +59934,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="Y5" t="s">
         <v>2713</v>
@@ -59933,7 +59949,7 @@
         <v>2026</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="AE5" s="249">
         <v>16</v>
@@ -59998,10 +60014,10 @@
         <v>6</v>
       </c>
       <c r="X6" t="s">
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="Y6" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -60013,7 +60029,7 @@
         <v>2026</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="AE6" s="249">
         <v>16</v>
@@ -60078,7 +60094,7 @@
         <v>8</v>
       </c>
       <c r="X7" s="98" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="Y7" t="s">
         <v>2697</v>
@@ -60158,7 +60174,7 @@
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="Y8" s="95" t="s">
         <v>1343</v>
@@ -60231,7 +60247,7 @@
         <v>11</v>
       </c>
       <c r="X9" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="Y9" s="95" t="s">
         <v>1023</v>
@@ -60304,7 +60320,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="Y10" s="95" t="s">
         <v>1367</v>
@@ -60377,10 +60393,10 @@
         <v>14</v>
       </c>
       <c r="X11" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="Y11" s="95" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="AA11">
         <v>1.2</v>
@@ -60450,10 +60466,10 @@
         <v>15</v>
       </c>
       <c r="X12" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="AA12">
         <v>1.2</v>
@@ -60523,7 +60539,7 @@
         <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>1343</v>
@@ -60596,7 +60612,7 @@
         <v>18</v>
       </c>
       <c r="X14" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y14" s="95" t="s">
         <v>1023</v>
@@ -60669,7 +60685,7 @@
         <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y15" s="95" t="s">
         <v>1367</v>
@@ -60742,10 +60758,10 @@
         <v>22</v>
       </c>
       <c r="X16" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y16" s="95" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="AA16">
         <v>1.2</v>
@@ -60815,10 +60831,10 @@
         <v>23</v>
       </c>
       <c r="X17" t="s">
+        <v>2872</v>
+      </c>
+      <c r="Y17" s="95" t="s">
         <v>2871</v>
-      </c>
-      <c r="Y17" s="95" t="s">
-        <v>2870</v>
       </c>
       <c r="AA17">
         <v>1.2</v>
@@ -60888,7 +60904,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y18" s="95" t="s">
         <v>1343</v>
@@ -60961,7 +60977,7 @@
         <v>33</v>
       </c>
       <c r="X19" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y19" s="95" t="s">
         <v>1023</v>
@@ -61034,7 +61050,7 @@
         <v>34</v>
       </c>
       <c r="X20" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y20" s="95" t="s">
         <v>1367</v>
@@ -61107,10 +61123,10 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y21" s="95" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="AA21">
         <v>1.2</v>
@@ -61180,10 +61196,10 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y22" s="95" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="AA22">
         <v>1.2</v>
@@ -61253,7 +61269,7 @@
         <v>39</v>
       </c>
       <c r="X23" s="98" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y23" s="95" t="s">
         <v>2713</v>
@@ -61326,10 +61342,10 @@
         <v>41</v>
       </c>
       <c r="X24" s="98" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y24" s="95" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -61399,7 +61415,7 @@
         <v>43</v>
       </c>
       <c r="X25" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y25" s="95" t="s">
         <v>855</v>
@@ -61472,10 +61488,10 @@
         <v>45</v>
       </c>
       <c r="X26" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y26" s="95" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -61548,7 +61564,7 @@
         <v>47</v>
       </c>
       <c r="X27" s="256" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y27" s="95" t="s">
         <v>2713</v>
@@ -61621,10 +61637,10 @@
         <v>49</v>
       </c>
       <c r="X28" s="256" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -61694,7 +61710,7 @@
         <v>50</v>
       </c>
       <c r="X29" s="256" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="Y29" s="95" t="s">
         <v>2713</v>
@@ -61767,10 +61783,10 @@
         <v>51</v>
       </c>
       <c r="X30" s="256" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="Y30" s="95" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -61840,7 +61856,7 @@
         <v>56</v>
       </c>
       <c r="X31" s="256" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y31" s="95" t="s">
         <v>472</v>
@@ -61916,7 +61932,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="256" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Y32" t="s">
         <v>1343</v>
@@ -61992,10 +62008,10 @@
         <v>59</v>
       </c>
       <c r="X33" s="256" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Y33" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="Z33">
         <v>4</v>
@@ -62005,7 +62021,7 @@
       </c>
       <c r="AC33" s="250"/>
       <c r="AD33" s="251" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="AE33" s="252">
         <f>SUM(AE3:AE32)</f>
@@ -62071,10 +62087,10 @@
         <v>60</v>
       </c>
       <c r="X34" s="256" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Y34" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -62142,7 +62158,7 @@
         <v>62</v>
       </c>
       <c r="X35" s="256" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Y35" t="s">
         <v>108</v>
@@ -62213,7 +62229,7 @@
         <v>63</v>
       </c>
       <c r="X36" s="256" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Y36" t="s">
         <v>549</v>
@@ -62284,7 +62300,7 @@
         <v>64</v>
       </c>
       <c r="X37" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="Y37" t="s">
         <v>418</v>
@@ -62355,7 +62371,7 @@
         <v>74</v>
       </c>
       <c r="X38" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="Y38" s="259" t="s">
         <v>1096</v>
@@ -62426,7 +62442,7 @@
         <v>77</v>
       </c>
       <c r="X39" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="Y39" t="s">
         <v>549</v>
@@ -62497,7 +62513,7 @@
         <v>79</v>
       </c>
       <c r="X40" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="Y40" t="s">
         <v>472</v>
@@ -62540,17 +62556,35 @@
       <c r="J41" s="163">
         <v>13.8</v>
       </c>
-      <c r="R41" t="str">
-        <v/>
-      </c>
-      <c r="S41" t="str">
-        <v/>
+      <c r="L41">
+        <v>2026</v>
+      </c>
+      <c r="M41" t="str">
+        <v>2026-049</v>
+      </c>
+      <c r="N41" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="O41" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco</v>
+      </c>
+      <c r="R41">
+        <v>5</v>
+      </c>
+      <c r="S41">
+        <v>86</v>
       </c>
       <c r="T41">
         <v>81</v>
       </c>
       <c r="X41" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="Y41" t="s">
         <v>1472</v>
@@ -62599,11 +62633,14 @@
       <c r="S42" t="str">
         <v/>
       </c>
+      <c r="T42">
+        <v>86</v>
+      </c>
       <c r="X42" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="Y42" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -62650,7 +62687,7 @@
         <v/>
       </c>
       <c r="X43" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y43" s="95" t="s">
         <v>2713</v>
@@ -62697,10 +62734,10 @@
         <v/>
       </c>
       <c r="X44" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y44" s="95" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="AA44">
         <v>0</v>
@@ -62744,10 +62781,10 @@
         <v/>
       </c>
       <c r="X45" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y45" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Z45">
         <v>1</v>
@@ -62794,10 +62831,10 @@
         <v/>
       </c>
       <c r="X46" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y46" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Z46">
         <v>1</v>
@@ -62844,10 +62881,10 @@
         <v/>
       </c>
       <c r="X47" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y47" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Z47">
         <v>1</v>
@@ -62894,10 +62931,10 @@
         <v/>
       </c>
       <c r="X48" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y48" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Z48">
         <v>1</v>
@@ -62944,10 +62981,10 @@
         <v/>
       </c>
       <c r="X49" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y49" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -62994,7 +63031,7 @@
         <v/>
       </c>
       <c r="X50" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y50" t="s">
         <v>935</v>
@@ -63044,10 +63081,10 @@
         <v/>
       </c>
       <c r="X51" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y51" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="Z51">
         <v>1</v>
@@ -63094,7 +63131,7 @@
         <v/>
       </c>
       <c r="X52" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y52" t="s">
         <v>1343</v>
@@ -63144,10 +63181,10 @@
         <v/>
       </c>
       <c r="X53" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y53" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="Z53">
         <v>1</v>
@@ -63194,10 +63231,10 @@
         <v/>
       </c>
       <c r="X54" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y54" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -64271,6 +64308,36 @@
       </c>
     </row>
     <row r="83" spans="1:19">
+      <c r="A83">
+        <v>2026</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2026-049</v>
+      </c>
+      <c r="C83" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D83" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
+      </c>
+      <c r="G83">
+        <v>5</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
       <c r="R83" t="str">
         <v/>
       </c>
@@ -64279,6 +64346,36 @@
       </c>
     </row>
     <row r="84" spans="1:19">
+      <c r="A84">
+        <v>2026</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2026-049</v>
+      </c>
+      <c r="C84" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D84" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Adriana Cuoco Portugal</v>
+      </c>
+      <c r="G84">
+        <v>5</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
       <c r="R84" t="str">
         <v/>
       </c>
@@ -64287,6 +64384,36 @@
       </c>
     </row>
     <row r="85" spans="1:19">
+      <c r="A85">
+        <v>2026</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2026-049</v>
+      </c>
+      <c r="C85" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D85" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Fernanda Viana de Souza</v>
+      </c>
+      <c r="G85">
+        <v>5</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
       <c r="R85" t="str">
         <v/>
       </c>
@@ -64295,6 +64422,36 @@
       </c>
     </row>
     <row r="86" spans="1:19">
+      <c r="A86">
+        <v>2026</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2026-049</v>
+      </c>
+      <c r="C86" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D86" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Denise Duarte Guirra Kuhlmann</v>
+      </c>
+      <c r="G86">
+        <v>5</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
       <c r="R86" t="str">
         <v/>
       </c>
@@ -64303,6 +64460,36 @@
       </c>
     </row>
     <row r="87" spans="1:19">
+      <c r="A87">
+        <v>2026</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2026-049</v>
+      </c>
+      <c r="C87" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D87" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Priscila Nolasco</v>
+      </c>
+      <c r="G87">
+        <v>5</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
       <c r="R87" t="str">
         <v/>
       </c>
@@ -65237,7 +65424,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1">
       <c r="A1" s="278" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="B1" s="278"/>
       <c r="C1" s="278"/>
@@ -65258,15 +65445,15 @@
     <row r="3" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1">
       <c r="A4" s="279" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="B4" s="280"/>
       <c r="D4" s="281" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="E4" s="282"/>
       <c r="G4" s="125" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1">
@@ -65275,14 +65462,14 @@
         <v>49</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
         <v>32</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
@@ -65300,32 +65487,32 @@
     </row>
     <row r="8" spans="1:7" ht="17.25">
       <c r="A8" s="277" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="B8" s="277"/>
       <c r="D8" s="277" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="E8" s="277"/>
     </row>
     <row r="9" spans="1:7" ht="5.0999999999999996" customHeight="1">
-      <c r="A9" s="289"/>
-      <c r="B9" s="289"/>
-      <c r="D9" s="289"/>
-      <c r="E9" s="289"/>
+      <c r="A9" s="290"/>
+      <c r="B9" s="290"/>
+      <c r="D9" s="290"/>
+      <c r="E9" s="290"/>
     </row>
     <row r="10" spans="1:7" ht="24.95" customHeight="1">
       <c r="A10" s="108" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="108" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="D10" s="108" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="E10" s="108" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.95" customHeight="1">
@@ -65337,7 +65524,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="109" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -65353,7 +65540,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -65369,7 +65556,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="109" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -65378,14 +65565,14 @@
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1">
       <c r="A14" s="113" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
         <v>32</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
@@ -65394,7 +65581,7 @@
     </row>
     <row r="30" spans="1:5" ht="17.25">
       <c r="A30" s="277" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="B30" s="277"/>
       <c r="C30" s="277"/>
@@ -65402,27 +65589,27 @@
       <c r="E30" s="277"/>
     </row>
     <row r="31" spans="1:5" ht="5.0999999999999996" customHeight="1">
-      <c r="A31" s="289"/>
-      <c r="B31" s="289"/>
-      <c r="C31" s="289"/>
-      <c r="D31" s="289"/>
-      <c r="E31" s="289"/>
+      <c r="A31" s="290"/>
+      <c r="B31" s="290"/>
+      <c r="C31" s="290"/>
+      <c r="D31" s="290"/>
+      <c r="E31" s="290"/>
     </row>
     <row r="32" spans="1:5" ht="24.95" customHeight="1">
       <c r="A32" s="108" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="108" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="C32" s="108" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="D32" s="108" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1">
@@ -65616,7 +65803,7 @@
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1">
       <c r="A42" s="156" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="B42" s="153">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A42)</f>
@@ -65658,7 +65845,7 @@
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1">
       <c r="A44" s="148" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,"")</f>
@@ -65679,7 +65866,7 @@
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1">
       <c r="A45" s="113" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
@@ -65730,163 +65917,163 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1729</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>457</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>199</v>
@@ -65895,15 +66082,15 @@
         <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>364</v>
@@ -65912,7 +66099,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
     </row>
   </sheetData>
@@ -65934,16 +66121,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>2838</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1">
@@ -65954,7 +66141,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>2765</v>
@@ -65968,7 +66155,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>2664</v>
@@ -66019,180 +66206,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>2690</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>2711</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>2695</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>199</v>
@@ -66201,15 +66388,15 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>364</v>
@@ -66218,7 +66405,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
     </row>
   </sheetData>
@@ -66236,43 +66423,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
-      <c r="A1" s="290" t="s">
-        <v>2963</v>
-      </c>
-      <c r="B1" s="290"/>
-      <c r="C1" s="290"/>
-      <c r="D1" s="290"/>
-      <c r="E1" s="290"/>
-      <c r="F1" s="290"/>
+      <c r="A1" s="291" t="s">
+        <v>2964</v>
+      </c>
+      <c r="B1" s="291"/>
+      <c r="C1" s="291"/>
+      <c r="D1" s="291"/>
+      <c r="E1" s="291"/>
+      <c r="F1" s="291"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="291" t="s">
-        <v>2964</v>
-      </c>
-      <c r="B2" s="291"/>
-      <c r="C2" s="291"/>
-      <c r="D2" s="291"/>
-      <c r="E2" s="291"/>
-      <c r="F2" s="291"/>
+      <c r="A2" s="292" t="s">
+        <v>2965</v>
+      </c>
+      <c r="B2" s="292"/>
+      <c r="C2" s="292"/>
+      <c r="D2" s="292"/>
+      <c r="E2" s="292"/>
+      <c r="F2" s="292"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="102" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
       <c r="E4" s="102" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="F4" s="102" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -66298,7 +66485,7 @@
       </c>
       <c r="F5" s="101">
         <f>IF($A5="","",COUNTIFS('GECC 2026'!F$2:F$200,$A5))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="101">
         <f>IF($A5="","",COUNTIFS('GECC 2026'!G$2:G$200,$A5))</f>
@@ -66452,7 +66639,7 @@
       </c>
       <c r="F11" s="101">
         <f>IF($A11="","",COUNTIFS('GECC 2026'!F$2:F$200,$A11))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -66527,7 +66714,7 @@
       </c>
       <c r="F14" s="101">
         <f>IF($A14="","",COUNTIFS('GECC 2026'!F$2:F$200,$A14))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -66652,7 +66839,7 @@
       </c>
       <c r="F19" s="101">
         <f>IF($A19="","",COUNTIFS('GECC 2026'!F$2:F$200,$A19))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -67077,7 +67264,7 @@
       </c>
       <c r="F36" s="101">
         <f>IF($A36="","",COUNTIFS('GECC 2026'!F$2:F$200,$A36))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -68551,7 +68738,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="241" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="B105" s="242">
         <f>SUM(B5:B100)</f>
@@ -68571,7 +68758,7 @@
       </c>
       <c r="F105" s="243">
         <f>SUM(F5:F100)</f>
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -68602,7 +68789,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1">
       <c r="A1" s="283" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
       <c r="B1" s="283"/>
       <c r="C1" s="283"/>
@@ -68614,20 +68801,20 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="130" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1">
       <c r="A4" s="284" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="B4" s="285"/>
       <c r="D4" s="284" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="E4" s="285"/>
       <c r="G4" s="284" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="H4" s="285"/>
     </row>
@@ -68651,28 +68838,28 @@
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1">
       <c r="A7" s="143" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="C7" s="143" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="143" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="E7" s="143" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="F7" s="143" t="s">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="G7" s="143" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="143" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5070" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56A22FF4-A15C-4859-A755-F5E74EACC5ED}"/>
+  <xr:revisionPtr revIDLastSave="5079" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43A23BF0-8EE0-4EEE-9981-572563414416}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6574" uniqueCount="2978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6580" uniqueCount="2978">
   <si>
     <t>ID</t>
   </si>
@@ -58257,10 +58257,14 @@
       <c r="H706" s="221"/>
       <c r="I706" s="222"/>
       <c r="J706" s="222"/>
-      <c r="K706" s="218"/>
+      <c r="K706" s="218" t="s">
+        <v>35</v>
+      </c>
       <c r="L706" s="223"/>
       <c r="M706" s="214"/>
-      <c r="N706" s="225"/>
+      <c r="N706" s="225">
+        <v>80</v>
+      </c>
       <c r="O706" s="224"/>
       <c r="P706" s="224"/>
       <c r="Q706" s="224"/>
@@ -58269,7 +58273,9 @@
         <v/>
       </c>
       <c r="S706" s="218"/>
-      <c r="T706" s="217"/>
+      <c r="T706" s="43" t="s">
+        <v>2741</v>
+      </c>
     </row>
     <row r="707" spans="1:20" ht="23.25" customHeight="1">
       <c r="A707" s="208" t="str">
@@ -58285,10 +58291,14 @@
       <c r="H707" s="212"/>
       <c r="I707" s="213"/>
       <c r="J707" s="213"/>
-      <c r="K707" s="209"/>
+      <c r="K707" s="209" t="s">
+        <v>35</v>
+      </c>
       <c r="L707" s="223"/>
       <c r="M707" s="214"/>
-      <c r="N707" s="215"/>
+      <c r="N707" s="215">
+        <v>80</v>
+      </c>
       <c r="O707" s="216"/>
       <c r="P707" s="216"/>
       <c r="Q707" s="216"/>
@@ -58297,7 +58307,9 @@
         <v/>
       </c>
       <c r="S707" s="209"/>
-      <c r="T707" s="208"/>
+      <c r="T707" s="43" t="s">
+        <v>2741</v>
+      </c>
     </row>
     <row r="708" spans="1:20" ht="23.25" customHeight="1">
       <c r="A708" s="217" t="str">
@@ -58313,10 +58325,14 @@
       <c r="H708" s="221"/>
       <c r="I708" s="222"/>
       <c r="J708" s="222"/>
-      <c r="K708" s="218"/>
+      <c r="K708" s="218" t="s">
+        <v>35</v>
+      </c>
       <c r="L708" s="223"/>
       <c r="M708" s="214"/>
-      <c r="N708" s="225"/>
+      <c r="N708" s="225">
+        <v>80</v>
+      </c>
       <c r="O708" s="224"/>
       <c r="P708" s="224"/>
       <c r="Q708" s="224"/>
@@ -58325,7 +58341,9 @@
         <v/>
       </c>
       <c r="S708" s="218"/>
-      <c r="T708" s="217"/>
+      <c r="T708" s="43" t="s">
+        <v>2741</v>
+      </c>
     </row>
     <row r="709" spans="1:20" ht="23.25" customHeight="1">
       <c r="A709" s="208" t="str">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5079" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43A23BF0-8EE0-4EEE-9981-572563414416}"/>
+  <xr:revisionPtr revIDLastSave="5087" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF4060DF-6094-4982-A36A-516437CABBDD}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6580" uniqueCount="2978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6585" uniqueCount="2978">
   <si>
     <t>ID</t>
   </si>
@@ -13033,7 +13033,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -58246,12 +58246,18 @@
     <row r="706" spans="1:20" ht="23.25" customHeight="1">
       <c r="A706" s="217" t="str">
         <f>IF(B706="","",B706&amp;"-"&amp;TEXT(COUNTIF(B$2:B706,B706),"000"))</f>
-        <v/>
-      </c>
-      <c r="B706" s="218"/>
-      <c r="C706" s="218"/>
+        <v>2026-050</v>
+      </c>
+      <c r="B706" s="218">
+        <v>2026</v>
+      </c>
+      <c r="C706" s="218" t="s">
+        <v>2765</v>
+      </c>
       <c r="D706" s="218"/>
-      <c r="E706" s="219"/>
+      <c r="E706" s="210" t="s">
+        <v>2836</v>
+      </c>
       <c r="F706" s="220"/>
       <c r="G706" s="217"/>
       <c r="H706" s="221"/>
@@ -58268,9 +58274,9 @@
       <c r="O706" s="224"/>
       <c r="P706" s="224"/>
       <c r="Q706" s="224"/>
-      <c r="R706" s="224" t="str">
+      <c r="R706" s="224">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S706" s="218"/>
       <c r="T706" s="43" t="s">
@@ -58280,12 +58286,18 @@
     <row r="707" spans="1:20" ht="23.25" customHeight="1">
       <c r="A707" s="208" t="str">
         <f>IF(B707="","",B707&amp;"-"&amp;TEXT(COUNTIF(B$2:B707,B707),"000"))</f>
-        <v/>
-      </c>
-      <c r="B707" s="209"/>
-      <c r="C707" s="218"/>
+        <v>2026-051</v>
+      </c>
+      <c r="B707" s="209">
+        <v>2026</v>
+      </c>
+      <c r="C707" s="218" t="s">
+        <v>2765</v>
+      </c>
       <c r="D707" s="209"/>
-      <c r="E707" s="210"/>
+      <c r="E707" s="210" t="s">
+        <v>2836</v>
+      </c>
       <c r="F707" s="211"/>
       <c r="G707" s="208"/>
       <c r="H707" s="212"/>
@@ -58302,9 +58314,9 @@
       <c r="O707" s="216"/>
       <c r="P707" s="216"/>
       <c r="Q707" s="216"/>
-      <c r="R707" s="216" t="str">
+      <c r="R707" s="216">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S707" s="209"/>
       <c r="T707" s="43" t="s">
@@ -58314,12 +58326,16 @@
     <row r="708" spans="1:20" ht="23.25" customHeight="1">
       <c r="A708" s="217" t="str">
         <f>IF(B708="","",B708&amp;"-"&amp;TEXT(COUNTIF(B$2:B708,B708),"000"))</f>
-        <v/>
-      </c>
-      <c r="B708" s="218"/>
+        <v>2026-052</v>
+      </c>
+      <c r="B708" s="218">
+        <v>2026</v>
+      </c>
       <c r="C708" s="218"/>
       <c r="D708" s="218"/>
-      <c r="E708" s="219"/>
+      <c r="E708" s="210" t="s">
+        <v>2836</v>
+      </c>
       <c r="F708" s="220"/>
       <c r="G708" s="217"/>
       <c r="H708" s="221"/>
@@ -58336,9 +58352,9 @@
       <c r="O708" s="224"/>
       <c r="P708" s="224"/>
       <c r="Q708" s="224"/>
-      <c r="R708" s="224" t="str">
+      <c r="R708" s="224">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S708" s="218"/>
       <c r="T708" s="43" t="s">
@@ -59677,7 +59693,7 @@
     </row>
     <row r="2" spans="1:31">
       <c r="A2" s="98" cm="1">
-        <f t="array" ref="A2:J87">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
+        <f t="array" ref="A2:J102">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
         <v>2026</v>
       </c>
       <c r="B2" s="98" t="str">
@@ -59841,7 +59857,7 @@
         <v>5.2</v>
       </c>
       <c r="L4" cm="1">
-        <f t="array" ref="L4:Q41">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
+        <f t="array" ref="L4:Q44">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
         <v>2026</v>
       </c>
       <c r="M4" t="str">
@@ -59868,7 +59884,7 @@
         <v>1</v>
       </c>
       <c r="T4" cm="1">
-        <f t="array" ref="T4:T42">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
+        <f t="array" ref="T4:T45">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
         <v>0</v>
       </c>
       <c r="X4" t="s">
@@ -62645,11 +62661,29 @@
       <c r="J42" s="163">
         <v>13.8</v>
       </c>
-      <c r="R42" t="str">
-        <v/>
-      </c>
-      <c r="S42" t="str">
-        <v/>
+      <c r="L42">
+        <v>2026</v>
+      </c>
+      <c r="M42" t="str">
+        <v>2026-050</v>
+      </c>
+      <c r="N42" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="O42" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="str">
+        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco</v>
+      </c>
+      <c r="R42">
+        <v>5</v>
+      </c>
+      <c r="S42">
+        <v>91</v>
       </c>
       <c r="T42">
         <v>86</v>
@@ -62698,11 +62732,32 @@
       <c r="J43">
         <v>27.6</v>
       </c>
-      <c r="R43" t="str">
-        <v/>
-      </c>
-      <c r="S43" t="str">
-        <v/>
+      <c r="L43">
+        <v>2026</v>
+      </c>
+      <c r="M43" t="str">
+        <v>2026-051</v>
+      </c>
+      <c r="N43" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="O43" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="str">
+        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco</v>
+      </c>
+      <c r="R43">
+        <v>5</v>
+      </c>
+      <c r="S43">
+        <v>96</v>
+      </c>
+      <c r="T43">
+        <v>91</v>
       </c>
       <c r="X43" t="s">
         <v>2889</v>
@@ -62745,11 +62800,32 @@
       <c r="J44">
         <v>27.6</v>
       </c>
-      <c r="R44" t="str">
-        <v/>
-      </c>
-      <c r="S44" t="str">
-        <v/>
+      <c r="L44">
+        <v>2026</v>
+      </c>
+      <c r="M44" t="str">
+        <v>2026-052</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="str">
+        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco</v>
+      </c>
+      <c r="R44">
+        <v>5</v>
+      </c>
+      <c r="S44">
+        <v>101</v>
+      </c>
+      <c r="T44">
+        <v>96</v>
       </c>
       <c r="X44" t="s">
         <v>2889</v>
@@ -62798,6 +62874,9 @@
       <c r="S45" t="str">
         <v/>
       </c>
+      <c r="T45">
+        <v>101</v>
+      </c>
       <c r="X45" t="s">
         <v>2890</v>
       </c>
@@ -64516,6 +64595,36 @@
       </c>
     </row>
     <row r="88" spans="1:19">
+      <c r="A88">
+        <v>2026</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2026-050</v>
+      </c>
+      <c r="C88" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D88" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
+      </c>
+      <c r="G88">
+        <v>5</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
       <c r="R88" t="str">
         <v/>
       </c>
@@ -64524,6 +64633,36 @@
       </c>
     </row>
     <row r="89" spans="1:19">
+      <c r="A89">
+        <v>2026</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2026-050</v>
+      </c>
+      <c r="C89" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D89" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Adriana Cuoco Portugal</v>
+      </c>
+      <c r="G89">
+        <v>5</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
       <c r="R89" t="str">
         <v/>
       </c>
@@ -64532,6 +64671,36 @@
       </c>
     </row>
     <row r="90" spans="1:19">
+      <c r="A90">
+        <v>2026</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2026-050</v>
+      </c>
+      <c r="C90" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D90" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Fernanda Viana de Souza</v>
+      </c>
+      <c r="G90">
+        <v>5</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
       <c r="R90" t="str">
         <v/>
       </c>
@@ -64540,6 +64709,36 @@
       </c>
     </row>
     <row r="91" spans="1:19">
+      <c r="A91">
+        <v>2026</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2026-050</v>
+      </c>
+      <c r="C91" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D91" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Denise Duarte Guirra Kuhlmann</v>
+      </c>
+      <c r="G91">
+        <v>5</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
       <c r="R91" t="str">
         <v/>
       </c>
@@ -64548,6 +64747,36 @@
       </c>
     </row>
     <row r="92" spans="1:19">
+      <c r="A92">
+        <v>2026</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2026-050</v>
+      </c>
+      <c r="C92" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D92" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Priscila Nolasco</v>
+      </c>
+      <c r="G92">
+        <v>5</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
       <c r="R92" t="str">
         <v/>
       </c>
@@ -64556,6 +64785,36 @@
       </c>
     </row>
     <row r="93" spans="1:19">
+      <c r="A93">
+        <v>2026</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2026-051</v>
+      </c>
+      <c r="C93" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D93" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
+      </c>
+      <c r="G93">
+        <v>5</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
       <c r="R93" t="str">
         <v/>
       </c>
@@ -64564,6 +64823,36 @@
       </c>
     </row>
     <row r="94" spans="1:19">
+      <c r="A94">
+        <v>2026</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2026-051</v>
+      </c>
+      <c r="C94" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D94" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Adriana Cuoco Portugal</v>
+      </c>
+      <c r="G94">
+        <v>5</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
       <c r="R94" t="str">
         <v/>
       </c>
@@ -64572,6 +64861,36 @@
       </c>
     </row>
     <row r="95" spans="1:19">
+      <c r="A95">
+        <v>2026</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2026-051</v>
+      </c>
+      <c r="C95" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D95" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Fernanda Viana de Souza</v>
+      </c>
+      <c r="G95">
+        <v>5</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
       <c r="R95" t="str">
         <v/>
       </c>
@@ -64580,6 +64899,36 @@
       </c>
     </row>
     <row r="96" spans="1:19">
+      <c r="A96">
+        <v>2026</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2026-051</v>
+      </c>
+      <c r="C96" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D96" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Denise Duarte Guirra Kuhlmann</v>
+      </c>
+      <c r="G96">
+        <v>5</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
       <c r="R96" t="str">
         <v/>
       </c>
@@ -64587,7 +64936,37 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="18:19">
+    <row r="97" spans="1:19">
+      <c r="A97">
+        <v>2026</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2026-051</v>
+      </c>
+      <c r="C97" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D97" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Priscila Nolasco</v>
+      </c>
+      <c r="G97">
+        <v>5</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
       <c r="R97" t="str">
         <v/>
       </c>
@@ -64595,7 +64974,37 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="18:19">
+    <row r="98" spans="1:19">
+      <c r="A98">
+        <v>2026</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2026-052</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
+      </c>
+      <c r="G98">
+        <v>5</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
       <c r="R98" t="str">
         <v/>
       </c>
@@ -64603,7 +65012,37 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="18:19">
+    <row r="99" spans="1:19">
+      <c r="A99">
+        <v>2026</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2026-052</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Adriana Cuoco Portugal</v>
+      </c>
+      <c r="G99">
+        <v>5</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
       <c r="R99" t="str">
         <v/>
       </c>
@@ -64611,7 +65050,37 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="18:19">
+    <row r="100" spans="1:19">
+      <c r="A100">
+        <v>2026</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2026-052</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Fernanda Viana de Souza</v>
+      </c>
+      <c r="G100">
+        <v>5</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
       <c r="R100" t="str">
         <v/>
       </c>
@@ -64619,7 +65088,37 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="18:19">
+    <row r="101" spans="1:19">
+      <c r="A101">
+        <v>2026</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2026-052</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Denise Duarte Guirra Kuhlmann</v>
+      </c>
+      <c r="G101">
+        <v>5</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
       <c r="R101" t="str">
         <v/>
       </c>
@@ -64627,7 +65126,37 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="18:19">
+    <row r="102" spans="1:19">
+      <c r="A102">
+        <v>2026</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2026-052</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Priscila Nolasco</v>
+      </c>
+      <c r="G102">
+        <v>5</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
       <c r="R102" t="str">
         <v/>
       </c>
@@ -64635,7 +65164,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="18:19">
+    <row r="103" spans="1:19">
       <c r="R103" t="str">
         <v/>
       </c>
@@ -64643,7 +65172,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="18:19">
+    <row r="104" spans="1:19">
       <c r="R104" t="str">
         <v/>
       </c>
@@ -64651,7 +65180,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="18:19">
+    <row r="105" spans="1:19">
       <c r="R105" t="str">
         <v/>
       </c>
@@ -64659,7 +65188,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="18:19">
+    <row r="106" spans="1:19">
       <c r="R106" t="str">
         <v/>
       </c>
@@ -64667,7 +65196,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="18:19">
+    <row r="107" spans="1:19">
       <c r="R107" t="str">
         <v/>
       </c>
@@ -64675,7 +65204,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="18:19">
+    <row r="108" spans="1:19">
       <c r="R108" t="str">
         <v/>
       </c>
@@ -64683,7 +65212,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="18:19">
+    <row r="109" spans="1:19">
       <c r="R109" t="str">
         <v/>
       </c>
@@ -64691,7 +65220,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="18:19">
+    <row r="110" spans="1:19">
       <c r="R110" t="str">
         <v/>
       </c>
@@ -64699,7 +65228,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="18:19">
+    <row r="111" spans="1:19">
       <c r="R111" t="str">
         <v/>
       </c>
@@ -64707,7 +65236,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="18:19">
+    <row r="112" spans="1:19">
       <c r="R112" t="str">
         <v/>
       </c>
@@ -65477,7 +66006,7 @@
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1">
       <c r="A5" s="115">
         <f>COUNTIF('Ações InCompany'!B:B,2026)</f>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B5" s="116" t="s">
         <v>2903</v>
@@ -65491,7 +66020,7 @@
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="5.0999999999999996" customHeight="1">
@@ -65648,7 +66177,7 @@
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.22727272727272727</v>
+        <v>0.21739130434782608</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1">
@@ -65669,7 +66198,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>6.8181818181818177E-2</v>
+        <v>6.5217391304347824E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1">
@@ -65690,7 +66219,7 @@
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>0.11363636363636363</v>
+        <v>0.10869565217391304</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1">
@@ -65711,7 +66240,7 @@
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>2.2727272727272728E-2</v>
+        <v>2.1739130434782608E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1">
@@ -65732,7 +66261,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>4.5454545454545456E-2</v>
+        <v>4.3478260869565216E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1">
@@ -65753,7 +66282,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.18181818181818182</v>
+        <v>0.17391304347826086</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1">
@@ -65774,7 +66303,7 @@
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>9.0909090909090912E-2</v>
+        <v>8.6956521739130432E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1">
@@ -65795,7 +66324,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.3478260869565216E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1">
@@ -65816,7 +66345,7 @@
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.15909090909090909</v>
+        <v>0.15217391304347827</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1">
@@ -65858,7 +66387,7 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>4.5454545454545456E-2</v>
+        <v>4.3478260869565216E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1">
@@ -65871,15 +66400,15 @@
       </c>
       <c r="C44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,"")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44" s="149">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" s="150">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.3478260869565216E-2</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1">
@@ -65892,15 +66421,15 @@
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>
-        <v>0.99999999999999989</v>
+        <v>0.99999999999999978</v>
       </c>
     </row>
   </sheetData>
@@ -66503,7 +67032,7 @@
       </c>
       <c r="F5" s="101">
         <f>IF($A5="","",COUNTIFS('GECC 2026'!F$2:F$200,$A5))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G5" s="101">
         <f>IF($A5="","",COUNTIFS('GECC 2026'!G$2:G$200,$A5))</f>
@@ -66657,7 +67186,7 @@
       </c>
       <c r="F11" s="101">
         <f>IF($A11="","",COUNTIFS('GECC 2026'!F$2:F$200,$A11))</f>
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -66732,7 +67261,7 @@
       </c>
       <c r="F14" s="101">
         <f>IF($A14="","",COUNTIFS('GECC 2026'!F$2:F$200,$A14))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -66857,7 +67386,7 @@
       </c>
       <c r="F19" s="101">
         <f>IF($A19="","",COUNTIFS('GECC 2026'!F$2:F$200,$A19))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -67282,7 +67811,7 @@
       </c>
       <c r="F36" s="101">
         <f>IF($A36="","",COUNTIFS('GECC 2026'!F$2:F$200,$A36))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -68776,7 +69305,7 @@
       </c>
       <c r="F105" s="243">
         <f>SUM(F5:F100)</f>
-        <v>86</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5087" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF4060DF-6094-4982-A36A-516437CABBDD}"/>
+  <xr:revisionPtr revIDLastSave="5091" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98526D00-D820-4042-8B34-6A457CD8E96D}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6585" uniqueCount="2978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6589" uniqueCount="2978">
   <si>
     <t>ID</t>
   </si>
@@ -13033,7 +13033,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -58258,7 +58258,9 @@
       <c r="E706" s="210" t="s">
         <v>2836</v>
       </c>
-      <c r="F706" s="220"/>
+      <c r="F706" s="220" t="s">
+        <v>81</v>
+      </c>
       <c r="G706" s="217"/>
       <c r="H706" s="221"/>
       <c r="I706" s="222"/>
@@ -58298,7 +58300,9 @@
       <c r="E707" s="210" t="s">
         <v>2836</v>
       </c>
-      <c r="F707" s="211"/>
+      <c r="F707" s="211" t="s">
+        <v>81</v>
+      </c>
       <c r="G707" s="208"/>
       <c r="H707" s="212"/>
       <c r="I707" s="213"/>
@@ -58331,12 +58335,16 @@
       <c r="B708" s="218">
         <v>2026</v>
       </c>
-      <c r="C708" s="218"/>
+      <c r="C708" s="218" t="s">
+        <v>2765</v>
+      </c>
       <c r="D708" s="218"/>
       <c r="E708" s="210" t="s">
         <v>2836</v>
       </c>
-      <c r="F708" s="220"/>
+      <c r="F708" s="220" t="s">
+        <v>81</v>
+      </c>
       <c r="G708" s="217"/>
       <c r="H708" s="221"/>
       <c r="I708" s="222"/>
@@ -62806,8 +62814,8 @@
       <c r="M44" t="str">
         <v>2026-052</v>
       </c>
-      <c r="N44">
-        <v>0</v>
+      <c r="N44" t="str">
+        <v>A realizar</v>
       </c>
       <c r="O44" t="str">
         <v>TCendo o Futuro</v>
@@ -64981,8 +64989,8 @@
       <c r="B98" t="str">
         <v>2026-052</v>
       </c>
-      <c r="C98">
-        <v>0</v>
+      <c r="C98" t="str">
+        <v>A realizar</v>
       </c>
       <c r="D98" t="str">
         <v>TCendo o Futuro</v>
@@ -65019,8 +65027,8 @@
       <c r="B99" t="str">
         <v>2026-052</v>
       </c>
-      <c r="C99">
-        <v>0</v>
+      <c r="C99" t="str">
+        <v>A realizar</v>
       </c>
       <c r="D99" t="str">
         <v>TCendo o Futuro</v>
@@ -65057,8 +65065,8 @@
       <c r="B100" t="str">
         <v>2026-052</v>
       </c>
-      <c r="C100">
-        <v>0</v>
+      <c r="C100" t="str">
+        <v>A realizar</v>
       </c>
       <c r="D100" t="str">
         <v>TCendo o Futuro</v>
@@ -65095,8 +65103,8 @@
       <c r="B101" t="str">
         <v>2026-052</v>
       </c>
-      <c r="C101">
-        <v>0</v>
+      <c r="C101" t="str">
+        <v>A realizar</v>
       </c>
       <c r="D101" t="str">
         <v>TCendo o Futuro</v>
@@ -65133,8 +65141,8 @@
       <c r="B102" t="str">
         <v>2026-052</v>
       </c>
-      <c r="C102">
-        <v>0</v>
+      <c r="C102" t="str">
+        <v>A realizar</v>
       </c>
       <c r="D102" t="str">
         <v>TCendo o Futuro</v>
@@ -66020,7 +66028,7 @@
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="5.0999999999999996" customHeight="1">
@@ -66177,7 +66185,7 @@
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.21739130434782608</v>
+        <v>0.21276595744680851</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1">
@@ -66198,7 +66206,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>6.5217391304347824E-2</v>
+        <v>6.3829787234042548E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1">
@@ -66219,7 +66227,7 @@
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>0.10869565217391304</v>
+        <v>0.10638297872340426</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1">
@@ -66240,7 +66248,7 @@
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>2.1739130434782608E-2</v>
+        <v>2.1276595744680851E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1">
@@ -66261,7 +66269,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>4.3478260869565216E-2</v>
+        <v>4.2553191489361701E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1">
@@ -66282,7 +66290,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.17391304347826086</v>
+        <v>0.1702127659574468</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1">
@@ -66303,7 +66311,7 @@
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>8.6956521739130432E-2</v>
+        <v>8.5106382978723402E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1">
@@ -66324,7 +66332,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>4.3478260869565216E-2</v>
+        <v>4.2553191489361701E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1">
@@ -66345,7 +66353,7 @@
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.15217391304347827</v>
+        <v>0.14893617021276595</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1">
@@ -66387,7 +66395,7 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>4.3478260869565216E-2</v>
+        <v>4.2553191489361701E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1">
@@ -66400,15 +66408,15 @@
       </c>
       <c r="C44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" s="149">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" s="150">
         <f t="shared" si="1"/>
-        <v>4.3478260869565216E-2</v>
+        <v>6.3829787234042548E-2</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1">
@@ -66421,15 +66429,15 @@
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>
-        <v>0.99999999999999978</v>
+        <v>0.99999999999999989</v>
       </c>
     </row>
   </sheetData>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5091" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98526D00-D820-4042-8B34-6A457CD8E96D}"/>
+  <xr:revisionPtr revIDLastSave="5096" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B623952A-3216-448F-9254-2ADE8992BEBD}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6589" uniqueCount="2978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6593" uniqueCount="2979">
   <si>
     <t>ID</t>
   </si>
@@ -8681,6 +8681,9 @@
   </si>
   <si>
     <t>20/08/2026 e 21/08/2026</t>
+  </si>
+  <si>
+    <t>17/09/2026 e 18/09/2026</t>
   </si>
   <si>
     <t>ID Ação</t>
@@ -9884,7 +9887,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="293">
+  <cellXfs count="294">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10693,6 +10696,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="33" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -13015,7 +13021,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
@@ -13033,7 +13039,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -58261,9 +58267,15 @@
       <c r="F706" s="220" t="s">
         <v>81</v>
       </c>
-      <c r="G706" s="217"/>
-      <c r="H706" s="221"/>
-      <c r="I706" s="222"/>
+      <c r="G706" s="269" t="s">
+        <v>2727</v>
+      </c>
+      <c r="H706" s="290" t="s">
+        <v>2838</v>
+      </c>
+      <c r="I706" s="222">
+        <v>46282</v>
+      </c>
       <c r="J706" s="222"/>
       <c r="K706" s="218" t="s">
         <v>35</v>
@@ -58303,7 +58315,9 @@
       <c r="F707" s="211" t="s">
         <v>81</v>
       </c>
-      <c r="G707" s="208"/>
+      <c r="G707" s="260" t="s">
+        <v>2727</v>
+      </c>
       <c r="H707" s="212"/>
       <c r="I707" s="213"/>
       <c r="J707" s="213"/>
@@ -58345,7 +58359,9 @@
       <c r="F708" s="220" t="s">
         <v>81</v>
       </c>
-      <c r="G708" s="217"/>
+      <c r="G708" s="269" t="s">
+        <v>2727</v>
+      </c>
       <c r="H708" s="221"/>
       <c r="I708" s="222"/>
       <c r="J708" s="222"/>
@@ -59653,50 +59669,50 @@
         <v>1</v>
       </c>
       <c r="B1" s="96" t="s">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="C1" s="96" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="D1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="F1" s="96" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="96" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="H1" s="96" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="I1" s="96" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="J1" s="96" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="L1" s="129" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="M1" s="100">
         <v>2026</v>
       </c>
       <c r="U1" s="162" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="V1" s="161"/>
       <c r="X1" s="159" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="Y1" s="107"/>
       <c r="Z1" s="107"/>
       <c r="AA1" s="107"/>
       <c r="AC1" s="253" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="2" spans="1:31">
@@ -59732,25 +59748,25 @@
         <v>10.4</v>
       </c>
       <c r="X2" s="160" t="s">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="Y2" s="160" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="160" t="s">
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="AA2" s="160" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
       <c r="AC2" s="254" t="s">
         <v>1</v>
       </c>
       <c r="AD2" s="254" t="s">
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="AE2" s="254" t="s">
-        <v>2852</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -59785,34 +59801,34 @@
         <v>5.2</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>2855</v>
+        <v>2856</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>2857</v>
+        <v>2858</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>2858</v>
+        <v>2859</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>2860</v>
+        <v>2861</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>2861</v>
+        <v>2862</v>
       </c>
       <c r="X3" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="Y3" t="s">
         <v>2697</v>
@@ -59896,7 +59912,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="Y4" t="s">
         <v>2697</v>
@@ -59976,7 +59992,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="Y5" t="s">
         <v>2713</v>
@@ -59991,7 +60007,7 @@
         <v>2026</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="AE5" s="249">
         <v>16</v>
@@ -60056,10 +60072,10 @@
         <v>6</v>
       </c>
       <c r="X6" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="Y6" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -60071,7 +60087,7 @@
         <v>2026</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="AE6" s="249">
         <v>16</v>
@@ -60136,7 +60152,7 @@
         <v>8</v>
       </c>
       <c r="X7" s="98" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="Y7" t="s">
         <v>2697</v>
@@ -60216,7 +60232,7 @@
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="Y8" s="95" t="s">
         <v>1343</v>
@@ -60289,7 +60305,7 @@
         <v>11</v>
       </c>
       <c r="X9" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="Y9" s="95" t="s">
         <v>1023</v>
@@ -60362,7 +60378,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="Y10" s="95" t="s">
         <v>1367</v>
@@ -60435,10 +60451,10 @@
         <v>14</v>
       </c>
       <c r="X11" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="Y11" s="95" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="AA11">
         <v>1.2</v>
@@ -60508,10 +60524,10 @@
         <v>15</v>
       </c>
       <c r="X12" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="AA12">
         <v>1.2</v>
@@ -60581,7 +60597,7 @@
         <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>1343</v>
@@ -60654,7 +60670,7 @@
         <v>18</v>
       </c>
       <c r="X14" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y14" s="95" t="s">
         <v>1023</v>
@@ -60727,7 +60743,7 @@
         <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y15" s="95" t="s">
         <v>1367</v>
@@ -60800,10 +60816,10 @@
         <v>22</v>
       </c>
       <c r="X16" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y16" s="95" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="AA16">
         <v>1.2</v>
@@ -60873,10 +60889,10 @@
         <v>23</v>
       </c>
       <c r="X17" t="s">
+        <v>2873</v>
+      </c>
+      <c r="Y17" s="95" t="s">
         <v>2872</v>
-      </c>
-      <c r="Y17" s="95" t="s">
-        <v>2871</v>
       </c>
       <c r="AA17">
         <v>1.2</v>
@@ -60946,7 +60962,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y18" s="95" t="s">
         <v>1343</v>
@@ -61019,7 +61035,7 @@
         <v>33</v>
       </c>
       <c r="X19" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y19" s="95" t="s">
         <v>1023</v>
@@ -61092,7 +61108,7 @@
         <v>34</v>
       </c>
       <c r="X20" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y20" s="95" t="s">
         <v>1367</v>
@@ -61165,10 +61181,10 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y21" s="95" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="AA21">
         <v>1.2</v>
@@ -61238,10 +61254,10 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y22" s="95" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="AA22">
         <v>1.2</v>
@@ -61311,7 +61327,7 @@
         <v>39</v>
       </c>
       <c r="X23" s="98" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y23" s="95" t="s">
         <v>2713</v>
@@ -61384,10 +61400,10 @@
         <v>41</v>
       </c>
       <c r="X24" s="98" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y24" s="95" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -61457,7 +61473,7 @@
         <v>43</v>
       </c>
       <c r="X25" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y25" s="95" t="s">
         <v>855</v>
@@ -61530,10 +61546,10 @@
         <v>45</v>
       </c>
       <c r="X26" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y26" s="95" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -61606,7 +61622,7 @@
         <v>47</v>
       </c>
       <c r="X27" s="256" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="Y27" s="95" t="s">
         <v>2713</v>
@@ -61679,10 +61695,10 @@
         <v>49</v>
       </c>
       <c r="X28" s="256" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -61752,7 +61768,7 @@
         <v>50</v>
       </c>
       <c r="X29" s="256" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y29" s="95" t="s">
         <v>2713</v>
@@ -61825,10 +61841,10 @@
         <v>51</v>
       </c>
       <c r="X30" s="256" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y30" s="95" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -61898,7 +61914,7 @@
         <v>56</v>
       </c>
       <c r="X31" s="256" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Y31" s="95" t="s">
         <v>472</v>
@@ -61974,7 +61990,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="256" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="Y32" t="s">
         <v>1343</v>
@@ -62050,10 +62066,10 @@
         <v>59</v>
       </c>
       <c r="X33" s="256" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="Y33" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="Z33">
         <v>4</v>
@@ -62063,7 +62079,7 @@
       </c>
       <c r="AC33" s="250"/>
       <c r="AD33" s="251" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="AE33" s="252">
         <f>SUM(AE3:AE32)</f>
@@ -62129,10 +62145,10 @@
         <v>60</v>
       </c>
       <c r="X34" s="256" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="Y34" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -62200,7 +62216,7 @@
         <v>62</v>
       </c>
       <c r="X35" s="256" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="Y35" t="s">
         <v>108</v>
@@ -62271,7 +62287,7 @@
         <v>63</v>
       </c>
       <c r="X36" s="256" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="Y36" t="s">
         <v>549</v>
@@ -62342,7 +62358,7 @@
         <v>64</v>
       </c>
       <c r="X37" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="Y37" t="s">
         <v>418</v>
@@ -62413,7 +62429,7 @@
         <v>74</v>
       </c>
       <c r="X38" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="Y38" s="259" t="s">
         <v>1096</v>
@@ -62484,7 +62500,7 @@
         <v>77</v>
       </c>
       <c r="X39" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="Y39" t="s">
         <v>549</v>
@@ -62555,7 +62571,7 @@
         <v>79</v>
       </c>
       <c r="X40" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="Y40" t="s">
         <v>472</v>
@@ -62626,7 +62642,7 @@
         <v>81</v>
       </c>
       <c r="X41" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="Y41" t="s">
         <v>1472</v>
@@ -62697,10 +62713,10 @@
         <v>86</v>
       </c>
       <c r="X42" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="Y42" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -62768,7 +62784,7 @@
         <v>91</v>
       </c>
       <c r="X43" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y43" s="95" t="s">
         <v>2713</v>
@@ -62836,10 +62852,10 @@
         <v>96</v>
       </c>
       <c r="X44" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y44" s="95" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="AA44">
         <v>0</v>
@@ -62886,10 +62902,10 @@
         <v>101</v>
       </c>
       <c r="X45" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y45" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Z45">
         <v>1</v>
@@ -62936,10 +62952,10 @@
         <v/>
       </c>
       <c r="X46" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y46" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Z46">
         <v>1</v>
@@ -62986,10 +63002,10 @@
         <v/>
       </c>
       <c r="X47" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y47" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Z47">
         <v>1</v>
@@ -63036,10 +63052,10 @@
         <v/>
       </c>
       <c r="X48" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y48" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="Z48">
         <v>1</v>
@@ -63086,10 +63102,10 @@
         <v/>
       </c>
       <c r="X49" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y49" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -63136,7 +63152,7 @@
         <v/>
       </c>
       <c r="X50" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y50" t="s">
         <v>935</v>
@@ -63186,10 +63202,10 @@
         <v/>
       </c>
       <c r="X51" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y51" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="Z51">
         <v>1</v>
@@ -63236,7 +63252,7 @@
         <v/>
       </c>
       <c r="X52" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y52" t="s">
         <v>1343</v>
@@ -63286,10 +63302,10 @@
         <v/>
       </c>
       <c r="X53" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y53" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Z53">
         <v>1</v>
@@ -63336,10 +63352,10 @@
         <v/>
       </c>
       <c r="X54" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y54" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -65979,7 +65995,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1">
       <c r="A1" s="278" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="B1" s="278"/>
       <c r="C1" s="278"/>
@@ -66000,15 +66016,15 @@
     <row r="3" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1">
       <c r="A4" s="279" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="B4" s="280"/>
       <c r="D4" s="281" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="E4" s="282"/>
       <c r="G4" s="125" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1">
@@ -66017,14 +66033,14 @@
         <v>52</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
         <v>32</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
@@ -66042,32 +66058,32 @@
     </row>
     <row r="8" spans="1:7" ht="17.25">
       <c r="A8" s="277" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="B8" s="277"/>
       <c r="D8" s="277" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="E8" s="277"/>
     </row>
     <row r="9" spans="1:7" ht="5.0999999999999996" customHeight="1">
-      <c r="A9" s="290"/>
-      <c r="B9" s="290"/>
-      <c r="D9" s="290"/>
-      <c r="E9" s="290"/>
+      <c r="A9" s="291"/>
+      <c r="B9" s="291"/>
+      <c r="D9" s="291"/>
+      <c r="E9" s="291"/>
     </row>
     <row r="10" spans="1:7" ht="24.95" customHeight="1">
       <c r="A10" s="108" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="108" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="D10" s="108" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="E10" s="108" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.95" customHeight="1">
@@ -66079,7 +66095,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="109" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66095,7 +66111,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66111,7 +66127,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="109" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66120,14 +66136,14 @@
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1">
       <c r="A14" s="113" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
         <v>32</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
@@ -66136,7 +66152,7 @@
     </row>
     <row r="30" spans="1:5" ht="17.25">
       <c r="A30" s="277" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="B30" s="277"/>
       <c r="C30" s="277"/>
@@ -66144,27 +66160,27 @@
       <c r="E30" s="277"/>
     </row>
     <row r="31" spans="1:5" ht="5.0999999999999996" customHeight="1">
-      <c r="A31" s="290"/>
-      <c r="B31" s="290"/>
-      <c r="C31" s="290"/>
-      <c r="D31" s="290"/>
-      <c r="E31" s="290"/>
+      <c r="A31" s="291"/>
+      <c r="B31" s="291"/>
+      <c r="C31" s="291"/>
+      <c r="D31" s="291"/>
+      <c r="E31" s="291"/>
     </row>
     <row r="32" spans="1:5" ht="24.95" customHeight="1">
       <c r="A32" s="108" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="108" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="C32" s="108" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="D32" s="108" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1">
@@ -66282,15 +66298,15 @@
       </c>
       <c r="C38" s="128">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A38)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D38" s="119">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.1702127659574468</v>
+        <v>0.23404255319148937</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1">
@@ -66358,7 +66374,7 @@
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1">
       <c r="A42" s="156" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B42" s="153">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A42)</f>
@@ -66400,7 +66416,7 @@
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1">
       <c r="A44" s="148" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="B44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,"")</f>
@@ -66408,20 +66424,20 @@
       </c>
       <c r="C44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,"")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D44" s="149">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E44" s="150">
         <f t="shared" si="1"/>
-        <v>6.3829787234042548E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1">
       <c r="A45" s="113" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
@@ -66472,163 +66488,163 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1729</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>457</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>199</v>
@@ -66637,15 +66653,15 @@
         <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>364</v>
@@ -66654,7 +66670,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
     </row>
   </sheetData>
@@ -66676,16 +66692,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1">
@@ -66696,7 +66712,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>2765</v>
@@ -66710,7 +66726,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>2664</v>
@@ -66761,180 +66777,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>2690</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>2711</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>2695</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>199</v>
@@ -66943,15 +66959,15 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>364</v>
@@ -66960,7 +66976,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
     </row>
   </sheetData>
@@ -66978,43 +66994,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
-      <c r="A1" s="291" t="s">
-        <v>2964</v>
-      </c>
-      <c r="B1" s="291"/>
-      <c r="C1" s="291"/>
-      <c r="D1" s="291"/>
-      <c r="E1" s="291"/>
-      <c r="F1" s="291"/>
+      <c r="A1" s="292" t="s">
+        <v>2965</v>
+      </c>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
+      <c r="F1" s="292"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="292" t="s">
-        <v>2965</v>
-      </c>
-      <c r="B2" s="292"/>
-      <c r="C2" s="292"/>
-      <c r="D2" s="292"/>
-      <c r="E2" s="292"/>
-      <c r="F2" s="292"/>
+      <c r="A2" s="293" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B2" s="293"/>
+      <c r="C2" s="293"/>
+      <c r="D2" s="293"/>
+      <c r="E2" s="293"/>
+      <c r="F2" s="293"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="102" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="E4" s="102" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="F4" s="102" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -69293,7 +69309,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="241" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="B105" s="242">
         <f>SUM(B5:B100)</f>
@@ -69344,7 +69360,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1">
       <c r="A1" s="283" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="B1" s="283"/>
       <c r="C1" s="283"/>
@@ -69356,20 +69372,20 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="130" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1">
       <c r="A4" s="284" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="B4" s="285"/>
       <c r="D4" s="284" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="E4" s="285"/>
       <c r="G4" s="284" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="H4" s="285"/>
     </row>
@@ -69393,28 +69409,28 @@
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1">
       <c r="A7" s="143" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="C7" s="143" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="143" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="E7" s="143" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="F7" s="143" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="G7" s="143" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="143" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5096" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B623952A-3216-448F-9254-2ADE8992BEBD}"/>
+  <xr:revisionPtr revIDLastSave="5099" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F4A6E8C-ACD3-4988-AC77-47EEBF57BE37}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6593" uniqueCount="2979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6594" uniqueCount="2980">
   <si>
     <t>ID</t>
   </si>
@@ -8684,6 +8684,9 @@
   </si>
   <si>
     <t>17/09/2026 e 18/09/2026</t>
+  </si>
+  <si>
+    <t>24/09/2026 e 25/09/2026</t>
   </si>
   <si>
     <t>ID Ação</t>
@@ -58276,7 +58279,9 @@
       <c r="I706" s="222">
         <v>46282</v>
       </c>
-      <c r="J706" s="222"/>
+      <c r="J706" s="222">
+        <v>46283</v>
+      </c>
       <c r="K706" s="218" t="s">
         <v>35</v>
       </c>
@@ -58318,8 +58323,12 @@
       <c r="G707" s="260" t="s">
         <v>2727</v>
       </c>
-      <c r="H707" s="212"/>
-      <c r="I707" s="213"/>
+      <c r="H707" s="289" t="s">
+        <v>2839</v>
+      </c>
+      <c r="I707" s="213">
+        <v>46289</v>
+      </c>
       <c r="J707" s="213"/>
       <c r="K707" s="209" t="s">
         <v>35</v>
@@ -59669,50 +59678,50 @@
         <v>1</v>
       </c>
       <c r="B1" s="96" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="C1" s="96" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="D1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="F1" s="96" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="96" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="H1" s="96" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="I1" s="96" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="J1" s="96" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="L1" s="129" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="M1" s="100">
         <v>2026</v>
       </c>
       <c r="U1" s="162" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="V1" s="161"/>
       <c r="X1" s="159" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="Y1" s="107"/>
       <c r="Z1" s="107"/>
       <c r="AA1" s="107"/>
       <c r="AC1" s="253" t="s">
-        <v>2849</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="2" spans="1:31">
@@ -59748,25 +59757,25 @@
         <v>10.4</v>
       </c>
       <c r="X2" s="160" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="Y2" s="160" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="160" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
       <c r="AA2" s="160" t="s">
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="AC2" s="254" t="s">
         <v>1</v>
       </c>
       <c r="AD2" s="254" t="s">
-        <v>2852</v>
+        <v>2853</v>
       </c>
       <c r="AE2" s="254" t="s">
-        <v>2853</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -59801,34 +59810,34 @@
         <v>5.2</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>2855</v>
+        <v>2856</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>2857</v>
+        <v>2858</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>2858</v>
+        <v>2859</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>2860</v>
+        <v>2861</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>2861</v>
+        <v>2862</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="X3" t="s">
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="Y3" t="s">
         <v>2697</v>
@@ -59912,7 +59921,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="Y4" t="s">
         <v>2697</v>
@@ -59992,7 +60001,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="Y5" t="s">
         <v>2713</v>
@@ -60007,7 +60016,7 @@
         <v>2026</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="AE5" s="249">
         <v>16</v>
@@ -60072,10 +60081,10 @@
         <v>6</v>
       </c>
       <c r="X6" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="Y6" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -60087,7 +60096,7 @@
         <v>2026</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="AE6" s="249">
         <v>16</v>
@@ -60152,7 +60161,7 @@
         <v>8</v>
       </c>
       <c r="X7" s="98" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="Y7" t="s">
         <v>2697</v>
@@ -60232,7 +60241,7 @@
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="Y8" s="95" t="s">
         <v>1343</v>
@@ -60305,7 +60314,7 @@
         <v>11</v>
       </c>
       <c r="X9" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="Y9" s="95" t="s">
         <v>1023</v>
@@ -60378,7 +60387,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="Y10" s="95" t="s">
         <v>1367</v>
@@ -60451,10 +60460,10 @@
         <v>14</v>
       </c>
       <c r="X11" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="Y11" s="95" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="AA11">
         <v>1.2</v>
@@ -60524,10 +60533,10 @@
         <v>15</v>
       </c>
       <c r="X12" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="AA12">
         <v>1.2</v>
@@ -60597,7 +60606,7 @@
         <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>1343</v>
@@ -60670,7 +60679,7 @@
         <v>18</v>
       </c>
       <c r="X14" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y14" s="95" t="s">
         <v>1023</v>
@@ -60743,7 +60752,7 @@
         <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y15" s="95" t="s">
         <v>1367</v>
@@ -60816,10 +60825,10 @@
         <v>22</v>
       </c>
       <c r="X16" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="Y16" s="95" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="AA16">
         <v>1.2</v>
@@ -60889,10 +60898,10 @@
         <v>23</v>
       </c>
       <c r="X17" t="s">
+        <v>2874</v>
+      </c>
+      <c r="Y17" s="95" t="s">
         <v>2873</v>
-      </c>
-      <c r="Y17" s="95" t="s">
-        <v>2872</v>
       </c>
       <c r="AA17">
         <v>1.2</v>
@@ -60962,7 +60971,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y18" s="95" t="s">
         <v>1343</v>
@@ -61035,7 +61044,7 @@
         <v>33</v>
       </c>
       <c r="X19" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y19" s="95" t="s">
         <v>1023</v>
@@ -61108,7 +61117,7 @@
         <v>34</v>
       </c>
       <c r="X20" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y20" s="95" t="s">
         <v>1367</v>
@@ -61181,10 +61190,10 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y21" s="95" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="AA21">
         <v>1.2</v>
@@ -61254,10 +61263,10 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y22" s="95" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="AA22">
         <v>1.2</v>
@@ -61327,7 +61336,7 @@
         <v>39</v>
       </c>
       <c r="X23" s="98" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y23" s="95" t="s">
         <v>2713</v>
@@ -61400,10 +61409,10 @@
         <v>41</v>
       </c>
       <c r="X24" s="98" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y24" s="95" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -61473,7 +61482,7 @@
         <v>43</v>
       </c>
       <c r="X25" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y25" s="95" t="s">
         <v>855</v>
@@ -61546,10 +61555,10 @@
         <v>45</v>
       </c>
       <c r="X26" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y26" s="95" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -61622,7 +61631,7 @@
         <v>47</v>
       </c>
       <c r="X27" s="256" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y27" s="95" t="s">
         <v>2713</v>
@@ -61695,10 +61704,10 @@
         <v>49</v>
       </c>
       <c r="X28" s="256" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -61768,7 +61777,7 @@
         <v>50</v>
       </c>
       <c r="X29" s="256" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Y29" s="95" t="s">
         <v>2713</v>
@@ -61841,10 +61850,10 @@
         <v>51</v>
       </c>
       <c r="X30" s="256" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Y30" s="95" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -61914,7 +61923,7 @@
         <v>56</v>
       </c>
       <c r="X31" s="256" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="Y31" s="95" t="s">
         <v>472</v>
@@ -61990,7 +61999,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="256" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="Y32" t="s">
         <v>1343</v>
@@ -62066,10 +62075,10 @@
         <v>59</v>
       </c>
       <c r="X33" s="256" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="Y33" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="Z33">
         <v>4</v>
@@ -62079,7 +62088,7 @@
       </c>
       <c r="AC33" s="250"/>
       <c r="AD33" s="251" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="AE33" s="252">
         <f>SUM(AE3:AE32)</f>
@@ -62145,10 +62154,10 @@
         <v>60</v>
       </c>
       <c r="X34" s="256" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="Y34" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -62216,7 +62225,7 @@
         <v>62</v>
       </c>
       <c r="X35" s="256" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="Y35" t="s">
         <v>108</v>
@@ -62287,7 +62296,7 @@
         <v>63</v>
       </c>
       <c r="X36" s="256" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="Y36" t="s">
         <v>549</v>
@@ -62358,7 +62367,7 @@
         <v>64</v>
       </c>
       <c r="X37" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="Y37" t="s">
         <v>418</v>
@@ -62429,7 +62438,7 @@
         <v>74</v>
       </c>
       <c r="X38" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="Y38" s="259" t="s">
         <v>1096</v>
@@ -62500,7 +62509,7 @@
         <v>77</v>
       </c>
       <c r="X39" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="Y39" t="s">
         <v>549</v>
@@ -62571,7 +62580,7 @@
         <v>79</v>
       </c>
       <c r="X40" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="Y40" t="s">
         <v>472</v>
@@ -62642,7 +62651,7 @@
         <v>81</v>
       </c>
       <c r="X41" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y41" t="s">
         <v>1472</v>
@@ -62713,10 +62722,10 @@
         <v>86</v>
       </c>
       <c r="X42" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y42" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -62784,7 +62793,7 @@
         <v>91</v>
       </c>
       <c r="X43" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y43" s="95" t="s">
         <v>2713</v>
@@ -62852,10 +62861,10 @@
         <v>96</v>
       </c>
       <c r="X44" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y44" s="95" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="AA44">
         <v>0</v>
@@ -62902,10 +62911,10 @@
         <v>101</v>
       </c>
       <c r="X45" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y45" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Z45">
         <v>1</v>
@@ -62952,10 +62961,10 @@
         <v/>
       </c>
       <c r="X46" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y46" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Z46">
         <v>1</v>
@@ -63002,10 +63011,10 @@
         <v/>
       </c>
       <c r="X47" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y47" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="Z47">
         <v>1</v>
@@ -63052,10 +63061,10 @@
         <v/>
       </c>
       <c r="X48" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y48" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="Z48">
         <v>1</v>
@@ -63102,10 +63111,10 @@
         <v/>
       </c>
       <c r="X49" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y49" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -63152,7 +63161,7 @@
         <v/>
       </c>
       <c r="X50" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y50" t="s">
         <v>935</v>
@@ -63202,10 +63211,10 @@
         <v/>
       </c>
       <c r="X51" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y51" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Z51">
         <v>1</v>
@@ -63252,7 +63261,7 @@
         <v/>
       </c>
       <c r="X52" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y52" t="s">
         <v>1343</v>
@@ -63302,10 +63311,10 @@
         <v/>
       </c>
       <c r="X53" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y53" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="Z53">
         <v>1</v>
@@ -63352,10 +63361,10 @@
         <v/>
       </c>
       <c r="X54" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y54" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -65995,7 +66004,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1">
       <c r="A1" s="278" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="B1" s="278"/>
       <c r="C1" s="278"/>
@@ -66016,15 +66025,15 @@
     <row r="3" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1">
       <c r="A4" s="279" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="B4" s="280"/>
       <c r="D4" s="281" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="E4" s="282"/>
       <c r="G4" s="125" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1">
@@ -66033,14 +66042,14 @@
         <v>52</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
         <v>32</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
@@ -66058,11 +66067,11 @@
     </row>
     <row r="8" spans="1:7" ht="17.25">
       <c r="A8" s="277" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="B8" s="277"/>
       <c r="D8" s="277" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="E8" s="277"/>
     </row>
@@ -66077,13 +66086,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="108" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="D10" s="108" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="E10" s="108" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.95" customHeight="1">
@@ -66095,7 +66104,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="109" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66111,7 +66120,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66127,7 +66136,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="109" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66136,14 +66145,14 @@
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1">
       <c r="A14" s="113" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
         <v>32</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
@@ -66152,7 +66161,7 @@
     </row>
     <row r="30" spans="1:5" ht="17.25">
       <c r="A30" s="277" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="B30" s="277"/>
       <c r="C30" s="277"/>
@@ -66171,16 +66180,16 @@
         <v>6</v>
       </c>
       <c r="B32" s="108" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="C32" s="108" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="D32" s="108" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1">
@@ -66374,7 +66383,7 @@
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1">
       <c r="A42" s="156" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="B42" s="153">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A42)</f>
@@ -66416,7 +66425,7 @@
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1">
       <c r="A44" s="148" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="B44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,"")</f>
@@ -66437,7 +66446,7 @@
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1">
       <c r="A45" s="113" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
@@ -66488,163 +66497,163 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1729</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>457</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>199</v>
@@ -66653,15 +66662,15 @@
         <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>364</v>
@@ -66670,7 +66679,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
     </row>
   </sheetData>
@@ -66692,16 +66701,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1">
@@ -66712,7 +66721,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>2765</v>
@@ -66726,7 +66735,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>2664</v>
@@ -66777,180 +66786,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>2690</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>2711</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>2695</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>199</v>
@@ -66959,15 +66968,15 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>364</v>
@@ -66976,7 +66985,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
     </row>
   </sheetData>
@@ -66995,7 +67004,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
       <c r="A1" s="292" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
       <c r="B1" s="292"/>
       <c r="C1" s="292"/>
@@ -67005,7 +67014,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="293" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="B2" s="293"/>
       <c r="C2" s="293"/>
@@ -67018,19 +67027,19 @@
         <v>19</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
       <c r="E4" s="102" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="F4" s="102" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -69309,7 +69318,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="241" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="B105" s="242">
         <f>SUM(B5:B100)</f>
@@ -69360,7 +69369,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1">
       <c r="A1" s="283" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="B1" s="283"/>
       <c r="C1" s="283"/>
@@ -69372,20 +69381,20 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="130" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1">
       <c r="A4" s="284" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="B4" s="285"/>
       <c r="D4" s="284" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="E4" s="285"/>
       <c r="G4" s="284" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="H4" s="285"/>
     </row>
@@ -69409,28 +69418,28 @@
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1">
       <c r="A7" s="143" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="C7" s="143" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="143" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="E7" s="143" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="F7" s="143" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="G7" s="143" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="143" t="s">
-        <v>2978</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5099" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F4A6E8C-ACD3-4988-AC77-47EEBF57BE37}"/>
+  <xr:revisionPtr revIDLastSave="5103" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{573BC8D1-FAAE-466C-96A0-F399CC6DEE23}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6594" uniqueCount="2980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6595" uniqueCount="2981">
   <si>
     <t>ID</t>
   </si>
@@ -8687,6 +8687,9 @@
   </si>
   <si>
     <t>24/09/2026 e 25/09/2026</t>
+  </si>
+  <si>
+    <t>08/10/2026 e 09/10/2026</t>
   </si>
   <si>
     <t>ID Ação</t>
@@ -58329,7 +58332,9 @@
       <c r="I707" s="213">
         <v>46289</v>
       </c>
-      <c r="J707" s="213"/>
+      <c r="J707" s="213">
+        <v>46290</v>
+      </c>
       <c r="K707" s="209" t="s">
         <v>35</v>
       </c>
@@ -58371,8 +58376,12 @@
       <c r="G708" s="269" t="s">
         <v>2727</v>
       </c>
-      <c r="H708" s="221"/>
-      <c r="I708" s="222"/>
+      <c r="H708" s="290" t="s">
+        <v>2840</v>
+      </c>
+      <c r="I708" s="222">
+        <v>46303</v>
+      </c>
       <c r="J708" s="222"/>
       <c r="K708" s="218" t="s">
         <v>35</v>
@@ -59678,50 +59687,50 @@
         <v>1</v>
       </c>
       <c r="B1" s="96" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="C1" s="96" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="D1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="F1" s="96" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="96" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="H1" s="96" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="I1" s="96" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="J1" s="96" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="L1" s="129" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="M1" s="100">
         <v>2026</v>
       </c>
       <c r="U1" s="162" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="V1" s="161"/>
       <c r="X1" s="159" t="s">
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="Y1" s="107"/>
       <c r="Z1" s="107"/>
       <c r="AA1" s="107"/>
       <c r="AC1" s="253" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="2" spans="1:31">
@@ -59757,25 +59766,25 @@
         <v>10.4</v>
       </c>
       <c r="X2" s="160" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="Y2" s="160" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="160" t="s">
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="AA2" s="160" t="s">
-        <v>2852</v>
+        <v>2853</v>
       </c>
       <c r="AC2" s="254" t="s">
         <v>1</v>
       </c>
       <c r="AD2" s="254" t="s">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="AE2" s="254" t="s">
-        <v>2854</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -59810,34 +59819,34 @@
         <v>5.2</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>2855</v>
+        <v>2856</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>2857</v>
+        <v>2858</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>2858</v>
+        <v>2859</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>2860</v>
+        <v>2861</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>2861</v>
+        <v>2862</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="X3" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="Y3" t="s">
         <v>2697</v>
@@ -59921,7 +59930,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="Y4" t="s">
         <v>2697</v>
@@ -60001,7 +60010,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="Y5" t="s">
         <v>2713</v>
@@ -60016,7 +60025,7 @@
         <v>2026</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="AE5" s="249">
         <v>16</v>
@@ -60081,10 +60090,10 @@
         <v>6</v>
       </c>
       <c r="X6" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="Y6" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -60096,7 +60105,7 @@
         <v>2026</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="AE6" s="249">
         <v>16</v>
@@ -60161,7 +60170,7 @@
         <v>8</v>
       </c>
       <c r="X7" s="98" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="Y7" t="s">
         <v>2697</v>
@@ -60241,7 +60250,7 @@
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y8" s="95" t="s">
         <v>1343</v>
@@ -60314,7 +60323,7 @@
         <v>11</v>
       </c>
       <c r="X9" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y9" s="95" t="s">
         <v>1023</v>
@@ -60387,7 +60396,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y10" s="95" t="s">
         <v>1367</v>
@@ -60460,10 +60469,10 @@
         <v>14</v>
       </c>
       <c r="X11" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y11" s="95" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="AA11">
         <v>1.2</v>
@@ -60533,10 +60542,10 @@
         <v>15</v>
       </c>
       <c r="X12" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="AA12">
         <v>1.2</v>
@@ -60606,7 +60615,7 @@
         <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>1343</v>
@@ -60679,7 +60688,7 @@
         <v>18</v>
       </c>
       <c r="X14" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y14" s="95" t="s">
         <v>1023</v>
@@ -60752,7 +60761,7 @@
         <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y15" s="95" t="s">
         <v>1367</v>
@@ -60825,10 +60834,10 @@
         <v>22</v>
       </c>
       <c r="X16" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="Y16" s="95" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="AA16">
         <v>1.2</v>
@@ -60898,10 +60907,10 @@
         <v>23</v>
       </c>
       <c r="X17" t="s">
+        <v>2875</v>
+      </c>
+      <c r="Y17" s="95" t="s">
         <v>2874</v>
-      </c>
-      <c r="Y17" s="95" t="s">
-        <v>2873</v>
       </c>
       <c r="AA17">
         <v>1.2</v>
@@ -60971,7 +60980,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y18" s="95" t="s">
         <v>1343</v>
@@ -61044,7 +61053,7 @@
         <v>33</v>
       </c>
       <c r="X19" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y19" s="95" t="s">
         <v>1023</v>
@@ -61117,7 +61126,7 @@
         <v>34</v>
       </c>
       <c r="X20" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y20" s="95" t="s">
         <v>1367</v>
@@ -61190,10 +61199,10 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y21" s="95" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="AA21">
         <v>1.2</v>
@@ -61263,10 +61272,10 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y22" s="95" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="AA22">
         <v>1.2</v>
@@ -61336,7 +61345,7 @@
         <v>39</v>
       </c>
       <c r="X23" s="98" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y23" s="95" t="s">
         <v>2713</v>
@@ -61409,10 +61418,10 @@
         <v>41</v>
       </c>
       <c r="X24" s="98" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y24" s="95" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -61482,7 +61491,7 @@
         <v>43</v>
       </c>
       <c r="X25" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="Y25" s="95" t="s">
         <v>855</v>
@@ -61555,10 +61564,10 @@
         <v>45</v>
       </c>
       <c r="X26" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="Y26" s="95" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -61631,7 +61640,7 @@
         <v>47</v>
       </c>
       <c r="X27" s="256" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Y27" s="95" t="s">
         <v>2713</v>
@@ -61704,10 +61713,10 @@
         <v>49</v>
       </c>
       <c r="X28" s="256" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -61777,7 +61786,7 @@
         <v>50</v>
       </c>
       <c r="X29" s="256" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="Y29" s="95" t="s">
         <v>2713</v>
@@ -61850,10 +61859,10 @@
         <v>51</v>
       </c>
       <c r="X30" s="256" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="Y30" s="95" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -61923,7 +61932,7 @@
         <v>56</v>
       </c>
       <c r="X31" s="256" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="Y31" s="95" t="s">
         <v>472</v>
@@ -61999,7 +62008,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="256" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="Y32" t="s">
         <v>1343</v>
@@ -62075,10 +62084,10 @@
         <v>59</v>
       </c>
       <c r="X33" s="256" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="Y33" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="Z33">
         <v>4</v>
@@ -62088,7 +62097,7 @@
       </c>
       <c r="AC33" s="250"/>
       <c r="AD33" s="251" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="AE33" s="252">
         <f>SUM(AE3:AE32)</f>
@@ -62154,10 +62163,10 @@
         <v>60</v>
       </c>
       <c r="X34" s="256" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="Y34" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -62225,7 +62234,7 @@
         <v>62</v>
       </c>
       <c r="X35" s="256" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="Y35" t="s">
         <v>108</v>
@@ -62296,7 +62305,7 @@
         <v>63</v>
       </c>
       <c r="X36" s="256" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="Y36" t="s">
         <v>549</v>
@@ -62367,7 +62376,7 @@
         <v>64</v>
       </c>
       <c r="X37" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="Y37" t="s">
         <v>418</v>
@@ -62438,7 +62447,7 @@
         <v>74</v>
       </c>
       <c r="X38" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="Y38" s="259" t="s">
         <v>1096</v>
@@ -62509,7 +62518,7 @@
         <v>77</v>
       </c>
       <c r="X39" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="Y39" t="s">
         <v>549</v>
@@ -62580,7 +62589,7 @@
         <v>79</v>
       </c>
       <c r="X40" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y40" t="s">
         <v>472</v>
@@ -62651,7 +62660,7 @@
         <v>81</v>
       </c>
       <c r="X41" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y41" t="s">
         <v>1472</v>
@@ -62722,10 +62731,10 @@
         <v>86</v>
       </c>
       <c r="X42" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y42" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -62793,7 +62802,7 @@
         <v>91</v>
       </c>
       <c r="X43" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y43" s="95" t="s">
         <v>2713</v>
@@ -62861,10 +62870,10 @@
         <v>96</v>
       </c>
       <c r="X44" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Y44" s="95" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="AA44">
         <v>0</v>
@@ -62911,10 +62920,10 @@
         <v>101</v>
       </c>
       <c r="X45" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y45" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Z45">
         <v>1</v>
@@ -62961,10 +62970,10 @@
         <v/>
       </c>
       <c r="X46" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y46" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="Z46">
         <v>1</v>
@@ -63011,10 +63020,10 @@
         <v/>
       </c>
       <c r="X47" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y47" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="Z47">
         <v>1</v>
@@ -63061,10 +63070,10 @@
         <v/>
       </c>
       <c r="X48" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y48" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="Z48">
         <v>1</v>
@@ -63111,10 +63120,10 @@
         <v/>
       </c>
       <c r="X49" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y49" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -63161,7 +63170,7 @@
         <v/>
       </c>
       <c r="X50" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y50" t="s">
         <v>935</v>
@@ -63211,10 +63220,10 @@
         <v/>
       </c>
       <c r="X51" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y51" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="Z51">
         <v>1</v>
@@ -63261,7 +63270,7 @@
         <v/>
       </c>
       <c r="X52" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y52" t="s">
         <v>1343</v>
@@ -63311,10 +63320,10 @@
         <v/>
       </c>
       <c r="X53" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y53" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="Z53">
         <v>1</v>
@@ -63361,10 +63370,10 @@
         <v/>
       </c>
       <c r="X54" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y54" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -66004,7 +66013,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1">
       <c r="A1" s="278" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="B1" s="278"/>
       <c r="C1" s="278"/>
@@ -66025,15 +66034,15 @@
     <row r="3" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1">
       <c r="A4" s="279" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="B4" s="280"/>
       <c r="D4" s="281" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="E4" s="282"/>
       <c r="G4" s="125" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1">
@@ -66042,14 +66051,14 @@
         <v>52</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
         <v>32</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
@@ -66067,11 +66076,11 @@
     </row>
     <row r="8" spans="1:7" ht="17.25">
       <c r="A8" s="277" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="B8" s="277"/>
       <c r="D8" s="277" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="E8" s="277"/>
     </row>
@@ -66086,13 +66095,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="108" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="D10" s="108" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="E10" s="108" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.95" customHeight="1">
@@ -66104,7 +66113,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="109" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66120,7 +66129,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66136,7 +66145,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="109" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66145,14 +66154,14 @@
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1">
       <c r="A14" s="113" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
         <v>32</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
@@ -66161,7 +66170,7 @@
     </row>
     <row r="30" spans="1:5" ht="17.25">
       <c r="A30" s="277" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="B30" s="277"/>
       <c r="C30" s="277"/>
@@ -66180,16 +66189,16 @@
         <v>6</v>
       </c>
       <c r="B32" s="108" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="C32" s="108" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="D32" s="108" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1">
@@ -66383,7 +66392,7 @@
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1">
       <c r="A42" s="156" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="B42" s="153">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A42)</f>
@@ -66425,7 +66434,7 @@
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1">
       <c r="A44" s="148" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="B44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,"")</f>
@@ -66446,7 +66455,7 @@
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1">
       <c r="A45" s="113" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
@@ -66497,163 +66506,163 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1729</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>457</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>199</v>
@@ -66662,15 +66671,15 @@
         <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>364</v>
@@ -66679,7 +66688,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
     </row>
   </sheetData>
@@ -66701,16 +66710,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1">
@@ -66721,7 +66730,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>2765</v>
@@ -66735,7 +66744,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>2664</v>
@@ -66786,180 +66795,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>2690</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>2711</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>2695</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>199</v>
@@ -66968,15 +66977,15 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>364</v>
@@ -66985,7 +66994,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
     </row>
   </sheetData>
@@ -67004,7 +67013,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
       <c r="A1" s="292" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="B1" s="292"/>
       <c r="C1" s="292"/>
@@ -67014,7 +67023,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="293" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
       <c r="B2" s="293"/>
       <c r="C2" s="293"/>
@@ -67027,19 +67036,19 @@
         <v>19</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="E4" s="102" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="F4" s="102" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -69318,7 +69327,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="241" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="B105" s="242">
         <f>SUM(B5:B100)</f>
@@ -69369,7 +69378,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1">
       <c r="A1" s="283" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="B1" s="283"/>
       <c r="C1" s="283"/>
@@ -69381,20 +69390,20 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="130" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1">
       <c r="A4" s="284" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="B4" s="285"/>
       <c r="D4" s="284" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="E4" s="285"/>
       <c r="G4" s="284" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="H4" s="285"/>
     </row>
@@ -69418,28 +69427,28 @@
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1">
       <c r="A7" s="143" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="C7" s="143" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="143" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="E7" s="143" t="s">
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="F7" s="143" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="G7" s="143" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="143" t="s">
-        <v>2979</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5103" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{573BC8D1-FAAE-466C-96A0-F399CC6DEE23}"/>
+  <xr:revisionPtr revIDLastSave="5104" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12DDB975-2324-46D4-91D1-E6A6FC4CDCB1}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58382,7 +58382,9 @@
       <c r="I708" s="222">
         <v>46303</v>
       </c>
-      <c r="J708" s="222"/>
+      <c r="J708" s="222">
+        <v>46304</v>
+      </c>
       <c r="K708" s="218" t="s">
         <v>35</v>
       </c>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5104" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12DDB975-2324-46D4-91D1-E6A6FC4CDCB1}"/>
+  <xr:revisionPtr revIDLastSave="5109" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE1321DD-781B-48F5-B301-A055146C4BE2}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6595" uniqueCount="2981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="2982">
   <si>
     <t>ID</t>
   </si>
@@ -8681,6 +8681,9 @@
   </si>
   <si>
     <t>20/08/2026 e 21/08/2026</t>
+  </si>
+  <si>
+    <t>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco; Luiz Felipe Tenório de Lima Gondim</t>
   </si>
   <si>
     <t>17/09/2026 e 18/09/2026</t>
@@ -58216,7 +58219,9 @@
       <c r="C705" s="218" t="s">
         <v>2765</v>
       </c>
-      <c r="D705" s="209"/>
+      <c r="D705" s="209" t="s">
+        <v>2739</v>
+      </c>
       <c r="E705" s="210" t="s">
         <v>2836</v>
       </c>
@@ -58252,7 +58257,7 @@
       </c>
       <c r="S705" s="209"/>
       <c r="T705" s="43" t="s">
-        <v>2741</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="706" spans="1:20" ht="23.25" customHeight="1">
@@ -58277,7 +58282,7 @@
         <v>2727</v>
       </c>
       <c r="H706" s="290" t="s">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="I706" s="222">
         <v>46282</v>
@@ -58302,7 +58307,7 @@
       </c>
       <c r="S706" s="218"/>
       <c r="T706" s="43" t="s">
-        <v>2741</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="707" spans="1:20" ht="23.25" customHeight="1">
@@ -58327,7 +58332,7 @@
         <v>2727</v>
       </c>
       <c r="H707" s="289" t="s">
-        <v>2839</v>
+        <v>2840</v>
       </c>
       <c r="I707" s="213">
         <v>46289</v>
@@ -58352,7 +58357,7 @@
       </c>
       <c r="S707" s="209"/>
       <c r="T707" s="43" t="s">
-        <v>2741</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="708" spans="1:20" ht="23.25" customHeight="1">
@@ -58377,7 +58382,7 @@
         <v>2727</v>
       </c>
       <c r="H708" s="290" t="s">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="I708" s="222">
         <v>46303</v>
@@ -58402,7 +58407,7 @@
       </c>
       <c r="S708" s="218"/>
       <c r="T708" s="43" t="s">
-        <v>2741</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="709" spans="1:20" ht="23.25" customHeight="1">
@@ -59689,55 +59694,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="96" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="C1" s="96" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="D1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="F1" s="96" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="96" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="H1" s="96" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="I1" s="96" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="J1" s="96" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="L1" s="129" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="M1" s="100">
         <v>2026</v>
       </c>
       <c r="U1" s="162" t="s">
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="V1" s="161"/>
       <c r="X1" s="159" t="s">
-        <v>2850</v>
+        <v>2851</v>
       </c>
       <c r="Y1" s="107"/>
       <c r="Z1" s="107"/>
       <c r="AA1" s="107"/>
       <c r="AC1" s="253" t="s">
-        <v>2851</v>
+        <v>2852</v>
       </c>
     </row>
     <row r="2" spans="1:31">
       <c r="A2" s="98" cm="1">
-        <f t="array" ref="A2:J102">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
+        <f t="array" ref="A2:J106">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
         <v>2026</v>
       </c>
       <c r="B2" s="98" t="str">
@@ -59768,25 +59773,25 @@
         <v>10.4</v>
       </c>
       <c r="X2" s="160" t="s">
-        <v>2841</v>
+        <v>2842</v>
       </c>
       <c r="Y2" s="160" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="160" t="s">
-        <v>2852</v>
+        <v>2853</v>
       </c>
       <c r="AA2" s="160" t="s">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="AC2" s="254" t="s">
         <v>1</v>
       </c>
       <c r="AD2" s="254" t="s">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="AE2" s="254" t="s">
-        <v>2855</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -59821,34 +59826,34 @@
         <v>5.2</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>2857</v>
+        <v>2858</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>2858</v>
+        <v>2859</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>2860</v>
+        <v>2861</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>2861</v>
+        <v>2862</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="X3" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="Y3" t="s">
         <v>2697</v>
@@ -59932,7 +59937,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="Y4" t="s">
         <v>2697</v>
@@ -60012,7 +60017,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="Y5" t="s">
         <v>2713</v>
@@ -60027,7 +60032,7 @@
         <v>2026</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="AE5" s="249">
         <v>16</v>
@@ -60092,10 +60097,10 @@
         <v>6</v>
       </c>
       <c r="X6" t="s">
-        <v>2867</v>
+        <v>2868</v>
       </c>
       <c r="Y6" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -60107,7 +60112,7 @@
         <v>2026</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="AE6" s="249">
         <v>16</v>
@@ -60172,7 +60177,7 @@
         <v>8</v>
       </c>
       <c r="X7" s="98" t="s">
-        <v>2871</v>
+        <v>2872</v>
       </c>
       <c r="Y7" t="s">
         <v>2697</v>
@@ -60252,7 +60257,7 @@
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y8" s="95" t="s">
         <v>1343</v>
@@ -60325,7 +60330,7 @@
         <v>11</v>
       </c>
       <c r="X9" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y9" s="95" t="s">
         <v>1023</v>
@@ -60398,7 +60403,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y10" s="95" t="s">
         <v>1367</v>
@@ -60471,10 +60476,10 @@
         <v>14</v>
       </c>
       <c r="X11" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y11" s="95" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="AA11">
         <v>1.2</v>
@@ -60544,10 +60549,10 @@
         <v>15</v>
       </c>
       <c r="X12" t="s">
-        <v>2872</v>
+        <v>2873</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="AA12">
         <v>1.2</v>
@@ -60617,7 +60622,7 @@
         <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>1343</v>
@@ -60690,7 +60695,7 @@
         <v>18</v>
       </c>
       <c r="X14" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y14" s="95" t="s">
         <v>1023</v>
@@ -60763,7 +60768,7 @@
         <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y15" s="95" t="s">
         <v>1367</v>
@@ -60836,10 +60841,10 @@
         <v>22</v>
       </c>
       <c r="X16" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="Y16" s="95" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="AA16">
         <v>1.2</v>
@@ -60909,10 +60914,10 @@
         <v>23</v>
       </c>
       <c r="X17" t="s">
+        <v>2876</v>
+      </c>
+      <c r="Y17" s="95" t="s">
         <v>2875</v>
-      </c>
-      <c r="Y17" s="95" t="s">
-        <v>2874</v>
       </c>
       <c r="AA17">
         <v>1.2</v>
@@ -60982,7 +60987,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y18" s="95" t="s">
         <v>1343</v>
@@ -61055,7 +61060,7 @@
         <v>33</v>
       </c>
       <c r="X19" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y19" s="95" t="s">
         <v>1023</v>
@@ -61128,7 +61133,7 @@
         <v>34</v>
       </c>
       <c r="X20" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y20" s="95" t="s">
         <v>1367</v>
@@ -61201,10 +61206,10 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y21" s="95" t="s">
-        <v>2873</v>
+        <v>2874</v>
       </c>
       <c r="AA21">
         <v>1.2</v>
@@ -61274,10 +61279,10 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="Y22" s="95" t="s">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="AA22">
         <v>1.2</v>
@@ -61347,7 +61352,7 @@
         <v>39</v>
       </c>
       <c r="X23" s="98" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="Y23" s="95" t="s">
         <v>2713</v>
@@ -61420,10 +61425,10 @@
         <v>41</v>
       </c>
       <c r="X24" s="98" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="Y24" s="95" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -61493,7 +61498,7 @@
         <v>43</v>
       </c>
       <c r="X25" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y25" s="95" t="s">
         <v>855</v>
@@ -61566,10 +61571,10 @@
         <v>45</v>
       </c>
       <c r="X26" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="Y26" s="95" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -61642,7 +61647,7 @@
         <v>47</v>
       </c>
       <c r="X27" s="256" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="Y27" s="95" t="s">
         <v>2713</v>
@@ -61715,10 +61720,10 @@
         <v>49</v>
       </c>
       <c r="X28" s="256" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -61788,7 +61793,7 @@
         <v>50</v>
       </c>
       <c r="X29" s="256" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="Y29" s="95" t="s">
         <v>2713</v>
@@ -61861,10 +61866,10 @@
         <v>51</v>
       </c>
       <c r="X30" s="256" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="Y30" s="95" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -61934,7 +61939,7 @@
         <v>56</v>
       </c>
       <c r="X31" s="256" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="Y31" s="95" t="s">
         <v>472</v>
@@ -62010,7 +62015,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="256" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="Y32" t="s">
         <v>1343</v>
@@ -62086,10 +62091,10 @@
         <v>59</v>
       </c>
       <c r="X33" s="256" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="Y33" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="Z33">
         <v>4</v>
@@ -62099,7 +62104,7 @@
       </c>
       <c r="AC33" s="250"/>
       <c r="AD33" s="251" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="AE33" s="252">
         <f>SUM(AE3:AE32)</f>
@@ -62165,10 +62170,10 @@
         <v>60</v>
       </c>
       <c r="X34" s="256" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="Y34" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -62236,7 +62241,7 @@
         <v>62</v>
       </c>
       <c r="X35" s="256" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="Y35" t="s">
         <v>108</v>
@@ -62307,7 +62312,7 @@
         <v>63</v>
       </c>
       <c r="X36" s="256" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="Y36" t="s">
         <v>549</v>
@@ -62378,7 +62383,7 @@
         <v>64</v>
       </c>
       <c r="X37" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="Y37" t="s">
         <v>418</v>
@@ -62449,7 +62454,7 @@
         <v>74</v>
       </c>
       <c r="X38" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="Y38" s="259" t="s">
         <v>1096</v>
@@ -62520,7 +62525,7 @@
         <v>77</v>
       </c>
       <c r="X39" t="s">
-        <v>2888</v>
+        <v>2889</v>
       </c>
       <c r="Y39" t="s">
         <v>549</v>
@@ -62591,7 +62596,7 @@
         <v>79</v>
       </c>
       <c r="X40" t="s">
-        <v>2889</v>
+        <v>2890</v>
       </c>
       <c r="Y40" t="s">
         <v>472</v>
@@ -62650,19 +62655,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="str">
-        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco</v>
+        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco; Luiz Felipe Tenório de Lima Gondim</v>
       </c>
       <c r="R41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S41">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T41">
         <v>81</v>
       </c>
       <c r="X41" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y41" t="s">
         <v>1472</v>
@@ -62721,22 +62726,22 @@
         <v>0</v>
       </c>
       <c r="Q42" t="str">
-        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco</v>
+        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco; Luiz Felipe Tenório de Lima Gondim</v>
       </c>
       <c r="R42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S42">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="T42">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="X42" t="s">
-        <v>2890</v>
+        <v>2891</v>
       </c>
       <c r="Y42" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -62792,19 +62797,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="str">
-        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco</v>
+        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco; Luiz Felipe Tenório de Lima Gondim</v>
       </c>
       <c r="R43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S43">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="T43">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="X43" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y43" s="95" t="s">
         <v>2713</v>
@@ -62860,22 +62865,22 @@
         <v>0</v>
       </c>
       <c r="Q44" t="str">
-        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco</v>
+        <v>Cinthia Thais de Carvalho Luz Thomazi; Adriana Cuoco Portugal; Fernanda Viana de Souza; Denise Duarte Guirra Kuhlmann;  Priscila Nolasco; Luiz Felipe Tenório de Lima Gondim</v>
       </c>
       <c r="R44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S44">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="T44">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="X44" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="Y44" s="95" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="AA44">
         <v>0</v>
@@ -62919,13 +62924,13 @@
         <v/>
       </c>
       <c r="T45">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="X45" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Y45" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="Z45">
         <v>1</v>
@@ -62972,10 +62977,10 @@
         <v/>
       </c>
       <c r="X46" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Y46" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="Z46">
         <v>1</v>
@@ -63022,10 +63027,10 @@
         <v/>
       </c>
       <c r="X47" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Y47" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="Z47">
         <v>1</v>
@@ -63072,10 +63077,10 @@
         <v/>
       </c>
       <c r="X48" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Y48" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Z48">
         <v>1</v>
@@ -63122,10 +63127,10 @@
         <v/>
       </c>
       <c r="X49" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Y49" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -63172,7 +63177,7 @@
         <v/>
       </c>
       <c r="X50" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Y50" t="s">
         <v>935</v>
@@ -63222,10 +63227,10 @@
         <v/>
       </c>
       <c r="X51" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Y51" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="Z51">
         <v>1</v>
@@ -63272,7 +63277,7 @@
         <v/>
       </c>
       <c r="X52" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Y52" t="s">
         <v>1343</v>
@@ -63322,10 +63327,10 @@
         <v/>
       </c>
       <c r="X53" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Y53" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="Z53">
         <v>1</v>
@@ -63372,10 +63377,10 @@
         <v/>
       </c>
       <c r="X54" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="Y54" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -64468,7 +64473,7 @@
         <v>Cinthia Thais de Carvalho Luz Thomazi</v>
       </c>
       <c r="G83">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H83">
         <v>0</v>
@@ -64506,7 +64511,7 @@
         <v>Adriana Cuoco Portugal</v>
       </c>
       <c r="G84">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -64544,7 +64549,7 @@
         <v>Fernanda Viana de Souza</v>
       </c>
       <c r="G85">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -64582,7 +64587,7 @@
         <v>Denise Duarte Guirra Kuhlmann</v>
       </c>
       <c r="G86">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -64620,7 +64625,7 @@
         <v>Priscila Nolasco</v>
       </c>
       <c r="G87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -64643,7 +64648,7 @@
         <v>2026</v>
       </c>
       <c r="B88" t="str">
-        <v>2026-050</v>
+        <v>2026-049</v>
       </c>
       <c r="C88" t="str">
         <v>A realizar</v>
@@ -64655,10 +64660,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="str">
-        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
+        <v>Luiz Felipe Tenório de Lima Gondim</v>
       </c>
       <c r="G88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -64693,10 +64698,10 @@
         <v>0</v>
       </c>
       <c r="F89" t="str">
-        <v>Adriana Cuoco Portugal</v>
+        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
       </c>
       <c r="G89">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -64731,10 +64736,10 @@
         <v>0</v>
       </c>
       <c r="F90" t="str">
-        <v>Fernanda Viana de Souza</v>
+        <v>Adriana Cuoco Portugal</v>
       </c>
       <c r="G90">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -64769,10 +64774,10 @@
         <v>0</v>
       </c>
       <c r="F91" t="str">
-        <v>Denise Duarte Guirra Kuhlmann</v>
+        <v>Fernanda Viana de Souza</v>
       </c>
       <c r="G91">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -64807,10 +64812,10 @@
         <v>0</v>
       </c>
       <c r="F92" t="str">
-        <v>Priscila Nolasco</v>
+        <v>Denise Duarte Guirra Kuhlmann</v>
       </c>
       <c r="G92">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -64833,7 +64838,7 @@
         <v>2026</v>
       </c>
       <c r="B93" t="str">
-        <v>2026-051</v>
+        <v>2026-050</v>
       </c>
       <c r="C93" t="str">
         <v>A realizar</v>
@@ -64845,10 +64850,10 @@
         <v>0</v>
       </c>
       <c r="F93" t="str">
-        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
+        <v>Priscila Nolasco</v>
       </c>
       <c r="G93">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -64871,7 +64876,7 @@
         <v>2026</v>
       </c>
       <c r="B94" t="str">
-        <v>2026-051</v>
+        <v>2026-050</v>
       </c>
       <c r="C94" t="str">
         <v>A realizar</v>
@@ -64883,10 +64888,10 @@
         <v>0</v>
       </c>
       <c r="F94" t="str">
-        <v>Adriana Cuoco Portugal</v>
+        <v>Luiz Felipe Tenório de Lima Gondim</v>
       </c>
       <c r="G94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -64921,10 +64926,10 @@
         <v>0</v>
       </c>
       <c r="F95" t="str">
-        <v>Fernanda Viana de Souza</v>
+        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
       </c>
       <c r="G95">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H95">
         <v>0</v>
@@ -64959,10 +64964,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="str">
-        <v>Denise Duarte Guirra Kuhlmann</v>
+        <v>Adriana Cuoco Portugal</v>
       </c>
       <c r="G96">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -64997,10 +65002,10 @@
         <v>0</v>
       </c>
       <c r="F97" t="str">
-        <v>Priscila Nolasco</v>
+        <v>Fernanda Viana de Souza</v>
       </c>
       <c r="G97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -65023,7 +65028,7 @@
         <v>2026</v>
       </c>
       <c r="B98" t="str">
-        <v>2026-052</v>
+        <v>2026-051</v>
       </c>
       <c r="C98" t="str">
         <v>A realizar</v>
@@ -65035,10 +65040,10 @@
         <v>0</v>
       </c>
       <c r="F98" t="str">
-        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
+        <v>Denise Duarte Guirra Kuhlmann</v>
       </c>
       <c r="G98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -65061,7 +65066,7 @@
         <v>2026</v>
       </c>
       <c r="B99" t="str">
-        <v>2026-052</v>
+        <v>2026-051</v>
       </c>
       <c r="C99" t="str">
         <v>A realizar</v>
@@ -65073,10 +65078,10 @@
         <v>0</v>
       </c>
       <c r="F99" t="str">
-        <v>Adriana Cuoco Portugal</v>
+        <v>Priscila Nolasco</v>
       </c>
       <c r="G99">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -65099,7 +65104,7 @@
         <v>2026</v>
       </c>
       <c r="B100" t="str">
-        <v>2026-052</v>
+        <v>2026-051</v>
       </c>
       <c r="C100" t="str">
         <v>A realizar</v>
@@ -65111,10 +65116,10 @@
         <v>0</v>
       </c>
       <c r="F100" t="str">
-        <v>Fernanda Viana de Souza</v>
+        <v>Luiz Felipe Tenório de Lima Gondim</v>
       </c>
       <c r="G100">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -65149,10 +65154,10 @@
         <v>0</v>
       </c>
       <c r="F101" t="str">
-        <v>Denise Duarte Guirra Kuhlmann</v>
+        <v>Cinthia Thais de Carvalho Luz Thomazi</v>
       </c>
       <c r="G101">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -65187,10 +65192,10 @@
         <v>0</v>
       </c>
       <c r="F102" t="str">
-        <v>Priscila Nolasco</v>
+        <v>Adriana Cuoco Portugal</v>
       </c>
       <c r="G102">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -65209,6 +65214,36 @@
       </c>
     </row>
     <row r="103" spans="1:19">
+      <c r="A103">
+        <v>2026</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2026-052</v>
+      </c>
+      <c r="C103" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D103" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Fernanda Viana de Souza</v>
+      </c>
+      <c r="G103">
+        <v>6</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
       <c r="R103" t="str">
         <v/>
       </c>
@@ -65217,6 +65252,36 @@
       </c>
     </row>
     <row r="104" spans="1:19">
+      <c r="A104">
+        <v>2026</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2026-052</v>
+      </c>
+      <c r="C104" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D104" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Denise Duarte Guirra Kuhlmann</v>
+      </c>
+      <c r="G104">
+        <v>6</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
       <c r="R104" t="str">
         <v/>
       </c>
@@ -65225,6 +65290,36 @@
       </c>
     </row>
     <row r="105" spans="1:19">
+      <c r="A105">
+        <v>2026</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2026-052</v>
+      </c>
+      <c r="C105" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D105" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Priscila Nolasco</v>
+      </c>
+      <c r="G105">
+        <v>6</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
       <c r="R105" t="str">
         <v/>
       </c>
@@ -65233,6 +65328,36 @@
       </c>
     </row>
     <row r="106" spans="1:19">
+      <c r="A106">
+        <v>2026</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2026-052</v>
+      </c>
+      <c r="C106" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D106" t="str">
+        <v>TCendo o Futuro</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Luiz Felipe Tenório de Lima Gondim</v>
+      </c>
+      <c r="G106">
+        <v>6</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
       <c r="R106" t="str">
         <v/>
       </c>
@@ -66015,7 +66140,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1">
       <c r="A1" s="278" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="B1" s="278"/>
       <c r="C1" s="278"/>
@@ -66036,15 +66161,15 @@
     <row r="3" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1">
       <c r="A4" s="279" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="B4" s="280"/>
       <c r="D4" s="281" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="E4" s="282"/>
       <c r="G4" s="125" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1">
@@ -66053,14 +66178,14 @@
         <v>52</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
         <v>32</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
@@ -66078,11 +66203,11 @@
     </row>
     <row r="8" spans="1:7" ht="17.25">
       <c r="A8" s="277" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="B8" s="277"/>
       <c r="D8" s="277" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="E8" s="277"/>
     </row>
@@ -66097,13 +66222,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="108" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="D10" s="108" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="E10" s="108" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.95" customHeight="1">
@@ -66115,7 +66240,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="109" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66131,7 +66256,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66147,7 +66272,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="109" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66156,14 +66281,14 @@
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1">
       <c r="A14" s="113" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
         <v>32</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
@@ -66172,7 +66297,7 @@
     </row>
     <row r="30" spans="1:5" ht="17.25">
       <c r="A30" s="277" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="B30" s="277"/>
       <c r="C30" s="277"/>
@@ -66191,16 +66316,16 @@
         <v>6</v>
       </c>
       <c r="B32" s="108" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="C32" s="108" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="D32" s="108" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1">
@@ -66394,7 +66519,7 @@
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1">
       <c r="A42" s="156" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="B42" s="153">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A42)</f>
@@ -66436,7 +66561,7 @@
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1">
       <c r="A44" s="148" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="B44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,"")</f>
@@ -66457,7 +66582,7 @@
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1">
       <c r="A45" s="113" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
@@ -66508,163 +66633,163 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1729</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>457</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>199</v>
@@ -66673,15 +66798,15 @@
         <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>364</v>
@@ -66690,7 +66815,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
     </row>
   </sheetData>
@@ -66712,16 +66837,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1">
@@ -66732,7 +66857,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>2765</v>
@@ -66746,7 +66871,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>2664</v>
@@ -66797,180 +66922,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>2690</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>2711</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>2695</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>199</v>
@@ -66979,15 +67104,15 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>364</v>
@@ -66996,7 +67121,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
     </row>
   </sheetData>
@@ -67015,7 +67140,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
       <c r="A1" s="292" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
       <c r="B1" s="292"/>
       <c r="C1" s="292"/>
@@ -67025,7 +67150,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="293" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="B2" s="293"/>
       <c r="C2" s="293"/>
@@ -67038,24 +67163,24 @@
         <v>19</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="E4" s="102" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="F4" s="102" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="str" cm="1">
-        <f t="array" ref="A5:A43">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32),_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32)&lt;&gt;""))),"")</f>
+        <f t="array" ref="A5:A44">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32),_xlfn.VSTACK('GECC 2026'!F2:F200,'GECC 2026'!AD3:AD32)&lt;&gt;""))),"")</f>
         <v>Adriana Cuoco Portugal</v>
       </c>
       <c r="B5" s="103">
@@ -67710,7 +67835,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="str">
-        <v>Marcelo Bálbio Moraes</v>
+        <v>Luiz Felipe Tenório de Lima Gondim</v>
       </c>
       <c r="B31" s="103">
         <f>IF($A31="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A31))</f>
@@ -67722,70 +67847,70 @@
       </c>
       <c r="D31" s="255">
         <f>IF($A31="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E31" s="240">
         <f>IF($A31="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A31)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A31))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F31" s="101">
         <f>IF($A31="","",COUNTIFS('GECC 2026'!F$2:F$200,$A31))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="str">
-        <v>Marcelo Santana</v>
+        <v>Marcelo Bálbio Moraes</v>
       </c>
       <c r="B32" s="103">
         <f>IF($A32="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" s="103">
         <f>IF($A32="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A32))</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D32" s="255">
         <f>IF($A32="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E32" s="240">
         <f>IF($A32="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A32)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A32))</f>
-        <v>1.3</v>
+        <v>16</v>
       </c>
       <c r="F32" s="101">
         <f>IF($A32="","",COUNTIFS('GECC 2026'!F$2:F$200,$A32))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="str">
-        <v>Mauri Siqueira Montessi</v>
+        <v>Marcelo Santana</v>
       </c>
       <c r="B33" s="103">
         <f>IF($A33="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A33))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" s="103">
         <f>IF($A33="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A33))</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D33" s="255">
         <f>IF($A33="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A33))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E33" s="240">
         <f>IF($A33="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A33)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A33))</f>
-        <v>16</v>
+        <v>1.3</v>
       </c>
       <c r="F33" s="101">
         <f>IF($A33="","",COUNTIFS('GECC 2026'!F$2:F$200,$A33))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="str">
-        <v>Michel Martins de Morais</v>
+        <v>Mauri Siqueira Montessi</v>
       </c>
       <c r="B34" s="103">
         <f>IF($A34="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A34))</f>
@@ -67810,40 +67935,40 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="str">
-        <v>Paulo José Góes Daltro</v>
+        <v>Michel Martins de Morais</v>
       </c>
       <c r="B35" s="103">
         <f>IF($A35="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A35))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C35" s="103">
         <f>IF($A35="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A35))</f>
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="D35" s="255">
         <f>IF($A35="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A35))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E35" s="240">
         <f>IF($A35="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A35)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A35))</f>
-        <v>20.8</v>
+        <v>16</v>
       </c>
       <c r="F35" s="101">
         <f>IF($A35="","",COUNTIFS('GECC 2026'!F$2:F$200,$A35))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="str">
-        <v>Priscila Nolasco</v>
+        <v>Paulo José Góes Daltro</v>
       </c>
       <c r="B36" s="103">
         <f>IF($A36="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A36))</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C36" s="103">
         <f>IF($A36="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A36))</f>
-        <v>2.6399999999999997</v>
+        <v>4.8</v>
       </c>
       <c r="D36" s="255">
         <f>IF($A36="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A36))</f>
@@ -67851,24 +67976,24 @@
       </c>
       <c r="E36" s="240">
         <f>IF($A36="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A36)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A36))</f>
-        <v>14.64</v>
+        <v>20.8</v>
       </c>
       <c r="F36" s="101">
         <f>IF($A36="","",COUNTIFS('GECC 2026'!F$2:F$200,$A36))</f>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="str">
-        <v>Reinaldo Alencar</v>
+        <v>Priscila Nolasco</v>
       </c>
       <c r="B37" s="103">
         <f>IF($A37="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A37))</f>
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C37" s="103">
         <f>IF($A37="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A37))</f>
-        <v>7.1999999999999993</v>
+        <v>2.6399999999999997</v>
       </c>
       <c r="D37" s="255">
         <f>IF($A37="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A37))</f>
@@ -67876,16 +68001,16 @@
       </c>
       <c r="E37" s="240">
         <f>IF($A37="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A37)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A37))</f>
-        <v>55.2</v>
+        <v>14.64</v>
       </c>
       <c r="F37" s="101">
         <f>IF($A37="","",COUNTIFS('GECC 2026'!F$2:F$200,$A37))</f>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="str">
-        <v>Rogério Ribeiro</v>
+        <v>Reinaldo Alencar</v>
       </c>
       <c r="B38" s="103">
         <f>IF($A38="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A38))</f>
@@ -67910,65 +68035,65 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="str">
-        <v>Rômulo Miranda Alvim</v>
+        <v>Rogério Ribeiro</v>
       </c>
       <c r="B39" s="103">
         <f>IF($A39="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A39))</f>
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C39" s="103">
         <f>IF($A39="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A39))</f>
-        <v>3.6</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="D39" s="255">
         <f>IF($A39="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A39))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E39" s="240">
         <f>IF($A39="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A39)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A39))</f>
-        <v>43.6</v>
+        <v>55.2</v>
       </c>
       <c r="F39" s="101">
         <f>IF($A39="","",COUNTIFS('GECC 2026'!F$2:F$200,$A39))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="str">
-        <v>Servidores, colaboradores e estagiários do TCDF</v>
+        <v>Rômulo Miranda Alvim</v>
       </c>
       <c r="B40" s="103">
         <f>IF($A40="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A40))</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C40" s="103">
         <f>IF($A40="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A40))</f>
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="D40" s="255">
         <f>IF($A40="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A40))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E40" s="240">
         <f>IF($A40="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A40)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A40))</f>
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="F40" s="101">
         <f>IF($A40="","",COUNTIFS('GECC 2026'!F$2:F$200,$A40))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="str">
-        <v>Silvia Lima Damasceno Carvalho</v>
+        <v>Servidores, colaboradores e estagiários do TCDF</v>
       </c>
       <c r="B41" s="103">
         <f>IF($A41="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A41))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="103">
         <f>IF($A41="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A41))</f>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D41" s="255">
         <f>IF($A41="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A41))</f>
@@ -67976,7 +68101,7 @@
       </c>
       <c r="E41" s="240">
         <f>IF($A41="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A41)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A41))</f>
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="F41" s="101">
         <f>IF($A41="","",COUNTIFS('GECC 2026'!F$2:F$200,$A41))</f>
@@ -67985,15 +68110,15 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="str">
-        <v>Tarsila Firmino Ely</v>
+        <v>Silvia Lima Damasceno Carvalho</v>
       </c>
       <c r="B42" s="103">
         <f>IF($A42="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A42))</f>
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C42" s="103">
         <f>IF($A42="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A42))</f>
-        <v>96.4</v>
+        <v>0.3</v>
       </c>
       <c r="D42" s="255">
         <f>IF($A42="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A42))</f>
@@ -68001,24 +68126,24 @@
       </c>
       <c r="E42" s="240">
         <f>IF($A42="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A42)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A42))</f>
-        <v>152.4</v>
+        <v>1.3</v>
       </c>
       <c r="F42" s="101">
         <f>IF($A42="","",COUNTIFS('GECC 2026'!F$2:F$200,$A42))</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="str">
-        <v>Túllio Herbeth Teixeira Moraes</v>
+        <v>Tarsila Firmino Ely</v>
       </c>
       <c r="B43" s="103">
         <f>IF($A43="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A43))</f>
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C43" s="103">
         <f>IF($A43="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A43))</f>
-        <v>0.44999999999999996</v>
+        <v>96.4</v>
       </c>
       <c r="D43" s="255">
         <f>IF($A43="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A43))</f>
@@ -68026,33 +68151,36 @@
       </c>
       <c r="E43" s="240">
         <f>IF($A43="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A43)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A43))</f>
-        <v>3.45</v>
+        <v>152.4</v>
       </c>
       <c r="F43" s="101">
         <f>IF($A43="","",COUNTIFS('GECC 2026'!F$2:F$200,$A43))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="str">
+        <v>Túllio Herbeth Teixeira Moraes</v>
+      </c>
+      <c r="B44" s="103">
+        <f>IF($A44="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A44))</f>
+        <v>3</v>
+      </c>
+      <c r="C44" s="103">
+        <f>IF($A44="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A44))</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="D44" s="255">
+        <f>IF($A44="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A44))</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="240">
+        <f>IF($A44="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A44)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A44))</f>
+        <v>3.45</v>
+      </c>
+      <c r="F44" s="101">
+        <f>IF($A44="","",COUNTIFS('GECC 2026'!F$2:F$200,$A44))</f>
         <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="B44" s="103" t="str">
-        <f>IF($A44="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A44))</f>
-        <v/>
-      </c>
-      <c r="C44" s="103" t="str">
-        <f>IF($A44="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A44))</f>
-        <v/>
-      </c>
-      <c r="D44" s="255" t="str">
-        <f>IF($A44="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A44))</f>
-        <v/>
-      </c>
-      <c r="E44" s="240" t="str">
-        <f>IF($A44="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A44)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A44))</f>
-        <v/>
-      </c>
-      <c r="F44" s="101" t="str">
-        <f>IF($A44="","",COUNTIFS('GECC 2026'!F$2:F$200,$A44))</f>
-        <v/>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -69329,7 +69457,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="241" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="B105" s="242">
         <f>SUM(B5:B100)</f>
@@ -69349,7 +69477,7 @@
       </c>
       <c r="F105" s="243">
         <f>SUM(F5:F100)</f>
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -69380,7 +69508,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1">
       <c r="A1" s="283" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="B1" s="283"/>
       <c r="C1" s="283"/>
@@ -69392,20 +69520,20 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="130" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1">
       <c r="A4" s="284" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="B4" s="285"/>
       <c r="D4" s="284" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="E4" s="285"/>
       <c r="G4" s="284" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="H4" s="285"/>
     </row>
@@ -69429,28 +69557,28 @@
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1">
       <c r="A7" s="143" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="C7" s="143" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="143" t="s">
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="E7" s="143" t="s">
-        <v>2979</v>
+        <v>2980</v>
       </c>
       <c r="F7" s="143" t="s">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="G7" s="143" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="143" t="s">
-        <v>2980</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5109" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE1321DD-781B-48F5-B301-A055146C4BE2}"/>
+  <xr:revisionPtr revIDLastSave="5112" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91A2938E-1001-46BD-A486-C757D44989EE}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="2982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6599" uniqueCount="2982">
   <si>
     <t>ID</t>
   </si>
@@ -58271,7 +58271,9 @@
       <c r="C706" s="218" t="s">
         <v>2765</v>
       </c>
-      <c r="D706" s="218"/>
+      <c r="D706" s="209" t="s">
+        <v>2739</v>
+      </c>
       <c r="E706" s="210" t="s">
         <v>2836</v>
       </c>
@@ -58321,7 +58323,9 @@
       <c r="C707" s="218" t="s">
         <v>2765</v>
       </c>
-      <c r="D707" s="209"/>
+      <c r="D707" s="209" t="s">
+        <v>2739</v>
+      </c>
       <c r="E707" s="210" t="s">
         <v>2836</v>
       </c>
@@ -58371,7 +58375,9 @@
       <c r="C708" s="218" t="s">
         <v>2765</v>
       </c>
-      <c r="D708" s="218"/>
+      <c r="D708" s="209" t="s">
+        <v>2739</v>
+      </c>
       <c r="E708" s="210" t="s">
         <v>2836</v>
       </c>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5112" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91A2938E-1001-46BD-A486-C757D44989EE}"/>
+  <xr:revisionPtr revIDLastSave="5113" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA8CC6E9-ED05-4112-ACD4-919B810F56A4}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10668,6 +10668,12 @@
     <xf numFmtId="167" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="33" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -10703,12 +10709,6 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12170,7 +12170,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="pt-PT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12447,7 +12447,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="pt-PT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12754,7 +12754,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
+  <c:lang val="pt-PT"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -58231,7 +58231,7 @@
       <c r="G705" s="260" t="s">
         <v>2727</v>
       </c>
-      <c r="H705" s="289" t="s">
+      <c r="H705" s="277" t="s">
         <v>2837</v>
       </c>
       <c r="I705" s="213">
@@ -58283,7 +58283,7 @@
       <c r="G706" s="269" t="s">
         <v>2727</v>
       </c>
-      <c r="H706" s="290" t="s">
+      <c r="H706" s="278" t="s">
         <v>2839</v>
       </c>
       <c r="I706" s="222">
@@ -58335,7 +58335,7 @@
       <c r="G707" s="260" t="s">
         <v>2727</v>
       </c>
-      <c r="H707" s="289" t="s">
+      <c r="H707" s="277" t="s">
         <v>2840</v>
       </c>
       <c r="I707" s="213">
@@ -58387,7 +58387,7 @@
       <c r="G708" s="269" t="s">
         <v>2727</v>
       </c>
-      <c r="H708" s="290" t="s">
+      <c r="H708" s="278" t="s">
         <v>2841</v>
       </c>
       <c r="I708" s="222">
@@ -58419,9 +58419,11 @@
     <row r="709" spans="1:20" ht="23.25" customHeight="1">
       <c r="A709" s="208" t="str">
         <f>IF(B709="","",B709&amp;"-"&amp;TEXT(COUNTIF(B$2:B709,B709),"000"))</f>
-        <v/>
-      </c>
-      <c r="B709" s="209"/>
+        <v>2026-053</v>
+      </c>
+      <c r="B709" s="209">
+        <v>2026</v>
+      </c>
       <c r="C709" s="218"/>
       <c r="D709" s="209"/>
       <c r="E709" s="210"/>
@@ -58437,9 +58439,9 @@
       <c r="O709" s="216"/>
       <c r="P709" s="216"/>
       <c r="Q709" s="216"/>
-      <c r="R709" s="216" t="str">
+      <c r="R709" s="216">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S709" s="209"/>
       <c r="T709" s="208"/>
@@ -66145,15 +66147,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1">
-      <c r="A1" s="278" t="s">
+      <c r="A1" s="280" t="s">
         <v>2903</v>
       </c>
-      <c r="B1" s="278"/>
-      <c r="C1" s="278"/>
-      <c r="D1" s="278"/>
-      <c r="E1" s="278"/>
-      <c r="F1" s="278"/>
-      <c r="G1" s="278"/>
+      <c r="B1" s="280"/>
+      <c r="C1" s="280"/>
+      <c r="D1" s="280"/>
+      <c r="E1" s="280"/>
+      <c r="F1" s="280"/>
+      <c r="G1" s="280"/>
     </row>
     <row r="2" spans="1:7" ht="9.9499999999999993" customHeight="1">
       <c r="A2" s="107"/>
@@ -66166,14 +66168,14 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1">
-      <c r="A4" s="279" t="s">
+      <c r="A4" s="281" t="s">
         <v>2904</v>
       </c>
-      <c r="B4" s="280"/>
-      <c r="D4" s="281" t="s">
+      <c r="B4" s="282"/>
+      <c r="D4" s="283" t="s">
         <v>2905</v>
       </c>
-      <c r="E4" s="282"/>
+      <c r="E4" s="284"/>
       <c r="G4" s="125" t="s">
         <v>2906</v>
       </c>
@@ -66181,7 +66183,7 @@
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1">
       <c r="A5" s="115">
         <f>COUNTIF('Ações InCompany'!B:B,2026)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="116" t="s">
         <v>2907</v>
@@ -66208,14 +66210,14 @@
       <c r="G6" s="107"/>
     </row>
     <row r="8" spans="1:7" ht="17.25">
-      <c r="A8" s="277" t="s">
+      <c r="A8" s="279" t="s">
         <v>2908</v>
       </c>
-      <c r="B8" s="277"/>
-      <c r="D8" s="277" t="s">
+      <c r="B8" s="279"/>
+      <c r="D8" s="279" t="s">
         <v>2909</v>
       </c>
-      <c r="E8" s="277"/>
+      <c r="E8" s="279"/>
     </row>
     <row r="9" spans="1:7" ht="5.0999999999999996" customHeight="1">
       <c r="A9" s="291"/>
@@ -66302,13 +66304,13 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="17.25">
-      <c r="A30" s="277" t="s">
+      <c r="A30" s="279" t="s">
         <v>2918</v>
       </c>
-      <c r="B30" s="277"/>
-      <c r="C30" s="277"/>
-      <c r="D30" s="277"/>
-      <c r="E30" s="277"/>
+      <c r="B30" s="279"/>
+      <c r="C30" s="279"/>
+      <c r="D30" s="279"/>
+      <c r="E30" s="279"/>
     </row>
     <row r="31" spans="1:5" ht="5.0999999999999996" customHeight="1">
       <c r="A31" s="291"/>
@@ -69513,16 +69515,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1">
-      <c r="A1" s="283" t="s">
+      <c r="A1" s="285" t="s">
         <v>2972</v>
       </c>
-      <c r="B1" s="283"/>
-      <c r="C1" s="283"/>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
+      <c r="B1" s="285"/>
+      <c r="C1" s="285"/>
+      <c r="D1" s="285"/>
+      <c r="E1" s="285"/>
+      <c r="F1" s="285"/>
+      <c r="G1" s="285"/>
+      <c r="H1" s="285"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="130" t="s">
@@ -69530,35 +69532,35 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1">
-      <c r="A4" s="284" t="s">
+      <c r="A4" s="286" t="s">
         <v>2974</v>
       </c>
-      <c r="B4" s="285"/>
-      <c r="D4" s="284" t="s">
+      <c r="B4" s="287"/>
+      <c r="D4" s="286" t="s">
         <v>2975</v>
       </c>
-      <c r="E4" s="285"/>
-      <c r="G4" s="284" t="s">
+      <c r="E4" s="287"/>
+      <c r="G4" s="286" t="s">
         <v>2976</v>
       </c>
-      <c r="H4" s="285"/>
+      <c r="H4" s="287"/>
     </row>
     <row r="5" spans="1:8" ht="35.1" customHeight="1">
-      <c r="A5" s="288">
+      <c r="A5" s="290">
         <f>COUNTIF('Ações InCompany'!E:E,"*maratona*")</f>
         <v>13</v>
       </c>
-      <c r="B5" s="287"/>
-      <c r="D5" s="286">
+      <c r="B5" s="289"/>
+      <c r="D5" s="288">
         <f>SUM(H8:H100)</f>
         <v>1566</v>
       </c>
-      <c r="E5" s="287"/>
-      <c r="G5" s="286">
+      <c r="E5" s="289"/>
+      <c r="G5" s="288">
         <f>IFERROR(ROUND(D5/A5,0),"-")</f>
         <v>120</v>
       </c>
-      <c r="H5" s="287"/>
+      <c r="H5" s="289"/>
     </row>
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1">
@@ -69958,15 +69960,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052D3A7BF04652843BCB50FE90745AA50" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ef6274641b2f7d621af528393bef14e5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe686eaa-0658-4f15-b230-9e46c4d089fd" xmlns:ns3="91ce1707-6d34-452b-b217-9734c03e6729" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fa87a3bcf42251a9fb9988d55372596" ns2:_="" ns3:_="">
     <xsd:import namespace="fe686eaa-0658-4f15-b230-9e46c4d089fd"/>
@@ -70167,14 +70160,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54B26992-BCD1-4DF2-A87D-5F3BC1837C0B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}"/>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5113" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA8CC6E9-ED05-4112-ACD4-919B810F56A4}"/>
+  <xr:revisionPtr revIDLastSave="5123" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D782514-8B43-4F72-8E84-FE568ADC4578}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6599" uniqueCount="2982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6606" uniqueCount="2984">
   <si>
     <t>ID</t>
   </si>
@@ -8693,6 +8693,12 @@
   </si>
   <si>
     <t>08/10/2026 e 09/10/2026</t>
+  </si>
+  <si>
+    <t>7377/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alura </t>
   </si>
   <si>
     <t>ID Ação</t>
@@ -13021,7 +13027,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -58424,24 +58430,44 @@
       <c r="B709" s="209">
         <v>2026</v>
       </c>
-      <c r="C709" s="218"/>
-      <c r="D709" s="209"/>
-      <c r="E709" s="210"/>
-      <c r="F709" s="211"/>
-      <c r="G709" s="208"/>
-      <c r="H709" s="212"/>
+      <c r="C709" s="218" t="s">
+        <v>2765</v>
+      </c>
+      <c r="D709" s="209" t="s">
+        <v>2842</v>
+      </c>
+      <c r="E709" s="210" t="s">
+        <v>2843</v>
+      </c>
+      <c r="F709" s="211" t="s">
+        <v>23</v>
+      </c>
+      <c r="G709" s="208" t="s">
+        <v>2711</v>
+      </c>
+      <c r="H709" s="212" t="s">
+        <v>2801</v>
+      </c>
       <c r="I709" s="213"/>
       <c r="J709" s="213"/>
-      <c r="K709" s="209"/>
-      <c r="L709" s="223"/>
+      <c r="K709" s="209" t="s">
+        <v>26</v>
+      </c>
+      <c r="L709" s="223">
+        <v>203112</v>
+      </c>
       <c r="M709" s="214"/>
-      <c r="N709" s="215"/>
-      <c r="O709" s="216"/>
+      <c r="N709" s="215">
+        <v>78</v>
+      </c>
+      <c r="O709" s="216">
+        <v>78</v>
+      </c>
       <c r="P709" s="216"/>
       <c r="Q709" s="216"/>
       <c r="R709" s="216">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="S709" s="209"/>
       <c r="T709" s="208"/>
@@ -59702,50 +59728,50 @@
         <v>1</v>
       </c>
       <c r="B1" s="96" t="s">
-        <v>2842</v>
+        <v>2844</v>
       </c>
       <c r="C1" s="96" t="s">
-        <v>2843</v>
+        <v>2845</v>
       </c>
       <c r="D1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>2844</v>
+        <v>2846</v>
       </c>
       <c r="F1" s="96" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="96" t="s">
-        <v>2845</v>
+        <v>2847</v>
       </c>
       <c r="H1" s="96" t="s">
-        <v>2846</v>
+        <v>2848</v>
       </c>
       <c r="I1" s="96" t="s">
-        <v>2847</v>
+        <v>2849</v>
       </c>
       <c r="J1" s="96" t="s">
-        <v>2848</v>
+        <v>2850</v>
       </c>
       <c r="L1" s="129" t="s">
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="M1" s="100">
         <v>2026</v>
       </c>
       <c r="U1" s="162" t="s">
-        <v>2850</v>
+        <v>2852</v>
       </c>
       <c r="V1" s="161"/>
       <c r="X1" s="159" t="s">
-        <v>2851</v>
+        <v>2853</v>
       </c>
       <c r="Y1" s="107"/>
       <c r="Z1" s="107"/>
       <c r="AA1" s="107"/>
       <c r="AC1" s="253" t="s">
-        <v>2852</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="2" spans="1:31">
@@ -59781,25 +59807,25 @@
         <v>10.4</v>
       </c>
       <c r="X2" s="160" t="s">
-        <v>2842</v>
+        <v>2844</v>
       </c>
       <c r="Y2" s="160" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="160" t="s">
-        <v>2853</v>
+        <v>2855</v>
       </c>
       <c r="AA2" s="160" t="s">
-        <v>2854</v>
+        <v>2856</v>
       </c>
       <c r="AC2" s="254" t="s">
         <v>1</v>
       </c>
       <c r="AD2" s="254" t="s">
-        <v>2855</v>
+        <v>2857</v>
       </c>
       <c r="AE2" s="254" t="s">
-        <v>2856</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -59834,34 +59860,34 @@
         <v>5.2</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>2857</v>
+        <v>2859</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>2858</v>
+        <v>2860</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>2859</v>
+        <v>2861</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>2860</v>
+        <v>2862</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>2861</v>
+        <v>2863</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>2862</v>
+        <v>2864</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>2863</v>
+        <v>2865</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>2864</v>
+        <v>2866</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>2865</v>
+        <v>2867</v>
       </c>
       <c r="X3" t="s">
-        <v>2866</v>
+        <v>2868</v>
       </c>
       <c r="Y3" t="s">
         <v>2697</v>
@@ -59945,7 +59971,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>2867</v>
+        <v>2869</v>
       </c>
       <c r="Y4" t="s">
         <v>2697</v>
@@ -60025,7 +60051,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>2868</v>
+        <v>2870</v>
       </c>
       <c r="Y5" t="s">
         <v>2713</v>
@@ -60040,7 +60066,7 @@
         <v>2026</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>2869</v>
+        <v>2871</v>
       </c>
       <c r="AE5" s="249">
         <v>16</v>
@@ -60105,10 +60131,10 @@
         <v>6</v>
       </c>
       <c r="X6" t="s">
-        <v>2868</v>
+        <v>2870</v>
       </c>
       <c r="Y6" t="s">
-        <v>2870</v>
+        <v>2872</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -60120,7 +60146,7 @@
         <v>2026</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>2871</v>
+        <v>2873</v>
       </c>
       <c r="AE6" s="249">
         <v>16</v>
@@ -60185,7 +60211,7 @@
         <v>8</v>
       </c>
       <c r="X7" s="98" t="s">
-        <v>2872</v>
+        <v>2874</v>
       </c>
       <c r="Y7" t="s">
         <v>2697</v>
@@ -60265,7 +60291,7 @@
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="Y8" s="95" t="s">
         <v>1343</v>
@@ -60338,7 +60364,7 @@
         <v>11</v>
       </c>
       <c r="X9" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="Y9" s="95" t="s">
         <v>1023</v>
@@ -60411,7 +60437,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="Y10" s="95" t="s">
         <v>1367</v>
@@ -60484,10 +60510,10 @@
         <v>14</v>
       </c>
       <c r="X11" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="Y11" s="95" t="s">
-        <v>2874</v>
+        <v>2876</v>
       </c>
       <c r="AA11">
         <v>1.2</v>
@@ -60557,10 +60583,10 @@
         <v>15</v>
       </c>
       <c r="X12" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>2875</v>
+        <v>2877</v>
       </c>
       <c r="AA12">
         <v>1.2</v>
@@ -60630,7 +60656,7 @@
         <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>1343</v>
@@ -60703,7 +60729,7 @@
         <v>18</v>
       </c>
       <c r="X14" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="Y14" s="95" t="s">
         <v>1023</v>
@@ -60776,7 +60802,7 @@
         <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="Y15" s="95" t="s">
         <v>1367</v>
@@ -60849,10 +60875,10 @@
         <v>22</v>
       </c>
       <c r="X16" t="s">
+        <v>2878</v>
+      </c>
+      <c r="Y16" s="95" t="s">
         <v>2876</v>
-      </c>
-      <c r="Y16" s="95" t="s">
-        <v>2874</v>
       </c>
       <c r="AA16">
         <v>1.2</v>
@@ -60922,10 +60948,10 @@
         <v>23</v>
       </c>
       <c r="X17" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="Y17" s="95" t="s">
-        <v>2875</v>
+        <v>2877</v>
       </c>
       <c r="AA17">
         <v>1.2</v>
@@ -60995,7 +61021,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>2877</v>
+        <v>2879</v>
       </c>
       <c r="Y18" s="95" t="s">
         <v>1343</v>
@@ -61068,7 +61094,7 @@
         <v>33</v>
       </c>
       <c r="X19" t="s">
-        <v>2877</v>
+        <v>2879</v>
       </c>
       <c r="Y19" s="95" t="s">
         <v>1023</v>
@@ -61141,7 +61167,7 @@
         <v>34</v>
       </c>
       <c r="X20" t="s">
-        <v>2877</v>
+        <v>2879</v>
       </c>
       <c r="Y20" s="95" t="s">
         <v>1367</v>
@@ -61214,10 +61240,10 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>2877</v>
+        <v>2879</v>
       </c>
       <c r="Y21" s="95" t="s">
-        <v>2874</v>
+        <v>2876</v>
       </c>
       <c r="AA21">
         <v>1.2</v>
@@ -61287,10 +61313,10 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
+        <v>2879</v>
+      </c>
+      <c r="Y22" s="95" t="s">
         <v>2877</v>
-      </c>
-      <c r="Y22" s="95" t="s">
-        <v>2875</v>
       </c>
       <c r="AA22">
         <v>1.2</v>
@@ -61360,7 +61386,7 @@
         <v>39</v>
       </c>
       <c r="X23" s="98" t="s">
-        <v>2878</v>
+        <v>2880</v>
       </c>
       <c r="Y23" s="95" t="s">
         <v>2713</v>
@@ -61433,10 +61459,10 @@
         <v>41</v>
       </c>
       <c r="X24" s="98" t="s">
-        <v>2878</v>
+        <v>2880</v>
       </c>
       <c r="Y24" s="95" t="s">
-        <v>2870</v>
+        <v>2872</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -61506,7 +61532,7 @@
         <v>43</v>
       </c>
       <c r="X25" t="s">
-        <v>2879</v>
+        <v>2881</v>
       </c>
       <c r="Y25" s="95" t="s">
         <v>855</v>
@@ -61579,10 +61605,10 @@
         <v>45</v>
       </c>
       <c r="X26" t="s">
-        <v>2879</v>
+        <v>2881</v>
       </c>
       <c r="Y26" s="95" t="s">
-        <v>2880</v>
+        <v>2882</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -61655,7 +61681,7 @@
         <v>47</v>
       </c>
       <c r="X27" s="256" t="s">
-        <v>2881</v>
+        <v>2883</v>
       </c>
       <c r="Y27" s="95" t="s">
         <v>2713</v>
@@ -61728,10 +61754,10 @@
         <v>49</v>
       </c>
       <c r="X28" s="256" t="s">
-        <v>2881</v>
+        <v>2883</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>2870</v>
+        <v>2872</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -61801,7 +61827,7 @@
         <v>50</v>
       </c>
       <c r="X29" s="256" t="s">
-        <v>2882</v>
+        <v>2884</v>
       </c>
       <c r="Y29" s="95" t="s">
         <v>2713</v>
@@ -61874,10 +61900,10 @@
         <v>51</v>
       </c>
       <c r="X30" s="256" t="s">
-        <v>2882</v>
+        <v>2884</v>
       </c>
       <c r="Y30" s="95" t="s">
-        <v>2870</v>
+        <v>2872</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -61947,7 +61973,7 @@
         <v>56</v>
       </c>
       <c r="X31" s="256" t="s">
-        <v>2883</v>
+        <v>2885</v>
       </c>
       <c r="Y31" s="95" t="s">
         <v>472</v>
@@ -62023,7 +62049,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="256" t="s">
-        <v>2884</v>
+        <v>2886</v>
       </c>
       <c r="Y32" t="s">
         <v>1343</v>
@@ -62099,10 +62125,10 @@
         <v>59</v>
       </c>
       <c r="X33" s="256" t="s">
-        <v>2884</v>
+        <v>2886</v>
       </c>
       <c r="Y33" t="s">
-        <v>2885</v>
+        <v>2887</v>
       </c>
       <c r="Z33">
         <v>4</v>
@@ -62112,7 +62138,7 @@
       </c>
       <c r="AC33" s="250"/>
       <c r="AD33" s="251" t="s">
-        <v>2886</v>
+        <v>2888</v>
       </c>
       <c r="AE33" s="252">
         <f>SUM(AE3:AE32)</f>
@@ -62178,10 +62204,10 @@
         <v>60</v>
       </c>
       <c r="X34" s="256" t="s">
-        <v>2884</v>
+        <v>2886</v>
       </c>
       <c r="Y34" t="s">
-        <v>2887</v>
+        <v>2889</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -62249,7 +62275,7 @@
         <v>62</v>
       </c>
       <c r="X35" s="256" t="s">
-        <v>2884</v>
+        <v>2886</v>
       </c>
       <c r="Y35" t="s">
         <v>108</v>
@@ -62320,7 +62346,7 @@
         <v>63</v>
       </c>
       <c r="X36" s="256" t="s">
-        <v>2884</v>
+        <v>2886</v>
       </c>
       <c r="Y36" t="s">
         <v>549</v>
@@ -62391,7 +62417,7 @@
         <v>64</v>
       </c>
       <c r="X37" t="s">
-        <v>2888</v>
+        <v>2890</v>
       </c>
       <c r="Y37" t="s">
         <v>418</v>
@@ -62462,7 +62488,7 @@
         <v>74</v>
       </c>
       <c r="X38" t="s">
-        <v>2888</v>
+        <v>2890</v>
       </c>
       <c r="Y38" s="259" t="s">
         <v>1096</v>
@@ -62533,7 +62559,7 @@
         <v>77</v>
       </c>
       <c r="X39" t="s">
-        <v>2889</v>
+        <v>2891</v>
       </c>
       <c r="Y39" t="s">
         <v>549</v>
@@ -62604,7 +62630,7 @@
         <v>79</v>
       </c>
       <c r="X40" t="s">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="Y40" t="s">
         <v>472</v>
@@ -62675,7 +62701,7 @@
         <v>81</v>
       </c>
       <c r="X41" t="s">
-        <v>2891</v>
+        <v>2893</v>
       </c>
       <c r="Y41" t="s">
         <v>1472</v>
@@ -62746,10 +62772,10 @@
         <v>87</v>
       </c>
       <c r="X42" t="s">
-        <v>2891</v>
+        <v>2893</v>
       </c>
       <c r="Y42" t="s">
-        <v>2892</v>
+        <v>2894</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -62817,7 +62843,7 @@
         <v>93</v>
       </c>
       <c r="X43" t="s">
-        <v>2893</v>
+        <v>2895</v>
       </c>
       <c r="Y43" s="95" t="s">
         <v>2713</v>
@@ -62885,10 +62911,10 @@
         <v>99</v>
       </c>
       <c r="X44" t="s">
-        <v>2893</v>
+        <v>2895</v>
       </c>
       <c r="Y44" s="95" t="s">
-        <v>2870</v>
+        <v>2872</v>
       </c>
       <c r="AA44">
         <v>0</v>
@@ -62935,10 +62961,10 @@
         <v>105</v>
       </c>
       <c r="X45" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y45" t="s">
-        <v>2895</v>
+        <v>2897</v>
       </c>
       <c r="Z45">
         <v>1</v>
@@ -62985,10 +63011,10 @@
         <v/>
       </c>
       <c r="X46" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y46" t="s">
-        <v>2896</v>
+        <v>2898</v>
       </c>
       <c r="Z46">
         <v>1</v>
@@ -63035,10 +63061,10 @@
         <v/>
       </c>
       <c r="X47" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y47" t="s">
-        <v>2897</v>
+        <v>2899</v>
       </c>
       <c r="Z47">
         <v>1</v>
@@ -63085,10 +63111,10 @@
         <v/>
       </c>
       <c r="X48" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y48" t="s">
-        <v>2898</v>
+        <v>2900</v>
       </c>
       <c r="Z48">
         <v>1</v>
@@ -63135,10 +63161,10 @@
         <v/>
       </c>
       <c r="X49" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y49" t="s">
-        <v>2899</v>
+        <v>2901</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -63185,7 +63211,7 @@
         <v/>
       </c>
       <c r="X50" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y50" t="s">
         <v>935</v>
@@ -63235,10 +63261,10 @@
         <v/>
       </c>
       <c r="X51" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y51" t="s">
-        <v>2900</v>
+        <v>2902</v>
       </c>
       <c r="Z51">
         <v>1</v>
@@ -63285,7 +63311,7 @@
         <v/>
       </c>
       <c r="X52" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y52" t="s">
         <v>1343</v>
@@ -63335,10 +63361,10 @@
         <v/>
       </c>
       <c r="X53" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y53" t="s">
-        <v>2901</v>
+        <v>2903</v>
       </c>
       <c r="Z53">
         <v>1</v>
@@ -63385,10 +63411,10 @@
         <v/>
       </c>
       <c r="X54" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y54" t="s">
-        <v>2902</v>
+        <v>2904</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -66148,7 +66174,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1">
       <c r="A1" s="280" t="s">
-        <v>2903</v>
+        <v>2905</v>
       </c>
       <c r="B1" s="280"/>
       <c r="C1" s="280"/>
@@ -66169,15 +66195,15 @@
     <row r="3" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1">
       <c r="A4" s="281" t="s">
-        <v>2904</v>
+        <v>2906</v>
       </c>
       <c r="B4" s="282"/>
       <c r="D4" s="283" t="s">
-        <v>2905</v>
+        <v>2907</v>
       </c>
       <c r="E4" s="284"/>
       <c r="G4" s="125" t="s">
-        <v>2906</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1">
@@ -66186,18 +66212,18 @@
         <v>53</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>2907</v>
+        <v>2909</v>
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
         <v>32</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>2907</v>
+        <v>2909</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="5.0999999999999996" customHeight="1">
@@ -66211,11 +66237,11 @@
     </row>
     <row r="8" spans="1:7" ht="17.25">
       <c r="A8" s="279" t="s">
-        <v>2908</v>
+        <v>2910</v>
       </c>
       <c r="B8" s="279"/>
       <c r="D8" s="279" t="s">
-        <v>2909</v>
+        <v>2911</v>
       </c>
       <c r="E8" s="279"/>
     </row>
@@ -66230,13 +66256,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="108" t="s">
-        <v>2910</v>
+        <v>2912</v>
       </c>
       <c r="D10" s="108" t="s">
-        <v>2911</v>
+        <v>2913</v>
       </c>
       <c r="E10" s="108" t="s">
-        <v>2912</v>
+        <v>2914</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.95" customHeight="1">
@@ -66248,7 +66274,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="109" t="s">
-        <v>2913</v>
+        <v>2915</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66264,7 +66290,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>2914</v>
+        <v>2916</v>
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66280,7 +66306,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="109" t="s">
-        <v>2915</v>
+        <v>2917</v>
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66289,14 +66315,14 @@
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1">
       <c r="A14" s="113" t="s">
-        <v>2916</v>
+        <v>2918</v>
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
         <v>32</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>2917</v>
+        <v>2919</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
@@ -66305,7 +66331,7 @@
     </row>
     <row r="30" spans="1:5" ht="17.25">
       <c r="A30" s="279" t="s">
-        <v>2918</v>
+        <v>2920</v>
       </c>
       <c r="B30" s="279"/>
       <c r="C30" s="279"/>
@@ -66324,16 +66350,16 @@
         <v>6</v>
       </c>
       <c r="B32" s="108" t="s">
-        <v>2919</v>
+        <v>2921</v>
       </c>
       <c r="C32" s="108" t="s">
-        <v>2920</v>
+        <v>2922</v>
       </c>
       <c r="D32" s="108" t="s">
-        <v>2921</v>
+        <v>2923</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>2922</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1">
@@ -66354,7 +66380,7 @@
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.21276595744680851</v>
+        <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1">
@@ -66375,7 +66401,7 @@
       </c>
       <c r="E34" s="120">
         <f t="shared" si="1"/>
-        <v>6.3829787234042548E-2</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="24" customHeight="1">
@@ -66388,15 +66414,15 @@
       </c>
       <c r="C35" s="127">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A35)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="117">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="118">
         <f t="shared" si="1"/>
-        <v>0.10638297872340426</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="24" customHeight="1">
@@ -66417,7 +66443,7 @@
       </c>
       <c r="E36" s="120">
         <f t="shared" si="1"/>
-        <v>2.1276595744680851E-2</v>
+        <v>2.0833333333333332E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1">
@@ -66438,7 +66464,7 @@
       </c>
       <c r="E37" s="118">
         <f t="shared" si="1"/>
-        <v>4.2553191489361701E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1">
@@ -66459,7 +66485,7 @@
       </c>
       <c r="E38" s="120">
         <f t="shared" si="1"/>
-        <v>0.23404255319148937</v>
+        <v>0.22916666666666666</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="24" customHeight="1">
@@ -66480,7 +66506,7 @@
       </c>
       <c r="E39" s="147">
         <f t="shared" si="1"/>
-        <v>8.5106382978723402E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="24" customHeight="1">
@@ -66501,7 +66527,7 @@
       </c>
       <c r="E40" s="158">
         <f>D40/$D$45</f>
-        <v>4.2553191489361701E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="24" customHeight="1">
@@ -66522,12 +66548,12 @@
       </c>
       <c r="E41" s="157">
         <f>D41/$D$45</f>
-        <v>0.14893617021276595</v>
+        <v>0.14583333333333334</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1">
       <c r="A42" s="156" t="s">
-        <v>2923</v>
+        <v>2925</v>
       </c>
       <c r="B42" s="153">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A42)</f>
@@ -66564,12 +66590,12 @@
       </c>
       <c r="E43" s="157">
         <f>D43/$D$45</f>
-        <v>4.2553191489361701E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1">
       <c r="A44" s="148" t="s">
-        <v>2924</v>
+        <v>2926</v>
       </c>
       <c r="B44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,"")</f>
@@ -66590,7 +66616,7 @@
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1">
       <c r="A45" s="113" t="s">
-        <v>2916</v>
+        <v>2918</v>
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
@@ -66598,15 +66624,15 @@
       </c>
       <c r="C45" s="121">
         <f>SUM(C33:C44)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D45" s="121">
         <f>SUM(D33:D44)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E45" s="122">
         <f>SUM(E33:E44)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -66641,163 +66667,163 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2925</v>
+        <v>2927</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2926</v>
+        <v>2928</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2927</v>
+        <v>2929</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2928</v>
+        <v>2930</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2929</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2931</v>
+        <v>2933</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1729</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2932</v>
+        <v>2934</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>2933</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2931</v>
+        <v>2933</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2934</v>
+        <v>2936</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2935</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2931</v>
+        <v>2933</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2932</v>
+        <v>2934</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2936</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2931</v>
+        <v>2933</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>2937</v>
+        <v>2939</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2938</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2931</v>
+        <v>2933</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2939</v>
+        <v>2941</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2940</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2941</v>
+        <v>2943</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2942</v>
+        <v>2944</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2943</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2941</v>
+        <v>2943</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2944</v>
+        <v>2946</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2945</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2946</v>
+        <v>2948</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>457</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2947</v>
+        <v>2949</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2948</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2946</v>
+        <v>2948</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>199</v>
@@ -66806,15 +66832,15 @@
         <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2949</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2930</v>
+        <v>2932</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2946</v>
+        <v>2948</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>364</v>
@@ -66823,7 +66849,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2950</v>
+        <v>2952</v>
       </c>
     </row>
   </sheetData>
@@ -66845,16 +66871,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>2951</v>
+        <v>2953</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>2952</v>
+        <v>2954</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>2843</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1">
@@ -66865,7 +66891,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2953</v>
+        <v>2955</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>2765</v>
@@ -66879,7 +66905,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2954</v>
+        <v>2956</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>2664</v>
@@ -66930,180 +66956,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2925</v>
+        <v>2927</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2926</v>
+        <v>2928</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2927</v>
+        <v>2929</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2928</v>
+        <v>2930</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2929</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2931</v>
+        <v>2933</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2932</v>
+        <v>2934</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2956</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2931</v>
+        <v>2933</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2934</v>
+        <v>2936</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2957</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2931</v>
+        <v>2933</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2937</v>
+        <v>2939</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2958</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2931</v>
+        <v>2933</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>2690</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2959</v>
+        <v>2961</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2960</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2931</v>
+        <v>2933</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2939</v>
+        <v>2941</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2940</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2941</v>
+        <v>2943</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>2711</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2961</v>
+        <v>2963</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2962</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2941</v>
+        <v>2943</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2944</v>
+        <v>2946</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2945</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2941</v>
+        <v>2943</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>2695</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2963</v>
+        <v>2965</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>2964</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2965</v>
+        <v>2967</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2923</v>
+        <v>2925</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>2966</v>
+        <v>2968</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2965</v>
+        <v>2967</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>199</v>
@@ -67112,15 +67138,15 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2949</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2965</v>
+        <v>2967</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>364</v>
@@ -67129,7 +67155,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2950</v>
+        <v>2952</v>
       </c>
     </row>
   </sheetData>
@@ -67148,7 +67174,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
       <c r="A1" s="292" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
       <c r="B1" s="292"/>
       <c r="C1" s="292"/>
@@ -67158,7 +67184,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="293" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
       <c r="B2" s="293"/>
       <c r="C2" s="293"/>
@@ -67171,19 +67197,19 @@
         <v>19</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>2846</v>
+        <v>2848</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>2847</v>
+        <v>2849</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>2970</v>
+        <v>2972</v>
       </c>
       <c r="E4" s="102" t="s">
-        <v>2848</v>
+        <v>2850</v>
       </c>
       <c r="F4" s="102" t="s">
-        <v>2971</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -69465,7 +69491,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="241" t="s">
-        <v>2917</v>
+        <v>2919</v>
       </c>
       <c r="B105" s="242">
         <f>SUM(B5:B100)</f>
@@ -69516,7 +69542,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1">
       <c r="A1" s="285" t="s">
-        <v>2972</v>
+        <v>2974</v>
       </c>
       <c r="B1" s="285"/>
       <c r="C1" s="285"/>
@@ -69528,20 +69554,20 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="130" t="s">
-        <v>2973</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1">
       <c r="A4" s="286" t="s">
-        <v>2974</v>
+        <v>2976</v>
       </c>
       <c r="B4" s="287"/>
       <c r="D4" s="286" t="s">
-        <v>2975</v>
+        <v>2977</v>
       </c>
       <c r="E4" s="287"/>
       <c r="G4" s="286" t="s">
-        <v>2976</v>
+        <v>2978</v>
       </c>
       <c r="H4" s="287"/>
     </row>
@@ -69565,28 +69591,28 @@
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1">
       <c r="A7" s="143" t="s">
-        <v>2977</v>
+        <v>2979</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>2978</v>
+        <v>2980</v>
       </c>
       <c r="C7" s="143" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="143" t="s">
-        <v>2979</v>
+        <v>2981</v>
       </c>
       <c r="E7" s="143" t="s">
-        <v>2980</v>
+        <v>2982</v>
       </c>
       <c r="F7" s="143" t="s">
-        <v>2843</v>
+        <v>2845</v>
       </c>
       <c r="G7" s="143" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="143" t="s">
-        <v>2981</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -69949,14 +69975,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -70161,16 +70185,18 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fe686eaa-0658-4f15-b230-9e46c4d089fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91ce1707-6d34-452b-b217-9734c03e6729" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -70178,5 +70204,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09E963D1-4255-41FD-98AB-5B82B7F67BB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95AF67B-67F3-479D-896A-04A7BBE7C81F}"/>
 </file>
--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5127" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23CB1B71-DF9F-4CF1-87EA-5B7E1DA54506}"/>
+  <xr:revisionPtr revIDLastSave="5138" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53DA33FC-1F23-43D7-A1D6-3ED570BC537E}"/>
   <bookViews>
     <workbookView xWindow="-28770" yWindow="30" windowWidth="28770" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6608" uniqueCount="2985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6614" uniqueCount="2986">
   <si>
     <t>ID</t>
   </si>
@@ -8704,6 +8704,12 @@
     <t>7828/2026</t>
   </si>
   <si>
+    <t>Oficina Temática – SEMAT: Falhas recorrentes em contratações de TI</t>
+  </si>
+  <si>
+    <t>Felipe da Costa Malaquias</t>
+  </si>
+  <si>
     <t>ID Ação</t>
   </si>
   <si>
@@ -8852,9 +8858,6 @@
   </si>
   <si>
     <t>2026-047</t>
-  </si>
-  <si>
-    <t>Felipe da Costa Malaquias</t>
   </si>
   <si>
     <t>2026-048</t>
@@ -13024,7 +13027,7 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -13057,7 +13060,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -58489,16 +58492,32 @@
       <c r="D710" s="218" t="s">
         <v>2844</v>
       </c>
-      <c r="E710" s="219"/>
-      <c r="F710" s="220"/>
-      <c r="G710" s="217"/>
-      <c r="H710" s="221"/>
-      <c r="I710" s="222"/>
-      <c r="J710" s="222"/>
-      <c r="K710" s="218"/>
+      <c r="E710" s="210" t="s">
+        <v>2845</v>
+      </c>
+      <c r="F710" s="220" t="s">
+        <v>62</v>
+      </c>
+      <c r="G710" s="217" t="s">
+        <v>72</v>
+      </c>
+      <c r="H710" s="221" t="s">
+        <v>2816</v>
+      </c>
+      <c r="I710" s="222">
+        <v>46244</v>
+      </c>
+      <c r="J710" s="222">
+        <v>46245</v>
+      </c>
+      <c r="K710" s="218" t="s">
+        <v>35</v>
+      </c>
       <c r="L710" s="223"/>
       <c r="M710" s="214"/>
-      <c r="N710" s="225"/>
+      <c r="N710" s="225">
+        <v>40</v>
+      </c>
       <c r="O710" s="224"/>
       <c r="P710" s="224"/>
       <c r="Q710" s="224"/>
@@ -58506,8 +58525,12 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S710" s="218"/>
-      <c r="T710" s="217"/>
+      <c r="S710" s="218">
+        <v>8</v>
+      </c>
+      <c r="T710" s="259" t="s">
+        <v>2846</v>
+      </c>
     </row>
     <row r="711" spans="1:20" ht="23.25" customHeight="1">
       <c r="A711" s="208" t="str">
@@ -59737,55 +59760,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="96" t="s">
-        <v>2845</v>
+        <v>2847</v>
       </c>
       <c r="C1" s="96" t="s">
-        <v>2846</v>
+        <v>2848</v>
       </c>
       <c r="D1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="96" t="s">
-        <v>2847</v>
+        <v>2849</v>
       </c>
       <c r="F1" s="96" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="96" t="s">
-        <v>2848</v>
+        <v>2850</v>
       </c>
       <c r="H1" s="96" t="s">
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="I1" s="96" t="s">
-        <v>2850</v>
+        <v>2852</v>
       </c>
       <c r="J1" s="96" t="s">
-        <v>2851</v>
+        <v>2853</v>
       </c>
       <c r="L1" s="129" t="s">
-        <v>2852</v>
+        <v>2854</v>
       </c>
       <c r="M1" s="100">
         <v>2026</v>
       </c>
       <c r="U1" s="162" t="s">
-        <v>2853</v>
+        <v>2855</v>
       </c>
       <c r="V1" s="161"/>
       <c r="X1" s="159" t="s">
-        <v>2854</v>
+        <v>2856</v>
       </c>
       <c r="Y1" s="107"/>
       <c r="Z1" s="107"/>
       <c r="AA1" s="107"/>
       <c r="AC1" s="253" t="s">
-        <v>2855</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="2" spans="1:31">
       <c r="A2" s="98" cm="1">
-        <f t="array" ref="A2:J106">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
+        <f t="array" ref="A2:J107">_xlfn.LET(_xlpm.totalRows,MAX(S4:S200),_xlpm.seq,_xlfn.SEQUENCE(_xlpm.totalRows),_xlpm.srcRow,_xlfn.MAP(_xlpm.seq,_xlfn.LAMBDA(_xlpm.s,MATCH(_xlpm.s-1,T4:T200,1))),_xlpm.instrIdx,_xlfn.MAP(_xlpm.seq,_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.s,_xlpm.sr,_xlpm.s-INDEX(T4:T200,_xlpm.sr))),_xlpm.ano,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(L4:L200,_xlpm.sr))),_xlpm.id,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(M4:M200,_xlpm.sr))),_xlpm.status,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(N4:N200,_xlpm.sr))),_xlpm.curso,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(O4:O200,_xlpm.sr))),_xlpm.ch,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(P4:P200,_xlpm.sr)+0)),_xlpm.instrStr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(Q4:Q200,_xlpm.sr))),_xlpm.nInstr,_xlfn.MAP(_xlpm.srcRow,_xlfn.LAMBDA(_xlpm.sr,INDEX(R4:R200,_xlpm.sr)+0)),_xlpm.instrName,_xlfn.MAP(_xlpm.instrStr,_xlpm.instrIdx,_xlfn.LAMBDA(_xlpm.s,_xlpm.idx,TRIM(INDEX(_xlfn.TEXTSPLIT(_xlpm.s,"; "),,_xlpm.idx)))),_xlpm.ovKey,X3:X200&amp;"|"&amp;Y3:Y200,_xlpm.lookupKey,_xlpm.id&amp;"|"&amp;_xlpm.instrName,_xlpm.ovAula,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,Z3:Z200),""))),_xlpm.ovMat,_xlfn.MAP(_xlpm.lookupKey,_xlfn.LAMBDA(_xlpm.k,IFERROR(_xlfn.XLOOKUP(_xlpm.k,_xlpm.ovKey,AA3:AA200),""))),_xlpm.geccAula,_xlfn.MAP(_xlpm.ovAula,_xlpm.ch,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c))),_xlpm.geccMat,_xlfn.MAP(_xlpm.ovMat,_xlpm.ch,_xlpm.nInstr,_xlfn.LAMBDA(_xlpm.ov,_xlpm.c,_xlpm.n,IF(_xlpm.ov&lt;&gt;"",_xlpm.ov+0,_xlpm.c*0.3/_xlpm.n))),_xlpm.geccTotal,_xlpm.geccAula+_xlpm.geccMat,_xlfn.HSTACK(_xlpm.ano,_xlpm.id,_xlpm.status,_xlpm.curso,_xlpm.ch,_xlpm.instrName,_xlpm.nInstr,_xlpm.geccAula,_xlpm.geccMat,_xlpm.geccTotal))</f>
         <v>2026</v>
       </c>
       <c r="B2" s="98" t="str">
@@ -59816,25 +59839,25 @@
         <v>10.4</v>
       </c>
       <c r="X2" s="160" t="s">
-        <v>2845</v>
+        <v>2847</v>
       </c>
       <c r="Y2" s="160" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="160" t="s">
-        <v>2856</v>
+        <v>2858</v>
       </c>
       <c r="AA2" s="160" t="s">
-        <v>2857</v>
+        <v>2859</v>
       </c>
       <c r="AC2" s="254" t="s">
         <v>1</v>
       </c>
       <c r="AD2" s="254" t="s">
-        <v>2858</v>
+        <v>2860</v>
       </c>
       <c r="AE2" s="254" t="s">
-        <v>2859</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -59869,34 +59892,34 @@
         <v>5.2</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>2860</v>
+        <v>2862</v>
       </c>
       <c r="M3" s="19" t="s">
-        <v>2861</v>
+        <v>2863</v>
       </c>
       <c r="N3" s="19" t="s">
-        <v>2862</v>
+        <v>2864</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>2863</v>
+        <v>2865</v>
       </c>
       <c r="P3" s="19" t="s">
-        <v>2864</v>
+        <v>2866</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>2865</v>
+        <v>2867</v>
       </c>
       <c r="R3" s="19" t="s">
-        <v>2866</v>
+        <v>2868</v>
       </c>
       <c r="S3" s="19" t="s">
-        <v>2867</v>
+        <v>2869</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>2868</v>
+        <v>2870</v>
       </c>
       <c r="X3" t="s">
-        <v>2869</v>
+        <v>2871</v>
       </c>
       <c r="Y3" t="s">
         <v>2697</v>
@@ -59949,7 +59972,7 @@
         <v>5.2</v>
       </c>
       <c r="L4" cm="1">
-        <f t="array" ref="L4:Q44">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
+        <f t="array" ref="L4:Q45">_xlfn.LET(_xlpm.src,'Ações InCompany'!A2:T997,_xlpm.sAno,INDEX(_xlpm.src,,2),_xlpm.sMod,INDEX(_xlpm.src,,11),_xlfn._xlws.FILTER(_xlfn.HSTACK(INDEX(_xlpm.src,,2),INDEX(_xlpm.src,,1),INDEX(_xlpm.src,,3),INDEX(_xlpm.src,,5),INDEX(_xlpm.src,,19),INDEX(_xlpm.src,,20)),(_xlpm.sAno=M1)*(_xlpm.sMod="Instrutoria Interna"),""))</f>
         <v>2026</v>
       </c>
       <c r="M4" t="str">
@@ -59976,11 +59999,11 @@
         <v>1</v>
       </c>
       <c r="T4" cm="1">
-        <f t="array" ref="T4:T45">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
+        <f t="array" ref="T4:T46">_xlfn.VSTACK(0,_xlfn._xlws.FILTER(S4:S200,S4:S200&lt;&gt;""))</f>
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>2870</v>
+        <v>2872</v>
       </c>
       <c r="Y4" t="s">
         <v>2697</v>
@@ -60060,7 +60083,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>2871</v>
+        <v>2873</v>
       </c>
       <c r="Y5" t="s">
         <v>2713</v>
@@ -60075,7 +60098,7 @@
         <v>2026</v>
       </c>
       <c r="AD5" s="95" t="s">
-        <v>2872</v>
+        <v>2874</v>
       </c>
       <c r="AE5" s="249">
         <v>16</v>
@@ -60140,10 +60163,10 @@
         <v>6</v>
       </c>
       <c r="X6" t="s">
-        <v>2871</v>
+        <v>2873</v>
       </c>
       <c r="Y6" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="Z6">
         <v>1</v>
@@ -60155,7 +60178,7 @@
         <v>2026</v>
       </c>
       <c r="AD6" s="95" t="s">
-        <v>2874</v>
+        <v>2876</v>
       </c>
       <c r="AE6" s="249">
         <v>16</v>
@@ -60220,7 +60243,7 @@
         <v>8</v>
       </c>
       <c r="X7" s="98" t="s">
-        <v>2875</v>
+        <v>2877</v>
       </c>
       <c r="Y7" t="s">
         <v>2697</v>
@@ -60300,7 +60323,7 @@
         <v>9</v>
       </c>
       <c r="X8" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="Y8" s="95" t="s">
         <v>1343</v>
@@ -60373,7 +60396,7 @@
         <v>11</v>
       </c>
       <c r="X9" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="Y9" s="95" t="s">
         <v>1023</v>
@@ -60446,7 +60469,7 @@
         <v>12</v>
       </c>
       <c r="X10" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="Y10" s="95" t="s">
         <v>1367</v>
@@ -60519,10 +60542,10 @@
         <v>14</v>
       </c>
       <c r="X11" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="Y11" s="95" t="s">
-        <v>2877</v>
+        <v>2879</v>
       </c>
       <c r="AA11">
         <v>1.2</v>
@@ -60592,10 +60615,10 @@
         <v>15</v>
       </c>
       <c r="X12" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>2878</v>
+        <v>2880</v>
       </c>
       <c r="AA12">
         <v>1.2</v>
@@ -60665,7 +60688,7 @@
         <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>2879</v>
+        <v>2881</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>1343</v>
@@ -60738,7 +60761,7 @@
         <v>18</v>
       </c>
       <c r="X14" t="s">
-        <v>2879</v>
+        <v>2881</v>
       </c>
       <c r="Y14" s="95" t="s">
         <v>1023</v>
@@ -60811,7 +60834,7 @@
         <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>2879</v>
+        <v>2881</v>
       </c>
       <c r="Y15" s="95" t="s">
         <v>1367</v>
@@ -60884,10 +60907,10 @@
         <v>22</v>
       </c>
       <c r="X16" t="s">
+        <v>2881</v>
+      </c>
+      <c r="Y16" s="95" t="s">
         <v>2879</v>
-      </c>
-      <c r="Y16" s="95" t="s">
-        <v>2877</v>
       </c>
       <c r="AA16">
         <v>1.2</v>
@@ -60957,10 +60980,10 @@
         <v>23</v>
       </c>
       <c r="X17" t="s">
-        <v>2879</v>
+        <v>2881</v>
       </c>
       <c r="Y17" s="95" t="s">
-        <v>2878</v>
+        <v>2880</v>
       </c>
       <c r="AA17">
         <v>1.2</v>
@@ -61030,7 +61053,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>2880</v>
+        <v>2882</v>
       </c>
       <c r="Y18" s="95" t="s">
         <v>1343</v>
@@ -61103,7 +61126,7 @@
         <v>33</v>
       </c>
       <c r="X19" t="s">
-        <v>2880</v>
+        <v>2882</v>
       </c>
       <c r="Y19" s="95" t="s">
         <v>1023</v>
@@ -61176,7 +61199,7 @@
         <v>34</v>
       </c>
       <c r="X20" t="s">
-        <v>2880</v>
+        <v>2882</v>
       </c>
       <c r="Y20" s="95" t="s">
         <v>1367</v>
@@ -61249,10 +61272,10 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>2880</v>
+        <v>2882</v>
       </c>
       <c r="Y21" s="95" t="s">
-        <v>2877</v>
+        <v>2879</v>
       </c>
       <c r="AA21">
         <v>1.2</v>
@@ -61322,10 +61345,10 @@
         <v>38</v>
       </c>
       <c r="X22" t="s">
+        <v>2882</v>
+      </c>
+      <c r="Y22" s="95" t="s">
         <v>2880</v>
-      </c>
-      <c r="Y22" s="95" t="s">
-        <v>2878</v>
       </c>
       <c r="AA22">
         <v>1.2</v>
@@ -61395,7 +61418,7 @@
         <v>39</v>
       </c>
       <c r="X23" s="98" t="s">
-        <v>2881</v>
+        <v>2883</v>
       </c>
       <c r="Y23" s="95" t="s">
         <v>2713</v>
@@ -61468,10 +61491,10 @@
         <v>41</v>
       </c>
       <c r="X24" s="98" t="s">
-        <v>2881</v>
+        <v>2883</v>
       </c>
       <c r="Y24" s="95" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -61541,7 +61564,7 @@
         <v>43</v>
       </c>
       <c r="X25" t="s">
-        <v>2882</v>
+        <v>2884</v>
       </c>
       <c r="Y25" s="95" t="s">
         <v>855</v>
@@ -61614,10 +61637,10 @@
         <v>45</v>
       </c>
       <c r="X26" t="s">
-        <v>2882</v>
+        <v>2884</v>
       </c>
       <c r="Y26" s="95" t="s">
-        <v>2883</v>
+        <v>2885</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -61690,7 +61713,7 @@
         <v>47</v>
       </c>
       <c r="X27" s="256" t="s">
-        <v>2884</v>
+        <v>2886</v>
       </c>
       <c r="Y27" s="95" t="s">
         <v>2713</v>
@@ -61763,10 +61786,10 @@
         <v>49</v>
       </c>
       <c r="X28" s="256" t="s">
-        <v>2884</v>
+        <v>2886</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -61836,7 +61859,7 @@
         <v>50</v>
       </c>
       <c r="X29" s="256" t="s">
-        <v>2885</v>
+        <v>2887</v>
       </c>
       <c r="Y29" s="95" t="s">
         <v>2713</v>
@@ -61909,10 +61932,10 @@
         <v>51</v>
       </c>
       <c r="X30" s="256" t="s">
-        <v>2885</v>
+        <v>2887</v>
       </c>
       <c r="Y30" s="95" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -61982,7 +62005,7 @@
         <v>56</v>
       </c>
       <c r="X31" s="256" t="s">
-        <v>2886</v>
+        <v>2888</v>
       </c>
       <c r="Y31" s="95" t="s">
         <v>472</v>
@@ -62058,7 +62081,7 @@
         <v>58</v>
       </c>
       <c r="X32" s="256" t="s">
-        <v>2887</v>
+        <v>2889</v>
       </c>
       <c r="Y32" t="s">
         <v>1343</v>
@@ -62134,10 +62157,10 @@
         <v>59</v>
       </c>
       <c r="X33" s="256" t="s">
-        <v>2887</v>
+        <v>2889</v>
       </c>
       <c r="Y33" t="s">
-        <v>2888</v>
+        <v>2890</v>
       </c>
       <c r="Z33">
         <v>4</v>
@@ -62147,7 +62170,7 @@
       </c>
       <c r="AC33" s="250"/>
       <c r="AD33" s="251" t="s">
-        <v>2889</v>
+        <v>2891</v>
       </c>
       <c r="AE33" s="252">
         <f>SUM(AE3:AE32)</f>
@@ -62213,10 +62236,10 @@
         <v>60</v>
       </c>
       <c r="X34" s="256" t="s">
-        <v>2887</v>
+        <v>2889</v>
       </c>
       <c r="Y34" t="s">
-        <v>2890</v>
+        <v>2892</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -62284,7 +62307,7 @@
         <v>62</v>
       </c>
       <c r="X35" s="256" t="s">
-        <v>2887</v>
+        <v>2889</v>
       </c>
       <c r="Y35" t="s">
         <v>108</v>
@@ -62355,7 +62378,7 @@
         <v>63</v>
       </c>
       <c r="X36" s="256" t="s">
-        <v>2887</v>
+        <v>2889</v>
       </c>
       <c r="Y36" t="s">
         <v>549</v>
@@ -62426,7 +62449,7 @@
         <v>64</v>
       </c>
       <c r="X37" t="s">
-        <v>2891</v>
+        <v>2893</v>
       </c>
       <c r="Y37" t="s">
         <v>418</v>
@@ -62497,7 +62520,7 @@
         <v>74</v>
       </c>
       <c r="X38" t="s">
-        <v>2891</v>
+        <v>2893</v>
       </c>
       <c r="Y38" s="259" t="s">
         <v>1096</v>
@@ -62568,7 +62591,7 @@
         <v>77</v>
       </c>
       <c r="X39" t="s">
-        <v>2892</v>
+        <v>2894</v>
       </c>
       <c r="Y39" t="s">
         <v>549</v>
@@ -62639,7 +62662,7 @@
         <v>79</v>
       </c>
       <c r="X40" t="s">
-        <v>2893</v>
+        <v>2895</v>
       </c>
       <c r="Y40" t="s">
         <v>472</v>
@@ -62710,7 +62733,7 @@
         <v>81</v>
       </c>
       <c r="X41" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y41" t="s">
         <v>1472</v>
@@ -62781,10 +62804,10 @@
         <v>87</v>
       </c>
       <c r="X42" t="s">
-        <v>2894</v>
+        <v>2896</v>
       </c>
       <c r="Y42" t="s">
-        <v>2895</v>
+        <v>2846</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -62852,7 +62875,7 @@
         <v>93</v>
       </c>
       <c r="X43" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="Y43" s="95" t="s">
         <v>2713</v>
@@ -62920,10 +62943,10 @@
         <v>99</v>
       </c>
       <c r="X44" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="Y44" s="95" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="AA44">
         <v>0</v>
@@ -62960,20 +62983,38 @@
       <c r="J45">
         <v>15.6</v>
       </c>
-      <c r="R45" t="str">
-        <v/>
-      </c>
-      <c r="S45" t="str">
-        <v/>
+      <c r="L45">
+        <v>2026</v>
+      </c>
+      <c r="M45" t="str">
+        <v>2026-054</v>
+      </c>
+      <c r="N45" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="O45" t="str">
+        <v>Oficina Temática – SEMAT: Falhas recorrentes em contratações de TI</v>
+      </c>
+      <c r="P45">
+        <v>8</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>Felipe da Costa Malaquias</v>
+      </c>
+      <c r="R45">
+        <v>1</v>
+      </c>
+      <c r="S45">
+        <v>106</v>
       </c>
       <c r="T45">
         <v>105</v>
       </c>
       <c r="X45" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Y45" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="Z45">
         <v>1</v>
@@ -63019,11 +63060,14 @@
       <c r="S46" t="str">
         <v/>
       </c>
+      <c r="T46">
+        <v>106</v>
+      </c>
       <c r="X46" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Y46" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="Z46">
         <v>1</v>
@@ -63070,10 +63114,10 @@
         <v/>
       </c>
       <c r="X47" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Y47" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="Z47">
         <v>1</v>
@@ -63120,10 +63164,10 @@
         <v/>
       </c>
       <c r="X48" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Y48" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="Z48">
         <v>1</v>
@@ -63170,10 +63214,10 @@
         <v/>
       </c>
       <c r="X49" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Y49" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -63220,7 +63264,7 @@
         <v/>
       </c>
       <c r="X50" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Y50" t="s">
         <v>935</v>
@@ -63270,10 +63314,10 @@
         <v/>
       </c>
       <c r="X51" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Y51" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="Z51">
         <v>1</v>
@@ -63320,7 +63364,7 @@
         <v/>
       </c>
       <c r="X52" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Y52" t="s">
         <v>1343</v>
@@ -63370,10 +63414,10 @@
         <v/>
       </c>
       <c r="X53" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Y53" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="Z53">
         <v>1</v>
@@ -63420,10 +63464,10 @@
         <v/>
       </c>
       <c r="X54" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="Y54" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -65409,6 +65453,36 @@
       </c>
     </row>
     <row r="107" spans="1:19">
+      <c r="A107">
+        <v>2026</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2026-054</v>
+      </c>
+      <c r="C107" t="str">
+        <v>A realizar</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Oficina Temática – SEMAT: Falhas recorrentes em contratações de TI</v>
+      </c>
+      <c r="E107">
+        <v>8</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Felipe da Costa Malaquias</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>8</v>
+      </c>
+      <c r="I107">
+        <v>2.4</v>
+      </c>
+      <c r="J107">
+        <v>10.4</v>
+      </c>
       <c r="R107" t="str">
         <v/>
       </c>
@@ -66183,7 +66257,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="50.1" customHeight="1">
       <c r="A1" s="280" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="B1" s="280"/>
       <c r="C1" s="280"/>
@@ -66204,15 +66278,15 @@
     <row r="3" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:7" ht="24.95" customHeight="1">
       <c r="A4" s="281" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="B4" s="282"/>
       <c r="D4" s="283" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="E4" s="284"/>
       <c r="G4" s="125" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="54.95" customHeight="1" thickBot="1">
@@ -66221,14 +66295,14 @@
         <v>54</v>
       </c>
       <c r="B5" s="116" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="D5" s="123">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
         <v>32</v>
       </c>
       <c r="E5" s="124" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="G5" s="126">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar")</f>
@@ -66246,11 +66320,11 @@
     </row>
     <row r="8" spans="1:7" ht="17.25">
       <c r="A8" s="279" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="B8" s="279"/>
       <c r="D8" s="279" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="E8" s="279"/>
     </row>
@@ -66265,13 +66339,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="108" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="D10" s="108" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="E10" s="108" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.95" customHeight="1">
@@ -66283,7 +66357,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="109" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="E11" s="110">
         <f>SUMIFS('Ações InCompany'!O:O,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66299,7 +66373,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="111" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66315,7 +66389,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="109" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
@@ -66324,14 +66398,14 @@
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1">
       <c r="A14" s="113" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B14" s="114">
         <f>SUM(B11:B13)</f>
         <v>32</v>
       </c>
       <c r="D14" s="113" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
@@ -66340,7 +66414,7 @@
     </row>
     <row r="30" spans="1:5" ht="17.25">
       <c r="A30" s="279" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="B30" s="279"/>
       <c r="C30" s="279"/>
@@ -66359,16 +66433,16 @@
         <v>6</v>
       </c>
       <c r="B32" s="108" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="C32" s="108" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="D32" s="108" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="E32" s="108" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1">
@@ -66381,15 +66455,15 @@
       </c>
       <c r="C33" s="127">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,A33)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" s="117">
         <f t="shared" ref="D33:D44" si="0">B33+C33</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E33" s="118">
         <f t="shared" ref="E33:E44" si="1">D33/$D$45</f>
-        <v>0.20833333333333334</v>
+        <v>0.22916666666666666</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1">
@@ -66562,7 +66636,7 @@
     </row>
     <row r="42" spans="1:5" ht="24" customHeight="1">
       <c r="A42" s="156" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B42" s="153">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,A42)</f>
@@ -66604,7 +66678,7 @@
     </row>
     <row r="44" spans="1:5" ht="24" customHeight="1">
       <c r="A44" s="148" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado",'Ações InCompany'!G:G,"")</f>
@@ -66612,20 +66686,20 @@
       </c>
       <c r="C44" s="149">
         <f>COUNTIFS('Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"A realizar",'Ações InCompany'!G:G,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="149">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="150">
         <f t="shared" si="1"/>
-        <v>2.0833333333333332E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="24" customHeight="1">
       <c r="A45" s="113" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="B45" s="121">
         <f>SUM(B33:B44)</f>
@@ -66676,163 +66750,163 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1729</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>457</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>199</v>
@@ -66841,15 +66915,15 @@
         <v>23</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>364</v>
@@ -66858,7 +66932,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
     </row>
   </sheetData>
@@ -66880,16 +66954,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>2846</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1">
@@ -66900,7 +66974,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>2765</v>
@@ -66914,7 +66988,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>2664</v>
@@ -66965,180 +67039,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>2690</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>2727</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>2711</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>2695</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>199</v>
@@ -67147,15 +67221,15 @@
         <v>23</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>364</v>
@@ -67164,7 +67238,7 @@
         <v>23</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
     </row>
   </sheetData>
@@ -67183,7 +67257,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
       <c r="A1" s="292" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="B1" s="292"/>
       <c r="C1" s="292"/>
@@ -67193,7 +67267,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="293" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="B2" s="293"/>
       <c r="C2" s="293"/>
@@ -67206,19 +67280,19 @@
         <v>19</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>2850</v>
+        <v>2852</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="E4" s="102" t="s">
-        <v>2851</v>
+        <v>2853</v>
       </c>
       <c r="F4" s="102" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -67532,11 +67606,11 @@
       </c>
       <c r="B17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!H$2:H$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C17" s="103">
         <f>IF($A17="","",SUMIFS('GECC 2026'!I$2:I$200,'GECC 2026'!F$2:F$200,$A17))</f>
-        <v>34.9</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D17" s="255">
         <f>IF($A17="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
@@ -67544,11 +67618,11 @@
       </c>
       <c r="E17" s="240">
         <f>IF($A17="","",SUMIFS('GECC 2026'!J$2:J$200,'GECC 2026'!F$2:F$200,$A17)+SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A17))</f>
-        <v>34.9</v>
+        <v>45.3</v>
       </c>
       <c r="F17" s="101">
         <f>IF($A17="","",COUNTIFS('GECC 2026'!F$2:F$200,$A17))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -69500,15 +69574,15 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="241" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="B105" s="242">
         <f>SUM(B5:B100)</f>
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="C105" s="242">
         <f>SUM(C5:C100)</f>
-        <v>380.10000000000008</v>
+        <v>382.50000000000006</v>
       </c>
       <c r="D105" s="255">
         <f>IF($A105="","",SUMIFS('GECC 2026'!$AE$3:$AE$32,'GECC 2026'!$AD$3:$AD$32,$A105))</f>
@@ -69520,7 +69594,7 @@
       </c>
       <c r="F105" s="243">
         <f>SUM(F5:F100)</f>
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -69551,7 +69625,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="35.1" customHeight="1">
       <c r="A1" s="285" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="B1" s="285"/>
       <c r="C1" s="285"/>
@@ -69563,20 +69637,20 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="130" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21.95" customHeight="1">
       <c r="A4" s="286" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="B4" s="287"/>
       <c r="D4" s="286" t="s">
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="E4" s="287"/>
       <c r="G4" s="286" t="s">
-        <v>2979</v>
+        <v>2980</v>
       </c>
       <c r="H4" s="287"/>
     </row>
@@ -69600,28 +69674,28 @@
     <row r="6" spans="1:8" ht="9.9499999999999993" customHeight="1"/>
     <row r="7" spans="1:8" ht="24.95" customHeight="1" thickBot="1">
       <c r="A7" s="143" t="s">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="B7" s="143" t="s">
-        <v>2981</v>
+        <v>2982</v>
       </c>
       <c r="C7" s="143" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="143" t="s">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="E7" s="143" t="s">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="F7" s="143" t="s">
-        <v>2846</v>
+        <v>2848</v>
       </c>
       <c r="G7" s="143" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="143" t="s">
-        <v>2984</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5139" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19D3B452-1531-44B7-84EA-4B62199995CA}"/>
+  <xr:revisionPtr revIDLastSave="5141" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99F8EDAA-FF9A-4C95-9C2C-341AE1FB9A74}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12577,10 +12577,10 @@
                   <c:v>502</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>447</c:v>
+                  <c:v>561</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>370</c:v>
+                  <c:v>411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -56967,11 +56967,15 @@
       <c r="O682" s="185">
         <v>41</v>
       </c>
-      <c r="P682" s="185"/>
-      <c r="Q682" s="185"/>
+      <c r="P682" s="185">
+        <v>114</v>
+      </c>
+      <c r="Q682" s="185">
+        <v>41</v>
+      </c>
       <c r="R682" s="185">
         <f t="shared" si="13"/>
-        <v>41</v>
+        <v>196</v>
       </c>
       <c r="S682" s="180">
         <v>14</v>
@@ -66383,7 +66387,7 @@
       </c>
       <c r="E12" s="112">
         <f>SUMIFS('Ações InCompany'!P:P,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>447</v>
+        <v>561</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -66399,7 +66403,7 @@
       </c>
       <c r="E13" s="110">
         <f>SUMIFS('Ações InCompany'!Q:Q,'Ações InCompany'!B:B,2026,'Ações InCompany'!C:C,"Realizado")</f>
-        <v>370</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -66415,7 +66419,7 @@
       </c>
       <c r="E14" s="114">
         <f>SUM(E11:E13)</f>
-        <v>1319</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
@@ -69668,12 +69672,12 @@
       <c r="B5" s="292"/>
       <c r="D5" s="291">
         <f>SUM(H8:H100)</f>
-        <v>1607</v>
+        <v>1762</v>
       </c>
       <c r="E5" s="292"/>
       <c r="G5" s="291">
         <f>IFERROR(ROUND(D5/A5,0),"-")</f>
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="H5" s="292"/>
     </row>
@@ -69989,7 +69993,7 @@
         <v>Jurisdicionados</v>
       </c>
       <c r="H18" s="139">
-        <v>41</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5141" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99F8EDAA-FF9A-4C95-9C2C-341AE1FB9A74}"/>
+  <xr:revisionPtr revIDLastSave="5142" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88EF525E-2353-425D-9E12-72A4CC755B57}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -59757,7 +59757,8 @@
   <cols>
     <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" customWidth="1"/>
-    <col min="4" max="11" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" customWidth="1"/>
+    <col min="5" max="11" width="9.140625" customWidth="1"/>
     <col min="12" max="20" width="9.140625" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="21" max="21" width="9.140625" customWidth="1" collapsed="1"/>
     <col min="22" max="22" width="9.140625" customWidth="1"/>

--- a/planilhao.xlsx
+++ b/planilhao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcdf.sharepoint.com/sites/SAED/Shared Documents/General/SAED/Controles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5142" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88EF525E-2353-425D-9E12-72A4CC755B57}"/>
+  <xr:revisionPtr revIDLastSave="5144" documentId="13_ncr:1_{C887EC22-7CD1-4717-84BE-7303F42C5C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1AB2998-16E1-4308-A31C-F5AE11C59BD3}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ações InCompany" sheetId="3" r:id="rId1"/>
@@ -28,68 +28,68 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 41" guid="{CA3FE984-959D-4FD1-AD51-F273057287D0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 40" guid="{32D42168-6533-486B-BA4F-1FCBEE1D5E70}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 43" guid="{983434C3-FA2A-4410-B75A-EB842981FB7E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 42" guid="{66204134-7843-4E4D-9132-12589B1C9904}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 45" guid="{37A81383-EB82-4415-9CA7-3B544A1BA6DF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 44" guid="{466B00F4-CD06-4459-9EAD-5E099599461D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 47" guid="{B3051128-E594-4E84-A90F-3E0AA1920164}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 46" guid="{426752F7-EFAA-494A-8C44-3FE740F51102}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 49" guid="{888656D7-51D7-4D86-82B1-69398E74949E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 48" guid="{437C4520-960F-4EE8-BC29-5EAC5035FDE9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{34EB6BDD-DB10-46C3-8070-38A1FF20F467}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{DC0F290D-0110-4230-A92A-0C9FF5FA3573}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{69BC16F3-55B0-4A0A-9007-3B0C4D012204}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 7" guid="{E936EEA7-993F-4552-BBDF-E1DB0091DFDE}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{6A040256-BBC3-4938-A5D6-D77105714F23}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{1C752AA4-ECD6-4155-AAB6-DB036719A0D6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 4" guid="{091F3115-1E32-40D6-93A0-F16A7E814F96}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 30" guid="{2AB5F1EE-8485-44BA-A278-7AE3DE9CF145}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 32" guid="{265C295C-DFB6-4951-B01D-86C18934578C}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 31" guid="{678EC2BA-6745-461E-BAC1-D09F77FA1062}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 34" guid="{C7C27644-1A5D-4074-B300-764545BFC964}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 33" guid="{0C325FD1-5773-4650-8B0D-3332A38760DC}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 36" guid="{DA4468DA-23DF-4CE6-A7A1-D96801F812A5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 35" guid="{BD49A265-64CA-4E25-B77B-BEA5B216E8B0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 38" guid="{6F970FA6-35FA-43B5-8000-ED45D53ABBFB}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 37" guid="{AB062F27-A6C8-47F1-BE53-0FF9CA1DEF53}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 39" guid="{AA5A0339-5E84-4A56-8746-33FE6401E32F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 19" guid="{F8DFD977-D486-42A2-ADDC-71E97C40849F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 61" guid="{02C55D31-8E27-44A2-A753-221185C3D450}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 60" guid="{3A0B7064-EFB6-42D3-AA59-F49B2C2E28A3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 62" guid="{BF3829F5-7BD2-40A9-9D59-6FA51DE0B5DA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 21" guid="{A3242535-E588-41A5-A488-2E120680CF6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 20" guid="{70652B29-1ABA-485A-9A80-A46DCDFDCA82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 23" guid="{A1C80D12-5F51-43D3-B26D-C4E8E80E8CF2}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 22" guid="{371F802A-A094-48E0-BF99-0747C34D37B9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 25" guid="{743E0231-3395-43B3-ADCA-F3A128F1B83A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 9" guid="{2AF3BD90-56F5-45E9-AAA2-03E540B72567}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 24" guid="{9A493B68-EB00-440B-8491-378C02F67A40}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 8" guid="{7F93445C-3064-44FB-ABC5-E30DCF77756E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 27" guid="{23C9FC25-18F4-47EF-A3B5-759DEC27F9E9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 26" guid="{3B6786E1-C731-4815-9553-455D14481DD3}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 29" guid="{B5CEFD59-C042-4547-AAFF-F62EC921EEC6}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 28" guid="{1AB13F6B-0D74-43EC-B774-8B52A94E0814}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 50" guid="{5480ECB2-55D1-41C0-8514-F0684F861D24}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 52" guid="{560766DC-06F5-422D-B190-641D8FE5A38D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 51" guid="{0F15AC02-A38D-4E8A-8C4B-DD7F2868099F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 54" guid="{FB245C5C-9A8F-416D-A134-0975CF96E595}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 10" guid="{633FA869-BC39-409D-BF13-F2C3CBB9EA93}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 53" guid="{2BB93E5B-65F1-4C09-BB9E-66343F5B3E82}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 56" guid="{1105711C-AABE-4812-8827-ED6089DCF11E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 12" guid="{19CACD21-710C-4D14-9ACE-063162C7120B}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 55" guid="{D2A89341-BB3B-405B-B324-3BE49BB6E042}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 11" guid="{0904EB7B-8DCA-4D50-AD8B-0A671CE637AF}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 58" guid="{DA1621F1-9CA5-43AE-9A42-AC9D36F85B7D}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 14" guid="{ED877901-4C49-488E-89E7-42CF1935CA6E}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 13" guid="{DF0241CF-B7E5-4FA7-B0C8-FA54D26D77D7}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 57" guid="{6BA1C58C-C21F-47F7-B022-0FEA98904E5F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 16" guid="{9C7682D3-C31F-4FE6-8766-BC418D960F41}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 59" guid="{B2B68F91-0ADB-423D-BEF9-757DCA540FDD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 15" guid="{DDC390A9-8BCC-4E1B-8EE8-FEFD20C963E8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 18" guid="{990EC2BE-89D2-41CF-8152-E21202B6F8D8}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 17" guid="{77C5030A-63E1-4109-A4D5-32A3FB7E122A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -15028,10 +15028,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://